--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ED03511-CE5B-4E29-BEF8-E09342D97FCC}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56BA558B-4A3B-40BE-B112-453F7FF56BB1}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3822" uniqueCount="2218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3834" uniqueCount="2229">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8898,9 +8898,6 @@
   </si>
   <si>
     <t>勢</t>
-  </si>
-  <si>
-    <t>兆</t>
   </si>
   <si>
     <t>ゾ</t>
@@ -9226,12 +9223,59 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>卋</t>
+  </si>
+  <si>
+    <t>像/王?</t>
+    <rPh sb="0" eb="1">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凭</t>
+  </si>
+  <si>
+    <t>力</t>
+    <rPh sb="0" eb="1">
+      <t>チカラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>果</t>
+  </si>
+  <si>
+    <t>剸</t>
+  </si>
+  <si>
+    <t>文?</t>
+  </si>
+  <si>
+    <t>兆?</t>
+  </si>
+  <si>
+    <t>凾</t>
+  </si>
+  <si>
+    <t>剑</t>
+  </si>
+  <si>
+    <t>流?</t>
+  </si>
+  <si>
+    <t>交?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9391,6 +9435,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Underground"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -9485,7 +9536,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9591,10 +9642,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -9686,6 +9740,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10005,7 +10063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:C306"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -10013,7 +10071,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -10258,7 +10316,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="1" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -10370,7 +10428,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="C46">
         <v>43</v>
@@ -10514,7 +10572,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" s="1" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="C64">
         <v>61</v>
@@ -10561,7 +10619,7 @@
       </c>
     </row>
     <row r="70" spans="2:3">
-      <c r="B70" s="37" t="s">
+      <c r="B70" s="1" t="s">
         <v>1771</v>
       </c>
       <c r="C70">
@@ -10586,7 +10644,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C73" t="s">
         <v>1777</v>
@@ -10666,7 +10724,7 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="C83" t="s">
         <v>1795</v>
@@ -10682,7 +10740,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="1" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C85" t="s">
         <v>1798</v>
@@ -10690,7 +10748,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="1" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C86" t="s">
         <v>1799</v>
@@ -10698,7 +10756,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="1" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="C87" t="s">
         <v>990</v>
@@ -10722,7 +10780,7 @@
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C90" t="s">
         <v>1803</v>
@@ -10738,7 +10796,7 @@
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C92" t="s">
         <v>827</v>
@@ -10770,7 +10828,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" s="1" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="C96" t="s">
         <v>1812</v>
@@ -10802,7 +10860,7 @@
     </row>
     <row r="100" spans="2:3">
       <c r="B100" s="1" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C100" t="s">
         <v>832</v>
@@ -10818,7 +10876,7 @@
     </row>
     <row r="102" spans="2:3">
       <c r="B102" s="1" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="C102" t="s">
         <v>1820</v>
@@ -10826,7 +10884,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" s="1" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="C103" t="s">
         <v>1821</v>
@@ -10842,7 +10900,7 @@
     </row>
     <row r="105" spans="2:3">
       <c r="B105" s="1" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="C105" t="s">
         <v>1824</v>
@@ -10866,7 +10924,7 @@
     </row>
     <row r="108" spans="2:3">
       <c r="B108" s="1" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="C108" t="s">
         <v>1828</v>
@@ -10874,7 +10932,7 @@
     </row>
     <row r="109" spans="2:3">
       <c r="B109" s="1" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="C109" t="s">
         <v>1829</v>
@@ -10882,7 +10940,7 @@
     </row>
     <row r="110" spans="2:3">
       <c r="B110" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="C110" t="s">
         <v>1830</v>
@@ -10898,7 +10956,7 @@
     </row>
     <row r="112" spans="2:3">
       <c r="B112" s="1" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="C112" t="s">
         <v>1833</v>
@@ -10914,7 +10972,7 @@
     </row>
     <row r="114" spans="2:3">
       <c r="B114" s="1" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C114" t="s">
         <v>1836</v>
@@ -10922,7 +10980,7 @@
     </row>
     <row r="115" spans="2:3">
       <c r="B115" s="1" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="C115" t="s">
         <v>1837</v>
@@ -10930,7 +10988,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" s="1" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="C116" t="s">
         <v>1838</v>
@@ -10946,7 +11004,7 @@
     </row>
     <row r="118" spans="2:3">
       <c r="B118" s="1" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="C118" t="s">
         <v>1840</v>
@@ -10962,7 +11020,7 @@
     </row>
     <row r="120" spans="2:3">
       <c r="B120" s="1" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C120" t="s">
         <v>1843</v>
@@ -10978,7 +11036,7 @@
     </row>
     <row r="122" spans="2:3">
       <c r="B122" s="1" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="C122" t="s">
         <v>1846</v>
@@ -10986,7 +11044,7 @@
     </row>
     <row r="123" spans="2:3">
       <c r="B123" s="1" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="C123" t="s">
         <v>1847</v>
@@ -10994,7 +11052,7 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" s="1" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C124" t="s">
         <v>1848</v>
@@ -11002,7 +11060,7 @@
     </row>
     <row r="125" spans="2:3">
       <c r="B125" s="1" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="C125" t="s">
         <v>1849</v>
@@ -11034,7 +11092,7 @@
     </row>
     <row r="129" spans="2:3">
       <c r="B129" s="1" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="C129" t="s">
         <v>1856</v>
@@ -11058,7 +11116,7 @@
     </row>
     <row r="132" spans="2:3">
       <c r="B132" s="1" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="C132" t="s">
         <v>1860</v>
@@ -11074,7 +11132,7 @@
     </row>
     <row r="134" spans="2:3">
       <c r="B134" s="1" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C134" t="s">
         <v>1862</v>
@@ -11082,7 +11140,7 @@
     </row>
     <row r="135" spans="2:3">
       <c r="B135" s="1" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="C135" t="s">
         <v>1863</v>
@@ -11090,7 +11148,7 @@
     </row>
     <row r="136" spans="2:3">
       <c r="B136" s="1" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="C136" t="s">
         <v>1864</v>
@@ -11138,7 +11196,7 @@
     </row>
     <row r="142" spans="2:3">
       <c r="B142" s="1" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C142" t="s">
         <v>1875</v>
@@ -11194,7 +11252,7 @@
     </row>
     <row r="149" spans="2:3">
       <c r="B149" s="1" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="C149" t="s">
         <v>1888</v>
@@ -11218,7 +11276,7 @@
     </row>
     <row r="152" spans="2:3">
       <c r="B152" s="1" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="C152" t="s">
         <v>1893</v>
@@ -11226,7 +11284,7 @@
     </row>
     <row r="153" spans="2:3">
       <c r="B153" s="1" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="C153" t="s">
         <v>1894</v>
@@ -11258,7 +11316,7 @@
     </row>
     <row r="157" spans="2:3">
       <c r="B157" s="1" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="C157" t="s">
         <v>1900</v>
@@ -11298,7 +11356,7 @@
     </row>
     <row r="162" spans="2:3">
       <c r="B162" s="1" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="C162" t="s">
         <v>1909</v>
@@ -11322,7 +11380,7 @@
     </row>
     <row r="165" spans="2:3">
       <c r="B165" s="1" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="C165" t="s">
         <v>1914</v>
@@ -11338,7 +11396,7 @@
     </row>
     <row r="167" spans="2:3">
       <c r="B167" s="1" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="C167" t="s">
         <v>1917</v>
@@ -11386,7 +11444,7 @@
     </row>
     <row r="173" spans="2:3">
       <c r="B173" s="1" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="C173" t="s">
         <v>1927</v>
@@ -11426,7 +11484,7 @@
     </row>
     <row r="178" spans="2:3">
       <c r="B178" s="1" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C178" t="s">
         <v>1935</v>
@@ -11466,7 +11524,7 @@
     </row>
     <row r="183" spans="2:3">
       <c r="B183" s="1" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="C183" t="s">
         <v>1944</v>
@@ -11474,7 +11532,7 @@
     </row>
     <row r="184" spans="2:3">
       <c r="B184" s="1" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="C184" t="s">
         <v>1945</v>
@@ -11482,7 +11540,7 @@
     </row>
     <row r="185" spans="2:3">
       <c r="B185" s="1" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="C185" t="s">
         <v>1946</v>
@@ -11538,7 +11596,7 @@
     </row>
     <row r="192" spans="2:3">
       <c r="B192" s="1" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="C192" t="s">
         <v>1959</v>
@@ -11546,7 +11604,7 @@
     </row>
     <row r="193" spans="2:3">
       <c r="B193" s="1" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="C193" t="s">
         <v>1960</v>
@@ -11586,7 +11644,7 @@
     </row>
     <row r="198" spans="2:3">
       <c r="B198" s="1" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="C198" t="s">
         <v>1969</v>
@@ -11602,7 +11660,7 @@
     </row>
     <row r="200" spans="2:3">
       <c r="B200" s="1" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="C200" t="s">
         <v>1972</v>
@@ -11618,7 +11676,7 @@
     </row>
     <row r="202" spans="2:3">
       <c r="B202" s="1" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="C202" t="s">
         <v>1975</v>
@@ -11650,7 +11708,7 @@
     </row>
     <row r="206" spans="2:3">
       <c r="B206" s="1" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="C206" t="s">
         <v>1982</v>
@@ -11658,7 +11716,7 @@
     </row>
     <row r="207" spans="2:3">
       <c r="B207" s="1" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="C207" t="s">
         <v>1983</v>
@@ -11698,7 +11756,7 @@
     </row>
     <row r="212" spans="2:3">
       <c r="B212" s="1" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="C212" t="s">
         <v>1990</v>
@@ -11730,7 +11788,7 @@
     </row>
     <row r="216" spans="2:3">
       <c r="B216" s="1" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="C216" t="s">
         <v>1997</v>
@@ -11762,7 +11820,7 @@
     </row>
     <row r="220" spans="2:3">
       <c r="B220" s="1" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="C220" t="s">
         <v>2003</v>
@@ -11770,7 +11828,7 @@
     </row>
     <row r="221" spans="2:3">
       <c r="B221" s="1" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="C221" t="s">
         <v>2004</v>
@@ -11786,7 +11844,7 @@
     </row>
     <row r="223" spans="2:3">
       <c r="B223" s="1" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="C223" t="s">
         <v>2007</v>
@@ -11866,7 +11924,7 @@
     </row>
     <row r="233" spans="2:3">
       <c r="B233" s="1" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="C233" t="s">
         <v>2026</v>
@@ -11898,7 +11956,7 @@
     </row>
     <row r="237" spans="2:3">
       <c r="B237" s="1" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="C237" t="s">
         <v>2033</v>
@@ -11930,7 +11988,7 @@
     </row>
     <row r="241" spans="2:3">
       <c r="B241" s="1" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="C241" t="s">
         <v>2040</v>
@@ -11938,7 +11996,7 @@
     </row>
     <row r="242" spans="2:3">
       <c r="B242" s="1" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="C242" t="s">
         <v>2041</v>
@@ -11970,7 +12028,7 @@
     </row>
     <row r="246" spans="2:3">
       <c r="B246" s="1" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="C246" t="s">
         <v>2048</v>
@@ -11978,7 +12036,7 @@
     </row>
     <row r="247" spans="2:3">
       <c r="B247" s="1" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="C247" t="s">
         <v>2049</v>
@@ -11994,7 +12052,7 @@
     </row>
     <row r="249" spans="2:3">
       <c r="B249" s="1" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="C249" t="s">
         <v>2052</v>
@@ -12010,7 +12068,7 @@
     </row>
     <row r="251" spans="2:3">
       <c r="B251" s="1" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="C251" t="s">
         <v>2055</v>
@@ -12066,7 +12124,7 @@
     </row>
     <row r="258" spans="2:3">
       <c r="B258" s="1" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="C258" t="s">
         <v>2068</v>
@@ -12082,7 +12140,7 @@
     </row>
     <row r="260" spans="2:3">
       <c r="B260" s="1" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="C260" t="s">
         <v>2071</v>
@@ -12146,7 +12204,7 @@
     </row>
     <row r="268" spans="2:3">
       <c r="B268" s="1" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="C268" t="s">
         <v>2086</v>
@@ -12258,7 +12316,7 @@
     </row>
     <row r="282" spans="2:3">
       <c r="B282" s="1" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C282" t="s">
         <v>2112</v>
@@ -12306,13 +12364,13 @@
     </row>
     <row r="288" spans="2:3">
       <c r="B288" s="1" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C288" t="s">
         <v>2123</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
+    <row r="289" spans="2:3">
       <c r="B289" s="1" t="s">
         <v>2124</v>
       </c>
@@ -12320,89 +12378,137 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="2:3">
       <c r="B290" s="1" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="C290" t="s">
         <v>2032</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
+    <row r="291" spans="2:3">
       <c r="B291" s="1" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C291" t="s">
         <v>2126</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="2:3">
       <c r="B292" s="1" t="s">
         <v>2127</v>
       </c>
       <c r="C292" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3">
       <c r="B293" s="1" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C293" t="s">
         <v>2206</v>
       </c>
-      <c r="C293" t="s">
+    </row>
+    <row r="294" spans="2:3">
+      <c r="B294" s="1" t="s">
         <v>2207</v>
       </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="B294" s="1" t="s">
+      <c r="C294" t="s">
         <v>2208</v>
       </c>
-      <c r="C294" t="s">
+    </row>
+    <row r="295" spans="2:3">
+      <c r="B295" s="1" t="s">
         <v>2209</v>
       </c>
-    </row>
-    <row r="295" spans="1:3">
-      <c r="B295" s="1" t="s">
+      <c r="C295" t="s">
         <v>2210</v>
       </c>
-      <c r="C295" t="s">
+    </row>
+    <row r="296" spans="2:3">
+      <c r="B296" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="C296" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3">
+      <c r="B297" s="38" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3">
+      <c r="B298" s="1" t="s">
         <v>2211</v>
       </c>
-    </row>
-    <row r="296" spans="1:3">
-      <c r="B296" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="C296" t="s">
-        <v>2214</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3">
-      <c r="B297" s="35" t="s">
-        <v>1628</v>
-      </c>
-      <c r="C297" t="s">
+      <c r="C298" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3">
+      <c r="B299" s="35" t="s">
         <v>2215</v>
       </c>
-    </row>
-    <row r="298" spans="1:3">
-      <c r="B298" s="1" t="s">
-        <v>2212</v>
-      </c>
-      <c r="C298" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="B300" s="36" t="s">
+      <c r="C299" t="s">
         <v>2216</v>
       </c>
+    </row>
+    <row r="300" spans="2:3">
+      <c r="B300" s="1" t="s">
+        <v>2217</v>
+      </c>
       <c r="C300" t="s">
-        <v>2217</v>
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3">
+      <c r="B301" s="35" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C301" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3">
+      <c r="B302" s="21" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3">
+      <c r="B303" s="21" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C303" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3">
+      <c r="B304" s="21" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C304" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="B305" s="37" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
+        <v>2131</v>
       </c>
     </row>
   </sheetData>
@@ -12943,7 +13049,7 @@
       <c r="B2" s="7">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="36"/>
       <c r="D2" s="7">
         <v>1</v>
       </c>
@@ -13325,7 +13431,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -14692,7 +14798,7 @@
       </c>
       <c r="DA5" s="6" t="str">
         <f>_xlfn.XLOOKUP(CZ5,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>交?</v>
       </c>
       <c r="DB5" s="7" t="s">
         <v>298</v>
@@ -15762,7 +15868,7 @@
       </c>
       <c r="DM7" s="6" t="str">
         <f>_xlfn.XLOOKUP(DL7,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>文?</v>
       </c>
       <c r="DN7" s="7" t="s">
         <v>475</v>
@@ -16227,7 +16333,7 @@
       </c>
       <c r="CY8" s="6" t="str">
         <f>_xlfn.XLOOKUP(CX8,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>力</v>
       </c>
       <c r="CZ8" s="7" t="s">
         <v>554</v>
@@ -16262,7 +16368,7 @@
       </c>
       <c r="DI8" s="6" t="str">
         <f>_xlfn.XLOOKUP(DH8,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>流?</v>
       </c>
       <c r="DJ8" s="7" t="s">
         <v>559</v>
@@ -18881,7 +18987,7 @@
       </c>
       <c r="DW13" s="6" t="str">
         <f>_xlfn.XLOOKUP(DV13,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>兆</v>
+        <v>兆?</v>
       </c>
       <c r="DX13" s="7" t="s">
         <v>972</v>
@@ -21486,7 +21592,7 @@
       </c>
       <c r="EG18" s="6" t="str">
         <f>_xlfn.XLOOKUP(EF18,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>像/王?</v>
       </c>
       <c r="EH18" s="7" t="s">
         <v>1383</v>
@@ -22593,8 +22699,8 @@
         <v>1552</v>
       </c>
       <c r="M21" s="6" t="str">
-        <f>_xlfn.XLOOKUP(L21,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(L21,対応表!$B:$B,対応表!$C:$C,"常")</f>
+        <v>常</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>1554</v>
@@ -23107,8 +23213,8 @@
         <v>1636</v>
       </c>
       <c r="M22" s="6" t="str">
-        <f>_xlfn.XLOOKUP(L22,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(L22,対応表!$B:$B,対応表!$C:$C,"を")</f>
+        <v>を</v>
       </c>
       <c r="N22" s="7" t="s">
         <v>1637</v>
@@ -23121,8 +23227,8 @@
         <v>1638</v>
       </c>
       <c r="Q22" s="6" t="str">
-        <f>_xlfn.XLOOKUP(P22,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(P22,対応表!$B:$B,対応表!$C:$C,"う")</f>
+        <v>う</v>
       </c>
       <c r="R22" s="7" t="s">
         <v>1639</v>
@@ -23658,7 +23764,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56BA558B-4A3B-40BE-B112-453F7FF56BB1}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D507252-BDDC-4B57-BEE6-B3FBD4F20BC9}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3834" uniqueCount="2229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="2239">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8303,9 +8303,6 @@
     <t>丩</t>
   </si>
   <si>
-    <t>第?</t>
-  </si>
-  <si>
     <t>什</t>
   </si>
   <si>
@@ -8366,9 +8363,6 @@
     <t>侫</t>
   </si>
   <si>
-    <t>知?</t>
-  </si>
-  <si>
     <t>丑</t>
   </si>
   <si>
@@ -8402,9 +8396,6 @@
     <t>假</t>
   </si>
   <si>
-    <t>客?</t>
-  </si>
-  <si>
     <t>侂</t>
   </si>
   <si>
@@ -8780,9 +8771,6 @@
     <t>伏</t>
   </si>
   <si>
-    <t>街?</t>
-  </si>
-  <si>
     <t>侁</t>
   </si>
   <si>
@@ -8847,9 +8835,6 @@
   </si>
   <si>
     <t>儼</t>
-  </si>
-  <si>
-    <t>区?</t>
   </si>
   <si>
     <t>形</t>
@@ -9247,9 +9232,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>果</t>
-  </si>
-  <si>
     <t>剸</t>
   </si>
   <si>
@@ -9269,6 +9251,73 @@
   </si>
   <si>
     <t>交?</t>
+  </si>
+  <si>
+    <t>街</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>客?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>知</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>五</t>
+  </si>
+  <si>
+    <t>四?</t>
+    <rPh sb="0" eb="1">
+      <t>ヨン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亘</t>
+  </si>
+  <si>
+    <t>腹?</t>
+    <rPh sb="0" eb="1">
+      <t>ハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倂</t>
+  </si>
+  <si>
+    <t>匰</t>
+  </si>
+  <si>
+    <t>儽</t>
+  </si>
+  <si>
+    <t>○われ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兊</t>
+  </si>
+  <si>
+    <t>果?</t>
+    <rPh sb="0" eb="1">
+      <t>ハテ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -9536,7 +9585,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9651,14 +9700,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -9740,10 +9798,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10063,7 +10117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:C306"/>
+  <dimension ref="A1:C311"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -10071,7 +10125,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2136</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -10316,7 +10370,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="1" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -10428,7 +10482,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
-        <v>2129</v>
+        <v>2124</v>
       </c>
       <c r="C46">
         <v>43</v>
@@ -10572,7 +10626,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" s="1" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="C64">
         <v>61</v>
@@ -10644,7 +10698,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="1" t="s">
-        <v>2137</v>
+        <v>2132</v>
       </c>
       <c r="C73" t="s">
         <v>1777</v>
@@ -10724,7 +10778,7 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1" t="s">
-        <v>2138</v>
+        <v>2133</v>
       </c>
       <c r="C83" t="s">
         <v>1795</v>
@@ -10740,7 +10794,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="1" t="s">
-        <v>2139</v>
+        <v>2134</v>
       </c>
       <c r="C85" t="s">
         <v>1798</v>
@@ -10748,7 +10802,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="1" t="s">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="C86" t="s">
         <v>1799</v>
@@ -10756,7 +10810,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="1" t="s">
-        <v>2140</v>
+        <v>2135</v>
       </c>
       <c r="C87" t="s">
         <v>990</v>
@@ -10780,7 +10834,7 @@
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="1" t="s">
-        <v>2135</v>
+        <v>2130</v>
       </c>
       <c r="C90" t="s">
         <v>1803</v>
@@ -10796,7 +10850,7 @@
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="1" t="s">
-        <v>2141</v>
+        <v>2136</v>
       </c>
       <c r="C92" t="s">
         <v>827</v>
@@ -10828,7 +10882,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" s="1" t="s">
-        <v>2142</v>
+        <v>2137</v>
       </c>
       <c r="C96" t="s">
         <v>1812</v>
@@ -10860,7 +10914,7 @@
     </row>
     <row r="100" spans="2:3">
       <c r="B100" s="1" t="s">
-        <v>2143</v>
+        <v>2138</v>
       </c>
       <c r="C100" t="s">
         <v>832</v>
@@ -10876,7 +10930,7 @@
     </row>
     <row r="102" spans="2:3">
       <c r="B102" s="1" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
       <c r="C102" t="s">
         <v>1820</v>
@@ -10884,7 +10938,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" s="1" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="C103" t="s">
         <v>1821</v>
@@ -10900,7 +10954,7 @@
     </row>
     <row r="105" spans="2:3">
       <c r="B105" s="1" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="C105" t="s">
         <v>1824</v>
@@ -10924,7 +10978,7 @@
     </row>
     <row r="108" spans="2:3">
       <c r="B108" s="1" t="s">
-        <v>2147</v>
+        <v>2142</v>
       </c>
       <c r="C108" t="s">
         <v>1828</v>
@@ -10932,7 +10986,7 @@
     </row>
     <row r="109" spans="2:3">
       <c r="B109" s="1" t="s">
-        <v>2148</v>
+        <v>2143</v>
       </c>
       <c r="C109" t="s">
         <v>1829</v>
@@ -10940,7 +10994,7 @@
     </row>
     <row r="110" spans="2:3">
       <c r="B110" s="1" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="C110" t="s">
         <v>1830</v>
@@ -10956,7 +11010,7 @@
     </row>
     <row r="112" spans="2:3">
       <c r="B112" s="1" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="C112" t="s">
         <v>1833</v>
@@ -10972,7 +11026,7 @@
     </row>
     <row r="114" spans="2:3">
       <c r="B114" s="1" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
       <c r="C114" t="s">
         <v>1836</v>
@@ -10980,7 +11034,7 @@
     </row>
     <row r="115" spans="2:3">
       <c r="B115" s="1" t="s">
-        <v>2152</v>
+        <v>2147</v>
       </c>
       <c r="C115" t="s">
         <v>1837</v>
@@ -10988,7 +11042,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" s="1" t="s">
-        <v>2153</v>
+        <v>2148</v>
       </c>
       <c r="C116" t="s">
         <v>1838</v>
@@ -11004,7 +11058,7 @@
     </row>
     <row r="118" spans="2:3">
       <c r="B118" s="1" t="s">
-        <v>2154</v>
+        <v>2149</v>
       </c>
       <c r="C118" t="s">
         <v>1840</v>
@@ -11020,7 +11074,7 @@
     </row>
     <row r="120" spans="2:3">
       <c r="B120" s="1" t="s">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="C120" t="s">
         <v>1843</v>
@@ -11036,7 +11090,7 @@
     </row>
     <row r="122" spans="2:3">
       <c r="B122" s="1" t="s">
-        <v>2156</v>
+        <v>2151</v>
       </c>
       <c r="C122" t="s">
         <v>1846</v>
@@ -11044,7 +11098,7 @@
     </row>
     <row r="123" spans="2:3">
       <c r="B123" s="1" t="s">
-        <v>2157</v>
+        <v>2152</v>
       </c>
       <c r="C123" t="s">
         <v>1847</v>
@@ -11052,7 +11106,7 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" s="1" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
       <c r="C124" t="s">
         <v>1848</v>
@@ -11060,7 +11114,7 @@
     </row>
     <row r="125" spans="2:3">
       <c r="B125" s="1" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="C125" t="s">
         <v>1849</v>
@@ -11092,7 +11146,7 @@
     </row>
     <row r="129" spans="2:3">
       <c r="B129" s="1" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="C129" t="s">
         <v>1856</v>
@@ -11116,7 +11170,7 @@
     </row>
     <row r="132" spans="2:3">
       <c r="B132" s="1" t="s">
-        <v>2161</v>
+        <v>2156</v>
       </c>
       <c r="C132" t="s">
         <v>1860</v>
@@ -11132,7 +11186,7 @@
     </row>
     <row r="134" spans="2:3">
       <c r="B134" s="1" t="s">
-        <v>2162</v>
+        <v>2157</v>
       </c>
       <c r="C134" t="s">
         <v>1862</v>
@@ -11140,7 +11194,7 @@
     </row>
     <row r="135" spans="2:3">
       <c r="B135" s="1" t="s">
-        <v>2163</v>
+        <v>2158</v>
       </c>
       <c r="C135" t="s">
         <v>1863</v>
@@ -11148,7 +11202,7 @@
     </row>
     <row r="136" spans="2:3">
       <c r="B136" s="1" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="C136" t="s">
         <v>1864</v>
@@ -11196,7 +11250,7 @@
     </row>
     <row r="142" spans="2:3">
       <c r="B142" s="1" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
       <c r="C142" t="s">
         <v>1875</v>
@@ -11252,7 +11306,7 @@
     </row>
     <row r="149" spans="2:3">
       <c r="B149" s="1" t="s">
-        <v>2166</v>
+        <v>2161</v>
       </c>
       <c r="C149" t="s">
         <v>1888</v>
@@ -11276,7 +11330,7 @@
     </row>
     <row r="152" spans="2:3">
       <c r="B152" s="1" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="C152" t="s">
         <v>1893</v>
@@ -11284,7 +11338,7 @@
     </row>
     <row r="153" spans="2:3">
       <c r="B153" s="1" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="C153" t="s">
         <v>1894</v>
@@ -11316,7 +11370,7 @@
     </row>
     <row r="157" spans="2:3">
       <c r="B157" s="1" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="C157" t="s">
         <v>1900</v>
@@ -11356,7 +11410,7 @@
     </row>
     <row r="162" spans="2:3">
       <c r="B162" s="1" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
       <c r="C162" t="s">
         <v>1909</v>
@@ -11380,7 +11434,7 @@
     </row>
     <row r="165" spans="2:3">
       <c r="B165" s="1" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="C165" t="s">
         <v>1914</v>
@@ -11396,7 +11450,7 @@
     </row>
     <row r="167" spans="2:3">
       <c r="B167" s="1" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="C167" t="s">
         <v>1917</v>
@@ -11444,7 +11498,7 @@
     </row>
     <row r="173" spans="2:3">
       <c r="B173" s="1" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
       <c r="C173" t="s">
         <v>1927</v>
@@ -11455,20 +11509,20 @@
         <v>1928</v>
       </c>
       <c r="C174" t="s">
-        <v>1929</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="175" spans="2:3">
       <c r="B175" s="1" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C175" t="s">
         <v>1930</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="176" spans="2:3">
       <c r="B176" s="1" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="C176" t="s">
         <v>980</v>
@@ -11476,258 +11530,258 @@
     </row>
     <row r="177" spans="2:3">
       <c r="B177" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C177" t="s">
         <v>1933</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1934</v>
       </c>
     </row>
     <row r="178" spans="2:3">
       <c r="B178" s="1" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="C178" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="179" spans="2:3">
       <c r="B179" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C179" t="s">
         <v>1936</v>
-      </c>
-      <c r="C179" t="s">
-        <v>1937</v>
       </c>
     </row>
     <row r="180" spans="2:3">
       <c r="B180" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C180" t="s">
         <v>1938</v>
-      </c>
-      <c r="C180" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="181" spans="2:3">
       <c r="B181" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C181" t="s">
         <v>1940</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1941</v>
       </c>
     </row>
     <row r="182" spans="2:3">
       <c r="B182" s="1" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C182" t="s">
         <v>1942</v>
-      </c>
-      <c r="C182" t="s">
-        <v>1943</v>
       </c>
     </row>
     <row r="183" spans="2:3">
       <c r="B183" s="1" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="C183" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="184" spans="2:3">
       <c r="B184" s="1" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="C184" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="185" spans="2:3">
       <c r="B185" s="1" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="C185" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="186" spans="2:3">
       <c r="B186" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C186" t="s">
         <v>1947</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="187" spans="2:3">
       <c r="B187" s="1" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C187" t="s">
-        <v>1950</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="188" spans="2:3">
       <c r="B188" s="1" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C188" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="189" spans="2:3">
       <c r="B189" s="1" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="C189" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="190" spans="2:3">
       <c r="B190" s="1" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="C190" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="191" spans="2:3">
       <c r="B191" s="1" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="C191" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="192" spans="2:3">
       <c r="B192" s="1" t="s">
-        <v>2178</v>
+        <v>2173</v>
       </c>
       <c r="C192" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="193" spans="2:3">
       <c r="B193" s="1" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
       <c r="C193" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="194" spans="2:3">
       <c r="B194" s="1" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="C194" t="s">
-        <v>1962</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="195" spans="2:3">
       <c r="B195" s="1" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="C195" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="196" spans="2:3">
       <c r="B196" s="1" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="C196" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="197" spans="2:3">
       <c r="B197" s="1" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="C197" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="198" spans="2:3">
       <c r="B198" s="1" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="C198" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="199" spans="2:3">
       <c r="B199" s="1" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="C199" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="200" spans="2:3">
       <c r="B200" s="1" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
       <c r="C200" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="201" spans="2:3">
       <c r="B201" s="1" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="C201" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="202" spans="2:3">
       <c r="B202" s="1" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="C202" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="203" spans="2:3">
       <c r="B203" s="1" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="C203" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="204" spans="2:3">
       <c r="B204" s="1" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="C204" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="205" spans="2:3">
       <c r="B205" s="1" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="C205" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="206" spans="2:3">
       <c r="B206" s="1" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="C206" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="207" spans="2:3">
       <c r="B207" s="1" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="C207" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="208" spans="2:3">
       <c r="B208" s="1" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="C208" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="209" spans="2:3">
@@ -11735,15 +11789,15 @@
         <v>980</v>
       </c>
       <c r="C209" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="210" spans="2:3">
       <c r="B210" s="1" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="C210" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="211" spans="2:3">
@@ -11751,47 +11805,47 @@
         <v>1227</v>
       </c>
       <c r="C211" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="212" spans="2:3">
       <c r="B212" s="1" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
       <c r="C212" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="213" spans="2:3">
       <c r="B213" s="1" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="C213" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="214" spans="2:3">
       <c r="B214" s="1" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="C214" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="215" spans="2:3">
       <c r="B215" s="1" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="C215" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="216" spans="2:3">
       <c r="B216" s="1" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
       <c r="C216" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="217" spans="2:3">
@@ -11799,471 +11853,471 @@
         <v>1235</v>
       </c>
       <c r="C217" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="218" spans="2:3">
       <c r="B218" s="1" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="C218" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="219" spans="2:3">
       <c r="B219" s="1" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C219" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="220" spans="2:3">
       <c r="B220" s="1" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="C220" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="221" spans="2:3">
       <c r="B221" s="1" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="C221" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="222" spans="2:3">
       <c r="B222" s="1" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C222" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="223" spans="2:3">
       <c r="B223" s="1" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="C223" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="224" spans="2:3">
       <c r="B224" s="1" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="C224" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="225" spans="2:3">
       <c r="B225" s="1" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C225" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="226" spans="2:3">
       <c r="B226" s="1" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="C226" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="227" spans="2:3">
       <c r="B227" s="1" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C227" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="228" spans="2:3">
       <c r="B228" s="1" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C228" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="229" spans="2:3">
       <c r="B229" s="1" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C229" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="230" spans="2:3">
       <c r="B230" s="1" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C230" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="231" spans="2:3">
       <c r="B231" s="1" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C231" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="232" spans="2:3">
       <c r="B232" s="1" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C232" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="233" spans="2:3">
       <c r="B233" s="1" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
       <c r="C233" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="234" spans="2:3">
       <c r="B234" s="1" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="C234" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="235" spans="2:3">
       <c r="B235" s="1" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="C235" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="236" spans="2:3">
       <c r="B236" s="1" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
       <c r="C236" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="237" spans="2:3">
       <c r="B237" s="1" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="C237" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="238" spans="2:3">
       <c r="B238" s="1" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="C238" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="239" spans="2:3">
       <c r="B239" s="1" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="C239" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="240" spans="2:3">
       <c r="B240" s="1" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="C240" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="241" spans="2:3">
       <c r="B241" s="1" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="C241" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="242" spans="2:3">
       <c r="B242" s="1" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
       <c r="C242" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="243" spans="2:3">
       <c r="B243" s="1" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="C243" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="244" spans="2:3">
       <c r="B244" s="1" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
       <c r="C244" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="245" spans="2:3">
       <c r="B245" s="1" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
       <c r="C245" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="246" spans="2:3">
       <c r="B246" s="1" t="s">
-        <v>2194</v>
+        <v>2189</v>
       </c>
       <c r="C246" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="247" spans="2:3">
       <c r="B247" s="1" t="s">
-        <v>2195</v>
+        <v>2190</v>
       </c>
       <c r="C247" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="248" spans="2:3">
       <c r="B248" s="1" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
       <c r="C248" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="249" spans="2:3">
       <c r="B249" s="1" t="s">
-        <v>2196</v>
+        <v>2191</v>
       </c>
       <c r="C249" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="250" spans="2:3">
       <c r="B250" s="1" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
       <c r="C250" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="251" spans="2:3">
       <c r="B251" s="1" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="C251" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="252" spans="2:3">
       <c r="B252" s="1" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="C252" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="253" spans="2:3">
       <c r="B253" s="1" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="C253" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="254" spans="2:3">
       <c r="B254" s="1" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="C254" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="255" spans="2:3">
       <c r="B255" s="1" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="C255" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="256" spans="2:3">
       <c r="B256" s="1" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
       <c r="C256" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="257" spans="2:3">
       <c r="B257" s="1" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="C257" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="258" spans="2:3">
       <c r="B258" s="1" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="C258" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="259" spans="2:3">
       <c r="B259" s="1" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="C259" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="260" spans="2:3">
       <c r="B260" s="1" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
       <c r="C260" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="261" spans="2:3">
       <c r="B261" s="1" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="C261" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="262" spans="2:3">
       <c r="B262" s="1" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="C262" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="263" spans="2:3">
       <c r="B263" s="1" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="C263" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="264" spans="2:3">
       <c r="B264" s="1" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="C264" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="265" spans="2:3">
       <c r="B265" s="1" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="C265" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="266" spans="2:3">
       <c r="B266" s="1" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="C266" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="267" spans="2:3">
       <c r="B267" s="1" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="C267" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="268" spans="2:3">
       <c r="B268" s="1" t="s">
-        <v>2200</v>
+        <v>2195</v>
       </c>
       <c r="C268" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="269" spans="2:3">
       <c r="B269" s="1" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="C269" t="s">
-        <v>2088</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="270" spans="2:3">
       <c r="B270" s="1" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
       <c r="C270" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="271" spans="2:3">
       <c r="B271" s="1" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="C271" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="272" spans="2:3">
       <c r="B272" s="1" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="C272" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="273" spans="2:3">
       <c r="B273" s="1" t="s">
-        <v>2095</v>
+        <v>2091</v>
       </c>
       <c r="C273" t="s">
-        <v>2096</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="274" spans="2:3">
       <c r="B274" s="1" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="C274" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="275" spans="2:3">
       <c r="B275" s="1" t="s">
-        <v>2099</v>
+        <v>2095</v>
       </c>
       <c r="C275" t="s">
-        <v>2100</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="276" spans="2:3">
@@ -12271,261 +12325,301 @@
         <v>492</v>
       </c>
       <c r="C276" t="s">
-        <v>2101</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="277" spans="2:3">
       <c r="B277" s="1" t="s">
-        <v>2102</v>
+        <v>2098</v>
       </c>
       <c r="C277" t="s">
-        <v>2103</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="278" spans="2:3">
       <c r="B278" s="1" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
       <c r="C278" t="s">
-        <v>2105</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="279" spans="2:3">
       <c r="B279" s="1" t="s">
-        <v>2106</v>
+        <v>2102</v>
       </c>
       <c r="C279" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="280" spans="2:3">
       <c r="B280" s="1" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
       <c r="C280" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="281" spans="2:3">
       <c r="B281" s="1" t="s">
-        <v>2110</v>
+        <v>2106</v>
       </c>
       <c r="C281" t="s">
-        <v>2111</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="282" spans="2:3">
       <c r="B282" s="1" t="s">
-        <v>2201</v>
+        <v>2196</v>
       </c>
       <c r="C282" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="283" spans="2:3">
       <c r="B283" s="1" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
       <c r="C283" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="284" spans="2:3">
       <c r="B284" s="1" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="C284" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="285" spans="2:3">
       <c r="B285" s="1" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
       <c r="C285" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="286" spans="2:3">
       <c r="B286" s="1" t="s">
-        <v>2119</v>
+        <v>2114</v>
       </c>
       <c r="C286" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="287" spans="2:3">
       <c r="B287" s="1" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="C287" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="288" spans="2:3">
       <c r="B288" s="1" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="C288" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="289" spans="2:3">
       <c r="B289" s="1" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
       <c r="C289" t="s">
-        <v>2125</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="290" spans="2:3">
       <c r="B290" s="1" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="C290" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="291" spans="2:3">
       <c r="B291" s="1" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="C291" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="292" spans="2:3">
       <c r="B292" s="1" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="C292" t="s">
-        <v>2224</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="293" spans="2:3">
       <c r="B293" s="1" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="C293" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="294" spans="2:3">
       <c r="B294" s="1" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="C294" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="295" spans="2:3">
       <c r="B295" s="1" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C295" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3">
+      <c r="B296" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C296" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3">
+      <c r="B297" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C297" t="s">
         <v>2209</v>
-      </c>
-      <c r="C295" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="296" spans="2:3">
-      <c r="B296" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="C296" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="297" spans="2:3">
-      <c r="B297" s="38" t="s">
-        <v>1628</v>
-      </c>
-      <c r="C297" t="s">
-        <v>2214</v>
       </c>
     </row>
     <row r="298" spans="2:3">
       <c r="B298" s="1" t="s">
-        <v>2211</v>
+        <v>2206</v>
       </c>
       <c r="C298" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="299" spans="2:3">
       <c r="B299" s="35" t="s">
-        <v>2215</v>
+        <v>2210</v>
       </c>
       <c r="C299" t="s">
-        <v>2216</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="300" spans="2:3">
       <c r="B300" s="1" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="C300" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="301" spans="2:3">
       <c r="B301" s="35" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="C301" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="302" spans="2:3">
       <c r="B302" s="21" t="s">
-        <v>2115</v>
+        <v>2237</v>
       </c>
       <c r="C302" t="s">
-        <v>2221</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="303" spans="2:3">
       <c r="B303" s="21" t="s">
-        <v>2222</v>
+        <v>2216</v>
       </c>
       <c r="C303" t="s">
-        <v>2223</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="304" spans="2:3">
       <c r="B304" s="21" t="s">
-        <v>2225</v>
+        <v>2219</v>
       </c>
       <c r="C304" t="s">
-        <v>2228</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="B305" s="37" t="s">
-        <v>2226</v>
+        <v>2220</v>
       </c>
       <c r="C305" t="s">
-        <v>2227</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>2131</v>
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="B307" s="1" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C307" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="B308" s="1" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C308" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="B309" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C309" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="B310" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C310" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="B311" s="1" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C311" t="s">
+        <v>2236</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B70">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>RIGHT(B70,1)="?"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B296:B297">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>RIGHT(B296,1)="?"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13431,7 +13525,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -13941,7 +14035,7 @@
       </c>
       <c r="G4" s="6" t="str">
         <f>_xlfn.XLOOKUP(F4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>第?</v>
+        <v>第</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>163</v>
@@ -14735,7 +14829,7 @@
       </c>
       <c r="CI5" s="6" t="str">
         <f>_xlfn.XLOOKUP(CH5,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>果?</v>
       </c>
       <c r="CJ5" s="7" t="s">
         <v>289</v>
@@ -17158,7 +17252,7 @@
       </c>
       <c r="AS10" s="6" t="str">
         <f>_xlfn.XLOOKUP(AR10,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>知?</v>
+        <v>知</v>
       </c>
       <c r="AT10" s="7" t="s">
         <v>686</v>
@@ -17574,7 +17668,7 @@
       </c>
       <c r="Q11" s="6" t="str">
         <f>_xlfn.XLOOKUP(P11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>四?</v>
       </c>
       <c r="R11" s="7" t="s">
         <v>751</v>
@@ -17812,7 +17906,7 @@
       </c>
       <c r="CG11" s="6" t="str">
         <f>_xlfn.XLOOKUP(CF11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>区?</v>
+        <v>区</v>
       </c>
       <c r="CH11" s="7" t="s">
         <v>789</v>
@@ -17987,7 +18081,7 @@
       </c>
       <c r="EE11" s="6" t="str">
         <f>_xlfn.XLOOKUP(ED11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>◇</v>
       </c>
       <c r="EF11" s="7" t="s">
         <v>817</v>
@@ -18326,7 +18420,7 @@
       </c>
       <c r="CG12" s="6" t="str">
         <f>_xlfn.XLOOKUP(CF12,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>■</v>
       </c>
       <c r="CH12" s="7" t="s">
         <v>870</v>
@@ -19158,7 +19252,7 @@
       </c>
       <c r="AC14" s="6" t="str">
         <f>_xlfn.XLOOKUP(AB14,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>街?</v>
+        <v>街</v>
       </c>
       <c r="AD14" s="7" t="s">
         <v>999</v>
@@ -19630,7 +19724,7 @@
       </c>
       <c r="Q15" s="6" t="str">
         <f>_xlfn.XLOOKUP(P15,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>腹?</v>
       </c>
       <c r="R15" s="7" t="s">
         <v>1075</v>
@@ -20784,7 +20878,7 @@
       </c>
       <c r="BA17" s="6" t="str">
         <f>_xlfn.XLOOKUP(AZ17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>○われ</v>
       </c>
       <c r="BB17" s="7" t="s">
         <v>1257</v>
@@ -23698,10 +23792,10 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>RIGHT(A1,1)="?"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23764,7 +23858,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D507252-BDDC-4B57-BEE6-B3FBD4F20BC9}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D81FF0-192B-45CC-958A-04DCF1CFD43E}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="2239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3852" uniqueCount="2245">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8234,9 +8234,6 @@
     <t>備</t>
   </si>
   <si>
-    <t>新?</t>
-  </si>
-  <si>
     <t>冡</t>
   </si>
   <si>
@@ -8315,9 +8312,6 @@
     <t>丞</t>
   </si>
   <si>
-    <t>受?</t>
-  </si>
-  <si>
     <t>本</t>
   </si>
   <si>
@@ -8498,9 +8492,6 @@
     <t>訪</t>
   </si>
   <si>
-    <t>養?</t>
-  </si>
-  <si>
     <t>急?</t>
   </si>
   <si>
@@ -8534,9 +8525,6 @@
     <t>偉</t>
   </si>
   <si>
-    <t>丁?</t>
-  </si>
-  <si>
     <t>丮</t>
   </si>
   <si>
@@ -8564,15 +8552,9 @@
     <t>僮</t>
   </si>
   <si>
-    <t>中?</t>
-  </si>
-  <si>
     <t>僭</t>
   </si>
   <si>
-    <t>最?</t>
-  </si>
-  <si>
     <t>処</t>
   </si>
   <si>
@@ -8663,9 +8645,6 @@
     <t>指?</t>
   </si>
   <si>
-    <t>来?</t>
-  </si>
-  <si>
     <t>創</t>
   </si>
   <si>
@@ -8676,9 +8655,6 @@
   </si>
   <si>
     <t>匵</t>
-  </si>
-  <si>
-    <t>備?</t>
   </si>
   <si>
     <t>凃</t>
@@ -9298,18 +9274,6 @@
     <t>儽</t>
   </si>
   <si>
-    <t>○われ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>◇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>兊</t>
   </si>
   <si>
@@ -9317,6 +9281,82 @@
     <rPh sb="0" eb="1">
       <t>ハテ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亾</t>
+  </si>
+  <si>
+    <t>○?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>□?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防?</t>
+    <rPh sb="0" eb="1">
+      <t>フセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>養</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丁</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮</t>
+  </si>
+  <si>
+    <t>飾?</t>
+    <rPh sb="0" eb="1">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>冹</t>
+  </si>
+  <si>
+    <t>苦?</t>
+    <rPh sb="0" eb="1">
+      <t>ニガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乆</t>
+  </si>
+  <si>
+    <t>深?</t>
+    <rPh sb="0" eb="1">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>来</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9324,7 +9364,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9491,6 +9531,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Underground"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -9585,7 +9632,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9700,23 +9747,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color theme="1"/>
@@ -9798,6 +9836,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10117,7 +10159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:C311"/>
+  <dimension ref="A1:C315"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -10125,7 +10167,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2131</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -10370,7 +10412,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="1" t="s">
-        <v>2123</v>
+        <v>2115</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -10482,7 +10524,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
-        <v>2124</v>
+        <v>2116</v>
       </c>
       <c r="C46">
         <v>43</v>
@@ -10626,7 +10668,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" s="1" t="s">
-        <v>2125</v>
+        <v>2117</v>
       </c>
       <c r="C64">
         <v>61</v>
@@ -10698,7 +10740,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="1" t="s">
-        <v>2132</v>
+        <v>2124</v>
       </c>
       <c r="C73" t="s">
         <v>1777</v>
@@ -10778,7 +10820,7 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1" t="s">
-        <v>2133</v>
+        <v>2125</v>
       </c>
       <c r="C83" t="s">
         <v>1795</v>
@@ -10794,7 +10836,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="1" t="s">
-        <v>2134</v>
+        <v>2126</v>
       </c>
       <c r="C85" t="s">
         <v>1798</v>
@@ -10802,7 +10844,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="1" t="s">
-        <v>2129</v>
+        <v>2121</v>
       </c>
       <c r="C86" t="s">
         <v>1799</v>
@@ -10810,7 +10852,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="1" t="s">
-        <v>2135</v>
+        <v>2127</v>
       </c>
       <c r="C87" t="s">
         <v>990</v>
@@ -10834,7 +10876,7 @@
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="1" t="s">
-        <v>2130</v>
+        <v>2122</v>
       </c>
       <c r="C90" t="s">
         <v>1803</v>
@@ -10850,7 +10892,7 @@
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="1" t="s">
-        <v>2136</v>
+        <v>2128</v>
       </c>
       <c r="C92" t="s">
         <v>827</v>
@@ -10882,7 +10924,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" s="1" t="s">
-        <v>2137</v>
+        <v>2129</v>
       </c>
       <c r="C96" t="s">
         <v>1812</v>
@@ -10914,7 +10956,7 @@
     </row>
     <row r="100" spans="2:3">
       <c r="B100" s="1" t="s">
-        <v>2138</v>
+        <v>2130</v>
       </c>
       <c r="C100" t="s">
         <v>832</v>
@@ -10930,7 +10972,7 @@
     </row>
     <row r="102" spans="2:3">
       <c r="B102" s="1" t="s">
-        <v>2139</v>
+        <v>2131</v>
       </c>
       <c r="C102" t="s">
         <v>1820</v>
@@ -10938,7 +10980,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" s="1" t="s">
-        <v>2140</v>
+        <v>2132</v>
       </c>
       <c r="C103" t="s">
         <v>1821</v>
@@ -10954,7 +10996,7 @@
     </row>
     <row r="105" spans="2:3">
       <c r="B105" s="1" t="s">
-        <v>2141</v>
+        <v>2133</v>
       </c>
       <c r="C105" t="s">
         <v>1824</v>
@@ -10978,7 +11020,7 @@
     </row>
     <row r="108" spans="2:3">
       <c r="B108" s="1" t="s">
-        <v>2142</v>
+        <v>2134</v>
       </c>
       <c r="C108" t="s">
         <v>1828</v>
@@ -10986,7 +11028,7 @@
     </row>
     <row r="109" spans="2:3">
       <c r="B109" s="1" t="s">
-        <v>2143</v>
+        <v>2135</v>
       </c>
       <c r="C109" t="s">
         <v>1829</v>
@@ -10994,7 +11036,7 @@
     </row>
     <row r="110" spans="2:3">
       <c r="B110" s="1" t="s">
-        <v>2144</v>
+        <v>2136</v>
       </c>
       <c r="C110" t="s">
         <v>1830</v>
@@ -11010,7 +11052,7 @@
     </row>
     <row r="112" spans="2:3">
       <c r="B112" s="1" t="s">
-        <v>2145</v>
+        <v>2137</v>
       </c>
       <c r="C112" t="s">
         <v>1833</v>
@@ -11026,7 +11068,7 @@
     </row>
     <row r="114" spans="2:3">
       <c r="B114" s="1" t="s">
-        <v>2146</v>
+        <v>2138</v>
       </c>
       <c r="C114" t="s">
         <v>1836</v>
@@ -11034,7 +11076,7 @@
     </row>
     <row r="115" spans="2:3">
       <c r="B115" s="1" t="s">
-        <v>2147</v>
+        <v>2139</v>
       </c>
       <c r="C115" t="s">
         <v>1837</v>
@@ -11042,7 +11084,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" s="1" t="s">
-        <v>2148</v>
+        <v>2140</v>
       </c>
       <c r="C116" t="s">
         <v>1838</v>
@@ -11058,7 +11100,7 @@
     </row>
     <row r="118" spans="2:3">
       <c r="B118" s="1" t="s">
-        <v>2149</v>
+        <v>2141</v>
       </c>
       <c r="C118" t="s">
         <v>1840</v>
@@ -11074,7 +11116,7 @@
     </row>
     <row r="120" spans="2:3">
       <c r="B120" s="1" t="s">
-        <v>2150</v>
+        <v>2142</v>
       </c>
       <c r="C120" t="s">
         <v>1843</v>
@@ -11090,7 +11132,7 @@
     </row>
     <row r="122" spans="2:3">
       <c r="B122" s="1" t="s">
-        <v>2151</v>
+        <v>2143</v>
       </c>
       <c r="C122" t="s">
         <v>1846</v>
@@ -11098,7 +11140,7 @@
     </row>
     <row r="123" spans="2:3">
       <c r="B123" s="1" t="s">
-        <v>2152</v>
+        <v>2144</v>
       </c>
       <c r="C123" t="s">
         <v>1847</v>
@@ -11106,7 +11148,7 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" s="1" t="s">
-        <v>2153</v>
+        <v>2145</v>
       </c>
       <c r="C124" t="s">
         <v>1848</v>
@@ -11114,7 +11156,7 @@
     </row>
     <row r="125" spans="2:3">
       <c r="B125" s="1" t="s">
-        <v>2154</v>
+        <v>2146</v>
       </c>
       <c r="C125" t="s">
         <v>1849</v>
@@ -11146,7 +11188,7 @@
     </row>
     <row r="129" spans="2:3">
       <c r="B129" s="1" t="s">
-        <v>2155</v>
+        <v>2147</v>
       </c>
       <c r="C129" t="s">
         <v>1856</v>
@@ -11170,7 +11212,7 @@
     </row>
     <row r="132" spans="2:3">
       <c r="B132" s="1" t="s">
-        <v>2156</v>
+        <v>2148</v>
       </c>
       <c r="C132" t="s">
         <v>1860</v>
@@ -11186,7 +11228,7 @@
     </row>
     <row r="134" spans="2:3">
       <c r="B134" s="1" t="s">
-        <v>2157</v>
+        <v>2149</v>
       </c>
       <c r="C134" t="s">
         <v>1862</v>
@@ -11194,7 +11236,7 @@
     </row>
     <row r="135" spans="2:3">
       <c r="B135" s="1" t="s">
-        <v>2158</v>
+        <v>2150</v>
       </c>
       <c r="C135" t="s">
         <v>1863</v>
@@ -11202,7 +11244,7 @@
     </row>
     <row r="136" spans="2:3">
       <c r="B136" s="1" t="s">
-        <v>2159</v>
+        <v>2151</v>
       </c>
       <c r="C136" t="s">
         <v>1864</v>
@@ -11250,7 +11292,7 @@
     </row>
     <row r="142" spans="2:3">
       <c r="B142" s="1" t="s">
-        <v>2160</v>
+        <v>2152</v>
       </c>
       <c r="C142" t="s">
         <v>1875</v>
@@ -11306,7 +11348,7 @@
     </row>
     <row r="149" spans="2:3">
       <c r="B149" s="1" t="s">
-        <v>2161</v>
+        <v>2153</v>
       </c>
       <c r="C149" t="s">
         <v>1888</v>
@@ -11330,7 +11372,7 @@
     </row>
     <row r="152" spans="2:3">
       <c r="B152" s="1" t="s">
-        <v>2162</v>
+        <v>2154</v>
       </c>
       <c r="C152" t="s">
         <v>1893</v>
@@ -11338,7 +11380,7 @@
     </row>
     <row r="153" spans="2:3">
       <c r="B153" s="1" t="s">
-        <v>2163</v>
+        <v>2155</v>
       </c>
       <c r="C153" t="s">
         <v>1894</v>
@@ -11370,7 +11412,7 @@
     </row>
     <row r="157" spans="2:3">
       <c r="B157" s="1" t="s">
-        <v>2164</v>
+        <v>2156</v>
       </c>
       <c r="C157" t="s">
         <v>1900</v>
@@ -11397,100 +11439,100 @@
         <v>1905</v>
       </c>
       <c r="C160" t="s">
-        <v>1906</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="161" spans="2:3">
       <c r="B161" s="1" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C161" t="s">
         <v>1907</v>
-      </c>
-      <c r="C161" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="162" spans="2:3">
       <c r="B162" s="1" t="s">
-        <v>2165</v>
+        <v>2157</v>
       </c>
       <c r="C162" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="163" spans="2:3">
       <c r="B163" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C163" t="s">
         <v>1910</v>
-      </c>
-      <c r="C163" t="s">
-        <v>1911</v>
       </c>
     </row>
     <row r="164" spans="2:3">
       <c r="B164" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C164" t="s">
         <v>1912</v>
-      </c>
-      <c r="C164" t="s">
-        <v>1913</v>
       </c>
     </row>
     <row r="165" spans="2:3">
       <c r="B165" s="1" t="s">
-        <v>2166</v>
+        <v>2158</v>
       </c>
       <c r="C165" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="166" spans="2:3">
       <c r="B166" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C166" t="s">
         <v>1915</v>
-      </c>
-      <c r="C166" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="167" spans="2:3">
       <c r="B167" s="1" t="s">
-        <v>2167</v>
+        <v>2159</v>
       </c>
       <c r="C167" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="168" spans="2:3">
       <c r="B168" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C168" t="s">
         <v>1918</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="169" spans="2:3">
       <c r="B169" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C169" t="s">
         <v>1920</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1921</v>
       </c>
     </row>
     <row r="170" spans="2:3">
       <c r="B170" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C170" t="s">
         <v>1922</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="171" spans="2:3">
       <c r="B171" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C171" t="s">
         <v>1924</v>
-      </c>
-      <c r="C171" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="172" spans="2:3">
       <c r="B172" s="1" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="C172" t="s">
         <v>72</v>
@@ -11498,31 +11540,31 @@
     </row>
     <row r="173" spans="2:3">
       <c r="B173" s="1" t="s">
-        <v>2168</v>
+        <v>2160</v>
       </c>
       <c r="C173" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="174" spans="2:3">
       <c r="B174" s="1" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="C174" t="s">
-        <v>2228</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="175" spans="2:3">
       <c r="B175" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C175" t="s">
         <v>1929</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="176" spans="2:3">
       <c r="B176" s="1" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="C176" t="s">
         <v>980</v>
@@ -11530,258 +11572,258 @@
     </row>
     <row r="177" spans="2:3">
       <c r="B177" s="1" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="C177" t="s">
-        <v>1933</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="178" spans="2:3">
       <c r="B178" s="1" t="s">
-        <v>2169</v>
+        <v>2161</v>
       </c>
       <c r="C178" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="179" spans="2:3">
       <c r="B179" s="1" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="C179" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="180" spans="2:3">
       <c r="B180" s="1" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="C180" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="181" spans="2:3">
       <c r="B181" s="1" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="C181" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="182" spans="2:3">
       <c r="B182" s="1" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="C182" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="183" spans="2:3">
       <c r="B183" s="1" t="s">
-        <v>2170</v>
+        <v>2162</v>
       </c>
       <c r="C183" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="184" spans="2:3">
       <c r="B184" s="1" t="s">
-        <v>2171</v>
+        <v>2163</v>
       </c>
       <c r="C184" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="185" spans="2:3">
       <c r="B185" s="1" t="s">
-        <v>2172</v>
+        <v>2164</v>
       </c>
       <c r="C185" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="186" spans="2:3">
       <c r="B186" s="1" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="C186" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="187" spans="2:3">
       <c r="B187" s="1" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="C187" t="s">
-        <v>2225</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="188" spans="2:3">
       <c r="B188" s="1" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="C188" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="189" spans="2:3">
       <c r="B189" s="1" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C189" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="190" spans="2:3">
       <c r="B190" s="1" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="C190" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="191" spans="2:3">
       <c r="B191" s="1" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="C191" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="192" spans="2:3">
       <c r="B192" s="1" t="s">
-        <v>2173</v>
+        <v>2165</v>
       </c>
       <c r="C192" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="193" spans="2:3">
       <c r="B193" s="1" t="s">
-        <v>2174</v>
+        <v>2166</v>
       </c>
       <c r="C193" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="194" spans="2:3">
       <c r="B194" s="1" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="C194" t="s">
-        <v>2224</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="195" spans="2:3">
       <c r="B195" s="1" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="C195" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="196" spans="2:3">
       <c r="B196" s="1" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="C196" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="197" spans="2:3">
       <c r="B197" s="1" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="C197" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="198" spans="2:3">
       <c r="B198" s="1" t="s">
-        <v>2175</v>
+        <v>2167</v>
       </c>
       <c r="C198" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="199" spans="2:3">
       <c r="B199" s="1" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C199" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="200" spans="2:3">
       <c r="B200" s="1" t="s">
-        <v>2176</v>
+        <v>2168</v>
       </c>
       <c r="C200" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="201" spans="2:3">
       <c r="B201" s="1" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="C201" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="202" spans="2:3">
       <c r="B202" s="1" t="s">
-        <v>2177</v>
+        <v>2169</v>
       </c>
       <c r="C202" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="203" spans="2:3">
       <c r="B203" s="1" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="C203" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="204" spans="2:3">
       <c r="B204" s="1" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="C204" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="205" spans="2:3">
       <c r="B205" s="1" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="C205" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="206" spans="2:3">
       <c r="B206" s="1" t="s">
-        <v>2178</v>
+        <v>2170</v>
       </c>
       <c r="C206" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="207" spans="2:3">
       <c r="B207" s="1" t="s">
-        <v>2179</v>
+        <v>2171</v>
       </c>
       <c r="C207" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="208" spans="2:3">
       <c r="B208" s="1" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C208" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="209" spans="2:3">
@@ -11789,15 +11831,15 @@
         <v>980</v>
       </c>
       <c r="C209" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="210" spans="2:3">
       <c r="B210" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="C210" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="211" spans="2:3">
@@ -11805,47 +11847,47 @@
         <v>1227</v>
       </c>
       <c r="C211" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="212" spans="2:3">
       <c r="B212" s="1" t="s">
-        <v>2180</v>
+        <v>2172</v>
       </c>
       <c r="C212" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="213" spans="2:3">
       <c r="B213" s="1" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="C213" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="214" spans="2:3">
       <c r="B214" s="1" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="C214" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="215" spans="2:3">
       <c r="B215" s="1" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="C215" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="216" spans="2:3">
       <c r="B216" s="1" t="s">
-        <v>2181</v>
+        <v>2173</v>
       </c>
       <c r="C216" t="s">
-        <v>1994</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="217" spans="2:3">
@@ -11853,471 +11895,471 @@
         <v>1235</v>
       </c>
       <c r="C217" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="218" spans="2:3">
       <c r="B218" s="1" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="C218" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="219" spans="2:3">
       <c r="B219" s="1" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="C219" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="220" spans="2:3">
       <c r="B220" s="1" t="s">
-        <v>2182</v>
+        <v>2174</v>
       </c>
       <c r="C220" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="221" spans="2:3">
       <c r="B221" s="1" t="s">
-        <v>2183</v>
+        <v>2175</v>
       </c>
       <c r="C221" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="222" spans="2:3">
       <c r="B222" s="1" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C222" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="223" spans="2:3">
       <c r="B223" s="1" t="s">
-        <v>2184</v>
+        <v>2176</v>
       </c>
       <c r="C223" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="224" spans="2:3">
       <c r="B224" s="1" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C224" t="s">
-        <v>2006</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="225" spans="2:3">
       <c r="B225" s="1" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="C225" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="226" spans="2:3">
       <c r="B226" s="1" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="C226" t="s">
-        <v>2010</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="227" spans="2:3">
       <c r="B227" s="1" t="s">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C227" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="228" spans="2:3">
       <c r="B228" s="1" t="s">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="C228" t="s">
-        <v>2014</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="229" spans="2:3">
       <c r="B229" s="1" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C229" t="s">
-        <v>2016</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="2:3">
       <c r="B230" s="1" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C230" t="s">
-        <v>2018</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="231" spans="2:3">
       <c r="B231" s="1" t="s">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C231" t="s">
-        <v>2020</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="232" spans="2:3">
       <c r="B232" s="1" t="s">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C232" t="s">
-        <v>2022</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="233" spans="2:3">
       <c r="B233" s="1" t="s">
-        <v>2185</v>
+        <v>2177</v>
       </c>
       <c r="C233" t="s">
-        <v>2023</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="234" spans="2:3">
       <c r="B234" s="1" t="s">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="C234" t="s">
-        <v>2025</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="235" spans="2:3">
       <c r="B235" s="1" t="s">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="C235" t="s">
-        <v>2027</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="236" spans="2:3">
       <c r="B236" s="1" t="s">
-        <v>2028</v>
+        <v>2022</v>
       </c>
       <c r="C236" t="s">
-        <v>2029</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="237" spans="2:3">
       <c r="B237" s="1" t="s">
-        <v>2186</v>
+        <v>2178</v>
       </c>
       <c r="C237" t="s">
-        <v>2030</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="238" spans="2:3">
       <c r="B238" s="1" t="s">
-        <v>2031</v>
+        <v>2025</v>
       </c>
       <c r="C238" t="s">
-        <v>2032</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="239" spans="2:3">
       <c r="B239" s="1" t="s">
-        <v>2033</v>
+        <v>2027</v>
       </c>
       <c r="C239" t="s">
-        <v>2034</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="240" spans="2:3">
       <c r="B240" s="1" t="s">
-        <v>2035</v>
+        <v>2029</v>
       </c>
       <c r="C240" t="s">
-        <v>2036</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="241" spans="2:3">
       <c r="B241" s="1" t="s">
-        <v>2187</v>
+        <v>2179</v>
       </c>
       <c r="C241" t="s">
-        <v>2037</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="242" spans="2:3">
       <c r="B242" s="1" t="s">
-        <v>2188</v>
+        <v>2180</v>
       </c>
       <c r="C242" t="s">
-        <v>2038</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="243" spans="2:3">
       <c r="B243" s="1" t="s">
-        <v>2039</v>
+        <v>2033</v>
       </c>
       <c r="C243" t="s">
-        <v>2040</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="244" spans="2:3">
       <c r="B244" s="1" t="s">
-        <v>2041</v>
+        <v>2035</v>
       </c>
       <c r="C244" t="s">
-        <v>2042</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="245" spans="2:3">
       <c r="B245" s="1" t="s">
-        <v>2043</v>
+        <v>2037</v>
       </c>
       <c r="C245" t="s">
-        <v>2044</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="246" spans="2:3">
       <c r="B246" s="1" t="s">
-        <v>2189</v>
+        <v>2181</v>
       </c>
       <c r="C246" t="s">
-        <v>2045</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="247" spans="2:3">
       <c r="B247" s="1" t="s">
-        <v>2190</v>
+        <v>2182</v>
       </c>
       <c r="C247" t="s">
-        <v>2046</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="248" spans="2:3">
       <c r="B248" s="1" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="C248" t="s">
-        <v>2048</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="249" spans="2:3">
       <c r="B249" s="1" t="s">
-        <v>2191</v>
+        <v>2183</v>
       </c>
       <c r="C249" t="s">
-        <v>2049</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="250" spans="2:3">
       <c r="B250" s="1" t="s">
-        <v>2050</v>
+        <v>2043</v>
       </c>
       <c r="C250" t="s">
-        <v>2051</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="251" spans="2:3">
       <c r="B251" s="1" t="s">
-        <v>2192</v>
+        <v>2184</v>
       </c>
       <c r="C251" t="s">
-        <v>2052</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="252" spans="2:3">
       <c r="B252" s="1" t="s">
-        <v>2053</v>
+        <v>2046</v>
       </c>
       <c r="C252" t="s">
-        <v>2054</v>
+        <v>533</v>
       </c>
     </row>
     <row r="253" spans="2:3">
       <c r="B253" s="1" t="s">
-        <v>2055</v>
+        <v>2047</v>
       </c>
       <c r="C253" t="s">
-        <v>2056</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="254" spans="2:3">
       <c r="B254" s="1" t="s">
-        <v>2057</v>
+        <v>2049</v>
       </c>
       <c r="C254" t="s">
-        <v>2058</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="255" spans="2:3">
       <c r="B255" s="1" t="s">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="C255" t="s">
-        <v>2060</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="256" spans="2:3">
       <c r="B256" s="1" t="s">
-        <v>2061</v>
+        <v>2053</v>
       </c>
       <c r="C256" t="s">
-        <v>2062</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="257" spans="2:3">
       <c r="B257" s="1" t="s">
-        <v>2063</v>
+        <v>2055</v>
       </c>
       <c r="C257" t="s">
-        <v>2064</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="258" spans="2:3">
       <c r="B258" s="1" t="s">
-        <v>2193</v>
+        <v>2185</v>
       </c>
       <c r="C258" t="s">
-        <v>2065</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="259" spans="2:3">
       <c r="B259" s="1" t="s">
-        <v>2066</v>
+        <v>2058</v>
       </c>
       <c r="C259" t="s">
-        <v>2067</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="260" spans="2:3">
       <c r="B260" s="1" t="s">
-        <v>2194</v>
+        <v>2186</v>
       </c>
       <c r="C260" t="s">
-        <v>2068</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="261" spans="2:3">
       <c r="B261" s="1" t="s">
-        <v>2069</v>
+        <v>2061</v>
       </c>
       <c r="C261" t="s">
-        <v>2070</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="262" spans="2:3">
       <c r="B262" s="1" t="s">
-        <v>2071</v>
+        <v>2063</v>
       </c>
       <c r="C262" t="s">
-        <v>2072</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="263" spans="2:3">
       <c r="B263" s="1" t="s">
-        <v>2073</v>
+        <v>2065</v>
       </c>
       <c r="C263" t="s">
-        <v>2074</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="264" spans="2:3">
       <c r="B264" s="1" t="s">
-        <v>2075</v>
+        <v>2067</v>
       </c>
       <c r="C264" t="s">
-        <v>2076</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="265" spans="2:3">
       <c r="B265" s="1" t="s">
-        <v>2077</v>
+        <v>2069</v>
       </c>
       <c r="C265" t="s">
-        <v>2078</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="266" spans="2:3">
       <c r="B266" s="1" t="s">
-        <v>2079</v>
+        <v>2071</v>
       </c>
       <c r="C266" t="s">
-        <v>2080</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="267" spans="2:3">
       <c r="B267" s="1" t="s">
-        <v>2081</v>
+        <v>2073</v>
       </c>
       <c r="C267" t="s">
-        <v>2082</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="268" spans="2:3">
       <c r="B268" s="1" t="s">
-        <v>2195</v>
+        <v>2187</v>
       </c>
       <c r="C268" t="s">
-        <v>2083</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="269" spans="2:3">
       <c r="B269" s="1" t="s">
-        <v>2084</v>
+        <v>2076</v>
       </c>
       <c r="C269" t="s">
-        <v>2223</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="270" spans="2:3">
       <c r="B270" s="1" t="s">
-        <v>2085</v>
+        <v>2077</v>
       </c>
       <c r="C270" t="s">
-        <v>2086</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="271" spans="2:3">
       <c r="B271" s="1" t="s">
-        <v>2087</v>
+        <v>2079</v>
       </c>
       <c r="C271" t="s">
-        <v>2088</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="272" spans="2:3">
       <c r="B272" s="1" t="s">
-        <v>2089</v>
+        <v>2081</v>
       </c>
       <c r="C272" t="s">
-        <v>2090</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="273" spans="2:3">
       <c r="B273" s="1" t="s">
-        <v>2091</v>
+        <v>2083</v>
       </c>
       <c r="C273" t="s">
-        <v>2092</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="274" spans="2:3">
       <c r="B274" s="1" t="s">
-        <v>2093</v>
+        <v>2085</v>
       </c>
       <c r="C274" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="275" spans="2:3">
       <c r="B275" s="1" t="s">
-        <v>2095</v>
+        <v>2087</v>
       </c>
       <c r="C275" t="s">
-        <v>2096</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="276" spans="2:3">
@@ -12325,44 +12367,44 @@
         <v>492</v>
       </c>
       <c r="C276" t="s">
-        <v>2097</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="277" spans="2:3">
       <c r="B277" s="1" t="s">
-        <v>2098</v>
+        <v>2090</v>
       </c>
       <c r="C277" t="s">
-        <v>2099</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="278" spans="2:3">
       <c r="B278" s="1" t="s">
-        <v>2100</v>
+        <v>2092</v>
       </c>
       <c r="C278" t="s">
-        <v>2101</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="279" spans="2:3">
       <c r="B279" s="1" t="s">
-        <v>2102</v>
+        <v>2094</v>
       </c>
       <c r="C279" t="s">
-        <v>2103</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="280" spans="2:3">
       <c r="B280" s="1" t="s">
-        <v>2104</v>
+        <v>2096</v>
       </c>
       <c r="C280" t="s">
-        <v>2105</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="281" spans="2:3">
       <c r="B281" s="1" t="s">
-        <v>2106</v>
+        <v>2098</v>
       </c>
       <c r="C281" t="s">
         <v>1623</v>
@@ -12370,114 +12412,114 @@
     </row>
     <row r="282" spans="2:3">
       <c r="B282" s="1" t="s">
-        <v>2196</v>
+        <v>2188</v>
       </c>
       <c r="C282" t="s">
-        <v>2107</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="283" spans="2:3">
       <c r="B283" s="1" t="s">
-        <v>2108</v>
+        <v>2100</v>
       </c>
       <c r="C283" t="s">
-        <v>2109</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="284" spans="2:3">
       <c r="B284" s="1" t="s">
-        <v>2110</v>
+        <v>2102</v>
       </c>
       <c r="C284" t="s">
-        <v>2111</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="285" spans="2:3">
       <c r="B285" s="1" t="s">
-        <v>2112</v>
+        <v>2104</v>
       </c>
       <c r="C285" t="s">
-        <v>2113</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="286" spans="2:3">
       <c r="B286" s="1" t="s">
-        <v>2114</v>
+        <v>2106</v>
       </c>
       <c r="C286" t="s">
-        <v>2115</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="287" spans="2:3">
       <c r="B287" s="1" t="s">
-        <v>2116</v>
+        <v>2108</v>
       </c>
       <c r="C287" t="s">
-        <v>2117</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="288" spans="2:3">
       <c r="B288" s="1" t="s">
-        <v>2197</v>
+        <v>2189</v>
       </c>
       <c r="C288" t="s">
-        <v>2118</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="289" spans="2:3">
       <c r="B289" s="1" t="s">
-        <v>2119</v>
+        <v>2111</v>
       </c>
       <c r="C289" t="s">
-        <v>2120</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="290" spans="2:3">
       <c r="B290" s="1" t="s">
-        <v>2198</v>
+        <v>2190</v>
       </c>
       <c r="C290" t="s">
-        <v>2029</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="291" spans="2:3">
       <c r="B291" s="1" t="s">
-        <v>2199</v>
+        <v>2191</v>
       </c>
       <c r="C291" t="s">
-        <v>2121</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="292" spans="2:3">
       <c r="B292" s="1" t="s">
-        <v>2122</v>
+        <v>2114</v>
       </c>
       <c r="C292" t="s">
-        <v>2218</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="293" spans="2:3">
       <c r="B293" s="1" t="s">
-        <v>2200</v>
+        <v>2192</v>
       </c>
       <c r="C293" t="s">
-        <v>2201</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="294" spans="2:3">
       <c r="B294" s="1" t="s">
-        <v>2202</v>
+        <v>2194</v>
       </c>
       <c r="C294" t="s">
-        <v>2203</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="295" spans="2:3">
       <c r="B295" s="1" t="s">
-        <v>2204</v>
+        <v>2196</v>
       </c>
       <c r="C295" t="s">
-        <v>2205</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="296" spans="2:3">
@@ -12485,7 +12527,7 @@
         <v>320</v>
       </c>
       <c r="C296" t="s">
-        <v>2208</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="297" spans="2:3">
@@ -12493,133 +12535,165 @@
         <v>1628</v>
       </c>
       <c r="C297" t="s">
-        <v>2209</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="298" spans="2:3">
       <c r="B298" s="1" t="s">
-        <v>2206</v>
+        <v>2198</v>
       </c>
       <c r="C298" t="s">
-        <v>2207</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="299" spans="2:3">
       <c r="B299" s="35" t="s">
-        <v>2210</v>
+        <v>2202</v>
       </c>
       <c r="C299" t="s">
-        <v>2211</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="300" spans="2:3">
       <c r="B300" s="1" t="s">
-        <v>2212</v>
+        <v>2204</v>
       </c>
       <c r="C300" t="s">
-        <v>2213</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="301" spans="2:3">
       <c r="B301" s="35" t="s">
-        <v>2214</v>
+        <v>2206</v>
       </c>
       <c r="C301" t="s">
-        <v>2215</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="302" spans="2:3">
       <c r="B302" s="21" t="s">
-        <v>2237</v>
+        <v>2226</v>
       </c>
       <c r="C302" t="s">
-        <v>2238</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="303" spans="2:3">
       <c r="B303" s="21" t="s">
-        <v>2216</v>
+        <v>2208</v>
       </c>
       <c r="C303" t="s">
-        <v>2217</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="304" spans="2:3">
       <c r="B304" s="21" t="s">
-        <v>2219</v>
+        <v>2211</v>
       </c>
       <c r="C304" t="s">
-        <v>2222</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="B305" s="37" t="s">
-        <v>2220</v>
+        <v>2212</v>
       </c>
       <c r="C305" t="s">
-        <v>2221</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>2126</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="B307" s="1" t="s">
-        <v>2226</v>
+        <v>2218</v>
       </c>
       <c r="C307" t="s">
-        <v>2227</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="B308" s="1" t="s">
-        <v>2229</v>
+        <v>2221</v>
       </c>
       <c r="C308" t="s">
-        <v>2230</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="B309" s="1" t="s">
-        <v>2231</v>
+        <v>2223</v>
       </c>
       <c r="C309" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="B310" s="1" t="s">
-        <v>2232</v>
+        <v>2224</v>
       </c>
       <c r="C310" t="s">
-        <v>2235</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="B311" s="1" t="s">
-        <v>2233</v>
+        <v>2225</v>
       </c>
       <c r="C311" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="B312" s="1" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C312" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="B313" s="38" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C313" t="s">
         <v>2236</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="B314" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C314" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="B315" s="1" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C315" t="s">
+        <v>2240</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B70">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>RIGHT(B70,1)="?"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B296:B297">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>RIGHT(B296,1)="?"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13525,7 +13599,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>2127</v>
+        <v>2119</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -15084,7 +15158,7 @@
       </c>
       <c r="M6" s="6" t="str">
         <f>_xlfn.XLOOKUP(L6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>来?</v>
+        <v>来</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>329</v>
@@ -15752,7 +15826,7 @@
       </c>
       <c r="BE7" s="6" t="str">
         <f>_xlfn.XLOOKUP(BD7,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>養?</v>
+        <v>養</v>
       </c>
       <c r="BF7" s="7" t="s">
         <v>444</v>
@@ -16280,7 +16354,7 @@
       </c>
       <c r="BI8" s="6" t="str">
         <f>_xlfn.XLOOKUP(BH8,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>丁?</v>
+        <v>丁</v>
       </c>
       <c r="BJ8" s="7" t="s">
         <v>530</v>
@@ -16308,7 +16382,7 @@
       </c>
       <c r="BQ8" s="6" t="str">
         <f>_xlfn.XLOOKUP(BP8,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>新?</v>
+        <v>新</v>
       </c>
       <c r="BR8" s="7" t="s">
         <v>535</v>
@@ -18081,7 +18155,7 @@
       </c>
       <c r="EE11" s="6" t="str">
         <f>_xlfn.XLOOKUP(ED11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>◇</v>
+        <v>□?</v>
       </c>
       <c r="EF11" s="7" t="s">
         <v>817</v>
@@ -18392,7 +18466,7 @@
       </c>
       <c r="BY12" s="6" t="str">
         <f>_xlfn.XLOOKUP(BX12,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>最?</v>
+        <v>最</v>
       </c>
       <c r="BZ12" s="7" t="s">
         <v>866</v>
@@ -18420,7 +18494,7 @@
       </c>
       <c r="CG12" s="6" t="str">
         <f>_xlfn.XLOOKUP(CF12,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>■</v>
+        <v>■?</v>
       </c>
       <c r="CH12" s="7" t="s">
         <v>870</v>
@@ -18654,7 +18728,7 @@
       </c>
       <c r="E13" s="6" t="str" cm="1">
         <f t="array" ref="E13">_xlfn.XLOOKUP(D13,対応表!$B:B,対応表!$C:C," ")</f>
-        <v>受?</v>
+        <v>受</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>905</v>
@@ -18668,7 +18742,7 @@
       </c>
       <c r="I13" s="6" t="str">
         <f>_xlfn.XLOOKUP(H13,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>深?</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>907</v>
@@ -18710,7 +18784,7 @@
       </c>
       <c r="U13" s="6" t="str">
         <f>_xlfn.XLOOKUP(T13,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>防?</v>
       </c>
       <c r="V13" s="7" t="s">
         <v>913</v>
@@ -18906,7 +18980,7 @@
       </c>
       <c r="BY13" s="6" t="str">
         <f>_xlfn.XLOOKUP(BX13,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>中?</v>
+        <v>中</v>
       </c>
       <c r="BZ13" s="7" t="s">
         <v>945</v>
@@ -20518,7 +20592,7 @@
       </c>
       <c r="CS16" s="6" t="str">
         <f>_xlfn.XLOOKUP(CR16,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>苦?</v>
       </c>
       <c r="CT16" s="7" t="s">
         <v>1201</v>
@@ -20651,7 +20725,7 @@
       </c>
       <c r="EE16" s="6" t="str">
         <f>_xlfn.XLOOKUP(ED16,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>備?</v>
+        <v>備</v>
       </c>
       <c r="EF16" s="7" t="s">
         <v>1223</v>
@@ -20878,7 +20952,7 @@
       </c>
       <c r="BA17" s="6" t="str">
         <f>_xlfn.XLOOKUP(AZ17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>○われ</v>
+        <v>○?</v>
       </c>
       <c r="BB17" s="7" t="s">
         <v>1257</v>
@@ -22836,7 +22910,7 @@
       </c>
       <c r="Y21" s="6" t="str">
         <f>_xlfn.XLOOKUP(X21,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>飾?</v>
       </c>
       <c r="Z21" s="7" t="s">
         <v>1561</v>
@@ -23792,10 +23866,10 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>RIGHT(A1,1)="?"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23858,7 +23932,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
-        <v>2128</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D81FF0-192B-45CC-958A-04DCF1CFD43E}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C14C940-6F33-4A01-9E00-E11B84A5C0F0}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3852" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3867" uniqueCount="2259">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8534,9 +8534,6 @@
     <t>佃</t>
   </si>
   <si>
-    <t>持?</t>
-  </si>
-  <si>
     <t>俜</t>
   </si>
   <si>
@@ -8573,9 +8570,6 @@
     <t>剃</t>
   </si>
   <si>
-    <t>清?</t>
-  </si>
-  <si>
     <t>勇</t>
   </si>
   <si>
@@ -8640,9 +8634,6 @@
   </si>
   <si>
     <t>俯</t>
-  </si>
-  <si>
-    <t>指?</t>
   </si>
   <si>
     <t>創</t>
@@ -9357,6 +9348,82 @@
   </si>
   <si>
     <t>来</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勀</t>
+  </si>
+  <si>
+    <t>持</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>♦?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凄</t>
+  </si>
+  <si>
+    <t>房?</t>
+    <rPh sb="0" eb="1">
+      <t>フサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>准</t>
+  </si>
+  <si>
+    <t>凇</t>
+  </si>
+  <si>
+    <t>隔?</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>離?</t>
+    <rPh sb="0" eb="1">
+      <t>リ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亵刻</t>
+  </si>
+  <si>
+    <t>捌?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>刻</t>
+  </si>
+  <si>
+    <t>首?</t>
+    <rPh sb="0" eb="1">
+      <t>クビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斬?</t>
+    <rPh sb="0" eb="1">
+      <t>ザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>別</t>
+  </si>
+  <si>
+    <t>指</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>清</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9838,10 +9905,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -10159,7 +10222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:C315"/>
+  <dimension ref="A1:C322"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -10167,7 +10230,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -10412,7 +10475,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="1" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -10524,7 +10587,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="C46">
         <v>43</v>
@@ -10668,7 +10731,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" s="1" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="C64">
         <v>61</v>
@@ -10740,7 +10803,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="1" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="C73" t="s">
         <v>1777</v>
@@ -10820,7 +10883,7 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
       <c r="C83" t="s">
         <v>1795</v>
@@ -10836,7 +10899,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="1" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="C85" t="s">
         <v>1798</v>
@@ -10844,7 +10907,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
       <c r="C86" t="s">
         <v>1799</v>
@@ -10852,7 +10915,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="1" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="C87" t="s">
         <v>990</v>
@@ -10876,7 +10939,7 @@
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="1" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="C90" t="s">
         <v>1803</v>
@@ -10892,7 +10955,7 @@
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="1" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="C92" t="s">
         <v>827</v>
@@ -10924,7 +10987,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" s="1" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="C96" t="s">
         <v>1812</v>
@@ -10956,7 +11019,7 @@
     </row>
     <row r="100" spans="2:3">
       <c r="B100" s="1" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="C100" t="s">
         <v>832</v>
@@ -10972,7 +11035,7 @@
     </row>
     <row r="102" spans="2:3">
       <c r="B102" s="1" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="C102" t="s">
         <v>1820</v>
@@ -10980,7 +11043,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" s="1" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="C103" t="s">
         <v>1821</v>
@@ -10996,7 +11059,7 @@
     </row>
     <row r="105" spans="2:3">
       <c r="B105" s="1" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="C105" t="s">
         <v>1824</v>
@@ -11020,7 +11083,7 @@
     </row>
     <row r="108" spans="2:3">
       <c r="B108" s="1" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="C108" t="s">
         <v>1828</v>
@@ -11028,7 +11091,7 @@
     </row>
     <row r="109" spans="2:3">
       <c r="B109" s="1" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="C109" t="s">
         <v>1829</v>
@@ -11036,7 +11099,7 @@
     </row>
     <row r="110" spans="2:3">
       <c r="B110" s="1" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="C110" t="s">
         <v>1830</v>
@@ -11052,7 +11115,7 @@
     </row>
     <row r="112" spans="2:3">
       <c r="B112" s="1" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="C112" t="s">
         <v>1833</v>
@@ -11068,7 +11131,7 @@
     </row>
     <row r="114" spans="2:3">
       <c r="B114" s="1" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="C114" t="s">
         <v>1836</v>
@@ -11076,7 +11139,7 @@
     </row>
     <row r="115" spans="2:3">
       <c r="B115" s="1" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
       <c r="C115" t="s">
         <v>1837</v>
@@ -11084,7 +11147,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" s="1" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
       <c r="C116" t="s">
         <v>1838</v>
@@ -11100,7 +11163,7 @@
     </row>
     <row r="118" spans="2:3">
       <c r="B118" s="1" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="C118" t="s">
         <v>1840</v>
@@ -11116,7 +11179,7 @@
     </row>
     <row r="120" spans="2:3">
       <c r="B120" s="1" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="C120" t="s">
         <v>1843</v>
@@ -11132,7 +11195,7 @@
     </row>
     <row r="122" spans="2:3">
       <c r="B122" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C122" t="s">
         <v>1846</v>
@@ -11140,7 +11203,7 @@
     </row>
     <row r="123" spans="2:3">
       <c r="B123" s="1" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="C123" t="s">
         <v>1847</v>
@@ -11148,7 +11211,7 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C124" t="s">
         <v>1848</v>
@@ -11156,7 +11219,7 @@
     </row>
     <row r="125" spans="2:3">
       <c r="B125" s="1" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="C125" t="s">
         <v>1849</v>
@@ -11188,7 +11251,7 @@
     </row>
     <row r="129" spans="2:3">
       <c r="B129" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C129" t="s">
         <v>1856</v>
@@ -11212,7 +11275,7 @@
     </row>
     <row r="132" spans="2:3">
       <c r="B132" s="1" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="C132" t="s">
         <v>1860</v>
@@ -11228,7 +11291,7 @@
     </row>
     <row r="134" spans="2:3">
       <c r="B134" s="1" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="C134" t="s">
         <v>1862</v>
@@ -11236,7 +11299,7 @@
     </row>
     <row r="135" spans="2:3">
       <c r="B135" s="1" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="C135" t="s">
         <v>1863</v>
@@ -11244,7 +11307,7 @@
     </row>
     <row r="136" spans="2:3">
       <c r="B136" s="1" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="C136" t="s">
         <v>1864</v>
@@ -11292,7 +11355,7 @@
     </row>
     <row r="142" spans="2:3">
       <c r="B142" s="1" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C142" t="s">
         <v>1875</v>
@@ -11348,7 +11411,7 @@
     </row>
     <row r="149" spans="2:3">
       <c r="B149" s="1" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="C149" t="s">
         <v>1888</v>
@@ -11372,7 +11435,7 @@
     </row>
     <row r="152" spans="2:3">
       <c r="B152" s="1" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="C152" t="s">
         <v>1893</v>
@@ -11380,7 +11443,7 @@
     </row>
     <row r="153" spans="2:3">
       <c r="B153" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="C153" t="s">
         <v>1894</v>
@@ -11412,7 +11475,7 @@
     </row>
     <row r="157" spans="2:3">
       <c r="B157" s="1" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="C157" t="s">
         <v>1900</v>
@@ -11439,7 +11502,7 @@
         <v>1905</v>
       </c>
       <c r="C160" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="161" spans="2:3">
@@ -11452,7 +11515,7 @@
     </row>
     <row r="162" spans="2:3">
       <c r="B162" s="1" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="C162" t="s">
         <v>1908</v>
@@ -11476,7 +11539,7 @@
     </row>
     <row r="165" spans="2:3">
       <c r="B165" s="1" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="C165" t="s">
         <v>1913</v>
@@ -11492,7 +11555,7 @@
     </row>
     <row r="167" spans="2:3">
       <c r="B167" s="1" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="C167" t="s">
         <v>1916</v>
@@ -11540,7 +11603,7 @@
     </row>
     <row r="173" spans="2:3">
       <c r="B173" s="1" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="C173" t="s">
         <v>1926</v>
@@ -11551,7 +11614,7 @@
         <v>1927</v>
       </c>
       <c r="C174" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="175" spans="2:3">
@@ -11575,12 +11638,12 @@
         <v>1931</v>
       </c>
       <c r="C177" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="178" spans="2:3">
       <c r="B178" s="1" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="C178" t="s">
         <v>1932</v>
@@ -11620,7 +11683,7 @@
     </row>
     <row r="183" spans="2:3">
       <c r="B183" s="1" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
       <c r="C183" t="s">
         <v>1941</v>
@@ -11628,7 +11691,7 @@
     </row>
     <row r="184" spans="2:3">
       <c r="B184" s="1" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="C184" t="s">
         <v>1942</v>
@@ -11636,7 +11699,7 @@
     </row>
     <row r="185" spans="2:3">
       <c r="B185" s="1" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="C185" t="s">
         <v>1943</v>
@@ -11655,7 +11718,7 @@
         <v>1946</v>
       </c>
       <c r="C187" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="188" spans="2:3">
@@ -11692,7 +11755,7 @@
     </row>
     <row r="192" spans="2:3">
       <c r="B192" s="1" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="C192" t="s">
         <v>1955</v>
@@ -11700,7 +11763,7 @@
     </row>
     <row r="193" spans="2:3">
       <c r="B193" s="1" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C193" t="s">
         <v>1956</v>
@@ -11711,7 +11774,7 @@
         <v>1957</v>
       </c>
       <c r="C194" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="195" spans="2:3">
@@ -11740,7 +11803,7 @@
     </row>
     <row r="198" spans="2:3">
       <c r="B198" s="1" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C198" t="s">
         <v>1964</v>
@@ -11756,7 +11819,7 @@
     </row>
     <row r="200" spans="2:3">
       <c r="B200" s="1" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="C200" t="s">
         <v>1967</v>
@@ -11772,7 +11835,7 @@
     </row>
     <row r="202" spans="2:3">
       <c r="B202" s="1" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C202" t="s">
         <v>1970</v>
@@ -11804,7 +11867,7 @@
     </row>
     <row r="206" spans="2:3">
       <c r="B206" s="1" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="C206" t="s">
         <v>1977</v>
@@ -11812,7 +11875,7 @@
     </row>
     <row r="207" spans="2:3">
       <c r="B207" s="1" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="C207" t="s">
         <v>1978</v>
@@ -11852,7 +11915,7 @@
     </row>
     <row r="212" spans="2:3">
       <c r="B212" s="1" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="C212" t="s">
         <v>1985</v>
@@ -11884,10 +11947,10 @@
     </row>
     <row r="216" spans="2:3">
       <c r="B216" s="1" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="C216" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="217" spans="2:3">
@@ -11916,7 +11979,7 @@
     </row>
     <row r="220" spans="2:3">
       <c r="B220" s="1" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
       <c r="C220" t="s">
         <v>1997</v>
@@ -11924,7 +11987,7 @@
     </row>
     <row r="221" spans="2:3">
       <c r="B221" s="1" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
       <c r="C221" t="s">
         <v>1998</v>
@@ -11940,7 +12003,7 @@
     </row>
     <row r="223" spans="2:3">
       <c r="B223" s="1" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
       <c r="C223" t="s">
         <v>2001</v>
@@ -11951,7 +12014,7 @@
         <v>2002</v>
       </c>
       <c r="C224" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="225" spans="2:3">
@@ -11967,28 +12030,28 @@
         <v>2005</v>
       </c>
       <c r="C226" t="s">
-        <v>2006</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="227" spans="2:3">
       <c r="B227" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C227" t="s">
         <v>2007</v>
-      </c>
-      <c r="C227" t="s">
-        <v>2008</v>
       </c>
     </row>
     <row r="228" spans="2:3">
       <c r="B228" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C228" t="s">
         <v>2009</v>
-      </c>
-      <c r="C228" t="s">
-        <v>2010</v>
       </c>
     </row>
     <row r="229" spans="2:3">
       <c r="B229" s="1" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C229" t="s">
         <v>494</v>
@@ -11996,183 +12059,183 @@
     </row>
     <row r="230" spans="2:3">
       <c r="B230" s="1" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C230" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="231" spans="2:3">
       <c r="B231" s="1" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C231" t="s">
         <v>2013</v>
-      </c>
-      <c r="C231" t="s">
-        <v>2014</v>
       </c>
     </row>
     <row r="232" spans="2:3">
       <c r="B232" s="1" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C232" t="s">
         <v>2015</v>
-      </c>
-      <c r="C232" t="s">
-        <v>2016</v>
       </c>
     </row>
     <row r="233" spans="2:3">
       <c r="B233" s="1" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="C233" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="234" spans="2:3">
       <c r="B234" s="1" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C234" t="s">
-        <v>2019</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="235" spans="2:3">
       <c r="B235" s="1" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C235" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="236" spans="2:3">
       <c r="B236" s="1" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C236" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="237" spans="2:3">
       <c r="B237" s="1" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
       <c r="C237" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="238" spans="2:3">
       <c r="B238" s="1" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C238" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="239" spans="2:3">
       <c r="B239" s="1" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="C239" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="240" spans="2:3">
       <c r="B240" s="1" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="C240" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="241" spans="2:3">
       <c r="B241" s="1" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="C241" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="242" spans="2:3">
       <c r="B242" s="1" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="C242" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="243" spans="2:3">
       <c r="B243" s="1" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="C243" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="244" spans="2:3">
       <c r="B244" s="1" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="C244" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="245" spans="2:3">
       <c r="B245" s="1" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="C245" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="246" spans="2:3">
       <c r="B246" s="1" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="C246" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="247" spans="2:3">
       <c r="B247" s="1" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="C247" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="248" spans="2:3">
       <c r="B248" s="1" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="C248" t="s">
-        <v>2042</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="249" spans="2:3">
       <c r="B249" s="1" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="C249" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="250" spans="2:3">
       <c r="B250" s="1" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="C250" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="251" spans="2:3">
       <c r="B251" s="1" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="C251" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="252" spans="2:3">
       <c r="B252" s="1" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
       <c r="C252" t="s">
         <v>533</v>
@@ -12180,186 +12243,186 @@
     </row>
     <row r="253" spans="2:3">
       <c r="B253" s="1" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="C253" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="254" spans="2:3">
       <c r="B254" s="1" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
       <c r="C254" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="255" spans="2:3">
       <c r="B255" s="1" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="C255" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="256" spans="2:3">
       <c r="B256" s="1" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
       <c r="C256" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="257" spans="2:3">
       <c r="B257" s="1" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
       <c r="C257" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="258" spans="2:3">
       <c r="B258" s="1" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="C258" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="259" spans="2:3">
       <c r="B259" s="1" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="C259" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="260" spans="2:3">
       <c r="B260" s="1" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="C260" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="261" spans="2:3">
       <c r="B261" s="1" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="C261" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="262" spans="2:3">
       <c r="B262" s="1" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
       <c r="C262" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="263" spans="2:3">
       <c r="B263" s="1" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="C263" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="264" spans="2:3">
       <c r="B264" s="1" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="C264" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="265" spans="2:3">
       <c r="B265" s="1" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="C265" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="266" spans="2:3">
       <c r="B266" s="1" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="C266" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="267" spans="2:3">
       <c r="B267" s="1" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="C267" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="268" spans="2:3">
       <c r="B268" s="1" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="C268" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="269" spans="2:3">
       <c r="B269" s="1" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="C269" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="270" spans="2:3">
       <c r="B270" s="1" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="C270" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="271" spans="2:3">
       <c r="B271" s="1" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="C271" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="272" spans="2:3">
       <c r="B272" s="1" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="C272" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="273" spans="2:3">
       <c r="B273" s="1" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="C273" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="274" spans="2:3">
       <c r="B274" s="1" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="C274" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="275" spans="2:3">
       <c r="B275" s="1" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="C275" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="276" spans="2:3">
@@ -12367,44 +12430,44 @@
         <v>492</v>
       </c>
       <c r="C276" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="277" spans="2:3">
       <c r="B277" s="1" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="C277" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="278" spans="2:3">
       <c r="B278" s="1" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="C278" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="279" spans="2:3">
       <c r="B279" s="1" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
       <c r="C279" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="280" spans="2:3">
       <c r="B280" s="1" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="C280" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="281" spans="2:3">
       <c r="B281" s="1" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="C281" t="s">
         <v>1623</v>
@@ -12412,114 +12475,114 @@
     </row>
     <row r="282" spans="2:3">
       <c r="B282" s="1" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="C282" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="283" spans="2:3">
       <c r="B283" s="1" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="C283" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="284" spans="2:3">
       <c r="B284" s="1" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="C284" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="285" spans="2:3">
       <c r="B285" s="1" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="C285" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="286" spans="2:3">
       <c r="B286" s="1" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="C286" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="287" spans="2:3">
       <c r="B287" s="1" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="C287" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="288" spans="2:3">
       <c r="B288" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="C288" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="289" spans="2:3">
       <c r="B289" s="1" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="C289" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="290" spans="2:3">
       <c r="B290" s="1" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="C290" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="291" spans="2:3">
       <c r="B291" s="1" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="C291" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="292" spans="2:3">
       <c r="B292" s="1" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="C292" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="293" spans="2:3">
       <c r="B293" s="1" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="C293" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="294" spans="2:3">
       <c r="B294" s="1" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="C294" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="295" spans="2:3">
       <c r="B295" s="1" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="C295" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="296" spans="2:3">
@@ -12527,7 +12590,7 @@
         <v>320</v>
       </c>
       <c r="C296" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="297" spans="2:3">
@@ -12535,148 +12598,204 @@
         <v>1628</v>
       </c>
       <c r="C297" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="298" spans="2:3">
       <c r="B298" s="1" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C298" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="299" spans="2:3">
       <c r="B299" s="35" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="C299" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="300" spans="2:3">
       <c r="B300" s="1" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="C300" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="301" spans="2:3">
       <c r="B301" s="35" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="C301" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="302" spans="2:3">
       <c r="B302" s="21" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="C302" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="303" spans="2:3">
       <c r="B303" s="21" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="C303" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="304" spans="2:3">
       <c r="B304" s="21" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C304" t="s">
         <v>2211</v>
-      </c>
-      <c r="C304" t="s">
-        <v>2214</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="B305" s="37" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="C305" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="B307" s="1" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="C307" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="B308" s="1" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="C308" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="B309" s="1" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="C309" t="s">
         <v>2229</v>
       </c>
     </row>
     <row r="310" spans="1:3">
-      <c r="B310" s="1" t="s">
-        <v>2224</v>
+      <c r="B310" s="38" t="s">
+        <v>2232</v>
       </c>
       <c r="C310" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="B311" s="1" t="s">
-        <v>2225</v>
+        <v>2234</v>
       </c>
       <c r="C311" t="s">
-        <v>2231</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="B312" s="1" t="s">
-        <v>2228</v>
+        <v>2236</v>
       </c>
       <c r="C312" t="s">
-        <v>2232</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="313" spans="1:3">
-      <c r="B313" s="38" t="s">
-        <v>2235</v>
+      <c r="B313" s="1" t="s">
+        <v>2245</v>
       </c>
       <c r="C313" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="B314" s="1" t="s">
-        <v>2237</v>
+        <v>2247</v>
       </c>
       <c r="C314" t="s">
-        <v>2238</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="B315" s="1" t="s">
-        <v>2239</v>
+        <v>2248</v>
       </c>
       <c r="C315" t="s">
-        <v>2240</v>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="B316" s="1" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C316" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="B317" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C317" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="B318" s="1" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C318" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="B319" s="1" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C319" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="B320" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C320" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3">
+      <c r="B321" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C321" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="322" spans="2:3">
+      <c r="B322" s="1" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C322" t="s">
+        <v>2254</v>
       </c>
     </row>
   </sheetData>
@@ -13599,7 +13718,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -14158,7 +14277,7 @@
       </c>
       <c r="U4" s="6" t="str">
         <f>_xlfn.XLOOKUP(T4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>斬?</v>
       </c>
       <c r="V4" s="7" t="s">
         <v>172</v>
@@ -14466,7 +14585,7 @@
       </c>
       <c r="DE4" s="6" t="str">
         <f>_xlfn.XLOOKUP(DD4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>捌?</v>
       </c>
       <c r="DF4" s="7" t="s">
         <v>219</v>
@@ -15235,7 +15354,7 @@
       </c>
       <c r="AI6" s="6" t="str">
         <f>_xlfn.XLOOKUP(AH6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>持?</v>
+        <v>持</v>
       </c>
       <c r="AJ6" s="20" t="s">
         <v>344</v>
@@ -15501,7 +15620,7 @@
       </c>
       <c r="DG6" s="6" t="str">
         <f>_xlfn.XLOOKUP(DF6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>首?</v>
       </c>
       <c r="DH6" s="7" t="s">
         <v>390</v>
@@ -15973,7 +16092,7 @@
       </c>
       <c r="CU7" s="6" t="str">
         <f>_xlfn.XLOOKUP(CT7,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>房?</v>
       </c>
       <c r="CV7" s="7" t="s">
         <v>465</v>
@@ -17001,7 +17120,7 @@
       </c>
       <c r="CU9" s="6" t="str">
         <f>_xlfn.XLOOKUP(CT9,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>隔?</v>
       </c>
       <c r="CV9" s="7" t="s">
         <v>635</v>
@@ -17515,7 +17634,7 @@
       </c>
       <c r="CU10" s="6" t="str">
         <f>_xlfn.XLOOKUP(CT10,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>離?</v>
       </c>
       <c r="CV10" s="7" t="s">
         <v>716</v>
@@ -19613,7 +19732,7 @@
       </c>
       <c r="DG14" s="6" t="str">
         <f>_xlfn.XLOOKUP(DF14,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>清?</v>
+        <v>清</v>
       </c>
       <c r="DH14" s="7" t="s">
         <v>1048</v>
@@ -21459,7 +21578,7 @@
       </c>
       <c r="AY18" s="6" t="str">
         <f>_xlfn.XLOOKUP(AX18,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>指?</v>
+        <v>指</v>
       </c>
       <c r="AZ18" s="7" t="s">
         <v>1337</v>
@@ -22225,7 +22344,7 @@
       </c>
       <c r="DS19" s="6" t="str">
         <f>_xlfn.XLOOKUP(DR19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>♦?</v>
       </c>
       <c r="DT19" s="7" t="s">
         <v>1455</v>
@@ -23924,7 +24043,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A3841C-3E42-4AC2-9AD3-BA0FFE4A947C}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -23932,7 +24051,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="34" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -23978,6 +24097,11 @@
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
         <v>427</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>2251</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C14C940-6F33-4A01-9E00-E11B84A5C0F0}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7846591-E8DA-45E0-96F8-D60E71690043}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3867" uniqueCount="2259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3890" uniqueCount="2281">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8235,9 +8235,6 @@
   </si>
   <si>
     <t>冡</t>
-  </si>
-  <si>
-    <t>命?</t>
   </si>
   <si>
     <t>味</t>
@@ -9143,9 +9140,6 @@
     <t>两</t>
   </si>
   <si>
-    <t>掟?</t>
-  </si>
-  <si>
     <t>凳</t>
   </si>
   <si>
@@ -9392,9 +9386,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>亵刻</t>
-  </si>
-  <si>
     <t>捌?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -9424,6 +9415,112 @@
   </si>
   <si>
     <t>清</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亵刻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凾剑</t>
+  </si>
+  <si>
+    <t>匰儽</t>
+  </si>
+  <si>
+    <t>丣個僇亵乐卜丸亡</t>
+  </si>
+  <si>
+    <t>主別丟</t>
+  </si>
+  <si>
+    <t>勢丣</t>
+  </si>
+  <si>
+    <t>俚介</t>
+  </si>
+  <si>
+    <t>凗凘三</t>
+  </si>
+  <si>
+    <t>僌侫乏乐</t>
+  </si>
+  <si>
+    <t>乄偄卋</t>
+  </si>
+  <si>
+    <t>勻</t>
+  </si>
+  <si>
+    <t>守?</t>
+    <rPh sb="0" eb="1">
+      <t>マモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>匙</t>
+  </si>
+  <si>
+    <t>散?</t>
+    <rPh sb="0" eb="1">
+      <t>サン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>冟</t>
+  </si>
+  <si>
+    <t>劚</t>
+  </si>
+  <si>
+    <t>づ/付？</t>
+    <rPh sb="2" eb="3">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正?</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>命</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同?</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俚</t>
+  </si>
+  <si>
+    <t>噴?</t>
+    <rPh sb="0" eb="1">
+      <t>フン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>介</t>
+  </si>
+  <si>
+    <t>水?</t>
+    <rPh sb="0" eb="1">
+      <t>スイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>掟</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9431,7 +9528,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9605,6 +9702,27 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF333333"/>
+      <name val="Underground"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color rgb="FF333333"/>
+      <name val="Underground"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Underground"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -9699,7 +9817,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9817,6 +9935,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9903,6 +10030,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10222,7 +10353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C329"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -10230,7 +10361,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -10475,7 +10606,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -10587,7 +10718,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="C46">
         <v>43</v>
@@ -10731,7 +10862,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" s="1" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="C64">
         <v>61</v>
@@ -10803,7 +10934,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="C73" t="s">
         <v>1777</v>
@@ -10883,7 +11014,7 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C83" t="s">
         <v>1795</v>
@@ -10899,7 +11030,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="1" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="C85" t="s">
         <v>1798</v>
@@ -10907,7 +11038,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="1" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="C86" t="s">
         <v>1799</v>
@@ -10915,7 +11046,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="1" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="C87" t="s">
         <v>990</v>
@@ -10939,7 +11070,7 @@
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="C90" t="s">
         <v>1803</v>
@@ -10955,7 +11086,7 @@
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="1" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="C92" t="s">
         <v>827</v>
@@ -10987,7 +11118,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" s="1" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="C96" t="s">
         <v>1812</v>
@@ -11019,7 +11150,7 @@
     </row>
     <row r="100" spans="2:3">
       <c r="B100" s="1" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C100" t="s">
         <v>832</v>
@@ -11035,7 +11166,7 @@
     </row>
     <row r="102" spans="2:3">
       <c r="B102" s="1" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="C102" t="s">
         <v>1820</v>
@@ -11043,7 +11174,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" s="1" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C103" t="s">
         <v>1821</v>
@@ -11059,7 +11190,7 @@
     </row>
     <row r="105" spans="2:3">
       <c r="B105" s="1" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="C105" t="s">
         <v>1824</v>
@@ -11083,7 +11214,7 @@
     </row>
     <row r="108" spans="2:3">
       <c r="B108" s="1" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="C108" t="s">
         <v>1828</v>
@@ -11091,7 +11222,7 @@
     </row>
     <row r="109" spans="2:3">
       <c r="B109" s="1" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="C109" t="s">
         <v>1829</v>
@@ -11099,7 +11230,7 @@
     </row>
     <row r="110" spans="2:3">
       <c r="B110" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C110" t="s">
         <v>1830</v>
@@ -11115,7 +11246,7 @@
     </row>
     <row r="112" spans="2:3">
       <c r="B112" s="1" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="C112" t="s">
         <v>1833</v>
@@ -11131,7 +11262,7 @@
     </row>
     <row r="114" spans="2:3">
       <c r="B114" s="1" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C114" t="s">
         <v>1836</v>
@@ -11139,7 +11270,7 @@
     </row>
     <row r="115" spans="2:3">
       <c r="B115" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C115" t="s">
         <v>1837</v>
@@ -11147,7 +11278,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C116" t="s">
         <v>1838</v>
@@ -11163,7 +11294,7 @@
     </row>
     <row r="118" spans="2:3">
       <c r="B118" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C118" t="s">
         <v>1840</v>
@@ -11179,7 +11310,7 @@
     </row>
     <row r="120" spans="2:3">
       <c r="B120" s="1" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="C120" t="s">
         <v>1843</v>
@@ -11195,7 +11326,7 @@
     </row>
     <row r="122" spans="2:3">
       <c r="B122" s="1" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C122" t="s">
         <v>1846</v>
@@ -11203,7 +11334,7 @@
     </row>
     <row r="123" spans="2:3">
       <c r="B123" s="1" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="C123" t="s">
         <v>1847</v>
@@ -11211,7 +11342,7 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C124" t="s">
         <v>1848</v>
@@ -11219,7 +11350,7 @@
     </row>
     <row r="125" spans="2:3">
       <c r="B125" s="1" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="C125" t="s">
         <v>1849</v>
@@ -11251,7 +11382,7 @@
     </row>
     <row r="129" spans="2:3">
       <c r="B129" s="1" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C129" t="s">
         <v>1856</v>
@@ -11275,7 +11406,7 @@
     </row>
     <row r="132" spans="2:3">
       <c r="B132" s="1" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="C132" t="s">
         <v>1860</v>
@@ -11291,7 +11422,7 @@
     </row>
     <row r="134" spans="2:3">
       <c r="B134" s="1" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="C134" t="s">
         <v>1862</v>
@@ -11299,7 +11430,7 @@
     </row>
     <row r="135" spans="2:3">
       <c r="B135" s="1" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="C135" t="s">
         <v>1863</v>
@@ -11307,7 +11438,7 @@
     </row>
     <row r="136" spans="2:3">
       <c r="B136" s="1" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="C136" t="s">
         <v>1864</v>
@@ -11355,7 +11486,7 @@
     </row>
     <row r="142" spans="2:3">
       <c r="B142" s="1" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="C142" t="s">
         <v>1875</v>
@@ -11411,7 +11542,7 @@
     </row>
     <row r="149" spans="2:3">
       <c r="B149" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="C149" t="s">
         <v>1888</v>
@@ -11435,7 +11566,7 @@
     </row>
     <row r="152" spans="2:3">
       <c r="B152" s="1" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="C152" t="s">
         <v>1893</v>
@@ -11443,7 +11574,7 @@
     </row>
     <row r="153" spans="2:3">
       <c r="B153" s="1" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C153" t="s">
         <v>1894</v>
@@ -11475,7 +11606,7 @@
     </row>
     <row r="157" spans="2:3">
       <c r="B157" s="1" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="C157" t="s">
         <v>1900</v>
@@ -11502,7 +11633,7 @@
         <v>1905</v>
       </c>
       <c r="C160" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="161" spans="2:3">
@@ -11510,92 +11641,92 @@
         <v>1906</v>
       </c>
       <c r="C161" t="s">
-        <v>1907</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="162" spans="2:3">
       <c r="B162" s="1" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="C162" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="163" spans="2:3">
       <c r="B163" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C163" t="s">
         <v>1909</v>
-      </c>
-      <c r="C163" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="164" spans="2:3">
       <c r="B164" s="1" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C164" t="s">
         <v>1911</v>
-      </c>
-      <c r="C164" t="s">
-        <v>1912</v>
       </c>
     </row>
     <row r="165" spans="2:3">
       <c r="B165" s="1" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="C165" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="166" spans="2:3">
       <c r="B166" s="1" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C166" t="s">
         <v>1914</v>
-      </c>
-      <c r="C166" t="s">
-        <v>1915</v>
       </c>
     </row>
     <row r="167" spans="2:3">
       <c r="B167" s="1" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C167" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="168" spans="2:3">
       <c r="B168" s="1" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C168" t="s">
         <v>1917</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1918</v>
       </c>
     </row>
     <row r="169" spans="2:3">
       <c r="B169" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C169" t="s">
         <v>1919</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1920</v>
       </c>
     </row>
     <row r="170" spans="2:3">
       <c r="B170" s="1" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C170" t="s">
         <v>1921</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1922</v>
       </c>
     </row>
     <row r="171" spans="2:3">
       <c r="B171" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C171" t="s">
         <v>1923</v>
-      </c>
-      <c r="C171" t="s">
-        <v>1924</v>
       </c>
     </row>
     <row r="172" spans="2:3">
       <c r="B172" s="1" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C172" t="s">
         <v>72</v>
@@ -11603,31 +11734,31 @@
     </row>
     <row r="173" spans="2:3">
       <c r="B173" s="1" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="C173" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="174" spans="2:3">
       <c r="B174" s="1" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C174" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="175" spans="2:3">
       <c r="B175" s="1" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C175" t="s">
         <v>1928</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1929</v>
       </c>
     </row>
     <row r="176" spans="2:3">
       <c r="B176" s="1" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="C176" t="s">
         <v>980</v>
@@ -11635,258 +11766,258 @@
     </row>
     <row r="177" spans="2:3">
       <c r="B177" s="1" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="C177" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="178" spans="2:3">
       <c r="B178" s="1" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="C178" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="179" spans="2:3">
       <c r="B179" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C179" t="s">
         <v>1933</v>
-      </c>
-      <c r="C179" t="s">
-        <v>1934</v>
       </c>
     </row>
     <row r="180" spans="2:3">
       <c r="B180" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C180" t="s">
         <v>1935</v>
-      </c>
-      <c r="C180" t="s">
-        <v>1936</v>
       </c>
     </row>
     <row r="181" spans="2:3">
       <c r="B181" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C181" t="s">
         <v>1937</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="182" spans="2:3">
       <c r="B182" s="1" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C182" t="s">
         <v>1939</v>
-      </c>
-      <c r="C182" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="183" spans="2:3">
       <c r="B183" s="1" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C183" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="184" spans="2:3">
       <c r="B184" s="1" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="C184" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="185" spans="2:3">
       <c r="B185" s="1" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="C185" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="186" spans="2:3">
       <c r="B186" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C186" t="s">
         <v>1944</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1945</v>
       </c>
     </row>
     <row r="187" spans="2:3">
       <c r="B187" s="1" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C187" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="188" spans="2:3">
       <c r="B188" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C188" t="s">
         <v>1947</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="189" spans="2:3">
       <c r="B189" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C189" t="s">
         <v>1949</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="190" spans="2:3">
       <c r="B190" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C190" t="s">
         <v>1951</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="191" spans="2:3">
       <c r="B191" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C191" t="s">
         <v>1953</v>
-      </c>
-      <c r="C191" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="192" spans="2:3">
       <c r="B192" s="1" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="C192" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="193" spans="2:3">
       <c r="B193" s="1" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C193" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="194" spans="2:3">
       <c r="B194" s="1" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C194" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="195" spans="2:3">
       <c r="B195" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C195" t="s">
         <v>1958</v>
-      </c>
-      <c r="C195" t="s">
-        <v>1959</v>
       </c>
     </row>
     <row r="196" spans="2:3">
       <c r="B196" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C196" t="s">
         <v>1960</v>
-      </c>
-      <c r="C196" t="s">
-        <v>1961</v>
       </c>
     </row>
     <row r="197" spans="2:3">
       <c r="B197" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C197" t="s">
         <v>1962</v>
-      </c>
-      <c r="C197" t="s">
-        <v>1963</v>
       </c>
     </row>
     <row r="198" spans="2:3">
       <c r="B198" s="1" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="C198" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="199" spans="2:3">
       <c r="B199" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C199" t="s">
         <v>1965</v>
-      </c>
-      <c r="C199" t="s">
-        <v>1966</v>
       </c>
     </row>
     <row r="200" spans="2:3">
       <c r="B200" s="1" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="C200" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="201" spans="2:3">
       <c r="B201" s="1" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C201" t="s">
         <v>1968</v>
-      </c>
-      <c r="C201" t="s">
-        <v>1969</v>
       </c>
     </row>
     <row r="202" spans="2:3">
       <c r="B202" s="1" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C202" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="203" spans="2:3">
       <c r="B203" s="1" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C203" t="s">
         <v>1971</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1972</v>
       </c>
     </row>
     <row r="204" spans="2:3">
       <c r="B204" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C204" t="s">
         <v>1973</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1974</v>
       </c>
     </row>
     <row r="205" spans="2:3">
       <c r="B205" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C205" t="s">
         <v>1975</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1976</v>
       </c>
     </row>
     <row r="206" spans="2:3">
       <c r="B206" s="1" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="C206" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="207" spans="2:3">
       <c r="B207" s="1" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="C207" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="208" spans="2:3">
       <c r="B208" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C208" t="s">
         <v>1979</v>
-      </c>
-      <c r="C208" t="s">
-        <v>1980</v>
       </c>
     </row>
     <row r="209" spans="2:3">
@@ -11894,15 +12025,15 @@
         <v>980</v>
       </c>
       <c r="C209" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="210" spans="2:3">
       <c r="B210" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C210" t="s">
         <v>1982</v>
-      </c>
-      <c r="C210" t="s">
-        <v>1983</v>
       </c>
     </row>
     <row r="211" spans="2:3">
@@ -11910,47 +12041,47 @@
         <v>1227</v>
       </c>
       <c r="C211" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="212" spans="2:3">
       <c r="B212" s="1" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="C212" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="213" spans="2:3">
       <c r="B213" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C213" t="s">
         <v>1986</v>
-      </c>
-      <c r="C213" t="s">
-        <v>1987</v>
       </c>
     </row>
     <row r="214" spans="2:3">
       <c r="B214" s="1" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C214" t="s">
         <v>1988</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1989</v>
       </c>
     </row>
     <row r="215" spans="2:3">
       <c r="B215" s="1" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C215" t="s">
         <v>1990</v>
-      </c>
-      <c r="C215" t="s">
-        <v>1991</v>
       </c>
     </row>
     <row r="216" spans="2:3">
       <c r="B216" s="1" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="C216" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="217" spans="2:3">
@@ -11958,100 +12089,100 @@
         <v>1235</v>
       </c>
       <c r="C217" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="218" spans="2:3">
       <c r="B218" s="1" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C218" t="s">
         <v>1993</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1994</v>
       </c>
     </row>
     <row r="219" spans="2:3">
       <c r="B219" s="1" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C219" t="s">
         <v>1995</v>
-      </c>
-      <c r="C219" t="s">
-        <v>1996</v>
       </c>
     </row>
     <row r="220" spans="2:3">
       <c r="B220" s="1" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="C220" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="221" spans="2:3">
       <c r="B221" s="1" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="C221" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="222" spans="2:3">
       <c r="B222" s="1" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C222" t="s">
         <v>1999</v>
-      </c>
-      <c r="C222" t="s">
-        <v>2000</v>
       </c>
     </row>
     <row r="223" spans="2:3">
       <c r="B223" s="1" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="C223" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="224" spans="2:3">
       <c r="B224" s="1" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C224" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="225" spans="2:3">
       <c r="B225" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C225" t="s">
         <v>2003</v>
-      </c>
-      <c r="C225" t="s">
-        <v>2004</v>
       </c>
     </row>
     <row r="226" spans="2:3">
       <c r="B226" s="1" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C226" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="227" spans="2:3">
       <c r="B227" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C227" t="s">
         <v>2006</v>
-      </c>
-      <c r="C227" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="228" spans="2:3">
       <c r="B228" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C228" t="s">
         <v>2008</v>
-      </c>
-      <c r="C228" t="s">
-        <v>2009</v>
       </c>
     </row>
     <row r="229" spans="2:3">
       <c r="B229" s="1" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C229" t="s">
         <v>494</v>
@@ -12059,183 +12190,183 @@
     </row>
     <row r="230" spans="2:3">
       <c r="B230" s="1" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C230" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="231" spans="2:3">
       <c r="B231" s="1" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C231" t="s">
         <v>2012</v>
-      </c>
-      <c r="C231" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="232" spans="2:3">
       <c r="B232" s="1" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C232" t="s">
         <v>2014</v>
-      </c>
-      <c r="C232" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="233" spans="2:3">
       <c r="B233" s="1" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="C233" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="234" spans="2:3">
       <c r="B234" s="1" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C234" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="235" spans="2:3">
       <c r="B235" s="1" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C235" t="s">
         <v>2018</v>
-      </c>
-      <c r="C235" t="s">
-        <v>2019</v>
       </c>
     </row>
     <row r="236" spans="2:3">
       <c r="B236" s="1" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C236" t="s">
         <v>2020</v>
-      </c>
-      <c r="C236" t="s">
-        <v>2021</v>
       </c>
     </row>
     <row r="237" spans="2:3">
       <c r="B237" s="1" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C237" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="238" spans="2:3">
       <c r="B238" s="1" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C238" t="s">
         <v>2023</v>
-      </c>
-      <c r="C238" t="s">
-        <v>2024</v>
       </c>
     </row>
     <row r="239" spans="2:3">
       <c r="B239" s="1" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C239" t="s">
         <v>2025</v>
-      </c>
-      <c r="C239" t="s">
-        <v>2026</v>
       </c>
     </row>
     <row r="240" spans="2:3">
       <c r="B240" s="1" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C240" t="s">
         <v>2027</v>
-      </c>
-      <c r="C240" t="s">
-        <v>2028</v>
       </c>
     </row>
     <row r="241" spans="2:3">
       <c r="B241" s="1" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="C241" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="242" spans="2:3">
       <c r="B242" s="1" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="C242" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="243" spans="2:3">
       <c r="B243" s="1" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C243" t="s">
         <v>2031</v>
-      </c>
-      <c r="C243" t="s">
-        <v>2032</v>
       </c>
     </row>
     <row r="244" spans="2:3">
       <c r="B244" s="1" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C244" t="s">
         <v>2033</v>
-      </c>
-      <c r="C244" t="s">
-        <v>2034</v>
       </c>
     </row>
     <row r="245" spans="2:3">
       <c r="B245" s="1" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C245" t="s">
         <v>2035</v>
-      </c>
-      <c r="C245" t="s">
-        <v>2036</v>
       </c>
     </row>
     <row r="246" spans="2:3">
       <c r="B246" s="1" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="C246" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="247" spans="2:3">
       <c r="B247" s="1" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="C247" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="248" spans="2:3">
       <c r="B248" s="1" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="C248" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="249" spans="2:3">
       <c r="B249" s="1" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="C249" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="250" spans="2:3">
       <c r="B250" s="1" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C250" t="s">
         <v>2040</v>
-      </c>
-      <c r="C250" t="s">
-        <v>2041</v>
       </c>
     </row>
     <row r="251" spans="2:3">
       <c r="B251" s="1" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="C251" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="252" spans="2:3">
       <c r="B252" s="1" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="C252" t="s">
         <v>533</v>
@@ -12243,186 +12374,186 @@
     </row>
     <row r="253" spans="2:3">
       <c r="B253" s="1" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C253" t="s">
         <v>2044</v>
-      </c>
-      <c r="C253" t="s">
-        <v>2045</v>
       </c>
     </row>
     <row r="254" spans="2:3">
       <c r="B254" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C254" t="s">
         <v>2046</v>
-      </c>
-      <c r="C254" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="255" spans="2:3">
       <c r="B255" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C255" t="s">
         <v>2048</v>
-      </c>
-      <c r="C255" t="s">
-        <v>2049</v>
       </c>
     </row>
     <row r="256" spans="2:3">
       <c r="B256" s="1" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C256" t="s">
         <v>2050</v>
-      </c>
-      <c r="C256" t="s">
-        <v>2051</v>
       </c>
     </row>
     <row r="257" spans="2:3">
       <c r="B257" s="1" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C257" t="s">
         <v>2052</v>
-      </c>
-      <c r="C257" t="s">
-        <v>2053</v>
       </c>
     </row>
     <row r="258" spans="2:3">
       <c r="B258" s="1" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="C258" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="259" spans="2:3">
       <c r="B259" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C259" t="s">
         <v>2055</v>
-      </c>
-      <c r="C259" t="s">
-        <v>2056</v>
       </c>
     </row>
     <row r="260" spans="2:3">
       <c r="B260" s="1" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="C260" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="261" spans="2:3">
       <c r="B261" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C261" t="s">
         <v>2058</v>
-      </c>
-      <c r="C261" t="s">
-        <v>2059</v>
       </c>
     </row>
     <row r="262" spans="2:3">
       <c r="B262" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C262" t="s">
         <v>2060</v>
-      </c>
-      <c r="C262" t="s">
-        <v>2061</v>
       </c>
     </row>
     <row r="263" spans="2:3">
       <c r="B263" s="1" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C263" t="s">
         <v>2062</v>
-      </c>
-      <c r="C263" t="s">
-        <v>2063</v>
       </c>
     </row>
     <row r="264" spans="2:3">
       <c r="B264" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C264" t="s">
         <v>2064</v>
-      </c>
-      <c r="C264" t="s">
-        <v>2065</v>
       </c>
     </row>
     <row r="265" spans="2:3">
       <c r="B265" s="1" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C265" t="s">
         <v>2066</v>
-      </c>
-      <c r="C265" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="266" spans="2:3">
       <c r="B266" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C266" t="s">
         <v>2068</v>
-      </c>
-      <c r="C266" t="s">
-        <v>2069</v>
       </c>
     </row>
     <row r="267" spans="2:3">
       <c r="B267" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C267" t="s">
         <v>2070</v>
-      </c>
-      <c r="C267" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="268" spans="2:3">
       <c r="B268" s="1" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="C268" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="269" spans="2:3">
       <c r="B269" s="1" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="C269" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="270" spans="2:3">
       <c r="B270" s="1" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C270" t="s">
         <v>2074</v>
-      </c>
-      <c r="C270" t="s">
-        <v>2075</v>
       </c>
     </row>
     <row r="271" spans="2:3">
       <c r="B271" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C271" t="s">
         <v>2076</v>
-      </c>
-      <c r="C271" t="s">
-        <v>2077</v>
       </c>
     </row>
     <row r="272" spans="2:3">
       <c r="B272" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C272" t="s">
         <v>2078</v>
-      </c>
-      <c r="C272" t="s">
-        <v>2079</v>
       </c>
     </row>
     <row r="273" spans="2:3">
       <c r="B273" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C273" t="s">
         <v>2080</v>
-      </c>
-      <c r="C273" t="s">
-        <v>2081</v>
       </c>
     </row>
     <row r="274" spans="2:3">
       <c r="B274" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C274" t="s">
         <v>2082</v>
-      </c>
-      <c r="C274" t="s">
-        <v>2083</v>
       </c>
     </row>
     <row r="275" spans="2:3">
       <c r="B275" s="1" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C275" t="s">
         <v>2084</v>
-      </c>
-      <c r="C275" t="s">
-        <v>2085</v>
       </c>
     </row>
     <row r="276" spans="2:3">
@@ -12430,44 +12561,44 @@
         <v>492</v>
       </c>
       <c r="C276" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="277" spans="2:3">
       <c r="B277" s="1" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C277" t="s">
         <v>2087</v>
-      </c>
-      <c r="C277" t="s">
-        <v>2088</v>
       </c>
     </row>
     <row r="278" spans="2:3">
       <c r="B278" s="1" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C278" t="s">
         <v>2089</v>
-      </c>
-      <c r="C278" t="s">
-        <v>2090</v>
       </c>
     </row>
     <row r="279" spans="2:3">
       <c r="B279" s="1" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C279" t="s">
         <v>2091</v>
-      </c>
-      <c r="C279" t="s">
-        <v>2092</v>
       </c>
     </row>
     <row r="280" spans="2:3">
       <c r="B280" s="1" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C280" t="s">
         <v>2093</v>
-      </c>
-      <c r="C280" t="s">
-        <v>2094</v>
       </c>
     </row>
     <row r="281" spans="2:3">
       <c r="B281" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="C281" t="s">
         <v>1623</v>
@@ -12475,114 +12606,114 @@
     </row>
     <row r="282" spans="2:3">
       <c r="B282" s="1" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="C282" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="283" spans="2:3">
       <c r="B283" s="1" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C283" t="s">
         <v>2097</v>
-      </c>
-      <c r="C283" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="284" spans="2:3">
       <c r="B284" s="1" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C284" t="s">
         <v>2099</v>
-      </c>
-      <c r="C284" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="285" spans="2:3">
       <c r="B285" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C285" t="s">
         <v>2101</v>
-      </c>
-      <c r="C285" t="s">
-        <v>2102</v>
       </c>
     </row>
     <row r="286" spans="2:3">
       <c r="B286" s="1" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C286" t="s">
         <v>2103</v>
-      </c>
-      <c r="C286" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="287" spans="2:3">
       <c r="B287" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C287" t="s">
         <v>2105</v>
-      </c>
-      <c r="C287" t="s">
-        <v>2106</v>
       </c>
     </row>
     <row r="288" spans="2:3">
       <c r="B288" s="1" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="C288" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="289" spans="2:3">
       <c r="B289" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C289" t="s">
         <v>2108</v>
-      </c>
-      <c r="C289" t="s">
-        <v>2109</v>
       </c>
     </row>
     <row r="290" spans="2:3">
       <c r="B290" s="1" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="C290" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="291" spans="2:3">
       <c r="B291" s="1" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="C291" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="292" spans="2:3">
       <c r="B292" s="1" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C292" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="293" spans="2:3">
       <c r="B293" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C293" t="s">
         <v>2189</v>
-      </c>
-      <c r="C293" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="294" spans="2:3">
       <c r="B294" s="1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C294" t="s">
         <v>2191</v>
-      </c>
-      <c r="C294" t="s">
-        <v>2192</v>
       </c>
     </row>
     <row r="295" spans="2:3">
       <c r="B295" s="1" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="C295" t="s">
-        <v>2194</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="296" spans="2:3">
@@ -12590,7 +12721,7 @@
         <v>320</v>
       </c>
       <c r="C296" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="297" spans="2:3">
@@ -12598,111 +12729,114 @@
         <v>1628</v>
       </c>
       <c r="C297" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="298" spans="2:3">
       <c r="B298" s="1" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="C298" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="299" spans="2:3">
       <c r="B299" s="35" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C299" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="300" spans="2:3">
       <c r="B300" s="1" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C300" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="301" spans="2:3">
       <c r="B301" s="35" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C301" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="302" spans="2:3">
       <c r="B302" s="21" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="C302" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="303" spans="2:3">
       <c r="B303" s="21" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C303" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="304" spans="2:3">
       <c r="B304" s="21" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C304" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3">
+      <c r="B305" s="37" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C305" t="s">
         <v>2208</v>
       </c>
-      <c r="C304" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3">
-      <c r="B305" s="37" t="s">
-        <v>2209</v>
-      </c>
-      <c r="C305" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3">
-      <c r="A306" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3">
+    </row>
+    <row r="306" spans="2:3">
+      <c r="B306" s="1" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3">
       <c r="B307" s="1" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="C307" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3">
       <c r="B308" s="1" t="s">
-        <v>2218</v>
+        <v>2223</v>
       </c>
       <c r="C308" t="s">
-        <v>2219</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3">
-      <c r="B309" s="1" t="s">
-        <v>2225</v>
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3">
+      <c r="B309" s="38" t="s">
+        <v>2230</v>
       </c>
       <c r="C309" t="s">
-        <v>2229</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3">
-      <c r="B310" s="38" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="310" spans="2:3">
+      <c r="B310" s="1" t="s">
         <v>2232</v>
       </c>
       <c r="C310" t="s">
         <v>2233</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="2:3">
       <c r="B311" s="1" t="s">
         <v>2234</v>
       </c>
@@ -12710,92 +12844,145 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="312" spans="1:3">
+    <row r="312" spans="2:3">
       <c r="B312" s="1" t="s">
-        <v>2236</v>
+        <v>2243</v>
       </c>
       <c r="C312" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3">
       <c r="B313" s="1" t="s">
         <v>2245</v>
       </c>
       <c r="C313" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3">
+      <c r="B314" s="1" t="s">
         <v>2246</v>
       </c>
-    </row>
-    <row r="314" spans="1:3">
-      <c r="B314" s="1" t="s">
-        <v>2247</v>
-      </c>
       <c r="C314" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3">
+      <c r="B315" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C315" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3">
+      <c r="B316" s="1" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C316" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3">
+      <c r="B317" s="1" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C317" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="318" spans="2:3">
+      <c r="B318" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C318" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3">
+      <c r="B319" s="1" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C319" t="s">
         <v>2249</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
-      <c r="B315" s="1" t="s">
-        <v>2248</v>
-      </c>
-      <c r="C315" t="s">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3">
-      <c r="B316" s="1" t="s">
-        <v>2242</v>
-      </c>
-      <c r="C316" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3">
-      <c r="B317" s="1" t="s">
-        <v>2220</v>
-      </c>
-      <c r="C317" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3">
-      <c r="B318" s="1" t="s">
-        <v>2221</v>
-      </c>
-      <c r="C318" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3">
-      <c r="B319" s="1" t="s">
-        <v>2222</v>
-      </c>
-      <c r="C319" t="s">
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="2:3">
       <c r="B320" s="1" t="s">
-        <v>2256</v>
+        <v>171</v>
       </c>
       <c r="C320" t="s">
         <v>2252</v>
       </c>
     </row>
-    <row r="321" spans="2:3">
+    <row r="321" spans="1:3">
       <c r="B321" s="1" t="s">
-        <v>171</v>
+        <v>2250</v>
       </c>
       <c r="C321" t="s">
-        <v>2255</v>
-      </c>
-    </row>
-    <row r="322" spans="2:3">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
       <c r="B322" s="1" t="s">
-        <v>2253</v>
+        <v>2266</v>
       </c>
       <c r="C322" t="s">
-        <v>2254</v>
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="B323" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C323" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="B324" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C324" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="B325" s="41" t="s">
+        <v>942</v>
+      </c>
+      <c r="C325" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="B326" s="1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C326" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="B327" s="1" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C327" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="B328" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C328" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" t="s">
+        <v>2114</v>
       </c>
     </row>
   </sheetData>
@@ -13718,7 +13905,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -15312,7 +15499,7 @@
       </c>
       <c r="W6" s="6" t="str">
         <f>_xlfn.XLOOKUP(V6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>水?</v>
       </c>
       <c r="X6" s="20" t="s">
         <v>337</v>
@@ -16725,7 +16912,7 @@
       </c>
       <c r="EC8" s="6" t="str">
         <f>_xlfn.XLOOKUP(EB8,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>散?</v>
       </c>
       <c r="ED8" s="7" t="s">
         <v>569</v>
@@ -17620,7 +17807,7 @@
       </c>
       <c r="CQ10" s="6" t="str">
         <f>_xlfn.XLOOKUP(CP10,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>づ/付？</v>
       </c>
       <c r="CR10" s="7" t="s">
         <v>714</v>
@@ -18648,7 +18835,7 @@
       </c>
       <c r="CQ12" s="6" t="str">
         <f>_xlfn.XLOOKUP(CP12,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>命?</v>
+        <v>命</v>
       </c>
       <c r="CR12" s="7" t="s">
         <v>876</v>
@@ -19092,7 +19279,7 @@
       </c>
       <c r="BW13" s="6" t="str">
         <f>_xlfn.XLOOKUP(BV13,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>同?</v>
       </c>
       <c r="BX13" s="7" t="s">
         <v>943</v>
@@ -21057,7 +21244,7 @@
       </c>
       <c r="AW17" s="6" t="str">
         <f>_xlfn.XLOOKUP(AV17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>噴?</v>
       </c>
       <c r="AX17" s="20" t="s">
         <v>1255</v>
@@ -21851,7 +22038,7 @@
       </c>
       <c r="DY18" s="6" t="str">
         <f>_xlfn.XLOOKUP(DX18,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>守?</v>
       </c>
       <c r="DZ18" s="7" t="s">
         <v>1379</v>
@@ -21931,7 +22118,7 @@
       </c>
       <c r="E19" s="25" t="str" cm="1">
         <f t="array" ref="E19">_xlfn.XLOOKUP(D19,対応表!$B:B,対応表!$C:C,"掟?")</f>
-        <v>掟?</v>
+        <v>掟</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>1388</v>
@@ -23358,7 +23545,7 @@
       </c>
       <c r="DO21" s="6" t="str">
         <f>_xlfn.XLOOKUP(DN21,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>正?</v>
       </c>
       <c r="DP21" s="7" t="s">
         <v>1616</v>
@@ -24043,65 +24230,104 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A3841C-3E42-4AC2-9AD3-BA0FFE4A947C}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" s="34" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>2251</v>
+    <row r="12" spans="1:3" ht="20.25">
+      <c r="C12" s="40" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20.25">
+      <c r="A13" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20.25">
+      <c r="A14" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.25">
+      <c r="A16" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" ht="20.25">
+      <c r="C18" s="39" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" ht="20.25">
+      <c r="C19" s="40" t="s">
+        <v>2263</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7846591-E8DA-45E0-96F8-D60E71690043}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BD095EA-F53C-4FE3-BB0F-E93500B31DD6}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3890" uniqueCount="2281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3892" uniqueCount="2283">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -9128,13 +9128,7 @@
     <t>倄</t>
   </si>
   <si>
-    <t>歴?</t>
-  </si>
-  <si>
     <t>乼</t>
-  </si>
-  <si>
-    <t>史?</t>
   </si>
   <si>
     <t>两</t>
@@ -9440,9 +9434,6 @@
     <t>俚介</t>
   </si>
   <si>
-    <t>凗凘三</t>
-  </si>
-  <si>
     <t>僌侫乏乐</t>
   </si>
   <si>
@@ -9475,13 +9466,6 @@
     <t>劚</t>
   </si>
   <si>
-    <t>づ/付？</t>
-    <rPh sb="2" eb="3">
-      <t>ツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>正?</t>
     <rPh sb="0" eb="1">
       <t>タダ</t>
@@ -9521,6 +9505,38 @@
   </si>
   <si>
     <t>掟</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凗凘三</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沿?</t>
+    <rPh sb="0" eb="1">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>革?</t>
+    <rPh sb="0" eb="1">
+      <t>カワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>づ/付?</t>
+    <rPh sb="2" eb="3">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凘</t>
+  </si>
+  <si>
+    <t>♢?</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10353,7 +10369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:C329"/>
+  <dimension ref="A1:C330"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -11633,7 +11649,7 @@
         <v>1905</v>
       </c>
       <c r="C160" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="161" spans="2:3">
@@ -11641,7 +11657,7 @@
         <v>1906</v>
       </c>
       <c r="C161" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="162" spans="2:3">
@@ -11745,7 +11761,7 @@
         <v>1926</v>
       </c>
       <c r="C174" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="175" spans="2:3">
@@ -11769,7 +11785,7 @@
         <v>1930</v>
       </c>
       <c r="C177" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="178" spans="2:3">
@@ -11849,7 +11865,7 @@
         <v>1945</v>
       </c>
       <c r="C187" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="188" spans="2:3">
@@ -11905,7 +11921,7 @@
         <v>1956</v>
       </c>
       <c r="C194" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="195" spans="2:3">
@@ -12081,7 +12097,7 @@
         <v>2169</v>
       </c>
       <c r="C216" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="217" spans="2:3">
@@ -12145,7 +12161,7 @@
         <v>2001</v>
       </c>
       <c r="C224" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="225" spans="2:3">
@@ -12161,7 +12177,7 @@
         <v>2004</v>
       </c>
       <c r="C226" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="227" spans="2:3">
@@ -12193,7 +12209,7 @@
         <v>2010</v>
       </c>
       <c r="C230" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="231" spans="2:3">
@@ -12225,7 +12241,7 @@
         <v>2016</v>
       </c>
       <c r="C234" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="235" spans="2:3">
@@ -12337,7 +12353,7 @@
         <v>2038</v>
       </c>
       <c r="C248" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="249" spans="2:3">
@@ -12345,7 +12361,7 @@
         <v>2179</v>
       </c>
       <c r="C249" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="250" spans="2:3">
@@ -12505,7 +12521,7 @@
         <v>2072</v>
       </c>
       <c r="C269" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="270" spans="2:3">
@@ -12689,7 +12705,7 @@
         <v>2110</v>
       </c>
       <c r="C292" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="293" spans="2:3">
@@ -12697,23 +12713,23 @@
         <v>2188</v>
       </c>
       <c r="C293" t="s">
-        <v>2189</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="294" spans="2:3">
       <c r="B294" s="1" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="C294" t="s">
-        <v>2191</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="295" spans="2:3">
       <c r="B295" s="1" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="C295" t="s">
-        <v>2280</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="296" spans="2:3">
@@ -12721,7 +12737,7 @@
         <v>320</v>
       </c>
       <c r="C296" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="297" spans="2:3">
@@ -12729,259 +12745,267 @@
         <v>1628</v>
       </c>
       <c r="C297" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="298" spans="2:3">
       <c r="B298" s="1" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="C298" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="299" spans="2:3">
       <c r="B299" s="35" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C299" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="300" spans="2:3">
       <c r="B300" s="1" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C300" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="301" spans="2:3">
       <c r="B301" s="35" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C301" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="302" spans="2:3">
       <c r="B302" s="21" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="C302" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="303" spans="2:3">
       <c r="B303" s="21" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C303" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="304" spans="2:3">
       <c r="B304" s="21" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C304" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="305" spans="2:3">
       <c r="B305" s="37" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="C305" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="306" spans="2:3">
       <c r="B306" s="1" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="C306" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="307" spans="2:3">
       <c r="B307" s="1" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="C307" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="308" spans="2:3">
       <c r="B308" s="1" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="C308" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="309" spans="2:3">
       <c r="B309" s="38" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="C309" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="310" spans="2:3">
       <c r="B310" s="1" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="C310" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="311" spans="2:3">
       <c r="B311" s="1" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="C311" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="312" spans="2:3">
       <c r="B312" s="1" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="C312" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="313" spans="2:3">
       <c r="B313" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C313" t="s">
         <v>2245</v>
-      </c>
-      <c r="C313" t="s">
-        <v>2247</v>
       </c>
     </row>
     <row r="314" spans="2:3">
       <c r="B314" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C314" t="s">
         <v>2246</v>
-      </c>
-      <c r="C314" t="s">
-        <v>2248</v>
       </c>
     </row>
     <row r="315" spans="2:3">
       <c r="B315" s="1" t="s">
-        <v>2240</v>
+        <v>2251</v>
       </c>
       <c r="C315" t="s">
-        <v>2242</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="316" spans="2:3">
       <c r="B316" s="1" t="s">
-        <v>2218</v>
+        <v>171</v>
       </c>
       <c r="C316" t="s">
-        <v>2224</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="317" spans="2:3">
       <c r="B317" s="1" t="s">
-        <v>2219</v>
+        <v>2248</v>
       </c>
       <c r="C317" t="s">
-        <v>2225</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="318" spans="2:3">
       <c r="B318" s="1" t="s">
-        <v>2220</v>
+        <v>2263</v>
       </c>
       <c r="C318" t="s">
-        <v>2226</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="319" spans="2:3">
       <c r="B319" s="1" t="s">
-        <v>2253</v>
+        <v>2265</v>
       </c>
       <c r="C319" t="s">
-        <v>2249</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="320" spans="2:3">
       <c r="B320" s="1" t="s">
-        <v>171</v>
+        <v>2267</v>
       </c>
       <c r="C320" t="s">
-        <v>2252</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="321" spans="1:3">
-      <c r="B321" s="1" t="s">
-        <v>2250</v>
+      <c r="B321" s="41" t="s">
+        <v>942</v>
       </c>
       <c r="C321" t="s">
-        <v>2251</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="B322" s="1" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="C322" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="B323" s="1" t="s">
-        <v>2268</v>
+        <v>2272</v>
       </c>
       <c r="C323" t="s">
-        <v>2269</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="B324" s="1" t="s">
-        <v>2270</v>
+        <v>2274</v>
       </c>
       <c r="C324" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="B325" s="41" t="s">
-        <v>942</v>
+      <c r="B325" s="1" t="s">
+        <v>2238</v>
       </c>
       <c r="C325" t="s">
-        <v>2275</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="B326" s="1" t="s">
-        <v>2271</v>
+        <v>2216</v>
       </c>
       <c r="C326" t="s">
-        <v>2273</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="B327" s="1" t="s">
-        <v>2276</v>
+        <v>2217</v>
       </c>
       <c r="C327" t="s">
-        <v>2277</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="B328" s="1" t="s">
-        <v>2278</v>
+        <v>2218</v>
       </c>
       <c r="C328" t="s">
-        <v>2279</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" t="s">
+      <c r="B329" s="1" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C329" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" t="s">
         <v>2114</v>
       </c>
     </row>
@@ -15250,8 +15274,8 @@
         <v>294</v>
       </c>
       <c r="CU5" s="6" t="str">
-        <f>_xlfn.XLOOKUP(CT5,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(CT5,対応表!$B:$B,対応表!$C:$C,"影")</f>
+        <v>影</v>
       </c>
       <c r="CV5" s="7" t="s">
         <v>295</v>
@@ -15985,7 +16009,7 @@
       </c>
       <c r="O7" s="6" t="str">
         <f>_xlfn.XLOOKUP(N7,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>史?</v>
+        <v>革?</v>
       </c>
       <c r="P7" s="7" t="s">
         <v>417</v>
@@ -16286,7 +16310,7 @@
       </c>
       <c r="CW7" s="6" t="str">
         <f>_xlfn.XLOOKUP(CV7,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>♢?</v>
       </c>
       <c r="CX7" s="7" t="s">
         <v>466</v>
@@ -17807,7 +17831,7 @@
       </c>
       <c r="CQ10" s="6" t="str">
         <f>_xlfn.XLOOKUP(CP10,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>づ/付？</v>
+        <v>づ/付?</v>
       </c>
       <c r="CR10" s="7" t="s">
         <v>714</v>
@@ -18320,8 +18344,8 @@
         <v>793</v>
       </c>
       <c r="CQ11" s="6" t="str">
-        <f>_xlfn.XLOOKUP(CP11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(CP11,対応表!$B:$B,対応表!$C:$C,"く")</f>
+        <v>く</v>
       </c>
       <c r="CR11" s="7" t="s">
         <v>794</v>
@@ -21103,8 +21127,8 @@
         <v>1232</v>
       </c>
       <c r="I17" s="6" t="str">
-        <f>_xlfn.XLOOKUP(H17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(H17,対応表!$B:$B,対応表!$C:$C,"隅")</f>
+        <v>隅</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>1233</v>
@@ -22286,7 +22310,7 @@
       </c>
       <c r="BA19" s="6" t="str">
         <f>_xlfn.XLOOKUP(AZ19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>歴?</v>
+        <v>沿?</v>
       </c>
       <c r="BB19" s="7" t="s">
         <v>1417</v>
@@ -22645,8 +22669,8 @@
         <v>1470</v>
       </c>
       <c r="I20" s="6" t="str">
-        <f>_xlfn.XLOOKUP(H20,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(H20,対応表!$B:$B,対応表!$C:$C,"で")</f>
+        <v>で</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>1471</v>
@@ -24230,10 +24254,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A3841C-3E42-4AC2-9AD3-BA0FFE4A947C}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="11" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -24288,46 +24312,52 @@
     </row>
     <row r="12" spans="1:3" ht="20.25">
       <c r="C12" s="40" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.25">
-      <c r="A13" s="1" t="s">
-        <v>2256</v>
-      </c>
       <c r="C13" s="39" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.25">
-      <c r="A14" s="1" t="s">
+      <c r="C14" s="39" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.25">
+      <c r="C16" s="39" t="s">
         <v>2257</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>2258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="20.25">
-      <c r="A16" s="1" t="s">
-        <v>2265</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>2259</v>
       </c>
     </row>
     <row r="18" spans="3:3" ht="20.25">
       <c r="C18" s="39" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="19" spans="3:3" ht="20.25">
       <c r="C19" s="40" t="s">
-        <v>2263</v>
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="1" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="1" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="1" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="1" t="s">
+        <v>2262</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BD095EA-F53C-4FE3-BB0F-E93500B31DD6}"/>
+  <xr:revisionPtr revIDLastSave="695" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA667CCD-3349-420D-88DB-DCF2ACB27C03}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView minimized="1" xWindow="7305" yWindow="4470" windowWidth="21600" windowHeight="11835" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3892" uniqueCount="2283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4065" uniqueCount="2393">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8688,9 +8688,6 @@
   </si>
   <si>
     <t>割</t>
-  </si>
-  <si>
-    <t>加?</t>
   </si>
   <si>
     <t>偊</t>
@@ -9539,12 +9536,659 @@
     <t>♢?</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>　。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○われ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>♦客</t>
+    <rPh sb="1" eb="2">
+      <t>キャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>URL①</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑥</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひと息</t>
+    <rPh sb="2" eb="3">
+      <t>イキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お急ぎ</t>
+    <rPh sb="1" eb="2">
+      <t>イソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>親しまれて</t>
+    <rPh sb="0" eb="1">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お越し</t>
+    <rPh sb="1" eb="2">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変わります</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以ぜん</t>
+    <rPh sb="0" eb="1">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>塞ぐ</t>
+    <rPh sb="0" eb="1">
+      <t>フサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佁</t>
+  </si>
+  <si>
+    <t>●</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●壁</t>
+    <rPh sb="1" eb="2">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防人</t>
+    <rPh sb="0" eb="2">
+      <t>サキモリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飾ります</t>
+    <rPh sb="0" eb="1">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考/用例</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お客様</t>
+    <rPh sb="1" eb="3">
+      <t>キャクサマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>交流の場</t>
+    <rPh sb="0" eb="2">
+      <t>コウリュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩きまわる</t>
+    <rPh sb="0" eb="1">
+      <t>アル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過ごせる</t>
+    <rPh sb="0" eb="1">
+      <t>ス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おきに入り</t>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第四区</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ヨン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>感じた</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相次いで</t>
+    <rPh sb="0" eb="2">
+      <t>アイツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兆し</t>
+    <rPh sb="0" eb="1">
+      <t>キザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重ね</t>
+    <rPh sb="0" eb="1">
+      <t>カサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご確にん</t>
+    <rPh sb="1" eb="2">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沿革</t>
+    <rPh sb="0" eb="2">
+      <t>エンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご報こく/情報</t>
+    <rPh sb="1" eb="2">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文化</t>
+    <rPh sb="0" eb="2">
+      <t>ブンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>扱う</t>
+    <rPh sb="0" eb="1">
+      <t>アツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集めた</t>
+    <rPh sb="0" eb="1">
+      <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再へん</t>
+    <rPh sb="0" eb="1">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対おう</t>
+    <rPh sb="0" eb="1">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>□■せーる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常明王など</t>
+    <rPh sb="0" eb="2">
+      <t>ツネアキラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>導く</t>
+    <rPh sb="0" eb="1">
+      <t>ミチビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未来</t>
+    <rPh sb="0" eb="2">
+      <t>ミライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>りずむと音</t>
+    <rPh sb="4" eb="5">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はば広い</t>
+    <rPh sb="2" eb="3">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お求めやすい</t>
+    <rPh sb="1" eb="2">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>価かく</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おたち寄り</t>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>早いし上げ</t>
+    <rPh sb="0" eb="1">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぞう加/さん加</t>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>影捌けの舞</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>隔離するための場所</t>
+    <rPh sb="0" eb="2">
+      <t>カクリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斬首などのつぐない</t>
+    <rPh sb="0" eb="2">
+      <t>ザンシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>影封房</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>フウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>フサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腹が満たされた</t>
+    <rPh sb="0" eb="1">
+      <t>ハラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満たされた合ず</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過♢</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>守られていない</t>
+    <rPh sb="0" eb="1">
+      <t>マモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>散見</t>
+    <rPh sb="0" eb="2">
+      <t>サンケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正しく行どう</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>噴水（ランドマーク）</t>
+    <rPh sb="0" eb="2">
+      <t>フンスイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちか付く</t>
+    <rPh sb="2" eb="3">
+      <t>ヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目印</t>
+    <rPh sb="0" eb="2">
+      <t>メジルシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関/携わる</t>
+    <rPh sb="0" eb="1">
+      <t>カカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タズサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご来場の際</t>
+    <rPh sb="1" eb="3">
+      <t>ライジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>照明を消し</t>
+    <rPh sb="0" eb="2">
+      <t>ショウメイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>限定</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異なります</t>
+    <rPh sb="0" eb="1">
+      <t>コト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苦味</t>
+    <rPh sb="0" eb="2">
+      <t>ニガミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>深め</t>
+    <rPh sb="0" eb="1">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>傎</t>
+  </si>
+  <si>
+    <t>γ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>γにあった</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色んな</t>
+    <rPh sb="0" eb="1">
+      <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沿革？</t>
+  </si>
+  <si>
+    <t>にく屋</t>
+  </si>
+  <si>
+    <t>さかな屋</t>
+  </si>
+  <si>
+    <t>くつ屋</t>
+  </si>
+  <si>
+    <t>地しんのお知らせ</t>
+  </si>
+  <si>
+    <t>掟に関するお知らせ</t>
+  </si>
+  <si>
+    <t>さい場</t>
+  </si>
+  <si>
+    <t>噴水？</t>
+  </si>
+  <si>
+    <t>○われ？</t>
+  </si>
+  <si>
+    <t>常明像/王？</t>
+  </si>
+  <si>
+    <t>第四区封さのお知らせ</t>
+  </si>
+  <si>
+    <t>第一区は出所</t>
+  </si>
+  <si>
+    <t>化しょう屋</t>
+  </si>
+  <si>
+    <t>きっさ屋</t>
+  </si>
+  <si>
+    <t>影封房？</t>
+  </si>
+  <si>
+    <t>なき子</t>
+  </si>
+  <si>
+    <t>●壁？</t>
+  </si>
+  <si>
+    <t>うらない屋</t>
+  </si>
+  <si>
+    <t>休けい所</t>
+  </si>
+  <si>
+    <t>じゃずばー</t>
+  </si>
+  <si>
+    <t>祭だん</t>
+  </si>
+  <si>
+    <t>時けい屋</t>
+  </si>
+  <si>
+    <t>くすり屋</t>
+  </si>
+  <si>
+    <t>無影言本祭</t>
+  </si>
+  <si>
+    <t>無影言本祭のお知らせ</t>
+  </si>
+  <si>
+    <t>防人？</t>
+  </si>
+  <si>
+    <t>地下街について</t>
+  </si>
+  <si>
+    <t>いべんとのお知らせ</t>
+  </si>
+  <si>
+    <t>くりーにんぐ屋</t>
+  </si>
+  <si>
+    <t>ろう</t>
+  </si>
+  <si>
+    <t>清そう屋</t>
+  </si>
+  <si>
+    <t>うんそう屋</t>
+  </si>
+  <si>
+    <t>本屋</t>
+  </si>
+  <si>
+    <t>うどん屋</t>
+  </si>
+  <si>
+    <t>ほーむ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9739,6 +10383,15 @@
       <name val="Underground"/>
       <family val="3"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -9790,7 +10443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -9827,13 +10480,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9960,8 +10636,21 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
@@ -10046,10 +10735,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10369,18 +11054,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:C330"/>
+  <dimension ref="A1:J332"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
+    <col min="4" max="5" width="21.375" style="44" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.125" style="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>2119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>2118</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>2286</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>2287</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>2289</v>
+      </c>
+      <c r="J1" s="42" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="B2" s="1" t="s">
         <v>1775</v>
       </c>
@@ -10388,7 +11098,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:10">
       <c r="B3" s="1" t="s">
         <v>1707</v>
       </c>
@@ -10396,7 +11106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:10">
       <c r="B4" s="1" t="s">
         <v>1708</v>
       </c>
@@ -10404,7 +11114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:10">
       <c r="B5" s="1" t="s">
         <v>1709</v>
       </c>
@@ -10412,7 +11122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:10">
       <c r="B6" s="1" t="s">
         <v>1710</v>
       </c>
@@ -10420,7 +11130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:10">
       <c r="B7" s="1" t="s">
         <v>1711</v>
       </c>
@@ -10428,7 +11138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>1712</v>
       </c>
@@ -10436,7 +11146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
         <v>1713</v>
       </c>
@@ -10444,7 +11154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:10">
       <c r="B10" s="1" t="s">
         <v>1714</v>
       </c>
@@ -10452,7 +11162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>1715</v>
       </c>
@@ -10460,7 +11170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:10">
       <c r="B12" s="1" t="s">
         <v>1716</v>
       </c>
@@ -10468,7 +11178,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>1717</v>
       </c>
@@ -10476,7 +11186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:10">
       <c r="B14" s="1" t="s">
         <v>1718</v>
       </c>
@@ -10484,7 +11194,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:10">
       <c r="B15" s="1" t="s">
         <v>1719</v>
       </c>
@@ -10492,7 +11202,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:10">
       <c r="B16" s="1" t="s">
         <v>1720</v>
       </c>
@@ -10622,7 +11332,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="1" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -10734,7 +11444,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="C46">
         <v>43</v>
@@ -10878,7 +11588,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" s="1" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="C64">
         <v>61</v>
@@ -10950,7 +11660,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="1" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="C73" t="s">
         <v>1777</v>
@@ -11030,7 +11740,7 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="C83" t="s">
         <v>1795</v>
@@ -11046,7 +11756,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="1" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C85" t="s">
         <v>1798</v>
@@ -11054,7 +11764,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="1" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="C86" t="s">
         <v>1799</v>
@@ -11062,7 +11772,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="1" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="C87" t="s">
         <v>990</v>
@@ -11086,7 +11796,7 @@
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="1" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="C90" t="s">
         <v>1803</v>
@@ -11102,7 +11812,7 @@
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="1" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="C92" t="s">
         <v>827</v>
@@ -11134,7 +11844,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" s="1" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="C96" t="s">
         <v>1812</v>
@@ -11166,7 +11876,7 @@
     </row>
     <row r="100" spans="2:3">
       <c r="B100" s="1" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="C100" t="s">
         <v>832</v>
@@ -11182,7 +11892,7 @@
     </row>
     <row r="102" spans="2:3">
       <c r="B102" s="1" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="C102" t="s">
         <v>1820</v>
@@ -11190,7 +11900,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" s="1" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="C103" t="s">
         <v>1821</v>
@@ -11206,7 +11916,7 @@
     </row>
     <row r="105" spans="2:3">
       <c r="B105" s="1" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C105" t="s">
         <v>1824</v>
@@ -11230,7 +11940,7 @@
     </row>
     <row r="108" spans="2:3">
       <c r="B108" s="1" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="C108" t="s">
         <v>1828</v>
@@ -11238,7 +11948,7 @@
     </row>
     <row r="109" spans="2:3">
       <c r="B109" s="1" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="C109" t="s">
         <v>1829</v>
@@ -11246,7 +11956,7 @@
     </row>
     <row r="110" spans="2:3">
       <c r="B110" s="1" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="C110" t="s">
         <v>1830</v>
@@ -11262,7 +11972,7 @@
     </row>
     <row r="112" spans="2:3">
       <c r="B112" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="C112" t="s">
         <v>1833</v>
@@ -11278,7 +11988,7 @@
     </row>
     <row r="114" spans="2:3">
       <c r="B114" s="1" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="C114" t="s">
         <v>1836</v>
@@ -11286,7 +11996,7 @@
     </row>
     <row r="115" spans="2:3">
       <c r="B115" s="1" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C115" t="s">
         <v>1837</v>
@@ -11294,7 +12004,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" s="1" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="C116" t="s">
         <v>1838</v>
@@ -11310,7 +12020,7 @@
     </row>
     <row r="118" spans="2:3">
       <c r="B118" s="1" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="C118" t="s">
         <v>1840</v>
@@ -11326,7 +12036,7 @@
     </row>
     <row r="120" spans="2:3">
       <c r="B120" s="1" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C120" t="s">
         <v>1843</v>
@@ -11342,7 +12052,7 @@
     </row>
     <row r="122" spans="2:3">
       <c r="B122" s="1" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="C122" t="s">
         <v>1846</v>
@@ -11350,7 +12060,7 @@
     </row>
     <row r="123" spans="2:3">
       <c r="B123" s="1" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="C123" t="s">
         <v>1847</v>
@@ -11358,7 +12068,7 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" s="1" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="C124" t="s">
         <v>1848</v>
@@ -11366,7 +12076,7 @@
     </row>
     <row r="125" spans="2:3">
       <c r="B125" s="1" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C125" t="s">
         <v>1849</v>
@@ -11398,7 +12108,7 @@
     </row>
     <row r="129" spans="2:3">
       <c r="B129" s="1" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="C129" t="s">
         <v>1856</v>
@@ -11422,7 +12132,7 @@
     </row>
     <row r="132" spans="2:3">
       <c r="B132" s="1" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C132" t="s">
         <v>1860</v>
@@ -11438,7 +12148,7 @@
     </row>
     <row r="134" spans="2:3">
       <c r="B134" s="1" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="C134" t="s">
         <v>1862</v>
@@ -11446,7 +12156,7 @@
     </row>
     <row r="135" spans="2:3">
       <c r="B135" s="1" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="C135" t="s">
         <v>1863</v>
@@ -11454,7 +12164,7 @@
     </row>
     <row r="136" spans="2:3">
       <c r="B136" s="1" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="C136" t="s">
         <v>1864</v>
@@ -11502,7 +12212,7 @@
     </row>
     <row r="142" spans="2:3">
       <c r="B142" s="1" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="C142" t="s">
         <v>1875</v>
@@ -11524,7 +12234,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="145" spans="2:3">
+    <row r="145" spans="2:5">
       <c r="B145" s="1" t="s">
         <v>1880</v>
       </c>
@@ -11532,7 +12242,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="146" spans="2:3">
+    <row r="146" spans="2:5">
       <c r="B146" s="1" t="s">
         <v>1882</v>
       </c>
@@ -11540,7 +12250,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="147" spans="2:3">
+    <row r="147" spans="2:5">
       <c r="B147" s="1" t="s">
         <v>1884</v>
       </c>
@@ -11548,7 +12258,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="148" spans="2:3">
+    <row r="148" spans="2:5">
       <c r="B148" s="1" t="s">
         <v>1886</v>
       </c>
@@ -11556,15 +12266,15 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="149" spans="2:3">
+    <row r="149" spans="2:5">
       <c r="B149" s="1" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="C149" t="s">
         <v>1888</v>
       </c>
     </row>
-    <row r="150" spans="2:3">
+    <row r="150" spans="2:5">
       <c r="B150" s="1" t="s">
         <v>1889</v>
       </c>
@@ -11572,7 +12282,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="151" spans="2:3">
+    <row r="151" spans="2:5">
       <c r="B151" s="1" t="s">
         <v>1891</v>
       </c>
@@ -11580,23 +12290,23 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="152" spans="2:3">
+    <row r="152" spans="2:5">
       <c r="B152" s="1" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="C152" t="s">
         <v>1893</v>
       </c>
     </row>
-    <row r="153" spans="2:3">
+    <row r="153" spans="2:5">
       <c r="B153" s="1" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="C153" t="s">
         <v>1894</v>
       </c>
     </row>
-    <row r="154" spans="2:3">
+    <row r="154" spans="2:5">
       <c r="B154" s="1" t="s">
         <v>1895</v>
       </c>
@@ -11604,7 +12314,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="155" spans="2:3">
+    <row r="155" spans="2:5">
       <c r="B155" s="1" t="s">
         <v>1897</v>
       </c>
@@ -11612,7 +12322,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="156" spans="2:3">
+    <row r="156" spans="2:5">
       <c r="B156" s="1" t="s">
         <v>1898</v>
       </c>
@@ -11620,15 +12330,15 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="157" spans="2:3">
+    <row r="157" spans="2:5">
       <c r="B157" s="1" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C157" t="s">
         <v>1900</v>
       </c>
     </row>
-    <row r="158" spans="2:3">
+    <row r="158" spans="2:5">
       <c r="B158" s="1" t="s">
         <v>1901</v>
       </c>
@@ -11636,63 +12346,81 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="159" spans="2:3">
+    <row r="159" spans="2:5">
       <c r="B159" s="1" t="s">
         <v>1903</v>
       </c>
       <c r="C159" t="s">
         <v>1904</v>
       </c>
-    </row>
-    <row r="160" spans="2:3">
+      <c r="D159" s="44" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E159" s="45" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5">
       <c r="B160" s="1" t="s">
         <v>1905</v>
       </c>
       <c r="C160" t="s">
-        <v>2235</v>
-      </c>
-    </row>
-    <row r="161" spans="2:3">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5">
       <c r="B161" s="1" t="s">
         <v>1906</v>
       </c>
       <c r="C161" t="s">
-        <v>2270</v>
-      </c>
-    </row>
-    <row r="162" spans="2:3">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="C162" t="s">
         <v>1907</v>
       </c>
     </row>
-    <row r="163" spans="2:3">
+    <row r="163" spans="2:5">
       <c r="B163" s="1" t="s">
         <v>1908</v>
       </c>
       <c r="C163" t="s">
         <v>1909</v>
       </c>
-    </row>
-    <row r="164" spans="2:3">
+      <c r="D163" s="44" t="s">
+        <v>2357</v>
+      </c>
+      <c r="E163" s="45" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5">
       <c r="B164" s="1" t="s">
         <v>1910</v>
       </c>
       <c r="C164" t="s">
         <v>1911</v>
       </c>
-    </row>
-    <row r="165" spans="2:3">
+      <c r="D164" s="44" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E164" s="45" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="C165" t="s">
         <v>1912</v>
       </c>
     </row>
-    <row r="166" spans="2:3">
+    <row r="166" spans="2:5">
       <c r="B166" s="1" t="s">
         <v>1913</v>
       </c>
@@ -11700,15 +12428,15 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="167" spans="2:3">
+    <row r="167" spans="2:5">
       <c r="B167" s="1" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="C167" t="s">
         <v>1915</v>
       </c>
     </row>
-    <row r="168" spans="2:3">
+    <row r="168" spans="2:5">
       <c r="B168" s="1" t="s">
         <v>1916</v>
       </c>
@@ -11716,7 +12444,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="169" spans="2:3">
+    <row r="169" spans="2:5">
       <c r="B169" s="1" t="s">
         <v>1918</v>
       </c>
@@ -11724,7 +12452,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="170" spans="2:3">
+    <row r="170" spans="2:5">
       <c r="B170" s="1" t="s">
         <v>1920</v>
       </c>
@@ -11732,7 +12460,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="171" spans="2:3">
+    <row r="171" spans="2:5">
       <c r="B171" s="1" t="s">
         <v>1922</v>
       </c>
@@ -11740,7 +12468,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="172" spans="2:3">
+    <row r="172" spans="2:5">
       <c r="B172" s="1" t="s">
         <v>1924</v>
       </c>
@@ -11748,23 +12476,23 @@
         <v>72</v>
       </c>
     </row>
-    <row r="173" spans="2:3">
+    <row r="173" spans="2:5">
       <c r="B173" s="1" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C173" t="s">
         <v>1925</v>
       </c>
     </row>
-    <row r="174" spans="2:3">
+    <row r="174" spans="2:5">
       <c r="B174" s="1" t="s">
         <v>1926</v>
       </c>
       <c r="C174" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="175" spans="2:3">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5">
       <c r="B175" s="1" t="s">
         <v>1927</v>
       </c>
@@ -11772,7 +12500,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="176" spans="2:3">
+    <row r="176" spans="2:5">
       <c r="B176" s="1" t="s">
         <v>1929</v>
       </c>
@@ -11780,23 +12508,23 @@
         <v>980</v>
       </c>
     </row>
-    <row r="177" spans="2:3">
+    <row r="177" spans="2:6">
       <c r="B177" s="1" t="s">
         <v>1930</v>
       </c>
       <c r="C177" t="s">
-        <v>2236</v>
-      </c>
-    </row>
-    <row r="178" spans="2:3">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6">
       <c r="B178" s="1" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="C178" t="s">
         <v>1931</v>
       </c>
     </row>
-    <row r="179" spans="2:3">
+    <row r="179" spans="2:6">
       <c r="B179" s="1" t="s">
         <v>1932</v>
       </c>
@@ -11804,23 +12532,41 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="180" spans="2:3">
+    <row r="180" spans="2:6">
       <c r="B180" s="1" t="s">
         <v>1934</v>
       </c>
       <c r="C180" t="s">
         <v>1935</v>
       </c>
-    </row>
-    <row r="181" spans="2:3">
+      <c r="D180" s="44" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E180" s="45" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F180" s="43" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="181" spans="2:6">
       <c r="B181" s="1" t="s">
         <v>1936</v>
       </c>
       <c r="C181" t="s">
         <v>1937</v>
       </c>
-    </row>
-    <row r="182" spans="2:3">
+      <c r="D181" s="44" t="s">
+        <v>2308</v>
+      </c>
+      <c r="E181" s="45" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F181" s="43" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>1938</v>
       </c>
@@ -11828,31 +12574,43 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="183" spans="2:3">
+    <row r="183" spans="2:6">
       <c r="B183" s="1" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="C183" t="s">
         <v>1940</v>
       </c>
     </row>
-    <row r="184" spans="2:3">
+    <row r="184" spans="2:6">
       <c r="B184" s="1" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C184" t="s">
         <v>1941</v>
       </c>
-    </row>
-    <row r="185" spans="2:3">
+      <c r="D184" s="44" t="s">
+        <v>2306</v>
+      </c>
+      <c r="E184" s="45" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="C185" t="s">
         <v>1942</v>
       </c>
-    </row>
-    <row r="186" spans="2:3">
+      <c r="D185" s="44" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E185" s="45" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="186" spans="2:6">
       <c r="B186" s="1" t="s">
         <v>1943</v>
       </c>
@@ -11860,15 +12618,15 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="187" spans="2:3">
+    <row r="187" spans="2:6">
       <c r="B187" s="1" t="s">
         <v>1945</v>
       </c>
       <c r="C187" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="188" spans="2:3">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="188" spans="2:6">
       <c r="B188" s="1" t="s">
         <v>1946</v>
       </c>
@@ -11876,15 +12634,21 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="189" spans="2:3">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>1948</v>
       </c>
       <c r="C189" t="s">
         <v>1949</v>
       </c>
-    </row>
-    <row r="190" spans="2:3">
+      <c r="D189" s="44" t="s">
+        <v>2311</v>
+      </c>
+      <c r="E189" s="45" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6">
       <c r="B190" s="1" t="s">
         <v>1950</v>
       </c>
@@ -11892,7 +12656,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="191" spans="2:3">
+    <row r="191" spans="2:6">
       <c r="B191" s="1" t="s">
         <v>1952</v>
       </c>
@@ -11900,47 +12664,77 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="192" spans="2:3">
+    <row r="192" spans="2:6">
       <c r="B192" s="1" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="C192" t="s">
         <v>1954</v>
       </c>
     </row>
-    <row r="193" spans="2:3">
+    <row r="193" spans="2:7">
       <c r="B193" s="1" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="C193" t="s">
         <v>1955</v>
       </c>
     </row>
-    <row r="194" spans="2:3">
+    <row r="194" spans="2:7">
       <c r="B194" s="1" t="s">
         <v>1956</v>
       </c>
       <c r="C194" t="s">
-        <v>2209</v>
-      </c>
-    </row>
-    <row r="195" spans="2:3">
+        <v>2208</v>
+      </c>
+      <c r="D194" s="44" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E194" s="45" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F194" s="43" t="s">
+        <v>2388</v>
+      </c>
+      <c r="G194" s="43" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="195" spans="2:7">
       <c r="B195" s="1" t="s">
         <v>1957</v>
       </c>
       <c r="C195" t="s">
         <v>1958</v>
       </c>
-    </row>
-    <row r="196" spans="2:3">
+      <c r="D195" s="44" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E195" s="45" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F195" s="43" t="s">
+        <v>2388</v>
+      </c>
+      <c r="G195" s="43" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7">
       <c r="B196" s="1" t="s">
         <v>1959</v>
       </c>
       <c r="C196" t="s">
         <v>1960</v>
       </c>
-    </row>
-    <row r="197" spans="2:3">
+      <c r="D196" s="44" t="s">
+        <v>2350</v>
+      </c>
+      <c r="E196" s="45" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="197" spans="2:7">
       <c r="B197" s="1" t="s">
         <v>1961</v>
       </c>
@@ -11948,15 +12742,21 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="198" spans="2:3">
+    <row r="198" spans="2:7">
       <c r="B198" s="1" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="C198" t="s">
         <v>1963</v>
       </c>
-    </row>
-    <row r="199" spans="2:3">
+      <c r="D198" s="44" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E198" s="45" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7">
       <c r="B199" s="1" t="s">
         <v>1964</v>
       </c>
@@ -11964,15 +12764,24 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="200" spans="2:3">
+    <row r="200" spans="2:7">
       <c r="B200" s="1" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="C200" t="s">
         <v>1966</v>
       </c>
-    </row>
-    <row r="201" spans="2:3">
+      <c r="D200" s="44" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E200" s="45" t="s">
+        <v>2385</v>
+      </c>
+      <c r="F200" s="43" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="201" spans="2:7">
       <c r="B201" s="1" t="s">
         <v>1967</v>
       </c>
@@ -11980,15 +12789,15 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="202" spans="2:3">
+    <row r="202" spans="2:7">
       <c r="B202" s="1" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="C202" t="s">
         <v>1969</v>
       </c>
     </row>
-    <row r="203" spans="2:3">
+    <row r="203" spans="2:7">
       <c r="B203" s="1" t="s">
         <v>1970</v>
       </c>
@@ -11996,7 +12805,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="204" spans="2:3">
+    <row r="204" spans="2:7">
       <c r="B204" s="1" t="s">
         <v>1972</v>
       </c>
@@ -12004,7 +12813,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="205" spans="2:3">
+    <row r="205" spans="2:7">
       <c r="B205" s="1" t="s">
         <v>1974</v>
       </c>
@@ -12012,23 +12821,29 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="206" spans="2:3">
+    <row r="206" spans="2:7">
       <c r="B206" s="1" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="C206" t="s">
         <v>1976</v>
       </c>
-    </row>
-    <row r="207" spans="2:3">
+      <c r="D206" s="44" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E206" s="45" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="207" spans="2:7">
       <c r="B207" s="1" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="C207" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="208" spans="2:3">
+    <row r="208" spans="2:7">
       <c r="B208" s="1" t="s">
         <v>1978</v>
       </c>
@@ -12036,15 +12851,21 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="209" spans="2:3">
+    <row r="209" spans="2:6">
       <c r="B209" s="1" t="s">
         <v>980</v>
       </c>
       <c r="C209" t="s">
         <v>1980</v>
       </c>
-    </row>
-    <row r="210" spans="2:3">
+      <c r="D209" s="44" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E209" s="45" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6">
       <c r="B210" s="1" t="s">
         <v>1981</v>
       </c>
@@ -12052,7 +12873,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="211" spans="2:3">
+    <row r="211" spans="2:6">
       <c r="B211" s="1" t="s">
         <v>1227</v>
       </c>
@@ -12060,23 +12881,32 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="212" spans="2:3">
+    <row r="212" spans="2:6">
       <c r="B212" s="1" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="C212" t="s">
         <v>1984</v>
       </c>
     </row>
-    <row r="213" spans="2:3">
+    <row r="213" spans="2:6">
       <c r="B213" s="1" t="s">
         <v>1985</v>
       </c>
       <c r="C213" t="s">
         <v>1986</v>
       </c>
-    </row>
-    <row r="214" spans="2:3">
+      <c r="D213" s="44" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E213" s="45" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F213" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6">
       <c r="B214" s="1" t="s">
         <v>1987</v>
       </c>
@@ -12084,7 +12914,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="215" spans="2:3">
+    <row r="215" spans="2:6">
       <c r="B215" s="1" t="s">
         <v>1989</v>
       </c>
@@ -12092,23 +12922,29 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="216" spans="2:3">
+    <row r="216" spans="2:6">
       <c r="B216" s="1" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="C216" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="217" spans="2:3">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6">
       <c r="B217" s="1" t="s">
         <v>1235</v>
       </c>
       <c r="C217" t="s">
         <v>1991</v>
       </c>
-    </row>
-    <row r="218" spans="2:3">
+      <c r="D217" s="44" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E217" s="45" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6">
       <c r="B218" s="1" t="s">
         <v>1992</v>
       </c>
@@ -12116,7 +12952,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="219" spans="2:3">
+    <row r="219" spans="2:6">
       <c r="B219" s="1" t="s">
         <v>1994</v>
       </c>
@@ -12124,23 +12960,29 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="220" spans="2:3">
+    <row r="220" spans="2:6">
       <c r="B220" s="1" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="C220" t="s">
         <v>1996</v>
       </c>
-    </row>
-    <row r="221" spans="2:3">
+      <c r="D220" s="44" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E220" s="45" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="221" spans="2:6">
       <c r="B221" s="1" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="C221" t="s">
         <v>1997</v>
       </c>
     </row>
-    <row r="222" spans="2:3">
+    <row r="222" spans="2:6">
       <c r="B222" s="1" t="s">
         <v>1998</v>
       </c>
@@ -12148,23 +12990,23 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="223" spans="2:3">
+    <row r="223" spans="2:6">
       <c r="B223" s="1" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="C223" t="s">
         <v>2000</v>
       </c>
     </row>
-    <row r="224" spans="2:3">
+    <row r="224" spans="2:6">
       <c r="B224" s="1" t="s">
         <v>2001</v>
       </c>
       <c r="C224" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="225" spans="2:3">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="225" spans="2:5">
       <c r="B225" s="1" t="s">
         <v>2002</v>
       </c>
@@ -12172,15 +13014,15 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="226" spans="2:3">
+    <row r="226" spans="2:5">
       <c r="B226" s="1" t="s">
         <v>2004</v>
       </c>
       <c r="C226" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="227" spans="2:3">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5">
       <c r="B227" s="1" t="s">
         <v>2005</v>
       </c>
@@ -12188,7 +13030,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="228" spans="2:3">
+    <row r="228" spans="2:5">
       <c r="B228" s="1" t="s">
         <v>2007</v>
       </c>
@@ -12196,7 +13038,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="229" spans="2:3">
+    <row r="229" spans="2:5">
       <c r="B229" s="1" t="s">
         <v>2009</v>
       </c>
@@ -12204,15 +13046,15 @@
         <v>494</v>
       </c>
     </row>
-    <row r="230" spans="2:3">
+    <row r="230" spans="2:5">
       <c r="B230" s="1" t="s">
         <v>2010</v>
       </c>
       <c r="C230" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="231" spans="2:3">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="231" spans="2:5">
       <c r="B231" s="1" t="s">
         <v>2011</v>
       </c>
@@ -12220,31 +13062,43 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="232" spans="2:3">
+    <row r="232" spans="2:5">
       <c r="B232" s="1" t="s">
         <v>2013</v>
       </c>
       <c r="C232" t="s">
         <v>2014</v>
       </c>
-    </row>
-    <row r="233" spans="2:3">
+      <c r="D232" s="44" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E232" s="45" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="233" spans="2:5">
       <c r="B233" s="1" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="C233" t="s">
         <v>2015</v>
       </c>
-    </row>
-    <row r="234" spans="2:3">
+      <c r="D233" s="44" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E233" s="45" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="234" spans="2:5">
       <c r="B234" s="1" t="s">
         <v>2016</v>
       </c>
       <c r="C234" t="s">
-        <v>2253</v>
-      </c>
-    </row>
-    <row r="235" spans="2:3">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="235" spans="2:5">
       <c r="B235" s="1" t="s">
         <v>2017</v>
       </c>
@@ -12252,7 +13106,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="236" spans="2:3">
+    <row r="236" spans="2:5">
       <c r="B236" s="1" t="s">
         <v>2019</v>
       </c>
@@ -12260,15 +13114,15 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="237" spans="2:3">
+    <row r="237" spans="2:5">
       <c r="B237" s="1" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="C237" t="s">
         <v>2021</v>
       </c>
     </row>
-    <row r="238" spans="2:3">
+    <row r="238" spans="2:5">
       <c r="B238" s="1" t="s">
         <v>2022</v>
       </c>
@@ -12276,7 +13130,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="239" spans="2:3">
+    <row r="239" spans="2:5">
       <c r="B239" s="1" t="s">
         <v>2024</v>
       </c>
@@ -12284,7 +13138,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="240" spans="2:3">
+    <row r="240" spans="2:5">
       <c r="B240" s="1" t="s">
         <v>2026</v>
       </c>
@@ -12292,31 +13146,52 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="241" spans="2:3">
+    <row r="241" spans="2:6">
       <c r="B241" s="1" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C241" t="s">
         <v>2028</v>
       </c>
-    </row>
-    <row r="242" spans="2:3">
+      <c r="D241" s="44" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E241" s="45" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="242" spans="2:6">
       <c r="B242" s="1" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="C242" t="s">
         <v>2029</v>
       </c>
-    </row>
-    <row r="243" spans="2:3">
+      <c r="D242" s="44" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E242" s="45" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="243" spans="2:6">
       <c r="B243" s="1" t="s">
         <v>2030</v>
       </c>
       <c r="C243" t="s">
         <v>2031</v>
       </c>
-    </row>
-    <row r="244" spans="2:3">
+      <c r="D243" s="44" t="s">
+        <v>2330</v>
+      </c>
+      <c r="E243" s="45" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F243" s="45" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="244" spans="2:6">
       <c r="B244" s="1" t="s">
         <v>2032</v>
       </c>
@@ -12324,63 +13199,93 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="245" spans="2:3">
+    <row r="245" spans="2:6">
       <c r="B245" s="1" t="s">
         <v>2034</v>
       </c>
       <c r="C245" t="s">
         <v>2035</v>
       </c>
-    </row>
-    <row r="246" spans="2:3">
+      <c r="D245" s="44" t="s">
+        <v>2331</v>
+      </c>
+      <c r="E245" s="45" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="246" spans="2:6">
       <c r="B246" s="1" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="C246" t="s">
         <v>2036</v>
       </c>
-    </row>
-    <row r="247" spans="2:3">
+      <c r="D246" s="44" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E246" s="45" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="247" spans="2:6">
       <c r="B247" s="1" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="C247" t="s">
         <v>2037</v>
       </c>
-    </row>
-    <row r="248" spans="2:3">
+      <c r="D247" s="44" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E247" s="45" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="248" spans="2:6">
       <c r="B248" s="1" t="s">
         <v>2038</v>
       </c>
       <c r="C248" t="s">
-        <v>2252</v>
-      </c>
-    </row>
-    <row r="249" spans="2:3">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="249" spans="2:6">
       <c r="B249" s="1" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="C249" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="250" spans="2:3">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="250" spans="2:6">
       <c r="B250" s="1" t="s">
         <v>2039</v>
       </c>
       <c r="C250" t="s">
         <v>2040</v>
       </c>
-    </row>
-    <row r="251" spans="2:3">
+      <c r="D250" s="44" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E250" s="45" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="251" spans="2:6">
       <c r="B251" s="1" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="C251" t="s">
         <v>2041</v>
       </c>
-    </row>
-    <row r="252" spans="2:3">
+      <c r="D251" s="44" t="s">
+        <v>2347</v>
+      </c>
+      <c r="E251" s="45" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="252" spans="2:6">
       <c r="B252" s="1" t="s">
         <v>2042</v>
       </c>
@@ -12388,7 +13293,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="253" spans="2:3">
+    <row r="253" spans="2:6">
       <c r="B253" s="1" t="s">
         <v>2043</v>
       </c>
@@ -12396,15 +13301,21 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="254" spans="2:3">
+    <row r="254" spans="2:6">
       <c r="B254" s="1" t="s">
         <v>2045</v>
       </c>
       <c r="C254" t="s">
         <v>2046</v>
       </c>
-    </row>
-    <row r="255" spans="2:3">
+      <c r="D254" s="44" t="s">
+        <v>2316</v>
+      </c>
+      <c r="E254" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="255" spans="2:6">
       <c r="B255" s="1" t="s">
         <v>2047</v>
       </c>
@@ -12412,7 +13323,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="256" spans="2:3">
+    <row r="256" spans="2:6">
       <c r="B256" s="1" t="s">
         <v>2049</v>
       </c>
@@ -12420,7 +13331,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="257" spans="2:3">
+    <row r="257" spans="2:6">
       <c r="B257" s="1" t="s">
         <v>2051</v>
       </c>
@@ -12428,15 +13339,21 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="258" spans="2:3">
+    <row r="258" spans="2:6">
       <c r="B258" s="1" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="C258" t="s">
         <v>2053</v>
       </c>
-    </row>
-    <row r="259" spans="2:3">
+      <c r="D258" s="44" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E258" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="259" spans="2:6">
       <c r="B259" s="1" t="s">
         <v>2054</v>
       </c>
@@ -12444,569 +13361,861 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="260" spans="2:3">
+    <row r="260" spans="2:6">
       <c r="B260" s="1" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="C260" t="s">
         <v>2056</v>
       </c>
-    </row>
-    <row r="261" spans="2:3">
+      <c r="D260" s="44" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E260" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="261" spans="2:6">
       <c r="B261" s="1" t="s">
         <v>2057</v>
       </c>
       <c r="C261" t="s">
+        <v>476</v>
+      </c>
+      <c r="D261" s="44" t="s">
+        <v>2333</v>
+      </c>
+      <c r="E261" s="45" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F261" s="43" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="262" spans="2:6">
+      <c r="B262" s="1" t="s">
         <v>2058</v>
       </c>
-    </row>
-    <row r="262" spans="2:3">
-      <c r="B262" s="1" t="s">
+      <c r="C262" t="s">
         <v>2059</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" s="44" t="s">
+        <v>2313</v>
+      </c>
+      <c r="E262" s="45" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="263" spans="2:6">
+      <c r="B263" s="1" t="s">
         <v>2060</v>
       </c>
-    </row>
-    <row r="263" spans="2:3">
-      <c r="B263" s="1" t="s">
+      <c r="C263" t="s">
         <v>2061</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" s="44" t="s">
+        <v>2349</v>
+      </c>
+      <c r="E263" s="45" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="264" spans="2:6">
+      <c r="B264" s="1" t="s">
         <v>2062</v>
       </c>
-    </row>
-    <row r="264" spans="2:3">
-      <c r="B264" s="1" t="s">
+      <c r="C264" t="s">
         <v>2063</v>
       </c>
-      <c r="C264" t="s">
+    </row>
+    <row r="265" spans="2:6">
+      <c r="B265" s="1" t="s">
         <v>2064</v>
       </c>
-    </row>
-    <row r="265" spans="2:3">
-      <c r="B265" s="1" t="s">
+      <c r="C265" t="s">
         <v>2065</v>
       </c>
-      <c r="C265" t="s">
+    </row>
+    <row r="266" spans="2:6">
+      <c r="B266" s="1" t="s">
         <v>2066</v>
       </c>
-    </row>
-    <row r="266" spans="2:3">
-      <c r="B266" s="1" t="s">
+      <c r="C266" t="s">
         <v>2067</v>
       </c>
-      <c r="C266" t="s">
+    </row>
+    <row r="267" spans="2:6">
+      <c r="B267" s="1" t="s">
         <v>2068</v>
       </c>
-    </row>
-    <row r="267" spans="2:3">
-      <c r="B267" s="1" t="s">
+      <c r="C267" t="s">
         <v>2069</v>
       </c>
-      <c r="C267" t="s">
+    </row>
+    <row r="268" spans="2:6">
+      <c r="B268" s="1" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C268" t="s">
         <v>2070</v>
       </c>
-    </row>
-    <row r="268" spans="2:3">
-      <c r="B268" s="1" t="s">
-        <v>2183</v>
-      </c>
-      <c r="C268" t="s">
+      <c r="D268" s="44" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E268" s="45" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="269" spans="2:6">
+      <c r="B269" s="1" t="s">
         <v>2071</v>
       </c>
-    </row>
-    <row r="269" spans="2:3">
-      <c r="B269" s="1" t="s">
+      <c r="C269" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="270" spans="2:6">
+      <c r="B270" s="1" t="s">
         <v>2072</v>
       </c>
-      <c r="C269" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="270" spans="2:3">
-      <c r="B270" s="1" t="s">
+      <c r="C270" t="s">
         <v>2073</v>
       </c>
-      <c r="C270" t="s">
+    </row>
+    <row r="271" spans="2:6">
+      <c r="B271" s="1" t="s">
         <v>2074</v>
       </c>
-    </row>
-    <row r="271" spans="2:3">
-      <c r="B271" s="1" t="s">
+      <c r="C271" t="s">
         <v>2075</v>
       </c>
-      <c r="C271" t="s">
+    </row>
+    <row r="272" spans="2:6">
+      <c r="B272" s="1" t="s">
         <v>2076</v>
       </c>
-    </row>
-    <row r="272" spans="2:3">
-      <c r="B272" s="1" t="s">
+      <c r="C272" t="s">
         <v>2077</v>
       </c>
-      <c r="C272" t="s">
+    </row>
+    <row r="273" spans="2:5">
+      <c r="B273" s="1" t="s">
         <v>2078</v>
       </c>
-    </row>
-    <row r="273" spans="2:3">
-      <c r="B273" s="1" t="s">
+      <c r="C273" t="s">
         <v>2079</v>
       </c>
-      <c r="C273" t="s">
+    </row>
+    <row r="274" spans="2:5">
+      <c r="B274" s="1" t="s">
         <v>2080</v>
       </c>
-    </row>
-    <row r="274" spans="2:3">
-      <c r="B274" s="1" t="s">
+      <c r="C274" t="s">
         <v>2081</v>
       </c>
-      <c r="C274" t="s">
+    </row>
+    <row r="275" spans="2:5">
+      <c r="B275" s="1" t="s">
         <v>2082</v>
       </c>
-    </row>
-    <row r="275" spans="2:3">
-      <c r="B275" s="1" t="s">
+      <c r="C275" t="s">
         <v>2083</v>
       </c>
-      <c r="C275" t="s">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="276" spans="2:3">
+    </row>
+    <row r="276" spans="2:5">
       <c r="B276" s="1" t="s">
         <v>492</v>
       </c>
       <c r="C276" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="277" spans="2:5">
+      <c r="B277" s="1" t="s">
         <v>2085</v>
       </c>
-    </row>
-    <row r="277" spans="2:3">
-      <c r="B277" s="1" t="s">
+      <c r="C277" t="s">
         <v>2086</v>
       </c>
-      <c r="C277" t="s">
+    </row>
+    <row r="278" spans="2:5">
+      <c r="B278" s="1" t="s">
         <v>2087</v>
       </c>
-    </row>
-    <row r="278" spans="2:3">
-      <c r="B278" s="1" t="s">
+      <c r="C278" t="s">
         <v>2088</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" s="44" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E278" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="279" spans="2:5">
+      <c r="B279" s="1" t="s">
         <v>2089</v>
       </c>
-    </row>
-    <row r="279" spans="2:3">
-      <c r="B279" s="1" t="s">
+      <c r="C279" t="s">
         <v>2090</v>
       </c>
-      <c r="C279" t="s">
+      <c r="D279" s="44" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E279" s="45" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="280" spans="2:5">
+      <c r="B280" s="1" t="s">
         <v>2091</v>
       </c>
-    </row>
-    <row r="280" spans="2:3">
-      <c r="B280" s="1" t="s">
+      <c r="C280" t="s">
         <v>2092</v>
       </c>
-      <c r="C280" t="s">
+      <c r="D280" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="E280" s="45" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="281" spans="2:5">
+      <c r="B281" s="1" t="s">
         <v>2093</v>
-      </c>
-    </row>
-    <row r="281" spans="2:3">
-      <c r="B281" s="1" t="s">
-        <v>2094</v>
       </c>
       <c r="C281" t="s">
         <v>1623</v>
       </c>
     </row>
-    <row r="282" spans="2:3">
+    <row r="282" spans="2:5">
       <c r="B282" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C282" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="283" spans="2:5">
+      <c r="B283" s="1" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C283" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="284" spans="2:5">
+      <c r="B284" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C284" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="285" spans="2:5">
+      <c r="B285" s="1" t="s">
+        <v>2099</v>
+      </c>
+      <c r="C285" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="286" spans="2:5">
+      <c r="B286" s="1" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C286" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="287" spans="2:5">
+      <c r="B287" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C287" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="288" spans="2:5">
+      <c r="B288" s="1" t="s">
         <v>2184</v>
       </c>
-      <c r="C282" t="s">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="283" spans="2:3">
-      <c r="B283" s="1" t="s">
-        <v>2096</v>
-      </c>
-      <c r="C283" t="s">
-        <v>2097</v>
-      </c>
-    </row>
-    <row r="284" spans="2:3">
-      <c r="B284" s="1" t="s">
-        <v>2098</v>
-      </c>
-      <c r="C284" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="285" spans="2:3">
-      <c r="B285" s="1" t="s">
-        <v>2100</v>
-      </c>
-      <c r="C285" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="286" spans="2:3">
-      <c r="B286" s="1" t="s">
-        <v>2102</v>
-      </c>
-      <c r="C286" t="s">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="287" spans="2:3">
-      <c r="B287" s="1" t="s">
-        <v>2104</v>
-      </c>
-      <c r="C287" t="s">
+      <c r="C288" t="s">
         <v>2105</v>
       </c>
-    </row>
-    <row r="288" spans="2:3">
-      <c r="B288" s="1" t="s">
+      <c r="D288" s="44" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E288" s="45" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="289" spans="2:6">
+      <c r="B289" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C289" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="290" spans="2:6">
+      <c r="B290" s="1" t="s">
         <v>2185</v>
-      </c>
-      <c r="C288" t="s">
-        <v>2106</v>
-      </c>
-    </row>
-    <row r="289" spans="2:3">
-      <c r="B289" s="1" t="s">
-        <v>2107</v>
-      </c>
-      <c r="C289" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="290" spans="2:3">
-      <c r="B290" s="1" t="s">
-        <v>2186</v>
       </c>
       <c r="C290" t="s">
         <v>2020</v>
       </c>
     </row>
-    <row r="291" spans="2:3">
+    <row r="291" spans="2:6">
       <c r="B291" s="1" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C291" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="292" spans="2:6">
+      <c r="B292" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C292" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D292" s="44" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E292" s="45" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F292" s="43" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="293" spans="2:6">
+      <c r="B293" s="1" t="s">
         <v>2187</v>
       </c>
-      <c r="C291" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="292" spans="2:3">
-      <c r="B292" s="1" t="s">
-        <v>2110</v>
-      </c>
-      <c r="C292" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="293" spans="2:3">
-      <c r="B293" s="1" t="s">
+      <c r="C293" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D293" s="44" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E293" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="294" spans="2:6">
+      <c r="B294" s="1" t="s">
         <v>2188</v>
       </c>
-      <c r="C293" t="s">
+      <c r="C294" t="s">
         <v>2278</v>
       </c>
-    </row>
-    <row r="294" spans="2:3">
-      <c r="B294" s="1" t="s">
+      <c r="D294" s="44" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E294" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="295" spans="2:6">
+      <c r="B295" s="1" t="s">
         <v>2189</v>
       </c>
-      <c r="C294" t="s">
-        <v>2279</v>
-      </c>
-    </row>
-    <row r="295" spans="2:3">
-      <c r="B295" s="1" t="s">
-        <v>2190</v>
-      </c>
       <c r="C295" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="296" spans="2:3">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="296" spans="2:6">
       <c r="B296" s="1" t="s">
         <v>320</v>
       </c>
       <c r="C296" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="297" spans="2:3">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="297" spans="2:6">
       <c r="B297" s="1" t="s">
         <v>1628</v>
       </c>
       <c r="C297" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="298" spans="2:6">
+      <c r="B298" s="1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C298" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="299" spans="2:6">
+      <c r="B299" s="35" t="s">
         <v>2194</v>
       </c>
-    </row>
-    <row r="298" spans="2:3">
-      <c r="B298" s="1" t="s">
-        <v>2191</v>
-      </c>
-      <c r="C298" t="s">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="299" spans="2:3">
-      <c r="B299" s="35" t="s">
+      <c r="C299" t="s">
         <v>2195</v>
       </c>
-      <c r="C299" t="s">
+      <c r="D299" s="44" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E299" s="43" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="300" spans="2:6">
+      <c r="B300" s="1" t="s">
         <v>2196</v>
       </c>
-    </row>
-    <row r="300" spans="2:3">
-      <c r="B300" s="1" t="s">
+      <c r="C300" t="s">
         <v>2197</v>
       </c>
-      <c r="C300" t="s">
+      <c r="D300" s="44" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E300" s="45" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="301" spans="2:6">
+      <c r="B301" s="35" t="s">
         <v>2198</v>
       </c>
-    </row>
-    <row r="301" spans="2:3">
-      <c r="B301" s="35" t="s">
+      <c r="C301" t="s">
         <v>2199</v>
       </c>
-      <c r="C301" t="s">
+    </row>
+    <row r="302" spans="2:6">
+      <c r="B302" s="21" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="303" spans="2:6">
+      <c r="B303" s="21" t="s">
         <v>2200</v>
       </c>
-    </row>
-    <row r="302" spans="2:3">
-      <c r="B302" s="21" t="s">
-        <v>2219</v>
-      </c>
-      <c r="C302" t="s">
+      <c r="C303" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D303" s="44" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E303" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="304" spans="2:6">
+      <c r="B304" s="21" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C304" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D304" s="44" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E304" s="45" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="305" spans="2:6">
+      <c r="B305" s="37" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D305" s="44" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E305" s="45" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="306" spans="2:6">
+      <c r="B306" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D306" s="44" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E306" s="45" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="307" spans="2:6">
+      <c r="B307" s="1" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C307" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D307" s="44" t="s">
+        <v>2338</v>
+      </c>
+      <c r="E307" s="43" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="308" spans="2:6">
+      <c r="B308" s="1" t="s">
         <v>2220</v>
       </c>
-    </row>
-    <row r="303" spans="2:3">
-      <c r="B303" s="21" t="s">
-        <v>2201</v>
-      </c>
-      <c r="C303" t="s">
-        <v>2202</v>
-      </c>
-    </row>
-    <row r="304" spans="2:3">
-      <c r="B304" s="21" t="s">
-        <v>2204</v>
-      </c>
-      <c r="C304" t="s">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="305" spans="2:3">
-      <c r="B305" s="37" t="s">
-        <v>2205</v>
-      </c>
-      <c r="C305" t="s">
-        <v>2206</v>
-      </c>
-    </row>
-    <row r="306" spans="2:3">
-      <c r="B306" s="1" t="s">
-        <v>2211</v>
-      </c>
-      <c r="C306" t="s">
-        <v>2212</v>
-      </c>
-    </row>
-    <row r="307" spans="2:3">
-      <c r="B307" s="1" t="s">
-        <v>2214</v>
-      </c>
-      <c r="C307" t="s">
-        <v>2215</v>
-      </c>
-    </row>
-    <row r="308" spans="2:3">
-      <c r="B308" s="1" t="s">
-        <v>2221</v>
-      </c>
       <c r="C308" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="309" spans="2:3">
+        <v>2224</v>
+      </c>
+      <c r="D308" s="44" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E308" s="45" t="s">
+        <v>2369</v>
+      </c>
+      <c r="F308" s="43" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="309" spans="2:6">
       <c r="B309" s="38" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C309" t="s">
         <v>2228</v>
       </c>
-      <c r="C309" t="s">
+      <c r="D309" s="44" t="s">
+        <v>2302</v>
+      </c>
+      <c r="E309" s="45" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="310" spans="2:6">
+      <c r="B310" s="1" t="s">
         <v>2229</v>
       </c>
-    </row>
-    <row r="310" spans="2:3">
-      <c r="B310" s="1" t="s">
+      <c r="C310" t="s">
         <v>2230</v>
       </c>
-      <c r="C310" t="s">
+      <c r="D310" s="44" t="s">
+        <v>2352</v>
+      </c>
+      <c r="E310" s="45" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="311" spans="2:6">
+      <c r="B311" s="1" t="s">
         <v>2231</v>
       </c>
-    </row>
-    <row r="311" spans="2:3">
-      <c r="B311" s="1" t="s">
+      <c r="C311" t="s">
         <v>2232</v>
       </c>
-      <c r="C311" t="s">
-        <v>2233</v>
-      </c>
-    </row>
-    <row r="312" spans="2:3">
+      <c r="D311" s="44" t="s">
+        <v>2353</v>
+      </c>
+      <c r="E311" s="45" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="312" spans="2:6">
       <c r="B312" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C312" t="s">
         <v>2241</v>
       </c>
-      <c r="C312" t="s">
+      <c r="D312" s="44" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E312" s="45" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="313" spans="2:6">
+      <c r="B313" s="1" t="s">
         <v>2242</v>
       </c>
-    </row>
-    <row r="313" spans="2:3">
-      <c r="B313" s="1" t="s">
+      <c r="C313" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D313" s="44" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E313" s="45" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="314" spans="2:6">
+      <c r="B314" s="1" t="s">
         <v>2243</v>
       </c>
-      <c r="C313" t="s">
+      <c r="C314" t="s">
         <v>2245</v>
       </c>
-    </row>
-    <row r="314" spans="2:3">
-      <c r="B314" s="1" t="s">
-        <v>2244</v>
-      </c>
-      <c r="C314" t="s">
+      <c r="D314" s="44" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E314" s="45" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="315" spans="2:6">
+      <c r="B315" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="C315" t="s">
         <v>2246</v>
       </c>
-    </row>
-    <row r="315" spans="2:3">
-      <c r="B315" s="1" t="s">
-        <v>2251</v>
-      </c>
-      <c r="C315" t="s">
-        <v>2247</v>
-      </c>
-    </row>
-    <row r="316" spans="2:3">
+      <c r="D315" s="44" t="s">
+        <v>2334</v>
+      </c>
+      <c r="E315" s="45" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="316" spans="2:6">
       <c r="B316" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C316" t="s">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="317" spans="2:3">
+        <v>2249</v>
+      </c>
+      <c r="D316" s="44" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E316" s="45" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="317" spans="2:6">
       <c r="B317" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C317" t="s">
         <v>2248</v>
       </c>
-      <c r="C317" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="318" spans="2:3">
+      <c r="D317" s="44" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E317" s="45" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="318" spans="2:6">
       <c r="B318" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C318" t="s">
         <v>2263</v>
       </c>
-      <c r="C318" t="s">
+      <c r="D318" s="44" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E318" s="45" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F318" s="43" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="319" spans="2:6">
+      <c r="B319" s="1" t="s">
         <v>2264</v>
       </c>
-    </row>
-    <row r="319" spans="2:3">
-      <c r="B319" s="1" t="s">
+      <c r="C319" t="s">
         <v>2265</v>
       </c>
-      <c r="C319" t="s">
+      <c r="D319" s="44" t="s">
+        <v>2342</v>
+      </c>
+      <c r="E319" s="45" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="320" spans="2:6">
+      <c r="B320" s="1" t="s">
         <v>2266</v>
       </c>
-    </row>
-    <row r="320" spans="2:3">
-      <c r="B320" s="1" t="s">
-        <v>2267</v>
-      </c>
       <c r="C320" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3">
+        <v>2279</v>
+      </c>
+      <c r="D320" s="44" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E320" s="45" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F320" s="43" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
       <c r="B321" s="41" t="s">
         <v>942</v>
       </c>
       <c r="C321" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="B322" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C322" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D322" s="44" t="s">
+        <v>2343</v>
+      </c>
+      <c r="E322" s="45" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="B323" s="1" t="s">
         <v>2271</v>
       </c>
-    </row>
-    <row r="322" spans="1:3">
-      <c r="B322" s="1" t="s">
-        <v>2268</v>
-      </c>
-      <c r="C322" t="s">
-        <v>2269</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3">
-      <c r="B323" s="1" t="s">
+      <c r="C323" t="s">
         <v>2272</v>
       </c>
-      <c r="C323" t="s">
+      <c r="D323" s="44" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E323" s="45" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F323" s="43" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="B324" s="1" t="s">
         <v>2273</v>
       </c>
-    </row>
-    <row r="324" spans="1:3">
-      <c r="B324" s="1" t="s">
+      <c r="C324" t="s">
         <v>2274</v>
       </c>
-      <c r="C324" t="s">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
+      <c r="D324" s="44" t="s">
+        <v>2344</v>
+      </c>
+      <c r="E324" s="45" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F324" s="43" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
       <c r="B325" s="1" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="C325" t="s">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3">
+        <v>2239</v>
+      </c>
+      <c r="D325" s="44" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E325" s="45" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
       <c r="B326" s="1" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C326" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D326" s="44" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E326" s="45" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F326" s="43" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="B327" s="1" t="s">
         <v>2216</v>
       </c>
-      <c r="C326" t="s">
+      <c r="C327" t="s">
         <v>2222</v>
       </c>
-    </row>
-    <row r="327" spans="1:3">
-      <c r="B327" s="1" t="s">
+      <c r="D327" s="44" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E327" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="B328" s="1" t="s">
         <v>2217</v>
       </c>
-      <c r="C327" t="s">
+      <c r="C328" t="s">
         <v>2223</v>
       </c>
-    </row>
-    <row r="328" spans="1:3">
-      <c r="B328" s="1" t="s">
-        <v>2218</v>
-      </c>
-      <c r="C328" t="s">
-        <v>2224</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3">
+      <c r="D328" s="44" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E328" s="45" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
       <c r="B329" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C329" t="s">
         <v>2281</v>
       </c>
-      <c r="C329" t="s">
-        <v>2282</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3">
+      <c r="D329" s="44" t="s">
+        <v>2340</v>
+      </c>
+      <c r="E329" s="45" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>2114</v>
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="B331" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C331" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D331" s="44" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E331" s="45" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="B332" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C332" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D332" s="44" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E332" s="45" t="s">
+        <v>2374</v>
       </c>
     </row>
   </sheetData>
@@ -13027,6 +14236,97 @@
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="E217" r:id="rId1" xr:uid="{2BD22168-2F0F-4260-8DC6-FCDAA83902A4}"/>
+    <hyperlink ref="E220" r:id="rId2" xr:uid="{5A86A9C8-18B7-49D4-B0DA-510F8507220D}"/>
+    <hyperlink ref="E242" r:id="rId3" xr:uid="{E8BDD6E9-53E1-49ED-9A35-0FFE574C21E6}"/>
+    <hyperlink ref="E331" r:id="rId4" xr:uid="{15456AB3-5F70-432C-91F1-C3B6D972B050}"/>
+    <hyperlink ref="E325" r:id="rId5" xr:uid="{B5E564C1-2202-4076-A41F-2A29B21EEF86}"/>
+    <hyperlink ref="E309" r:id="rId6" xr:uid="{4E8F2926-23D8-4338-A705-D1EB793CFD3E}"/>
+    <hyperlink ref="E308" r:id="rId7" xr:uid="{82427E63-C1DB-4ADE-A529-AB11239EFCCF}"/>
+    <hyperlink ref="E181" r:id="rId8" xr:uid="{FA78759D-C553-403D-992E-421D714D9F9A}"/>
+    <hyperlink ref="E306" r:id="rId9" xr:uid="{E0B36401-B236-49E7-82D8-7ED63A6D7DBE}"/>
+    <hyperlink ref="E189" r:id="rId10" xr:uid="{4ADE96FD-5709-4E9D-A184-C7F392590887}"/>
+    <hyperlink ref="E261" r:id="rId11" xr:uid="{4D6FC0FA-E825-4FA8-A960-70D867620EC0}"/>
+    <hyperlink ref="E180" r:id="rId12" xr:uid="{D49DD08F-1EF6-4D4C-A0E4-8B16E7D228CC}"/>
+    <hyperlink ref="E300" r:id="rId13" xr:uid="{FFBE8D92-DB52-4411-9DBA-7061F3A88180}"/>
+    <hyperlink ref="E288" r:id="rId14" xr:uid="{F56E8B3B-C96C-4C92-BDF3-0433DFF6F363}"/>
+    <hyperlink ref="E233" r:id="rId15" xr:uid="{C8B3A9F6-E20B-4806-986C-21837F397D46}"/>
+    <hyperlink ref="E164" r:id="rId16" xr:uid="{4FE6B493-0A62-44D8-B265-E4BE0CF30A01}"/>
+    <hyperlink ref="E159" r:id="rId17" xr:uid="{E7F50912-0B82-46DE-BFC1-44F9BF8D5AA1}"/>
+    <hyperlink ref="F180" r:id="rId18" xr:uid="{DB06038A-C39A-4D4D-842D-EFA08F8E8C30}"/>
+    <hyperlink ref="E310" r:id="rId19" xr:uid="{80642AE9-EB09-43F8-8ED4-4296F935955A}"/>
+    <hyperlink ref="E163" r:id="rId20" xr:uid="{AA4E558B-E442-4D3F-A743-A0D4BF133471}"/>
+    <hyperlink ref="F194" r:id="rId21" xr:uid="{D0003710-B87A-4132-8F8C-F03A94DB0D8E}"/>
+    <hyperlink ref="G195" r:id="rId22" xr:uid="{E145CBB8-9029-48BC-9EF6-24A9D6546912}"/>
+    <hyperlink ref="E200" r:id="rId23" xr:uid="{069318CA-733C-4637-8231-71BF8BDE174C}"/>
+    <hyperlink ref="F200" r:id="rId24" xr:uid="{606F5CDB-9747-4F64-AA15-7F28234FF649}"/>
+    <hyperlink ref="E243" r:id="rId25" xr:uid="{E4A3FF73-4921-408C-8FC8-576088C455C5}"/>
+    <hyperlink ref="F261" r:id="rId26" xr:uid="{FD6022E8-CD2D-453D-B9BD-977A5A45A79A}"/>
+    <hyperlink ref="F308" r:id="rId27" xr:uid="{CB76E612-3F74-438D-AE6C-4556B87A3117}"/>
+    <hyperlink ref="E312" r:id="rId28" xr:uid="{400C510C-E456-4A27-B24C-418D350D90BD}"/>
+    <hyperlink ref="E315" r:id="rId29" xr:uid="{14C34214-6147-4305-92F1-69B213D1FA29}"/>
+    <hyperlink ref="F318" r:id="rId30" xr:uid="{DB7A9083-BA12-48B2-8FF0-15D58BECB5DE}"/>
+    <hyperlink ref="F326" r:id="rId31" xr:uid="{B463ECED-0070-4C60-AB9F-1E345749E26F}"/>
+    <hyperlink ref="E329" r:id="rId32" xr:uid="{47859955-5A53-430D-A74C-A6B0CB190025}"/>
+    <hyperlink ref="E254" r:id="rId33" xr:uid="{4F5E8AA4-E2BF-41E9-9FF9-67C354DB7071}"/>
+    <hyperlink ref="E258" r:id="rId34" xr:uid="{6212D2A7-A60E-4A8A-AC13-A29B95A7B7AD}"/>
+    <hyperlink ref="E260" r:id="rId35" xr:uid="{A312B211-7E36-48C6-86A6-43FFD50F9564}"/>
+    <hyperlink ref="E278" r:id="rId36" xr:uid="{57B1F815-44C0-490D-8DD0-A2C57F66B381}"/>
+    <hyperlink ref="E303" r:id="rId37" xr:uid="{10DAE240-14E7-4DE4-9086-1C76A7B2C1C2}"/>
+    <hyperlink ref="E327" r:id="rId38" xr:uid="{DD87348E-9210-439B-954F-C4B341F5F286}"/>
+    <hyperlink ref="E328" r:id="rId39" xr:uid="{B82F962C-17C5-48A6-9F5B-B7CD6194D005}"/>
+    <hyperlink ref="F213" r:id="rId40" xr:uid="{FBE5799F-EC50-4A5B-9DE1-C5C4BFCCC92C}"/>
+    <hyperlink ref="E293" r:id="rId41" xr:uid="{1EE495D5-212D-491A-9CC1-04E3004E4F7E}"/>
+    <hyperlink ref="E294" r:id="rId42" xr:uid="{466A8EC9-5237-4A15-8DB6-88D959EA8FF9}"/>
+    <hyperlink ref="E241" r:id="rId43" xr:uid="{43CF7CFC-B575-4CEF-990F-50420F12A526}"/>
+    <hyperlink ref="E213" r:id="rId44" xr:uid="{CD293A95-0BE7-4049-9C45-13227B9B3899}"/>
+    <hyperlink ref="E247" r:id="rId45" xr:uid="{9F3BBE7C-4C0F-46BC-A332-52D676A47F56}"/>
+    <hyperlink ref="E292" r:id="rId46" xr:uid="{C71E14FD-F4AF-4F58-8BDE-DD61974BA0D0}"/>
+    <hyperlink ref="E326" r:id="rId47" xr:uid="{202F65B8-C4AF-4ACA-B5DD-3359FDDB3851}"/>
+    <hyperlink ref="E318" r:id="rId48" xr:uid="{B3E5CA03-F23F-4660-8FD9-608AB24280FA}"/>
+    <hyperlink ref="E319" r:id="rId49" xr:uid="{EB737DD4-0742-419E-9E5F-D79F798CAFB3}"/>
+    <hyperlink ref="E320" r:id="rId50" xr:uid="{F5DBAF4B-522C-4066-916B-EC63B938A1A7}"/>
+    <hyperlink ref="E322" r:id="rId51" xr:uid="{5D318D21-33B6-4EC2-B2FC-9D2D18DA583E}"/>
+    <hyperlink ref="E323" r:id="rId52" xr:uid="{2440F621-12BF-4E2B-8789-A46D2B2500BA}"/>
+    <hyperlink ref="E324" r:id="rId53" xr:uid="{D3D217CB-5189-4926-B0BA-F3BF364E8F77}"/>
+    <hyperlink ref="F320" r:id="rId54" xr:uid="{47BDEA1B-924E-4CE2-8E98-6DD194EE2BAD}"/>
+    <hyperlink ref="F323" r:id="rId55" xr:uid="{D6773DAB-BA6A-4BBB-A631-F34DE69BC44B}"/>
+    <hyperlink ref="F324" r:id="rId56" xr:uid="{56916333-2FE8-4766-9AD9-7CB741BE8F6E}"/>
+    <hyperlink ref="F292" r:id="rId57" xr:uid="{741D84FD-594F-41A0-945B-9693BA5B2E43}"/>
+    <hyperlink ref="E299" r:id="rId58" xr:uid="{ABBB5A2A-2058-4BC7-8A5A-FA3B7DA10D51}"/>
+    <hyperlink ref="E307" r:id="rId59" xr:uid="{4FD41E72-4F8A-4977-9FC9-2C3A2484ADA0}"/>
+    <hyperlink ref="E311" r:id="rId60" xr:uid="{40287632-DAC3-4AF3-B01C-FF7ACA2A9408}"/>
+    <hyperlink ref="E313" r:id="rId61" xr:uid="{4016A78B-17C1-4E02-A76A-CAC2C130042E}"/>
+    <hyperlink ref="E314" r:id="rId62" xr:uid="{8814CF23-11DC-4AAF-98EB-6B1811273784}"/>
+    <hyperlink ref="E316" r:id="rId63" xr:uid="{43DA7E86-7356-439E-AEED-52273000DEC4}"/>
+    <hyperlink ref="E317" r:id="rId64" xr:uid="{D06B01CC-EC81-497A-A370-F094234CA4E4}"/>
+    <hyperlink ref="E332" r:id="rId65" xr:uid="{938EF0F2-7159-482C-9152-9C79365F2758}"/>
+    <hyperlink ref="E279" r:id="rId66" xr:uid="{F5547310-3DBD-47CC-86FC-04975E314E85}"/>
+    <hyperlink ref="E280" r:id="rId67" xr:uid="{9BB4BE41-FB94-4B97-8554-61B5C6BC7B19}"/>
+    <hyperlink ref="E232" r:id="rId68" xr:uid="{1E3206D5-6A5F-4BB3-B908-778C9EFD5B9B}"/>
+    <hyperlink ref="E246" r:id="rId69" xr:uid="{EC9D25F5-D3F5-4CFA-85E1-606706827C8F}"/>
+    <hyperlink ref="E245" r:id="rId70" xr:uid="{89A880A0-70F6-481F-8C12-0EE7303F03A2}"/>
+    <hyperlink ref="E250" r:id="rId71" xr:uid="{80A3A707-71DD-4447-82C9-04C263DDF404}"/>
+    <hyperlink ref="E251" r:id="rId72" xr:uid="{AB5C6BC9-BE79-41AB-8C59-570A0C795D4C}"/>
+    <hyperlink ref="E263" r:id="rId73" xr:uid="{C88C226C-07AE-4A36-8C1B-EE98C4EBF5DB}"/>
+    <hyperlink ref="E268" r:id="rId74" xr:uid="{F5172BF6-206F-4BB4-97A1-2BAE2C75241E}"/>
+    <hyperlink ref="E262" r:id="rId75" xr:uid="{83D6BB10-418D-422C-AA91-29FBCD86F8A1}"/>
+    <hyperlink ref="E209" r:id="rId76" xr:uid="{60BD73C8-48D6-44C7-B368-D1C7ECE0C9BC}"/>
+    <hyperlink ref="E206" r:id="rId77" xr:uid="{D3F60027-F747-4C8E-BFCB-BF56F7B70CF6}"/>
+    <hyperlink ref="E196" r:id="rId78" xr:uid="{BD5558B2-94A0-4F99-B693-982BFB0500B8}"/>
+    <hyperlink ref="E198" r:id="rId79" xr:uid="{375C6F58-F39A-4C58-88CA-0A2B8A19765B}"/>
+    <hyperlink ref="F243" r:id="rId80" xr:uid="{99AFF788-2968-42F3-B9A1-9905C969BC3D}"/>
+    <hyperlink ref="F195" r:id="rId81" xr:uid="{B43EF602-57AE-4CEB-93FF-6DC559FC4614}"/>
+    <hyperlink ref="G194" r:id="rId82" xr:uid="{1042BE84-60D9-4073-AE17-3A6941A318F6}"/>
+    <hyperlink ref="F181" r:id="rId83" xr:uid="{FC76A82A-A970-4297-80CC-32FC7060A565}"/>
+    <hyperlink ref="E184" r:id="rId84" xr:uid="{9A3CDCCF-A808-431C-80A7-55C881940664}"/>
+    <hyperlink ref="E185" r:id="rId85" xr:uid="{EF80A702-ACBB-45A9-86FB-8B71571E0E16}"/>
+    <hyperlink ref="E194" r:id="rId86" xr:uid="{94AF04F0-7E17-48D8-8076-7DD3D7AD03A8}"/>
+    <hyperlink ref="E195" r:id="rId87" xr:uid="{5C158E04-14E5-4376-BB48-6F0429F6732B}"/>
+    <hyperlink ref="E304" r:id="rId88" xr:uid="{D2590237-3BED-4C60-B750-4560557DBC76}"/>
+    <hyperlink ref="E305" r:id="rId89" xr:uid="{913DCE0F-4E27-441E-A370-EBDC71595DDE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13925,11 +15225,11 @@
         <v>76</v>
       </c>
       <c r="G3" s="6" t="str">
-        <f>_xlfn.XLOOKUP(F3,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(F3,対応表!$B:$B,対応表!$C:$C,"。")</f>
+        <v>。</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -14537,7 +15837,7 @@
       </c>
       <c r="AI4" s="6" t="str">
         <f>_xlfn.XLOOKUP(AH4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>●</v>
       </c>
       <c r="AJ4" s="7" t="s">
         <v>181</v>
@@ -14980,8 +16280,8 @@
         <v>248</v>
       </c>
       <c r="O5" s="6" t="str">
-        <f>_xlfn.XLOOKUP(N5,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(N5,対応表!$B:$B,対応表!$C:$C,"に")</f>
+        <v>に</v>
       </c>
       <c r="P5" s="7" t="s">
         <v>249</v>
@@ -21141,8 +22441,8 @@
         <v>1234</v>
       </c>
       <c r="M17" s="6" t="str">
-        <f>_xlfn.XLOOKUP(L17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(L17,対応表!$B:$B,対応表!$C:$C,"。")</f>
+        <v>。</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>1235</v>
@@ -21331,7 +22631,7 @@
       </c>
       <c r="BO17" s="6" t="str">
         <f>_xlfn.XLOOKUP(BN17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>γ</v>
       </c>
       <c r="BP17" s="7" t="s">
         <v>1266</v>
@@ -21655,8 +22955,8 @@
         <v>1313</v>
       </c>
       <c r="M18" s="6" t="str">
-        <f>_xlfn.XLOOKUP(L18,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(L18,対応表!$B:$B,対応表!$C:$C,"こ")</f>
+        <v>こ</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>1314</v>
@@ -22162,15 +23462,15 @@
         <v>1391</v>
       </c>
       <c r="K19" s="6" t="str">
-        <f>_xlfn.XLOOKUP(J19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(J19,対応表!$B:$B,対応表!$C:$C,"。")</f>
+        <v>。</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>1392</v>
       </c>
       <c r="M19" s="6" t="str">
-        <f>_xlfn.XLOOKUP(L19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(L19,対応表!$B:$B,対応表!$C:$C,"の")</f>
+        <v>の</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>1393</v>
@@ -22655,8 +23955,8 @@
         <v>1468</v>
       </c>
       <c r="E20" s="25" t="str" cm="1">
-        <f t="array" ref="E20">_xlfn.XLOOKUP(D20,対応表!$B:B,対応表!$C:C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f t="array" ref="E20">_xlfn.XLOOKUP(D20,対応表!$B:B,対応表!$C:C,"で")</f>
+        <v>で</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>1469</v>
@@ -23169,8 +24469,8 @@
         <v>1546</v>
       </c>
       <c r="E21" s="25" t="str" cm="1">
-        <f t="array" ref="E21">_xlfn.XLOOKUP(D21,対応表!$B:B,対応表!$C:C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f t="array" ref="E21">_xlfn.XLOOKUP(D21,対応表!$B:B,対応表!$C:C,"あ")</f>
+        <v>あ</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>1547</v>
@@ -23555,7 +24855,7 @@
       </c>
       <c r="DK21" s="6" t="str">
         <f>_xlfn.XLOOKUP(DJ21,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>加?</v>
+        <v>加</v>
       </c>
       <c r="DL21" s="7" t="s">
         <v>1613</v>
@@ -23683,8 +24983,8 @@
         <v>1630</v>
       </c>
       <c r="E22" s="25" t="str" cm="1">
-        <f t="array" ref="E22">_xlfn.XLOOKUP(D22,対応表!$B:B,対応表!$C:C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f t="array" ref="E22">_xlfn.XLOOKUP(D22,対応表!$B:B,対応表!$C:C,"る")</f>
+        <v>る</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>1631</v>
@@ -23711,8 +25011,8 @@
         <v>1636</v>
       </c>
       <c r="M22" s="6" t="str">
-        <f>_xlfn.XLOOKUP(L22,対応表!$B:$B,対応表!$C:$C,"を")</f>
-        <v>を</v>
+        <f>_xlfn.XLOOKUP(L22,対応表!$B:$B,対応表!$C:$C,"の")</f>
+        <v>の</v>
       </c>
       <c r="N22" s="7" t="s">
         <v>1637</v>
@@ -24262,7 +25562,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="34" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -24312,52 +25612,52 @@
     </row>
     <row r="12" spans="1:3" ht="20.25">
       <c r="C12" s="40" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.25">
       <c r="C13" s="39" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.25">
       <c r="C14" s="39" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.25">
       <c r="C16" s="39" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="18" spans="3:3" ht="20.25">
       <c r="C18" s="39" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="19" spans="3:3" ht="20.25">
       <c r="C19" s="40" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" s="1" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" s="1" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="22" spans="3:3">
       <c r="C22" s="1" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="23" spans="3:3">
       <c r="C23" s="1" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
     </row>
   </sheetData>
@@ -32010,6 +33310,11 @@
         <v>1773</v>
       </c>
     </row>
+    <row r="2" spans="2:134">
+      <c r="B2" s="1" t="s">
+        <v>2282</v>
+      </c>
+    </row>
     <row r="5" spans="2:134">
       <c r="DW5" t="s">
         <v>1774</v>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="695" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA667CCD-3349-420D-88DB-DCF2ACB27C03}"/>
+  <xr:revisionPtr revIDLastSave="711" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28824D42-5EF0-4D7A-ABA7-9C6452D98AF6}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="7305" yWindow="4470" windowWidth="21600" windowHeight="11835" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4065" uniqueCount="2393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="2398">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -9628,10 +9628,6 @@
     <t>佁</t>
   </si>
   <si>
-    <t>●</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>●壁</t>
     <rPh sb="1" eb="2">
       <t>カベ</t>
@@ -9871,16 +9867,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>早いし上げ</t>
-    <rPh sb="0" eb="1">
-      <t>ハヤ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ぞう加/さん加</t>
     <rPh sb="2" eb="3">
       <t>カ</t>
@@ -9982,13 +9968,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>噴水（ランドマーク）</t>
-    <rPh sb="0" eb="2">
-      <t>フンスイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ちか付く</t>
     <rPh sb="2" eb="3">
       <t>ヅ</t>
@@ -10064,10 +10043,6 @@
     <t>傎</t>
   </si>
   <si>
-    <t>γ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>γにあった</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -10182,6 +10157,66 @@
   </si>
   <si>
     <t>ほーむ</t>
+  </si>
+  <si>
+    <t>●?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>γ?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>噴水</t>
+    <rPh sb="0" eb="2">
+      <t>フンスイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いべんとのお知らせ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>早いし上げ/お早めに</t>
+    <rPh sb="0" eb="1">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>決まります</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同時に</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けんさくけっ果</t>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unicode文より</t>
+    <rPh sb="7" eb="8">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -11069,7 +11104,7 @@
         <v>2118</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="E1" s="44" t="s">
         <v>2285</v>
@@ -12234,7 +12269,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="145" spans="2:5">
+    <row r="145" spans="2:6">
       <c r="B145" s="1" t="s">
         <v>1880</v>
       </c>
@@ -12242,7 +12277,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="146" spans="2:5">
+    <row r="146" spans="2:6">
       <c r="B146" s="1" t="s">
         <v>1882</v>
       </c>
@@ -12250,7 +12285,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="147" spans="2:5">
+    <row r="147" spans="2:6">
       <c r="B147" s="1" t="s">
         <v>1884</v>
       </c>
@@ -12258,7 +12293,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="148" spans="2:5">
+    <row r="148" spans="2:6">
       <c r="B148" s="1" t="s">
         <v>1886</v>
       </c>
@@ -12266,7 +12301,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="149" spans="2:5">
+    <row r="149" spans="2:6">
       <c r="B149" s="1" t="s">
         <v>2148</v>
       </c>
@@ -12274,7 +12309,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="150" spans="2:5">
+    <row r="150" spans="2:6">
       <c r="B150" s="1" t="s">
         <v>1889</v>
       </c>
@@ -12282,7 +12317,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="151" spans="2:5">
+    <row r="151" spans="2:6">
       <c r="B151" s="1" t="s">
         <v>1891</v>
       </c>
@@ -12290,7 +12325,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="152" spans="2:5">
+    <row r="152" spans="2:6">
       <c r="B152" s="1" t="s">
         <v>2149</v>
       </c>
@@ -12298,7 +12333,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="153" spans="2:5">
+    <row r="153" spans="2:6">
       <c r="B153" s="1" t="s">
         <v>2150</v>
       </c>
@@ -12306,7 +12341,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="154" spans="2:5">
+    <row r="154" spans="2:6">
       <c r="B154" s="1" t="s">
         <v>1895</v>
       </c>
@@ -12314,7 +12349,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="155" spans="2:5">
+    <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
         <v>1897</v>
       </c>
@@ -12322,7 +12357,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="156" spans="2:5">
+    <row r="156" spans="2:6">
       <c r="B156" s="1" t="s">
         <v>1898</v>
       </c>
@@ -12330,7 +12365,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="157" spans="2:5">
+    <row r="157" spans="2:6">
       <c r="B157" s="1" t="s">
         <v>2151</v>
       </c>
@@ -12338,7 +12373,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="158" spans="2:5">
+    <row r="158" spans="2:6">
       <c r="B158" s="1" t="s">
         <v>1901</v>
       </c>
@@ -12346,7 +12381,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="159" spans="2:5">
+    <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
         <v>1903</v>
       </c>
@@ -12357,10 +12392,13 @@
         <v>2294</v>
       </c>
       <c r="E159" s="45" t="s">
-        <v>2359</v>
-      </c>
-    </row>
-    <row r="160" spans="2:5">
+        <v>2355</v>
+      </c>
+      <c r="F159" s="45" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
       <c r="B160" s="1" t="s">
         <v>1905</v>
       </c>
@@ -12392,10 +12430,10 @@
         <v>1909</v>
       </c>
       <c r="D163" s="44" t="s">
-        <v>2357</v>
+        <v>2353</v>
       </c>
       <c r="E163" s="45" t="s">
-        <v>2360</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="164" spans="2:5">
@@ -12406,10 +12444,10 @@
         <v>1911</v>
       </c>
       <c r="D164" s="44" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="E164" s="45" t="s">
-        <v>2361</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="165" spans="2:5">
@@ -12540,13 +12578,13 @@
         <v>1935</v>
       </c>
       <c r="D180" s="44" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="E180" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
       <c r="F180" s="43" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="181" spans="2:6">
@@ -12557,13 +12595,13 @@
         <v>1937</v>
       </c>
       <c r="D181" s="44" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="E181" s="45" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="F181" s="43" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="182" spans="2:6">
@@ -12590,10 +12628,10 @@
         <v>1941</v>
       </c>
       <c r="D184" s="44" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="E184" s="45" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="185" spans="2:6">
@@ -12604,10 +12642,10 @@
         <v>1942</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="E185" s="45" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="186" spans="2:6">
@@ -12642,10 +12680,10 @@
         <v>1949</v>
       </c>
       <c r="D189" s="44" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="E189" s="45" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="190" spans="2:6">
@@ -12688,16 +12726,16 @@
         <v>2208</v>
       </c>
       <c r="D194" s="44" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E194" s="45" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="F194" s="43" t="s">
-        <v>2388</v>
+        <v>2384</v>
       </c>
       <c r="G194" s="43" t="s">
-        <v>2389</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="195" spans="2:7">
@@ -12708,16 +12746,16 @@
         <v>1958</v>
       </c>
       <c r="D195" s="44" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="E195" s="45" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="F195" s="43" t="s">
-        <v>2388</v>
+        <v>2384</v>
       </c>
       <c r="G195" s="43" t="s">
-        <v>2389</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="196" spans="2:7">
@@ -12728,10 +12766,10 @@
         <v>1960</v>
       </c>
       <c r="D196" s="44" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="E196" s="45" t="s">
-        <v>2385</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="197" spans="2:7">
@@ -12750,10 +12788,13 @@
         <v>1963</v>
       </c>
       <c r="D198" s="44" t="s">
-        <v>2332</v>
+        <v>2393</v>
       </c>
       <c r="E198" s="45" t="s">
-        <v>2386</v>
+        <v>2382</v>
+      </c>
+      <c r="F198" s="45" t="s">
+        <v>2392</v>
       </c>
     </row>
     <row r="199" spans="2:7">
@@ -12772,13 +12813,13 @@
         <v>1966</v>
       </c>
       <c r="D200" s="44" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
       <c r="E200" s="45" t="s">
-        <v>2385</v>
+        <v>2381</v>
       </c>
       <c r="F200" s="43" t="s">
-        <v>2387</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="201" spans="2:7">
@@ -12832,7 +12873,10 @@
         <v>2293</v>
       </c>
       <c r="E206" s="45" t="s">
-        <v>2367</v>
+        <v>2363</v>
+      </c>
+      <c r="F206" s="45" t="s">
+        <v>2388</v>
       </c>
     </row>
     <row r="207" spans="2:7">
@@ -12859,10 +12903,10 @@
         <v>1980</v>
       </c>
       <c r="D209" s="44" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="E209" s="45" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="210" spans="2:6">
@@ -12897,13 +12941,13 @@
         <v>1986</v>
       </c>
       <c r="D213" s="44" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="E213" s="45" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
       <c r="F213" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="214" spans="2:6">
@@ -12941,7 +12985,7 @@
         <v>2292</v>
       </c>
       <c r="E217" s="45" t="s">
-        <v>2391</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="218" spans="2:6">
@@ -12971,7 +13015,7 @@
         <v>2291</v>
       </c>
       <c r="E220" s="45" t="s">
-        <v>2376</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="221" spans="2:6">
@@ -13070,10 +13114,10 @@
         <v>2014</v>
       </c>
       <c r="D232" s="44" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="E232" s="45" t="s">
-        <v>2375</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="233" spans="2:5">
@@ -13084,10 +13128,10 @@
         <v>2015</v>
       </c>
       <c r="D233" s="44" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="E233" s="45" t="s">
-        <v>2377</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="234" spans="2:5">
@@ -13129,6 +13173,12 @@
       <c r="C238" t="s">
         <v>2023</v>
       </c>
+      <c r="D238" s="44" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E238" s="45" t="s">
+        <v>2356</v>
+      </c>
     </row>
     <row r="239" spans="2:5">
       <c r="B239" s="1" t="s">
@@ -13157,7 +13207,7 @@
         <v>2295</v>
       </c>
       <c r="E241" s="45" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="242" spans="2:6">
@@ -13171,7 +13221,7 @@
         <v>2296</v>
       </c>
       <c r="E242" s="45" t="s">
-        <v>2378</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="243" spans="2:6">
@@ -13182,13 +13232,13 @@
         <v>2031</v>
       </c>
       <c r="D243" s="44" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="E243" s="45" t="s">
-        <v>2379</v>
+        <v>2375</v>
       </c>
       <c r="F243" s="45" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="244" spans="2:6">
@@ -13207,10 +13257,10 @@
         <v>2035</v>
       </c>
       <c r="D245" s="44" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="E245" s="45" t="s">
-        <v>2380</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="246" spans="2:6">
@@ -13221,10 +13271,10 @@
         <v>2036</v>
       </c>
       <c r="D246" s="44" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="E246" s="45" t="s">
-        <v>2379</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="247" spans="2:6">
@@ -13235,10 +13285,10 @@
         <v>2037</v>
       </c>
       <c r="D247" s="44" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="E247" s="45" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="248" spans="2:6">
@@ -13265,10 +13315,10 @@
         <v>2040</v>
       </c>
       <c r="D250" s="44" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="E250" s="45" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="251" spans="2:6">
@@ -13279,10 +13329,10 @@
         <v>2041</v>
       </c>
       <c r="D251" s="44" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="E251" s="45" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="252" spans="2:6">
@@ -13309,10 +13359,10 @@
         <v>2046</v>
       </c>
       <c r="D254" s="44" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="E254" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="255" spans="2:6">
@@ -13347,10 +13397,10 @@
         <v>2053</v>
       </c>
       <c r="D258" s="44" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="E258" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="259" spans="2:6">
@@ -13369,10 +13419,10 @@
         <v>2056</v>
       </c>
       <c r="D260" s="44" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="E260" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="261" spans="2:6">
@@ -13383,13 +13433,13 @@
         <v>476</v>
       </c>
       <c r="D261" s="44" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="E261" s="45" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="F261" s="43" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="262" spans="2:6">
@@ -13400,10 +13450,10 @@
         <v>2059</v>
       </c>
       <c r="D262" s="44" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="E262" s="45" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="263" spans="2:6">
@@ -13414,10 +13464,10 @@
         <v>2061</v>
       </c>
       <c r="D263" s="44" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="E263" s="45" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="264" spans="2:6">
@@ -13460,10 +13510,10 @@
         <v>2070</v>
       </c>
       <c r="D268" s="44" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="E268" s="45" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="269" spans="2:6">
@@ -13546,10 +13596,10 @@
         <v>2088</v>
       </c>
       <c r="D278" s="44" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="E278" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="279" spans="2:5">
@@ -13563,7 +13613,7 @@
         <v>2297</v>
       </c>
       <c r="E279" s="45" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="280" spans="2:5">
@@ -13577,7 +13627,7 @@
         <v>432</v>
       </c>
       <c r="E280" s="45" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="281" spans="2:5">
@@ -13644,10 +13694,10 @@
         <v>2105</v>
       </c>
       <c r="D288" s="44" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="E288" s="45" t="s">
-        <v>2375</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="289" spans="2:6">
@@ -13682,13 +13732,13 @@
         <v>2202</v>
       </c>
       <c r="D292" s="44" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="E292" s="45" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F292" s="43" t="s">
         <v>2362</v>
-      </c>
-      <c r="F292" s="43" t="s">
-        <v>2366</v>
       </c>
     </row>
     <row r="293" spans="2:6">
@@ -13699,10 +13749,10 @@
         <v>2277</v>
       </c>
       <c r="D293" s="44" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="E293" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="294" spans="2:6">
@@ -13713,10 +13763,10 @@
         <v>2278</v>
       </c>
       <c r="D294" s="44" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="E294" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="295" spans="2:6">
@@ -13734,6 +13784,9 @@
       <c r="C296" t="s">
         <v>2192</v>
       </c>
+      <c r="D296" s="44" t="s">
+        <v>2397</v>
+      </c>
     </row>
     <row r="297" spans="2:6">
       <c r="B297" s="1" t="s">
@@ -13742,6 +13795,9 @@
       <c r="C297" t="s">
         <v>2193</v>
       </c>
+      <c r="D297" s="44" t="s">
+        <v>2397</v>
+      </c>
     </row>
     <row r="298" spans="2:6">
       <c r="B298" s="1" t="s">
@@ -13759,10 +13815,10 @@
         <v>2195</v>
       </c>
       <c r="D299" s="44" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="E299" s="43" t="s">
-        <v>2366</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="300" spans="2:6">
@@ -13773,10 +13829,10 @@
         <v>2197</v>
       </c>
       <c r="D300" s="44" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="E300" s="45" t="s">
-        <v>2367</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="301" spans="2:6">
@@ -13794,6 +13850,9 @@
       <c r="C302" t="s">
         <v>2219</v>
       </c>
+      <c r="D302" s="44" t="s">
+        <v>2396</v>
+      </c>
     </row>
     <row r="303" spans="2:6">
       <c r="B303" s="21" t="s">
@@ -13803,10 +13862,10 @@
         <v>2201</v>
       </c>
       <c r="D303" s="44" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="E303" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="304" spans="2:6">
@@ -13817,10 +13876,10 @@
         <v>2206</v>
       </c>
       <c r="D304" s="44" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="E304" s="45" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="305" spans="2:6">
@@ -13831,10 +13890,10 @@
         <v>2205</v>
       </c>
       <c r="D305" s="44" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="E305" s="45" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="306" spans="2:6">
@@ -13845,10 +13904,10 @@
         <v>2211</v>
       </c>
       <c r="D306" s="44" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="E306" s="45" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="307" spans="2:6">
@@ -13859,10 +13918,10 @@
         <v>2214</v>
       </c>
       <c r="D307" s="44" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="E307" s="43" t="s">
-        <v>2366</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="308" spans="2:6">
@@ -13873,13 +13932,13 @@
         <v>2224</v>
       </c>
       <c r="D308" s="44" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="E308" s="45" t="s">
-        <v>2369</v>
+        <v>2365</v>
       </c>
       <c r="F308" s="43" t="s">
-        <v>2383</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="309" spans="2:6">
@@ -13890,10 +13949,10 @@
         <v>2228</v>
       </c>
       <c r="D309" s="44" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="E309" s="45" t="s">
-        <v>2370</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="310" spans="2:6">
@@ -13904,10 +13963,10 @@
         <v>2230</v>
       </c>
       <c r="D310" s="44" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
       <c r="E310" s="45" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="311" spans="2:6">
@@ -13918,10 +13977,10 @@
         <v>2232</v>
       </c>
       <c r="D311" s="44" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
       <c r="E311" s="45" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="312" spans="2:6">
@@ -13932,10 +13991,10 @@
         <v>2241</v>
       </c>
       <c r="D312" s="44" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="E312" s="45" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="313" spans="2:6">
@@ -13946,10 +14005,10 @@
         <v>2244</v>
       </c>
       <c r="D313" s="44" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="E313" s="45" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="314" spans="2:6">
@@ -13960,10 +14019,10 @@
         <v>2245</v>
       </c>
       <c r="D314" s="44" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="E314" s="45" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="315" spans="2:6">
@@ -13974,10 +14033,10 @@
         <v>2246</v>
       </c>
       <c r="D315" s="44" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="E315" s="45" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="316" spans="2:6">
@@ -13988,10 +14047,10 @@
         <v>2249</v>
       </c>
       <c r="D316" s="44" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="E316" s="45" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="317" spans="2:6">
@@ -14002,10 +14061,10 @@
         <v>2248</v>
       </c>
       <c r="D317" s="44" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="E317" s="45" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="318" spans="2:6">
@@ -14016,13 +14075,13 @@
         <v>2263</v>
       </c>
       <c r="D318" s="44" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="E318" s="45" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="F318" s="43" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="319" spans="2:6">
@@ -14033,10 +14092,10 @@
         <v>2265</v>
       </c>
       <c r="D319" s="44" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="E319" s="45" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="320" spans="2:6">
@@ -14047,13 +14106,13 @@
         <v>2279</v>
       </c>
       <c r="D320" s="44" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="E320" s="45" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="F320" s="43" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -14063,6 +14122,12 @@
       <c r="C321" t="s">
         <v>2270</v>
       </c>
+      <c r="D321" s="44" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E321" s="43" t="s">
+        <v>2361</v>
+      </c>
     </row>
     <row r="322" spans="1:6">
       <c r="B322" s="1" t="s">
@@ -14072,10 +14137,10 @@
         <v>2268</v>
       </c>
       <c r="D322" s="44" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="E322" s="45" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -14086,13 +14151,13 @@
         <v>2272</v>
       </c>
       <c r="D323" s="44" t="s">
-        <v>2344</v>
+        <v>2391</v>
       </c>
       <c r="E323" s="45" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="F323" s="43" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -14103,13 +14168,13 @@
         <v>2274</v>
       </c>
       <c r="D324" s="44" t="s">
-        <v>2344</v>
+        <v>2391</v>
       </c>
       <c r="E324" s="45" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="F324" s="43" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -14123,7 +14188,7 @@
         <v>2284</v>
       </c>
       <c r="E325" s="45" t="s">
-        <v>2364</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -14137,10 +14202,10 @@
         <v>2283</v>
       </c>
       <c r="E326" s="45" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F326" s="43" t="s">
         <v>2362</v>
-      </c>
-      <c r="F326" s="43" t="s">
-        <v>2366</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -14151,10 +14216,10 @@
         <v>2222</v>
       </c>
       <c r="D327" s="44" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="E327" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -14165,10 +14230,10 @@
         <v>2223</v>
       </c>
       <c r="D328" s="44" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="E328" s="45" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -14179,10 +14244,10 @@
         <v>2281</v>
       </c>
       <c r="D329" s="44" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="E329" s="45" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -14195,27 +14260,27 @@
         <v>2298</v>
       </c>
       <c r="C331" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D331" s="44" t="s">
         <v>2299</v>
       </c>
-      <c r="D331" s="44" t="s">
-        <v>2300</v>
-      </c>
       <c r="E331" s="45" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="B332" s="1" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="C332" t="s">
-        <v>2355</v>
+        <v>2390</v>
       </c>
       <c r="D332" s="44" t="s">
-        <v>2356</v>
+        <v>2352</v>
       </c>
       <c r="E332" s="45" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
   </sheetData>
@@ -14326,6 +14391,11 @@
     <hyperlink ref="E195" r:id="rId87" xr:uid="{5C158E04-14E5-4376-BB48-6F0429F6732B}"/>
     <hyperlink ref="E304" r:id="rId88" xr:uid="{D2590237-3BED-4C60-B750-4560557DBC76}"/>
     <hyperlink ref="E305" r:id="rId89" xr:uid="{913DCE0F-4E27-441E-A370-EBDC71595DDE}"/>
+    <hyperlink ref="F206" r:id="rId90" xr:uid="{CF2F3FBE-5420-4936-8AF6-831F3F2157A3}"/>
+    <hyperlink ref="F159" r:id="rId91" xr:uid="{7F726D61-7F7F-4413-A22C-4011E2BCCB5F}"/>
+    <hyperlink ref="F198" r:id="rId92" xr:uid="{4865438C-E32A-496F-93EF-F7813CFF1DD3}"/>
+    <hyperlink ref="E238" r:id="rId93" xr:uid="{ADF7B2D9-F611-44B4-B8A5-05758C923B02}"/>
+    <hyperlink ref="E321" r:id="rId94" xr:uid="{51F6EE0C-4BDA-4D40-B448-F44D8CE199AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15837,7 +15907,7 @@
       </c>
       <c r="AI4" s="6" t="str">
         <f>_xlfn.XLOOKUP(AH4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>●</v>
+        <v>●?</v>
       </c>
       <c r="AJ4" s="7" t="s">
         <v>181</v>
@@ -22631,7 +22701,7 @@
       </c>
       <c r="BO17" s="6" t="str">
         <f>_xlfn.XLOOKUP(BN17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>γ</v>
+        <v>γ?</v>
       </c>
       <c r="BP17" s="7" t="s">
         <v>1266</v>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="711" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28824D42-5EF0-4D7A-ABA7-9C6452D98AF6}"/>
+  <xr:revisionPtr revIDLastSave="724" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F1196D-07DD-41E7-8E43-FDF8F822F23C}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="2398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4079" uniqueCount="2398">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -9683,13 +9683,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>過ごせる</t>
-    <rPh sb="0" eb="1">
-      <t>ス</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>おきに入り</t>
     <rPh sb="3" eb="4">
       <t>イ</t>
@@ -9759,16 +9752,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ご報こく/情報</t>
-    <rPh sb="1" eb="2">
-      <t>ホウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>文化</t>
     <rPh sb="0" eb="2">
       <t>ブンカ</t>
@@ -9801,10 +9784,6 @@
     <rPh sb="0" eb="1">
       <t>タイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>□■せーる</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -10215,6 +10194,33 @@
     <t>unicode文より</t>
     <rPh sb="7" eb="8">
       <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ご報こく/情?報</t>
+    <rPh sb="1" eb="2">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>□■せーる/□■なひととき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過ごせる/過ごす/過♢</t>
+    <rPh sb="0" eb="1">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ス</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -11093,7 +11099,8 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="4" max="5" width="21.375" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.375" style="44" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="42" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="42" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="9" style="42"/>
@@ -12392,10 +12399,10 @@
         <v>2294</v>
       </c>
       <c r="E159" s="45" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="F159" s="45" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="160" spans="2:6">
@@ -12430,10 +12437,10 @@
         <v>1909</v>
       </c>
       <c r="D163" s="44" t="s">
+        <v>2350</v>
+      </c>
+      <c r="E163" s="45" t="s">
         <v>2353</v>
-      </c>
-      <c r="E163" s="45" t="s">
-        <v>2356</v>
       </c>
     </row>
     <row r="164" spans="2:5">
@@ -12444,10 +12451,10 @@
         <v>1911</v>
       </c>
       <c r="D164" s="44" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="E164" s="45" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="165" spans="2:5">
@@ -12546,7 +12553,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="177" spans="2:6">
+    <row r="177" spans="2:7">
       <c r="B177" s="1" t="s">
         <v>1930</v>
       </c>
@@ -12554,7 +12561,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="178" spans="2:6">
+    <row r="178" spans="2:7">
       <c r="B178" s="1" t="s">
         <v>2156</v>
       </c>
@@ -12562,7 +12569,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="179" spans="2:6">
+    <row r="179" spans="2:7">
       <c r="B179" s="1" t="s">
         <v>1932</v>
       </c>
@@ -12570,7 +12577,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="180" spans="2:6">
+    <row r="180" spans="2:7">
       <c r="B180" s="1" t="s">
         <v>1934</v>
       </c>
@@ -12578,16 +12585,16 @@
         <v>1935</v>
       </c>
       <c r="D180" s="44" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="E180" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="F180" s="43" t="s">
-        <v>2386</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="181" spans="2:7">
       <c r="B181" s="1" t="s">
         <v>1936</v>
       </c>
@@ -12595,16 +12602,16 @@
         <v>1937</v>
       </c>
       <c r="D181" s="44" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="E181" s="45" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="F181" s="43" t="s">
-        <v>2386</v>
-      </c>
-    </row>
-    <row r="182" spans="2:6">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="182" spans="2:7">
       <c r="B182" s="1" t="s">
         <v>1938</v>
       </c>
@@ -12612,7 +12619,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="183" spans="2:6">
+    <row r="183" spans="2:7">
       <c r="B183" s="1" t="s">
         <v>2157</v>
       </c>
@@ -12620,7 +12627,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="184" spans="2:6">
+    <row r="184" spans="2:7">
       <c r="B184" s="1" t="s">
         <v>2158</v>
       </c>
@@ -12631,10 +12638,10 @@
         <v>2305</v>
       </c>
       <c r="E184" s="45" t="s">
-        <v>2388</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="185" spans="2:7">
       <c r="B185" s="1" t="s">
         <v>2159</v>
       </c>
@@ -12642,13 +12649,19 @@
         <v>1942</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>2306</v>
+        <v>2397</v>
       </c>
       <c r="E185" s="45" t="s">
-        <v>2388</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
+        <v>2385</v>
+      </c>
+      <c r="F185" s="45" t="s">
+        <v>2375</v>
+      </c>
+      <c r="G185" s="45" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="186" spans="2:7">
       <c r="B186" s="1" t="s">
         <v>1943</v>
       </c>
@@ -12656,7 +12669,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="187" spans="2:6">
+    <row r="187" spans="2:7">
       <c r="B187" s="1" t="s">
         <v>1945</v>
       </c>
@@ -12664,7 +12677,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="188" spans="2:6">
+    <row r="188" spans="2:7">
       <c r="B188" s="1" t="s">
         <v>1946</v>
       </c>
@@ -12672,7 +12685,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="189" spans="2:6">
+    <row r="189" spans="2:7">
       <c r="B189" s="1" t="s">
         <v>1948</v>
       </c>
@@ -12680,13 +12693,13 @@
         <v>1949</v>
       </c>
       <c r="D189" s="44" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="E189" s="45" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="190" spans="2:6">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="190" spans="2:7">
       <c r="B190" s="1" t="s">
         <v>1950</v>
       </c>
@@ -12694,7 +12707,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="191" spans="2:6">
+    <row r="191" spans="2:7">
       <c r="B191" s="1" t="s">
         <v>1952</v>
       </c>
@@ -12702,7 +12715,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="192" spans="2:6">
+    <row r="192" spans="2:7">
       <c r="B192" s="1" t="s">
         <v>2160</v>
       </c>
@@ -12729,13 +12742,13 @@
         <v>2303</v>
       </c>
       <c r="E194" s="45" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="F194" s="43" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
       <c r="G194" s="43" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="195" spans="2:7">
@@ -12749,13 +12762,13 @@
         <v>2303</v>
       </c>
       <c r="E195" s="45" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="F195" s="43" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
       <c r="G195" s="43" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="196" spans="2:7">
@@ -12766,10 +12779,10 @@
         <v>1960</v>
       </c>
       <c r="D196" s="44" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="E196" s="45" t="s">
-        <v>2381</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="197" spans="2:7">
@@ -12788,13 +12801,13 @@
         <v>1963</v>
       </c>
       <c r="D198" s="44" t="s">
-        <v>2393</v>
+        <v>2390</v>
       </c>
       <c r="E198" s="45" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="F198" s="45" t="s">
-        <v>2392</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="199" spans="2:7">
@@ -12813,13 +12826,13 @@
         <v>1966</v>
       </c>
       <c r="D200" s="44" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="E200" s="45" t="s">
-        <v>2381</v>
+        <v>2378</v>
       </c>
       <c r="F200" s="43" t="s">
-        <v>2383</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="201" spans="2:7">
@@ -12873,10 +12886,10 @@
         <v>2293</v>
       </c>
       <c r="E206" s="45" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
       <c r="F206" s="45" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="207" spans="2:7">
@@ -12903,10 +12916,10 @@
         <v>1980</v>
       </c>
       <c r="D209" s="44" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="E209" s="45" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="210" spans="2:6">
@@ -12941,13 +12954,13 @@
         <v>1986</v>
       </c>
       <c r="D213" s="44" t="s">
-        <v>2316</v>
+        <v>2395</v>
       </c>
       <c r="E213" s="45" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="F213" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="214" spans="2:6">
@@ -12985,7 +12998,7 @@
         <v>2292</v>
       </c>
       <c r="E217" s="45" t="s">
-        <v>2387</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="218" spans="2:6">
@@ -13015,7 +13028,7 @@
         <v>2291</v>
       </c>
       <c r="E220" s="45" t="s">
-        <v>2372</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="221" spans="2:6">
@@ -13114,10 +13127,10 @@
         <v>2014</v>
       </c>
       <c r="D232" s="44" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="E232" s="45" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="233" spans="2:5">
@@ -13128,10 +13141,10 @@
         <v>2015</v>
       </c>
       <c r="D233" s="44" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
       <c r="E233" s="45" t="s">
-        <v>2373</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="234" spans="2:5">
@@ -13174,10 +13187,10 @@
         <v>2023</v>
       </c>
       <c r="D238" s="44" t="s">
-        <v>2394</v>
+        <v>2391</v>
       </c>
       <c r="E238" s="45" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="239" spans="2:5">
@@ -13207,7 +13220,7 @@
         <v>2295</v>
       </c>
       <c r="E241" s="45" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="242" spans="2:6">
@@ -13221,7 +13234,7 @@
         <v>2296</v>
       </c>
       <c r="E242" s="45" t="s">
-        <v>2374</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="243" spans="2:6">
@@ -13232,13 +13245,13 @@
         <v>2031</v>
       </c>
       <c r="D243" s="44" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
       <c r="E243" s="45" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="F243" s="45" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="244" spans="2:6">
@@ -13257,10 +13270,10 @@
         <v>2035</v>
       </c>
       <c r="D245" s="44" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="E245" s="45" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="246" spans="2:6">
@@ -13271,10 +13284,10 @@
         <v>2036</v>
       </c>
       <c r="D246" s="44" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="E246" s="45" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="247" spans="2:6">
@@ -13285,10 +13298,10 @@
         <v>2037</v>
       </c>
       <c r="D247" s="44" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="E247" s="45" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="248" spans="2:6">
@@ -13315,10 +13328,10 @@
         <v>2040</v>
       </c>
       <c r="D250" s="44" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="E250" s="45" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="251" spans="2:6">
@@ -13329,10 +13342,10 @@
         <v>2041</v>
       </c>
       <c r="D251" s="44" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="E251" s="45" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="252" spans="2:6">
@@ -13359,10 +13372,10 @@
         <v>2046</v>
       </c>
       <c r="D254" s="44" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="E254" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="255" spans="2:6">
@@ -13397,10 +13410,10 @@
         <v>2053</v>
       </c>
       <c r="D258" s="44" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="E258" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="259" spans="2:6">
@@ -13419,10 +13432,10 @@
         <v>2056</v>
       </c>
       <c r="D260" s="44" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="E260" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="261" spans="2:6">
@@ -13433,13 +13446,13 @@
         <v>476</v>
       </c>
       <c r="D261" s="44" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="E261" s="45" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
       <c r="F261" s="43" t="s">
-        <v>2377</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="262" spans="2:6">
@@ -13450,10 +13463,10 @@
         <v>2059</v>
       </c>
       <c r="D262" s="44" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="E262" s="45" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="263" spans="2:6">
@@ -13464,10 +13477,10 @@
         <v>2061</v>
       </c>
       <c r="D263" s="44" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="E263" s="45" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="264" spans="2:6">
@@ -13510,10 +13523,10 @@
         <v>2070</v>
       </c>
       <c r="D268" s="44" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="E268" s="45" t="s">
-        <v>2378</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="269" spans="2:6">
@@ -13596,10 +13609,10 @@
         <v>2088</v>
       </c>
       <c r="D278" s="44" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="E278" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="279" spans="2:5">
@@ -13613,7 +13626,7 @@
         <v>2297</v>
       </c>
       <c r="E279" s="45" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="280" spans="2:5">
@@ -13627,7 +13640,7 @@
         <v>432</v>
       </c>
       <c r="E280" s="45" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="281" spans="2:5">
@@ -13694,10 +13707,10 @@
         <v>2105</v>
       </c>
       <c r="D288" s="44" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="E288" s="45" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="289" spans="2:6">
@@ -13732,13 +13745,13 @@
         <v>2202</v>
       </c>
       <c r="D292" s="44" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="E292" s="45" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="F292" s="43" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="293" spans="2:6">
@@ -13749,10 +13762,10 @@
         <v>2277</v>
       </c>
       <c r="D293" s="44" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="E293" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="294" spans="2:6">
@@ -13763,10 +13776,10 @@
         <v>2278</v>
       </c>
       <c r="D294" s="44" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="E294" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="295" spans="2:6">
@@ -13785,7 +13798,7 @@
         <v>2192</v>
       </c>
       <c r="D296" s="44" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="297" spans="2:6">
@@ -13796,7 +13809,7 @@
         <v>2193</v>
       </c>
       <c r="D297" s="44" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="298" spans="2:6">
@@ -13815,10 +13828,10 @@
         <v>2195</v>
       </c>
       <c r="D299" s="44" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="E299" s="43" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="300" spans="2:6">
@@ -13829,10 +13842,10 @@
         <v>2197</v>
       </c>
       <c r="D300" s="44" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="E300" s="45" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="301" spans="2:6">
@@ -13851,7 +13864,7 @@
         <v>2219</v>
       </c>
       <c r="D302" s="44" t="s">
-        <v>2396</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="303" spans="2:6">
@@ -13862,10 +13875,10 @@
         <v>2201</v>
       </c>
       <c r="D303" s="44" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="E303" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="304" spans="2:6">
@@ -13879,7 +13892,7 @@
         <v>2304</v>
       </c>
       <c r="E304" s="45" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="305" spans="2:6">
@@ -13893,7 +13906,7 @@
         <v>2304</v>
       </c>
       <c r="E305" s="45" t="s">
-        <v>2388</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="306" spans="2:6">
@@ -13904,10 +13917,10 @@
         <v>2211</v>
       </c>
       <c r="D306" s="44" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="E306" s="45" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="307" spans="2:6">
@@ -13918,10 +13931,10 @@
         <v>2214</v>
       </c>
       <c r="D307" s="44" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="E307" s="43" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="308" spans="2:6">
@@ -13935,10 +13948,10 @@
         <v>2300</v>
       </c>
       <c r="E308" s="45" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
       <c r="F308" s="43" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="309" spans="2:6">
@@ -13952,7 +13965,7 @@
         <v>2301</v>
       </c>
       <c r="E309" s="45" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="310" spans="2:6">
@@ -13963,10 +13976,10 @@
         <v>2230</v>
       </c>
       <c r="D310" s="44" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="E310" s="45" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="311" spans="2:6">
@@ -13977,10 +13990,10 @@
         <v>2232</v>
       </c>
       <c r="D311" s="44" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="E311" s="45" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="312" spans="2:6">
@@ -13991,10 +14004,10 @@
         <v>2241</v>
       </c>
       <c r="D312" s="44" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="E312" s="45" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="313" spans="2:6">
@@ -14005,10 +14018,10 @@
         <v>2244</v>
       </c>
       <c r="D313" s="44" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="E313" s="45" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="314" spans="2:6">
@@ -14019,10 +14032,10 @@
         <v>2245</v>
       </c>
       <c r="D314" s="44" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="E314" s="45" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="315" spans="2:6">
@@ -14033,10 +14046,10 @@
         <v>2246</v>
       </c>
       <c r="D315" s="44" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="E315" s="45" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="316" spans="2:6">
@@ -14047,10 +14060,10 @@
         <v>2249</v>
       </c>
       <c r="D316" s="44" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="E316" s="45" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="317" spans="2:6">
@@ -14061,10 +14074,10 @@
         <v>2248</v>
       </c>
       <c r="D317" s="44" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="E317" s="45" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="318" spans="2:6">
@@ -14075,13 +14088,13 @@
         <v>2263</v>
       </c>
       <c r="D318" s="44" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="E318" s="45" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="F318" s="43" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="319" spans="2:6">
@@ -14092,10 +14105,10 @@
         <v>2265</v>
       </c>
       <c r="D319" s="44" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
       <c r="E319" s="45" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="320" spans="2:6">
@@ -14106,13 +14119,13 @@
         <v>2279</v>
       </c>
       <c r="D320" s="44" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="E320" s="45" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="F320" s="43" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -14123,10 +14136,10 @@
         <v>2270</v>
       </c>
       <c r="D321" s="44" t="s">
-        <v>2395</v>
+        <v>2392</v>
       </c>
       <c r="E321" s="43" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -14137,10 +14150,10 @@
         <v>2268</v>
       </c>
       <c r="D322" s="44" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="E322" s="45" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -14151,13 +14164,13 @@
         <v>2272</v>
       </c>
       <c r="D323" s="44" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="E323" s="45" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="F323" s="43" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -14168,13 +14181,13 @@
         <v>2274</v>
       </c>
       <c r="D324" s="44" t="s">
-        <v>2391</v>
+        <v>2388</v>
       </c>
       <c r="E324" s="45" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="F324" s="43" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -14188,7 +14201,7 @@
         <v>2284</v>
       </c>
       <c r="E325" s="45" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -14202,10 +14215,10 @@
         <v>2283</v>
       </c>
       <c r="E326" s="45" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="F326" s="43" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -14216,10 +14229,13 @@
         <v>2222</v>
       </c>
       <c r="D327" s="44" t="s">
-        <v>2322</v>
+        <v>2396</v>
       </c>
       <c r="E327" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
+      </c>
+      <c r="F327" s="45" t="s">
+        <v>2375</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -14230,10 +14246,13 @@
         <v>2223</v>
       </c>
       <c r="D328" s="44" t="s">
-        <v>2322</v>
+        <v>2396</v>
       </c>
       <c r="E328" s="45" t="s">
-        <v>2354</v>
+        <v>2351</v>
+      </c>
+      <c r="F328" s="45" t="s">
+        <v>2375</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -14244,43 +14263,43 @@
         <v>2281</v>
       </c>
       <c r="D329" s="44" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="E329" s="45" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="330" spans="1:6">
-      <c r="A330" t="s">
-        <v>2113</v>
+      <c r="B330" s="1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C330" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D330" s="44" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E330" s="45" t="s">
+        <v>2367</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="B331" s="1" t="s">
-        <v>2298</v>
+        <v>2348</v>
       </c>
       <c r="C331" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="D331" s="44" t="s">
-        <v>2299</v>
+        <v>2349</v>
       </c>
       <c r="E331" s="45" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="332" spans="1:6">
-      <c r="B332" s="1" t="s">
-        <v>2351</v>
-      </c>
-      <c r="C332" t="s">
-        <v>2390</v>
-      </c>
-      <c r="D332" s="44" t="s">
-        <v>2352</v>
-      </c>
-      <c r="E332" s="45" t="s">
-        <v>2370</v>
+      <c r="A332" t="s">
+        <v>2113</v>
       </c>
     </row>
   </sheetData>
@@ -14305,7 +14324,7 @@
     <hyperlink ref="E217" r:id="rId1" xr:uid="{2BD22168-2F0F-4260-8DC6-FCDAA83902A4}"/>
     <hyperlink ref="E220" r:id="rId2" xr:uid="{5A86A9C8-18B7-49D4-B0DA-510F8507220D}"/>
     <hyperlink ref="E242" r:id="rId3" xr:uid="{E8BDD6E9-53E1-49ED-9A35-0FFE574C21E6}"/>
-    <hyperlink ref="E331" r:id="rId4" xr:uid="{15456AB3-5F70-432C-91F1-C3B6D972B050}"/>
+    <hyperlink ref="E330" r:id="rId4" xr:uid="{15456AB3-5F70-432C-91F1-C3B6D972B050}"/>
     <hyperlink ref="E325" r:id="rId5" xr:uid="{B5E564C1-2202-4076-A41F-2A29B21EEF86}"/>
     <hyperlink ref="E309" r:id="rId6" xr:uid="{4E8F2926-23D8-4338-A705-D1EB793CFD3E}"/>
     <hyperlink ref="E308" r:id="rId7" xr:uid="{82427E63-C1DB-4ADE-A529-AB11239EFCCF}"/>
@@ -14366,7 +14385,7 @@
     <hyperlink ref="E314" r:id="rId62" xr:uid="{8814CF23-11DC-4AAF-98EB-6B1811273784}"/>
     <hyperlink ref="E316" r:id="rId63" xr:uid="{43DA7E86-7356-439E-AEED-52273000DEC4}"/>
     <hyperlink ref="E317" r:id="rId64" xr:uid="{D06B01CC-EC81-497A-A370-F094234CA4E4}"/>
-    <hyperlink ref="E332" r:id="rId65" xr:uid="{938EF0F2-7159-482C-9152-9C79365F2758}"/>
+    <hyperlink ref="E331" r:id="rId65" xr:uid="{938EF0F2-7159-482C-9152-9C79365F2758}"/>
     <hyperlink ref="E279" r:id="rId66" xr:uid="{F5547310-3DBD-47CC-86FC-04975E314E85}"/>
     <hyperlink ref="E280" r:id="rId67" xr:uid="{9BB4BE41-FB94-4B97-8554-61B5C6BC7B19}"/>
     <hyperlink ref="E232" r:id="rId68" xr:uid="{1E3206D5-6A5F-4BB3-B908-778C9EFD5B9B}"/>
@@ -14396,6 +14415,10 @@
     <hyperlink ref="F198" r:id="rId92" xr:uid="{4865438C-E32A-496F-93EF-F7813CFF1DD3}"/>
     <hyperlink ref="E238" r:id="rId93" xr:uid="{ADF7B2D9-F611-44B4-B8A5-05758C923B02}"/>
     <hyperlink ref="E321" r:id="rId94" xr:uid="{51F6EE0C-4BDA-4D40-B448-F44D8CE199AF}"/>
+    <hyperlink ref="F327" r:id="rId95" xr:uid="{FA1433D3-A125-4D91-8655-CE3041406BBF}"/>
+    <hyperlink ref="F328" r:id="rId96" xr:uid="{E87B89B3-92DB-4654-B59A-DBB66B4F00DE}"/>
+    <hyperlink ref="F185" r:id="rId97" xr:uid="{0CEED77C-AE3C-4AC3-BA83-9660F17E5B98}"/>
+    <hyperlink ref="G185" r:id="rId98" xr:uid="{D649C43C-4568-4298-B2DB-D4088A7995C4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="724" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F1196D-07DD-41E7-8E43-FDF8F822F23C}"/>
+  <xr:revisionPtr revIDLastSave="802" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9D04B72-34D8-4B06-9425-1882854493E7}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
     <sheet name="unicode" sheetId="5" r:id="rId2"/>
     <sheet name="検索文字" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId5"/>
+    <sheet name="メモ" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -407,7 +408,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4079" uniqueCount="2398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4102" uniqueCount="2416">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8339,9 +8340,6 @@
     <t>性</t>
   </si>
   <si>
-    <t>歩?</t>
-  </si>
-  <si>
     <t>過?</t>
   </si>
   <si>
@@ -8405,13 +8403,7 @@
     <t>切</t>
   </si>
   <si>
-    <t>早?</t>
-  </si>
-  <si>
     <t>乄</t>
-  </si>
-  <si>
-    <t>常</t>
   </si>
   <si>
     <t>異?</t>
@@ -9267,14 +9259,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>□?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>防?</t>
     <rPh sb="0" eb="1">
       <t>フセ</t>
@@ -9363,20 +9347,6 @@
     <t>凇</t>
   </si>
   <si>
-    <t>隔?</t>
-    <rPh sb="0" eb="1">
-      <t>カク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>離?</t>
-    <rPh sb="0" eb="1">
-      <t>リ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>捌?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -9417,9 +9387,6 @@
   </si>
   <si>
     <t>匰儽</t>
-  </si>
-  <si>
-    <t>丣個僇亵乐卜丸亡</t>
   </si>
   <si>
     <t>主別丟</t>
@@ -9672,13 +9639,6 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>バ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>歩きまわる</t>
-    <rPh sb="0" eb="1">
-      <t>アル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9846,32 +9806,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ぞう加/さん加</t>
-    <rPh sb="2" eb="3">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>影捌けの舞</t>
     <rPh sb="0" eb="1">
       <t>カゲ</t>
     </rPh>
     <rPh sb="4" eb="5">
       <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>隔離するための場所</t>
-    <rPh sb="0" eb="2">
-      <t>カクリ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バショ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10157,70 +10097,291 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>早いし上げ/お早めに</t>
+    <t>決まります</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同時に</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>けんさくけっ果</t>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unicode文より</t>
+    <rPh sb="7" eb="8">
+      <t>ブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世乥一儵</t>
+  </si>
+  <si>
+    <t>たばこ屋</t>
+    <rPh sb="3" eb="4">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索することで消える前の画像が見られるのでは？</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桶文字</t>
+    <rPh sb="0" eb="3">
+      <t>オケモジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語</t>
+    <rPh sb="0" eb="3">
+      <t>ニホンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水覗像/王？</t>
+  </si>
+  <si>
+    <t>早いし上げ ・お早めに</t>
     <rPh sb="0" eb="1">
       <t>ハヤ</t>
     </rPh>
     <rPh sb="3" eb="4">
       <t>ア</t>
     </rPh>
-    <rPh sb="7" eb="8">
+    <rPh sb="8" eb="9">
       <t>ハヤ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>決まります</t>
-    <rPh sb="0" eb="1">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>同時に</t>
-    <rPh sb="0" eb="2">
-      <t>ドウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>けんさくけっ果</t>
-    <rPh sb="6" eb="7">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>unicode文より</t>
-    <rPh sb="7" eb="8">
-      <t>ブン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ご報こく/情?報</t>
+    <t>ご報こく ・情?報</t>
     <rPh sb="1" eb="2">
       <t>ホウ</t>
     </rPh>
-    <rPh sb="5" eb="6">
+    <rPh sb="6" eb="7">
       <t>ジョウ</t>
     </rPh>
-    <rPh sb="7" eb="8">
+    <rPh sb="8" eb="9">
       <t>ホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>□■せーる/□■なひととき</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>過ごせる/過ごす/過♢</t>
+    <t>ぞう加 ・さん加</t>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>噴水 ・水覗象/王</t>
+    <rPh sb="0" eb="2">
+      <t>フンスイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過ごせる ・過ごす ・過♢</t>
     <rPh sb="0" eb="1">
       <t>ス</t>
     </rPh>
-    <rPh sb="5" eb="6">
+    <rPh sb="6" eb="7">
       <t>ス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩きまわる ・歩み</t>
+    <rPh sb="0" eb="1">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アユ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特?</t>
+    <rPh sb="0" eb="1">
+      <t>トク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>別?</t>
+    <rPh sb="0" eb="1">
+      <t>ベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特別セール ・特別なひととき</t>
+    <rPh sb="0" eb="2">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トクベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>早</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お知らせ</t>
+    <rPh sb="1" eb="2">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兆し？</t>
+    <rPh sb="0" eb="1">
+      <t>キザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>影捌け？</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丣個僇亵乐卜丸亡</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>噴水？</t>
+    <rPh sb="0" eb="2">
+      <t>フンスイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>つぐない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>交流？</t>
+    <rPh sb="0" eb="2">
+      <t>コウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常明像</t>
+    <rPh sb="0" eb="1">
+      <t>ツネ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>アキラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特別？</t>
+    <rPh sb="0" eb="2">
+      <t>トクベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>准凇</t>
+  </si>
+  <si>
+    <t>隔離？</t>
+    <rPh sb="0" eb="2">
+      <t>カクリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収?</t>
+    <rPh sb="0" eb="1">
+      <t>オサム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>監?</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収監するための場所</t>
+    <rPh sb="0" eb="2">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バショ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10229,7 +10390,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10433,6 +10594,21 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Underground"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -10484,7 +10660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -10541,6 +10717,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -10550,7 +10741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10687,6 +10878,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11101,35 +11304,35 @@
     <col min="2" max="2" width="9" style="1"/>
     <col min="4" max="4" width="26.5" style="44" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.375" style="44" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.125" style="42" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="42" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.125" style="42" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="9" style="42"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>2302</v>
+        <v>2294</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>2285</v>
+        <v>2277</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>2286</v>
+        <v>2278</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>2287</v>
+        <v>2279</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>2288</v>
+        <v>2280</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>2289</v>
+        <v>2281</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>2290</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -11374,7 +11577,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="1" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -11486,7 +11689,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" s="1" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="C46">
         <v>43</v>
@@ -11630,7 +11833,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" s="1" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
       <c r="C64">
         <v>61</v>
@@ -11702,7 +11905,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" s="1" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="C73" t="s">
         <v>1777</v>
@@ -11782,7 +11985,7 @@
     </row>
     <row r="83" spans="2:3">
       <c r="B83" s="1" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="C83" t="s">
         <v>1795</v>
@@ -11798,7 +12001,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="B85" s="1" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
       <c r="C85" t="s">
         <v>1798</v>
@@ -11806,7 +12009,7 @@
     </row>
     <row r="86" spans="2:3">
       <c r="B86" s="1" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="C86" t="s">
         <v>1799</v>
@@ -11814,7 +12017,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="B87" s="1" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="C87" t="s">
         <v>990</v>
@@ -11838,7 +12041,7 @@
     </row>
     <row r="90" spans="2:3">
       <c r="B90" s="1" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="C90" t="s">
         <v>1803</v>
@@ -11854,7 +12057,7 @@
     </row>
     <row r="92" spans="2:3">
       <c r="B92" s="1" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="C92" t="s">
         <v>827</v>
@@ -11886,7 +12089,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" s="1" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="C96" t="s">
         <v>1812</v>
@@ -11918,7 +12121,7 @@
     </row>
     <row r="100" spans="2:3">
       <c r="B100" s="1" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
       <c r="C100" t="s">
         <v>832</v>
@@ -11934,7 +12137,7 @@
     </row>
     <row r="102" spans="2:3">
       <c r="B102" s="1" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="C102" t="s">
         <v>1820</v>
@@ -11942,7 +12145,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" s="1" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="C103" t="s">
         <v>1821</v>
@@ -11958,7 +12161,7 @@
     </row>
     <row r="105" spans="2:3">
       <c r="B105" s="1" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="C105" t="s">
         <v>1824</v>
@@ -11982,7 +12185,7 @@
     </row>
     <row r="108" spans="2:3">
       <c r="B108" s="1" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="C108" t="s">
         <v>1828</v>
@@ -11990,7 +12193,7 @@
     </row>
     <row r="109" spans="2:3">
       <c r="B109" s="1" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="C109" t="s">
         <v>1829</v>
@@ -11998,7 +12201,7 @@
     </row>
     <row r="110" spans="2:3">
       <c r="B110" s="1" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="C110" t="s">
         <v>1830</v>
@@ -12014,7 +12217,7 @@
     </row>
     <row r="112" spans="2:3">
       <c r="B112" s="1" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="C112" t="s">
         <v>1833</v>
@@ -12030,7 +12233,7 @@
     </row>
     <row r="114" spans="2:3">
       <c r="B114" s="1" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="C114" t="s">
         <v>1836</v>
@@ -12038,7 +12241,7 @@
     </row>
     <row r="115" spans="2:3">
       <c r="B115" s="1" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="C115" t="s">
         <v>1837</v>
@@ -12046,7 +12249,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" s="1" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="C116" t="s">
         <v>1838</v>
@@ -12062,7 +12265,7 @@
     </row>
     <row r="118" spans="2:3">
       <c r="B118" s="1" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="C118" t="s">
         <v>1840</v>
@@ -12078,7 +12281,7 @@
     </row>
     <row r="120" spans="2:3">
       <c r="B120" s="1" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="C120" t="s">
         <v>1843</v>
@@ -12094,7 +12297,7 @@
     </row>
     <row r="122" spans="2:3">
       <c r="B122" s="1" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="C122" t="s">
         <v>1846</v>
@@ -12102,7 +12305,7 @@
     </row>
     <row r="123" spans="2:3">
       <c r="B123" s="1" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
       <c r="C123" t="s">
         <v>1847</v>
@@ -12110,7 +12313,7 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" s="1" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
       <c r="C124" t="s">
         <v>1848</v>
@@ -12118,7 +12321,7 @@
     </row>
     <row r="125" spans="2:3">
       <c r="B125" s="1" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="C125" t="s">
         <v>1849</v>
@@ -12150,7 +12353,7 @@
     </row>
     <row r="129" spans="2:3">
       <c r="B129" s="1" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="C129" t="s">
         <v>1856</v>
@@ -12174,7 +12377,7 @@
     </row>
     <row r="132" spans="2:3">
       <c r="B132" s="1" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="C132" t="s">
         <v>1860</v>
@@ -12190,7 +12393,7 @@
     </row>
     <row r="134" spans="2:3">
       <c r="B134" s="1" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="C134" t="s">
         <v>1862</v>
@@ -12198,7 +12401,7 @@
     </row>
     <row r="135" spans="2:3">
       <c r="B135" s="1" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="C135" t="s">
         <v>1863</v>
@@ -12206,7 +12409,7 @@
     </row>
     <row r="136" spans="2:3">
       <c r="B136" s="1" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="C136" t="s">
         <v>1864</v>
@@ -12254,7 +12457,7 @@
     </row>
     <row r="142" spans="2:3">
       <c r="B142" s="1" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="C142" t="s">
         <v>1875</v>
@@ -12276,7 +12479,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="145" spans="2:6">
+    <row r="145" spans="2:7">
       <c r="B145" s="1" t="s">
         <v>1880</v>
       </c>
@@ -12284,7 +12487,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="146" spans="2:6">
+    <row r="146" spans="2:7">
       <c r="B146" s="1" t="s">
         <v>1882</v>
       </c>
@@ -12292,7 +12495,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
+    <row r="147" spans="2:7">
       <c r="B147" s="1" t="s">
         <v>1884</v>
       </c>
@@ -12300,7 +12503,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="148" spans="2:6">
+    <row r="148" spans="2:7">
       <c r="B148" s="1" t="s">
         <v>1886</v>
       </c>
@@ -12308,15 +12511,15 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
+    <row r="149" spans="2:7">
       <c r="B149" s="1" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="C149" t="s">
         <v>1888</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
+    <row r="150" spans="2:7">
       <c r="B150" s="1" t="s">
         <v>1889</v>
       </c>
@@ -12324,7 +12527,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="151" spans="2:6">
+    <row r="151" spans="2:7">
       <c r="B151" s="1" t="s">
         <v>1891</v>
       </c>
@@ -12332,23 +12535,23 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
+    <row r="152" spans="2:7">
       <c r="B152" s="1" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="C152" t="s">
         <v>1893</v>
       </c>
     </row>
-    <row r="153" spans="2:6">
+    <row r="153" spans="2:7">
       <c r="B153" s="1" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="C153" t="s">
         <v>1894</v>
       </c>
     </row>
-    <row r="154" spans="2:6">
+    <row r="154" spans="2:7">
       <c r="B154" s="1" t="s">
         <v>1895</v>
       </c>
@@ -12356,7 +12559,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="155" spans="2:6">
+    <row r="155" spans="2:7">
       <c r="B155" s="1" t="s">
         <v>1897</v>
       </c>
@@ -12364,7 +12567,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="156" spans="2:6">
+    <row r="156" spans="2:7">
       <c r="B156" s="1" t="s">
         <v>1898</v>
       </c>
@@ -12372,15 +12575,15 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="157" spans="2:6">
+    <row r="157" spans="2:7">
       <c r="B157" s="1" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="C157" t="s">
         <v>1900</v>
       </c>
     </row>
-    <row r="158" spans="2:6">
+    <row r="158" spans="2:7">
       <c r="B158" s="1" t="s">
         <v>1901</v>
       </c>
@@ -12388,7 +12591,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="159" spans="2:6">
+    <row r="159" spans="2:7">
       <c r="B159" s="1" t="s">
         <v>1903</v>
       </c>
@@ -12396,21 +12599,24 @@
         <v>1904</v>
       </c>
       <c r="D159" s="44" t="s">
-        <v>2294</v>
+        <v>2286</v>
       </c>
       <c r="E159" s="45" t="s">
-        <v>2352</v>
+        <v>2341</v>
       </c>
       <c r="F159" s="45" t="s">
-        <v>2385</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6">
+        <v>2374</v>
+      </c>
+      <c r="G159" s="45" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7">
       <c r="B160" s="1" t="s">
         <v>1905</v>
       </c>
       <c r="C160" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="161" spans="2:5">
@@ -12418,12 +12624,12 @@
         <v>1906</v>
       </c>
       <c r="C161" t="s">
-        <v>2269</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C162" t="s">
         <v>1907</v>
@@ -12437,10 +12643,10 @@
         <v>1909</v>
       </c>
       <c r="D163" s="44" t="s">
-        <v>2350</v>
+        <v>2339</v>
       </c>
       <c r="E163" s="45" t="s">
-        <v>2353</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="164" spans="2:5">
@@ -12451,15 +12657,15 @@
         <v>1911</v>
       </c>
       <c r="D164" s="44" t="s">
-        <v>2324</v>
+        <v>2315</v>
       </c>
       <c r="E164" s="45" t="s">
-        <v>2354</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="C165" t="s">
         <v>1912</v>
@@ -12475,7 +12681,7 @@
     </row>
     <row r="167" spans="2:5">
       <c r="B167" s="1" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="C167" t="s">
         <v>1915</v>
@@ -12523,7 +12729,7 @@
     </row>
     <row r="173" spans="2:5">
       <c r="B173" s="1" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="C173" t="s">
         <v>1925</v>
@@ -12534,7 +12740,7 @@
         <v>1926</v>
       </c>
       <c r="C174" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="175" spans="2:5">
@@ -12558,12 +12764,12 @@
         <v>1930</v>
       </c>
       <c r="C177" t="s">
-        <v>2235</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="178" spans="2:7">
       <c r="B178" s="1" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="C178" t="s">
         <v>1931</v>
@@ -12585,13 +12791,13 @@
         <v>1935</v>
       </c>
       <c r="D180" s="44" t="s">
-        <v>2316</v>
+        <v>2307</v>
       </c>
       <c r="E180" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
       </c>
       <c r="F180" s="43" t="s">
-        <v>2383</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="181" spans="2:7">
@@ -12602,13 +12808,13 @@
         <v>1937</v>
       </c>
       <c r="D181" s="44" t="s">
-        <v>2306</v>
+        <v>2297</v>
       </c>
       <c r="E181" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
       </c>
       <c r="F181" s="43" t="s">
-        <v>2383</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="182" spans="2:7">
@@ -12621,7 +12827,7 @@
     </row>
     <row r="183" spans="2:7">
       <c r="B183" s="1" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="C183" t="s">
         <v>1940</v>
@@ -12629,283 +12835,289 @@
     </row>
     <row r="184" spans="2:7">
       <c r="B184" s="1" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="C184" t="s">
-        <v>1941</v>
+        <v>2396</v>
       </c>
       <c r="D184" s="44" t="s">
-        <v>2305</v>
+        <v>2395</v>
       </c>
       <c r="E184" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
+      </c>
+      <c r="F184" s="45" t="s">
+        <v>2366</v>
       </c>
     </row>
     <row r="185" spans="2:7">
       <c r="B185" s="1" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="C185" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>2397</v>
+        <v>2394</v>
       </c>
       <c r="E185" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
       </c>
       <c r="F185" s="45" t="s">
-        <v>2375</v>
+        <v>2364</v>
       </c>
       <c r="G185" s="45" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="186" spans="2:7">
       <c r="B186" s="1" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C186" t="s">
         <v>1943</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="187" spans="2:7">
       <c r="B187" s="1" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C187" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="188" spans="2:7">
       <c r="B188" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C188" t="s">
         <v>1946</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1947</v>
       </c>
     </row>
     <row r="189" spans="2:7">
       <c r="B189" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C189" t="s">
         <v>1948</v>
       </c>
-      <c r="C189" t="s">
-        <v>1949</v>
-      </c>
       <c r="D189" s="44" t="s">
-        <v>2309</v>
+        <v>2300</v>
       </c>
       <c r="E189" s="45" t="s">
-        <v>2355</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="190" spans="2:7">
       <c r="B190" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C190" t="s">
         <v>1950</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1951</v>
       </c>
     </row>
     <row r="191" spans="2:7">
       <c r="B191" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C191" t="s">
         <v>1952</v>
-      </c>
-      <c r="C191" t="s">
-        <v>1953</v>
       </c>
     </row>
     <row r="192" spans="2:7">
       <c r="B192" s="1" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="C192" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="193" spans="2:7">
       <c r="B193" s="1" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="C193" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="194" spans="2:7">
       <c r="B194" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C194" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="D194" s="44" t="s">
-        <v>2303</v>
+        <v>2295</v>
       </c>
       <c r="E194" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
       </c>
       <c r="F194" s="43" t="s">
-        <v>2381</v>
+        <v>2370</v>
       </c>
       <c r="G194" s="43" t="s">
-        <v>2382</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="195" spans="2:7">
       <c r="B195" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C195" t="s">
         <v>1957</v>
       </c>
-      <c r="C195" t="s">
-        <v>1958</v>
-      </c>
       <c r="D195" s="44" t="s">
-        <v>2303</v>
+        <v>2295</v>
       </c>
       <c r="E195" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
       </c>
       <c r="F195" s="43" t="s">
-        <v>2381</v>
+        <v>2370</v>
       </c>
       <c r="G195" s="43" t="s">
-        <v>2382</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="196" spans="2:7">
       <c r="B196" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C196" t="s">
         <v>1959</v>
       </c>
-      <c r="C196" t="s">
-        <v>1960</v>
-      </c>
       <c r="D196" s="44" t="s">
-        <v>2344</v>
+        <v>2333</v>
       </c>
       <c r="E196" s="45" t="s">
-        <v>2378</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="197" spans="2:7">
       <c r="B197" s="1" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C197" t="s">
         <v>1961</v>
-      </c>
-      <c r="C197" t="s">
-        <v>1962</v>
       </c>
     </row>
     <row r="198" spans="2:7">
       <c r="B198" s="1" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
       <c r="C198" t="s">
-        <v>1963</v>
+        <v>2400</v>
       </c>
       <c r="D198" s="44" t="s">
         <v>2390</v>
       </c>
       <c r="E198" s="45" t="s">
-        <v>2379</v>
+        <v>2368</v>
       </c>
       <c r="F198" s="45" t="s">
-        <v>2389</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="199" spans="2:7">
       <c r="B199" s="1" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="C199" t="s">
-        <v>1965</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="200" spans="2:7">
       <c r="B200" s="1" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="C200" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="D200" s="44" t="s">
-        <v>2345</v>
+        <v>2334</v>
       </c>
       <c r="E200" s="45" t="s">
-        <v>2378</v>
+        <v>2367</v>
       </c>
       <c r="F200" s="43" t="s">
-        <v>2380</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="201" spans="2:7">
       <c r="B201" s="1" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="C201" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="202" spans="2:7">
       <c r="B202" s="1" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="C202" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="203" spans="2:7">
       <c r="B203" s="1" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="C203" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="204" spans="2:7">
       <c r="B204" s="1" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="C204" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="205" spans="2:7">
       <c r="B205" s="1" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="C205" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="206" spans="2:7">
       <c r="B206" s="1" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="C206" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="D206" s="44" t="s">
-        <v>2293</v>
+        <v>2285</v>
       </c>
       <c r="E206" s="45" t="s">
-        <v>2360</v>
+        <v>2349</v>
       </c>
       <c r="F206" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
+      </c>
+      <c r="G206" s="45" t="s">
+        <v>2340</v>
       </c>
     </row>
     <row r="207" spans="2:7">
       <c r="B207" s="1" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="C207" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="208" spans="2:7">
       <c r="B208" s="1" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="C208" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="209" spans="2:6">
@@ -12913,21 +13125,21 @@
         <v>980</v>
       </c>
       <c r="C209" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="D209" s="44" t="s">
-        <v>2312</v>
+        <v>2303</v>
       </c>
       <c r="E209" s="45" t="s">
-        <v>2377</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="210" spans="2:6">
       <c r="B210" s="1" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="C210" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="211" spans="2:6">
@@ -12935,56 +13147,56 @@
         <v>1227</v>
       </c>
       <c r="C211" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="212" spans="2:6">
       <c r="B212" s="1" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="C212" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="213" spans="2:6">
       <c r="B213" s="1" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="C213" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="D213" s="44" t="s">
-        <v>2395</v>
+        <v>2391</v>
       </c>
       <c r="E213" s="45" t="s">
-        <v>2355</v>
+        <v>2344</v>
       </c>
       <c r="F213" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="214" spans="2:6">
       <c r="B214" s="1" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="C214" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="215" spans="2:6">
       <c r="B215" s="1" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="C215" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="216" spans="2:6">
       <c r="B216" s="1" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="C216" t="s">
-        <v>2225</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="217" spans="2:6">
@@ -12992,112 +13204,112 @@
         <v>1235</v>
       </c>
       <c r="C217" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="D217" s="44" t="s">
-        <v>2292</v>
+        <v>2284</v>
       </c>
       <c r="E217" s="45" t="s">
-        <v>2384</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="218" spans="2:6">
       <c r="B218" s="1" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="C218" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="219" spans="2:6">
       <c r="B219" s="1" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="C219" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="220" spans="2:6">
       <c r="B220" s="1" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="C220" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="D220" s="44" t="s">
-        <v>2291</v>
+        <v>2283</v>
       </c>
       <c r="E220" s="45" t="s">
-        <v>2369</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="221" spans="2:6">
       <c r="B221" s="1" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="C221" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="222" spans="2:6">
       <c r="B222" s="1" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="C222" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="223" spans="2:6">
       <c r="B223" s="1" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="C223" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="224" spans="2:6">
       <c r="B224" s="1" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C224" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="225" spans="2:5">
       <c r="B225" s="1" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C225" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="226" spans="2:5">
       <c r="B226" s="1" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C226" t="s">
-        <v>2238</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="227" spans="2:5">
       <c r="B227" s="1" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C227" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="228" spans="2:5">
       <c r="B228" s="1" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="C228" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="229" spans="2:5">
       <c r="B229" s="1" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C229" t="s">
         <v>494</v>
@@ -13105,252 +13317,252 @@
     </row>
     <row r="230" spans="2:5">
       <c r="B230" s="1" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C230" t="s">
-        <v>2233</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="231" spans="2:5">
       <c r="B231" s="1" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C231" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="232" spans="2:5">
       <c r="B232" s="1" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C232" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="D232" s="44" t="s">
-        <v>2321</v>
+        <v>2312</v>
       </c>
       <c r="E232" s="45" t="s">
-        <v>2368</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="233" spans="2:5">
       <c r="B233" s="1" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="C233" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="D233" s="44" t="s">
-        <v>2323</v>
+        <v>2314</v>
       </c>
       <c r="E233" s="45" t="s">
-        <v>2370</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="234" spans="2:5">
       <c r="B234" s="1" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C234" t="s">
-        <v>2252</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="235" spans="2:5">
       <c r="B235" s="1" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C235" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="236" spans="2:5">
       <c r="B236" s="1" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C236" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="237" spans="2:5">
       <c r="B237" s="1" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="C237" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="238" spans="2:5">
       <c r="B238" s="1" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C238" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D238" s="44" t="s">
-        <v>2391</v>
+        <v>2379</v>
       </c>
       <c r="E238" s="45" t="s">
-        <v>2353</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="239" spans="2:5">
       <c r="B239" s="1" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C239" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="240" spans="2:5">
       <c r="B240" s="1" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="C240" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="241" spans="2:6">
       <c r="B241" s="1" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
       <c r="C241" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="D241" s="44" t="s">
-        <v>2295</v>
+        <v>2287</v>
       </c>
       <c r="E241" s="45" t="s">
-        <v>2352</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="242" spans="2:6">
       <c r="B242" s="1" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
       <c r="C242" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D242" s="44" t="s">
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E242" s="45" t="s">
-        <v>2371</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="243" spans="2:6">
       <c r="B243" s="1" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="C243" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
       <c r="D243" s="44" t="s">
-        <v>2326</v>
+        <v>2317</v>
       </c>
       <c r="E243" s="45" t="s">
-        <v>2372</v>
+        <v>2361</v>
       </c>
       <c r="F243" s="45" t="s">
-        <v>2379</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="244" spans="2:6">
       <c r="B244" s="1" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="C244" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="245" spans="2:6">
       <c r="B245" s="1" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="C245" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="D245" s="44" t="s">
-        <v>2327</v>
+        <v>2318</v>
       </c>
       <c r="E245" s="45" t="s">
-        <v>2373</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="246" spans="2:6">
       <c r="B246" s="1" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
       <c r="C246" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="D246" s="44" t="s">
-        <v>2325</v>
+        <v>2316</v>
       </c>
       <c r="E246" s="45" t="s">
-        <v>2372</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="247" spans="2:6">
       <c r="B247" s="1" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="C247" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="D247" s="44" t="s">
-        <v>2308</v>
+        <v>2299</v>
       </c>
       <c r="E247" s="45" t="s">
-        <v>2355</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="248" spans="2:6">
       <c r="B248" s="1" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="C248" t="s">
-        <v>2251</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="249" spans="2:6">
       <c r="B249" s="1" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
       <c r="C249" t="s">
-        <v>2236</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="250" spans="2:6">
       <c r="B250" s="1" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="C250" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="D250" s="44" t="s">
-        <v>2342</v>
+        <v>2331</v>
       </c>
       <c r="E250" s="45" t="s">
-        <v>2375</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="251" spans="2:6">
       <c r="B251" s="1" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="C251" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="D251" s="44" t="s">
-        <v>2341</v>
+        <v>2330</v>
       </c>
       <c r="E251" s="45" t="s">
-        <v>2375</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="252" spans="2:6">
       <c r="B252" s="1" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="C252" t="s">
         <v>533</v>
@@ -13358,231 +13570,231 @@
     </row>
     <row r="253" spans="2:6">
       <c r="B253" s="1" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="C253" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="254" spans="2:6">
       <c r="B254" s="1" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
       <c r="C254" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
       <c r="D254" s="44" t="s">
-        <v>2314</v>
+        <v>2305</v>
       </c>
       <c r="E254" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="255" spans="2:6">
       <c r="B255" s="1" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="C255" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="256" spans="2:6">
       <c r="B256" s="1" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
       <c r="C256" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="257" spans="2:6">
       <c r="B257" s="1" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="C257" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="258" spans="2:6">
       <c r="B258" s="1" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="C258" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
       <c r="D258" s="44" t="s">
-        <v>2317</v>
+        <v>2308</v>
       </c>
       <c r="E258" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="259" spans="2:6">
       <c r="B259" s="1" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
       <c r="C259" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="260" spans="2:6">
       <c r="B260" s="1" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="C260" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="D260" s="44" t="s">
-        <v>2319</v>
+        <v>2310</v>
       </c>
       <c r="E260" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="261" spans="2:6">
       <c r="B261" s="1" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
       <c r="C261" t="s">
         <v>476</v>
       </c>
       <c r="D261" s="44" t="s">
-        <v>2328</v>
+        <v>2392</v>
       </c>
       <c r="E261" s="45" t="s">
-        <v>2377</v>
+        <v>2366</v>
       </c>
       <c r="F261" s="43" t="s">
-        <v>2374</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="262" spans="2:6">
       <c r="B262" s="1" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="C262" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="D262" s="44" t="s">
-        <v>2311</v>
+        <v>2302</v>
       </c>
       <c r="E262" s="45" t="s">
-        <v>2377</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="263" spans="2:6">
       <c r="B263" s="1" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="C263" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="D263" s="44" t="s">
-        <v>2343</v>
+        <v>2332</v>
       </c>
       <c r="E263" s="45" t="s">
-        <v>2375</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="264" spans="2:6">
       <c r="B264" s="1" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="C264" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="265" spans="2:6">
       <c r="B265" s="1" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
       <c r="C265" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="266" spans="2:6">
       <c r="B266" s="1" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="C266" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="267" spans="2:6">
       <c r="B267" s="1" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="C267" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="268" spans="2:6">
       <c r="B268" s="1" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="C268" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="D268" s="44" t="s">
-        <v>2340</v>
+        <v>2329</v>
       </c>
       <c r="E268" s="45" t="s">
-        <v>2375</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="269" spans="2:6">
       <c r="B269" s="1" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="C269" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="270" spans="2:6">
       <c r="B270" s="1" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="C270" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="271" spans="2:6">
       <c r="B271" s="1" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="C271" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="272" spans="2:6">
       <c r="B272" s="1" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="C272" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="273" spans="2:5">
       <c r="B273" s="1" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="C273" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="274" spans="2:5">
       <c r="B274" s="1" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="C274" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="275" spans="2:5">
       <c r="B275" s="1" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="C275" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="276" spans="2:5">
@@ -13590,62 +13802,62 @@
         <v>492</v>
       </c>
       <c r="C276" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="277" spans="2:5">
       <c r="B277" s="1" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="C277" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="278" spans="2:5">
       <c r="B278" s="1" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="C278" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
       <c r="D278" s="44" t="s">
-        <v>2318</v>
+        <v>2309</v>
       </c>
       <c r="E278" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="279" spans="2:5">
       <c r="B279" s="1" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="C279" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="D279" s="44" t="s">
-        <v>2297</v>
+        <v>2289</v>
       </c>
       <c r="E279" s="45" t="s">
-        <v>2367</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="280" spans="2:5">
       <c r="B280" s="1" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="C280" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="D280" s="44" t="s">
         <v>432</v>
       </c>
       <c r="E280" s="45" t="s">
-        <v>2367</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="281" spans="2:5">
       <c r="B281" s="1" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="C281" t="s">
         <v>1623</v>
@@ -13653,141 +13865,147 @@
     </row>
     <row r="282" spans="2:5">
       <c r="B282" s="1" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="C282" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="283" spans="2:5">
       <c r="B283" s="1" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
       <c r="C283" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="284" spans="2:5">
       <c r="B284" s="1" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="C284" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="285" spans="2:5">
       <c r="B285" s="1" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
       <c r="C285" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="286" spans="2:5">
       <c r="B286" s="1" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="C286" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="287" spans="2:5">
       <c r="B287" s="1" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="C287" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="288" spans="2:5">
       <c r="B288" s="1" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="C288" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="D288" s="44" t="s">
-        <v>2322</v>
+        <v>2313</v>
       </c>
       <c r="E288" s="45" t="s">
-        <v>2368</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="289" spans="2:6">
       <c r="B289" s="1" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="C289" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="290" spans="2:6">
       <c r="B290" s="1" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="C290" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="291" spans="2:6">
       <c r="B291" s="1" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="C291" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="292" spans="2:6">
       <c r="B292" s="1" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="C292" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="D292" s="44" t="s">
-        <v>2310</v>
+        <v>2301</v>
       </c>
       <c r="E292" s="45" t="s">
-        <v>2355</v>
+        <v>2344</v>
       </c>
       <c r="F292" s="43" t="s">
-        <v>2359</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="293" spans="2:6">
       <c r="B293" s="1" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="C293" t="s">
-        <v>2277</v>
+        <v>2269</v>
       </c>
       <c r="D293" s="44" t="s">
-        <v>2313</v>
+        <v>2304</v>
       </c>
       <c r="E293" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
+      </c>
+      <c r="F293" s="45" t="s">
+        <v>2366</v>
       </c>
     </row>
     <row r="294" spans="2:6">
       <c r="B294" s="1" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="C294" t="s">
-        <v>2278</v>
+        <v>2270</v>
       </c>
       <c r="D294" s="44" t="s">
-        <v>2313</v>
+        <v>2304</v>
       </c>
       <c r="E294" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
+      </c>
+      <c r="F294" s="45" t="s">
+        <v>2366</v>
       </c>
     </row>
     <row r="295" spans="2:6">
       <c r="B295" s="1" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="C295" t="s">
-        <v>2275</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="296" spans="2:6">
@@ -13795,10 +14013,10 @@
         <v>320</v>
       </c>
       <c r="C296" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="D296" s="44" t="s">
-        <v>2394</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="297" spans="2:6">
@@ -13806,250 +14024,250 @@
         <v>1628</v>
       </c>
       <c r="C297" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="D297" s="44" t="s">
-        <v>2394</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="298" spans="2:6">
       <c r="B298" s="1" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="C298" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="299" spans="2:6">
       <c r="B299" s="35" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="C299" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="D299" s="44" t="s">
-        <v>2334</v>
+        <v>2323</v>
       </c>
       <c r="E299" s="43" t="s">
-        <v>2359</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="300" spans="2:6">
       <c r="B300" s="1" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="C300" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="D300" s="44" t="s">
-        <v>2320</v>
+        <v>2311</v>
       </c>
       <c r="E300" s="45" t="s">
-        <v>2360</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="301" spans="2:6">
       <c r="B301" s="35" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C301" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="302" spans="2:6">
       <c r="B302" s="21" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="C302" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="D302" s="44" t="s">
-        <v>2393</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="303" spans="2:6">
       <c r="B303" s="21" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="C303" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="D303" s="44" t="s">
-        <v>2315</v>
+        <v>2306</v>
       </c>
       <c r="E303" s="45" t="s">
-        <v>2351</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="304" spans="2:6">
       <c r="B304" s="21" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C304" t="s">
         <v>2203</v>
       </c>
-      <c r="C304" t="s">
-        <v>2206</v>
-      </c>
       <c r="D304" s="44" t="s">
-        <v>2304</v>
+        <v>2296</v>
       </c>
       <c r="E304" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="305" spans="2:6">
       <c r="B305" s="37" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="C305" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="D305" s="44" t="s">
-        <v>2304</v>
+        <v>2296</v>
       </c>
       <c r="E305" s="45" t="s">
-        <v>2385</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="306" spans="2:6">
       <c r="B306" s="1" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="C306" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="D306" s="44" t="s">
-        <v>2307</v>
+        <v>2298</v>
       </c>
       <c r="E306" s="45" t="s">
-        <v>2361</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="307" spans="2:6">
       <c r="B307" s="1" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="C307" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="D307" s="44" t="s">
-        <v>2333</v>
+        <v>2322</v>
       </c>
       <c r="E307" s="43" t="s">
-        <v>2359</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="308" spans="2:6">
       <c r="B308" s="1" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="C308" t="s">
-        <v>2224</v>
+        <v>2219</v>
       </c>
       <c r="D308" s="44" t="s">
-        <v>2300</v>
+        <v>2292</v>
       </c>
       <c r="E308" s="45" t="s">
-        <v>2362</v>
+        <v>2351</v>
       </c>
       <c r="F308" s="43" t="s">
-        <v>2376</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="309" spans="2:6">
       <c r="B309" s="38" t="s">
-        <v>2227</v>
+        <v>2222</v>
       </c>
       <c r="C309" t="s">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="D309" s="44" t="s">
-        <v>2301</v>
+        <v>2293</v>
       </c>
       <c r="E309" s="45" t="s">
-        <v>2363</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="310" spans="2:6">
       <c r="B310" s="1" t="s">
-        <v>2229</v>
+        <v>2224</v>
       </c>
       <c r="C310" t="s">
-        <v>2230</v>
+        <v>2225</v>
       </c>
       <c r="D310" s="44" t="s">
-        <v>2346</v>
+        <v>2335</v>
       </c>
       <c r="E310" s="45" t="s">
-        <v>2364</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="311" spans="2:6">
       <c r="B311" s="1" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="C311" t="s">
-        <v>2232</v>
+        <v>2227</v>
       </c>
       <c r="D311" s="44" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
       <c r="E311" s="45" t="s">
-        <v>2364</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="312" spans="2:6">
       <c r="B312" s="1" t="s">
-        <v>2240</v>
+        <v>2235</v>
       </c>
       <c r="C312" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="D312" s="44" t="s">
-        <v>2332</v>
+        <v>2321</v>
       </c>
       <c r="E312" s="45" t="s">
-        <v>2365</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="313" spans="2:6">
       <c r="B313" s="1" t="s">
-        <v>2242</v>
+        <v>2237</v>
       </c>
       <c r="C313" t="s">
-        <v>2244</v>
+        <v>2413</v>
       </c>
       <c r="D313" s="44" t="s">
-        <v>2330</v>
+        <v>2415</v>
       </c>
       <c r="E313" s="45" t="s">
-        <v>2365</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="314" spans="2:6">
       <c r="B314" s="1" t="s">
-        <v>2243</v>
+        <v>2238</v>
       </c>
       <c r="C314" t="s">
-        <v>2245</v>
+        <v>2414</v>
       </c>
       <c r="D314" s="44" t="s">
-        <v>2330</v>
+        <v>2415</v>
       </c>
       <c r="E314" s="45" t="s">
-        <v>2365</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="315" spans="2:6">
       <c r="B315" s="1" t="s">
-        <v>2250</v>
+        <v>2243</v>
       </c>
       <c r="C315" t="s">
-        <v>2246</v>
+        <v>2239</v>
       </c>
       <c r="D315" s="44" t="s">
-        <v>2329</v>
+        <v>2319</v>
       </c>
       <c r="E315" s="45" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="316" spans="2:6">
@@ -14057,249 +14275,252 @@
         <v>171</v>
       </c>
       <c r="C316" t="s">
-        <v>2249</v>
+        <v>2242</v>
       </c>
       <c r="D316" s="44" t="s">
-        <v>2331</v>
+        <v>2320</v>
       </c>
       <c r="E316" s="45" t="s">
-        <v>2365</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="317" spans="2:6">
       <c r="B317" s="1" t="s">
-        <v>2247</v>
+        <v>2240</v>
       </c>
       <c r="C317" t="s">
-        <v>2248</v>
+        <v>2241</v>
       </c>
       <c r="D317" s="44" t="s">
-        <v>2331</v>
+        <v>2320</v>
       </c>
       <c r="E317" s="45" t="s">
-        <v>2365</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="318" spans="2:6">
       <c r="B318" s="1" t="s">
-        <v>2262</v>
+        <v>2254</v>
       </c>
       <c r="C318" t="s">
-        <v>2263</v>
+        <v>2255</v>
       </c>
       <c r="D318" s="44" t="s">
-        <v>2336</v>
+        <v>2325</v>
       </c>
       <c r="E318" s="45" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
       <c r="F318" s="43" t="s">
-        <v>2358</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="319" spans="2:6">
       <c r="B319" s="1" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
       <c r="C319" t="s">
-        <v>2265</v>
+        <v>2257</v>
       </c>
       <c r="D319" s="44" t="s">
-        <v>2337</v>
+        <v>2326</v>
       </c>
       <c r="E319" s="45" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="320" spans="2:6">
       <c r="B320" s="1" t="s">
-        <v>2266</v>
+        <v>2258</v>
       </c>
       <c r="C320" t="s">
-        <v>2279</v>
+        <v>2271</v>
       </c>
       <c r="D320" s="44" t="s">
-        <v>2339</v>
+        <v>2328</v>
       </c>
       <c r="E320" s="45" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
       <c r="F320" s="43" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
       <c r="B321" s="41" t="s">
         <v>942</v>
       </c>
       <c r="C321" t="s">
-        <v>2270</v>
+        <v>2262</v>
       </c>
       <c r="D321" s="44" t="s">
-        <v>2392</v>
+        <v>2380</v>
       </c>
       <c r="E321" s="43" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
       <c r="B322" s="1" t="s">
-        <v>2267</v>
+        <v>2259</v>
       </c>
       <c r="C322" t="s">
-        <v>2268</v>
+        <v>2260</v>
       </c>
       <c r="D322" s="44" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E322" s="45" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="B323" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C323" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D323" s="44" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E323" s="45" t="s">
+        <v>2345</v>
+      </c>
+      <c r="F323" s="43" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="B324" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C324" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D324" s="44" t="s">
+        <v>2393</v>
+      </c>
+      <c r="E324" s="45" t="s">
+        <v>2345</v>
+      </c>
+      <c r="F324" s="43" t="s">
+        <v>2347</v>
+      </c>
+      <c r="G324" s="43" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="B325" s="1" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C325" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D325" s="44" t="s">
+        <v>2399</v>
+      </c>
+      <c r="E325" s="45" t="s">
+        <v>2340</v>
+      </c>
+      <c r="F325" s="45" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="B326" s="1" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C326" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D326" s="44" t="s">
+        <v>2399</v>
+      </c>
+      <c r="E326" s="45" t="s">
+        <v>2340</v>
+      </c>
+      <c r="F326" s="45" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="B327" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C327" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D327" s="44" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E327" s="45" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="B328" s="1" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C328" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D328" s="44" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E328" s="45" t="s">
+        <v>2344</v>
+      </c>
+      <c r="F328" s="43" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="B329" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C329" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D329" s="44" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E329" s="45" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="B330" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C330" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D330" s="44" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E330" s="45" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="B331" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C331" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D331" s="44" t="s">
         <v>2338</v>
       </c>
-      <c r="E322" s="45" t="s">
+      <c r="E331" s="45" t="s">
         <v>2356</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
-      <c r="B323" s="1" t="s">
-        <v>2271</v>
-      </c>
-      <c r="C323" t="s">
-        <v>2272</v>
-      </c>
-      <c r="D323" s="44" t="s">
-        <v>2388</v>
-      </c>
-      <c r="E323" s="45" t="s">
-        <v>2356</v>
-      </c>
-      <c r="F323" s="43" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6">
-      <c r="B324" s="1" t="s">
-        <v>2273</v>
-      </c>
-      <c r="C324" t="s">
-        <v>2274</v>
-      </c>
-      <c r="D324" s="44" t="s">
-        <v>2388</v>
-      </c>
-      <c r="E324" s="45" t="s">
-        <v>2356</v>
-      </c>
-      <c r="F324" s="43" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="325" spans="1:6">
-      <c r="B325" s="1" t="s">
-        <v>2237</v>
-      </c>
-      <c r="C325" t="s">
-        <v>2239</v>
-      </c>
-      <c r="D325" s="44" t="s">
-        <v>2284</v>
-      </c>
-      <c r="E325" s="45" t="s">
-        <v>2357</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6">
-      <c r="B326" s="1" t="s">
-        <v>2215</v>
-      </c>
-      <c r="C326" t="s">
-        <v>2221</v>
-      </c>
-      <c r="D326" s="44" t="s">
-        <v>2283</v>
-      </c>
-      <c r="E326" s="45" t="s">
-        <v>2355</v>
-      </c>
-      <c r="F326" s="43" t="s">
-        <v>2359</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6">
-      <c r="B327" s="1" t="s">
-        <v>2216</v>
-      </c>
-      <c r="C327" t="s">
-        <v>2222</v>
-      </c>
-      <c r="D327" s="44" t="s">
-        <v>2396</v>
-      </c>
-      <c r="E327" s="45" t="s">
-        <v>2351</v>
-      </c>
-      <c r="F327" s="45" t="s">
-        <v>2375</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6">
-      <c r="B328" s="1" t="s">
-        <v>2217</v>
-      </c>
-      <c r="C328" t="s">
-        <v>2223</v>
-      </c>
-      <c r="D328" s="44" t="s">
-        <v>2396</v>
-      </c>
-      <c r="E328" s="45" t="s">
-        <v>2351</v>
-      </c>
-      <c r="F328" s="45" t="s">
-        <v>2375</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6">
-      <c r="B329" s="1" t="s">
-        <v>2280</v>
-      </c>
-      <c r="C329" t="s">
-        <v>2281</v>
-      </c>
-      <c r="D329" s="44" t="s">
-        <v>2335</v>
-      </c>
-      <c r="E329" s="45" t="s">
-        <v>2356</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6">
-      <c r="B330" s="1" t="s">
-        <v>2298</v>
-      </c>
-      <c r="C330" t="s">
-        <v>2386</v>
-      </c>
-      <c r="D330" s="44" t="s">
-        <v>2299</v>
-      </c>
-      <c r="E330" s="45" t="s">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6">
-      <c r="B331" s="1" t="s">
-        <v>2348</v>
-      </c>
-      <c r="C331" t="s">
-        <v>2387</v>
-      </c>
-      <c r="D331" s="44" t="s">
-        <v>2349</v>
-      </c>
-      <c r="E331" s="45" t="s">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
   </sheetData>
@@ -14325,7 +14546,7 @@
     <hyperlink ref="E220" r:id="rId2" xr:uid="{5A86A9C8-18B7-49D4-B0DA-510F8507220D}"/>
     <hyperlink ref="E242" r:id="rId3" xr:uid="{E8BDD6E9-53E1-49ED-9A35-0FFE574C21E6}"/>
     <hyperlink ref="E330" r:id="rId4" xr:uid="{15456AB3-5F70-432C-91F1-C3B6D972B050}"/>
-    <hyperlink ref="E325" r:id="rId5" xr:uid="{B5E564C1-2202-4076-A41F-2A29B21EEF86}"/>
+    <hyperlink ref="E327" r:id="rId5" xr:uid="{B5E564C1-2202-4076-A41F-2A29B21EEF86}"/>
     <hyperlink ref="E309" r:id="rId6" xr:uid="{4E8F2926-23D8-4338-A705-D1EB793CFD3E}"/>
     <hyperlink ref="E308" r:id="rId7" xr:uid="{82427E63-C1DB-4ADE-A529-AB11239EFCCF}"/>
     <hyperlink ref="E181" r:id="rId8" xr:uid="{FA78759D-C553-403D-992E-421D714D9F9A}"/>
@@ -14351,15 +14572,15 @@
     <hyperlink ref="E312" r:id="rId28" xr:uid="{400C510C-E456-4A27-B24C-418D350D90BD}"/>
     <hyperlink ref="E315" r:id="rId29" xr:uid="{14C34214-6147-4305-92F1-69B213D1FA29}"/>
     <hyperlink ref="F318" r:id="rId30" xr:uid="{DB7A9083-BA12-48B2-8FF0-15D58BECB5DE}"/>
-    <hyperlink ref="F326" r:id="rId31" xr:uid="{B463ECED-0070-4C60-AB9F-1E345749E26F}"/>
+    <hyperlink ref="F328" r:id="rId31" xr:uid="{B463ECED-0070-4C60-AB9F-1E345749E26F}"/>
     <hyperlink ref="E329" r:id="rId32" xr:uid="{47859955-5A53-430D-A74C-A6B0CB190025}"/>
     <hyperlink ref="E254" r:id="rId33" xr:uid="{4F5E8AA4-E2BF-41E9-9FF9-67C354DB7071}"/>
     <hyperlink ref="E258" r:id="rId34" xr:uid="{6212D2A7-A60E-4A8A-AC13-A29B95A7B7AD}"/>
     <hyperlink ref="E260" r:id="rId35" xr:uid="{A312B211-7E36-48C6-86A6-43FFD50F9564}"/>
     <hyperlink ref="E278" r:id="rId36" xr:uid="{57B1F815-44C0-490D-8DD0-A2C57F66B381}"/>
     <hyperlink ref="E303" r:id="rId37" xr:uid="{10DAE240-14E7-4DE4-9086-1C76A7B2C1C2}"/>
-    <hyperlink ref="E327" r:id="rId38" xr:uid="{DD87348E-9210-439B-954F-C4B341F5F286}"/>
-    <hyperlink ref="E328" r:id="rId39" xr:uid="{B82F962C-17C5-48A6-9F5B-B7CD6194D005}"/>
+    <hyperlink ref="E325" r:id="rId38" xr:uid="{DD87348E-9210-439B-954F-C4B341F5F286}"/>
+    <hyperlink ref="E326" r:id="rId39" xr:uid="{B82F962C-17C5-48A6-9F5B-B7CD6194D005}"/>
     <hyperlink ref="F213" r:id="rId40" xr:uid="{FBE5799F-EC50-4A5B-9DE1-C5C4BFCCC92C}"/>
     <hyperlink ref="E293" r:id="rId41" xr:uid="{1EE495D5-212D-491A-9CC1-04E3004E4F7E}"/>
     <hyperlink ref="E294" r:id="rId42" xr:uid="{466A8EC9-5237-4A15-8DB6-88D959EA8FF9}"/>
@@ -14367,7 +14588,7 @@
     <hyperlink ref="E213" r:id="rId44" xr:uid="{CD293A95-0BE7-4049-9C45-13227B9B3899}"/>
     <hyperlink ref="E247" r:id="rId45" xr:uid="{9F3BBE7C-4C0F-46BC-A332-52D676A47F56}"/>
     <hyperlink ref="E292" r:id="rId46" xr:uid="{C71E14FD-F4AF-4F58-8BDE-DD61974BA0D0}"/>
-    <hyperlink ref="E326" r:id="rId47" xr:uid="{202F65B8-C4AF-4ACA-B5DD-3359FDDB3851}"/>
+    <hyperlink ref="E328" r:id="rId47" xr:uid="{202F65B8-C4AF-4ACA-B5DD-3359FDDB3851}"/>
     <hyperlink ref="E318" r:id="rId48" xr:uid="{B3E5CA03-F23F-4660-8FD9-608AB24280FA}"/>
     <hyperlink ref="E319" r:id="rId49" xr:uid="{EB737DD4-0742-419E-9E5F-D79F798CAFB3}"/>
     <hyperlink ref="E320" r:id="rId50" xr:uid="{F5DBAF4B-522C-4066-916B-EC63B938A1A7}"/>
@@ -14415,10 +14636,16 @@
     <hyperlink ref="F198" r:id="rId92" xr:uid="{4865438C-E32A-496F-93EF-F7813CFF1DD3}"/>
     <hyperlink ref="E238" r:id="rId93" xr:uid="{ADF7B2D9-F611-44B4-B8A5-05758C923B02}"/>
     <hyperlink ref="E321" r:id="rId94" xr:uid="{51F6EE0C-4BDA-4D40-B448-F44D8CE199AF}"/>
-    <hyperlink ref="F327" r:id="rId95" xr:uid="{FA1433D3-A125-4D91-8655-CE3041406BBF}"/>
-    <hyperlink ref="F328" r:id="rId96" xr:uid="{E87B89B3-92DB-4654-B59A-DBB66B4F00DE}"/>
+    <hyperlink ref="F325" r:id="rId95" xr:uid="{FA1433D3-A125-4D91-8655-CE3041406BBF}"/>
+    <hyperlink ref="F326" r:id="rId96" xr:uid="{E87B89B3-92DB-4654-B59A-DBB66B4F00DE}"/>
     <hyperlink ref="F185" r:id="rId97" xr:uid="{0CEED77C-AE3C-4AC3-BA83-9660F17E5B98}"/>
     <hyperlink ref="G185" r:id="rId98" xr:uid="{D649C43C-4568-4298-B2DB-D4088A7995C4}"/>
+    <hyperlink ref="G324" r:id="rId99" xr:uid="{F00D9D1B-26F7-488C-B91C-F8141BE4536E}"/>
+    <hyperlink ref="F293" r:id="rId100" xr:uid="{2B802E9B-5D25-4BD1-AA45-D2032BA9C78D}"/>
+    <hyperlink ref="F294" r:id="rId101" xr:uid="{FE3EEB68-9021-4277-AAD9-27391243C61E}"/>
+    <hyperlink ref="F184" r:id="rId102" xr:uid="{97AC6B31-C5D9-4148-8AE1-3A52BFB6EC05}"/>
+    <hyperlink ref="G159" r:id="rId103" xr:uid="{B9C0917D-E21E-43D6-A01B-7E82133087C0}"/>
+    <hyperlink ref="G206" r:id="rId104" xr:uid="{AA239A2B-C23F-48FF-888A-322981A2C098}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15322,7 +15549,7 @@
         <v>。</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -18724,7 +18951,7 @@
       </c>
       <c r="CU9" s="6" t="str">
         <f>_xlfn.XLOOKUP(CT9,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>隔?</v>
+        <v>収?</v>
       </c>
       <c r="CV9" s="7" t="s">
         <v>635</v>
@@ -19238,7 +19465,7 @@
       </c>
       <c r="CU10" s="6" t="str">
         <f>_xlfn.XLOOKUP(CT10,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>離?</v>
+        <v>監?</v>
       </c>
       <c r="CV10" s="7" t="s">
         <v>716</v>
@@ -19514,7 +19741,7 @@
       </c>
       <c r="AE11" s="6" t="str">
         <f>_xlfn.XLOOKUP(AD11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>早?</v>
+        <v>早</v>
       </c>
       <c r="AF11" s="7" t="s">
         <v>760</v>
@@ -19878,7 +20105,7 @@
       </c>
       <c r="EE11" s="6" t="str">
         <f>_xlfn.XLOOKUP(ED11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>□?</v>
+        <v>特?</v>
       </c>
       <c r="EF11" s="7" t="s">
         <v>817</v>
@@ -19950,8 +20177,8 @@
         <v>825</v>
       </c>
       <c r="I12" s="6" t="str">
-        <f>_xlfn.XLOOKUP(H12,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(H12,対応表!$B:$B,対応表!$C:$C,"に")</f>
+        <v>に</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>826</v>
@@ -20217,7 +20444,7 @@
       </c>
       <c r="CG12" s="6" t="str">
         <f>_xlfn.XLOOKUP(CF12,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>■?</v>
+        <v>別?</v>
       </c>
       <c r="CH12" s="7" t="s">
         <v>870</v>
@@ -25259,7 +25486,7 @@
       </c>
       <c r="BE22" s="6" t="str">
         <f>_xlfn.XLOOKUP(BD22,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>歩?</v>
+        <v>歩</v>
       </c>
       <c r="BF22" s="7" t="s">
         <v>1662</v>
@@ -25647,110 +25874,147 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A3841C-3E42-4AC2-9AD3-BA0FFE4A947C}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="11" width="9" style="1"/>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="49"/>
+    <col min="5" max="11" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="34" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="20.25">
+    <row r="12" spans="1:4" ht="20.25">
       <c r="C12" s="40" t="s">
-        <v>2260</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20.25">
+        <v>2252</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="20.25">
       <c r="C13" s="39" t="s">
-        <v>2258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="20.25">
+        <v>2250</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20.25">
       <c r="C14" s="39" t="s">
-        <v>2257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="20.25">
+        <v>2249</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="20.25">
       <c r="C16" s="39" t="s">
-        <v>2256</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" ht="20.25">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" ht="20.25">
       <c r="C18" s="39" t="s">
-        <v>2259</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" ht="20.25">
+        <v>2251</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" ht="20.25">
       <c r="C19" s="40" t="s">
-        <v>2276</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3">
+        <v>2268</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4">
       <c r="C20" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4">
+      <c r="C21" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4">
+      <c r="C22" s="1" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" s="1" t="s">
         <v>2253</v>
       </c>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="1" t="s">
-        <v>2254</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="1" t="s">
-        <v>2255</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="1" t="s">
-        <v>2261</v>
+      <c r="D23" s="49" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" s="1" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>2412</v>
       </c>
     </row>
   </sheetData>
@@ -25760,6 +26024,44 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C5E931-1AEC-434D-81A1-3EA98DBB914E}">
+  <dimension ref="B1:D2"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="9" style="46"/>
+    <col min="3" max="3" width="9" style="47"/>
+    <col min="4" max="4" width="48.25" style="47" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4">
+      <c r="B1" s="46" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
+      <c r="B2" s="48" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EB3F03-5923-4BB0-9F29-755ABED01E72}">
   <dimension ref="A1:HK25"/>
   <sheetFormatPr defaultRowHeight="35.25"/>
@@ -33195,7 +33497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9733B9-FF68-449B-887F-E9348BF07D10}">
   <dimension ref="B1:ED5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -33405,7 +33707,7 @@
     </row>
     <row r="2" spans="2:134">
       <c r="B2" s="1" t="s">
-        <v>2282</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="5" spans="2:134">

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1503" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2B41854-93AE-490B-9C2F-743949D863C6}"/>
+  <xr:revisionPtr revIDLastSave="1511" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D550DB7-F1D4-43B4-909C-04BF8FCBFB8B}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" activeTab="4" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -10826,46 +10826,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>凘?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>過凘</t>
     <rPh sb="0" eb="1">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>勀?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>倂?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>佁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>?</t>
-    </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -10896,10 +10860,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>傎?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>傎にあった</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -11172,11 +11132,62 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>俚?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>介??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>傎??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俚??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勀??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倂??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凘??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>佁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11742,6 +11753,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -13626,7 +13641,7 @@
         <v>2132</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
@@ -14310,10 +14325,10 @@
         <v>1962</v>
       </c>
       <c r="C250" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
       <c r="E250" s="34" t="s">
         <v>2132</v>
@@ -14597,7 +14612,7 @@
         <v>2064</v>
       </c>
       <c r="E278" s="43" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.4">
@@ -14611,7 +14626,7 @@
         <v>376</v>
       </c>
       <c r="E279" s="43" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.4">
@@ -14722,7 +14737,7 @@
         <v>2115</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
@@ -14808,7 +14823,7 @@
         <v>2096</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
@@ -14911,7 +14926,7 @@
         <v>2095</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
@@ -15068,7 +15083,7 @@
         <v>2098</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="F317" s="32" t="s">
         <v>2117</v>
@@ -15085,7 +15100,7 @@
         <v>2099</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
@@ -15099,7 +15114,7 @@
         <v>2101</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="F319" s="32" t="s">
         <v>2117</v>
@@ -15130,7 +15145,7 @@
         <v>2100</v>
       </c>
       <c r="E321" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.4">
@@ -15138,13 +15153,13 @@
         <v>1094</v>
       </c>
       <c r="C322" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="D322" s="33" t="s">
         <v>2143</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="F322" s="32" t="s">
         <v>2117</v>
@@ -15155,13 +15170,13 @@
         <v>296</v>
       </c>
       <c r="C323" t="s">
-        <v>2549</v>
+        <v>2543</v>
       </c>
       <c r="D323" s="33" t="s">
         <v>2159</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="F323" s="32" t="s">
         <v>2117</v>
@@ -15209,7 +15224,7 @@
         <v>2017</v>
       </c>
       <c r="C326" t="s">
-        <v>2504</v>
+        <v>2546</v>
       </c>
       <c r="D326" s="33" t="s">
         <v>2501</v>
@@ -15223,7 +15238,7 @@
         <v>1998</v>
       </c>
       <c r="C327" t="s">
-        <v>2505</v>
+        <v>2547</v>
       </c>
       <c r="D327" s="33" t="s">
         <v>2500</v>
@@ -15232,7 +15247,7 @@
         <v>2115</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.4">
@@ -15240,13 +15255,13 @@
         <v>407</v>
       </c>
       <c r="C328" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D328" s="33" t="s">
         <v>2502</v>
       </c>
-      <c r="D328" s="33" t="s">
-        <v>2503</v>
-      </c>
       <c r="E328" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.4">
@@ -15254,13 +15269,13 @@
         <v>160</v>
       </c>
       <c r="C329" s="41" t="s">
-        <v>2506</v>
+        <v>2549</v>
       </c>
       <c r="D329" s="42" t="s">
-        <v>2507</v>
+        <v>2503</v>
       </c>
       <c r="E329" s="43" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.4">
@@ -15268,13 +15283,13 @@
         <v>1103</v>
       </c>
       <c r="C330" t="s">
-        <v>2508</v>
+        <v>2544</v>
       </c>
       <c r="D330" s="33" t="s">
-        <v>2509</v>
+        <v>2504</v>
       </c>
       <c r="E330" s="43" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.4">
@@ -16933,7 +16948,7 @@
       </c>
       <c r="AI4" s="6" t="str">
         <f>_xlfn.XLOOKUP(AH4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>佁?</v>
+        <v>佁??</v>
       </c>
       <c r="AJ4" s="7" t="s">
         <v>161</v>
@@ -18706,7 +18721,7 @@
       </c>
       <c r="CW7" s="6" t="str">
         <f>_xlfn.XLOOKUP(CV7,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>凘?</v>
+        <v>凘??</v>
       </c>
       <c r="CX7" s="7" t="s">
         <v>408</v>
@@ -23664,7 +23679,7 @@
       </c>
       <c r="AW17" s="6" t="str">
         <f>_xlfn.XLOOKUP(AV17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>俚?</v>
+        <v>俚??</v>
       </c>
       <c r="AX17" s="17" t="s">
         <v>1095</v>
@@ -23678,7 +23693,7 @@
       </c>
       <c r="BA17" s="6" t="str">
         <f>_xlfn.XLOOKUP(AZ17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>倂?</v>
+        <v>倂??</v>
       </c>
       <c r="BB17" s="7" t="s">
         <v>1097</v>
@@ -23727,7 +23742,7 @@
       </c>
       <c r="BO17" s="6" t="str">
         <f>_xlfn.XLOOKUP(BN17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>傎?</v>
+        <v>傎??</v>
       </c>
       <c r="BP17" s="7" t="s">
         <v>1104</v>
@@ -24951,7 +24966,7 @@
       </c>
       <c r="DS19" s="6" t="str">
         <f>_xlfn.XLOOKUP(DR19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>勀?</v>
+        <v>勀??</v>
       </c>
       <c r="DT19" s="7" t="s">
         <v>1273</v>
@@ -28524,18 +28539,18 @@
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
@@ -28887,7 +28902,7 @@
         <v>2467</v>
       </c>
       <c r="C224" s="43" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.4">
@@ -29076,7 +29091,7 @@
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="C248" s="34" t="s">
         <v>2124</v>
@@ -29084,7 +29099,7 @@
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2512</v>
+        <v>2507</v>
       </c>
       <c r="C249" s="34" t="s">
         <v>2124</v>
@@ -29092,7 +29107,7 @@
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="C250" s="34" t="s">
         <v>2124</v>
@@ -29100,7 +29115,7 @@
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
       <c r="C251" s="34" t="s">
         <v>2124</v>
@@ -29108,7 +29123,7 @@
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2516</v>
+        <v>2511</v>
       </c>
       <c r="C252" s="34" t="s">
         <v>2123</v>
@@ -29116,7 +29131,7 @@
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2517</v>
+        <v>2512</v>
       </c>
       <c r="C253" s="32" t="s">
         <v>2133</v>
@@ -29124,7 +29139,7 @@
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="C254" s="32" t="s">
         <v>2133</v>
@@ -29132,7 +29147,7 @@
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2519</v>
+        <v>2514</v>
       </c>
       <c r="C255" s="32" t="s">
         <v>2133</v>
@@ -29140,58 +29155,58 @@
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2520</v>
+        <v>2515</v>
       </c>
       <c r="C256" s="34" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2521</v>
+        <v>2516</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
+        <v>2517</v>
+      </c>
+      <c r="C258" s="34" t="s">
         <v>2522</v>
-      </c>
-      <c r="C258" s="34" t="s">
-        <v>2527</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
-        <v>2523</v>
+        <v>2518</v>
       </c>
       <c r="C259" s="34" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2524</v>
+        <v>2519</v>
       </c>
       <c r="C260" s="34" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
@@ -29199,47 +29214,47 @@
         <v>2364</v>
       </c>
       <c r="C263" s="34" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2528</v>
+        <v>2523</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
-        <v>2529</v>
+        <v>2524</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2530</v>
+        <v>2525</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2531</v>
+        <v>2526</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C268" s="34" t="s">
         <v>2532</v>
-      </c>
-      <c r="C268" s="34" t="s">
-        <v>2537</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
@@ -29247,31 +29262,31 @@
         <v>2273</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2533</v>
+        <v>2528</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
-        <v>2534</v>
+        <v>2529</v>
       </c>
       <c r="C271" s="34" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2538</v>
+        <v>2533</v>
       </c>
       <c r="C272" s="32" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
@@ -29279,36 +29294,36 @@
         <v>2236</v>
       </c>
       <c r="C273" s="32" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
       <c r="C274" s="32" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
       <c r="C275" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
-        <v>2541</v>
+        <v>2536</v>
       </c>
       <c r="C276" s="34" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="C277" s="32" t="s">
         <v>2117</v>
@@ -29316,7 +29331,7 @@
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="C278" s="32" t="s">
         <v>2117</v>
@@ -29324,7 +29339,7 @@
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
       <c r="C279" s="32" t="s">
         <v>2117</v>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1511" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D550DB7-F1D4-43B4-909C-04BF8FCBFB8B}"/>
+  <xr:revisionPtr revIDLastSave="1557" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD7B0B71-8A2A-445A-8B0B-5ED507A6979E}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="2550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="2561">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -7611,16 +7611,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>亘</t>
-  </si>
-  <si>
-    <t>腹?</t>
-    <rPh sb="0" eb="1">
-      <t>ハラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>倂</t>
   </si>
   <si>
@@ -8164,16 +8154,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>腹が満たされた</t>
-    <rPh sb="0" eb="1">
-      <t>ハラ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>満たされた合ず</t>
     <rPh sb="0" eb="1">
       <t>ミ</t>
@@ -8700,13 +8680,6 @@
     <t>長</t>
     <rPh sb="0" eb="1">
       <t>ナガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>間</t>
-    <rPh sb="0" eb="1">
-      <t>アイダ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -11190,12 +11163,174 @@
     </r>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>完</t>
+    <rPh sb="0" eb="1">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亘??</t>
+    <rPh sb="0" eb="1">
+      <t>ワタリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亘が満たされた</t>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伭</t>
+  </si>
+  <si>
+    <r>
+      <t>伭名像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/王？</t>
+    </r>
+    <rPh sb="1" eb="2">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伭名像/王？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>伭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>??</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乳偗像/王？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>偗</t>
+  </si>
+  <si>
+    <t>侸</t>
+  </si>
+  <si>
+    <t>侻</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>侻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>像/王？</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>侸</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>侻像/王？</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さかな屋</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11409,6 +11544,22 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -11529,7 +11680,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11660,6 +11811,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -12074,7 +12228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:J331"/>
+  <dimension ref="A1:J336"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -12096,25 +12250,25 @@
         <v>1563</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="E1" s="33" t="s">
+        <v>2050</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>2051</v>
+      </c>
+      <c r="G1" s="31" t="s">
         <v>2052</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="H1" s="31" t="s">
         <v>2053</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="I1" s="31" t="s">
         <v>2054</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="J1" s="31" t="s">
         <v>2055</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>2056</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>2057</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -13373,16 +13527,16 @@
         <v>1691</v>
       </c>
       <c r="D158" s="33" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="E158" s="34" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
       <c r="F158" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="G158" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.4">
@@ -13390,7 +13544,7 @@
         <v>1692</v>
       </c>
       <c r="C159" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.4">
@@ -13398,7 +13552,7 @@
         <v>1693</v>
       </c>
       <c r="C160" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.4">
@@ -13417,10 +13571,10 @@
         <v>1696</v>
       </c>
       <c r="D162" s="33" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="E162" s="34" t="s">
-        <v>2113</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.4">
@@ -13431,10 +13585,10 @@
         <v>1698</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.4">
@@ -13538,7 +13692,7 @@
         <v>1717</v>
       </c>
       <c r="C176" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.4">
@@ -13565,13 +13719,13 @@
         <v>1722</v>
       </c>
       <c r="D179" s="33" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="E179" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="F179" s="32" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.4">
@@ -13582,13 +13736,13 @@
         <v>1724</v>
       </c>
       <c r="D180" s="33" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="E180" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
@@ -13612,16 +13766,16 @@
         <v>1941</v>
       </c>
       <c r="C183" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
       <c r="D183" s="33" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="E183" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.4">
@@ -13632,16 +13786,16 @@
         <v>1728</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="E184" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
@@ -13676,10 +13830,10 @@
         <v>1735</v>
       </c>
       <c r="D188" s="33" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="E188" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.4">
@@ -13722,16 +13876,16 @@
         <v>1991</v>
       </c>
       <c r="D193" s="33" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="E193" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="F193" s="32" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="G193" s="32" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.4">
@@ -13742,16 +13896,16 @@
         <v>1744</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="E194" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.4">
@@ -13762,10 +13916,10 @@
         <v>1746</v>
       </c>
       <c r="D195" s="33" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="E195" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="196" spans="2:7" x14ac:dyDescent="0.4">
@@ -13781,16 +13935,16 @@
         <v>1945</v>
       </c>
       <c r="C197" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="E197" s="34" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="F197" s="34" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.4">
@@ -13798,7 +13952,7 @@
         <v>1749</v>
       </c>
       <c r="C198" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.4">
@@ -13809,13 +13963,13 @@
         <v>1750</v>
       </c>
       <c r="D199" s="33" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="E199" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="F199" s="32" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.4">
@@ -13866,16 +14020,16 @@
         <v>1760</v>
       </c>
       <c r="D205" s="33" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="E205" s="34" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
       <c r="F205" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="G205" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="206" spans="2:7" x14ac:dyDescent="0.4">
@@ -13902,10 +14056,10 @@
         <v>1764</v>
       </c>
       <c r="D208" s="33" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="E208" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.4">
@@ -13940,13 +14094,13 @@
         <v>1770</v>
       </c>
       <c r="D212" s="33" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="E212" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="F212" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.4">
@@ -13970,7 +14124,7 @@
         <v>1951</v>
       </c>
       <c r="C215" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.4">
@@ -13981,10 +14135,10 @@
         <v>1775</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="E216" s="34" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
@@ -14011,10 +14165,10 @@
         <v>1780</v>
       </c>
       <c r="D219" s="33" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="E219" s="34" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.4">
@@ -14046,7 +14200,7 @@
         <v>1785</v>
       </c>
       <c r="C223" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.4">
@@ -14062,7 +14216,7 @@
         <v>1788</v>
       </c>
       <c r="C225" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.4">
@@ -14094,7 +14248,7 @@
         <v>1794</v>
       </c>
       <c r="C229" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.4">
@@ -14113,10 +14267,10 @@
         <v>1798</v>
       </c>
       <c r="D231" s="33" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="E231" s="34" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.4">
@@ -14127,10 +14281,10 @@
         <v>1799</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="E232" s="34" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.4">
@@ -14138,7 +14292,7 @@
         <v>1800</v>
       </c>
       <c r="C233" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="234" spans="2:5" x14ac:dyDescent="0.4">
@@ -14173,10 +14327,10 @@
         <v>1807</v>
       </c>
       <c r="D237" s="33" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="E237" s="34" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.4">
@@ -14203,10 +14357,10 @@
         <v>1812</v>
       </c>
       <c r="D240" s="33" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="E240" s="34" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.4">
@@ -14217,10 +14371,10 @@
         <v>1813</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.4">
@@ -14231,13 +14385,13 @@
         <v>1815</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
@@ -14256,10 +14410,10 @@
         <v>1819</v>
       </c>
       <c r="D244" s="33" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="E244" s="34" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.4">
@@ -14270,10 +14424,10 @@
         <v>1820</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.4">
@@ -14284,10 +14438,10 @@
         <v>1821</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.4">
@@ -14295,7 +14449,7 @@
         <v>1822</v>
       </c>
       <c r="C247" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.4">
@@ -14303,7 +14457,7 @@
         <v>1961</v>
       </c>
       <c r="C248" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.4">
@@ -14314,10 +14468,10 @@
         <v>1824</v>
       </c>
       <c r="D249" s="33" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="E249" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.4">
@@ -14325,13 +14479,13 @@
         <v>1962</v>
       </c>
       <c r="C250" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2539</v>
+        <v>2535</v>
       </c>
       <c r="E250" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
@@ -14358,10 +14512,10 @@
         <v>1829</v>
       </c>
       <c r="D253" s="33" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="E253" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.4">
@@ -14396,10 +14550,10 @@
         <v>1836</v>
       </c>
       <c r="D257" s="33" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="E257" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
@@ -14418,10 +14572,10 @@
         <v>1839</v>
       </c>
       <c r="D259" s="33" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="E259" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
@@ -14432,13 +14586,13 @@
         <v>417</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="E260" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
@@ -14449,10 +14603,10 @@
         <v>1842</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="E261" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
@@ -14463,10 +14617,10 @@
         <v>1844</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="E262" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
@@ -14509,10 +14663,10 @@
         <v>1853</v>
       </c>
       <c r="D267" s="33" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="E267" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.4">
@@ -14595,10 +14749,10 @@
         <v>1871</v>
       </c>
       <c r="D277" s="33" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="E277" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.4">
@@ -14609,10 +14763,10 @@
         <v>1873</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="E278" s="43" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.4">
@@ -14626,7 +14780,7 @@
         <v>376</v>
       </c>
       <c r="E279" s="43" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.4">
@@ -14693,10 +14847,10 @@
         <v>1888</v>
       </c>
       <c r="D287" s="33" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="E287" s="34" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.4">
@@ -14731,13 +14885,13 @@
         <v>1985</v>
       </c>
       <c r="D291" s="33" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="E291" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
@@ -14745,16 +14899,16 @@
         <v>1970</v>
       </c>
       <c r="C292" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="D292" s="33" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="E292" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="F292" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
@@ -14762,16 +14916,16 @@
         <v>1971</v>
       </c>
       <c r="C293" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="E293" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.4">
@@ -14779,7 +14933,7 @@
         <v>1972</v>
       </c>
       <c r="C294" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
@@ -14790,7 +14944,7 @@
         <v>1975</v>
       </c>
       <c r="D295" s="33" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.4">
@@ -14801,7 +14955,7 @@
         <v>1976</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
@@ -14820,10 +14974,10 @@
         <v>1978</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
@@ -14834,10 +14988,10 @@
         <v>1980</v>
       </c>
       <c r="D299" s="33" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="E299" s="34" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.4">
@@ -14850,13 +15004,13 @@
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B301" s="18" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C301" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="D301" s="33" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.4">
@@ -14867,10 +15021,10 @@
         <v>1984</v>
       </c>
       <c r="D302" s="33" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="E302" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.4">
@@ -14881,10 +15035,10 @@
         <v>1989</v>
       </c>
       <c r="D303" s="33" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="E303" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.4">
@@ -14895,10 +15049,10 @@
         <v>1988</v>
       </c>
       <c r="D304" s="33" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="E304" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.4">
@@ -14909,139 +15063,139 @@
         <v>1994</v>
       </c>
       <c r="D305" s="33" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="E305" s="34" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B306" s="1" t="s">
-        <v>1996</v>
+        <v>936</v>
       </c>
       <c r="C306" t="s">
-        <v>1997</v>
+        <v>2548</v>
       </c>
       <c r="D306" s="33" t="s">
-        <v>2095</v>
+        <v>2549</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B307" s="1" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C307" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D307" s="33" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="E307" s="34" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="F307" s="32" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B308" s="27" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C308" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="D308" s="33" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="E308" s="34" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B309" s="1" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C309" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="D309" s="33" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
       <c r="E309" s="34" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B310" s="1" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C310" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D310" s="33" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="E310" s="34" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B311" s="1" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C311" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D311" s="33" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="E311" s="34" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B312" s="1" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C312" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="D312" s="33" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="E312" s="34" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B313" s="1" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C313" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="D313" s="33" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="E313" s="34" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B314" s="1" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="C314" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D314" s="33" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="E314" s="34" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
@@ -15049,75 +15203,75 @@
         <v>153</v>
       </c>
       <c r="C315" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D315" s="33" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="E315" s="34" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B316" s="1" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C316" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D316" s="33" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="E316" s="34" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B317" s="1" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="C317" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="D317" s="33" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="F317" s="32" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B318" s="1" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="C318" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="D318" s="33" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B319" s="1" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="C319" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="D319" s="33" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="F319" s="32" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.4">
@@ -15125,27 +15279,27 @@
         <v>822</v>
       </c>
       <c r="C320" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="D320" s="33" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="E320" s="32" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B321" s="1" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="C321" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="D321" s="33" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="E321" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.4">
@@ -15153,16 +15307,16 @@
         <v>1094</v>
       </c>
       <c r="C322" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="F322" s="32" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.4">
@@ -15170,84 +15324,84 @@
         <v>296</v>
       </c>
       <c r="C323" t="s">
-        <v>2543</v>
+        <v>2539</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="F323" s="32" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B324" s="1" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C324" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="E324" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="F324" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B325" s="1" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="C325" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="D325" s="33" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="E325" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="F325" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B326" s="1" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C326" t="s">
-        <v>2546</v>
+        <v>2542</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>2501</v>
+        <v>2497</v>
       </c>
       <c r="E326" s="34" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B327" s="1" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C327" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2500</v>
+        <v>2496</v>
       </c>
       <c r="E327" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.4">
@@ -15255,13 +15409,13 @@
         <v>407</v>
       </c>
       <c r="C328" t="s">
-        <v>2548</v>
+        <v>2544</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2502</v>
+        <v>2498</v>
       </c>
       <c r="E328" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.4">
@@ -15269,13 +15423,13 @@
         <v>160</v>
       </c>
       <c r="C329" s="41" t="s">
-        <v>2549</v>
+        <v>2545</v>
       </c>
       <c r="D329" s="42" t="s">
-        <v>2503</v>
+        <v>2499</v>
       </c>
       <c r="E329" s="43" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.4">
@@ -15283,17 +15437,87 @@
         <v>1103</v>
       </c>
       <c r="C330" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="D330" s="33" t="s">
-        <v>2504</v>
+        <v>2500</v>
       </c>
       <c r="E330" s="43" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A331" t="s">
+      <c r="B331" s="1" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C331" s="41" t="s">
+        <v>2553</v>
+      </c>
+      <c r="D331" s="44" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E331" s="34" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B332" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D332" s="33" t="s">
+        <v>2554</v>
+      </c>
+      <c r="E332" s="34" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B333" s="1" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C333" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D333" s="33" t="s">
+        <v>2554</v>
+      </c>
+      <c r="E333" s="34" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B334" s="1" t="s">
+        <v>2556</v>
+      </c>
+      <c r="C334" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D334" s="42" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E334" s="34" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B335" s="1" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C335" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D335" s="42" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E335" s="34" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A336" t="s">
         <v>1896</v>
       </c>
     </row>
@@ -15417,9 +15641,14 @@
     <hyperlink ref="E322" r:id="rId102" display="掟に関するお知らせ" xr:uid="{48C7A341-761D-4FF9-B9EE-044C09F865E1}"/>
     <hyperlink ref="E323" r:id="rId103" display="掟に関するお知らせ" xr:uid="{3F2B7D36-0F1F-424A-9F17-A1DE9DCD445A}"/>
     <hyperlink ref="E328" r:id="rId104" display="掟に関するお知らせ" xr:uid="{0D72F1A9-4220-4BA0-8A4A-23A1D38533F1}"/>
+    <hyperlink ref="E331" r:id="rId105" xr:uid="{4E7486E6-9C9B-4F2B-B7BD-443D1F6304CC}"/>
+    <hyperlink ref="E332" r:id="rId106" xr:uid="{A0441298-7143-419D-A793-E976EACA92E3}"/>
+    <hyperlink ref="E333" r:id="rId107" xr:uid="{129E740A-4AA0-4F11-88A1-0B9A03860FF2}"/>
+    <hyperlink ref="E334" r:id="rId108" xr:uid="{C56117F9-1196-45F7-BA62-047C42ECB7D7}"/>
+    <hyperlink ref="E335" r:id="rId109" xr:uid="{E85A37DE-DD8D-4FF4-AA31-96B38F5902E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId105"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId110"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -16476,7 +16705,7 @@
       </c>
       <c r="AU3" s="6" t="str">
         <f>_xlfn.XLOOKUP(AT3,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>侸</v>
       </c>
       <c r="AV3" s="7" t="s">
         <v>96</v>
@@ -16941,7 +17170,7 @@
       </c>
       <c r="AG4" s="6" t="str">
         <f>_xlfn.XLOOKUP(AF4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>伭??</v>
       </c>
       <c r="AH4" s="7" t="s">
         <v>160</v>
@@ -18018,7 +18247,7 @@
       </c>
       <c r="AU6" s="6" t="str">
         <f>_xlfn.XLOOKUP(AT6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>侻</v>
       </c>
       <c r="AV6" s="7" t="s">
         <v>309</v>
@@ -22539,7 +22768,7 @@
       </c>
       <c r="Q15" s="6" t="str">
         <f>_xlfn.XLOOKUP(P15,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>腹?</v>
+        <v>亘??</v>
       </c>
       <c r="R15" s="7" t="s">
         <v>937</v>
@@ -24067,7 +24296,7 @@
       </c>
       <c r="M18" s="6" t="str">
         <f>_xlfn.XLOOKUP(L18,対応表!$B:$B,対応表!$C:$C,"こ")</f>
-        <v>こ</v>
+        <v>乳</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>1148</v>
@@ -26291,7 +26520,7 @@
       </c>
       <c r="BI22" s="6" t="str">
         <f>_xlfn.XLOOKUP(BH22,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>偗</v>
       </c>
       <c r="BJ22" s="17" t="s">
         <v>1456</v>
@@ -26725,87 +26954,87 @@
     </row>
     <row r="12" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
       <c r="C12" s="29" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
       <c r="C13" s="28" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
       <c r="C14" s="28" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
       <c r="C16" s="28" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="20.25" x14ac:dyDescent="0.4">
       <c r="C18" s="28" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="20.25" x14ac:dyDescent="0.4">
       <c r="C19" s="29" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C20" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C21" s="1" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C22" s="1" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C23" s="1" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C24" s="1" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
     </row>
   </sheetData>
@@ -26827,265 +27056,265 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B1" s="35" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>2278</v>
+        <v>2274</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2279</v>
+        <v>2275</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
-        <v>2280</v>
+        <v>2276</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>2281</v>
+        <v>2277</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>2282</v>
+        <v>2278</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
-        <v>2283</v>
+        <v>2279</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>2284</v>
+        <v>2280</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>2285</v>
+        <v>2281</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>2288</v>
+        <v>2284</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2289</v>
+        <v>2285</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2290</v>
+        <v>2286</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
-        <v>2291</v>
+        <v>2287</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>2292</v>
+        <v>2288</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>2293</v>
+        <v>2289</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2295</v>
+        <v>2291</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
-        <v>2296</v>
+        <v>2292</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>2297</v>
+        <v>2293</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
-        <v>2299</v>
+        <v>2295</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2383</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2301</v>
+        <v>2297</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
-        <v>2379</v>
+        <v>2375</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>2380</v>
+        <v>2376</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2452</v>
+        <v>2448</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2451</v>
+        <v>2447</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
-        <v>2453</v>
+        <v>2449</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>2454</v>
+        <v>2450</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2456</v>
+        <v>2452</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2455</v>
+        <v>2451</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="35" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2457</v>
+        <v>2453</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
-        <v>2497</v>
+        <v>2493</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>2498</v>
+        <v>2494</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>2499</v>
+        <v>2495</v>
       </c>
     </row>
   </sheetData>
@@ -27096,7 +27325,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED28C13D-14D9-4671-B3CF-1ADD2E368C21}">
-  <dimension ref="B1:D279"/>
+  <dimension ref="B1:D280"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="31"/>
@@ -27106,434 +27335,434 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B1" s="31" t="s">
-        <v>2232</v>
+        <v>2228</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>2233</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B3" s="31" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B4" s="31" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B5" s="31" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B6" s="31" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B7" s="31" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B8" s="31" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B9" s="31" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B10" s="31" t="s">
-        <v>2192</v>
+        <v>2185</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B11" s="31" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B12" s="31" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B14" s="31" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B15" s="31" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B16" s="31" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="31" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="31" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="31" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="31" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="31" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="31" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="31" t="s">
-        <v>2203</v>
+        <v>2247</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="31" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="31" t="s">
-        <v>2252</v>
+        <v>2200</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>2142</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="31" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="31" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="31" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="31" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>2119</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="31" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="31" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="31" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>2115</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
-        <v>2222</v>
+        <v>2230</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
-        <v>2234</v>
+        <v>2219</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>2135</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B48" s="31" t="s">
-        <v>2225</v>
+        <v>1161</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
-        <v>1161</v>
+        <v>2222</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.4">
@@ -27541,722 +27770,722 @@
         <v>2231</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B65" s="31" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B66" s="31" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B67" s="31" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B68" s="31" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B69" s="31" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B70" s="31" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B71" s="31" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>2134</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="31" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B73" s="31" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B74" s="31" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
+      </c>
+      <c r="D75" s="34" t="s">
+        <v>2121</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>2111</v>
-      </c>
-      <c r="D76" s="34" t="s">
-        <v>2124</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="31" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="31" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B79" s="31" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B80" s="31" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B81" s="31" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B82" s="31" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="C82" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B83" s="31" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B84" s="31" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="C84" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B85" s="31" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="C85" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B86" s="31" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="C86" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B87" s="31" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B88" s="31" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B89" s="31" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B90" s="31" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B91" s="31" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B92" s="31" t="s">
-        <v>2273</v>
+        <v>2298</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>2111</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B93" s="31" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>2303</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B95" s="31" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>2118</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B96" s="31" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2308</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
-        <v>2307</v>
+        <v>2315</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>2308</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2319</v>
+        <v>2305</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2308</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="31" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="31" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="31" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B102" s="31" t="s">
-        <v>2312</v>
+        <v>950</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>950</v>
+        <v>2309</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="31" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B105" s="31" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C105" s="34" t="s">
         <v>2314</v>
-      </c>
-      <c r="C105" s="34" t="s">
-        <v>2318</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="31" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="31" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2324</v>
+        <v>2316</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>2318</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="31" t="s">
-        <v>2320</v>
+        <v>2317</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="31" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="31" t="s">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>2141</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="31" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="31" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="31" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="31" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="31" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="31" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="31" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="31" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="31" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2126</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="31" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="31" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2335</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="31" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="31" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="31" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B129" s="31" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B130" s="31" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C130" s="34" t="s">
         <v>2342</v>
-      </c>
-      <c r="C130" s="34" t="s">
-        <v>2346</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B131" s="31" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B132" s="31" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2346</v>
+        <v>2342</v>
+      </c>
+      <c r="D132" s="34" t="s">
+        <v>2403</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>2346</v>
-      </c>
-      <c r="D133" s="34" t="s">
-        <v>2407</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B134" s="31" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B135" s="31" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B136" s="31" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C136" s="34" t="s">
         <v>2349</v>
-      </c>
-      <c r="C136" s="34" t="s">
-        <v>2353</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B137" s="31" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B138" s="31" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B140" s="31" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B141" s="31" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C141" s="34" t="s">
         <v>2355</v>
-      </c>
-      <c r="C141" s="34" t="s">
-        <v>2359</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B142" s="31" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="C142" s="34" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B143" s="31" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="C144" s="34" t="s">
         <v>2359</v>
@@ -28264,189 +28493,189 @@
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B145" s="31" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="C145" s="34" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B146" s="31" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2363</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B148" s="31" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B149" s="31" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B150" s="31" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B151" s="31" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B152" s="31" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="C152" s="34" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B153" s="31" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C153" s="34" t="s">
         <v>2369</v>
-      </c>
-      <c r="C153" s="34" t="s">
-        <v>2373</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B154" s="31" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="C154" s="34" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B155" s="31" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="C156" s="34" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B157" s="31" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C157" s="34" t="s">
         <v>2374</v>
-      </c>
-      <c r="C157" s="34" t="s">
-        <v>2378</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B158" s="31" t="s">
-        <v>2375</v>
+        <v>2372</v>
       </c>
       <c r="C158" s="34" t="s">
-        <v>2378</v>
+        <v>2374</v>
+      </c>
+      <c r="D158" s="34" t="s">
+        <v>2419</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B159" s="31" t="s">
-        <v>2376</v>
+        <v>2373</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2378</v>
-      </c>
-      <c r="D159" s="34" t="s">
-        <v>2423</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2378</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
-        <v>2384</v>
+        <v>2381</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
-        <v>2385</v>
+        <v>2382</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
-        <v>2386</v>
+        <v>2383</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
-        <v>2387</v>
+        <v>2384</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C165" s="34" t="s">
         <v>2388</v>
-      </c>
-      <c r="C165" s="34" t="s">
-        <v>2392</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="C166" s="34" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
-        <v>2390</v>
+        <v>2387</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.4">
@@ -28454,31 +28683,31 @@
         <v>2391</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
-        <v>2395</v>
+        <v>2392</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2397</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
-        <v>2396</v>
+        <v>2389</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>2397</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C171" s="34" t="s">
         <v>2393</v>
-      </c>
-      <c r="C171" s="34" t="s">
-        <v>2397</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.4">
@@ -28486,156 +28715,156 @@
         <v>2394</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
-        <v>2398</v>
+        <v>2395</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>2403</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C174" s="34" t="s">
         <v>2399</v>
-      </c>
-      <c r="C174" s="34" t="s">
-        <v>2403</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
       <c r="C175" s="34" t="s">
-        <v>2403</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
-        <v>2401</v>
+        <v>2398</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2403</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
-        <v>2404</v>
+        <v>2526</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>2405</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2530</v>
+        <v>2527</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2531</v>
+        <v>2402</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2532</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>2407</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B182" s="31" t="s">
-        <v>2408</v>
+        <v>2405</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2407</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B183" s="31" t="s">
-        <v>2409</v>
+        <v>2406</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2407</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B184" s="31" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C184" s="34" t="s">
         <v>2410</v>
-      </c>
-      <c r="C184" s="34" t="s">
-        <v>2407</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B185" s="31" t="s">
-        <v>2411</v>
+        <v>2408</v>
       </c>
       <c r="C185" s="34" t="s">
-        <v>2414</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B186" s="31" t="s">
-        <v>2412</v>
+        <v>2409</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2414</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B188" s="31" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C188" s="34" t="s">
         <v>2415</v>
-      </c>
-      <c r="C188" s="34" t="s">
-        <v>2419</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B189" s="31" t="s">
-        <v>2416</v>
+        <v>2413</v>
       </c>
       <c r="C189" s="34" t="s">
-        <v>2419</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B190" s="31" t="s">
-        <v>2417</v>
+        <v>2414</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2419</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="C191" s="34" t="s">
         <v>2419</v>
@@ -28643,183 +28872,183 @@
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B192" s="31" t="s">
-        <v>2420</v>
+        <v>2417</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>2423</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B193" s="31" t="s">
-        <v>2421</v>
+        <v>2418</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2423</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
-        <v>2422</v>
+        <v>2222</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>2423</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
-        <v>2226</v>
+        <v>2420</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B196" s="31" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C196" s="34" t="s">
         <v>2424</v>
-      </c>
-      <c r="C196" s="34" t="s">
-        <v>2428</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B197" s="31" t="s">
-        <v>2425</v>
+        <v>2422</v>
       </c>
       <c r="C197" s="34" t="s">
-        <v>2428</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B198" s="31" t="s">
-        <v>2426</v>
+        <v>2423</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2428</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B200" s="31" t="s">
-        <v>2429</v>
+        <v>2426</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B201" s="31" t="s">
+        <v>2427</v>
+      </c>
+      <c r="C201" s="34" t="s">
         <v>2430</v>
-      </c>
-      <c r="C201" s="34" t="s">
-        <v>2434</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B202" s="31" t="s">
-        <v>2431</v>
+        <v>2428</v>
       </c>
       <c r="C202" s="34" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B203" s="31" t="s">
-        <v>2432</v>
+        <v>2429</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
-        <v>2436</v>
+        <v>2431</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>2441</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>2441</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B207" s="31" t="s">
+        <v>2434</v>
+      </c>
+      <c r="C207" s="34" t="s">
         <v>2437</v>
-      </c>
-      <c r="C207" s="34" t="s">
-        <v>2441</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B208" s="31" t="s">
-        <v>2438</v>
+        <v>2435</v>
       </c>
       <c r="C208" s="34" t="s">
-        <v>2441</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B209" s="31" t="s">
-        <v>2439</v>
+        <v>2436</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2441</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B211" s="31" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C211" s="34" t="s">
         <v>2442</v>
-      </c>
-      <c r="C211" s="34" t="s">
-        <v>2446</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B212" s="31" t="s">
-        <v>2443</v>
+        <v>2440</v>
       </c>
       <c r="C212" s="34" t="s">
-        <v>2446</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B213" s="31" t="s">
-        <v>2444</v>
+        <v>2441</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2446</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="C214" s="34" t="s">
         <v>2446</v>
@@ -28827,26 +29056,26 @@
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B215" s="31" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="C215" s="34" t="s">
-        <v>2450</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B216" s="31" t="s">
-        <v>2448</v>
+        <v>2445</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2450</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2449</v>
+        <v>2454</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2450</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
@@ -28854,84 +29083,84 @@
         <v>2458</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2461</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
-        <v>2462</v>
+        <v>2455</v>
       </c>
       <c r="C219" s="34" t="s">
-        <v>2461</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B220" s="31" t="s">
-        <v>2459</v>
+        <v>2456</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2461</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
+        <v>2459</v>
+      </c>
+      <c r="C221" s="34" t="s">
         <v>2460</v>
-      </c>
-      <c r="C221" s="34" t="s">
-        <v>2461</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2465</v>
-      </c>
-      <c r="C223" s="34" t="s">
-        <v>2466</v>
+        <v>2463</v>
+      </c>
+      <c r="C223" s="43" t="s">
+        <v>2501</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C224" s="34" t="s">
         <v>2467</v>
-      </c>
-      <c r="C224" s="43" t="s">
-        <v>2505</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B225" s="31" t="s">
-        <v>2468</v>
+        <v>2465</v>
       </c>
       <c r="C225" s="34" t="s">
-        <v>2471</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B226" s="31" t="s">
-        <v>2469</v>
+        <v>2466</v>
       </c>
       <c r="C226" s="34" t="s">
-        <v>2471</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B227" s="31" t="s">
-        <v>2470</v>
+        <v>2386</v>
       </c>
       <c r="C227" s="34" t="s">
-        <v>2471</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B228" s="31" t="s">
-        <v>2390</v>
+        <v>2468</v>
       </c>
       <c r="C228" s="34" t="s">
         <v>2471</v>
@@ -28939,545 +29168,551 @@
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B229" s="31" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
       <c r="C229" s="34" t="s">
-        <v>2475</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B230" s="31" t="s">
-        <v>2473</v>
+        <v>2470</v>
       </c>
       <c r="C230" s="34" t="s">
-        <v>2475</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B231" s="31" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="C231" s="34" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B232" s="31" t="s">
-        <v>2476</v>
+        <v>2473</v>
       </c>
       <c r="C232" s="34" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B233" s="31" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C233" s="34" t="s">
         <v>2477</v>
-      </c>
-      <c r="C233" s="34" t="s">
-        <v>2481</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B234" s="31" t="s">
-        <v>2478</v>
+        <v>2475</v>
       </c>
       <c r="C234" s="34" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B235" s="31" t="s">
-        <v>2479</v>
+        <v>2476</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B236" s="31" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="C236" s="34" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B237" s="31" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="C237" s="34" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B238" s="31" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="C238" s="34" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B239" s="31" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="C239" s="34" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="240" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B240" s="31" t="s">
-        <v>2488</v>
+        <v>2485</v>
       </c>
       <c r="C240" s="34" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B241" s="31" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C241" s="34" t="s">
         <v>2489</v>
-      </c>
-      <c r="C241" s="34" t="s">
-        <v>2493</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B242" s="31" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B243" s="31" t="s">
-        <v>2491</v>
+        <v>2488</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="C244" s="34" t="s">
-        <v>2493</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
-        <v>2494</v>
+        <v>2491</v>
       </c>
       <c r="C245" s="34" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B246" s="31" t="s">
-        <v>2495</v>
+        <v>2492</v>
       </c>
       <c r="C246" s="34" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
-        <v>2496</v>
+        <v>2502</v>
       </c>
       <c r="C247" s="34" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="C248" s="34" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="C249" s="34" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="C250" s="34" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="C251" s="34" t="s">
-        <v>2124</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2511</v>
-      </c>
-      <c r="C252" s="34" t="s">
-        <v>2123</v>
+        <v>2508</v>
+      </c>
+      <c r="C252" s="32" t="s">
+        <v>2130</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2512</v>
+        <v>2509</v>
       </c>
       <c r="C253" s="32" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="C254" s="32" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2514</v>
-      </c>
-      <c r="C255" s="32" t="s">
-        <v>2133</v>
+        <v>2511</v>
+      </c>
+      <c r="C255" s="34" t="s">
+        <v>2518</v>
       </c>
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="C256" s="34" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="C258" s="34" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
+        <v>2515</v>
+      </c>
+      <c r="C259" s="34" t="s">
         <v>2518</v>
-      </c>
-      <c r="C259" s="34" t="s">
-        <v>2522</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="C260" s="34" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
-        <v>2521</v>
+        <v>2360</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
-        <v>2364</v>
+        <v>2519</v>
       </c>
       <c r="C263" s="34" t="s">
-        <v>2522</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
-        <v>2527</v>
+        <v>2269</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2273</v>
+        <v>2524</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
+        <v>2525</v>
+      </c>
+      <c r="C270" s="34" t="s">
         <v>2528</v>
-      </c>
-      <c r="C270" s="34" t="s">
-        <v>2532</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
         <v>2529</v>
       </c>
-      <c r="C271" s="34" t="s">
-        <v>2532</v>
+      <c r="C271" s="32" t="s">
+        <v>2506</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2533</v>
+        <v>2232</v>
       </c>
       <c r="C272" s="32" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
-        <v>2236</v>
+        <v>2530</v>
       </c>
       <c r="C273" s="32" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2534</v>
-      </c>
-      <c r="C274" s="32" t="s">
-        <v>2510</v>
+        <v>2531</v>
+      </c>
+      <c r="C274" s="34" t="s">
+        <v>2533</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="C275" s="34" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
         <v>2536</v>
       </c>
-      <c r="C276" s="34" t="s">
-        <v>2537</v>
+      <c r="C276" s="32" t="s">
+        <v>2114</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2540</v>
+        <v>2537</v>
       </c>
       <c r="C277" s="32" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
       <c r="C278" s="32" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2542</v>
-      </c>
-      <c r="C279" s="32" t="s">
-        <v>2117</v>
+        <v>2546</v>
+      </c>
+      <c r="C279" s="34" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B280" s="31" t="s">
+        <v>2547</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{0EB44661-183D-4646-80E2-AA1D4A96912E}"/>
-    <hyperlink ref="C26" r:id="rId2" xr:uid="{105BFC71-5226-47EF-8B88-42C08E33B880}"/>
-    <hyperlink ref="C27" r:id="rId3" xr:uid="{158B496B-D8CE-4C70-B207-69BDFE910B67}"/>
-    <hyperlink ref="C28" r:id="rId4" xr:uid="{7F7C648E-7156-4AE0-95FF-F49439BC92D7}"/>
-    <hyperlink ref="C29" r:id="rId5" xr:uid="{74A23EE2-81A4-492E-9B92-8B15616E0D11}"/>
-    <hyperlink ref="C30" r:id="rId6" xr:uid="{D535204F-D3DC-4E0D-B9F9-99AF95FA4ACD}"/>
-    <hyperlink ref="C31" r:id="rId7" xr:uid="{F949B8EB-99D0-4C2B-B0EB-F92A3C0F8F49}"/>
-    <hyperlink ref="C32" r:id="rId8" xr:uid="{710F7492-3506-4999-BAFA-7F573B8E3A8A}"/>
-    <hyperlink ref="C33" r:id="rId9" xr:uid="{B592B173-D1C1-4413-8C1C-C0AF4E431AD3}"/>
-    <hyperlink ref="C34" r:id="rId10" xr:uid="{6C4BA2E9-C727-43B0-A29D-D09435B3A288}"/>
-    <hyperlink ref="C35" r:id="rId11" xr:uid="{B43E2E47-BFAF-448C-B814-95A48DA6EFA1}"/>
-    <hyperlink ref="C36" r:id="rId12" xr:uid="{1E906BC9-34FA-4F98-8758-5B43998F4730}"/>
-    <hyperlink ref="C37" r:id="rId13" xr:uid="{42A07109-BDC8-435A-AF7F-AB27AB51DD2E}"/>
-    <hyperlink ref="C38" r:id="rId14" xr:uid="{9529E9B7-FEF9-478F-98E2-12EBDA4A1130}"/>
-    <hyperlink ref="C39" r:id="rId15" xr:uid="{9E1AA43B-AC4A-4B02-A331-BD7ABB83419D}"/>
-    <hyperlink ref="C40" r:id="rId16" xr:uid="{7A8A5653-053D-4678-8755-B3EB6C021AEC}"/>
-    <hyperlink ref="C41" r:id="rId17" xr:uid="{49A53077-CE6B-4084-B12F-727CDC458BF6}"/>
-    <hyperlink ref="C42" r:id="rId18" xr:uid="{3A9C678F-E518-4BD6-A5B9-951EC9806F52}"/>
-    <hyperlink ref="C43" r:id="rId19" xr:uid="{E1ABD804-6F32-4267-9363-5C4BB0DE4380}"/>
-    <hyperlink ref="C44" r:id="rId20" xr:uid="{1F532866-B172-4F5C-866C-F14392BC837D}"/>
-    <hyperlink ref="C45" r:id="rId21" xr:uid="{DEDE46D3-59A7-45B3-B474-6064F9E31660}"/>
-    <hyperlink ref="C46" r:id="rId22" xr:uid="{868BF141-2DE6-497E-9FBC-4AE8EC561280}"/>
-    <hyperlink ref="C47" r:id="rId23" xr:uid="{1A9D101D-5436-418A-B1D3-A10E55DCAEB0}"/>
-    <hyperlink ref="C48" r:id="rId24" xr:uid="{0A543EEC-AD1C-411F-A874-A73994BFF645}"/>
-    <hyperlink ref="C49" r:id="rId25" xr:uid="{FAA02E2D-6E05-489A-8A5A-296E4ADE0743}"/>
-    <hyperlink ref="C50" r:id="rId26" xr:uid="{E76663FA-92C7-4086-959F-FF12131FC1F4}"/>
-    <hyperlink ref="C51" r:id="rId27" xr:uid="{3BB3B688-BCDB-4AB1-9E05-E996CDE2B37C}"/>
-    <hyperlink ref="C52" r:id="rId28" xr:uid="{5F7D4CDD-3586-460F-9482-2C0C25F4310E}"/>
-    <hyperlink ref="C53" r:id="rId29" xr:uid="{7A32BA52-AC52-440B-A5C8-B8010FDB3A3E}"/>
-    <hyperlink ref="C54" r:id="rId30" xr:uid="{1755F908-0626-4A13-8A41-AE3B869ED573}"/>
-    <hyperlink ref="C55" r:id="rId31" xr:uid="{DC52ED96-0637-49FF-A28E-36F20A51C33C}"/>
-    <hyperlink ref="C56:C70" r:id="rId32" display="地下街について" xr:uid="{CB188704-BC12-4A02-9FD0-638054C90375}"/>
-    <hyperlink ref="C71" r:id="rId33" xr:uid="{7928797A-C5DF-4728-9549-ABC52D4EACEE}"/>
-    <hyperlink ref="C72" r:id="rId34" xr:uid="{F76AB73C-F876-4DF2-96C6-6163DA320730}"/>
-    <hyperlink ref="C73:C92" r:id="rId35" display="沿革？" xr:uid="{F4EE62D7-4C6F-4EA2-9B9C-33FB3A6EC0E3}"/>
-    <hyperlink ref="C93" r:id="rId36" xr:uid="{583C6BD0-F972-4FCE-9396-2CBCC08D6FDE}"/>
-    <hyperlink ref="C94" r:id="rId37" xr:uid="{F06D86F4-AB96-409E-8DDD-94645E5FE304}"/>
-    <hyperlink ref="C95" r:id="rId38" xr:uid="{650ECBC7-1D3E-47F9-A04B-91409F4AFD82}"/>
-    <hyperlink ref="C96" r:id="rId39" xr:uid="{75F24C6E-979A-4ECB-95F5-2AB7E52FFB3E}"/>
-    <hyperlink ref="C97" r:id="rId40" xr:uid="{D9C0E6B3-F6F4-4826-91A7-073BB4A33382}"/>
-    <hyperlink ref="C99" r:id="rId41" xr:uid="{C71D6526-B182-4F76-AF5F-B6B680D9C45A}"/>
-    <hyperlink ref="C100:C108" r:id="rId42" display="そば屋" xr:uid="{40157A7E-CAB9-47AA-A338-F67391C4503D}"/>
-    <hyperlink ref="C98" r:id="rId43" xr:uid="{420879CC-989A-4756-8081-0E73B34C1E0E}"/>
-    <hyperlink ref="C110" r:id="rId44" xr:uid="{08AFE583-4426-461B-979B-F49FE83DAB8B}"/>
-    <hyperlink ref="C111" r:id="rId45" xr:uid="{4B7DEC01-3433-493D-B1C4-DB5A8E94100F}"/>
-    <hyperlink ref="C112" r:id="rId46" xr:uid="{033DA32D-FAE1-4F14-8183-633E4BD0685F}"/>
-    <hyperlink ref="C113" r:id="rId47" xr:uid="{F5795EE1-139B-45EA-B58B-15E854EAAE5A}"/>
-    <hyperlink ref="C109" r:id="rId48" xr:uid="{F2014E68-B566-4189-B5F6-D6EDBE18923E}"/>
-    <hyperlink ref="C114" r:id="rId49" xr:uid="{15F4FF79-5F95-4C8F-A6B7-69888A1FCE6D}"/>
-    <hyperlink ref="C115:C119" r:id="rId50" display="化しょう屋" xr:uid="{C36F89E4-6767-4188-A309-322ABD51A23A}"/>
-    <hyperlink ref="C120" r:id="rId51" xr:uid="{B25A19F7-C29D-4D44-AC0C-A8DB47267A0C}"/>
-    <hyperlink ref="C121" r:id="rId52" xr:uid="{A1A626FD-0CE4-486F-8590-123D1319E54C}"/>
-    <hyperlink ref="C122" r:id="rId53" xr:uid="{1F8B8F90-51A5-4592-921F-1E537FBAAB02}"/>
-    <hyperlink ref="C123" r:id="rId54" xr:uid="{87BFCFB8-139F-4781-AF48-25318B2E8D71}"/>
-    <hyperlink ref="C124" r:id="rId55" xr:uid="{F40A3028-CD41-4895-810E-85739533F5BA}"/>
-    <hyperlink ref="C125" r:id="rId56" xr:uid="{C3EF1F2D-B6BA-4AE2-8B14-1F43AFE56D4E}"/>
-    <hyperlink ref="C126" r:id="rId57" xr:uid="{D6C949E3-BDA6-4B98-8D49-849E42D416EA}"/>
-    <hyperlink ref="C127:C133" r:id="rId58" display="すし屋" xr:uid="{19CFE92A-BD95-4F91-A784-CB5138E9E5C4}"/>
-    <hyperlink ref="C134" r:id="rId59" xr:uid="{C0DB6F37-9F22-4FB7-9A59-FCA8F06DF804}"/>
-    <hyperlink ref="C135:C139" r:id="rId60" display="らーめん屋" xr:uid="{63D1B813-7B17-494F-BFD0-6ED9C23C668E}"/>
-    <hyperlink ref="C140" r:id="rId61" xr:uid="{64CD0AF5-A92E-4E7F-AE38-241FA8F9302D}"/>
-    <hyperlink ref="C141:C144" r:id="rId62" display="ばー" xr:uid="{BEED3297-1DC6-4F65-91E1-A74DB10D382C}"/>
-    <hyperlink ref="C145" r:id="rId63" xr:uid="{C5C057AE-4947-4F4D-ADF4-6DFE9B7B1190}"/>
-    <hyperlink ref="C146:C147" r:id="rId64" display="とこ屋" xr:uid="{B04EB1D9-D776-4BFF-BCDF-98FA89FFC4F6}"/>
-    <hyperlink ref="C148" r:id="rId65" xr:uid="{46895BCD-A492-42BA-8537-5F5398E80386}"/>
-    <hyperlink ref="C149:C156" r:id="rId66" display="いざか屋" xr:uid="{39266F4C-B934-4957-9402-7811D42AFD6B}"/>
-    <hyperlink ref="C157" r:id="rId67" xr:uid="{F198DF54-7E95-4394-BF80-8CA922FC47ED}"/>
-    <hyperlink ref="C158:C160" r:id="rId68" display="おにぎり屋" xr:uid="{398BF49B-AA77-45F5-BA77-9B3365BBE736}"/>
-    <hyperlink ref="C161" r:id="rId69" xr:uid="{F98B3542-E61E-4C4A-A541-D41290107680}"/>
-    <hyperlink ref="C162:C168" r:id="rId70" display="中かりょうり屋" xr:uid="{AE87470A-3000-4C0E-8365-72BCD5DCBF4F}"/>
-    <hyperlink ref="C169" r:id="rId71" xr:uid="{0363DCBF-B486-4536-A7A7-05A05D0E5287}"/>
-    <hyperlink ref="C170:C172" r:id="rId72" display="きっさ屋" xr:uid="{0041D719-6E11-42B7-8456-4D8C7DB65987}"/>
-    <hyperlink ref="C173" r:id="rId73" xr:uid="{D6B4BEFA-5954-43EB-B798-B392F55C96FE}"/>
-    <hyperlink ref="C174:C177" r:id="rId74" display="花屋" xr:uid="{21461B74-589B-4F4E-B344-8583D17BD3E1}"/>
-    <hyperlink ref="C178" r:id="rId75" xr:uid="{FB788C7B-4C32-4CE4-91C4-B0A314142046}"/>
-    <hyperlink ref="C181" r:id="rId76" xr:uid="{D8150307-7C4F-4883-93D1-DE938BDA255F}"/>
-    <hyperlink ref="D133" r:id="rId77" xr:uid="{D7B5F7EF-8A3E-4EF9-BE9B-87BD25B1DEC3}"/>
-    <hyperlink ref="C182:C184" r:id="rId78" display="うらない屋" xr:uid="{BD5B9AA7-BEE9-4B4D-869C-96CBA2E0AB53}"/>
-    <hyperlink ref="C185" r:id="rId79" xr:uid="{A956E415-925E-4BE7-8C7B-34E6470531C7}"/>
-    <hyperlink ref="C186:C187" r:id="rId80" display="じゃずばー" xr:uid="{F3C1261E-4D64-4AF6-B5B1-D120DE06DE1E}"/>
-    <hyperlink ref="C188" r:id="rId81" xr:uid="{23FCEF9A-0D1E-42CA-AFD5-D7B4C91E6D26}"/>
-    <hyperlink ref="C189:C191" r:id="rId82" display="れこーど屋" xr:uid="{67DEEB48-8CEC-4228-8750-64B86E077C59}"/>
-    <hyperlink ref="C192" r:id="rId83" xr:uid="{80EE8314-4DD1-46C4-AE4C-CA0FD6A68933}"/>
-    <hyperlink ref="C193:C195" r:id="rId84" display="くつ屋" xr:uid="{3788FC8E-1620-4335-8625-8DCA71AC925D}"/>
-    <hyperlink ref="D159" r:id="rId85" xr:uid="{1AC6C13F-D00F-4482-98BE-1C2CCF13D05D}"/>
-    <hyperlink ref="C196" r:id="rId86" xr:uid="{63988F07-EA6D-4F26-9226-45FD114364DC}"/>
-    <hyperlink ref="C197:C199" r:id="rId87" display="本屋" xr:uid="{2A3A625B-6EA8-437E-81C7-68CF5E700BFC}"/>
-    <hyperlink ref="C200" r:id="rId88" xr:uid="{11E58C7C-D20F-4332-BA3A-857C1491B32B}"/>
-    <hyperlink ref="C201:C204" r:id="rId89" display="けーき屋" xr:uid="{88195962-BB93-453B-81A1-52FA5CBE67AF}"/>
-    <hyperlink ref="C205" r:id="rId90" xr:uid="{724A06D0-79BF-46A2-B58C-0C3ECBBFDB45}"/>
-    <hyperlink ref="C206:C210" r:id="rId91" display="清そう屋" xr:uid="{9E37B236-0ED6-47F6-BF18-86B12BD98E6B}"/>
-    <hyperlink ref="C211" r:id="rId92" xr:uid="{EF971420-17D4-4182-8132-56F00A167A2C}"/>
-    <hyperlink ref="C212:C214" r:id="rId93" display="時けい屋" xr:uid="{6C295750-0F27-47E0-9129-453CA0F3E98B}"/>
-    <hyperlink ref="C215" r:id="rId94" xr:uid="{DB4BE4EC-BA0C-456D-B5AB-A0C311E10FC4}"/>
-    <hyperlink ref="C216:C217" r:id="rId95" display="くすり屋" xr:uid="{C21A8AF9-DE63-4441-BD5E-F5FF047CB554}"/>
-    <hyperlink ref="C218" r:id="rId96" xr:uid="{D901BE77-9912-45E3-9CE7-FF143E1A7C55}"/>
-    <hyperlink ref="C220:C221" r:id="rId97" display="くりーにんぐ屋" xr:uid="{404FE6C1-57C6-4D57-9720-912B76B3036C}"/>
-    <hyperlink ref="C219" r:id="rId98" xr:uid="{E32A61DB-E7C1-4C00-A9EA-3C2EE69560FA}"/>
-    <hyperlink ref="C222" r:id="rId99" xr:uid="{F3012094-E137-4787-AE48-4A8F62EFE745}"/>
-    <hyperlink ref="C223" r:id="rId100" xr:uid="{25CF5C66-B1C6-4B3A-84C7-C4ADF6D77959}"/>
-    <hyperlink ref="C225" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
-    <hyperlink ref="C226:C228" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
-    <hyperlink ref="C229" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
-    <hyperlink ref="C230:C231" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
-    <hyperlink ref="C232" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
-    <hyperlink ref="C233:C236" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
-    <hyperlink ref="C237" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
-    <hyperlink ref="C238" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
-    <hyperlink ref="C239" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
-    <hyperlink ref="C240" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
-    <hyperlink ref="C241:C244" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
-    <hyperlink ref="C224" r:id="rId112" display="●壁？" xr:uid="{49CFE894-D6FF-4DAD-A18A-E33C19DC9AC5}"/>
-    <hyperlink ref="C245" r:id="rId113" xr:uid="{9AC2C8BA-0A2B-4264-BFE4-5067BC7FCBBD}"/>
-    <hyperlink ref="C246:C251" r:id="rId114" display="なき子" xr:uid="{CCC49224-E3E0-47BD-9BA3-ED7C3711BAF4}"/>
-    <hyperlink ref="D76" r:id="rId115" xr:uid="{F3D3E429-A98C-4A89-8517-136EBFF9C669}"/>
-    <hyperlink ref="C252" r:id="rId116" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
-    <hyperlink ref="C253" r:id="rId117" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
-    <hyperlink ref="C254:C255" r:id="rId118" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
-    <hyperlink ref="C256" r:id="rId119" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
-    <hyperlink ref="C257:C263" r:id="rId120" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
-    <hyperlink ref="C264" r:id="rId121" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
-    <hyperlink ref="C265:C271" r:id="rId122" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
-    <hyperlink ref="C272" r:id="rId123" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
-    <hyperlink ref="C273" r:id="rId124" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
-    <hyperlink ref="C274" r:id="rId125" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
-    <hyperlink ref="C275" r:id="rId126" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
-    <hyperlink ref="C276" r:id="rId127" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
-    <hyperlink ref="C277" r:id="rId128" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
-    <hyperlink ref="C278" r:id="rId129" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
-    <hyperlink ref="C279" r:id="rId130" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
+    <hyperlink ref="C25" r:id="rId2" xr:uid="{105BFC71-5226-47EF-8B88-42C08E33B880}"/>
+    <hyperlink ref="C26" r:id="rId3" xr:uid="{158B496B-D8CE-4C70-B207-69BDFE910B67}"/>
+    <hyperlink ref="C27" r:id="rId4" xr:uid="{7F7C648E-7156-4AE0-95FF-F49439BC92D7}"/>
+    <hyperlink ref="C28" r:id="rId5" xr:uid="{74A23EE2-81A4-492E-9B92-8B15616E0D11}"/>
+    <hyperlink ref="C29" r:id="rId6" xr:uid="{D535204F-D3DC-4E0D-B9F9-99AF95FA4ACD}"/>
+    <hyperlink ref="C30" r:id="rId7" xr:uid="{F949B8EB-99D0-4C2B-B0EB-F92A3C0F8F49}"/>
+    <hyperlink ref="C31" r:id="rId8" xr:uid="{710F7492-3506-4999-BAFA-7F573B8E3A8A}"/>
+    <hyperlink ref="C32" r:id="rId9" xr:uid="{B592B173-D1C1-4413-8C1C-C0AF4E431AD3}"/>
+    <hyperlink ref="C33" r:id="rId10" xr:uid="{6C4BA2E9-C727-43B0-A29D-D09435B3A288}"/>
+    <hyperlink ref="C34" r:id="rId11" xr:uid="{B43E2E47-BFAF-448C-B814-95A48DA6EFA1}"/>
+    <hyperlink ref="C35" r:id="rId12" xr:uid="{1E906BC9-34FA-4F98-8758-5B43998F4730}"/>
+    <hyperlink ref="C36" r:id="rId13" xr:uid="{42A07109-BDC8-435A-AF7F-AB27AB51DD2E}"/>
+    <hyperlink ref="C37" r:id="rId14" xr:uid="{9529E9B7-FEF9-478F-98E2-12EBDA4A1130}"/>
+    <hyperlink ref="C38" r:id="rId15" xr:uid="{9E1AA43B-AC4A-4B02-A331-BD7ABB83419D}"/>
+    <hyperlink ref="C39" r:id="rId16" xr:uid="{7A8A5653-053D-4678-8755-B3EB6C021AEC}"/>
+    <hyperlink ref="C40" r:id="rId17" xr:uid="{49A53077-CE6B-4084-B12F-727CDC458BF6}"/>
+    <hyperlink ref="C41" r:id="rId18" xr:uid="{3A9C678F-E518-4BD6-A5B9-951EC9806F52}"/>
+    <hyperlink ref="C42" r:id="rId19" xr:uid="{E1ABD804-6F32-4267-9363-5C4BB0DE4380}"/>
+    <hyperlink ref="C43" r:id="rId20" xr:uid="{1F532866-B172-4F5C-866C-F14392BC837D}"/>
+    <hyperlink ref="C44" r:id="rId21" xr:uid="{DEDE46D3-59A7-45B3-B474-6064F9E31660}"/>
+    <hyperlink ref="C45" r:id="rId22" xr:uid="{868BF141-2DE6-497E-9FBC-4AE8EC561280}"/>
+    <hyperlink ref="C46" r:id="rId23" xr:uid="{1A9D101D-5436-418A-B1D3-A10E55DCAEB0}"/>
+    <hyperlink ref="C47" r:id="rId24" xr:uid="{0A543EEC-AD1C-411F-A874-A73994BFF645}"/>
+    <hyperlink ref="C48" r:id="rId25" xr:uid="{FAA02E2D-6E05-489A-8A5A-296E4ADE0743}"/>
+    <hyperlink ref="C49" r:id="rId26" xr:uid="{E76663FA-92C7-4086-959F-FF12131FC1F4}"/>
+    <hyperlink ref="C50" r:id="rId27" xr:uid="{3BB3B688-BCDB-4AB1-9E05-E996CDE2B37C}"/>
+    <hyperlink ref="C51" r:id="rId28" xr:uid="{5F7D4CDD-3586-460F-9482-2C0C25F4310E}"/>
+    <hyperlink ref="C52" r:id="rId29" xr:uid="{7A32BA52-AC52-440B-A5C8-B8010FDB3A3E}"/>
+    <hyperlink ref="C53" r:id="rId30" xr:uid="{1755F908-0626-4A13-8A41-AE3B869ED573}"/>
+    <hyperlink ref="C54" r:id="rId31" xr:uid="{DC52ED96-0637-49FF-A28E-36F20A51C33C}"/>
+    <hyperlink ref="C55:C69" r:id="rId32" display="地下街について" xr:uid="{CB188704-BC12-4A02-9FD0-638054C90375}"/>
+    <hyperlink ref="C70" r:id="rId33" xr:uid="{7928797A-C5DF-4728-9549-ABC52D4EACEE}"/>
+    <hyperlink ref="C71" r:id="rId34" xr:uid="{F76AB73C-F876-4DF2-96C6-6163DA320730}"/>
+    <hyperlink ref="C72:C91" r:id="rId35" display="沿革？" xr:uid="{F4EE62D7-4C6F-4EA2-9B9C-33FB3A6EC0E3}"/>
+    <hyperlink ref="C92" r:id="rId36" xr:uid="{583C6BD0-F972-4FCE-9396-2CBCC08D6FDE}"/>
+    <hyperlink ref="C93" r:id="rId37" xr:uid="{F06D86F4-AB96-409E-8DDD-94645E5FE304}"/>
+    <hyperlink ref="C94" r:id="rId38" xr:uid="{650ECBC7-1D3E-47F9-A04B-91409F4AFD82}"/>
+    <hyperlink ref="C95" r:id="rId39" xr:uid="{75F24C6E-979A-4ECB-95F5-2AB7E52FFB3E}"/>
+    <hyperlink ref="C96" r:id="rId40" xr:uid="{D9C0E6B3-F6F4-4826-91A7-073BB4A33382}"/>
+    <hyperlink ref="C98" r:id="rId41" xr:uid="{C71D6526-B182-4F76-AF5F-B6B680D9C45A}"/>
+    <hyperlink ref="C99:C107" r:id="rId42" display="そば屋" xr:uid="{40157A7E-CAB9-47AA-A338-F67391C4503D}"/>
+    <hyperlink ref="C97" r:id="rId43" xr:uid="{420879CC-989A-4756-8081-0E73B34C1E0E}"/>
+    <hyperlink ref="C109" r:id="rId44" xr:uid="{08AFE583-4426-461B-979B-F49FE83DAB8B}"/>
+    <hyperlink ref="C110" r:id="rId45" xr:uid="{4B7DEC01-3433-493D-B1C4-DB5A8E94100F}"/>
+    <hyperlink ref="C111" r:id="rId46" xr:uid="{033DA32D-FAE1-4F14-8183-633E4BD0685F}"/>
+    <hyperlink ref="C112" r:id="rId47" xr:uid="{F5795EE1-139B-45EA-B58B-15E854EAAE5A}"/>
+    <hyperlink ref="C108" r:id="rId48" xr:uid="{F2014E68-B566-4189-B5F6-D6EDBE18923E}"/>
+    <hyperlink ref="C113" r:id="rId49" xr:uid="{15F4FF79-5F95-4C8F-A6B7-69888A1FCE6D}"/>
+    <hyperlink ref="C114:C118" r:id="rId50" display="化しょう屋" xr:uid="{C36F89E4-6767-4188-A309-322ABD51A23A}"/>
+    <hyperlink ref="C119" r:id="rId51" xr:uid="{B25A19F7-C29D-4D44-AC0C-A8DB47267A0C}"/>
+    <hyperlink ref="C120" r:id="rId52" xr:uid="{A1A626FD-0CE4-486F-8590-123D1319E54C}"/>
+    <hyperlink ref="C121" r:id="rId53" xr:uid="{1F8B8F90-51A5-4592-921F-1E537FBAAB02}"/>
+    <hyperlink ref="C122" r:id="rId54" xr:uid="{87BFCFB8-139F-4781-AF48-25318B2E8D71}"/>
+    <hyperlink ref="C123" r:id="rId55" xr:uid="{F40A3028-CD41-4895-810E-85739533F5BA}"/>
+    <hyperlink ref="C124" r:id="rId56" xr:uid="{C3EF1F2D-B6BA-4AE2-8B14-1F43AFE56D4E}"/>
+    <hyperlink ref="C125" r:id="rId57" xr:uid="{D6C949E3-BDA6-4B98-8D49-849E42D416EA}"/>
+    <hyperlink ref="C126:C132" r:id="rId58" display="すし屋" xr:uid="{19CFE92A-BD95-4F91-A784-CB5138E9E5C4}"/>
+    <hyperlink ref="C133" r:id="rId59" xr:uid="{C0DB6F37-9F22-4FB7-9A59-FCA8F06DF804}"/>
+    <hyperlink ref="C134:C138" r:id="rId60" display="らーめん屋" xr:uid="{63D1B813-7B17-494F-BFD0-6ED9C23C668E}"/>
+    <hyperlink ref="C139" r:id="rId61" xr:uid="{64CD0AF5-A92E-4E7F-AE38-241FA8F9302D}"/>
+    <hyperlink ref="C140:C143" r:id="rId62" display="ばー" xr:uid="{BEED3297-1DC6-4F65-91E1-A74DB10D382C}"/>
+    <hyperlink ref="C144" r:id="rId63" xr:uid="{C5C057AE-4947-4F4D-ADF4-6DFE9B7B1190}"/>
+    <hyperlink ref="C145:C146" r:id="rId64" display="とこ屋" xr:uid="{B04EB1D9-D776-4BFF-BCDF-98FA89FFC4F6}"/>
+    <hyperlink ref="C147" r:id="rId65" xr:uid="{46895BCD-A492-42BA-8537-5F5398E80386}"/>
+    <hyperlink ref="C148:C155" r:id="rId66" display="いざか屋" xr:uid="{39266F4C-B934-4957-9402-7811D42AFD6B}"/>
+    <hyperlink ref="C156" r:id="rId67" xr:uid="{F198DF54-7E95-4394-BF80-8CA922FC47ED}"/>
+    <hyperlink ref="C157:C159" r:id="rId68" display="おにぎり屋" xr:uid="{398BF49B-AA77-45F5-BA77-9B3365BBE736}"/>
+    <hyperlink ref="C160" r:id="rId69" xr:uid="{F98B3542-E61E-4C4A-A541-D41290107680}"/>
+    <hyperlink ref="C161:C167" r:id="rId70" display="中かりょうり屋" xr:uid="{AE87470A-3000-4C0E-8365-72BCD5DCBF4F}"/>
+    <hyperlink ref="C168" r:id="rId71" xr:uid="{0363DCBF-B486-4536-A7A7-05A05D0E5287}"/>
+    <hyperlink ref="C169:C171" r:id="rId72" display="きっさ屋" xr:uid="{0041D719-6E11-42B7-8456-4D8C7DB65987}"/>
+    <hyperlink ref="C172" r:id="rId73" xr:uid="{D6B4BEFA-5954-43EB-B798-B392F55C96FE}"/>
+    <hyperlink ref="C173:C176" r:id="rId74" display="花屋" xr:uid="{21461B74-589B-4F4E-B344-8583D17BD3E1}"/>
+    <hyperlink ref="C177" r:id="rId75" xr:uid="{FB788C7B-4C32-4CE4-91C4-B0A314142046}"/>
+    <hyperlink ref="C180" r:id="rId76" xr:uid="{D8150307-7C4F-4883-93D1-DE938BDA255F}"/>
+    <hyperlink ref="D132" r:id="rId77" xr:uid="{D7B5F7EF-8A3E-4EF9-BE9B-87BD25B1DEC3}"/>
+    <hyperlink ref="C181:C183" r:id="rId78" display="うらない屋" xr:uid="{BD5B9AA7-BEE9-4B4D-869C-96CBA2E0AB53}"/>
+    <hyperlink ref="C184" r:id="rId79" xr:uid="{A956E415-925E-4BE7-8C7B-34E6470531C7}"/>
+    <hyperlink ref="C185:C186" r:id="rId80" display="じゃずばー" xr:uid="{F3C1261E-4D64-4AF6-B5B1-D120DE06DE1E}"/>
+    <hyperlink ref="C187" r:id="rId81" xr:uid="{23FCEF9A-0D1E-42CA-AFD5-D7B4C91E6D26}"/>
+    <hyperlink ref="C188:C190" r:id="rId82" display="れこーど屋" xr:uid="{67DEEB48-8CEC-4228-8750-64B86E077C59}"/>
+    <hyperlink ref="C191" r:id="rId83" xr:uid="{80EE8314-4DD1-46C4-AE4C-CA0FD6A68933}"/>
+    <hyperlink ref="C192:C194" r:id="rId84" display="くつ屋" xr:uid="{3788FC8E-1620-4335-8625-8DCA71AC925D}"/>
+    <hyperlink ref="D158" r:id="rId85" xr:uid="{1AC6C13F-D00F-4482-98BE-1C2CCF13D05D}"/>
+    <hyperlink ref="C195" r:id="rId86" xr:uid="{63988F07-EA6D-4F26-9226-45FD114364DC}"/>
+    <hyperlink ref="C196:C198" r:id="rId87" display="本屋" xr:uid="{2A3A625B-6EA8-437E-81C7-68CF5E700BFC}"/>
+    <hyperlink ref="C199" r:id="rId88" xr:uid="{11E58C7C-D20F-4332-BA3A-857C1491B32B}"/>
+    <hyperlink ref="C200:C203" r:id="rId89" display="けーき屋" xr:uid="{88195962-BB93-453B-81A1-52FA5CBE67AF}"/>
+    <hyperlink ref="C204" r:id="rId90" xr:uid="{724A06D0-79BF-46A2-B58C-0C3ECBBFDB45}"/>
+    <hyperlink ref="C205:C209" r:id="rId91" display="清そう屋" xr:uid="{9E37B236-0ED6-47F6-BF18-86B12BD98E6B}"/>
+    <hyperlink ref="C210" r:id="rId92" xr:uid="{EF971420-17D4-4182-8132-56F00A167A2C}"/>
+    <hyperlink ref="C211:C213" r:id="rId93" display="時けい屋" xr:uid="{6C295750-0F27-47E0-9129-453CA0F3E98B}"/>
+    <hyperlink ref="C214" r:id="rId94" xr:uid="{DB4BE4EC-BA0C-456D-B5AB-A0C311E10FC4}"/>
+    <hyperlink ref="C215:C216" r:id="rId95" display="くすり屋" xr:uid="{C21A8AF9-DE63-4441-BD5E-F5FF047CB554}"/>
+    <hyperlink ref="C217" r:id="rId96" xr:uid="{D901BE77-9912-45E3-9CE7-FF143E1A7C55}"/>
+    <hyperlink ref="C219:C220" r:id="rId97" display="くりーにんぐ屋" xr:uid="{404FE6C1-57C6-4D57-9720-912B76B3036C}"/>
+    <hyperlink ref="C218" r:id="rId98" xr:uid="{E32A61DB-E7C1-4C00-A9EA-3C2EE69560FA}"/>
+    <hyperlink ref="C221" r:id="rId99" xr:uid="{F3012094-E137-4787-AE48-4A8F62EFE745}"/>
+    <hyperlink ref="C222" r:id="rId100" xr:uid="{25CF5C66-B1C6-4B3A-84C7-C4ADF6D77959}"/>
+    <hyperlink ref="C224" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
+    <hyperlink ref="C225:C227" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
+    <hyperlink ref="C228" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
+    <hyperlink ref="C229:C230" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
+    <hyperlink ref="C231" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
+    <hyperlink ref="C232:C235" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
+    <hyperlink ref="C236" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
+    <hyperlink ref="C237" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
+    <hyperlink ref="C238" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
+    <hyperlink ref="C239" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
+    <hyperlink ref="C240:C243" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
+    <hyperlink ref="C223" r:id="rId112" display="●壁？" xr:uid="{49CFE894-D6FF-4DAD-A18A-E33C19DC9AC5}"/>
+    <hyperlink ref="C244" r:id="rId113" xr:uid="{9AC2C8BA-0A2B-4264-BFE4-5067BC7FCBBD}"/>
+    <hyperlink ref="C245:C250" r:id="rId114" display="なき子" xr:uid="{CCC49224-E3E0-47BD-9BA3-ED7C3711BAF4}"/>
+    <hyperlink ref="D75" r:id="rId115" xr:uid="{F3D3E429-A98C-4A89-8517-136EBFF9C669}"/>
+    <hyperlink ref="C251" r:id="rId116" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
+    <hyperlink ref="C252" r:id="rId117" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
+    <hyperlink ref="C253:C254" r:id="rId118" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
+    <hyperlink ref="C255" r:id="rId119" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
+    <hyperlink ref="C256:C262" r:id="rId120" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
+    <hyperlink ref="C263" r:id="rId121" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
+    <hyperlink ref="C264:C270" r:id="rId122" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
+    <hyperlink ref="C271" r:id="rId123" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
+    <hyperlink ref="C272" r:id="rId124" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
+    <hyperlink ref="C273" r:id="rId125" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
+    <hyperlink ref="C274" r:id="rId126" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
+    <hyperlink ref="C275" r:id="rId127" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
+    <hyperlink ref="C276" r:id="rId128" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
+    <hyperlink ref="C277" r:id="rId129" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
+    <hyperlink ref="C278" r:id="rId130" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
+    <hyperlink ref="C279" r:id="rId131" xr:uid="{638B7DD6-1594-44CE-9207-871F21E21DD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1557" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD7B0B71-8A2A-445A-8B0B-5ED507A6979E}"/>
+  <xr:revisionPtr revIDLastSave="1561" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A26A8C0-B8D3-428E-AEAB-4D27C146359D}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="2561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="2565">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -11323,6 +11323,42 @@
   </si>
   <si>
     <t>さかな屋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乳??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>偗??</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>??</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>侻??</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11907,10 +11943,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -15465,7 +15497,7 @@
         <v>1147</v>
       </c>
       <c r="C332" t="s">
-        <v>1147</v>
+        <v>2561</v>
       </c>
       <c r="D332" s="33" t="s">
         <v>2554</v>
@@ -15479,7 +15511,7 @@
         <v>2555</v>
       </c>
       <c r="C333" t="s">
-        <v>2555</v>
+        <v>2562</v>
       </c>
       <c r="D333" s="33" t="s">
         <v>2554</v>
@@ -15492,8 +15524,8 @@
       <c r="B334" s="1" t="s">
         <v>2556</v>
       </c>
-      <c r="C334" t="s">
-        <v>2556</v>
+      <c r="C334" s="41" t="s">
+        <v>2563</v>
       </c>
       <c r="D334" s="42" t="s">
         <v>2558</v>
@@ -15507,7 +15539,7 @@
         <v>2557</v>
       </c>
       <c r="C335" t="s">
-        <v>2557</v>
+        <v>2564</v>
       </c>
       <c r="D335" s="42" t="s">
         <v>2558</v>
@@ -16705,7 +16737,7 @@
       </c>
       <c r="AU3" s="6" t="str">
         <f>_xlfn.XLOOKUP(AT3,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>侸</v>
+        <v>侸??</v>
       </c>
       <c r="AV3" s="7" t="s">
         <v>96</v>
@@ -18247,7 +18279,7 @@
       </c>
       <c r="AU6" s="6" t="str">
         <f>_xlfn.XLOOKUP(AT6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>侻</v>
+        <v>侻??</v>
       </c>
       <c r="AV6" s="7" t="s">
         <v>309</v>
@@ -24296,7 +24328,7 @@
       </c>
       <c r="M18" s="6" t="str">
         <f>_xlfn.XLOOKUP(L18,対応表!$B:$B,対応表!$C:$C,"こ")</f>
-        <v>乳</v>
+        <v>乳??</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>1148</v>
@@ -26520,7 +26552,7 @@
       </c>
       <c r="BI22" s="6" t="str">
         <f>_xlfn.XLOOKUP(BH22,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>偗</v>
+        <v>偗??</v>
       </c>
       <c r="BJ22" s="17" t="s">
         <v>1456</v>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1561" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A26A8C0-B8D3-428E-AEAB-4D27C146359D}"/>
+  <xr:revisionPtr revIDLastSave="1575" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CFEFE41-361E-42AD-9D5C-7FB5FBFD0828}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="8205" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="2565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="2544">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -7749,31 +7749,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>亵刻</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>凾剑</t>
-  </si>
-  <si>
-    <t>匰儽</t>
-  </si>
-  <si>
-    <t>主別丟</t>
-  </si>
-  <si>
-    <t>勢丣</t>
-  </si>
-  <si>
-    <t>俚介</t>
-  </si>
-  <si>
-    <t>僌侫乏乐</t>
-  </si>
-  <si>
-    <t>乄偄卋</t>
-  </si>
-  <si>
     <t>勻</t>
   </si>
   <si>
@@ -7819,10 +7794,6 @@
   </si>
   <si>
     <t>掟</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>凗凘三</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -8164,13 +8135,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>過♢</t>
-    <rPh sb="0" eb="1">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>守られていない</t>
     <rPh sb="0" eb="1">
       <t>マモ</t>
@@ -8449,9 +8413,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>水覗像/王？</t>
-  </si>
-  <si>
     <t>早いし上げ ・お早めに</t>
     <rPh sb="0" eb="1">
       <t>ハヤ</t>
@@ -8560,82 +8521,6 @@
   </si>
   <si>
     <t>常</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>お知らせ</t>
-    <rPh sb="1" eb="2">
-      <t>シ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>兆し？</t>
-    <rPh sb="0" eb="1">
-      <t>キザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>影捌け？</t>
-    <rPh sb="0" eb="1">
-      <t>カゲ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>丣個僇亵乐卜丸亡</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>噴水？</t>
-    <rPh sb="0" eb="2">
-      <t>フンスイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>つぐない</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>交流？</t>
-    <rPh sb="0" eb="2">
-      <t>コウリュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>常明像</t>
-    <rPh sb="0" eb="1">
-      <t>ツネ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>アキラ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ゾウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特別？</t>
-    <rPh sb="0" eb="2">
-      <t>トクベツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>准凇</t>
-  </si>
-  <si>
-    <t>隔離？</t>
-    <rPh sb="0" eb="2">
-      <t>カクリ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -11105,65 +10990,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>介??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>傎??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>俚??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>勀??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>倂??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>凘??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>佁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>?</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>完</t>
     <rPh sb="0" eb="1">
       <t>カン</t>
@@ -11221,30 +11047,6 @@
   </si>
   <si>
     <t>伭名像/王？</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>伭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>??</t>
-    </r>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>乳偗像/王？</t>
@@ -11326,14 +11128,134 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>乳??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>偗??</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
+    <t>介覗像/王？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[侻]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[俚]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[介]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[勀]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[倂]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[凘]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>佁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[傎]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>伭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]?</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[乳]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[偗]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>[</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -11351,14 +11273,20 @@
         <rFont val="游ゴシック"/>
         <family val="2"/>
         <charset val="128"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>??</t>
+      <t>?</t>
     </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>侻??</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11366,7 +11294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11595,6 +11523,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="7">
@@ -11840,9 +11775,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -11850,6 +11782,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11941,6 +11876,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12282,25 +12221,25 @@
         <v>1563</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>2065</v>
+        <v>2056</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>2050</v>
+        <v>2041</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>2051</v>
+        <v>2042</v>
       </c>
       <c r="G1" s="31" t="s">
-        <v>2052</v>
+        <v>2043</v>
       </c>
       <c r="H1" s="31" t="s">
-        <v>2053</v>
+        <v>2044</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>2054</v>
+        <v>2045</v>
       </c>
       <c r="J1" s="31" t="s">
-        <v>2055</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -13559,16 +13498,16 @@
         <v>1691</v>
       </c>
       <c r="D158" s="33" t="s">
-        <v>2059</v>
+        <v>2050</v>
       </c>
       <c r="E158" s="34" t="s">
-        <v>2109</v>
+        <v>2099</v>
       </c>
       <c r="F158" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="G158" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.4">
@@ -13584,7 +13523,7 @@
         <v>1693</v>
       </c>
       <c r="C160" t="s">
-        <v>2043</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.4">
@@ -13603,10 +13542,10 @@
         <v>1696</v>
       </c>
       <c r="D162" s="33" t="s">
-        <v>2107</v>
+        <v>2097</v>
       </c>
       <c r="E162" s="34" t="s">
-        <v>2560</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.4">
@@ -13617,10 +13556,10 @@
         <v>1698</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>2086</v>
+        <v>2077</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>2111</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.4">
@@ -13751,13 +13690,13 @@
         <v>1722</v>
       </c>
       <c r="D179" s="33" t="s">
-        <v>2078</v>
+        <v>2069</v>
       </c>
       <c r="E179" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="F179" s="32" t="s">
-        <v>2137</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.4">
@@ -13768,13 +13707,13 @@
         <v>1724</v>
       </c>
       <c r="D180" s="33" t="s">
-        <v>2068</v>
+        <v>2059</v>
       </c>
       <c r="E180" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>2137</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
@@ -13798,16 +13737,16 @@
         <v>1941</v>
       </c>
       <c r="C183" t="s">
-        <v>2159</v>
+        <v>2148</v>
       </c>
       <c r="D183" s="33" t="s">
-        <v>2158</v>
+        <v>2147</v>
       </c>
       <c r="E183" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.4">
@@ -13818,16 +13757,16 @@
         <v>1728</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2157</v>
+        <v>2146</v>
       </c>
       <c r="E184" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
@@ -13862,10 +13801,10 @@
         <v>1735</v>
       </c>
       <c r="D188" s="33" t="s">
-        <v>2071</v>
+        <v>2062</v>
       </c>
       <c r="E188" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.4">
@@ -13908,16 +13847,16 @@
         <v>1991</v>
       </c>
       <c r="D193" s="33" t="s">
-        <v>2066</v>
+        <v>2057</v>
       </c>
       <c r="E193" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="F193" s="32" t="s">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="G193" s="32" t="s">
-        <v>2136</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.4">
@@ -13928,16 +13867,16 @@
         <v>1744</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>2066</v>
+        <v>2057</v>
       </c>
       <c r="E194" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>2136</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.4">
@@ -13948,10 +13887,10 @@
         <v>1746</v>
       </c>
       <c r="D195" s="33" t="s">
-        <v>2102</v>
+        <v>2092</v>
       </c>
       <c r="E195" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="196" spans="2:7" x14ac:dyDescent="0.4">
@@ -13967,16 +13906,16 @@
         <v>1945</v>
       </c>
       <c r="C197" t="s">
-        <v>2163</v>
+        <v>2152</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>2153</v>
+        <v>2142</v>
       </c>
       <c r="E197" s="34" t="s">
-        <v>2133</v>
+        <v>2123</v>
       </c>
       <c r="F197" s="34" t="s">
-        <v>2141</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.4">
@@ -13984,7 +13923,7 @@
         <v>1749</v>
       </c>
       <c r="C198" t="s">
-        <v>2164</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.4">
@@ -13995,13 +13934,13 @@
         <v>1750</v>
       </c>
       <c r="D199" s="33" t="s">
-        <v>2103</v>
+        <v>2093</v>
       </c>
       <c r="E199" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
       <c r="F199" s="32" t="s">
-        <v>2134</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.4">
@@ -14052,16 +13991,16 @@
         <v>1760</v>
       </c>
       <c r="D205" s="33" t="s">
-        <v>2058</v>
+        <v>2049</v>
       </c>
       <c r="E205" s="34" t="s">
-        <v>2115</v>
+        <v>2105</v>
       </c>
       <c r="F205" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
       <c r="G205" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="206" spans="2:7" x14ac:dyDescent="0.4">
@@ -14088,10 +14027,10 @@
         <v>1764</v>
       </c>
       <c r="D208" s="33" t="s">
-        <v>2074</v>
+        <v>2065</v>
       </c>
       <c r="E208" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.4">
@@ -14126,13 +14065,13 @@
         <v>1770</v>
       </c>
       <c r="D212" s="33" t="s">
-        <v>2154</v>
+        <v>2143</v>
       </c>
       <c r="E212" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
       <c r="F212" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.4">
@@ -14167,10 +14106,10 @@
         <v>1775</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>2057</v>
+        <v>2048</v>
       </c>
       <c r="E216" s="34" t="s">
-        <v>2138</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
@@ -14197,10 +14136,10 @@
         <v>1780</v>
       </c>
       <c r="D219" s="33" t="s">
-        <v>2056</v>
+        <v>2047</v>
       </c>
       <c r="E219" s="34" t="s">
-        <v>2123</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.4">
@@ -14299,10 +14238,10 @@
         <v>1798</v>
       </c>
       <c r="D231" s="33" t="s">
-        <v>2083</v>
+        <v>2074</v>
       </c>
       <c r="E231" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.4">
@@ -14313,10 +14252,10 @@
         <v>1799</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>2085</v>
+        <v>2076</v>
       </c>
       <c r="E232" s="34" t="s">
-        <v>2124</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.4">
@@ -14359,10 +14298,10 @@
         <v>1807</v>
       </c>
       <c r="D237" s="33" t="s">
-        <v>2142</v>
+        <v>2132</v>
       </c>
       <c r="E237" s="34" t="s">
-        <v>2110</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.4">
@@ -14389,10 +14328,10 @@
         <v>1812</v>
       </c>
       <c r="D240" s="33" t="s">
-        <v>2060</v>
+        <v>2051</v>
       </c>
       <c r="E240" s="34" t="s">
-        <v>2109</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.4">
@@ -14403,10 +14342,10 @@
         <v>1813</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>2061</v>
+        <v>2052</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>2125</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.4">
@@ -14417,13 +14356,13 @@
         <v>1815</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>2088</v>
+        <v>2079</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>2126</v>
+        <v>2116</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>2133</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
@@ -14442,10 +14381,10 @@
         <v>1819</v>
       </c>
       <c r="D244" s="33" t="s">
-        <v>2089</v>
+        <v>2080</v>
       </c>
       <c r="E244" s="34" t="s">
-        <v>2127</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.4">
@@ -14456,10 +14395,10 @@
         <v>1820</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>2087</v>
+        <v>2078</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>2126</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.4">
@@ -14470,10 +14409,10 @@
         <v>1821</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>2070</v>
+        <v>2061</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.4">
@@ -14500,10 +14439,10 @@
         <v>1824</v>
       </c>
       <c r="D249" s="33" t="s">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="E249" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.4">
@@ -14511,13 +14450,13 @@
         <v>1962</v>
       </c>
       <c r="C250" t="s">
-        <v>2534</v>
+        <v>2512</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2535</v>
+        <v>2513</v>
       </c>
       <c r="E250" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
@@ -14544,10 +14483,10 @@
         <v>1829</v>
       </c>
       <c r="D253" s="33" t="s">
-        <v>2076</v>
+        <v>2067</v>
       </c>
       <c r="E253" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.4">
@@ -14582,10 +14521,10 @@
         <v>1836</v>
       </c>
       <c r="D257" s="33" t="s">
-        <v>2079</v>
+        <v>2070</v>
       </c>
       <c r="E257" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
@@ -14604,10 +14543,10 @@
         <v>1839</v>
       </c>
       <c r="D259" s="33" t="s">
-        <v>2081</v>
+        <v>2072</v>
       </c>
       <c r="E259" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
@@ -14618,13 +14557,13 @@
         <v>417</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
       <c r="E260" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2128</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
@@ -14635,10 +14574,10 @@
         <v>1842</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2073</v>
+        <v>2064</v>
       </c>
       <c r="E261" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
@@ -14649,10 +14588,10 @@
         <v>1844</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="E262" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
@@ -14695,10 +14634,10 @@
         <v>1853</v>
       </c>
       <c r="D267" s="33" t="s">
-        <v>2099</v>
+        <v>2089</v>
       </c>
       <c r="E267" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.4">
@@ -14781,10 +14720,10 @@
         <v>1871</v>
       </c>
       <c r="D277" s="33" t="s">
-        <v>2080</v>
+        <v>2071</v>
       </c>
       <c r="E277" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.4">
@@ -14795,10 +14734,10 @@
         <v>1873</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2062</v>
-      </c>
-      <c r="E278" s="43" t="s">
-        <v>2501</v>
+        <v>2053</v>
+      </c>
+      <c r="E278" s="42" t="s">
+        <v>2479</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.4">
@@ -14811,8 +14750,8 @@
       <c r="D279" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="E279" s="43" t="s">
-        <v>2501</v>
+      <c r="E279" s="42" t="s">
+        <v>2479</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.4">
@@ -14879,10 +14818,10 @@
         <v>1888</v>
       </c>
       <c r="D287" s="33" t="s">
-        <v>2084</v>
+        <v>2075</v>
       </c>
       <c r="E287" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.4">
@@ -14917,13 +14856,13 @@
         <v>1985</v>
       </c>
       <c r="D291" s="33" t="s">
-        <v>2072</v>
+        <v>2063</v>
       </c>
       <c r="E291" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2506</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
@@ -14931,16 +14870,16 @@
         <v>1970</v>
       </c>
       <c r="C292" t="s">
-        <v>2047</v>
+        <v>2038</v>
       </c>
       <c r="D292" s="33" t="s">
-        <v>2075</v>
+        <v>2066</v>
       </c>
       <c r="E292" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="F292" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
@@ -14948,16 +14887,16 @@
         <v>1971</v>
       </c>
       <c r="C293" t="s">
-        <v>2048</v>
+        <v>2039</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>2075</v>
+        <v>2066</v>
       </c>
       <c r="E293" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.4">
@@ -14965,7 +14904,7 @@
         <v>1972</v>
       </c>
       <c r="C294" t="s">
-        <v>2045</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
@@ -14976,7 +14915,7 @@
         <v>1975</v>
       </c>
       <c r="D295" s="33" t="s">
-        <v>2145</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.4">
@@ -14987,7 +14926,7 @@
         <v>1976</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2145</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
@@ -15006,10 +14945,10 @@
         <v>1978</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>2093</v>
+        <v>2084</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>2506</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
@@ -15020,10 +14959,10 @@
         <v>1980</v>
       </c>
       <c r="D299" s="33" t="s">
-        <v>2082</v>
+        <v>2073</v>
       </c>
       <c r="E299" s="34" t="s">
-        <v>2115</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.4">
@@ -15042,7 +14981,7 @@
         <v>2000</v>
       </c>
       <c r="D301" s="33" t="s">
-        <v>2144</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.4">
@@ -15053,10 +14992,10 @@
         <v>1984</v>
       </c>
       <c r="D302" s="33" t="s">
-        <v>2077</v>
+        <v>2068</v>
       </c>
       <c r="E302" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.4">
@@ -15067,10 +15006,10 @@
         <v>1989</v>
       </c>
       <c r="D303" s="33" t="s">
-        <v>2067</v>
+        <v>2058</v>
       </c>
       <c r="E303" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.4">
@@ -15081,10 +15020,10 @@
         <v>1988</v>
       </c>
       <c r="D304" s="33" t="s">
-        <v>2067</v>
+        <v>2058</v>
       </c>
       <c r="E304" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.4">
@@ -15095,10 +15034,10 @@
         <v>1994</v>
       </c>
       <c r="D305" s="33" t="s">
-        <v>2069</v>
+        <v>2060</v>
       </c>
       <c r="E305" s="34" t="s">
-        <v>2116</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.4">
@@ -15106,13 +15045,13 @@
         <v>936</v>
       </c>
       <c r="C306" t="s">
-        <v>2548</v>
+        <v>2519</v>
       </c>
       <c r="D306" s="33" t="s">
-        <v>2549</v>
+        <v>2520</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>2506</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
@@ -15123,13 +15062,13 @@
         <v>2002</v>
       </c>
       <c r="D307" s="33" t="s">
-        <v>2063</v>
+        <v>2054</v>
       </c>
       <c r="E307" s="34" t="s">
-        <v>2117</v>
+        <v>2107</v>
       </c>
       <c r="F307" s="32" t="s">
-        <v>2130</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.4">
@@ -15140,10 +15079,10 @@
         <v>2006</v>
       </c>
       <c r="D308" s="33" t="s">
-        <v>2064</v>
+        <v>2055</v>
       </c>
       <c r="E308" s="34" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.4">
@@ -15154,10 +15093,10 @@
         <v>2008</v>
       </c>
       <c r="D309" s="33" t="s">
-        <v>2104</v>
+        <v>2094</v>
       </c>
       <c r="E309" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.4">
@@ -15168,10 +15107,10 @@
         <v>2010</v>
       </c>
       <c r="D310" s="33" t="s">
-        <v>2105</v>
+        <v>2095</v>
       </c>
       <c r="E310" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.4">
@@ -15182,10 +15121,10 @@
         <v>2018</v>
       </c>
       <c r="D311" s="33" t="s">
-        <v>2092</v>
+        <v>2083</v>
       </c>
       <c r="E311" s="34" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.4">
@@ -15193,13 +15132,13 @@
         <v>2019</v>
       </c>
       <c r="C312" t="s">
-        <v>2176</v>
+        <v>2154</v>
       </c>
       <c r="D312" s="33" t="s">
-        <v>2178</v>
+        <v>2156</v>
       </c>
       <c r="E312" s="34" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.4">
@@ -15207,13 +15146,13 @@
         <v>2020</v>
       </c>
       <c r="C313" t="s">
-        <v>2177</v>
+        <v>2155</v>
       </c>
       <c r="D313" s="33" t="s">
-        <v>2178</v>
+        <v>2156</v>
       </c>
       <c r="E313" s="34" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.4">
@@ -15224,10 +15163,10 @@
         <v>2021</v>
       </c>
       <c r="D314" s="33" t="s">
-        <v>2090</v>
+        <v>2081</v>
       </c>
       <c r="E314" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
@@ -15238,10 +15177,10 @@
         <v>2024</v>
       </c>
       <c r="D315" s="33" t="s">
-        <v>2091</v>
+        <v>2082</v>
       </c>
       <c r="E315" s="34" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
@@ -15252,58 +15191,58 @@
         <v>2023</v>
       </c>
       <c r="D316" s="33" t="s">
-        <v>2091</v>
+        <v>2082</v>
       </c>
       <c r="E316" s="34" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B317" s="1" t="s">
-        <v>2036</v>
+        <v>2028</v>
       </c>
       <c r="C317" t="s">
-        <v>2037</v>
+        <v>2029</v>
       </c>
       <c r="D317" s="33" t="s">
-        <v>2095</v>
+        <v>2085</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
       <c r="F317" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B318" s="1" t="s">
-        <v>2038</v>
+        <v>2030</v>
       </c>
       <c r="C318" t="s">
-        <v>2039</v>
+        <v>2031</v>
       </c>
       <c r="D318" s="33" t="s">
-        <v>2096</v>
+        <v>2086</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B319" s="1" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C319" t="s">
         <v>2040</v>
       </c>
-      <c r="C319" t="s">
-        <v>2049</v>
-      </c>
       <c r="D319" s="33" t="s">
-        <v>2098</v>
+        <v>2088</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
       <c r="F319" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.4">
@@ -15311,27 +15250,27 @@
         <v>822</v>
       </c>
       <c r="C320" t="s">
-        <v>2044</v>
+        <v>2036</v>
       </c>
       <c r="D320" s="33" t="s">
-        <v>2143</v>
+        <v>2133</v>
       </c>
       <c r="E320" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B321" s="1" t="s">
-        <v>2041</v>
+        <v>2033</v>
       </c>
       <c r="C321" t="s">
-        <v>2042</v>
+        <v>2034</v>
       </c>
       <c r="D321" s="33" t="s">
-        <v>2097</v>
+        <v>2087</v>
       </c>
       <c r="E321" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.4">
@@ -15339,16 +15278,16 @@
         <v>1094</v>
       </c>
       <c r="C322" t="s">
-        <v>2541</v>
+        <v>2533</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
       <c r="F322" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.4">
@@ -15356,19 +15295,19 @@
         <v>296</v>
       </c>
       <c r="C323" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2156</v>
+        <v>2145</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
       <c r="F323" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>2152</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.4">
@@ -15376,16 +15315,16 @@
         <v>1997</v>
       </c>
       <c r="C324" t="s">
-        <v>2160</v>
+        <v>2149</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2162</v>
+        <v>2151</v>
       </c>
       <c r="E324" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="F324" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.4">
@@ -15393,16 +15332,16 @@
         <v>1998</v>
       </c>
       <c r="C325" t="s">
-        <v>2161</v>
+        <v>2150</v>
       </c>
       <c r="D325" s="33" t="s">
-        <v>2162</v>
+        <v>2151</v>
       </c>
       <c r="E325" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="F325" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.4">
@@ -15410,13 +15349,13 @@
         <v>2015</v>
       </c>
       <c r="C326" t="s">
-        <v>2542</v>
+        <v>2535</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>2497</v>
+        <v>2475</v>
       </c>
       <c r="E326" s="34" t="s">
-        <v>2113</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.4">
@@ -15424,16 +15363,16 @@
         <v>1996</v>
       </c>
       <c r="C327" t="s">
-        <v>2543</v>
+        <v>2536</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2496</v>
+        <v>2474</v>
       </c>
       <c r="E327" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2506</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.4">
@@ -15441,27 +15380,27 @@
         <v>407</v>
       </c>
       <c r="C328" t="s">
-        <v>2544</v>
+        <v>2537</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2498</v>
+        <v>2476</v>
       </c>
       <c r="E328" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B329" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C329" s="41" t="s">
-        <v>2545</v>
-      </c>
-      <c r="D329" s="42" t="s">
-        <v>2499</v>
-      </c>
-      <c r="E329" s="43" t="s">
-        <v>2501</v>
+      <c r="C329" s="44" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D329" s="41" t="s">
+        <v>2477</v>
+      </c>
+      <c r="E329" s="42" t="s">
+        <v>2479</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.4">
@@ -15469,27 +15408,27 @@
         <v>1103</v>
       </c>
       <c r="C330" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="D330" s="33" t="s">
-        <v>2500</v>
-      </c>
-      <c r="E330" s="43" t="s">
-        <v>2501</v>
+        <v>2478</v>
+      </c>
+      <c r="E330" s="42" t="s">
+        <v>2479</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B331" s="1" t="s">
-        <v>2550</v>
-      </c>
-      <c r="C331" s="41" t="s">
-        <v>2553</v>
-      </c>
-      <c r="D331" s="44" t="s">
-        <v>2551</v>
+        <v>2521</v>
+      </c>
+      <c r="C331" s="44" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D331" s="43" t="s">
+        <v>2522</v>
       </c>
       <c r="E331" s="34" t="s">
-        <v>2552</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.4">
@@ -15497,55 +15436,55 @@
         <v>1147</v>
       </c>
       <c r="C332" t="s">
-        <v>2561</v>
+        <v>2541</v>
       </c>
       <c r="D332" s="33" t="s">
-        <v>2554</v>
+        <v>2524</v>
       </c>
       <c r="E332" s="34" t="s">
-        <v>2554</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B333" s="1" t="s">
-        <v>2555</v>
+        <v>2525</v>
       </c>
       <c r="C333" t="s">
-        <v>2562</v>
+        <v>2542</v>
       </c>
       <c r="D333" s="33" t="s">
-        <v>2554</v>
+        <v>2524</v>
       </c>
       <c r="E333" s="34" t="s">
-        <v>2554</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B334" s="1" t="s">
-        <v>2556</v>
-      </c>
-      <c r="C334" s="41" t="s">
-        <v>2563</v>
-      </c>
-      <c r="D334" s="42" t="s">
-        <v>2558</v>
+        <v>2526</v>
+      </c>
+      <c r="C334" s="44" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D334" s="41" t="s">
+        <v>2528</v>
       </c>
       <c r="E334" s="34" t="s">
-        <v>2559</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
-        <v>2557</v>
+        <v>2527</v>
       </c>
       <c r="C335" t="s">
-        <v>2564</v>
-      </c>
-      <c r="D335" s="42" t="s">
-        <v>2558</v>
+        <v>2532</v>
+      </c>
+      <c r="D335" s="41" t="s">
+        <v>2528</v>
       </c>
       <c r="E335" s="34" t="s">
-        <v>2559</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.4">
@@ -15653,7 +15592,7 @@
     <hyperlink ref="F324" r:id="rId82" xr:uid="{FA1433D3-A125-4D91-8655-CE3041406BBF}"/>
     <hyperlink ref="F325" r:id="rId83" xr:uid="{E87B89B3-92DB-4654-B59A-DBB66B4F00DE}"/>
     <hyperlink ref="F184" r:id="rId84" xr:uid="{0CEED77C-AE3C-4AC3-BA83-9660F17E5B98}"/>
-    <hyperlink ref="G323" r:id="rId85" xr:uid="{F00D9D1B-26F7-488C-B91C-F8141BE4536E}"/>
+    <hyperlink ref="G323" r:id="rId85" display="水覗像/王？" xr:uid="{F00D9D1B-26F7-488C-B91C-F8141BE4536E}"/>
     <hyperlink ref="F292" r:id="rId86" xr:uid="{2B802E9B-5D25-4BD1-AA45-D2032BA9C78D}"/>
     <hyperlink ref="F293" r:id="rId87" xr:uid="{FE3EEB68-9021-4277-AAD9-27391243C61E}"/>
     <hyperlink ref="F183" r:id="rId88" xr:uid="{97AC6B31-C5D9-4148-8AE1-3A52BFB6EC05}"/>
@@ -16737,7 +16676,7 @@
       </c>
       <c r="AU3" s="6" t="str">
         <f>_xlfn.XLOOKUP(AT3,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>侸??</v>
+        <v>[侸]?</v>
       </c>
       <c r="AV3" s="7" t="s">
         <v>96</v>
@@ -17202,14 +17141,14 @@
       </c>
       <c r="AG4" s="6" t="str">
         <f>_xlfn.XLOOKUP(AF4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>伭??</v>
+        <v>[伭]?</v>
       </c>
       <c r="AH4" s="7" t="s">
         <v>160</v>
       </c>
       <c r="AI4" s="6" t="str">
         <f>_xlfn.XLOOKUP(AH4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>佁??</v>
+        <v>[佁]?</v>
       </c>
       <c r="AJ4" s="7" t="s">
         <v>161</v>
@@ -18195,7 +18134,7 @@
       </c>
       <c r="W6" s="6" t="str">
         <f>_xlfn.XLOOKUP(V6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>介??</v>
+        <v>[介]?</v>
       </c>
       <c r="X6" s="17" t="s">
         <v>297</v>
@@ -18279,7 +18218,7 @@
       </c>
       <c r="AU6" s="6" t="str">
         <f>_xlfn.XLOOKUP(AT6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>侻??</v>
+        <v>[侻]?</v>
       </c>
       <c r="AV6" s="7" t="s">
         <v>309</v>
@@ -18982,7 +18921,7 @@
       </c>
       <c r="CW7" s="6" t="str">
         <f>_xlfn.XLOOKUP(CV7,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>凘??</v>
+        <v>[凘]?</v>
       </c>
       <c r="CX7" s="7" t="s">
         <v>408</v>
@@ -23940,7 +23879,7 @@
       </c>
       <c r="AW17" s="6" t="str">
         <f>_xlfn.XLOOKUP(AV17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>俚??</v>
+        <v>[俚]?</v>
       </c>
       <c r="AX17" s="17" t="s">
         <v>1095</v>
@@ -23954,7 +23893,7 @@
       </c>
       <c r="BA17" s="6" t="str">
         <f>_xlfn.XLOOKUP(AZ17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>倂??</v>
+        <v>[倂]?</v>
       </c>
       <c r="BB17" s="7" t="s">
         <v>1097</v>
@@ -24003,7 +23942,7 @@
       </c>
       <c r="BO17" s="6" t="str">
         <f>_xlfn.XLOOKUP(BN17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>傎??</v>
+        <v>[傎]?</v>
       </c>
       <c r="BP17" s="7" t="s">
         <v>1104</v>
@@ -24328,7 +24267,7 @@
       </c>
       <c r="M18" s="6" t="str">
         <f>_xlfn.XLOOKUP(L18,対応表!$B:$B,対応表!$C:$C,"こ")</f>
-        <v>乳??</v>
+        <v>[乳]?</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>1148</v>
@@ -25227,7 +25166,7 @@
       </c>
       <c r="DS19" s="6" t="str">
         <f>_xlfn.XLOOKUP(DR19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>勀??</v>
+        <v>[勀]?</v>
       </c>
       <c r="DT19" s="7" t="s">
         <v>1273</v>
@@ -26552,7 +26491,7 @@
       </c>
       <c r="BI22" s="6" t="str">
         <f>_xlfn.XLOOKUP(BH22,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>偗??</v>
+        <v>[偗]?</v>
       </c>
       <c r="BJ22" s="17" t="s">
         <v>1456</v>
@@ -26926,7 +26865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A3841C-3E42-4AC2-9AD3-BA0FFE4A947C}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -26934,140 +26873,73 @@
     <col min="5" max="11" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
         <v>1898</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>1214</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="C12" s="29" t="s">
-        <v>2034</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="C13" s="28" t="s">
-        <v>2032</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="C14" s="28" t="s">
-        <v>2031</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>2167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="C16" s="28" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="C18" s="28" t="s">
-        <v>2033</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="C19" s="29" t="s">
-        <v>2046</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C20" s="1" t="s">
-        <v>2028</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C21" s="1" t="s">
-        <v>2029</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C22" s="1" t="s">
-        <v>2030</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C23" s="1" t="s">
-        <v>2035</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>2172</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="C24" s="1" t="s">
-        <v>2174</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>2175</v>
-      </c>
+    <row r="12" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="C12" s="29"/>
+    </row>
+    <row r="13" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="C13" s="28"/>
+    </row>
+    <row r="14" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="C14" s="28"/>
+    </row>
+    <row r="16" spans="1:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="C16" s="28"/>
+    </row>
+    <row r="18" spans="3:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="3:3" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="C19" s="29"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -27088,265 +26960,265 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B1" s="35" t="s">
-        <v>2149</v>
+        <v>2139</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>2151</v>
+        <v>2141</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>2377</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>2148</v>
+        <v>2138</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
-        <v>2270</v>
+        <v>2248</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>2271</v>
+        <v>2249</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>2272</v>
+        <v>2250</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
-        <v>2273</v>
+        <v>2251</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>2274</v>
+        <v>2252</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2275</v>
+        <v>2253</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
-        <v>2276</v>
+        <v>2254</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>2277</v>
+        <v>2255</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>2278</v>
+        <v>2256</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
-        <v>2279</v>
+        <v>2257</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>2280</v>
+        <v>2258</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>2281</v>
+        <v>2259</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
-        <v>2282</v>
+        <v>2260</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>2283</v>
+        <v>2261</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>2284</v>
+        <v>2262</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2285</v>
+        <v>2263</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>2077</v>
+        <v>2068</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2286</v>
+        <v>2264</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
-        <v>2287</v>
+        <v>2265</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>2288</v>
+        <v>2266</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>2289</v>
+        <v>2267</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2290</v>
+        <v>2268</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>2075</v>
+        <v>2066</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2291</v>
+        <v>2269</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
-        <v>2292</v>
+        <v>2270</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>2293</v>
+        <v>2271</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
-        <v>2295</v>
+        <v>2273</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2296</v>
+        <v>2274</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2379</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2297</v>
+        <v>2275</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>2080</v>
+        <v>2071</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
-        <v>2375</v>
+        <v>2353</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>2376</v>
+        <v>2354</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2448</v>
+        <v>2426</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2447</v>
+        <v>2425</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
-        <v>2449</v>
+        <v>2427</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>2450</v>
+        <v>2428</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2452</v>
+        <v>2430</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2451</v>
+        <v>2429</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="35" t="s">
-        <v>2106</v>
+        <v>2096</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2453</v>
+        <v>2431</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2294</v>
+        <v>2272</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2378</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
-        <v>2493</v>
+        <v>2471</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>2494</v>
+        <v>2472</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>2495</v>
+        <v>2473</v>
       </c>
     </row>
   </sheetData>
@@ -27367,378 +27239,378 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B1" s="31" t="s">
-        <v>2228</v>
+        <v>2206</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>2229</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
-        <v>2179</v>
+        <v>2157</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B3" s="31" t="s">
-        <v>2180</v>
+        <v>2158</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B4" s="31" t="s">
-        <v>2181</v>
+        <v>2159</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B5" s="31" t="s">
-        <v>2182</v>
+        <v>2160</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B6" s="31" t="s">
-        <v>2183</v>
+        <v>2161</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B7" s="31" t="s">
-        <v>2184</v>
+        <v>2162</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B8" s="31" t="s">
-        <v>2187</v>
+        <v>2165</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B9" s="31" t="s">
-        <v>2188</v>
+        <v>2166</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B10" s="31" t="s">
-        <v>2185</v>
+        <v>2163</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B11" s="31" t="s">
-        <v>2186</v>
+        <v>2164</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B12" s="31" t="s">
-        <v>2189</v>
+        <v>2167</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
-        <v>2190</v>
+        <v>2168</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B14" s="31" t="s">
-        <v>2191</v>
+        <v>2169</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B15" s="31" t="s">
-        <v>2192</v>
+        <v>2170</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B16" s="31" t="s">
-        <v>2193</v>
+        <v>2171</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="31" t="s">
-        <v>2194</v>
+        <v>2172</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="31" t="s">
-        <v>2195</v>
+        <v>2173</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="31" t="s">
-        <v>2196</v>
+        <v>2174</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="31" t="s">
-        <v>2197</v>
+        <v>2175</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="31" t="s">
-        <v>2198</v>
+        <v>2176</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="31" t="s">
-        <v>2199</v>
+        <v>2177</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="31" t="s">
-        <v>2247</v>
+        <v>2225</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="31" t="s">
-        <v>2248</v>
+        <v>2226</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>2139</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="31" t="s">
-        <v>2200</v>
+        <v>2178</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>2116</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="31" t="s">
-        <v>2201</v>
+        <v>2179</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>2116</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="31" t="s">
-        <v>2202</v>
+        <v>2180</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>2116</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="31" t="s">
-        <v>2203</v>
+        <v>2181</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>2116</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="31" t="s">
-        <v>2204</v>
+        <v>2182</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="31" t="s">
-        <v>2205</v>
+        <v>2183</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="31" t="s">
-        <v>2206</v>
+        <v>2184</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="31" t="s">
-        <v>2207</v>
+        <v>2185</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
-        <v>2208</v>
+        <v>2186</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
-        <v>2209</v>
+        <v>2187</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
-        <v>2210</v>
+        <v>2188</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
-        <v>2211</v>
+        <v>2189</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
-        <v>2212</v>
+        <v>2190</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
-        <v>2213</v>
+        <v>2191</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>2112</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
-        <v>2214</v>
+        <v>2192</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
-        <v>2215</v>
+        <v>2193</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
-        <v>2216</v>
+        <v>2194</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
-        <v>2217</v>
+        <v>2195</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
-        <v>2218</v>
+        <v>2196</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
-        <v>2230</v>
+        <v>2208</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
-        <v>2219</v>
+        <v>2197</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>2132</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
-        <v>2220</v>
+        <v>2198</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
-        <v>2221</v>
+        <v>2199</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.4">
@@ -27746,434 +27618,434 @@
         <v>1161</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
-        <v>2222</v>
+        <v>2200</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
-        <v>2223</v>
+        <v>2201</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
-        <v>2224</v>
+        <v>2202</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
-        <v>2225</v>
+        <v>2203</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
-        <v>2226</v>
+        <v>2204</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
-        <v>2227</v>
+        <v>2205</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B55" s="31" t="s">
-        <v>2231</v>
+        <v>2209</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
-        <v>2232</v>
+        <v>2210</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
-        <v>2233</v>
+        <v>2211</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
-        <v>2234</v>
+        <v>2212</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
-        <v>2235</v>
+        <v>2213</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
-        <v>2236</v>
+        <v>2214</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
-        <v>2237</v>
+        <v>2215</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
-        <v>2238</v>
+        <v>2216</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
-        <v>2239</v>
+        <v>2217</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
-        <v>2240</v>
+        <v>2218</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B65" s="31" t="s">
-        <v>2241</v>
+        <v>2219</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B66" s="31" t="s">
-        <v>2242</v>
+        <v>2220</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B67" s="31" t="s">
-        <v>2243</v>
+        <v>2221</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B68" s="31" t="s">
-        <v>2244</v>
+        <v>2222</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B69" s="31" t="s">
-        <v>2245</v>
+        <v>2223</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B70" s="31" t="s">
-        <v>2246</v>
+        <v>2224</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B71" s="31" t="s">
-        <v>2249</v>
+        <v>2227</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="31" t="s">
-        <v>2250</v>
+        <v>2228</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B73" s="31" t="s">
-        <v>2251</v>
+        <v>2229</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B74" s="31" t="s">
-        <v>2252</v>
+        <v>2230</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
-        <v>2253</v>
+        <v>2231</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
       <c r="D75" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
-        <v>2254</v>
+        <v>2232</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="31" t="s">
-        <v>2255</v>
+        <v>2233</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="31" t="s">
-        <v>2256</v>
+        <v>2234</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B79" s="31" t="s">
-        <v>2257</v>
+        <v>2235</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B80" s="31" t="s">
-        <v>2258</v>
+        <v>2236</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B81" s="31" t="s">
-        <v>2259</v>
+        <v>2237</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B82" s="31" t="s">
-        <v>2260</v>
+        <v>2238</v>
       </c>
       <c r="C82" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B83" s="31" t="s">
-        <v>2261</v>
+        <v>2239</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B84" s="31" t="s">
-        <v>2262</v>
+        <v>2240</v>
       </c>
       <c r="C84" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B85" s="31" t="s">
-        <v>2263</v>
+        <v>2241</v>
       </c>
       <c r="C85" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B86" s="31" t="s">
-        <v>2264</v>
+        <v>2242</v>
       </c>
       <c r="C86" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B87" s="31" t="s">
-        <v>2265</v>
+        <v>2243</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B88" s="31" t="s">
-        <v>2266</v>
+        <v>2244</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B89" s="31" t="s">
-        <v>2267</v>
+        <v>2245</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B90" s="31" t="s">
-        <v>2268</v>
+        <v>2246</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B91" s="31" t="s">
-        <v>2269</v>
+        <v>2247</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>2108</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B92" s="31" t="s">
-        <v>2298</v>
+        <v>2276</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>2299</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B93" s="31" t="s">
-        <v>2300</v>
+        <v>2278</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>2117</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2301</v>
+        <v>2279</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>2115</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B95" s="31" t="s">
-        <v>2302</v>
+        <v>2280</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>2304</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B96" s="31" t="s">
-        <v>2303</v>
+        <v>2281</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2304</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
-        <v>2315</v>
+        <v>2293</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>2304</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2305</v>
+        <v>2283</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="31" t="s">
-        <v>2306</v>
+        <v>2284</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="31" t="s">
-        <v>2307</v>
+        <v>2285</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="31" t="s">
-        <v>2308</v>
+        <v>2286</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
@@ -28181,1434 +28053,1434 @@
         <v>950</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>2309</v>
+        <v>2287</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="31" t="s">
-        <v>2310</v>
+        <v>2288</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B105" s="31" t="s">
-        <v>2311</v>
+        <v>2289</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="31" t="s">
-        <v>2312</v>
+        <v>2290</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="31" t="s">
-        <v>2313</v>
+        <v>2291</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
-        <v>2320</v>
+        <v>2298</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>2314</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2316</v>
+        <v>2294</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>2138</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="31" t="s">
-        <v>2317</v>
+        <v>2295</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>2138</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="31" t="s">
-        <v>2318</v>
+        <v>2296</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>2138</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="31" t="s">
-        <v>2319</v>
+        <v>2297</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>2138</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2321</v>
+        <v>2299</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="31" t="s">
-        <v>2322</v>
+        <v>2300</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="31" t="s">
-        <v>2323</v>
+        <v>2301</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="31" t="s">
-        <v>2324</v>
+        <v>2302</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="31" t="s">
-        <v>2325</v>
+        <v>2303</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="31" t="s">
-        <v>2326</v>
+        <v>2304</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>2118</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="31" t="s">
-        <v>2327</v>
+        <v>2305</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>2123</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="31" t="s">
-        <v>2328</v>
+        <v>2306</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>2123</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="31" t="s">
-        <v>2329</v>
+        <v>2307</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>2123</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="31" t="s">
-        <v>2330</v>
+        <v>2308</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2331</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
-        <v>2332</v>
+        <v>2310</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>2331</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="31" t="s">
-        <v>2333</v>
+        <v>2311</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2331</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="31" t="s">
-        <v>2334</v>
+        <v>2312</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="31" t="s">
-        <v>2335</v>
+        <v>2313</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="31" t="s">
-        <v>2336</v>
+        <v>2314</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="31" t="s">
-        <v>2337</v>
+        <v>2315</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B129" s="31" t="s">
-        <v>2338</v>
+        <v>2316</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B130" s="31" t="s">
-        <v>2339</v>
+        <v>2317</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B131" s="31" t="s">
-        <v>2340</v>
+        <v>2318</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B132" s="31" t="s">
-        <v>2341</v>
+        <v>2319</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2342</v>
+        <v>2320</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>2403</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
-        <v>2343</v>
+        <v>2321</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>2349</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B134" s="31" t="s">
-        <v>2344</v>
+        <v>2322</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2349</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B135" s="31" t="s">
-        <v>2345</v>
+        <v>2323</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>2349</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B136" s="31" t="s">
-        <v>2346</v>
+        <v>2324</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>2349</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B137" s="31" t="s">
-        <v>2347</v>
+        <v>2325</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>2349</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B138" s="31" t="s">
-        <v>2348</v>
+        <v>2326</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2349</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2350</v>
+        <v>2328</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2355</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B140" s="31" t="s">
-        <v>2351</v>
+        <v>2329</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>2355</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B141" s="31" t="s">
-        <v>2352</v>
+        <v>2330</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>2355</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B142" s="31" t="s">
-        <v>2353</v>
+        <v>2331</v>
       </c>
       <c r="C142" s="34" t="s">
-        <v>2355</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B143" s="31" t="s">
-        <v>2354</v>
+        <v>2332</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2355</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2356</v>
+        <v>2334</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>2359</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B145" s="31" t="s">
-        <v>2357</v>
+        <v>2335</v>
       </c>
       <c r="C145" s="34" t="s">
-        <v>2359</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B146" s="31" t="s">
-        <v>2358</v>
+        <v>2336</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2359</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2360</v>
+        <v>2338</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B148" s="31" t="s">
-        <v>2361</v>
+        <v>2339</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B149" s="31" t="s">
-        <v>2362</v>
+        <v>2340</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B150" s="31" t="s">
-        <v>2363</v>
+        <v>2341</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B151" s="31" t="s">
-        <v>2364</v>
+        <v>2342</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B152" s="31" t="s">
-        <v>2365</v>
+        <v>2343</v>
       </c>
       <c r="C152" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B153" s="31" t="s">
-        <v>2366</v>
+        <v>2344</v>
       </c>
       <c r="C153" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B154" s="31" t="s">
-        <v>2367</v>
+        <v>2345</v>
       </c>
       <c r="C154" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B155" s="31" t="s">
-        <v>2368</v>
+        <v>2346</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2369</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
-        <v>2370</v>
+        <v>2348</v>
       </c>
       <c r="C156" s="34" t="s">
-        <v>2374</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B157" s="31" t="s">
-        <v>2371</v>
+        <v>2349</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>2374</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B158" s="31" t="s">
-        <v>2372</v>
+        <v>2350</v>
       </c>
       <c r="C158" s="34" t="s">
-        <v>2374</v>
+        <v>2352</v>
       </c>
       <c r="D158" s="34" t="s">
-        <v>2419</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B159" s="31" t="s">
-        <v>2373</v>
+        <v>2351</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2374</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2380</v>
+        <v>2358</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
-        <v>2381</v>
+        <v>2359</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
-        <v>2382</v>
+        <v>2360</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
-        <v>2383</v>
+        <v>2361</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
-        <v>2384</v>
+        <v>2362</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
-        <v>2385</v>
+        <v>2363</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
-        <v>2386</v>
+        <v>2364</v>
       </c>
       <c r="C166" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
-        <v>2387</v>
+        <v>2365</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2388</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B168" s="31" t="s">
-        <v>2391</v>
+        <v>2369</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>2393</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
-        <v>2392</v>
+        <v>2370</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2393</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
-        <v>2389</v>
+        <v>2367</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>2393</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
-        <v>2390</v>
+        <v>2368</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>2393</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B172" s="31" t="s">
-        <v>2394</v>
+        <v>2372</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>2399</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
-        <v>2395</v>
+        <v>2373</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>2399</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
-        <v>2396</v>
+        <v>2374</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>2399</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
-        <v>2397</v>
+        <v>2375</v>
       </c>
       <c r="C175" s="34" t="s">
-        <v>2399</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
-        <v>2398</v>
+        <v>2376</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2399</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2400</v>
+        <v>2378</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2401</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
-        <v>2526</v>
+        <v>2504</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2527</v>
+        <v>2505</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2402</v>
+        <v>2380</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2403</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
-        <v>2404</v>
+        <v>2382</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>2403</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B182" s="31" t="s">
-        <v>2405</v>
+        <v>2383</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2403</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B183" s="31" t="s">
-        <v>2406</v>
+        <v>2384</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2403</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B184" s="31" t="s">
-        <v>2407</v>
+        <v>2385</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>2410</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B185" s="31" t="s">
-        <v>2408</v>
+        <v>2386</v>
       </c>
       <c r="C185" s="34" t="s">
-        <v>2410</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B186" s="31" t="s">
-        <v>2409</v>
+        <v>2387</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2410</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
-        <v>2411</v>
+        <v>2389</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>2415</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B188" s="31" t="s">
-        <v>2412</v>
+        <v>2390</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>2415</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B189" s="31" t="s">
-        <v>2413</v>
+        <v>2391</v>
       </c>
       <c r="C189" s="34" t="s">
-        <v>2415</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B190" s="31" t="s">
-        <v>2414</v>
+        <v>2392</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2415</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2416</v>
+        <v>2394</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>2419</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B192" s="31" t="s">
-        <v>2417</v>
+        <v>2395</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>2419</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B193" s="31" t="s">
-        <v>2418</v>
+        <v>2396</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2419</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
-        <v>2222</v>
+        <v>2200</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>2419</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
-        <v>2420</v>
+        <v>2398</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>2424</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B196" s="31" t="s">
-        <v>2421</v>
+        <v>2399</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>2424</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B197" s="31" t="s">
-        <v>2422</v>
+        <v>2400</v>
       </c>
       <c r="C197" s="34" t="s">
-        <v>2424</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B198" s="31" t="s">
-        <v>2423</v>
+        <v>2401</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2424</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2425</v>
+        <v>2403</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2430</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B200" s="31" t="s">
-        <v>2426</v>
+        <v>2404</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>2430</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B201" s="31" t="s">
-        <v>2427</v>
+        <v>2405</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>2430</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B202" s="31" t="s">
-        <v>2428</v>
+        <v>2406</v>
       </c>
       <c r="C202" s="34" t="s">
-        <v>2430</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B203" s="31" t="s">
-        <v>2429</v>
+        <v>2407</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2430</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2432</v>
+        <v>2410</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2437</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
-        <v>2431</v>
+        <v>2409</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>2437</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
-        <v>2433</v>
+        <v>2411</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>2437</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B207" s="31" t="s">
-        <v>2434</v>
+        <v>2412</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>2437</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B208" s="31" t="s">
-        <v>2435</v>
+        <v>2413</v>
       </c>
       <c r="C208" s="34" t="s">
-        <v>2437</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B209" s="31" t="s">
-        <v>2436</v>
+        <v>2414</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2437</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
-        <v>2438</v>
+        <v>2416</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>2442</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B211" s="31" t="s">
-        <v>2439</v>
+        <v>2417</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>2442</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B212" s="31" t="s">
-        <v>2440</v>
+        <v>2418</v>
       </c>
       <c r="C212" s="34" t="s">
-        <v>2442</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B213" s="31" t="s">
-        <v>2441</v>
+        <v>2419</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2442</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2443</v>
+        <v>2421</v>
       </c>
       <c r="C214" s="34" t="s">
-        <v>2446</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B215" s="31" t="s">
-        <v>2444</v>
+        <v>2422</v>
       </c>
       <c r="C215" s="34" t="s">
-        <v>2446</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B216" s="31" t="s">
-        <v>2445</v>
+        <v>2423</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2446</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2454</v>
+        <v>2432</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2457</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B218" s="31" t="s">
-        <v>2458</v>
+        <v>2436</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2457</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
-        <v>2455</v>
+        <v>2433</v>
       </c>
       <c r="C219" s="34" t="s">
-        <v>2457</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B220" s="31" t="s">
-        <v>2456</v>
+        <v>2434</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2457</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
-        <v>2459</v>
+        <v>2437</v>
       </c>
       <c r="C221" s="34" t="s">
-        <v>2460</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2461</v>
+        <v>2439</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2462</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2463</v>
-      </c>
-      <c r="C223" s="43" t="s">
-        <v>2501</v>
+        <v>2441</v>
+      </c>
+      <c r="C223" s="42" t="s">
+        <v>2479</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
-        <v>2464</v>
+        <v>2442</v>
       </c>
       <c r="C224" s="34" t="s">
-        <v>2467</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B225" s="31" t="s">
-        <v>2465</v>
+        <v>2443</v>
       </c>
       <c r="C225" s="34" t="s">
-        <v>2467</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B226" s="31" t="s">
-        <v>2466</v>
+        <v>2444</v>
       </c>
       <c r="C226" s="34" t="s">
-        <v>2467</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B227" s="31" t="s">
-        <v>2386</v>
+        <v>2364</v>
       </c>
       <c r="C227" s="34" t="s">
-        <v>2467</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B228" s="31" t="s">
-        <v>2468</v>
+        <v>2446</v>
       </c>
       <c r="C228" s="34" t="s">
-        <v>2471</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B229" s="31" t="s">
-        <v>2469</v>
+        <v>2447</v>
       </c>
       <c r="C229" s="34" t="s">
-        <v>2471</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B230" s="31" t="s">
-        <v>2470</v>
+        <v>2448</v>
       </c>
       <c r="C230" s="34" t="s">
-        <v>2471</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B231" s="31" t="s">
-        <v>2472</v>
+        <v>2450</v>
       </c>
       <c r="C231" s="34" t="s">
-        <v>2477</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B232" s="31" t="s">
-        <v>2473</v>
+        <v>2451</v>
       </c>
       <c r="C232" s="34" t="s">
-        <v>2477</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B233" s="31" t="s">
-        <v>2474</v>
+        <v>2452</v>
       </c>
       <c r="C233" s="34" t="s">
-        <v>2477</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B234" s="31" t="s">
-        <v>2475</v>
+        <v>2453</v>
       </c>
       <c r="C234" s="34" t="s">
-        <v>2477</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B235" s="31" t="s">
-        <v>2476</v>
+        <v>2454</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>2477</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B236" s="31" t="s">
-        <v>2478</v>
+        <v>2456</v>
       </c>
       <c r="C236" s="34" t="s">
-        <v>2479</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B237" s="31" t="s">
-        <v>2480</v>
+        <v>2458</v>
       </c>
       <c r="C237" s="34" t="s">
-        <v>2481</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B238" s="31" t="s">
-        <v>2482</v>
+        <v>2460</v>
       </c>
       <c r="C238" s="34" t="s">
-        <v>2483</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B239" s="31" t="s">
-        <v>2484</v>
+        <v>2462</v>
       </c>
       <c r="C239" s="34" t="s">
-        <v>2489</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="240" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B240" s="31" t="s">
-        <v>2485</v>
+        <v>2463</v>
       </c>
       <c r="C240" s="34" t="s">
-        <v>2489</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B241" s="31" t="s">
-        <v>2486</v>
+        <v>2464</v>
       </c>
       <c r="C241" s="34" t="s">
-        <v>2489</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B242" s="31" t="s">
-        <v>2487</v>
+        <v>2465</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2489</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B243" s="31" t="s">
-        <v>2488</v>
+        <v>2466</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2489</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2490</v>
+        <v>2468</v>
       </c>
       <c r="C244" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
-        <v>2491</v>
+        <v>2469</v>
       </c>
       <c r="C245" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B246" s="31" t="s">
-        <v>2492</v>
+        <v>2470</v>
       </c>
       <c r="C246" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
-        <v>2502</v>
+        <v>2480</v>
       </c>
       <c r="C247" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2503</v>
+        <v>2481</v>
       </c>
       <c r="C248" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2504</v>
+        <v>2482</v>
       </c>
       <c r="C249" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2505</v>
+        <v>2483</v>
       </c>
       <c r="C250" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2507</v>
+        <v>2485</v>
       </c>
       <c r="C251" s="34" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2508</v>
+        <v>2486</v>
       </c>
       <c r="C252" s="32" t="s">
-        <v>2130</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2509</v>
+        <v>2487</v>
       </c>
       <c r="C253" s="32" t="s">
-        <v>2130</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2510</v>
+        <v>2488</v>
       </c>
       <c r="C254" s="32" t="s">
-        <v>2130</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2511</v>
+        <v>2489</v>
       </c>
       <c r="C255" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2512</v>
+        <v>2490</v>
       </c>
       <c r="C256" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2513</v>
+        <v>2491</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
-        <v>2514</v>
+        <v>2492</v>
       </c>
       <c r="C258" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
-        <v>2515</v>
+        <v>2493</v>
       </c>
       <c r="C259" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2516</v>
+        <v>2494</v>
       </c>
       <c r="C260" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
-        <v>2517</v>
+        <v>2495</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
-        <v>2360</v>
+        <v>2338</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2518</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
-        <v>2519</v>
+        <v>2497</v>
       </c>
       <c r="C263" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2520</v>
+        <v>2498</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
-        <v>2521</v>
+        <v>2499</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2522</v>
+        <v>2500</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2523</v>
+        <v>2501</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
-        <v>2269</v>
+        <v>2247</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2524</v>
+        <v>2502</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2525</v>
+        <v>2503</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2528</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
-        <v>2529</v>
+        <v>2507</v>
       </c>
       <c r="C271" s="32" t="s">
-        <v>2506</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2232</v>
+        <v>2210</v>
       </c>
       <c r="C272" s="32" t="s">
-        <v>2506</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
-        <v>2530</v>
+        <v>2508</v>
       </c>
       <c r="C273" s="32" t="s">
-        <v>2506</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2531</v>
+        <v>2509</v>
       </c>
       <c r="C274" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2532</v>
+        <v>2510</v>
       </c>
       <c r="C275" s="34" t="s">
-        <v>2533</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
-        <v>2536</v>
+        <v>2514</v>
       </c>
       <c r="C276" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2537</v>
+        <v>2515</v>
       </c>
       <c r="C277" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2538</v>
+        <v>2516</v>
       </c>
       <c r="C278" s="32" t="s">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2546</v>
+        <v>2517</v>
       </c>
       <c r="C279" s="34" t="s">
-        <v>2296</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="280" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B280" s="31" t="s">
-        <v>2547</v>
+        <v>2518</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1575" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CFEFE41-361E-42AD-9D5C-7FB5FBFD0828}"/>
+  <xr:revisionPtr revIDLastSave="1576" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9112B406-113A-4DBE-B06E-9D81DDA76BFC}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="8205" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -11004,13 +11004,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>亘??</t>
-    <rPh sb="0" eb="1">
-      <t>ワタリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>亘が満たされた</t>
     <rPh sb="2" eb="3">
       <t>ミ</t>
@@ -11287,6 +11280,13 @@
       </rPr>
       <t>?</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[亘]?</t>
+    <rPh sb="1" eb="2">
+      <t>ワタリ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11651,7 +11651,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11784,9 +11784,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -11876,10 +11873,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13545,7 +13538,7 @@
         <v>2097</v>
       </c>
       <c r="E162" s="34" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.4">
@@ -15045,10 +15038,10 @@
         <v>936</v>
       </c>
       <c r="C306" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D306" s="33" t="s">
         <v>2519</v>
-      </c>
-      <c r="D306" s="33" t="s">
-        <v>2520</v>
       </c>
       <c r="E306" s="32" t="s">
         <v>2484</v>
@@ -15278,7 +15271,7 @@
         <v>1094</v>
       </c>
       <c r="C322" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="D322" s="33" t="s">
         <v>2130</v>
@@ -15295,7 +15288,7 @@
         <v>296</v>
       </c>
       <c r="C323" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="D323" s="33" t="s">
         <v>2145</v>
@@ -15307,7 +15300,7 @@
         <v>2104</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.4">
@@ -15349,7 +15342,7 @@
         <v>2015</v>
       </c>
       <c r="C326" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="D326" s="33" t="s">
         <v>2475</v>
@@ -15363,7 +15356,7 @@
         <v>1996</v>
       </c>
       <c r="C327" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="D327" s="33" t="s">
         <v>2474</v>
@@ -15380,7 +15373,7 @@
         <v>407</v>
       </c>
       <c r="C328" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="D328" s="33" t="s">
         <v>2476</v>
@@ -15393,8 +15386,8 @@
       <c r="B329" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C329" s="44" t="s">
-        <v>2538</v>
+      <c r="C329" t="s">
+        <v>2537</v>
       </c>
       <c r="D329" s="41" t="s">
         <v>2477</v>
@@ -15408,7 +15401,7 @@
         <v>1103</v>
       </c>
       <c r="C330" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="D330" s="33" t="s">
         <v>2478</v>
@@ -15419,16 +15412,16 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B331" s="1" t="s">
+        <v>2520</v>
+      </c>
+      <c r="C331" t="s">
+        <v>2539</v>
+      </c>
+      <c r="D331" s="43" t="s">
         <v>2521</v>
       </c>
-      <c r="C331" s="44" t="s">
-        <v>2540</v>
-      </c>
-      <c r="D331" s="43" t="s">
+      <c r="E331" s="34" t="s">
         <v>2522</v>
-      </c>
-      <c r="E331" s="34" t="s">
-        <v>2523</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.4">
@@ -15436,55 +15429,55 @@
         <v>1147</v>
       </c>
       <c r="C332" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="D332" s="33" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="E332" s="34" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B333" s="1" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C333" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="D333" s="33" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="E333" s="34" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B334" s="1" t="s">
-        <v>2526</v>
-      </c>
-      <c r="C334" s="44" t="s">
-        <v>2543</v>
+        <v>2525</v>
+      </c>
+      <c r="C334" t="s">
+        <v>2542</v>
       </c>
       <c r="D334" s="41" t="s">
+        <v>2527</v>
+      </c>
+      <c r="E334" s="34" t="s">
         <v>2528</v>
-      </c>
-      <c r="E334" s="34" t="s">
-        <v>2529</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
+        <v>2526</v>
+      </c>
+      <c r="C335" t="s">
+        <v>2531</v>
+      </c>
+      <c r="D335" s="41" t="s">
         <v>2527</v>
       </c>
-      <c r="C335" t="s">
-        <v>2532</v>
-      </c>
-      <c r="D335" s="41" t="s">
+      <c r="E335" s="34" t="s">
         <v>2528</v>
-      </c>
-      <c r="E335" s="34" t="s">
-        <v>2529</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.4">
@@ -22739,7 +22732,7 @@
       </c>
       <c r="Q15" s="6" t="str">
         <f>_xlfn.XLOOKUP(P15,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>亘??</v>
+        <v>[亘]?</v>
       </c>
       <c r="R15" s="7" t="s">
         <v>937</v>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1576" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9112B406-113A-4DBE-B06E-9D81DDA76BFC}"/>
+  <xr:revisionPtr revIDLastSave="1704" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA2B493A-716F-467C-900A-BA21F06ECF50}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="2544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3020" uniqueCount="2591">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -6035,9 +6035,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ァ</t>
-  </si>
-  <si>
     <t>ア</t>
   </si>
   <si>
@@ -6944,9 +6941,6 @@
     <t>導?</t>
   </si>
   <si>
-    <t>音?</t>
-  </si>
-  <si>
     <t>剃</t>
   </si>
   <si>
@@ -7053,9 +7047,6 @@
   </si>
   <si>
     <t>記</t>
-  </si>
-  <si>
-    <t>集?</t>
   </si>
   <si>
     <t>减</t>
@@ -7849,13 +7840,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>お急ぎ</t>
-    <rPh sb="1" eb="2">
-      <t>イソ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>親しまれて</t>
     <rPh sb="0" eb="1">
       <t>シタ</t>
@@ -8015,23 +7999,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>集めた</t>
-    <rPh sb="0" eb="1">
-      <t>アツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>再へん</t>
     <rPh sb="0" eb="1">
       <t>サイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>対おう</t>
-    <rPh sb="0" eb="1">
-      <t>タイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8060,20 +8030,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>りずむと音</t>
-    <rPh sb="4" eb="5">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>はば広い</t>
-    <rPh sb="2" eb="3">
-      <t>ヒロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>お求めやすい</t>
     <rPh sb="1" eb="2">
       <t>モト</t>
@@ -8095,16 +8051,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>影捌けの舞</t>
-    <rPh sb="0" eb="1">
-      <t>カゲ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>斬首などのつぐない</t>
     <rPh sb="0" eb="2">
       <t>ザンシュ</t>
@@ -8291,9 +8237,6 @@
     <t>くすり屋</t>
   </si>
   <si>
-    <t>無影言本祭</t>
-  </si>
-  <si>
     <t>無影言本祭のお知らせ</t>
   </si>
   <si>
@@ -8881,10 +8824,6 @@
     <rPh sb="0" eb="2">
       <t>カンジ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>URL</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -11289,12 +11228,470 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>いべんと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>ない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>😭</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丣亞乇偄</t>
+  </si>
+  <si>
+    <t>しょく明</t>
+    <rPh sb="3" eb="4">
+      <t>アカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>独特な言い回しだよね</t>
+    <rPh sb="0" eb="2">
+      <t>ドクトク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丅刄</t>
+  </si>
+  <si>
+    <t>記録</t>
+    <rPh sb="0" eb="2">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去のデータとか、でてきたり</t>
+    <rPh sb="0" eb="2">
+      <t>カコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丣伖乱刋丄劏侕儌</t>
+  </si>
+  <si>
+    <t>しゅう年きねん祭</t>
+  </si>
+  <si>
+    <t>乢伥僌丣佳</t>
+  </si>
+  <si>
+    <t>もよおし事</t>
+  </si>
+  <si>
+    <t>亝东侕代佃</t>
+  </si>
+  <si>
+    <t>ちあんい持</t>
+    <rPh sb="4" eb="5">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乇丆丝儵/乇丆丝举</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くすり屋/くすりや</t>
+    <rPh sb="3" eb="4">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一覧と詳細で表記が違う</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>チガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>代刬侕乛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勧</t>
+    <rPh sb="0" eb="1">
+      <t>ススム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誘</t>
+    <rPh sb="0" eb="1">
+      <t>ユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無影言本祭について</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主別丟三乌代</t>
+  </si>
+  <si>
+    <t>影捌(?)けのまい</t>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>东侕劏代</t>
+  </si>
+  <si>
+    <t>あんねい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>什儹</t>
+  </si>
+  <si>
+    <t>地上</t>
+    <rPh sb="0" eb="2">
+      <t>チジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あるべき姿的なのがあったりしないかな</t>
+    <rPh sb="4" eb="5">
+      <t>スガタ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>万侕伸侕</t>
+  </si>
+  <si>
+    <t>はんてん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亘</t>
+  </si>
+  <si>
+    <t>満たされたもの</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>减倏</t>
+  </si>
+  <si>
+    <t>閉店</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>多分調べた</t>
+    <rPh sb="0" eb="3">
+      <t>タブンシラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勀假</t>
+  </si>
+  <si>
+    <t>弔われる者</t>
+    <rPh sb="0" eb="1">
+      <t>トムラ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>且亞乱代侕</t>
+  </si>
+  <si>
+    <t>びょういん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倍</t>
+  </si>
+  <si>
+    <t>良</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たいちょう不良</t>
+    <rPh sb="5" eb="7">
+      <t>フリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お急ぎ ・急なやまい</t>
+    <rPh sb="1" eb="2">
+      <t>イソ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対おう ・対しょ</t>
+    <rPh sb="0" eb="1">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第1区</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はば広い ・広場</t>
+    <rPh sb="2" eb="3">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒロバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集かい所</t>
+    <rPh sb="0" eb="1">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集めた ・集かい所</t>
+    <rPh sb="0" eb="1">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>りずむと音 ・音楽ずき</t>
+    <rPh sb="4" eb="5">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オンガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第4区</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第5区</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>侱</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]?</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>捌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>影捌けの舞 ・捌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所？</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11531,6 +11928,38 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Underground"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -11651,7 +12080,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -11782,6 +12211,42 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -12192,7 +12657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:J336"/>
+  <dimension ref="A1:J339"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -12203,41 +12668,41 @@
     <col min="8" max="10" width="9" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:10" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="50" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>1562</v>
       </c>
-      <c r="C1" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>2056</v>
-      </c>
-      <c r="E1" s="33" t="s">
+      <c r="D1" s="52" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>2038</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H1" s="53" t="s">
         <v>2041</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="I1" s="53" t="s">
         <v>2042</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="J1" s="53" t="s">
         <v>2043</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>2044</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>2045</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>2046</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
-        <v>1496</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -12245,7 +12710,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -12253,7 +12718,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -12261,7 +12726,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -12269,7 +12734,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -12277,7 +12742,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B7" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -12285,7 +12750,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -12293,7 +12758,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -12301,7 +12766,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B10" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -12309,7 +12774,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B11" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -12317,7 +12782,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B12" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -12325,7 +12790,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C13">
         <v>11</v>
@@ -12333,7 +12798,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -12341,7 +12806,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -12349,7 +12814,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -12357,7 +12822,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C17">
         <v>15</v>
@@ -12365,7 +12830,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -12373,7 +12838,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C19">
         <v>17</v>
@@ -12381,7 +12846,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C20">
         <v>18</v>
@@ -12389,7 +12854,7 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C21">
         <v>19</v>
@@ -12397,7 +12862,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -12405,7 +12870,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C23">
         <v>21</v>
@@ -12413,7 +12878,7 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C24">
         <v>22</v>
@@ -12421,7 +12886,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C25">
         <v>23</v>
@@ -12429,7 +12894,7 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C26">
         <v>24</v>
@@ -12437,7 +12902,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C27">
         <v>25</v>
@@ -12445,7 +12910,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C28">
         <v>26</v>
@@ -12453,7 +12918,7 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C29">
         <v>27</v>
@@ -12461,7 +12926,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C30">
         <v>28</v>
@@ -12469,7 +12934,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="C31">
         <v>29</v>
@@ -12477,7 +12942,7 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C32">
         <v>30</v>
@@ -12485,7 +12950,7 @@
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B33" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C33">
         <v>31</v>
@@ -12493,7 +12958,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B34" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C34">
         <v>32</v>
@@ -12501,7 +12966,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C35">
         <v>33</v>
@@ -12509,7 +12974,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C36">
         <v>34</v>
@@ -12517,7 +12982,7 @@
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -12525,7 +12990,7 @@
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B38" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C38">
         <v>36</v>
@@ -12533,7 +12998,7 @@
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C39">
         <v>37</v>
@@ -12541,7 +13006,7 @@
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C40">
         <v>38</v>
@@ -12549,7 +13014,7 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B41" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C41">
         <v>39</v>
@@ -12557,7 +13022,7 @@
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B42" s="1" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C42">
         <v>40</v>
@@ -12565,7 +13030,7 @@
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C43">
         <v>41</v>
@@ -12573,7 +13038,7 @@
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B44" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C44">
         <v>42</v>
@@ -12581,7 +13046,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="1" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="C45">
         <v>43</v>
@@ -12589,7 +13054,7 @@
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B46" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C46">
         <v>44</v>
@@ -12597,7 +13062,7 @@
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B47" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="C47">
         <v>45</v>
@@ -12605,7 +13070,7 @@
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B48" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C48">
         <v>46</v>
@@ -12613,7 +13078,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B49" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C49">
         <v>47</v>
@@ -12621,7 +13086,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B50" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C50">
         <v>48</v>
@@ -12629,7 +13094,7 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B51" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C51">
         <v>49</v>
@@ -12637,7 +13102,7 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B52" s="1" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C52">
         <v>50</v>
@@ -12645,7 +13110,7 @@
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B53" s="1" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C53">
         <v>51</v>
@@ -12653,7 +13118,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B54" s="1" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C54">
         <v>52</v>
@@ -12661,7 +13126,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B55" s="1" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C55">
         <v>53</v>
@@ -12669,7 +13134,7 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B56" s="1" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="C56">
         <v>54</v>
@@ -12677,7 +13142,7 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B57" s="1" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C57">
         <v>55</v>
@@ -12685,7 +13150,7 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B58" s="1" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="C58">
         <v>56</v>
@@ -12693,7 +13158,7 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B59" s="1" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="C59">
         <v>57</v>
@@ -12701,7 +13166,7 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B60" s="1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C60">
         <v>58</v>
@@ -12709,7 +13174,7 @@
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B61" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="C61">
         <v>59</v>
@@ -12717,7 +13182,7 @@
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B62" s="1" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="C62">
         <v>60</v>
@@ -12725,7 +13190,7 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B63" s="1" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="C63">
         <v>61</v>
@@ -12733,7 +13198,7 @@
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B64" s="1" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="C64">
         <v>62</v>
@@ -12741,7 +13206,7 @@
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B65" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="C65">
         <v>63</v>
@@ -12749,7 +13214,7 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B66" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="C66">
         <v>64</v>
@@ -12757,7 +13222,7 @@
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B67" s="1" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C67">
         <v>65</v>
@@ -12765,7 +13230,7 @@
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B68" s="1" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C68">
         <v>66</v>
@@ -12773,7 +13238,7 @@
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B69" s="1" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="C69">
         <v>67</v>
@@ -12781,7 +13246,7 @@
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B70" s="1" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="C70">
         <v>68</v>
@@ -12797,74 +13262,74 @@
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B72" s="1" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
       <c r="C72" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B73" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C73" t="s">
         <v>1565</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1566</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B74" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C74" t="s">
         <v>1567</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B75" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C75" t="s">
         <v>1569</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B76" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C76" t="s">
         <v>1571</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B77" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C77" t="s">
         <v>1573</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B78" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C78" t="s">
         <v>1575</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1576</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B79" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C79" t="s">
         <v>1577</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1578</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B80" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C80" t="s">
         <v>1579</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
@@ -12872,44 +13337,44 @@
         <v>72</v>
       </c>
       <c r="C81" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B82" s="1" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
       <c r="C82" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B83" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C83" t="s">
         <v>1583</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B84" s="1" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
       <c r="C84" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B85" s="1" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="C85" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B86" s="1" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
       <c r="C86" t="s">
         <v>864</v>
@@ -12920,36 +13385,36 @@
         <v>216</v>
       </c>
       <c r="C87" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B88" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C88" t="s">
         <v>1588</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B89" s="1" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="C89" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B90" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C90" t="s">
         <v>1591</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B91" s="1" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="C91" t="s">
         <v>718</v>
@@ -12957,34 +13422,34 @@
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B92" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C92" t="s">
         <v>1593</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B93" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C93" t="s">
         <v>1595</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B94" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C94" t="s">
         <v>1597</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B95" s="1" t="s">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="C95" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.4">
@@ -12992,28 +13457,28 @@
         <v>713</v>
       </c>
       <c r="C96" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C97" t="s">
         <v>1601</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C98" t="s">
         <v>1603</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="1" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
       <c r="C99" t="s">
         <v>723</v>
@@ -13021,42 +13486,42 @@
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C100" t="s">
         <v>1605</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="1" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
       <c r="C101" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B102" s="1" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="C102" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C103" t="s">
         <v>1609</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="1" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
       <c r="C104" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
@@ -13064,87 +13529,87 @@
         <v>287</v>
       </c>
       <c r="C105" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C106" t="s">
         <v>1613</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="1" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
       <c r="C107" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="1" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="C108" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="1" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
       <c r="C109" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C110" t="s">
         <v>1618</v>
-      </c>
-      <c r="C110" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="1" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
       <c r="C111" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C112" t="s">
         <v>1621</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="1" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="C113" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="1" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="C114" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="1" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="C115" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
@@ -13152,116 +13617,116 @@
         <v>504</v>
       </c>
       <c r="C116" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="1" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="C117" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C118" t="s">
         <v>1628</v>
-      </c>
-      <c r="C118" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="1" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="C119" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C120" t="s">
         <v>1631</v>
-      </c>
-      <c r="C120" t="s">
-        <v>1632</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="1" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="C121" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="1" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="C122" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="1" t="s">
-        <v>1923</v>
+        <v>1920</v>
       </c>
       <c r="C123" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="1" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="C124" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C125" t="s">
         <v>1637</v>
-      </c>
-      <c r="C125" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C126" t="s">
         <v>1639</v>
-      </c>
-      <c r="C126" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C127" t="s">
         <v>1641</v>
-      </c>
-      <c r="C127" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="1" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="C128" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B129" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C129" t="s">
         <v>1644</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B130" s="1" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="C130" t="s">
         <v>81</v>
@@ -13269,10 +13734,10 @@
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B131" s="1" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="C131" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.4">
@@ -13280,180 +13745,180 @@
         <v>73</v>
       </c>
       <c r="C132" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B133" s="1" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="C133" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B134" s="1" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="C134" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B135" s="1" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="C135" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B136" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C136" t="s">
         <v>1652</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1653</v>
       </c>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B137" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C137" t="s">
         <v>1654</v>
-      </c>
-      <c r="C137" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="138" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B138" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C138" t="s">
         <v>1656</v>
-      </c>
-      <c r="C138" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="139" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B139" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C139" t="s">
         <v>1658</v>
-      </c>
-      <c r="C139" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B140" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C140" t="s">
         <v>1660</v>
-      </c>
-      <c r="C140" t="s">
-        <v>1661</v>
       </c>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B141" s="1" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="C141" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="142" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B142" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C142" t="s">
         <v>1663</v>
-      </c>
-      <c r="C142" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="143" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B143" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C143" t="s">
         <v>1665</v>
-      </c>
-      <c r="C143" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="144" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B144" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C144" t="s">
         <v>1667</v>
-      </c>
-      <c r="C144" t="s">
-        <v>1668</v>
       </c>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B145" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C145" t="s">
         <v>1669</v>
-      </c>
-      <c r="C145" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B146" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C146" t="s">
         <v>1671</v>
-      </c>
-      <c r="C146" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B147" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C147" t="s">
         <v>1673</v>
-      </c>
-      <c r="C147" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B148" s="1" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="C148" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B149" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C149" t="s">
         <v>1676</v>
-      </c>
-      <c r="C149" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B150" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C150" t="s">
         <v>1678</v>
-      </c>
-      <c r="C150" t="s">
-        <v>1679</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B151" s="1" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="C151" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B152" s="1" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="C152" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B153" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C153" t="s">
         <v>1682</v>
-      </c>
-      <c r="C153" t="s">
-        <v>1683</v>
       </c>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B154" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="C154" t="s">
         <v>1434</v>
@@ -13461,555 +13926,558 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B155" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C155" t="s">
         <v>1685</v>
-      </c>
-      <c r="C155" t="s">
-        <v>1686</v>
       </c>
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B156" s="1" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="C156" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B157" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C157" t="s">
         <v>1688</v>
-      </c>
-      <c r="C157" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B158" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C158" t="s">
         <v>1690</v>
       </c>
-      <c r="C158" t="s">
-        <v>1691</v>
-      </c>
       <c r="D158" s="33" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="E158" s="34" t="s">
-        <v>2099</v>
+        <v>2090</v>
       </c>
       <c r="F158" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="G158" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B159" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="C159" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B160" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C160" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B161" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C161" t="s">
         <v>1693</v>
       </c>
-      <c r="C160" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B161" s="1" t="s">
-        <v>1935</v>
-      </c>
-      <c r="C161" t="s">
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B162" s="1" t="s">
         <v>1694</v>
       </c>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B162" s="1" t="s">
+      <c r="C162" t="s">
         <v>1695</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" s="33" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E162" s="34" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B163" s="1" t="s">
         <v>1696</v>
       </c>
-      <c r="D162" s="33" t="s">
-        <v>2097</v>
-      </c>
-      <c r="E162" s="34" t="s">
-        <v>2529</v>
-      </c>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B163" s="1" t="s">
+      <c r="C163" t="s">
         <v>1697</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" s="33" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E163" s="34" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F163" s="32" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B164" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C164" t="s">
         <v>1698</v>
       </c>
-      <c r="D163" s="33" t="s">
-        <v>2077</v>
-      </c>
-      <c r="E163" s="34" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B164" s="1" t="s">
-        <v>1936</v>
-      </c>
-      <c r="C164" t="s">
+    </row>
+    <row r="165" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B165" s="1" t="s">
         <v>1699</v>
       </c>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B165" s="1" t="s">
+      <c r="C165" t="s">
         <v>1700</v>
       </c>
-      <c r="C165" t="s">
+    </row>
+    <row r="166" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B166" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C166" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B166" s="1" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C166" t="s">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B167" s="1" t="s">
         <v>1702</v>
       </c>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B167" s="1" t="s">
+      <c r="C167" t="s">
         <v>1703</v>
       </c>
-      <c r="C167" t="s">
+    </row>
+    <row r="168" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B168" s="1" t="s">
         <v>1704</v>
       </c>
-    </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B168" s="1" t="s">
+      <c r="C168" t="s">
         <v>1705</v>
       </c>
-      <c r="C168" t="s">
+    </row>
+    <row r="169" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B169" s="1" t="s">
         <v>1706</v>
       </c>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B169" s="1" t="s">
+      <c r="C169" t="s">
         <v>1707</v>
       </c>
-      <c r="C169" t="s">
+    </row>
+    <row r="170" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B170" s="1" t="s">
         <v>1708</v>
       </c>
-    </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B170" s="1" t="s">
+      <c r="C170" t="s">
         <v>1709</v>
       </c>
-      <c r="C170" t="s">
+    </row>
+    <row r="171" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B171" s="1" t="s">
         <v>1710</v>
-      </c>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B171" s="1" t="s">
-        <v>1711</v>
       </c>
       <c r="C171" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B172" s="1" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="C172" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B173" s="1" t="s">
         <v>1712</v>
       </c>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B173" s="1" t="s">
+      <c r="C173" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="174" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B174" s="1" t="s">
         <v>1713</v>
       </c>
-      <c r="C173" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B174" s="1" t="s">
+      <c r="C174" t="s">
         <v>1714</v>
       </c>
-      <c r="C174" t="s">
+    </row>
+    <row r="175" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B175" s="1" t="s">
         <v>1715</v>
-      </c>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B175" s="1" t="s">
-        <v>1716</v>
       </c>
       <c r="C175" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="176" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B176" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="C176" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B177" s="1" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="C177" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B178" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C178" t="s">
         <v>1719</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="179" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B179" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C179" t="s">
         <v>1721</v>
       </c>
-      <c r="C179" t="s">
-        <v>1722</v>
-      </c>
       <c r="D179" s="33" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="E179" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="F179" s="32" t="s">
-        <v>2127</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B180" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C180" t="s">
         <v>1723</v>
       </c>
-      <c r="C180" t="s">
-        <v>1724</v>
-      </c>
       <c r="D180" s="33" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="E180" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>2127</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B181" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C181" t="s">
         <v>1725</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B182" s="1" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="C182" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B183" s="1" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="C183" t="s">
-        <v>2148</v>
+        <v>2138</v>
       </c>
       <c r="D183" s="33" t="s">
-        <v>2147</v>
+        <v>2137</v>
       </c>
       <c r="E183" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B184" s="1" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="C184" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2146</v>
+        <v>2136</v>
       </c>
       <c r="E184" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B185" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C185" t="s">
         <v>1729</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B186" s="1" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="C186" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B187" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C187" t="s">
         <v>1732</v>
-      </c>
-      <c r="C187" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="188" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B188" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C188" t="s">
         <v>1734</v>
       </c>
-      <c r="C188" t="s">
-        <v>1735</v>
-      </c>
       <c r="D188" s="33" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="E188" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B189" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C189" t="s">
         <v>1736</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1737</v>
       </c>
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B190" s="1" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C190" t="s">
         <v>1738</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B191" s="1" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="C191" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B192" s="1" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="C192" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="193" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B193" s="1" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="C193" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="D193" s="33" t="s">
-        <v>2057</v>
+        <v>2053</v>
       </c>
       <c r="E193" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="F193" s="32" t="s">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="G193" s="32" t="s">
-        <v>2126</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B194" s="1" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C194" t="s">
         <v>1743</v>
       </c>
-      <c r="C194" t="s">
-        <v>1744</v>
-      </c>
       <c r="D194" s="33" t="s">
-        <v>2057</v>
+        <v>2053</v>
       </c>
       <c r="E194" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>2126</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B195" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C195" t="s">
         <v>1745</v>
       </c>
-      <c r="C195" t="s">
-        <v>1746</v>
-      </c>
       <c r="D195" s="33" t="s">
-        <v>2092</v>
+        <v>2083</v>
       </c>
       <c r="E195" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="196" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B196" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C196" t="s">
         <v>1747</v>
-      </c>
-      <c r="C196" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="197" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B197" s="1" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
       <c r="C197" t="s">
-        <v>2152</v>
+        <v>2142</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>2142</v>
+        <v>2132</v>
       </c>
       <c r="E197" s="34" t="s">
-        <v>2123</v>
+        <v>2113</v>
       </c>
       <c r="F197" s="34" t="s">
-        <v>2131</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B198" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="C198" t="s">
-        <v>2153</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B199" s="1" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
       <c r="C199" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="D199" s="33" t="s">
-        <v>2093</v>
+        <v>2084</v>
       </c>
       <c r="E199" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
       <c r="F199" s="32" t="s">
-        <v>2124</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B200" s="1" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C200" t="s">
         <v>1751</v>
-      </c>
-      <c r="C200" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="201" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B201" s="1" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="C201" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="202" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B202" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C202" t="s">
         <v>1754</v>
-      </c>
-      <c r="C202" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B203" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C203" t="s">
         <v>1756</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B204" s="1" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C204" t="s">
         <v>1758</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="205" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B205" s="1" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
       <c r="C205" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="D205" s="33" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="E205" s="34" t="s">
-        <v>2105</v>
+        <v>2096</v>
       </c>
       <c r="F205" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
       <c r="G205" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="206" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B206" s="1" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="C206" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B207" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C207" t="s">
         <v>1762</v>
-      </c>
-      <c r="C207" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.4">
@@ -14017,21 +14485,21 @@
         <v>857</v>
       </c>
       <c r="C208" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="D208" s="33" t="s">
-        <v>2065</v>
+        <v>2061</v>
       </c>
       <c r="E208" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B209" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C209" t="s">
         <v>1765</v>
-      </c>
-      <c r="C209" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.4">
@@ -14039,56 +14507,56 @@
         <v>1071</v>
       </c>
       <c r="C210" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B211" s="1" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="C211" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B212" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C212" t="s">
         <v>1769</v>
       </c>
-      <c r="C212" t="s">
-        <v>1770</v>
-      </c>
       <c r="D212" s="33" t="s">
-        <v>2143</v>
+        <v>2133</v>
       </c>
       <c r="E212" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
       <c r="F212" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B213" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C213" t="s">
         <v>1771</v>
-      </c>
-      <c r="C213" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B214" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C214" t="s">
         <v>1773</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B215" s="1" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="C215" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.4">
@@ -14096,365 +14564,371 @@
         <v>1077</v>
       </c>
       <c r="C216" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>2048</v>
+        <v>2576</v>
       </c>
       <c r="E216" s="34" t="s">
-        <v>2128</v>
+        <v>2118</v>
+      </c>
+      <c r="F216" s="32" t="s">
+        <v>2571</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B217" s="1" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C217" t="s">
         <v>1776</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B218" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C218" t="s">
         <v>1778</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B219" s="1" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="C219" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="D219" s="33" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="E219" s="34" t="s">
-        <v>2113</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B220" s="1" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
       <c r="C220" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B221" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C221" t="s">
         <v>1782</v>
-      </c>
-      <c r="C221" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B222" s="1" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
       <c r="C222" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B223" s="1" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="C223" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B224" s="1" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C224" t="s">
         <v>1786</v>
       </c>
-      <c r="C224" t="s">
+    </row>
+    <row r="225" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B225" s="1" t="s">
         <v>1787</v>
       </c>
-    </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B225" s="1" t="s">
+      <c r="C225" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B226" s="1" t="s">
         <v>1788</v>
       </c>
-      <c r="C225" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B226" s="1" t="s">
+      <c r="C226" t="s">
         <v>1789</v>
       </c>
-      <c r="C226" t="s">
+    </row>
+    <row r="227" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B227" s="1" t="s">
         <v>1790</v>
       </c>
-    </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B227" s="1" t="s">
+      <c r="C227" t="s">
         <v>1791</v>
       </c>
-      <c r="C227" t="s">
+    </row>
+    <row r="228" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B228" s="1" t="s">
         <v>1792</v>
-      </c>
-    </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B228" s="1" t="s">
-        <v>1793</v>
       </c>
       <c r="C228" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="229" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B229" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C229" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B230" s="1" t="s">
         <v>1794</v>
       </c>
-      <c r="C229" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B230" s="1" t="s">
+      <c r="C230" t="s">
         <v>1795</v>
       </c>
-      <c r="C230" t="s">
+    </row>
+    <row r="231" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B231" s="1" t="s">
         <v>1796</v>
       </c>
-    </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B231" s="1" t="s">
+      <c r="C231" t="s">
         <v>1797</v>
       </c>
-      <c r="C231" t="s">
+      <c r="D231" s="33" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E231" s="34" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="232" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B232" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C232" t="s">
+        <v>2583</v>
+      </c>
+      <c r="D232" s="33" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E232" s="34" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F232" s="32" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="233" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B233" s="1" t="s">
         <v>1798</v>
       </c>
-      <c r="D231" s="33" t="s">
-        <v>2074</v>
-      </c>
-      <c r="E231" s="34" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B232" s="1" t="s">
-        <v>1955</v>
-      </c>
-      <c r="C232" t="s">
+      <c r="C233" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="234" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B234" s="1" t="s">
         <v>1799</v>
       </c>
-      <c r="D232" s="33" t="s">
-        <v>2076</v>
-      </c>
-      <c r="E232" s="34" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B233" s="1" t="s">
+      <c r="C234" t="s">
         <v>1800</v>
       </c>
-      <c r="C233" t="s">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B234" s="1" t="s">
+    </row>
+    <row r="235" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B235" s="1" t="s">
         <v>1801</v>
       </c>
-      <c r="C234" t="s">
+      <c r="C235" t="s">
         <v>1802</v>
       </c>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B235" s="1" t="s">
+    <row r="236" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B236" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C236" t="s">
         <v>1803</v>
       </c>
-      <c r="C235" t="s">
+    </row>
+    <row r="237" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B237" s="1" t="s">
         <v>1804</v>
       </c>
-    </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B236" s="1" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C236" t="s">
+      <c r="C237" t="s">
         <v>1805</v>
       </c>
-    </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B237" s="1" t="s">
+      <c r="D237" s="33" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E237" s="34" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B238" s="1" t="s">
         <v>1806</v>
       </c>
-      <c r="C237" t="s">
+      <c r="C238" t="s">
         <v>1807</v>
       </c>
-      <c r="D237" s="33" t="s">
-        <v>2132</v>
-      </c>
-      <c r="E237" s="34" t="s">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B238" s="1" t="s">
+    </row>
+    <row r="239" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B239" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="C238" t="s">
+      <c r="C239" t="s">
         <v>1809</v>
       </c>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B239" s="1" t="s">
+    <row r="240" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B240" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C240" t="s">
         <v>1810</v>
       </c>
-      <c r="C239" t="s">
-        <v>1811</v>
-      </c>
-    </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B240" s="1" t="s">
-        <v>1957</v>
-      </c>
-      <c r="C240" t="s">
-        <v>1812</v>
-      </c>
       <c r="D240" s="33" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="E240" s="34" t="s">
-        <v>2099</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B241" s="1" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="C241" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>2115</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B242" s="1" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="C242" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>2079</v>
+        <v>2071</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>2116</v>
+        <v>2107</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>2123</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B243" s="1" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="C243" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B244" s="1" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="C244" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="D244" s="33" t="s">
-        <v>2080</v>
+        <v>2072</v>
       </c>
       <c r="E244" s="34" t="s">
-        <v>2117</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B245" s="1" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="C245" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>2078</v>
+        <v>2070</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>2116</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B246" s="1" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="C246" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B247" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="C247" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B248" s="1" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="C248" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B249" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C249" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="D249" s="33" t="s">
-        <v>2090</v>
+        <v>2081</v>
       </c>
       <c r="E249" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B250" s="1" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
       <c r="C250" t="s">
-        <v>2512</v>
+        <v>2501</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2513</v>
+        <v>2502</v>
       </c>
       <c r="E250" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B251" s="1" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C251" t="s">
         <v>462</v>
@@ -14462,231 +14936,237 @@
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B252" s="1" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="C252" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B253" s="1" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="C253" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="D253" s="33" t="s">
-        <v>2067</v>
+        <v>2063</v>
       </c>
       <c r="E253" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B254" s="1" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="C254" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B255" s="1" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="C255" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B256" s="1" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="C256" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B257" s="1" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="C257" t="s">
-        <v>1836</v>
+        <v>2582</v>
       </c>
       <c r="D257" s="33" t="s">
-        <v>2070</v>
+        <v>2581</v>
       </c>
       <c r="E257" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
+      </c>
+      <c r="F257" s="32" t="s">
+        <v>2580</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B258" s="1" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="C258" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B259" s="1" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="C259" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="D259" s="33" t="s">
-        <v>2072</v>
+        <v>2577</v>
       </c>
       <c r="E259" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
+      </c>
+      <c r="F259" s="32" t="s">
+        <v>2571</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B260" s="1" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="C260" t="s">
         <v>417</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2144</v>
+        <v>2134</v>
       </c>
       <c r="E260" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2118</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B261" s="1" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="C261" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="E261" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B262" s="1" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="C262" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>2091</v>
+        <v>2082</v>
       </c>
       <c r="E262" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B263" s="1" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
       <c r="C263" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="C264" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="C265" t="s">
-        <v>1850</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B266" s="1" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
       <c r="C266" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B267" s="1" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="C267" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
       <c r="D267" s="33" t="s">
-        <v>2089</v>
+        <v>2080</v>
       </c>
       <c r="E267" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B268" s="1" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
       <c r="C268" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B269" s="1" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="C269" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B270" s="1" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
       <c r="C270" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B271" s="1" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
       <c r="C271" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B272" s="1" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="C272" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B273" s="1" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
       <c r="C273" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B274" s="1" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="C274" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.4">
@@ -14694,62 +15174,62 @@
         <v>430</v>
       </c>
       <c r="C275" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B276" s="1" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="C276" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B277" s="1" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
       <c r="C277" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="D277" s="33" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="E277" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B278" s="1" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="C278" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="E278" s="42" t="s">
-        <v>2479</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B279" s="1" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
       <c r="C279" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="D279" s="33" t="s">
         <v>376</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>2479</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B280" s="1" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="C280" t="s">
         <v>1420</v>
@@ -14757,147 +15237,147 @@
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B281" s="1" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="C281" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B282" s="1" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="C282" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B283" s="1" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
       <c r="C283" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B284" s="1" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="C284" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B285" s="1" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="C285" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B286" s="1" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="C286" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B287" s="1" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="C287" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="D287" s="33" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="E287" s="34" t="s">
-        <v>2112</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B288" s="1" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="C288" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B289" s="1" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="C289" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B290" s="1" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="C290" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B291" s="1" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="C291" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="D291" s="33" t="s">
-        <v>2063</v>
+        <v>2059</v>
       </c>
       <c r="E291" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2484</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B292" s="1" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="C292" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="D292" s="33" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="E292" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="F292" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B293" s="1" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="C293" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="E293" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B294" s="1" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="C294" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
@@ -14905,10 +15385,10 @@
         <v>286</v>
       </c>
       <c r="C295" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="D295" s="33" t="s">
-        <v>2135</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.4">
@@ -14916,121 +15396,124 @@
         <v>1425</v>
       </c>
       <c r="C296" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2135</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B297" s="1" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="C297" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B298" s="24" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="C298" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>2084</v>
+        <v>2075</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>2484</v>
+        <v>2473</v>
+      </c>
+      <c r="F298" s="32" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B299" s="1" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="C299" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="D299" s="33" t="s">
-        <v>2073</v>
+        <v>2067</v>
       </c>
       <c r="E299" s="34" t="s">
-        <v>2105</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B300" s="24" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="C300" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B301" s="18" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="C301" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="D301" s="33" t="s">
-        <v>2134</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B302" s="18" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="C302" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="D302" s="33" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="E302" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B303" s="18" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C303" t="s">
         <v>1986</v>
       </c>
-      <c r="C303" t="s">
-        <v>1989</v>
-      </c>
       <c r="D303" s="33" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="E303" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B304" s="26" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="C304" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="D304" s="33" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="E304" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B305" s="1" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="C305" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="D305" s="33" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="E305" s="34" t="s">
-        <v>2106</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.4">
@@ -15038,128 +15521,131 @@
         <v>936</v>
       </c>
       <c r="C306" t="s">
-        <v>2543</v>
+        <v>2532</v>
       </c>
       <c r="D306" s="33" t="s">
-        <v>2519</v>
+        <v>2508</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>2484</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B307" s="1" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C307" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="D307" s="33" t="s">
-        <v>2054</v>
+        <v>2050</v>
       </c>
       <c r="E307" s="34" t="s">
-        <v>2107</v>
+        <v>2098</v>
       </c>
       <c r="F307" s="32" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B308" s="27" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C308" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="D308" s="33" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
       <c r="E308" s="34" t="s">
-        <v>2108</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B309" s="1" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="C309" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D309" s="33" t="s">
-        <v>2094</v>
+        <v>2085</v>
       </c>
       <c r="E309" s="34" t="s">
-        <v>2109</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B310" s="1" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C310" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D310" s="33" t="s">
-        <v>2095</v>
+        <v>2086</v>
       </c>
       <c r="E310" s="34" t="s">
-        <v>2109</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B311" s="1" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C311" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D311" s="33" t="s">
-        <v>2083</v>
+        <v>2074</v>
       </c>
       <c r="E311" s="34" t="s">
-        <v>2110</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B312" s="1" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C312" t="s">
-        <v>2154</v>
+        <v>2144</v>
       </c>
       <c r="D312" s="33" t="s">
-        <v>2156</v>
+        <v>2146</v>
       </c>
       <c r="E312" s="34" t="s">
-        <v>2110</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B313" s="1" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C313" t="s">
-        <v>2155</v>
+        <v>2145</v>
       </c>
       <c r="D313" s="33" t="s">
-        <v>2156</v>
+        <v>2146</v>
       </c>
       <c r="E313" s="34" t="s">
-        <v>2110</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B314" s="1" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C314" t="s">
-        <v>2021</v>
-      </c>
-      <c r="D314" s="33" t="s">
-        <v>2081</v>
+        <v>2018</v>
+      </c>
+      <c r="D314" s="54" t="s">
+        <v>2590</v>
       </c>
       <c r="E314" s="34" t="s">
-        <v>2111</v>
+        <v>2102</v>
+      </c>
+      <c r="F314" s="32" t="s">
+        <v>2586</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
@@ -15167,75 +15653,78 @@
         <v>153</v>
       </c>
       <c r="C315" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D315" s="33" t="s">
-        <v>2082</v>
+        <v>2073</v>
       </c>
       <c r="E315" s="34" t="s">
-        <v>2110</v>
+        <v>2101</v>
+      </c>
+      <c r="F315" s="32" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B316" s="1" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C316" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D316" s="33" t="s">
-        <v>2082</v>
+        <v>2073</v>
       </c>
       <c r="E316" s="34" t="s">
-        <v>2110</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B317" s="1" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="C317" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D317" s="33" t="s">
-        <v>2085</v>
+        <v>2076</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
       <c r="F317" s="32" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B318" s="1" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="C318" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
       <c r="D318" s="33" t="s">
-        <v>2086</v>
+        <v>2077</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B319" s="1" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="C319" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="D319" s="33" t="s">
-        <v>2088</v>
+        <v>2079</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
       <c r="F319" s="32" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.4">
@@ -15243,27 +15732,27 @@
         <v>822</v>
       </c>
       <c r="C320" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="D320" s="33" t="s">
-        <v>2133</v>
+        <v>2123</v>
       </c>
       <c r="E320" s="32" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B321" s="1" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="C321" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="D321" s="33" t="s">
-        <v>2087</v>
+        <v>2078</v>
       </c>
       <c r="E321" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.4">
@@ -15271,16 +15760,16 @@
         <v>1094</v>
       </c>
       <c r="C322" t="s">
-        <v>2532</v>
+        <v>2521</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
       <c r="F322" s="32" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.4">
@@ -15288,84 +15777,84 @@
         <v>296</v>
       </c>
       <c r="C323" t="s">
-        <v>2533</v>
+        <v>2522</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2145</v>
+        <v>2135</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
       <c r="F323" s="32" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>2530</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B324" s="1" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="C324" t="s">
-        <v>2149</v>
+        <v>2139</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2151</v>
+        <v>2141</v>
       </c>
       <c r="E324" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="F324" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B325" s="1" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="C325" t="s">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="D325" s="33" t="s">
-        <v>2151</v>
+        <v>2141</v>
       </c>
       <c r="E325" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="F325" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B326" s="1" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C326" t="s">
-        <v>2534</v>
+        <v>2523</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>2475</v>
+        <v>2464</v>
       </c>
       <c r="E326" s="34" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B327" s="1" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="C327" t="s">
-        <v>2535</v>
+        <v>2524</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2474</v>
+        <v>2463</v>
       </c>
       <c r="E327" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2484</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.4">
@@ -15373,13 +15862,13 @@
         <v>407</v>
       </c>
       <c r="C328" t="s">
-        <v>2536</v>
+        <v>2525</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2476</v>
+        <v>2465</v>
       </c>
       <c r="E328" s="34" t="s">
-        <v>2511</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.4">
@@ -15387,13 +15876,13 @@
         <v>160</v>
       </c>
       <c r="C329" t="s">
-        <v>2537</v>
+        <v>2526</v>
       </c>
       <c r="D329" s="41" t="s">
-        <v>2477</v>
+        <v>2466</v>
       </c>
       <c r="E329" s="42" t="s">
-        <v>2479</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.4">
@@ -15401,27 +15890,27 @@
         <v>1103</v>
       </c>
       <c r="C330" t="s">
-        <v>2538</v>
+        <v>2527</v>
       </c>
       <c r="D330" s="33" t="s">
-        <v>2478</v>
+        <v>2467</v>
       </c>
       <c r="E330" s="42" t="s">
-        <v>2479</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B331" s="1" t="s">
-        <v>2520</v>
+        <v>2509</v>
       </c>
       <c r="C331" t="s">
-        <v>2539</v>
+        <v>2528</v>
       </c>
       <c r="D331" s="43" t="s">
-        <v>2521</v>
+        <v>2510</v>
       </c>
       <c r="E331" s="34" t="s">
-        <v>2522</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.4">
@@ -15429,60 +15918,102 @@
         <v>1147</v>
       </c>
       <c r="C332" t="s">
-        <v>2540</v>
+        <v>2529</v>
       </c>
       <c r="D332" s="33" t="s">
-        <v>2523</v>
+        <v>2512</v>
       </c>
       <c r="E332" s="34" t="s">
-        <v>2523</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B333" s="1" t="s">
-        <v>2524</v>
+        <v>2513</v>
       </c>
       <c r="C333" t="s">
-        <v>2541</v>
+        <v>2530</v>
       </c>
       <c r="D333" s="33" t="s">
-        <v>2523</v>
+        <v>2512</v>
       </c>
       <c r="E333" s="34" t="s">
-        <v>2523</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B334" s="1" t="s">
-        <v>2525</v>
+        <v>2514</v>
       </c>
       <c r="C334" t="s">
-        <v>2542</v>
+        <v>2531</v>
       </c>
       <c r="D334" s="41" t="s">
-        <v>2527</v>
+        <v>2516</v>
       </c>
       <c r="E334" s="34" t="s">
-        <v>2528</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
-        <v>2526</v>
+        <v>2515</v>
       </c>
       <c r="C335" t="s">
-        <v>2531</v>
+        <v>2520</v>
       </c>
       <c r="D335" s="41" t="s">
-        <v>2527</v>
+        <v>2516</v>
       </c>
       <c r="E335" s="34" t="s">
-        <v>2528</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>1896</v>
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="337" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B337" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C337" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D337" s="33" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E337" s="34" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="338" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B338" s="1" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C338" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D338" s="33" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E338" s="34" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="339" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B339" s="1" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C339" s="55" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D339" s="33" t="s">
+        <v>2589</v>
+      </c>
+      <c r="E339" s="32" t="s">
+        <v>2586</v>
       </c>
     </row>
   </sheetData>
@@ -15526,7 +16057,7 @@
     <hyperlink ref="E199" r:id="rId23" xr:uid="{069318CA-733C-4637-8231-71BF8BDE174C}"/>
     <hyperlink ref="F199" r:id="rId24" xr:uid="{606F5CDB-9747-4F64-AA15-7F28234FF649}"/>
     <hyperlink ref="E242" r:id="rId25" xr:uid="{E4A3FF73-4921-408C-8FC8-576088C455C5}"/>
-    <hyperlink ref="F260" r:id="rId26" xr:uid="{FD6022E8-CD2D-453D-B9BD-977A5A45A79A}"/>
+    <hyperlink ref="F260" r:id="rId26" display="無影言本祭" xr:uid="{FD6022E8-CD2D-453D-B9BD-977A5A45A79A}"/>
     <hyperlink ref="F307" r:id="rId27" xr:uid="{CB76E612-3F74-438D-AE6C-4556B87A3117}"/>
     <hyperlink ref="E311" r:id="rId28" xr:uid="{400C510C-E456-4A27-B24C-418D350D90BD}"/>
     <hyperlink ref="E314" r:id="rId29" xr:uid="{14C34214-6147-4305-92F1-69B213D1FA29}"/>
@@ -15610,9 +16141,20 @@
     <hyperlink ref="E333" r:id="rId107" xr:uid="{129E740A-4AA0-4F11-88A1-0B9A03860FF2}"/>
     <hyperlink ref="E334" r:id="rId108" xr:uid="{C56117F9-1196-45F7-BA62-047C42ECB7D7}"/>
     <hyperlink ref="E335" r:id="rId109" xr:uid="{E85A37DE-DD8D-4FF4-AA31-96B38F5902E5}"/>
+    <hyperlink ref="F315" r:id="rId110" display="無影言本祭" xr:uid="{9A0CC19B-9348-48FF-A0CC-CA3DEFCF51A5}"/>
+    <hyperlink ref="F298" r:id="rId111" display="無影言本祭" xr:uid="{0BA89E84-457B-4E28-945D-1DCDB15B63B0}"/>
+    <hyperlink ref="E337" r:id="rId112" xr:uid="{C6217001-1ED9-4BE7-914A-0BDBF5BE318C}"/>
+    <hyperlink ref="E338" r:id="rId113" xr:uid="{BC9E6940-FF9A-4756-BB1B-0C4403762254}"/>
+    <hyperlink ref="F216" r:id="rId114" xr:uid="{3C6377C7-1B66-4476-8E9C-A9D5A878A0AE}"/>
+    <hyperlink ref="F259" r:id="rId115" xr:uid="{AA40B19D-9046-4C74-B04E-EDD95592AD0F}"/>
+    <hyperlink ref="F163" r:id="rId116" xr:uid="{921360D1-C8F1-47DC-8965-EF1A27211120}"/>
+    <hyperlink ref="F257" r:id="rId117" xr:uid="{D1CEAB88-533B-4592-96F7-9C2CA0598EF3}"/>
+    <hyperlink ref="F232" r:id="rId118" xr:uid="{35EA88DE-206B-4EF8-9259-9E1E793C9E5B}"/>
+    <hyperlink ref="F314" r:id="rId119" xr:uid="{00BD4916-443C-4D61-ADBA-08351BF0AA95}"/>
+    <hyperlink ref="E339" r:id="rId120" xr:uid="{35DD3EBE-71F4-4631-AFA7-387F800E7B2F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId110"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId121"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -16533,7 +17075,7 @@
         <v>。</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -17112,8 +17654,8 @@
         <v>156</v>
       </c>
       <c r="AA4" s="6" t="str">
-        <f>_xlfn.XLOOKUP(Z4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(Z4,対応表!$B:$B,対応表!$C:$C,"に")</f>
+        <v>に</v>
       </c>
       <c r="AB4" s="7" t="s">
         <v>157</v>
@@ -18120,7 +18662,7 @@
       </c>
       <c r="U6" s="6" t="str">
         <f>_xlfn.XLOOKUP(T6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>音?</v>
+        <v>音</v>
       </c>
       <c r="V6" s="7" t="s">
         <v>296</v>
@@ -19267,7 +19809,7 @@
       </c>
       <c r="BC8" s="6" t="str">
         <f>_xlfn.XLOOKUP(BB8,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>良</v>
       </c>
       <c r="BD8" s="7" t="s">
         <v>456</v>
@@ -20399,8 +20941,8 @@
         <v>612</v>
       </c>
       <c r="CG10" s="6" t="str">
-        <f>_xlfn.XLOOKUP(CF10,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(CF10,対応表!$B:$B,対応表!$C:$C,"の")</f>
+        <v>の</v>
       </c>
       <c r="CH10" s="7" t="s">
         <v>613</v>
@@ -21026,7 +21568,7 @@
       </c>
       <c r="DM11" s="6" t="str">
         <f>_xlfn.XLOOKUP(DL11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>集?</v>
+        <v>集</v>
       </c>
       <c r="DN11" s="7" t="s">
         <v>700</v>
@@ -21941,8 +22483,8 @@
         <v>827</v>
       </c>
       <c r="CG13" s="6" t="str">
-        <f>_xlfn.XLOOKUP(CF13,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(CF13,対応表!$B:$B,対応表!$C:$C,"が")</f>
+        <v>が</v>
       </c>
       <c r="CH13" s="7" t="s">
         <v>828</v>
@@ -22969,8 +23511,8 @@
         <v>971</v>
       </c>
       <c r="CG15" s="6" t="str">
-        <f>_xlfn.XLOOKUP(CF15,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(CF15,対応表!$B:$B,対応表!$C:$C,"在")</f>
+        <v>在</v>
       </c>
       <c r="CH15" s="7" t="s">
         <v>972</v>
@@ -23344,7 +23886,7 @@
       </c>
       <c r="AS16" s="6" t="str">
         <f>_xlfn.XLOOKUP(AR16,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>[侱]?</v>
       </c>
       <c r="AT16" s="7" t="s">
         <v>1023</v>
@@ -26868,7 +27410,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -26942,7 +27484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C5E931-1AEC-434D-81A1-3EA98DBB914E}">
-  <dimension ref="B1:E19"/>
+  <dimension ref="B1:E34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.25" style="35" bestFit="1" customWidth="1"/>
@@ -26952,266 +27494,455 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B1" s="35" t="s">
-        <v>2139</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>2140</v>
-      </c>
-      <c r="D1" s="36" t="s">
-        <v>2141</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>2355</v>
+      <c r="B1" s="45" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
-        <v>2136</v>
+        <v>2126</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>2137</v>
+        <v>2127</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>2138</v>
+        <v>2128</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
-        <v>2248</v>
+        <v>2237</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>2249</v>
+        <v>2238</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>2250</v>
+        <v>2239</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
-        <v>2251</v>
+        <v>2240</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>2252</v>
+        <v>2241</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2253</v>
+        <v>2242</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
-        <v>2254</v>
+        <v>2243</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>2255</v>
+        <v>2244</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>2256</v>
+        <v>2245</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
-        <v>2257</v>
+        <v>2246</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>2258</v>
+        <v>2247</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>2259</v>
+        <v>2248</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
-        <v>2260</v>
+        <v>2249</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>2261</v>
+        <v>2250</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>2262</v>
+        <v>2251</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2263</v>
+        <v>2252</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2264</v>
+        <v>2253</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
-        <v>2265</v>
+        <v>2254</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>2266</v>
+        <v>2255</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>2267</v>
+        <v>2256</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>2356</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2268</v>
+        <v>2257</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2269</v>
+        <v>2258</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
-        <v>2270</v>
+        <v>2259</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>2271</v>
+        <v>2260</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
-        <v>2273</v>
+        <v>2262</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2274</v>
+        <v>2263</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2357</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2275</v>
+        <v>2264</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
-        <v>2353</v>
+        <v>2342</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>2354</v>
+        <v>2343</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2426</v>
+        <v>2415</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2425</v>
+        <v>2414</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
-        <v>2427</v>
+        <v>2416</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>2428</v>
+        <v>2417</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2430</v>
+        <v>2419</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2429</v>
+        <v>2418</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="35" t="s">
-        <v>2096</v>
+        <v>2087</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2431</v>
+        <v>2420</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2272</v>
+        <v>2261</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2356</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
-        <v>2471</v>
+        <v>2460</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>2472</v>
+        <v>2461</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>2473</v>
+        <v>2462</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B20" s="44" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B21" s="35" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B22" s="35" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>2539</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>2540</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B23" s="35" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>2253</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B24" s="35" t="s">
+        <v>2543</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B25" s="35" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B26" s="35" t="s">
+        <v>2547</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B27" s="35" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B28" s="35" t="s">
+        <v>2556</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B29" s="35" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B30" s="35" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B31" s="35" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B32" s="35" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B33" s="35" t="s">
+        <v>2568</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>2569</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B34" s="35" t="s">
+        <v>2570</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>2261</v>
       </c>
     </row>
   </sheetData>
@@ -27222,388 +27953,391 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED28C13D-14D9-4671-B3CF-1ADD2E368C21}">
-  <dimension ref="B1:D280"/>
+  <dimension ref="B1:D282"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="31"/>
     <col min="3" max="3" width="21.375" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B1" s="31" t="s">
-        <v>2206</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:4" s="49" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="B1" s="47" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C1" s="48" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B3" s="31" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4" s="31" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B5" s="31" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B6" s="31" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B7" s="31" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B8" s="31" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B9" s="31" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B10" s="31" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B11" s="31" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B12" s="31" t="s">
         <v>2157</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B3" s="31" t="s">
+      <c r="C12" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B13" s="31" t="s">
         <v>2158</v>
       </c>
-      <c r="C3" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B4" s="31" t="s">
+      <c r="C13" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B14" s="31" t="s">
         <v>2159</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B5" s="31" t="s">
+      <c r="C14" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B15" s="31" t="s">
         <v>2160</v>
       </c>
-      <c r="C5" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B6" s="31" t="s">
+      <c r="C15" s="34" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B16" s="31" t="s">
         <v>2161</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B7" s="31" t="s">
-        <v>2162</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B8" s="31" t="s">
-        <v>2165</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B9" s="31" t="s">
-        <v>2166</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B10" s="31" t="s">
-        <v>2163</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B11" s="31" t="s">
-        <v>2164</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B12" s="31" t="s">
-        <v>2167</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B13" s="31" t="s">
-        <v>2168</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B14" s="31" t="s">
-        <v>2169</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B15" s="31" t="s">
-        <v>2170</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B16" s="31" t="s">
-        <v>2171</v>
-      </c>
       <c r="C16" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="31" t="s">
-        <v>2172</v>
+        <v>2162</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="31" t="s">
-        <v>2173</v>
+        <v>2163</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="31" t="s">
-        <v>2174</v>
+        <v>2164</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="31" t="s">
-        <v>2175</v>
+        <v>2165</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="31" t="s">
-        <v>2176</v>
+        <v>2166</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="31" t="s">
-        <v>2177</v>
+        <v>2167</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="31" t="s">
-        <v>2225</v>
+        <v>2214</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="31" t="s">
-        <v>2226</v>
+        <v>2215</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>2129</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="31" t="s">
-        <v>2178</v>
+        <v>2168</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>2106</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="31" t="s">
-        <v>2179</v>
+        <v>2169</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>2106</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="31" t="s">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>2106</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="31" t="s">
-        <v>2181</v>
+        <v>2171</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>2106</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="31" t="s">
-        <v>2182</v>
+        <v>2172</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="31" t="s">
-        <v>2183</v>
+        <v>2173</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="31" t="s">
-        <v>2184</v>
+        <v>2174</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="31" t="s">
-        <v>2185</v>
+        <v>2175</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
-        <v>2186</v>
+        <v>2176</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
-        <v>2187</v>
+        <v>2177</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
-        <v>2188</v>
+        <v>2178</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
-        <v>2189</v>
+        <v>2179</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
-        <v>2191</v>
+        <v>2181</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
-        <v>2192</v>
+        <v>2182</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
-        <v>2193</v>
+        <v>2183</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
-        <v>2194</v>
+        <v>2184</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
-        <v>2195</v>
+        <v>2185</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
-        <v>2196</v>
+        <v>2186</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
-        <v>2208</v>
+        <v>2197</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
-        <v>2197</v>
+        <v>2187</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
-        <v>2198</v>
+        <v>2188</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
-        <v>2199</v>
+        <v>2189</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.4">
@@ -27611,1869 +28345,1894 @@
         <v>1161</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
-        <v>2200</v>
+        <v>2190</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
-        <v>2201</v>
+        <v>2191</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
-        <v>2202</v>
+        <v>2192</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
-        <v>2203</v>
+        <v>2193</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
-        <v>2204</v>
+        <v>2194</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>2119</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
-        <v>2205</v>
+        <v>2195</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B55" s="31" t="s">
-        <v>2209</v>
+        <v>2198</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
-        <v>2210</v>
+        <v>2199</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
-        <v>2211</v>
+        <v>2200</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
-        <v>2212</v>
+        <v>2201</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
-        <v>2213</v>
+        <v>2202</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
-        <v>2214</v>
+        <v>2203</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
-        <v>2215</v>
+        <v>2204</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
-        <v>2216</v>
+        <v>2205</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
-        <v>2217</v>
+        <v>2206</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
-        <v>2218</v>
+        <v>2207</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B65" s="31" t="s">
-        <v>2219</v>
+        <v>2208</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B66" s="31" t="s">
-        <v>2220</v>
+        <v>2209</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B67" s="31" t="s">
-        <v>2221</v>
+        <v>2210</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B68" s="31" t="s">
-        <v>2222</v>
+        <v>2211</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B69" s="31" t="s">
-        <v>2223</v>
+        <v>2212</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B70" s="31" t="s">
-        <v>2224</v>
+        <v>2213</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B71" s="31" t="s">
-        <v>2227</v>
+        <v>2216</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="31" t="s">
-        <v>2228</v>
+        <v>2217</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B73" s="31" t="s">
-        <v>2229</v>
+        <v>2218</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B74" s="31" t="s">
-        <v>2230</v>
+        <v>2219</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
-        <v>2231</v>
+        <v>2220</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
       <c r="D75" s="34" t="s">
-        <v>2111</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
-        <v>2232</v>
+        <v>2221</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="31" t="s">
-        <v>2233</v>
+        <v>2222</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="31" t="s">
-        <v>2234</v>
+        <v>2223</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B79" s="31" t="s">
-        <v>2235</v>
+        <v>2224</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B80" s="31" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C80" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B81" s="31" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B82" s="31" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C82" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B83" s="31" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B84" s="31" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C84" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B85" s="31" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B86" s="31" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B87" s="31" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B88" s="31" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C88" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B89" s="31" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C89" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B90" s="31" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C90" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B91" s="31" t="s">
         <v>2236</v>
       </c>
-      <c r="C80" s="34" t="s">
+      <c r="C91" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B92" s="31" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C92" s="34" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B93" s="31" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C93" s="34" t="s">
         <v>2098</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B81" s="31" t="s">
-        <v>2237</v>
-      </c>
-      <c r="C81" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B82" s="31" t="s">
-        <v>2238</v>
-      </c>
-      <c r="C82" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B83" s="31" t="s">
-        <v>2239</v>
-      </c>
-      <c r="C83" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B84" s="31" t="s">
-        <v>2240</v>
-      </c>
-      <c r="C84" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B85" s="31" t="s">
-        <v>2241</v>
-      </c>
-      <c r="C85" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B86" s="31" t="s">
-        <v>2242</v>
-      </c>
-      <c r="C86" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B87" s="31" t="s">
-        <v>2243</v>
-      </c>
-      <c r="C87" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B88" s="31" t="s">
-        <v>2244</v>
-      </c>
-      <c r="C88" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B89" s="31" t="s">
-        <v>2245</v>
-      </c>
-      <c r="C89" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B90" s="31" t="s">
-        <v>2246</v>
-      </c>
-      <c r="C90" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B91" s="31" t="s">
-        <v>2247</v>
-      </c>
-      <c r="C91" s="34" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B92" s="31" t="s">
-        <v>2276</v>
-      </c>
-      <c r="C92" s="34" t="s">
-        <v>2277</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B93" s="31" t="s">
-        <v>2278</v>
-      </c>
-      <c r="C93" s="34" t="s">
-        <v>2107</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2279</v>
+        <v>2458</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2096</v>
+      </c>
+      <c r="D94" s="32" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B95" s="31" t="s">
-        <v>2280</v>
+        <v>2268</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>2282</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2096</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B96" s="31" t="s">
-        <v>2281</v>
+        <v>2269</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2282</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
-        <v>2293</v>
+        <v>2270</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>2282</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2292</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="31" t="s">
-        <v>2284</v>
+        <v>2272</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="31" t="s">
-        <v>2285</v>
+        <v>2273</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="31" t="s">
-        <v>2286</v>
+        <v>2274</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B102" s="31" t="s">
-        <v>950</v>
+        <v>2275</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>2287</v>
+        <v>950</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="31" t="s">
-        <v>2288</v>
+        <v>2276</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B105" s="31" t="s">
-        <v>2289</v>
+        <v>2277</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="31" t="s">
-        <v>2290</v>
+        <v>2278</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="31" t="s">
-        <v>2291</v>
+        <v>2279</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
-        <v>2298</v>
+        <v>2280</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>2292</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2294</v>
+        <v>2287</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>2128</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="31" t="s">
-        <v>2295</v>
+        <v>2283</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>2128</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="31" t="s">
-        <v>2296</v>
+        <v>2284</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>2128</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="31" t="s">
-        <v>2297</v>
+        <v>2285</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>2128</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2299</v>
+        <v>2286</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>2108</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="31" t="s">
-        <v>2300</v>
+        <v>2288</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>2108</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="31" t="s">
-        <v>2301</v>
+        <v>2289</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>2108</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="31" t="s">
-        <v>2302</v>
+        <v>2290</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>2108</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="31" t="s">
-        <v>2303</v>
+        <v>2291</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>2108</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="31" t="s">
-        <v>2304</v>
+        <v>2292</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>2108</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="31" t="s">
-        <v>2305</v>
+        <v>2293</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>2113</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="31" t="s">
-        <v>2306</v>
+        <v>2294</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>2113</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="31" t="s">
-        <v>2307</v>
+        <v>2295</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>2113</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="31" t="s">
-        <v>2308</v>
+        <v>2296</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2309</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
-        <v>2310</v>
+        <v>2297</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>2309</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="31" t="s">
-        <v>2311</v>
+        <v>2299</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2309</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="31" t="s">
-        <v>2312</v>
+        <v>2300</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2320</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="31" t="s">
-        <v>2313</v>
+        <v>2301</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2320</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="31" t="s">
-        <v>2314</v>
+        <v>2302</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>2320</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="31" t="s">
-        <v>2315</v>
+        <v>2303</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2320</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B129" s="31" t="s">
-        <v>2316</v>
+        <v>2304</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>2320</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B130" s="31" t="s">
-        <v>2317</v>
+        <v>2305</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>2320</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B131" s="31" t="s">
-        <v>2318</v>
+        <v>2306</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>2320</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B132" s="31" t="s">
-        <v>2319</v>
+        <v>2307</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2320</v>
+        <v>2309</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>2381</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
-        <v>2321</v>
+        <v>2308</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>2327</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B134" s="31" t="s">
-        <v>2322</v>
+        <v>2310</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2327</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B135" s="31" t="s">
-        <v>2323</v>
+        <v>2311</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>2327</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B136" s="31" t="s">
-        <v>2324</v>
+        <v>2312</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>2327</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B137" s="31" t="s">
-        <v>2325</v>
+        <v>2313</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>2327</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B138" s="31" t="s">
-        <v>2326</v>
+        <v>2314</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2327</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2328</v>
+        <v>2315</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2333</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B140" s="31" t="s">
-        <v>2329</v>
+        <v>2317</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>2333</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B141" s="31" t="s">
-        <v>2330</v>
+        <v>2318</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>2333</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B142" s="31" t="s">
-        <v>2331</v>
+        <v>2319</v>
       </c>
       <c r="C142" s="34" t="s">
-        <v>2333</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B143" s="31" t="s">
-        <v>2332</v>
+        <v>2320</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2333</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2334</v>
+        <v>2321</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>2337</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B145" s="31" t="s">
-        <v>2335</v>
+        <v>2323</v>
       </c>
       <c r="C145" s="34" t="s">
-        <v>2337</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B146" s="31" t="s">
-        <v>2336</v>
+        <v>2324</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2337</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2338</v>
+        <v>2325</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2347</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B148" s="31" t="s">
-        <v>2339</v>
+        <v>2327</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B149" s="31" t="s">
-        <v>2340</v>
+        <v>2328</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B150" s="31" t="s">
-        <v>2341</v>
+        <v>2329</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B151" s="31" t="s">
-        <v>2342</v>
+        <v>2330</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B152" s="31" t="s">
-        <v>2343</v>
+        <v>2331</v>
       </c>
       <c r="C152" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B153" s="31" t="s">
-        <v>2344</v>
+        <v>2332</v>
       </c>
       <c r="C153" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B154" s="31" t="s">
-        <v>2345</v>
+        <v>2333</v>
       </c>
       <c r="C154" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B155" s="31" t="s">
-        <v>2346</v>
+        <v>2334</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2347</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
-        <v>2348</v>
+        <v>2335</v>
       </c>
       <c r="C156" s="34" t="s">
-        <v>2352</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B157" s="31" t="s">
-        <v>2349</v>
+        <v>2337</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>2352</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B158" s="31" t="s">
-        <v>2350</v>
+        <v>2338</v>
       </c>
       <c r="C158" s="34" t="s">
-        <v>2352</v>
+        <v>2341</v>
       </c>
       <c r="D158" s="34" t="s">
-        <v>2397</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B159" s="31" t="s">
-        <v>2351</v>
+        <v>2339</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2352</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2358</v>
+        <v>2340</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2366</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
-        <v>2359</v>
+        <v>2347</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
-        <v>2360</v>
+        <v>2348</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
-        <v>2361</v>
+        <v>2349</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
-        <v>2362</v>
+        <v>2350</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
-        <v>2363</v>
+        <v>2351</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
-        <v>2364</v>
+        <v>2352</v>
       </c>
       <c r="C166" s="34" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
-        <v>2365</v>
+        <v>2353</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2366</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B168" s="31" t="s">
-        <v>2369</v>
+        <v>2354</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>2371</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
-        <v>2370</v>
+        <v>2358</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2371</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
-        <v>2367</v>
+        <v>2359</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>2371</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
-        <v>2368</v>
+        <v>2356</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>2371</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B172" s="31" t="s">
-        <v>2372</v>
+        <v>2357</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>2377</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
-        <v>2373</v>
+        <v>2361</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>2377</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
-        <v>2374</v>
+        <v>2362</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>2377</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
-        <v>2375</v>
+        <v>2363</v>
       </c>
       <c r="C175" s="34" t="s">
-        <v>2377</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
-        <v>2376</v>
+        <v>2364</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2377</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2378</v>
+        <v>2365</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2379</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
-        <v>2504</v>
+        <v>2367</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>2506</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2505</v>
+        <v>2493</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2506</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2380</v>
+        <v>2494</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2381</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
-        <v>2382</v>
+        <v>2369</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>2381</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B182" s="31" t="s">
-        <v>2383</v>
+        <v>2371</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2381</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B183" s="31" t="s">
-        <v>2384</v>
+        <v>2372</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2381</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B184" s="31" t="s">
-        <v>2385</v>
+        <v>2373</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>2388</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B185" s="31" t="s">
-        <v>2386</v>
+        <v>2374</v>
       </c>
       <c r="C185" s="34" t="s">
-        <v>2388</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B186" s="31" t="s">
-        <v>2387</v>
+        <v>2375</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2388</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
-        <v>2389</v>
+        <v>2376</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>2393</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B188" s="31" t="s">
-        <v>2390</v>
+        <v>2378</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>2393</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B189" s="31" t="s">
-        <v>2391</v>
+        <v>2379</v>
       </c>
       <c r="C189" s="34" t="s">
-        <v>2393</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B190" s="31" t="s">
-        <v>2392</v>
+        <v>2380</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2393</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2394</v>
+        <v>2381</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>2397</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B192" s="31" t="s">
-        <v>2395</v>
+        <v>2383</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>2397</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B193" s="31" t="s">
-        <v>2396</v>
+        <v>2384</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2397</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
-        <v>2200</v>
+        <v>2385</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>2397</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
-        <v>2398</v>
+        <v>2190</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>2402</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B196" s="31" t="s">
-        <v>2399</v>
+        <v>2387</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>2402</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B197" s="31" t="s">
-        <v>2400</v>
+        <v>2388</v>
       </c>
       <c r="C197" s="34" t="s">
-        <v>2402</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B198" s="31" t="s">
-        <v>2401</v>
+        <v>2389</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2402</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2403</v>
+        <v>2390</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2408</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B200" s="31" t="s">
-        <v>2404</v>
+        <v>2392</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>2408</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B201" s="31" t="s">
-        <v>2405</v>
+        <v>2393</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>2408</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B202" s="31" t="s">
-        <v>2406</v>
+        <v>2394</v>
       </c>
       <c r="C202" s="34" t="s">
-        <v>2408</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B203" s="31" t="s">
-        <v>2407</v>
+        <v>2395</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2408</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2410</v>
+        <v>2396</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2415</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
-        <v>2409</v>
+        <v>2399</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>2415</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
-        <v>2411</v>
+        <v>2398</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>2415</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B207" s="31" t="s">
-        <v>2412</v>
+        <v>2400</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>2415</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B208" s="31" t="s">
-        <v>2413</v>
+        <v>2401</v>
       </c>
       <c r="C208" s="34" t="s">
-        <v>2415</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B209" s="31" t="s">
-        <v>2414</v>
+        <v>2402</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2415</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
-        <v>2416</v>
+        <v>2403</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>2420</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B211" s="31" t="s">
-        <v>2417</v>
+        <v>2405</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>2420</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B212" s="31" t="s">
-        <v>2418</v>
+        <v>2406</v>
       </c>
       <c r="C212" s="34" t="s">
-        <v>2420</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B213" s="31" t="s">
-        <v>2419</v>
+        <v>2407</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2420</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2421</v>
+        <v>2408</v>
       </c>
       <c r="C214" s="34" t="s">
-        <v>2424</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B215" s="31" t="s">
-        <v>2422</v>
+        <v>2410</v>
       </c>
       <c r="C215" s="34" t="s">
-        <v>2424</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B216" s="31" t="s">
-        <v>2423</v>
+        <v>2411</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2424</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2432</v>
+        <v>2412</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2435</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B218" s="31" t="s">
-        <v>2436</v>
+        <v>2421</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2435</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
-        <v>2433</v>
+        <v>2425</v>
       </c>
       <c r="C219" s="34" t="s">
-        <v>2435</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B220" s="31" t="s">
-        <v>2434</v>
+        <v>2422</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2435</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
-        <v>2437</v>
+        <v>2423</v>
       </c>
       <c r="C221" s="34" t="s">
-        <v>2438</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2439</v>
+        <v>2426</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2440</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2441</v>
-      </c>
-      <c r="C223" s="42" t="s">
-        <v>2479</v>
+        <v>2428</v>
+      </c>
+      <c r="C223" s="34" t="s">
+        <v>2429</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C224" s="34" t="s">
-        <v>2445</v>
+        <v>2430</v>
+      </c>
+      <c r="C224" s="42" t="s">
+        <v>2468</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B225" s="31" t="s">
-        <v>2443</v>
+        <v>2431</v>
       </c>
       <c r="C225" s="34" t="s">
-        <v>2445</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B226" s="31" t="s">
-        <v>2444</v>
+        <v>2432</v>
       </c>
       <c r="C226" s="34" t="s">
-        <v>2445</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B227" s="31" t="s">
-        <v>2364</v>
+        <v>2433</v>
       </c>
       <c r="C227" s="34" t="s">
-        <v>2445</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B228" s="31" t="s">
-        <v>2446</v>
+        <v>2353</v>
       </c>
       <c r="C228" s="34" t="s">
-        <v>2449</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B229" s="31" t="s">
-        <v>2447</v>
+        <v>2435</v>
       </c>
       <c r="C229" s="34" t="s">
-        <v>2449</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B230" s="31" t="s">
-        <v>2448</v>
+        <v>2436</v>
       </c>
       <c r="C230" s="34" t="s">
-        <v>2449</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B231" s="31" t="s">
-        <v>2450</v>
+        <v>2437</v>
       </c>
       <c r="C231" s="34" t="s">
-        <v>2455</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B232" s="31" t="s">
-        <v>2451</v>
+        <v>2439</v>
       </c>
       <c r="C232" s="34" t="s">
-        <v>2455</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B233" s="31" t="s">
-        <v>2452</v>
+        <v>2440</v>
       </c>
       <c r="C233" s="34" t="s">
-        <v>2455</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B234" s="31" t="s">
-        <v>2453</v>
+        <v>2441</v>
       </c>
       <c r="C234" s="34" t="s">
-        <v>2455</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B235" s="31" t="s">
-        <v>2454</v>
+        <v>2442</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>2455</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B236" s="31" t="s">
-        <v>2456</v>
+        <v>2443</v>
       </c>
       <c r="C236" s="34" t="s">
-        <v>2457</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B237" s="31" t="s">
-        <v>2458</v>
+        <v>2445</v>
       </c>
       <c r="C237" s="34" t="s">
-        <v>2459</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B238" s="31" t="s">
-        <v>2460</v>
+        <v>2447</v>
       </c>
       <c r="C238" s="34" t="s">
-        <v>2461</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B239" s="31" t="s">
-        <v>2462</v>
+        <v>2449</v>
       </c>
       <c r="C239" s="34" t="s">
-        <v>2467</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="240" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B240" s="31" t="s">
-        <v>2463</v>
+        <v>2451</v>
       </c>
       <c r="C240" s="34" t="s">
-        <v>2467</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B241" s="31" t="s">
-        <v>2464</v>
+        <v>2452</v>
       </c>
       <c r="C241" s="34" t="s">
-        <v>2467</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B242" s="31" t="s">
-        <v>2465</v>
+        <v>2453</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2467</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B243" s="31" t="s">
-        <v>2466</v>
+        <v>2454</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2467</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2468</v>
+        <v>2455</v>
       </c>
       <c r="C244" s="34" t="s">
-        <v>2111</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
-        <v>2469</v>
-      </c>
-      <c r="C245" s="34" t="s">
-        <v>2111</v>
+        <v>2457</v>
+      </c>
+      <c r="C245" s="32" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B246" s="31" t="s">
-        <v>2470</v>
-      </c>
-      <c r="C246" s="34" t="s">
-        <v>2111</v>
+        <v>2551</v>
+      </c>
+      <c r="C246" s="32" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
-        <v>2480</v>
-      </c>
-      <c r="C247" s="34" t="s">
-        <v>2111</v>
+        <v>2552</v>
+      </c>
+      <c r="C247" s="32" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2481</v>
-      </c>
-      <c r="C248" s="34" t="s">
-        <v>2111</v>
+        <v>2459</v>
+      </c>
+      <c r="C248" s="32" t="s">
+        <v>2553</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2482</v>
+        <v>2469</v>
       </c>
       <c r="C249" s="34" t="s">
-        <v>2111</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2483</v>
+        <v>2470</v>
       </c>
       <c r="C250" s="34" t="s">
-        <v>2111</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2485</v>
+        <v>2471</v>
       </c>
       <c r="C251" s="34" t="s">
-        <v>2110</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2486</v>
-      </c>
-      <c r="C252" s="32" t="s">
-        <v>2120</v>
+        <v>2472</v>
+      </c>
+      <c r="C252" s="34" t="s">
+        <v>2102</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2487</v>
-      </c>
-      <c r="C253" s="32" t="s">
-        <v>2120</v>
+        <v>2474</v>
+      </c>
+      <c r="C253" s="34" t="s">
+        <v>2101</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2488</v>
+        <v>2475</v>
       </c>
       <c r="C254" s="32" t="s">
-        <v>2120</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2489</v>
-      </c>
-      <c r="C255" s="34" t="s">
-        <v>2496</v>
+        <v>2476</v>
+      </c>
+      <c r="C255" s="32" t="s">
+        <v>2110</v>
       </c>
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2490</v>
-      </c>
-      <c r="C256" s="34" t="s">
-        <v>2496</v>
+        <v>2477</v>
+      </c>
+      <c r="C256" s="32" t="s">
+        <v>2110</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2491</v>
+        <v>2478</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2496</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
-        <v>2492</v>
+        <v>2479</v>
       </c>
       <c r="C258" s="34" t="s">
-        <v>2496</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
-        <v>2493</v>
+        <v>2480</v>
       </c>
       <c r="C259" s="34" t="s">
-        <v>2496</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2494</v>
+        <v>2481</v>
       </c>
       <c r="C260" s="34" t="s">
-        <v>2496</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
-        <v>2495</v>
+        <v>2482</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2496</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
-        <v>2338</v>
+        <v>2483</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2496</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
-        <v>2497</v>
+        <v>2484</v>
       </c>
       <c r="C263" s="34" t="s">
-        <v>2506</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2498</v>
+        <v>2327</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2506</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
-        <v>2499</v>
+        <v>2486</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2506</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2500</v>
+        <v>2487</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2506</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2501</v>
+        <v>2488</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2506</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
-        <v>2247</v>
+        <v>2489</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2506</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2502</v>
+        <v>2490</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2506</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2503</v>
+        <v>2236</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2506</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
-        <v>2507</v>
-      </c>
-      <c r="C271" s="32" t="s">
-        <v>2484</v>
+        <v>2491</v>
+      </c>
+      <c r="C271" s="34" t="s">
+        <v>2495</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2210</v>
-      </c>
-      <c r="C272" s="32" t="s">
-        <v>2484</v>
+        <v>2492</v>
+      </c>
+      <c r="C272" s="34" t="s">
+        <v>2495</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
-        <v>2508</v>
+        <v>2496</v>
       </c>
       <c r="C273" s="32" t="s">
-        <v>2484</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2509</v>
-      </c>
-      <c r="C274" s="34" t="s">
-        <v>2511</v>
+        <v>2199</v>
+      </c>
+      <c r="C274" s="32" t="s">
+        <v>2473</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2510</v>
-      </c>
-      <c r="C275" s="34" t="s">
-        <v>2511</v>
+        <v>2497</v>
+      </c>
+      <c r="C275" s="32" t="s">
+        <v>2473</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
-        <v>2514</v>
-      </c>
-      <c r="C276" s="32" t="s">
-        <v>2104</v>
+        <v>2498</v>
+      </c>
+      <c r="C276" s="34" t="s">
+        <v>2500</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2515</v>
-      </c>
-      <c r="C277" s="32" t="s">
-        <v>2104</v>
+        <v>2499</v>
+      </c>
+      <c r="C277" s="34" t="s">
+        <v>2500</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2516</v>
+        <v>2503</v>
       </c>
       <c r="C278" s="32" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2517</v>
-      </c>
-      <c r="C279" s="34" t="s">
-        <v>2274</v>
+        <v>2504</v>
+      </c>
+      <c r="C279" s="32" t="s">
+        <v>2095</v>
       </c>
     </row>
     <row r="280" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B280" s="31" t="s">
-        <v>2518</v>
+        <v>2505</v>
+      </c>
+      <c r="C280" s="32" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B281" s="31" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C281" s="34" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B282" s="31" t="s">
+        <v>2507</v>
+      </c>
+      <c r="C282" s="34" t="s">
+        <v>2263</v>
       </c>
     </row>
   </sheetData>
@@ -29516,100 +30275,103 @@
     <hyperlink ref="C72:C91" r:id="rId35" display="沿革？" xr:uid="{F4EE62D7-4C6F-4EA2-9B9C-33FB3A6EC0E3}"/>
     <hyperlink ref="C92" r:id="rId36" xr:uid="{583C6BD0-F972-4FCE-9396-2CBCC08D6FDE}"/>
     <hyperlink ref="C93" r:id="rId37" xr:uid="{F06D86F4-AB96-409E-8DDD-94645E5FE304}"/>
-    <hyperlink ref="C94" r:id="rId38" xr:uid="{650ECBC7-1D3E-47F9-A04B-91409F4AFD82}"/>
-    <hyperlink ref="C95" r:id="rId39" xr:uid="{75F24C6E-979A-4ECB-95F5-2AB7E52FFB3E}"/>
-    <hyperlink ref="C96" r:id="rId40" xr:uid="{D9C0E6B3-F6F4-4826-91A7-073BB4A33382}"/>
-    <hyperlink ref="C98" r:id="rId41" xr:uid="{C71D6526-B182-4F76-AF5F-B6B680D9C45A}"/>
-    <hyperlink ref="C99:C107" r:id="rId42" display="そば屋" xr:uid="{40157A7E-CAB9-47AA-A338-F67391C4503D}"/>
-    <hyperlink ref="C97" r:id="rId43" xr:uid="{420879CC-989A-4756-8081-0E73B34C1E0E}"/>
-    <hyperlink ref="C109" r:id="rId44" xr:uid="{08AFE583-4426-461B-979B-F49FE83DAB8B}"/>
-    <hyperlink ref="C110" r:id="rId45" xr:uid="{4B7DEC01-3433-493D-B1C4-DB5A8E94100F}"/>
-    <hyperlink ref="C111" r:id="rId46" xr:uid="{033DA32D-FAE1-4F14-8183-633E4BD0685F}"/>
-    <hyperlink ref="C112" r:id="rId47" xr:uid="{F5795EE1-139B-45EA-B58B-15E854EAAE5A}"/>
-    <hyperlink ref="C108" r:id="rId48" xr:uid="{F2014E68-B566-4189-B5F6-D6EDBE18923E}"/>
-    <hyperlink ref="C113" r:id="rId49" xr:uid="{15F4FF79-5F95-4C8F-A6B7-69888A1FCE6D}"/>
-    <hyperlink ref="C114:C118" r:id="rId50" display="化しょう屋" xr:uid="{C36F89E4-6767-4188-A309-322ABD51A23A}"/>
-    <hyperlink ref="C119" r:id="rId51" xr:uid="{B25A19F7-C29D-4D44-AC0C-A8DB47267A0C}"/>
-    <hyperlink ref="C120" r:id="rId52" xr:uid="{A1A626FD-0CE4-486F-8590-123D1319E54C}"/>
-    <hyperlink ref="C121" r:id="rId53" xr:uid="{1F8B8F90-51A5-4592-921F-1E537FBAAB02}"/>
-    <hyperlink ref="C122" r:id="rId54" xr:uid="{87BFCFB8-139F-4781-AF48-25318B2E8D71}"/>
-    <hyperlink ref="C123" r:id="rId55" xr:uid="{F40A3028-CD41-4895-810E-85739533F5BA}"/>
-    <hyperlink ref="C124" r:id="rId56" xr:uid="{C3EF1F2D-B6BA-4AE2-8B14-1F43AFE56D4E}"/>
-    <hyperlink ref="C125" r:id="rId57" xr:uid="{D6C949E3-BDA6-4B98-8D49-849E42D416EA}"/>
-    <hyperlink ref="C126:C132" r:id="rId58" display="すし屋" xr:uid="{19CFE92A-BD95-4F91-A784-CB5138E9E5C4}"/>
-    <hyperlink ref="C133" r:id="rId59" xr:uid="{C0DB6F37-9F22-4FB7-9A59-FCA8F06DF804}"/>
-    <hyperlink ref="C134:C138" r:id="rId60" display="らーめん屋" xr:uid="{63D1B813-7B17-494F-BFD0-6ED9C23C668E}"/>
-    <hyperlink ref="C139" r:id="rId61" xr:uid="{64CD0AF5-A92E-4E7F-AE38-241FA8F9302D}"/>
-    <hyperlink ref="C140:C143" r:id="rId62" display="ばー" xr:uid="{BEED3297-1DC6-4F65-91E1-A74DB10D382C}"/>
-    <hyperlink ref="C144" r:id="rId63" xr:uid="{C5C057AE-4947-4F4D-ADF4-6DFE9B7B1190}"/>
-    <hyperlink ref="C145:C146" r:id="rId64" display="とこ屋" xr:uid="{B04EB1D9-D776-4BFF-BCDF-98FA89FFC4F6}"/>
-    <hyperlink ref="C147" r:id="rId65" xr:uid="{46895BCD-A492-42BA-8537-5F5398E80386}"/>
-    <hyperlink ref="C148:C155" r:id="rId66" display="いざか屋" xr:uid="{39266F4C-B934-4957-9402-7811D42AFD6B}"/>
-    <hyperlink ref="C156" r:id="rId67" xr:uid="{F198DF54-7E95-4394-BF80-8CA922FC47ED}"/>
-    <hyperlink ref="C157:C159" r:id="rId68" display="おにぎり屋" xr:uid="{398BF49B-AA77-45F5-BA77-9B3365BBE736}"/>
-    <hyperlink ref="C160" r:id="rId69" xr:uid="{F98B3542-E61E-4C4A-A541-D41290107680}"/>
-    <hyperlink ref="C161:C167" r:id="rId70" display="中かりょうり屋" xr:uid="{AE87470A-3000-4C0E-8365-72BCD5DCBF4F}"/>
-    <hyperlink ref="C168" r:id="rId71" xr:uid="{0363DCBF-B486-4536-A7A7-05A05D0E5287}"/>
-    <hyperlink ref="C169:C171" r:id="rId72" display="きっさ屋" xr:uid="{0041D719-6E11-42B7-8456-4D8C7DB65987}"/>
-    <hyperlink ref="C172" r:id="rId73" xr:uid="{D6B4BEFA-5954-43EB-B798-B392F55C96FE}"/>
-    <hyperlink ref="C173:C176" r:id="rId74" display="花屋" xr:uid="{21461B74-589B-4F4E-B344-8583D17BD3E1}"/>
-    <hyperlink ref="C177" r:id="rId75" xr:uid="{FB788C7B-4C32-4CE4-91C4-B0A314142046}"/>
-    <hyperlink ref="C180" r:id="rId76" xr:uid="{D8150307-7C4F-4883-93D1-DE938BDA255F}"/>
+    <hyperlink ref="C95" r:id="rId38" xr:uid="{650ECBC7-1D3E-47F9-A04B-91409F4AFD82}"/>
+    <hyperlink ref="C96" r:id="rId39" xr:uid="{75F24C6E-979A-4ECB-95F5-2AB7E52FFB3E}"/>
+    <hyperlink ref="C97" r:id="rId40" xr:uid="{D9C0E6B3-F6F4-4826-91A7-073BB4A33382}"/>
+    <hyperlink ref="C99" r:id="rId41" xr:uid="{C71D6526-B182-4F76-AF5F-B6B680D9C45A}"/>
+    <hyperlink ref="C100:C108" r:id="rId42" display="そば屋" xr:uid="{40157A7E-CAB9-47AA-A338-F67391C4503D}"/>
+    <hyperlink ref="C98" r:id="rId43" xr:uid="{420879CC-989A-4756-8081-0E73B34C1E0E}"/>
+    <hyperlink ref="C110" r:id="rId44" xr:uid="{08AFE583-4426-461B-979B-F49FE83DAB8B}"/>
+    <hyperlink ref="C111" r:id="rId45" xr:uid="{4B7DEC01-3433-493D-B1C4-DB5A8E94100F}"/>
+    <hyperlink ref="C112" r:id="rId46" xr:uid="{033DA32D-FAE1-4F14-8183-633E4BD0685F}"/>
+    <hyperlink ref="C113" r:id="rId47" xr:uid="{F5795EE1-139B-45EA-B58B-15E854EAAE5A}"/>
+    <hyperlink ref="C109" r:id="rId48" xr:uid="{F2014E68-B566-4189-B5F6-D6EDBE18923E}"/>
+    <hyperlink ref="C114" r:id="rId49" xr:uid="{15F4FF79-5F95-4C8F-A6B7-69888A1FCE6D}"/>
+    <hyperlink ref="C115:C119" r:id="rId50" display="化しょう屋" xr:uid="{C36F89E4-6767-4188-A309-322ABD51A23A}"/>
+    <hyperlink ref="C120" r:id="rId51" xr:uid="{B25A19F7-C29D-4D44-AC0C-A8DB47267A0C}"/>
+    <hyperlink ref="C121" r:id="rId52" xr:uid="{A1A626FD-0CE4-486F-8590-123D1319E54C}"/>
+    <hyperlink ref="C122" r:id="rId53" xr:uid="{1F8B8F90-51A5-4592-921F-1E537FBAAB02}"/>
+    <hyperlink ref="C123" r:id="rId54" xr:uid="{87BFCFB8-139F-4781-AF48-25318B2E8D71}"/>
+    <hyperlink ref="C124" r:id="rId55" xr:uid="{F40A3028-CD41-4895-810E-85739533F5BA}"/>
+    <hyperlink ref="C125" r:id="rId56" xr:uid="{C3EF1F2D-B6BA-4AE2-8B14-1F43AFE56D4E}"/>
+    <hyperlink ref="C126" r:id="rId57" xr:uid="{D6C949E3-BDA6-4B98-8D49-849E42D416EA}"/>
+    <hyperlink ref="C127:C133" r:id="rId58" display="すし屋" xr:uid="{19CFE92A-BD95-4F91-A784-CB5138E9E5C4}"/>
+    <hyperlink ref="C134" r:id="rId59" xr:uid="{C0DB6F37-9F22-4FB7-9A59-FCA8F06DF804}"/>
+    <hyperlink ref="C135:C139" r:id="rId60" display="らーめん屋" xr:uid="{63D1B813-7B17-494F-BFD0-6ED9C23C668E}"/>
+    <hyperlink ref="C140" r:id="rId61" xr:uid="{64CD0AF5-A92E-4E7F-AE38-241FA8F9302D}"/>
+    <hyperlink ref="C141:C144" r:id="rId62" display="ばー" xr:uid="{BEED3297-1DC6-4F65-91E1-A74DB10D382C}"/>
+    <hyperlink ref="C145" r:id="rId63" xr:uid="{C5C057AE-4947-4F4D-ADF4-6DFE9B7B1190}"/>
+    <hyperlink ref="C146:C147" r:id="rId64" display="とこ屋" xr:uid="{B04EB1D9-D776-4BFF-BCDF-98FA89FFC4F6}"/>
+    <hyperlink ref="C148" r:id="rId65" xr:uid="{46895BCD-A492-42BA-8537-5F5398E80386}"/>
+    <hyperlink ref="C149:C156" r:id="rId66" display="いざか屋" xr:uid="{39266F4C-B934-4957-9402-7811D42AFD6B}"/>
+    <hyperlink ref="C157" r:id="rId67" xr:uid="{F198DF54-7E95-4394-BF80-8CA922FC47ED}"/>
+    <hyperlink ref="C158:C160" r:id="rId68" display="おにぎり屋" xr:uid="{398BF49B-AA77-45F5-BA77-9B3365BBE736}"/>
+    <hyperlink ref="C161" r:id="rId69" xr:uid="{F98B3542-E61E-4C4A-A541-D41290107680}"/>
+    <hyperlink ref="C162:C168" r:id="rId70" display="中かりょうり屋" xr:uid="{AE87470A-3000-4C0E-8365-72BCD5DCBF4F}"/>
+    <hyperlink ref="C169" r:id="rId71" xr:uid="{0363DCBF-B486-4536-A7A7-05A05D0E5287}"/>
+    <hyperlink ref="C170:C172" r:id="rId72" display="きっさ屋" xr:uid="{0041D719-6E11-42B7-8456-4D8C7DB65987}"/>
+    <hyperlink ref="C173" r:id="rId73" xr:uid="{D6B4BEFA-5954-43EB-B798-B392F55C96FE}"/>
+    <hyperlink ref="C174:C177" r:id="rId74" display="花屋" xr:uid="{21461B74-589B-4F4E-B344-8583D17BD3E1}"/>
+    <hyperlink ref="C178" r:id="rId75" xr:uid="{FB788C7B-4C32-4CE4-91C4-B0A314142046}"/>
+    <hyperlink ref="C181" r:id="rId76" xr:uid="{D8150307-7C4F-4883-93D1-DE938BDA255F}"/>
     <hyperlink ref="D132" r:id="rId77" xr:uid="{D7B5F7EF-8A3E-4EF9-BE9B-87BD25B1DEC3}"/>
-    <hyperlink ref="C181:C183" r:id="rId78" display="うらない屋" xr:uid="{BD5B9AA7-BEE9-4B4D-869C-96CBA2E0AB53}"/>
-    <hyperlink ref="C184" r:id="rId79" xr:uid="{A956E415-925E-4BE7-8C7B-34E6470531C7}"/>
-    <hyperlink ref="C185:C186" r:id="rId80" display="じゃずばー" xr:uid="{F3C1261E-4D64-4AF6-B5B1-D120DE06DE1E}"/>
-    <hyperlink ref="C187" r:id="rId81" xr:uid="{23FCEF9A-0D1E-42CA-AFD5-D7B4C91E6D26}"/>
-    <hyperlink ref="C188:C190" r:id="rId82" display="れこーど屋" xr:uid="{67DEEB48-8CEC-4228-8750-64B86E077C59}"/>
-    <hyperlink ref="C191" r:id="rId83" xr:uid="{80EE8314-4DD1-46C4-AE4C-CA0FD6A68933}"/>
-    <hyperlink ref="C192:C194" r:id="rId84" display="くつ屋" xr:uid="{3788FC8E-1620-4335-8625-8DCA71AC925D}"/>
+    <hyperlink ref="C182:C184" r:id="rId78" display="うらない屋" xr:uid="{BD5B9AA7-BEE9-4B4D-869C-96CBA2E0AB53}"/>
+    <hyperlink ref="C185" r:id="rId79" xr:uid="{A956E415-925E-4BE7-8C7B-34E6470531C7}"/>
+    <hyperlink ref="C186:C187" r:id="rId80" display="じゃずばー" xr:uid="{F3C1261E-4D64-4AF6-B5B1-D120DE06DE1E}"/>
+    <hyperlink ref="C188" r:id="rId81" xr:uid="{23FCEF9A-0D1E-42CA-AFD5-D7B4C91E6D26}"/>
+    <hyperlink ref="C189:C191" r:id="rId82" display="れこーど屋" xr:uid="{67DEEB48-8CEC-4228-8750-64B86E077C59}"/>
+    <hyperlink ref="C192" r:id="rId83" xr:uid="{80EE8314-4DD1-46C4-AE4C-CA0FD6A68933}"/>
+    <hyperlink ref="C193:C195" r:id="rId84" display="くつ屋" xr:uid="{3788FC8E-1620-4335-8625-8DCA71AC925D}"/>
     <hyperlink ref="D158" r:id="rId85" xr:uid="{1AC6C13F-D00F-4482-98BE-1C2CCF13D05D}"/>
-    <hyperlink ref="C195" r:id="rId86" xr:uid="{63988F07-EA6D-4F26-9226-45FD114364DC}"/>
-    <hyperlink ref="C196:C198" r:id="rId87" display="本屋" xr:uid="{2A3A625B-6EA8-437E-81C7-68CF5E700BFC}"/>
-    <hyperlink ref="C199" r:id="rId88" xr:uid="{11E58C7C-D20F-4332-BA3A-857C1491B32B}"/>
-    <hyperlink ref="C200:C203" r:id="rId89" display="けーき屋" xr:uid="{88195962-BB93-453B-81A1-52FA5CBE67AF}"/>
-    <hyperlink ref="C204" r:id="rId90" xr:uid="{724A06D0-79BF-46A2-B58C-0C3ECBBFDB45}"/>
-    <hyperlink ref="C205:C209" r:id="rId91" display="清そう屋" xr:uid="{9E37B236-0ED6-47F6-BF18-86B12BD98E6B}"/>
-    <hyperlink ref="C210" r:id="rId92" xr:uid="{EF971420-17D4-4182-8132-56F00A167A2C}"/>
-    <hyperlink ref="C211:C213" r:id="rId93" display="時けい屋" xr:uid="{6C295750-0F27-47E0-9129-453CA0F3E98B}"/>
-    <hyperlink ref="C214" r:id="rId94" xr:uid="{DB4BE4EC-BA0C-456D-B5AB-A0C311E10FC4}"/>
-    <hyperlink ref="C215:C216" r:id="rId95" display="くすり屋" xr:uid="{C21A8AF9-DE63-4441-BD5E-F5FF047CB554}"/>
-    <hyperlink ref="C217" r:id="rId96" xr:uid="{D901BE77-9912-45E3-9CE7-FF143E1A7C55}"/>
-    <hyperlink ref="C219:C220" r:id="rId97" display="くりーにんぐ屋" xr:uid="{404FE6C1-57C6-4D57-9720-912B76B3036C}"/>
-    <hyperlink ref="C218" r:id="rId98" xr:uid="{E32A61DB-E7C1-4C00-A9EA-3C2EE69560FA}"/>
-    <hyperlink ref="C221" r:id="rId99" xr:uid="{F3012094-E137-4787-AE48-4A8F62EFE745}"/>
-    <hyperlink ref="C222" r:id="rId100" xr:uid="{25CF5C66-B1C6-4B3A-84C7-C4ADF6D77959}"/>
-    <hyperlink ref="C224" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
-    <hyperlink ref="C225:C227" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
-    <hyperlink ref="C228" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
-    <hyperlink ref="C229:C230" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
-    <hyperlink ref="C231" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
-    <hyperlink ref="C232:C235" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
-    <hyperlink ref="C236" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
-    <hyperlink ref="C237" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
-    <hyperlink ref="C238" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
-    <hyperlink ref="C239" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
-    <hyperlink ref="C240:C243" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
-    <hyperlink ref="C223" r:id="rId112" display="●壁？" xr:uid="{49CFE894-D6FF-4DAD-A18A-E33C19DC9AC5}"/>
-    <hyperlink ref="C244" r:id="rId113" xr:uid="{9AC2C8BA-0A2B-4264-BFE4-5067BC7FCBBD}"/>
-    <hyperlink ref="C245:C250" r:id="rId114" display="なき子" xr:uid="{CCC49224-E3E0-47BD-9BA3-ED7C3711BAF4}"/>
-    <hyperlink ref="D75" r:id="rId115" xr:uid="{F3D3E429-A98C-4A89-8517-136EBFF9C669}"/>
-    <hyperlink ref="C251" r:id="rId116" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
-    <hyperlink ref="C252" r:id="rId117" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
-    <hyperlink ref="C253:C254" r:id="rId118" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
-    <hyperlink ref="C255" r:id="rId119" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
-    <hyperlink ref="C256:C262" r:id="rId120" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
-    <hyperlink ref="C263" r:id="rId121" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
-    <hyperlink ref="C264:C270" r:id="rId122" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
-    <hyperlink ref="C271" r:id="rId123" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
-    <hyperlink ref="C272" r:id="rId124" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
-    <hyperlink ref="C273" r:id="rId125" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
-    <hyperlink ref="C274" r:id="rId126" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
-    <hyperlink ref="C275" r:id="rId127" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
-    <hyperlink ref="C276" r:id="rId128" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
-    <hyperlink ref="C277" r:id="rId129" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
-    <hyperlink ref="C278" r:id="rId130" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
-    <hyperlink ref="C279" r:id="rId131" xr:uid="{638B7DD6-1594-44CE-9207-871F21E21DD3}"/>
+    <hyperlink ref="C196" r:id="rId86" xr:uid="{63988F07-EA6D-4F26-9226-45FD114364DC}"/>
+    <hyperlink ref="C197:C199" r:id="rId87" display="本屋" xr:uid="{2A3A625B-6EA8-437E-81C7-68CF5E700BFC}"/>
+    <hyperlink ref="C200" r:id="rId88" xr:uid="{11E58C7C-D20F-4332-BA3A-857C1491B32B}"/>
+    <hyperlink ref="C201:C204" r:id="rId89" display="けーき屋" xr:uid="{88195962-BB93-453B-81A1-52FA5CBE67AF}"/>
+    <hyperlink ref="C205" r:id="rId90" xr:uid="{724A06D0-79BF-46A2-B58C-0C3ECBBFDB45}"/>
+    <hyperlink ref="C206:C210" r:id="rId91" display="清そう屋" xr:uid="{9E37B236-0ED6-47F6-BF18-86B12BD98E6B}"/>
+    <hyperlink ref="C211" r:id="rId92" xr:uid="{EF971420-17D4-4182-8132-56F00A167A2C}"/>
+    <hyperlink ref="C212:C214" r:id="rId93" display="時けい屋" xr:uid="{6C295750-0F27-47E0-9129-453CA0F3E98B}"/>
+    <hyperlink ref="C215" r:id="rId94" xr:uid="{DB4BE4EC-BA0C-456D-B5AB-A0C311E10FC4}"/>
+    <hyperlink ref="C216:C217" r:id="rId95" display="くすり屋" xr:uid="{C21A8AF9-DE63-4441-BD5E-F5FF047CB554}"/>
+    <hyperlink ref="C218" r:id="rId96" xr:uid="{D901BE77-9912-45E3-9CE7-FF143E1A7C55}"/>
+    <hyperlink ref="C220:C221" r:id="rId97" display="くりーにんぐ屋" xr:uid="{404FE6C1-57C6-4D57-9720-912B76B3036C}"/>
+    <hyperlink ref="C219" r:id="rId98" xr:uid="{E32A61DB-E7C1-4C00-A9EA-3C2EE69560FA}"/>
+    <hyperlink ref="C222" r:id="rId99" xr:uid="{F3012094-E137-4787-AE48-4A8F62EFE745}"/>
+    <hyperlink ref="C223" r:id="rId100" xr:uid="{25CF5C66-B1C6-4B3A-84C7-C4ADF6D77959}"/>
+    <hyperlink ref="C225" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
+    <hyperlink ref="C226:C228" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
+    <hyperlink ref="C229" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
+    <hyperlink ref="C230:C231" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
+    <hyperlink ref="C232" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
+    <hyperlink ref="C233:C236" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
+    <hyperlink ref="C237" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
+    <hyperlink ref="C238" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
+    <hyperlink ref="C239" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
+    <hyperlink ref="C240" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
+    <hyperlink ref="C241:C244" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
+    <hyperlink ref="C224" r:id="rId112" display="●壁？" xr:uid="{49CFE894-D6FF-4DAD-A18A-E33C19DC9AC5}"/>
+    <hyperlink ref="D75" r:id="rId113" xr:uid="{F3D3E429-A98C-4A89-8517-136EBFF9C669}"/>
+    <hyperlink ref="C253" r:id="rId114" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
+    <hyperlink ref="C254" r:id="rId115" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
+    <hyperlink ref="C255:C256" r:id="rId116" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
+    <hyperlink ref="C257" r:id="rId117" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
+    <hyperlink ref="C258:C264" r:id="rId118" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
+    <hyperlink ref="C265" r:id="rId119" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
+    <hyperlink ref="C266:C272" r:id="rId120" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
+    <hyperlink ref="C273" r:id="rId121" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
+    <hyperlink ref="C274" r:id="rId122" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
+    <hyperlink ref="C275" r:id="rId123" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
+    <hyperlink ref="C276" r:id="rId124" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
+    <hyperlink ref="C277" r:id="rId125" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
+    <hyperlink ref="C278" r:id="rId126" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
+    <hyperlink ref="C279" r:id="rId127" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
+    <hyperlink ref="C280" r:id="rId128" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
+    <hyperlink ref="C281" r:id="rId129" xr:uid="{638B7DD6-1594-44CE-9207-871F21E21DD3}"/>
+    <hyperlink ref="C282" r:id="rId130" xr:uid="{0A4BE00D-CD86-4A4E-ADBB-82650B816BF4}"/>
+    <hyperlink ref="C245" r:id="rId131" display="無影言本祭" xr:uid="{8D13B183-FF2F-461F-87EA-DF266C32877C}"/>
+    <hyperlink ref="C246" r:id="rId132" display="無影言本祭" xr:uid="{1204C86E-B414-49FA-9E5E-D39D616244E1}"/>
+    <hyperlink ref="C247:C248" r:id="rId133" display="無影言本祭" xr:uid="{E5562058-48A6-4B14-99CC-EFD928C85B1B}"/>
+    <hyperlink ref="C94" r:id="rId134" xr:uid="{157FEE6A-E3FD-4891-9A8C-DEA390CC9F8A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1704" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA2B493A-716F-467C-900A-BA21F06ECF50}"/>
+  <xr:revisionPtr revIDLastSave="1769" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D64B9D3-CA01-4853-AB6F-BCDA16F5A4EE}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" activeTab="4" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3020" uniqueCount="2591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3070" uniqueCount="2608">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8960,13 +8960,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>後</t>
-    <rPh sb="0" eb="1">
-      <t>ウシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>世</t>
     <rPh sb="0" eb="1">
       <t>ヨ</t>
@@ -11683,6 +11676,133 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体</t>
+    <rPh sb="0" eb="1">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処</t>
+    <rPh sb="0" eb="1">
+      <t>トコロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>台</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飲</t>
+    <rPh sb="0" eb="1">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第2区</t>
+  </si>
+  <si>
+    <t>趣</t>
+    <rPh sb="0" eb="1">
+      <t>オモムキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関</t>
+    <rPh sb="0" eb="1">
+      <t>セキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>工</t>
+    <rPh sb="0" eb="1">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成</t>
+    <rPh sb="0" eb="1">
+      <t>シゲル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第3区</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>復</t>
+    <rPh sb="0" eb="1">
+      <t>マタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>旧</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お客様 ・勀客 ・客を集めて</t>
+    <rPh sb="1" eb="3">
+      <t>キャクサマ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>験</t>
+    <rPh sb="0" eb="1">
+      <t>ゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>故</t>
+    <rPh sb="0" eb="1">
+      <t>ユエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佳一</t>
+  </si>
+  <si>
+    <t>事こ</t>
+    <rPh sb="0" eb="1">
+      <t>コト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -12340,6 +12460,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -12661,7 +12785,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="4" max="4" width="26.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.125" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.375" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.375" style="31" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.125" style="31" bestFit="1" customWidth="1"/>
@@ -14003,7 +14127,7 @@
         <v>2088</v>
       </c>
       <c r="E162" s="34" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.4">
@@ -14014,13 +14138,13 @@
         <v>1697</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="E163" s="34" t="s">
         <v>2092</v>
       </c>
       <c r="F163" s="32" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.4">
@@ -14227,7 +14351,7 @@
         <v>2109</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
@@ -14299,8 +14423,11 @@
       <c r="C192" t="s">
         <v>1740</v>
       </c>
-    </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="E192" s="34" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B193" s="1" t="s">
         <v>1741</v>
       </c>
@@ -14308,7 +14435,7 @@
         <v>1988</v>
       </c>
       <c r="D193" s="33" t="s">
-        <v>2053</v>
+        <v>2603</v>
       </c>
       <c r="E193" s="34" t="s">
         <v>2119</v>
@@ -14319,8 +14446,14 @@
       <c r="G193" s="32" t="s">
         <v>2116</v>
       </c>
-    </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="H193" s="32" t="s">
+        <v>2579</v>
+      </c>
+      <c r="I193" s="34" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B194" s="1" t="s">
         <v>1742</v>
       </c>
@@ -14340,7 +14473,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B195" s="1" t="s">
         <v>1744</v>
       </c>
@@ -14354,7 +14487,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B196" s="1" t="s">
         <v>1746</v>
       </c>
@@ -14362,7 +14495,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B197" s="1" t="s">
         <v>1942</v>
       </c>
@@ -14379,7 +14512,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B198" s="1" t="s">
         <v>1748</v>
       </c>
@@ -14387,7 +14520,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B199" s="1" t="s">
         <v>1943</v>
       </c>
@@ -14404,7 +14537,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B200" s="1" t="s">
         <v>1750</v>
       </c>
@@ -14412,7 +14545,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B201" s="1" t="s">
         <v>1944</v>
       </c>
@@ -14420,7 +14553,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B202" s="1" t="s">
         <v>1753</v>
       </c>
@@ -14428,7 +14561,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="203" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B203" s="1" t="s">
         <v>1755</v>
       </c>
@@ -14436,7 +14569,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="204" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B204" s="1" t="s">
         <v>1757</v>
       </c>
@@ -14444,7 +14577,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="205" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B205" s="1" t="s">
         <v>1945</v>
       </c>
@@ -14464,7 +14597,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="206" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B206" s="1" t="s">
         <v>1946</v>
       </c>
@@ -14472,7 +14605,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B207" s="1" t="s">
         <v>1761</v>
       </c>
@@ -14480,7 +14613,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="208" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B208" s="1" t="s">
         <v>857</v>
       </c>
@@ -14567,13 +14700,13 @@
         <v>1774</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="E216" s="34" t="s">
         <v>2118</v>
       </c>
       <c r="F216" s="32" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
@@ -14713,16 +14846,16 @@
         <v>1952</v>
       </c>
       <c r="C232" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D232" s="33" t="s">
         <v>2583</v>
-      </c>
-      <c r="D232" s="33" t="s">
-        <v>2584</v>
       </c>
       <c r="E232" s="34" t="s">
         <v>2105</v>
       </c>
       <c r="F232" s="32" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.4">
@@ -14917,10 +15050,10 @@
         <v>1959</v>
       </c>
       <c r="C250" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D250" s="33" t="s">
         <v>2501</v>
-      </c>
-      <c r="D250" s="33" t="s">
-        <v>2502</v>
       </c>
       <c r="E250" s="34" t="s">
         <v>2109</v>
@@ -14985,16 +15118,16 @@
         <v>1960</v>
       </c>
       <c r="C257" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="D257" s="33" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="E257" s="34" t="s">
         <v>2089</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
@@ -15013,13 +15146,13 @@
         <v>1836</v>
       </c>
       <c r="D259" s="33" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="E259" s="34" t="s">
         <v>2089</v>
       </c>
       <c r="F259" s="32" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
@@ -15036,7 +15169,7 @@
         <v>2111</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
@@ -15210,7 +15343,7 @@
         <v>2049</v>
       </c>
       <c r="E278" s="42" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.4">
@@ -15224,7 +15357,7 @@
         <v>376</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.4">
@@ -15335,7 +15468,7 @@
         <v>2093</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
@@ -15421,10 +15554,10 @@
         <v>2075</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="F298" s="32" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
@@ -15521,13 +15654,13 @@
         <v>936</v>
       </c>
       <c r="C306" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="D306" s="33" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
@@ -15639,13 +15772,13 @@
         <v>2018</v>
       </c>
       <c r="D314" s="54" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="E314" s="34" t="s">
         <v>2102</v>
       </c>
       <c r="F314" s="32" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
@@ -15662,7 +15795,7 @@
         <v>2101</v>
       </c>
       <c r="F315" s="32" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
@@ -15690,7 +15823,7 @@
         <v>2076</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="F317" s="32" t="s">
         <v>2095</v>
@@ -15707,7 +15840,7 @@
         <v>2077</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
@@ -15721,7 +15854,7 @@
         <v>2079</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="F319" s="32" t="s">
         <v>2095</v>
@@ -15752,7 +15885,7 @@
         <v>2078</v>
       </c>
       <c r="E321" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.4">
@@ -15760,13 +15893,13 @@
         <v>1094</v>
       </c>
       <c r="C322" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="D322" s="33" t="s">
         <v>2120</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="F322" s="32" t="s">
         <v>2095</v>
@@ -15777,19 +15910,19 @@
         <v>296</v>
       </c>
       <c r="C323" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="D323" s="33" t="s">
         <v>2135</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="F323" s="32" t="s">
         <v>2095</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.4">
@@ -15831,10 +15964,10 @@
         <v>2012</v>
       </c>
       <c r="C326" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="E326" s="34" t="s">
         <v>2094</v>
@@ -15845,16 +15978,16 @@
         <v>1993</v>
       </c>
       <c r="C327" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="E327" s="34" t="s">
         <v>2093</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.4">
@@ -15862,13 +15995,13 @@
         <v>407</v>
       </c>
       <c r="C328" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="E328" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.4">
@@ -15876,13 +16009,16 @@
         <v>160</v>
       </c>
       <c r="C329" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="D329" s="41" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="E329" s="42" t="s">
-        <v>2468</v>
+        <v>2467</v>
+      </c>
+      <c r="F329" s="32" t="s">
+        <v>2579</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.4">
@@ -15890,27 +16026,30 @@
         <v>1103</v>
       </c>
       <c r="C330" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="D330" s="33" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E330" s="42" t="s">
         <v>2467</v>
       </c>
-      <c r="E330" s="42" t="s">
-        <v>2468</v>
+      <c r="F330" s="32" t="s">
+        <v>2579</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B331" s="1" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C331" t="s">
+        <v>2527</v>
+      </c>
+      <c r="D331" s="43" t="s">
         <v>2509</v>
       </c>
-      <c r="C331" t="s">
-        <v>2528</v>
-      </c>
-      <c r="D331" s="43" t="s">
+      <c r="E331" s="34" t="s">
         <v>2510</v>
-      </c>
-      <c r="E331" s="34" t="s">
-        <v>2511</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.4">
@@ -15918,55 +16057,55 @@
         <v>1147</v>
       </c>
       <c r="C332" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="D332" s="33" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="E332" s="34" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B333" s="1" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="C333" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="D333" s="33" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="E333" s="34" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B334" s="1" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="C334" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="D334" s="41" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E334" s="34" t="s">
         <v>2516</v>
-      </c>
-      <c r="E334" s="34" t="s">
-        <v>2517</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C335" t="s">
+        <v>2519</v>
+      </c>
+      <c r="D335" s="41" t="s">
         <v>2515</v>
       </c>
-      <c r="C335" t="s">
-        <v>2520</v>
-      </c>
-      <c r="D335" s="41" t="s">
+      <c r="E335" s="34" t="s">
         <v>2516</v>
-      </c>
-      <c r="E335" s="34" t="s">
-        <v>2517</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.4">
@@ -15979,41 +16118,41 @@
         <v>1762</v>
       </c>
       <c r="C337" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="E337" s="34" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B338" s="1" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C338" t="s">
         <v>2573</v>
       </c>
-      <c r="C338" t="s">
+      <c r="D338" s="33" t="s">
         <v>2574</v>
       </c>
-      <c r="D338" s="33" t="s">
-        <v>2575</v>
-      </c>
       <c r="E338" s="34" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B339" s="1" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C339" s="55" t="s">
         <v>2587</v>
       </c>
-      <c r="C339" s="55" t="s">
+      <c r="D339" s="33" t="s">
         <v>2588</v>
       </c>
-      <c r="D339" s="33" t="s">
-        <v>2589</v>
-      </c>
       <c r="E339" s="32" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
     </row>
   </sheetData>
@@ -16152,9 +16291,14 @@
     <hyperlink ref="F232" r:id="rId118" xr:uid="{35EA88DE-206B-4EF8-9259-9E1E793C9E5B}"/>
     <hyperlink ref="F314" r:id="rId119" xr:uid="{00BD4916-443C-4D61-ADBA-08351BF0AA95}"/>
     <hyperlink ref="E339" r:id="rId120" xr:uid="{35DD3EBE-71F4-4631-AFA7-387F800E7B2F}"/>
+    <hyperlink ref="F330" r:id="rId121" xr:uid="{411BBBFD-4B20-4B8E-B6D7-4425E0FB9182}"/>
+    <hyperlink ref="F329" r:id="rId122" xr:uid="{8FE7C2D8-229B-435B-8354-9A0EA83B7570}"/>
+    <hyperlink ref="H193" r:id="rId123" xr:uid="{5A06E54E-D7FA-4163-B78F-09FB36783946}"/>
+    <hyperlink ref="E192" r:id="rId124" xr:uid="{F1E432DC-CBD9-4441-B594-95C84BFC9DE2}"/>
+    <hyperlink ref="I193" r:id="rId125" xr:uid="{26BA6F02-E1EA-4539-82D4-14963B73A27E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId121"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId126"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -20322,8 +20466,8 @@
         <v>526</v>
       </c>
       <c r="BC9" s="6" t="str">
-        <f>_xlfn.XLOOKUP(BB9,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(BB9,対応表!$B:$B,対応表!$C:$C,"く")</f>
+        <v>く</v>
       </c>
       <c r="BD9" s="7" t="s">
         <v>527</v>
@@ -21350,8 +21494,8 @@
         <v>668</v>
       </c>
       <c r="BC11" s="6" t="str">
-        <f>_xlfn.XLOOKUP(BB11,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(BB11,対応表!$B:$B,対応表!$C:$C,"を")</f>
+        <v>を</v>
       </c>
       <c r="BD11" s="7" t="s">
         <v>669</v>
@@ -27484,7 +27628,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C5E931-1AEC-434D-81A1-3EA98DBB914E}">
-  <dimension ref="B1:E34"/>
+  <dimension ref="B1:E35"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.25" style="35" bestFit="1" customWidth="1"/>
@@ -27504,7 +27648,7 @@
         <v>2131</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
@@ -27518,217 +27662,217 @@
         <v>2128</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C3" s="36" t="s">
         <v>2237</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="D3" s="36" t="s">
         <v>2238</v>
       </c>
-      <c r="D3" s="36" t="s">
-        <v>2239</v>
-      </c>
       <c r="E3" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C4" s="36" t="s">
         <v>2240</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="D4" s="36" t="s">
         <v>2241</v>
       </c>
-      <c r="D4" s="36" t="s">
-        <v>2242</v>
-      </c>
       <c r="E4" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C5" s="36" t="s">
         <v>2243</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="D5" s="36" t="s">
         <v>2244</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>2245</v>
-      </c>
       <c r="E5" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>2246</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="D6" s="36" t="s">
         <v>2247</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>2248</v>
-      </c>
       <c r="E6" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>2249</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="D7" s="36" t="s">
         <v>2250</v>
       </c>
-      <c r="D7" s="36" t="s">
-        <v>2251</v>
-      </c>
       <c r="E7" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>2064</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>2254</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="D9" s="36" t="s">
         <v>2255</v>
       </c>
-      <c r="D9" s="36" t="s">
-        <v>2256</v>
-      </c>
       <c r="E9" s="36" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>2062</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C11" s="36" t="s">
         <v>2259</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="D11" s="36" t="s">
         <v>2260</v>
       </c>
-      <c r="D11" s="36" t="s">
-        <v>2261</v>
-      </c>
       <c r="E11" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C12" s="40" t="s">
         <v>2262</v>
       </c>
-      <c r="C12" s="40" t="s">
-        <v>2263</v>
-      </c>
       <c r="D12" s="40" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>2066</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C14" s="36" t="s">
         <v>2342</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>2343</v>
-      </c>
       <c r="D14" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
+        <v>2415</v>
+      </c>
+      <c r="C16" s="36" t="s">
         <v>2416</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>2417</v>
-      </c>
       <c r="D16" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
@@ -27736,213 +27880,248 @@
         <v>2087</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
+        <v>2459</v>
+      </c>
+      <c r="C19" s="36" t="s">
         <v>2460</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="D19" s="36" t="s">
         <v>2461</v>
       </c>
-      <c r="D19" s="36" t="s">
-        <v>2462</v>
-      </c>
       <c r="E19" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="44" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="35" t="s">
+        <v>2534</v>
+      </c>
+      <c r="C21" s="36" t="s">
         <v>2535</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="D21" s="36" t="s">
         <v>2536</v>
       </c>
-      <c r="D21" s="36" t="s">
-        <v>2537</v>
-      </c>
       <c r="E21" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="35" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C22" s="36" t="s">
         <v>2538</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="D22" s="36" t="s">
         <v>2539</v>
       </c>
-      <c r="D22" s="36" t="s">
-        <v>2540</v>
-      </c>
       <c r="E22" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="35" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C23" s="36" t="s">
         <v>2541</v>
       </c>
-      <c r="C23" s="36" t="s">
-        <v>2542</v>
-      </c>
       <c r="D23" s="36" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="35" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C24" s="36" t="s">
         <v>2543</v>
       </c>
-      <c r="C24" s="36" t="s">
-        <v>2544</v>
-      </c>
       <c r="D24" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="35" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C25" s="36" t="s">
         <v>2545</v>
       </c>
-      <c r="C25" s="36" t="s">
-        <v>2546</v>
-      </c>
       <c r="D25" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B26" s="35" t="s">
+        <v>2546</v>
+      </c>
+      <c r="C26" s="36" t="s">
         <v>2547</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="D26" s="36" t="s">
         <v>2548</v>
       </c>
-      <c r="D26" s="36" t="s">
-        <v>2549</v>
-      </c>
       <c r="E26" s="36" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="35" t="s">
+        <v>2553</v>
+      </c>
+      <c r="C27" s="36" t="s">
         <v>2554</v>
       </c>
-      <c r="C27" s="36" t="s">
-        <v>2555</v>
-      </c>
       <c r="D27" s="36" t="s">
-        <v>2567</v>
+        <v>2566</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="35" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C28" s="36" t="s">
         <v>2556</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>2557</v>
-      </c>
       <c r="D28" s="36" t="s">
-        <v>2560</v>
+        <v>2559</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="35" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C29" s="36" t="s">
         <v>2558</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>2559</v>
-      </c>
       <c r="D29" s="36" t="s">
-        <v>2261</v>
+        <v>2260</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B30" s="35" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C30" s="36" t="s">
         <v>2561</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>2562</v>
-      </c>
       <c r="D30" s="36" t="s">
-        <v>2248</v>
+        <v>2247</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B31" s="35" t="s">
+        <v>2562</v>
+      </c>
+      <c r="C31" s="36" t="s">
         <v>2563</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>2564</v>
-      </c>
       <c r="D31" s="36" t="s">
-        <v>2248</v>
+        <v>2247</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>2344</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" s="35" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C32" s="36" t="s">
         <v>2565</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="D32" s="36" t="s">
         <v>2566</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="E32" s="36" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B33" s="35" t="s">
         <v>2567</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B33" s="35" t="s">
+      <c r="C33" s="36" t="s">
         <v>2568</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="D33" s="36" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B34" s="39" t="s">
         <v>2569</v>
       </c>
-      <c r="D33" s="36" t="s">
-        <v>2567</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B34" s="35" t="s">
+      <c r="C34" s="40" t="s">
         <v>2570</v>
       </c>
-      <c r="C34" s="36" t="s">
-        <v>2571</v>
-      </c>
-      <c r="D34" s="36" t="s">
-        <v>2261</v>
+      <c r="D34" s="40" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B35" s="35" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>2607</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>2260</v>
       </c>
     </row>
   </sheetData>
@@ -27953,7 +28132,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED28C13D-14D9-4671-B3CF-1ADD2E368C21}">
-  <dimension ref="B1:D282"/>
+  <dimension ref="B1:D297"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="31"/>
@@ -28220,15 +28399,18 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
         <v>2176</v>
       </c>
       <c r="C33" s="34" t="s">
         <v>2093</v>
       </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="D33" s="34" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
         <v>2177</v>
       </c>
@@ -28236,7 +28418,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
         <v>2178</v>
       </c>
@@ -28244,7 +28426,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
         <v>2179</v>
       </c>
@@ -28252,7 +28434,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
         <v>2180</v>
       </c>
@@ -28260,7 +28442,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
         <v>2181</v>
       </c>
@@ -28268,15 +28450,18 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
         <v>2182</v>
       </c>
       <c r="C39" s="34" t="s">
         <v>2112</v>
       </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="D39" s="34" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
         <v>2183</v>
       </c>
@@ -28284,7 +28469,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
         <v>2184</v>
       </c>
@@ -28292,7 +28477,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
         <v>2185</v>
       </c>
@@ -28300,7 +28485,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
         <v>2186</v>
       </c>
@@ -28308,7 +28493,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
         <v>2197</v>
       </c>
@@ -28316,7 +28501,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
         <v>2187</v>
       </c>
@@ -28324,7 +28509,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
         <v>2188</v>
       </c>
@@ -28332,7 +28517,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
         <v>2189</v>
       </c>
@@ -28340,7 +28525,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B48" s="31" t="s">
         <v>1161</v>
       </c>
@@ -28348,7 +28533,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
         <v>2190</v>
       </c>
@@ -28356,7 +28541,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
         <v>2191</v>
       </c>
@@ -28364,7 +28549,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
         <v>2192</v>
       </c>
@@ -28372,7 +28557,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
         <v>2193</v>
       </c>
@@ -28380,7 +28565,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
         <v>2194</v>
       </c>
@@ -28388,7 +28573,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
         <v>2195</v>
       </c>
@@ -28396,7 +28581,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B55" s="31" t="s">
         <v>2198</v>
       </c>
@@ -28404,7 +28589,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
         <v>2199</v>
       </c>
@@ -28412,7 +28597,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
         <v>2200</v>
       </c>
@@ -28420,7 +28605,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
         <v>2201</v>
       </c>
@@ -28428,7 +28613,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
         <v>2202</v>
       </c>
@@ -28436,7 +28621,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
         <v>2203</v>
       </c>
@@ -28444,7 +28629,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
         <v>2204</v>
       </c>
@@ -28452,15 +28637,18 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
         <v>2205</v>
       </c>
       <c r="C62" s="34" t="s">
         <v>2111</v>
       </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="D62" s="32" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
         <v>2206</v>
       </c>
@@ -28468,7 +28656,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
         <v>2207</v>
       </c>
@@ -28555,6 +28743,9 @@
       <c r="C74" s="34" t="s">
         <v>2089</v>
       </c>
+      <c r="D74" s="34" t="s">
+        <v>2102</v>
+      </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
@@ -28563,9 +28754,6 @@
       <c r="C75" s="34" t="s">
         <v>2089</v>
       </c>
-      <c r="D75" s="34" t="s">
-        <v>2102</v>
-      </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
@@ -28689,37 +28877,40 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B91" s="31" t="s">
-        <v>2236</v>
+        <v>2264</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>2089</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B92" s="31" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>2266</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B93" s="31" t="s">
-        <v>2267</v>
+        <v>2457</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>2098</v>
+        <v>2096</v>
+      </c>
+      <c r="D93" s="34" t="s">
+        <v>2552</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2458</v>
+        <v>2267</v>
       </c>
       <c r="C94" s="34" t="s">
         <v>2096</v>
       </c>
-      <c r="D94" s="32" t="s">
-        <v>2553</v>
+      <c r="D94" s="34" t="s">
+        <v>2552</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.4">
@@ -28727,10 +28918,7 @@
         <v>2268</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>2096</v>
-      </c>
-      <c r="D95" s="32" t="s">
-        <v>2553</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.4">
@@ -28738,23 +28926,23 @@
         <v>2269</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C97" s="34" t="s">
         <v>2270</v>
-      </c>
-      <c r="C97" s="34" t="s">
-        <v>2271</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2282</v>
+        <v>2271</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2271</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
@@ -28762,7 +28950,7 @@
         <v>2272</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
@@ -28770,7 +28958,7 @@
         <v>2273</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
@@ -28778,23 +28966,23 @@
         <v>2274</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B102" s="31" t="s">
-        <v>2275</v>
+        <v>950</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>950</v>
+        <v>2275</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
@@ -28802,7 +28990,7 @@
         <v>2276</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
@@ -28810,7 +28998,7 @@
         <v>2277</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
@@ -28818,7 +29006,7 @@
         <v>2278</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
@@ -28826,23 +29014,23 @@
         <v>2279</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C108" s="34" t="s">
         <v>2280</v>
-      </c>
-      <c r="C108" s="34" t="s">
-        <v>2281</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2287</v>
+        <v>2282</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>2281</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
@@ -28871,10 +29059,10 @@
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>2118</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
@@ -28922,7 +29110,7 @@
         <v>2293</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>2099</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
@@ -28946,15 +29134,15 @@
         <v>2296</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2104</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C123" s="34" t="s">
         <v>2297</v>
-      </c>
-      <c r="C123" s="34" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
@@ -28962,7 +29150,7 @@
         <v>2299</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
@@ -28970,7 +29158,7 @@
         <v>2300</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
@@ -28978,7 +29166,7 @@
         <v>2301</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
@@ -28986,7 +29174,7 @@
         <v>2302</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
@@ -28994,7 +29182,7 @@
         <v>2303</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
@@ -29002,7 +29190,7 @@
         <v>2304</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
@@ -29010,7 +29198,7 @@
         <v>2305</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
@@ -29018,7 +29206,10 @@
         <v>2306</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>2309</v>
+        <v>2308</v>
+      </c>
+      <c r="D131" s="34" t="s">
+        <v>2369</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
@@ -29026,18 +29217,15 @@
         <v>2307</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2309</v>
-      </c>
-      <c r="D132" s="34" t="s">
-        <v>2370</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>2309</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
@@ -29045,7 +29233,7 @@
         <v>2310</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
@@ -29053,7 +29241,7 @@
         <v>2311</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
@@ -29061,7 +29249,7 @@
         <v>2312</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
@@ -29069,7 +29257,7 @@
         <v>2313</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
@@ -29077,15 +29265,15 @@
         <v>2314</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2316</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
@@ -29093,7 +29281,7 @@
         <v>2317</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
@@ -29101,7 +29289,7 @@
         <v>2318</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
@@ -29109,7 +29297,7 @@
         <v>2319</v>
       </c>
       <c r="C142" s="34" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
@@ -29117,15 +29305,15 @@
         <v>2320</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
@@ -29133,7 +29321,7 @@
         <v>2323</v>
       </c>
       <c r="C145" s="34" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
@@ -29141,15 +29329,15 @@
         <v>2324</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2326</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
@@ -29157,7 +29345,7 @@
         <v>2327</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
@@ -29165,7 +29353,7 @@
         <v>2328</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
@@ -29173,7 +29361,7 @@
         <v>2329</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
@@ -29181,7 +29369,7 @@
         <v>2330</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
@@ -29189,7 +29377,7 @@
         <v>2331</v>
       </c>
       <c r="C152" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
@@ -29197,7 +29385,7 @@
         <v>2332</v>
       </c>
       <c r="C153" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
@@ -29205,7 +29393,7 @@
         <v>2333</v>
       </c>
       <c r="C154" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
@@ -29213,15 +29401,15 @@
         <v>2334</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="C156" s="34" t="s">
-        <v>2336</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
@@ -29229,7 +29417,10 @@
         <v>2337</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>2341</v>
+        <v>2340</v>
+      </c>
+      <c r="D157" s="34" t="s">
+        <v>2385</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
@@ -29237,10 +29428,7 @@
         <v>2338</v>
       </c>
       <c r="C158" s="34" t="s">
-        <v>2341</v>
-      </c>
-      <c r="D158" s="34" t="s">
-        <v>2386</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
@@ -29248,159 +29436,162 @@
         <v>2339</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2340</v>
+        <v>2346</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2341</v>
-      </c>
-    </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
         <v>2347</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
         <v>2348</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
         <v>2349</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
         <v>2350</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
         <v>2351</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
         <v>2352</v>
       </c>
       <c r="C166" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
         <v>2353</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B168" s="31" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>2355</v>
-      </c>
-    </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
         <v>2358</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2360</v>
-      </c>
-    </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C170" s="34" t="s">
         <v>2359</v>
       </c>
-      <c r="C170" s="34" t="s">
-        <v>2360</v>
-      </c>
-    </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
         <v>2356</v>
       </c>
       <c r="C171" s="34" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B172" s="31" t="s">
         <v>2360</v>
       </c>
-    </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B172" s="31" t="s">
-        <v>2357</v>
-      </c>
       <c r="C172" s="34" t="s">
-        <v>2360</v>
-      </c>
-    </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
         <v>2361</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>2366</v>
-      </c>
-    </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2365</v>
+      </c>
+      <c r="D173" s="34" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
         <v>2362</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>2366</v>
-      </c>
-    </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
         <v>2363</v>
       </c>
       <c r="C175" s="34" t="s">
-        <v>2366</v>
-      </c>
-    </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.4">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
         <v>2364</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
-        <v>2367</v>
+        <v>2492</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>2368</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
@@ -29408,23 +29599,23 @@
         <v>2493</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2494</v>
+        <v>2368</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2495</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C181" s="34" t="s">
         <v>2369</v>
-      </c>
-      <c r="C181" s="34" t="s">
-        <v>2370</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
@@ -29432,7 +29623,7 @@
         <v>2371</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
@@ -29440,7 +29631,7 @@
         <v>2372</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
@@ -29448,7 +29639,7 @@
         <v>2373</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>2370</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
@@ -29456,7 +29647,7 @@
         <v>2374</v>
       </c>
       <c r="C185" s="34" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
@@ -29464,15 +29655,15 @@
         <v>2375</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>2377</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
@@ -29480,7 +29671,7 @@
         <v>2378</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
@@ -29488,7 +29679,7 @@
         <v>2379</v>
       </c>
       <c r="C189" s="34" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
@@ -29496,15 +29687,15 @@
         <v>2380</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
@@ -29512,7 +29703,7 @@
         <v>2383</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
@@ -29520,23 +29711,23 @@
         <v>2384</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C194" s="34" t="s">
         <v>2385</v>
-      </c>
-      <c r="C194" s="34" t="s">
-        <v>2386</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
-        <v>2190</v>
+        <v>2386</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>2386</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
@@ -29544,7 +29735,7 @@
         <v>2387</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
@@ -29552,7 +29743,7 @@
         <v>2388</v>
       </c>
       <c r="C197" s="34" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
@@ -29560,15 +29751,15 @@
         <v>2389</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2391</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
@@ -29576,7 +29767,7 @@
         <v>2392</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
@@ -29584,7 +29775,7 @@
         <v>2393</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
@@ -29592,7 +29783,7 @@
         <v>2394</v>
       </c>
       <c r="C202" s="34" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
@@ -29600,31 +29791,31 @@
         <v>2395</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2397</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
@@ -29632,7 +29823,7 @@
         <v>2400</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
@@ -29640,7 +29831,7 @@
         <v>2401</v>
       </c>
       <c r="C208" s="34" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
@@ -29648,15 +29839,15 @@
         <v>2402</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>2404</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
@@ -29664,7 +29855,7 @@
         <v>2405</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
@@ -29672,7 +29863,7 @@
         <v>2406</v>
       </c>
       <c r="C212" s="34" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
@@ -29680,15 +29871,15 @@
         <v>2407</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C214" s="34" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
@@ -29696,7 +29887,7 @@
         <v>2410</v>
       </c>
       <c r="C215" s="34" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
@@ -29704,31 +29895,31 @@
         <v>2411</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2412</v>
+        <v>2420</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2413</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B218" s="31" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
-        <v>2425</v>
+        <v>2421</v>
       </c>
       <c r="C219" s="34" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
@@ -29736,39 +29927,39 @@
         <v>2422</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="C221" s="34" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2428</v>
-      </c>
-      <c r="C223" s="34" t="s">
         <v>2429</v>
+      </c>
+      <c r="C223" s="42" t="s">
+        <v>2467</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
         <v>2430</v>
       </c>
-      <c r="C224" s="42" t="s">
-        <v>2468</v>
+      <c r="C224" s="34" t="s">
+        <v>2433</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.4">
@@ -29776,7 +29967,7 @@
         <v>2431</v>
       </c>
       <c r="C225" s="34" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.4">
@@ -29784,23 +29975,23 @@
         <v>2432</v>
       </c>
       <c r="C226" s="34" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B227" s="31" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C227" s="34" t="s">
         <v>2433</v>
-      </c>
-      <c r="C227" s="34" t="s">
-        <v>2434</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B228" s="31" t="s">
-        <v>2353</v>
+        <v>2434</v>
       </c>
       <c r="C228" s="34" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.4">
@@ -29808,7 +29999,7 @@
         <v>2435</v>
       </c>
       <c r="C229" s="34" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.4">
@@ -29816,15 +30007,15 @@
         <v>2436</v>
       </c>
       <c r="C230" s="34" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B231" s="31" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="C231" s="34" t="s">
-        <v>2438</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.4">
@@ -29832,7 +30023,7 @@
         <v>2439</v>
       </c>
       <c r="C232" s="34" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.4">
@@ -29840,7 +30031,7 @@
         <v>2440</v>
       </c>
       <c r="C233" s="34" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.4">
@@ -29848,7 +30039,7 @@
         <v>2441</v>
       </c>
       <c r="C234" s="34" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.4">
@@ -29856,39 +30047,39 @@
         <v>2442</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B236" s="31" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="C236" s="34" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B237" s="31" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="C237" s="34" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B238" s="31" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="C238" s="34" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B239" s="31" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="C239" s="34" t="s">
-        <v>2450</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="240" spans="2:3" x14ac:dyDescent="0.4">
@@ -29896,7 +30087,7 @@
         <v>2451</v>
       </c>
       <c r="C240" s="34" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
@@ -29904,7 +30095,7 @@
         <v>2452</v>
       </c>
       <c r="C241" s="34" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
@@ -29912,7 +30103,7 @@
         <v>2453</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
@@ -29920,23 +30111,23 @@
         <v>2454</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2455</v>
-      </c>
-      <c r="C244" s="34" t="s">
         <v>2456</v>
+      </c>
+      <c r="C244" s="32" t="s">
+        <v>2552</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
-        <v>2457</v>
+        <v>2550</v>
       </c>
       <c r="C245" s="32" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
@@ -29944,23 +30135,23 @@
         <v>2551</v>
       </c>
       <c r="C246" s="32" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
+        <v>2458</v>
+      </c>
+      <c r="C247" s="32" t="s">
         <v>2552</v>
-      </c>
-      <c r="C247" s="32" t="s">
-        <v>2553</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2459</v>
-      </c>
-      <c r="C248" s="32" t="s">
-        <v>2553</v>
+        <v>2468</v>
+      </c>
+      <c r="C248" s="34" t="s">
+        <v>2102</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
@@ -29989,18 +30180,18 @@
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="C252" s="34" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
         <v>2474</v>
       </c>
-      <c r="C253" s="34" t="s">
-        <v>2101</v>
+      <c r="C253" s="32" t="s">
+        <v>2110</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
@@ -30023,8 +30214,8 @@
       <c r="B256" s="31" t="s">
         <v>2477</v>
       </c>
-      <c r="C256" s="32" t="s">
-        <v>2110</v>
+      <c r="C256" s="34" t="s">
+        <v>2484</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
@@ -30032,7 +30223,7 @@
         <v>2478</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
@@ -30040,7 +30231,7 @@
         <v>2479</v>
       </c>
       <c r="C258" s="34" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
@@ -30048,7 +30239,7 @@
         <v>2480</v>
       </c>
       <c r="C259" s="34" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
@@ -30056,7 +30247,7 @@
         <v>2481</v>
       </c>
       <c r="C260" s="34" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
@@ -30064,7 +30255,7 @@
         <v>2482</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
@@ -30072,23 +30263,23 @@
         <v>2483</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C263" s="34" t="s">
         <v>2484</v>
-      </c>
-      <c r="C263" s="34" t="s">
-        <v>2485</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2327</v>
+        <v>2485</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2485</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
@@ -30096,7 +30287,7 @@
         <v>2486</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
@@ -30104,7 +30295,7 @@
         <v>2487</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
@@ -30112,7 +30303,7 @@
         <v>2488</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
@@ -30120,23 +30311,23 @@
         <v>2489</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2490</v>
+        <v>2235</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2236</v>
+        <v>2490</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
@@ -30144,39 +30335,39 @@
         <v>2491</v>
       </c>
       <c r="C271" s="34" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2492</v>
-      </c>
-      <c r="C272" s="34" t="s">
         <v>2495</v>
+      </c>
+      <c r="C272" s="32" t="s">
+        <v>2472</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
-        <v>2496</v>
+        <v>2199</v>
       </c>
       <c r="C273" s="32" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2199</v>
+        <v>2496</v>
       </c>
       <c r="C274" s="32" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
         <v>2497</v>
       </c>
-      <c r="C275" s="32" t="s">
-        <v>2473</v>
+      <c r="C275" s="34" t="s">
+        <v>2499</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
@@ -30184,15 +30375,15 @@
         <v>2498</v>
       </c>
       <c r="C276" s="34" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2499</v>
-      </c>
-      <c r="C277" s="34" t="s">
-        <v>2500</v>
+        <v>2502</v>
+      </c>
+      <c r="C277" s="32" t="s">
+        <v>2095</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
@@ -30215,8 +30406,8 @@
       <c r="B280" s="31" t="s">
         <v>2505</v>
       </c>
-      <c r="C280" s="32" t="s">
-        <v>2095</v>
+      <c r="C280" s="34" t="s">
+        <v>2262</v>
       </c>
     </row>
     <row r="281" spans="2:3" x14ac:dyDescent="0.4">
@@ -30224,15 +30415,135 @@
         <v>2506</v>
       </c>
       <c r="C281" s="34" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="282" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B282" s="31" t="s">
-        <v>2507</v>
+        <v>2590</v>
       </c>
       <c r="C282" s="34" t="s">
-        <v>2263</v>
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B283" s="31" t="s">
+        <v>2591</v>
+      </c>
+      <c r="C283" s="34" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B284" s="31" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C284" s="34" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B285" s="31" t="s">
+        <v>2593</v>
+      </c>
+      <c r="C285" s="32" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B286" s="31" t="s">
+        <v>2594</v>
+      </c>
+      <c r="C286" s="34" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B287" s="31" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C287" s="34" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B288" s="31" t="s">
+        <v>2597</v>
+      </c>
+      <c r="C288" s="34" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B289" s="31" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C289" s="34" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B290" s="31" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C290" s="34" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B291" s="31" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C291" s="34" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B292" s="31" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C292" s="34" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B293" s="31" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C293" s="34" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B294" s="31" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C294" s="34" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B295" s="31" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C295" s="34" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B296" s="31" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C296" s="32" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B297" s="31" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C297" s="32" t="s">
+        <v>2579</v>
       </c>
     </row>
   </sheetData>
@@ -30271,107 +30582,126 @@
     <hyperlink ref="C54" r:id="rId31" xr:uid="{DC52ED96-0637-49FF-A28E-36F20A51C33C}"/>
     <hyperlink ref="C55:C69" r:id="rId32" display="地下街について" xr:uid="{CB188704-BC12-4A02-9FD0-638054C90375}"/>
     <hyperlink ref="C70" r:id="rId33" xr:uid="{7928797A-C5DF-4728-9549-ABC52D4EACEE}"/>
-    <hyperlink ref="C71" r:id="rId34" xr:uid="{F76AB73C-F876-4DF2-96C6-6163DA320730}"/>
-    <hyperlink ref="C72:C91" r:id="rId35" display="沿革？" xr:uid="{F4EE62D7-4C6F-4EA2-9B9C-33FB3A6EC0E3}"/>
-    <hyperlink ref="C92" r:id="rId36" xr:uid="{583C6BD0-F972-4FCE-9396-2CBCC08D6FDE}"/>
-    <hyperlink ref="C93" r:id="rId37" xr:uid="{F06D86F4-AB96-409E-8DDD-94645E5FE304}"/>
-    <hyperlink ref="C95" r:id="rId38" xr:uid="{650ECBC7-1D3E-47F9-A04B-91409F4AFD82}"/>
-    <hyperlink ref="C96" r:id="rId39" xr:uid="{75F24C6E-979A-4ECB-95F5-2AB7E52FFB3E}"/>
-    <hyperlink ref="C97" r:id="rId40" xr:uid="{D9C0E6B3-F6F4-4826-91A7-073BB4A33382}"/>
-    <hyperlink ref="C99" r:id="rId41" xr:uid="{C71D6526-B182-4F76-AF5F-B6B680D9C45A}"/>
-    <hyperlink ref="C100:C108" r:id="rId42" display="そば屋" xr:uid="{40157A7E-CAB9-47AA-A338-F67391C4503D}"/>
-    <hyperlink ref="C98" r:id="rId43" xr:uid="{420879CC-989A-4756-8081-0E73B34C1E0E}"/>
-    <hyperlink ref="C110" r:id="rId44" xr:uid="{08AFE583-4426-461B-979B-F49FE83DAB8B}"/>
-    <hyperlink ref="C111" r:id="rId45" xr:uid="{4B7DEC01-3433-493D-B1C4-DB5A8E94100F}"/>
-    <hyperlink ref="C112" r:id="rId46" xr:uid="{033DA32D-FAE1-4F14-8183-633E4BD0685F}"/>
-    <hyperlink ref="C113" r:id="rId47" xr:uid="{F5795EE1-139B-45EA-B58B-15E854EAAE5A}"/>
-    <hyperlink ref="C109" r:id="rId48" xr:uid="{F2014E68-B566-4189-B5F6-D6EDBE18923E}"/>
-    <hyperlink ref="C114" r:id="rId49" xr:uid="{15F4FF79-5F95-4C8F-A6B7-69888A1FCE6D}"/>
-    <hyperlink ref="C115:C119" r:id="rId50" display="化しょう屋" xr:uid="{C36F89E4-6767-4188-A309-322ABD51A23A}"/>
-    <hyperlink ref="C120" r:id="rId51" xr:uid="{B25A19F7-C29D-4D44-AC0C-A8DB47267A0C}"/>
-    <hyperlink ref="C121" r:id="rId52" xr:uid="{A1A626FD-0CE4-486F-8590-123D1319E54C}"/>
-    <hyperlink ref="C122" r:id="rId53" xr:uid="{1F8B8F90-51A5-4592-921F-1E537FBAAB02}"/>
-    <hyperlink ref="C123" r:id="rId54" xr:uid="{87BFCFB8-139F-4781-AF48-25318B2E8D71}"/>
-    <hyperlink ref="C124" r:id="rId55" xr:uid="{F40A3028-CD41-4895-810E-85739533F5BA}"/>
-    <hyperlink ref="C125" r:id="rId56" xr:uid="{C3EF1F2D-B6BA-4AE2-8B14-1F43AFE56D4E}"/>
-    <hyperlink ref="C126" r:id="rId57" xr:uid="{D6C949E3-BDA6-4B98-8D49-849E42D416EA}"/>
-    <hyperlink ref="C127:C133" r:id="rId58" display="すし屋" xr:uid="{19CFE92A-BD95-4F91-A784-CB5138E9E5C4}"/>
-    <hyperlink ref="C134" r:id="rId59" xr:uid="{C0DB6F37-9F22-4FB7-9A59-FCA8F06DF804}"/>
-    <hyperlink ref="C135:C139" r:id="rId60" display="らーめん屋" xr:uid="{63D1B813-7B17-494F-BFD0-6ED9C23C668E}"/>
-    <hyperlink ref="C140" r:id="rId61" xr:uid="{64CD0AF5-A92E-4E7F-AE38-241FA8F9302D}"/>
-    <hyperlink ref="C141:C144" r:id="rId62" display="ばー" xr:uid="{BEED3297-1DC6-4F65-91E1-A74DB10D382C}"/>
-    <hyperlink ref="C145" r:id="rId63" xr:uid="{C5C057AE-4947-4F4D-ADF4-6DFE9B7B1190}"/>
-    <hyperlink ref="C146:C147" r:id="rId64" display="とこ屋" xr:uid="{B04EB1D9-D776-4BFF-BCDF-98FA89FFC4F6}"/>
-    <hyperlink ref="C148" r:id="rId65" xr:uid="{46895BCD-A492-42BA-8537-5F5398E80386}"/>
-    <hyperlink ref="C149:C156" r:id="rId66" display="いざか屋" xr:uid="{39266F4C-B934-4957-9402-7811D42AFD6B}"/>
-    <hyperlink ref="C157" r:id="rId67" xr:uid="{F198DF54-7E95-4394-BF80-8CA922FC47ED}"/>
-    <hyperlink ref="C158:C160" r:id="rId68" display="おにぎり屋" xr:uid="{398BF49B-AA77-45F5-BA77-9B3365BBE736}"/>
-    <hyperlink ref="C161" r:id="rId69" xr:uid="{F98B3542-E61E-4C4A-A541-D41290107680}"/>
-    <hyperlink ref="C162:C168" r:id="rId70" display="中かりょうり屋" xr:uid="{AE87470A-3000-4C0E-8365-72BCD5DCBF4F}"/>
-    <hyperlink ref="C169" r:id="rId71" xr:uid="{0363DCBF-B486-4536-A7A7-05A05D0E5287}"/>
-    <hyperlink ref="C170:C172" r:id="rId72" display="きっさ屋" xr:uid="{0041D719-6E11-42B7-8456-4D8C7DB65987}"/>
-    <hyperlink ref="C173" r:id="rId73" xr:uid="{D6B4BEFA-5954-43EB-B798-B392F55C96FE}"/>
-    <hyperlink ref="C174:C177" r:id="rId74" display="花屋" xr:uid="{21461B74-589B-4F4E-B344-8583D17BD3E1}"/>
-    <hyperlink ref="C178" r:id="rId75" xr:uid="{FB788C7B-4C32-4CE4-91C4-B0A314142046}"/>
-    <hyperlink ref="C181" r:id="rId76" xr:uid="{D8150307-7C4F-4883-93D1-DE938BDA255F}"/>
-    <hyperlink ref="D132" r:id="rId77" xr:uid="{D7B5F7EF-8A3E-4EF9-BE9B-87BD25B1DEC3}"/>
-    <hyperlink ref="C182:C184" r:id="rId78" display="うらない屋" xr:uid="{BD5B9AA7-BEE9-4B4D-869C-96CBA2E0AB53}"/>
-    <hyperlink ref="C185" r:id="rId79" xr:uid="{A956E415-925E-4BE7-8C7B-34E6470531C7}"/>
-    <hyperlink ref="C186:C187" r:id="rId80" display="じゃずばー" xr:uid="{F3C1261E-4D64-4AF6-B5B1-D120DE06DE1E}"/>
-    <hyperlink ref="C188" r:id="rId81" xr:uid="{23FCEF9A-0D1E-42CA-AFD5-D7B4C91E6D26}"/>
-    <hyperlink ref="C189:C191" r:id="rId82" display="れこーど屋" xr:uid="{67DEEB48-8CEC-4228-8750-64B86E077C59}"/>
-    <hyperlink ref="C192" r:id="rId83" xr:uid="{80EE8314-4DD1-46C4-AE4C-CA0FD6A68933}"/>
-    <hyperlink ref="C193:C195" r:id="rId84" display="くつ屋" xr:uid="{3788FC8E-1620-4335-8625-8DCA71AC925D}"/>
-    <hyperlink ref="D158" r:id="rId85" xr:uid="{1AC6C13F-D00F-4482-98BE-1C2CCF13D05D}"/>
-    <hyperlink ref="C196" r:id="rId86" xr:uid="{63988F07-EA6D-4F26-9226-45FD114364DC}"/>
-    <hyperlink ref="C197:C199" r:id="rId87" display="本屋" xr:uid="{2A3A625B-6EA8-437E-81C7-68CF5E700BFC}"/>
-    <hyperlink ref="C200" r:id="rId88" xr:uid="{11E58C7C-D20F-4332-BA3A-857C1491B32B}"/>
-    <hyperlink ref="C201:C204" r:id="rId89" display="けーき屋" xr:uid="{88195962-BB93-453B-81A1-52FA5CBE67AF}"/>
-    <hyperlink ref="C205" r:id="rId90" xr:uid="{724A06D0-79BF-46A2-B58C-0C3ECBBFDB45}"/>
-    <hyperlink ref="C206:C210" r:id="rId91" display="清そう屋" xr:uid="{9E37B236-0ED6-47F6-BF18-86B12BD98E6B}"/>
-    <hyperlink ref="C211" r:id="rId92" xr:uid="{EF971420-17D4-4182-8132-56F00A167A2C}"/>
-    <hyperlink ref="C212:C214" r:id="rId93" display="時けい屋" xr:uid="{6C295750-0F27-47E0-9129-453CA0F3E98B}"/>
-    <hyperlink ref="C215" r:id="rId94" xr:uid="{DB4BE4EC-BA0C-456D-B5AB-A0C311E10FC4}"/>
-    <hyperlink ref="C216:C217" r:id="rId95" display="くすり屋" xr:uid="{C21A8AF9-DE63-4441-BD5E-F5FF047CB554}"/>
-    <hyperlink ref="C218" r:id="rId96" xr:uid="{D901BE77-9912-45E3-9CE7-FF143E1A7C55}"/>
-    <hyperlink ref="C220:C221" r:id="rId97" display="くりーにんぐ屋" xr:uid="{404FE6C1-57C6-4D57-9720-912B76B3036C}"/>
-    <hyperlink ref="C219" r:id="rId98" xr:uid="{E32A61DB-E7C1-4C00-A9EA-3C2EE69560FA}"/>
-    <hyperlink ref="C222" r:id="rId99" xr:uid="{F3012094-E137-4787-AE48-4A8F62EFE745}"/>
-    <hyperlink ref="C223" r:id="rId100" xr:uid="{25CF5C66-B1C6-4B3A-84C7-C4ADF6D77959}"/>
-    <hyperlink ref="C225" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
-    <hyperlink ref="C226:C228" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
-    <hyperlink ref="C229" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
-    <hyperlink ref="C230:C231" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
-    <hyperlink ref="C232" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
-    <hyperlink ref="C233:C236" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
-    <hyperlink ref="C237" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
-    <hyperlink ref="C238" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
-    <hyperlink ref="C239" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
-    <hyperlink ref="C240" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
-    <hyperlink ref="C241:C244" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
-    <hyperlink ref="C224" r:id="rId112" display="●壁？" xr:uid="{49CFE894-D6FF-4DAD-A18A-E33C19DC9AC5}"/>
-    <hyperlink ref="D75" r:id="rId113" xr:uid="{F3D3E429-A98C-4A89-8517-136EBFF9C669}"/>
-    <hyperlink ref="C253" r:id="rId114" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
-    <hyperlink ref="C254" r:id="rId115" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
-    <hyperlink ref="C255:C256" r:id="rId116" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
-    <hyperlink ref="C257" r:id="rId117" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
-    <hyperlink ref="C258:C264" r:id="rId118" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
-    <hyperlink ref="C265" r:id="rId119" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
-    <hyperlink ref="C266:C272" r:id="rId120" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
-    <hyperlink ref="C273" r:id="rId121" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
-    <hyperlink ref="C274" r:id="rId122" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
-    <hyperlink ref="C275" r:id="rId123" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
-    <hyperlink ref="C276" r:id="rId124" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
-    <hyperlink ref="C277" r:id="rId125" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
-    <hyperlink ref="C278" r:id="rId126" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
-    <hyperlink ref="C279" r:id="rId127" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
-    <hyperlink ref="C280" r:id="rId128" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
-    <hyperlink ref="C281" r:id="rId129" xr:uid="{638B7DD6-1594-44CE-9207-871F21E21DD3}"/>
-    <hyperlink ref="C282" r:id="rId130" xr:uid="{0A4BE00D-CD86-4A4E-ADBB-82650B816BF4}"/>
-    <hyperlink ref="C245" r:id="rId131" display="無影言本祭" xr:uid="{8D13B183-FF2F-461F-87EA-DF266C32877C}"/>
-    <hyperlink ref="C246" r:id="rId132" display="無影言本祭" xr:uid="{1204C86E-B414-49FA-9E5E-D39D616244E1}"/>
-    <hyperlink ref="C247:C248" r:id="rId133" display="無影言本祭" xr:uid="{E5562058-48A6-4B14-99CC-EFD928C85B1B}"/>
-    <hyperlink ref="C94" r:id="rId134" xr:uid="{157FEE6A-E3FD-4891-9A8C-DEA390CC9F8A}"/>
+    <hyperlink ref="D33" r:id="rId34" xr:uid="{F76AB73C-F876-4DF2-96C6-6163DA320730}"/>
+    <hyperlink ref="C71:C90" r:id="rId35" display="沿革？" xr:uid="{F4EE62D7-4C6F-4EA2-9B9C-33FB3A6EC0E3}"/>
+    <hyperlink ref="C91" r:id="rId36" xr:uid="{583C6BD0-F972-4FCE-9396-2CBCC08D6FDE}"/>
+    <hyperlink ref="C92" r:id="rId37" xr:uid="{F06D86F4-AB96-409E-8DDD-94645E5FE304}"/>
+    <hyperlink ref="C94" r:id="rId38" xr:uid="{650ECBC7-1D3E-47F9-A04B-91409F4AFD82}"/>
+    <hyperlink ref="C95" r:id="rId39" xr:uid="{75F24C6E-979A-4ECB-95F5-2AB7E52FFB3E}"/>
+    <hyperlink ref="C96" r:id="rId40" xr:uid="{D9C0E6B3-F6F4-4826-91A7-073BB4A33382}"/>
+    <hyperlink ref="C98" r:id="rId41" xr:uid="{C71D6526-B182-4F76-AF5F-B6B680D9C45A}"/>
+    <hyperlink ref="C99:C107" r:id="rId42" display="そば屋" xr:uid="{40157A7E-CAB9-47AA-A338-F67391C4503D}"/>
+    <hyperlink ref="C97" r:id="rId43" xr:uid="{420879CC-989A-4756-8081-0E73B34C1E0E}"/>
+    <hyperlink ref="C109" r:id="rId44" xr:uid="{08AFE583-4426-461B-979B-F49FE83DAB8B}"/>
+    <hyperlink ref="C110" r:id="rId45" xr:uid="{4B7DEC01-3433-493D-B1C4-DB5A8E94100F}"/>
+    <hyperlink ref="C111" r:id="rId46" xr:uid="{033DA32D-FAE1-4F14-8183-633E4BD0685F}"/>
+    <hyperlink ref="C112" r:id="rId47" xr:uid="{F5795EE1-139B-45EA-B58B-15E854EAAE5A}"/>
+    <hyperlink ref="C108" r:id="rId48" xr:uid="{F2014E68-B566-4189-B5F6-D6EDBE18923E}"/>
+    <hyperlink ref="C113" r:id="rId49" xr:uid="{15F4FF79-5F95-4C8F-A6B7-69888A1FCE6D}"/>
+    <hyperlink ref="C114:C118" r:id="rId50" display="化しょう屋" xr:uid="{C36F89E4-6767-4188-A309-322ABD51A23A}"/>
+    <hyperlink ref="C119" r:id="rId51" xr:uid="{B25A19F7-C29D-4D44-AC0C-A8DB47267A0C}"/>
+    <hyperlink ref="C120" r:id="rId52" xr:uid="{A1A626FD-0CE4-486F-8590-123D1319E54C}"/>
+    <hyperlink ref="C121" r:id="rId53" xr:uid="{1F8B8F90-51A5-4592-921F-1E537FBAAB02}"/>
+    <hyperlink ref="C122" r:id="rId54" xr:uid="{87BFCFB8-139F-4781-AF48-25318B2E8D71}"/>
+    <hyperlink ref="C123" r:id="rId55" xr:uid="{F40A3028-CD41-4895-810E-85739533F5BA}"/>
+    <hyperlink ref="C124" r:id="rId56" xr:uid="{C3EF1F2D-B6BA-4AE2-8B14-1F43AFE56D4E}"/>
+    <hyperlink ref="C125" r:id="rId57" xr:uid="{D6C949E3-BDA6-4B98-8D49-849E42D416EA}"/>
+    <hyperlink ref="C126:C132" r:id="rId58" display="すし屋" xr:uid="{19CFE92A-BD95-4F91-A784-CB5138E9E5C4}"/>
+    <hyperlink ref="C133" r:id="rId59" xr:uid="{C0DB6F37-9F22-4FB7-9A59-FCA8F06DF804}"/>
+    <hyperlink ref="C134:C138" r:id="rId60" display="らーめん屋" xr:uid="{63D1B813-7B17-494F-BFD0-6ED9C23C668E}"/>
+    <hyperlink ref="C139" r:id="rId61" xr:uid="{64CD0AF5-A92E-4E7F-AE38-241FA8F9302D}"/>
+    <hyperlink ref="C140:C143" r:id="rId62" display="ばー" xr:uid="{BEED3297-1DC6-4F65-91E1-A74DB10D382C}"/>
+    <hyperlink ref="C144" r:id="rId63" xr:uid="{C5C057AE-4947-4F4D-ADF4-6DFE9B7B1190}"/>
+    <hyperlink ref="C145:C146" r:id="rId64" display="とこ屋" xr:uid="{B04EB1D9-D776-4BFF-BCDF-98FA89FFC4F6}"/>
+    <hyperlink ref="C147" r:id="rId65" xr:uid="{46895BCD-A492-42BA-8537-5F5398E80386}"/>
+    <hyperlink ref="C148:C155" r:id="rId66" display="いざか屋" xr:uid="{39266F4C-B934-4957-9402-7811D42AFD6B}"/>
+    <hyperlink ref="C156" r:id="rId67" xr:uid="{F198DF54-7E95-4394-BF80-8CA922FC47ED}"/>
+    <hyperlink ref="C157:C159" r:id="rId68" display="おにぎり屋" xr:uid="{398BF49B-AA77-45F5-BA77-9B3365BBE736}"/>
+    <hyperlink ref="C160" r:id="rId69" xr:uid="{F98B3542-E61E-4C4A-A541-D41290107680}"/>
+    <hyperlink ref="C161:C167" r:id="rId70" display="中かりょうり屋" xr:uid="{AE87470A-3000-4C0E-8365-72BCD5DCBF4F}"/>
+    <hyperlink ref="C168" r:id="rId71" xr:uid="{0363DCBF-B486-4536-A7A7-05A05D0E5287}"/>
+    <hyperlink ref="C169:C171" r:id="rId72" display="きっさ屋" xr:uid="{0041D719-6E11-42B7-8456-4D8C7DB65987}"/>
+    <hyperlink ref="C172" r:id="rId73" xr:uid="{D6B4BEFA-5954-43EB-B798-B392F55C96FE}"/>
+    <hyperlink ref="C173:C176" r:id="rId74" display="花屋" xr:uid="{21461B74-589B-4F4E-B344-8583D17BD3E1}"/>
+    <hyperlink ref="C177" r:id="rId75" xr:uid="{FB788C7B-4C32-4CE4-91C4-B0A314142046}"/>
+    <hyperlink ref="C180" r:id="rId76" xr:uid="{D8150307-7C4F-4883-93D1-DE938BDA255F}"/>
+    <hyperlink ref="D131" r:id="rId77" xr:uid="{D7B5F7EF-8A3E-4EF9-BE9B-87BD25B1DEC3}"/>
+    <hyperlink ref="C181:C183" r:id="rId78" display="うらない屋" xr:uid="{BD5B9AA7-BEE9-4B4D-869C-96CBA2E0AB53}"/>
+    <hyperlink ref="C184" r:id="rId79" xr:uid="{A956E415-925E-4BE7-8C7B-34E6470531C7}"/>
+    <hyperlink ref="C185:C186" r:id="rId80" display="じゃずばー" xr:uid="{F3C1261E-4D64-4AF6-B5B1-D120DE06DE1E}"/>
+    <hyperlink ref="C187" r:id="rId81" xr:uid="{23FCEF9A-0D1E-42CA-AFD5-D7B4C91E6D26}"/>
+    <hyperlink ref="C188:C190" r:id="rId82" display="れこーど屋" xr:uid="{67DEEB48-8CEC-4228-8750-64B86E077C59}"/>
+    <hyperlink ref="C191" r:id="rId83" xr:uid="{80EE8314-4DD1-46C4-AE4C-CA0FD6A68933}"/>
+    <hyperlink ref="C192:C194" r:id="rId84" display="くつ屋" xr:uid="{3788FC8E-1620-4335-8625-8DCA71AC925D}"/>
+    <hyperlink ref="D157" r:id="rId85" xr:uid="{1AC6C13F-D00F-4482-98BE-1C2CCF13D05D}"/>
+    <hyperlink ref="C195" r:id="rId86" xr:uid="{63988F07-EA6D-4F26-9226-45FD114364DC}"/>
+    <hyperlink ref="C196:C198" r:id="rId87" display="本屋" xr:uid="{2A3A625B-6EA8-437E-81C7-68CF5E700BFC}"/>
+    <hyperlink ref="C199" r:id="rId88" xr:uid="{11E58C7C-D20F-4332-BA3A-857C1491B32B}"/>
+    <hyperlink ref="C200:C203" r:id="rId89" display="けーき屋" xr:uid="{88195962-BB93-453B-81A1-52FA5CBE67AF}"/>
+    <hyperlink ref="C204" r:id="rId90" xr:uid="{724A06D0-79BF-46A2-B58C-0C3ECBBFDB45}"/>
+    <hyperlink ref="C205:C209" r:id="rId91" display="清そう屋" xr:uid="{9E37B236-0ED6-47F6-BF18-86B12BD98E6B}"/>
+    <hyperlink ref="C210" r:id="rId92" xr:uid="{EF971420-17D4-4182-8132-56F00A167A2C}"/>
+    <hyperlink ref="C211:C213" r:id="rId93" display="時けい屋" xr:uid="{6C295750-0F27-47E0-9129-453CA0F3E98B}"/>
+    <hyperlink ref="C214" r:id="rId94" xr:uid="{DB4BE4EC-BA0C-456D-B5AB-A0C311E10FC4}"/>
+    <hyperlink ref="C215:C216" r:id="rId95" display="くすり屋" xr:uid="{C21A8AF9-DE63-4441-BD5E-F5FF047CB554}"/>
+    <hyperlink ref="C217" r:id="rId96" xr:uid="{D901BE77-9912-45E3-9CE7-FF143E1A7C55}"/>
+    <hyperlink ref="C219:C220" r:id="rId97" display="くりーにんぐ屋" xr:uid="{404FE6C1-57C6-4D57-9720-912B76B3036C}"/>
+    <hyperlink ref="C218" r:id="rId98" xr:uid="{E32A61DB-E7C1-4C00-A9EA-3C2EE69560FA}"/>
+    <hyperlink ref="C221" r:id="rId99" xr:uid="{F3012094-E137-4787-AE48-4A8F62EFE745}"/>
+    <hyperlink ref="C222" r:id="rId100" xr:uid="{25CF5C66-B1C6-4B3A-84C7-C4ADF6D77959}"/>
+    <hyperlink ref="C224" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
+    <hyperlink ref="C225:C227" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
+    <hyperlink ref="C228" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
+    <hyperlink ref="C229:C230" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
+    <hyperlink ref="C231" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
+    <hyperlink ref="C232:C235" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
+    <hyperlink ref="C236" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
+    <hyperlink ref="C237" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
+    <hyperlink ref="C238" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
+    <hyperlink ref="C239" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
+    <hyperlink ref="C240:C243" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
+    <hyperlink ref="C223" r:id="rId112" display="●壁？" xr:uid="{49CFE894-D6FF-4DAD-A18A-E33C19DC9AC5}"/>
+    <hyperlink ref="D74" r:id="rId113" xr:uid="{F3D3E429-A98C-4A89-8517-136EBFF9C669}"/>
+    <hyperlink ref="C252" r:id="rId114" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
+    <hyperlink ref="C253" r:id="rId115" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
+    <hyperlink ref="C254:C255" r:id="rId116" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
+    <hyperlink ref="C256" r:id="rId117" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
+    <hyperlink ref="C257:C263" r:id="rId118" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
+    <hyperlink ref="C264" r:id="rId119" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
+    <hyperlink ref="C265:C271" r:id="rId120" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
+    <hyperlink ref="C272" r:id="rId121" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
+    <hyperlink ref="C273" r:id="rId122" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
+    <hyperlink ref="C274" r:id="rId123" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
+    <hyperlink ref="C275" r:id="rId124" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
+    <hyperlink ref="C276" r:id="rId125" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
+    <hyperlink ref="C277" r:id="rId126" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
+    <hyperlink ref="C278" r:id="rId127" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
+    <hyperlink ref="C279" r:id="rId128" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
+    <hyperlink ref="C280" r:id="rId129" xr:uid="{638B7DD6-1594-44CE-9207-871F21E21DD3}"/>
+    <hyperlink ref="C281" r:id="rId130" xr:uid="{0A4BE00D-CD86-4A4E-ADBB-82650B816BF4}"/>
+    <hyperlink ref="C244" r:id="rId131" display="無影言本祭" xr:uid="{8D13B183-FF2F-461F-87EA-DF266C32877C}"/>
+    <hyperlink ref="C245" r:id="rId132" display="無影言本祭" xr:uid="{1204C86E-B414-49FA-9E5E-D39D616244E1}"/>
+    <hyperlink ref="C246:C247" r:id="rId133" display="無影言本祭" xr:uid="{E5562058-48A6-4B14-99CC-EFD928C85B1B}"/>
+    <hyperlink ref="C93" r:id="rId134" xr:uid="{157FEE6A-E3FD-4891-9A8C-DEA390CC9F8A}"/>
+    <hyperlink ref="C282" r:id="rId135" xr:uid="{0075B865-AC5C-4CD6-A96F-92FBBAAF2768}"/>
+    <hyperlink ref="C283" r:id="rId136" xr:uid="{C8BA9501-EE44-4CFB-8C71-4D8375052233}"/>
+    <hyperlink ref="C284" r:id="rId137" xr:uid="{C9150616-ED4F-4165-A477-B18E3B15B682}"/>
+    <hyperlink ref="D39" r:id="rId138" xr:uid="{A814B798-1BD3-434C-B188-D49492030CCC}"/>
+    <hyperlink ref="C285" r:id="rId139" xr:uid="{C9E65C9C-C25F-45E6-B444-462D5DEBAEC0}"/>
+    <hyperlink ref="C286" r:id="rId140" xr:uid="{DBF7BAF5-49A3-4A8E-9DED-4B2887F3CE62}"/>
+    <hyperlink ref="C287" r:id="rId141" xr:uid="{856CA673-DC5F-4AEC-815F-9AD163802F68}"/>
+    <hyperlink ref="C288" r:id="rId142" xr:uid="{66C8586D-D06E-4AD0-9AC5-6D8C307A0945}"/>
+    <hyperlink ref="C289" r:id="rId143" xr:uid="{4D110E06-13FA-4A06-A46C-5E1613222922}"/>
+    <hyperlink ref="C290" r:id="rId144" xr:uid="{747DC27C-EFD4-4C85-8D9E-98E8076C2057}"/>
+    <hyperlink ref="C291" r:id="rId145" xr:uid="{0A0905C2-C20B-4D6D-8798-163F00EBF73E}"/>
+    <hyperlink ref="C292" r:id="rId146" xr:uid="{E708436D-D4B2-4575-AB05-3A5582112BA8}"/>
+    <hyperlink ref="C293" r:id="rId147" xr:uid="{BD02B744-CCFC-4E17-A6F9-B307C10818EA}"/>
+    <hyperlink ref="C294" r:id="rId148" xr:uid="{2E536251-83F9-4A2E-959C-69A043D41889}"/>
+    <hyperlink ref="C295" r:id="rId149" xr:uid="{93AC0A76-F50F-4760-8C14-2AC67D3644FA}"/>
+    <hyperlink ref="D173" r:id="rId150" xr:uid="{46A5ADB1-85DA-423D-B952-8BE749A562E8}"/>
+    <hyperlink ref="C296" r:id="rId151" xr:uid="{31232A6A-CA23-40C2-A40C-340903C41016}"/>
+    <hyperlink ref="D62" r:id="rId152" xr:uid="{6E0266CA-E8F5-47A8-A403-F33C1896B0E2}"/>
+    <hyperlink ref="C297" r:id="rId153" xr:uid="{7999C9A8-B4CB-4554-A69B-8553BF2B0081}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1775" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5452D8E8-0FF2-4EEE-B303-8B304239090E}"/>
+  <xr:revisionPtr revIDLastSave="1776" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB71BE1-E191-44DA-8CB8-8E8157D1C142}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -11813,6 +11813,26 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
+      <t>壁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> ・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
       <t>佁</t>
     </r>
     <r>
@@ -11826,6 +11846,9 @@
       </rPr>
       <t>壁？</t>
     </r>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -12482,6 +12505,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1776" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB71BE1-E191-44DA-8CB8-8E8157D1C142}"/>
+  <xr:revisionPtr revIDLastSave="1802" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF414A3-A051-4F20-8FBD-CAC00631A1A8}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3071" uniqueCount="2608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3082" uniqueCount="2613">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -6629,9 +6629,6 @@
   </si>
   <si>
     <t>兎</t>
-  </si>
-  <si>
-    <t>広?</t>
   </si>
   <si>
     <t>合</t>
@@ -7695,10 +7692,6 @@
     <t>凇</t>
   </si>
   <si>
-    <t>捌?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>刻</t>
   </si>
   <si>
@@ -11551,115 +11544,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>侱</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>侱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]?</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>捌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>侱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>？</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>影捌けの舞 ・捌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>侱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所？</t>
-    </r>
-    <rPh sb="0" eb="1">
-      <t>カゲ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>体</t>
     <rPh sb="0" eb="1">
       <t>タイ</t>
@@ -11848,6 +11732,130 @@
     </r>
     <rPh sb="0" eb="1">
       <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前</t>
+    <rPh sb="0" eb="1">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>供</t>
+    <rPh sb="0" eb="1">
+      <t>ソナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勢</t>
+    <rPh sb="0" eb="1">
+      <t>ゼイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壇</t>
+    <rPh sb="0" eb="1">
+      <t>ダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>祭だん</t>
+    <rPh sb="0" eb="1">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ないっっ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>避?</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>影避けの舞 ・避</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所？</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>カゲ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>避難所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ヒナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>難?</t>
+    <rPh sb="0" eb="1">
+      <t>ナン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -12411,7 +12419,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -12503,10 +12511,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12839,7 +12843,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="50" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B1" s="51" t="s">
         <v>1560</v>
@@ -12848,25 +12852,25 @@
         <v>1561</v>
       </c>
       <c r="D1" s="52" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="E1" s="52" t="s">
+        <v>2033</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G1" s="53" t="s">
         <v>2035</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="H1" s="53" t="s">
         <v>2036</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="I1" s="53" t="s">
         <v>2037</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="J1" s="53" t="s">
         <v>2038</v>
-      </c>
-      <c r="I1" s="53" t="s">
-        <v>2039</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>2040</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -13103,7 +13107,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="C31">
         <v>29</v>
@@ -13215,7 +13219,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="1" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C45">
         <v>43</v>
@@ -13359,7 +13363,7 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B63" s="1" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="C63">
         <v>61</v>
@@ -13431,7 +13435,7 @@
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B72" s="1" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="C72" t="s">
         <v>1562</v>
@@ -13511,7 +13515,7 @@
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B82" s="1" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="C82" t="s">
         <v>1580</v>
@@ -13527,7 +13531,7 @@
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B84" s="1" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="C84" t="s">
         <v>1583</v>
@@ -13535,7 +13539,7 @@
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B85" s="1" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C85" t="s">
         <v>1584</v>
@@ -13543,7 +13547,7 @@
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B86" s="1" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="C86" t="s">
         <v>863</v>
@@ -13567,7 +13571,7 @@
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B89" s="1" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C89" t="s">
         <v>1588</v>
@@ -13583,7 +13587,7 @@
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B91" s="1" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="C91" t="s">
         <v>717</v>
@@ -13615,7 +13619,7 @@
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B95" s="1" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="C95" t="s">
         <v>1597</v>
@@ -13647,7 +13651,7 @@
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="1" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="C99" t="s">
         <v>722</v>
@@ -13663,7 +13667,7 @@
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="1" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="C101" t="s">
         <v>1605</v>
@@ -13671,7 +13675,7 @@
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B102" s="1" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="C102" t="s">
         <v>1606</v>
@@ -13687,7 +13691,7 @@
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="1" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="C104" t="s">
         <v>1609</v>
@@ -13711,7 +13715,7 @@
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="1" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="C107" t="s">
         <v>1613</v>
@@ -13719,7 +13723,7 @@
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="1" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="C108" t="s">
         <v>1614</v>
@@ -13727,7 +13731,7 @@
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="1" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="C109" t="s">
         <v>1615</v>
@@ -13743,7 +13747,7 @@
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="1" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="C111" t="s">
         <v>1618</v>
@@ -13759,7 +13763,7 @@
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="1" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="C113" t="s">
         <v>1621</v>
@@ -13767,7 +13771,7 @@
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="1" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="C114" t="s">
         <v>1622</v>
@@ -13775,7 +13779,7 @@
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="1" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C115" t="s">
         <v>1623</v>
@@ -13791,7 +13795,7 @@
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="1" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C117" t="s">
         <v>1625</v>
@@ -13807,7 +13811,7 @@
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="1" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C119" t="s">
         <v>1628</v>
@@ -13823,7 +13827,7 @@
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="1" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C121" t="s">
         <v>1631</v>
@@ -13831,7 +13835,7 @@
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="1" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C122" t="s">
         <v>1632</v>
@@ -13839,7 +13843,7 @@
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="1" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="C123" t="s">
         <v>1633</v>
@@ -13847,7 +13851,7 @@
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="1" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C124" t="s">
         <v>1634</v>
@@ -13879,7 +13883,7 @@
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="1" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="C128" t="s">
         <v>1641</v>
@@ -13903,7 +13907,7 @@
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B131" s="1" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="C131" t="s">
         <v>1645</v>
@@ -13919,7 +13923,7 @@
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B133" s="1" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="C133" t="s">
         <v>1647</v>
@@ -13927,7 +13931,7 @@
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B134" s="1" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="C134" t="s">
         <v>1648</v>
@@ -13935,7 +13939,7 @@
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B135" s="1" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C135" t="s">
         <v>1649</v>
@@ -13983,7 +13987,7 @@
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B141" s="1" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C141" t="s">
         <v>1660</v>
@@ -14039,7 +14043,7 @@
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B148" s="1" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C148" t="s">
         <v>1673</v>
@@ -14063,7 +14067,7 @@
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B151" s="1" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="C151" t="s">
         <v>1678</v>
@@ -14071,7 +14075,7 @@
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B152" s="1" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C152" t="s">
         <v>1679</v>
@@ -14103,7 +14107,7 @@
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B156" s="1" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="C156" t="s">
         <v>1685</v>
@@ -14125,16 +14129,16 @@
         <v>1689</v>
       </c>
       <c r="D158" s="33" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="E158" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="F158" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="G158" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.4">
@@ -14142,7 +14146,7 @@
         <v>1690</v>
       </c>
       <c r="C159" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.4">
@@ -14150,12 +14154,12 @@
         <v>1691</v>
       </c>
       <c r="C160" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B161" s="1" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="C161" t="s">
         <v>1692</v>
@@ -14169,10 +14173,10 @@
         <v>1694</v>
       </c>
       <c r="D162" s="33" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="E162" s="34" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.4">
@@ -14180,77 +14184,77 @@
         <v>1695</v>
       </c>
       <c r="C163" t="s">
-        <v>1696</v>
+        <v>2608</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="F163" s="32" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B164" s="1" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="C164" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B165" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C165" t="s">
         <v>1698</v>
-      </c>
-      <c r="C165" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B166" s="1" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="C166" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B167" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C167" t="s">
         <v>1701</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B168" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C168" t="s">
         <v>1703</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B169" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C169" t="s">
         <v>1705</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B170" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C170" t="s">
         <v>1707</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B171" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="C171" t="s">
         <v>72</v>
@@ -14258,31 +14262,31 @@
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B172" s="1" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="C172" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B173" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C173" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B174" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C174" t="s">
         <v>1712</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B175" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="C175" t="s">
         <v>856</v>
@@ -14290,372 +14294,372 @@
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B176" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C176" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B177" s="1" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="C177" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B178" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C178" t="s">
         <v>1717</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="179" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B179" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C179" t="s">
         <v>1719</v>
       </c>
-      <c r="C179" t="s">
-        <v>1720</v>
-      </c>
       <c r="D179" s="33" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="E179" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="F179" s="32" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B180" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C180" t="s">
         <v>1721</v>
       </c>
-      <c r="C180" t="s">
-        <v>1722</v>
-      </c>
       <c r="D180" s="33" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="E180" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B181" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C181" t="s">
         <v>1723</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B182" s="1" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="C182" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B183" s="1" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="C183" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="D183" s="33" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="E183" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B184" s="1" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="C184" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="E184" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B185" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C185" t="s">
         <v>1727</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B186" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="C186" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B187" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C187" t="s">
         <v>1730</v>
-      </c>
-      <c r="C187" t="s">
-        <v>1731</v>
       </c>
     </row>
     <row r="188" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B188" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C188" t="s">
         <v>1732</v>
       </c>
-      <c r="C188" t="s">
-        <v>1733</v>
-      </c>
       <c r="D188" s="33" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="E188" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B189" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C189" t="s">
         <v>1734</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B190" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C190" t="s">
         <v>1736</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1737</v>
       </c>
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B191" s="1" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="C191" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B192" s="1" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="C192" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="E192" s="34" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="193" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B193" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="C193" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="D193" s="33" t="s">
-        <v>2599</v>
+        <v>2593</v>
       </c>
       <c r="E193" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="F193" s="32" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="G193" s="32" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="H193" s="32" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="I193" s="34" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B194" s="1" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C194" t="s">
         <v>1741</v>
       </c>
-      <c r="C194" t="s">
-        <v>1742</v>
-      </c>
       <c r="D194" s="33" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="E194" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B195" s="1" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C195" t="s">
         <v>1743</v>
       </c>
-      <c r="C195" t="s">
-        <v>1744</v>
-      </c>
       <c r="D195" s="33" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="E195" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B196" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C196" t="s">
         <v>1745</v>
-      </c>
-      <c r="C196" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B197" s="1" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C197" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="D197" s="33" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="E197" s="34" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="F197" s="34" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B198" s="1" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="C198" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B199" s="1" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C199" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="D199" s="33" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="E199" s="34" t="s">
+        <v>2106</v>
+      </c>
+      <c r="F199" s="32" t="s">
         <v>2108</v>
-      </c>
-      <c r="F199" s="32" t="s">
-        <v>2110</v>
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B200" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C200" t="s">
         <v>1749</v>
-      </c>
-      <c r="C200" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B201" s="1" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="C201" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B202" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C202" t="s">
         <v>1752</v>
-      </c>
-      <c r="C202" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B203" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C203" t="s">
         <v>1754</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="204" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B204" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C204" t="s">
         <v>1756</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B205" s="1" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="C205" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="D205" s="33" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="E205" s="34" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="F205" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="G205" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B206" s="1" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C206" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B207" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C207" t="s">
         <v>1760</v>
-      </c>
-      <c r="C207" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.4">
@@ -14663,21 +14667,21 @@
         <v>856</v>
       </c>
       <c r="C208" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="D208" s="33" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="E208" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B209" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C209" t="s">
         <v>1763</v>
-      </c>
-      <c r="C209" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.4">
@@ -14685,56 +14689,56 @@
         <v>1070</v>
       </c>
       <c r="C210" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B211" s="1" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="C211" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B212" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C212" t="s">
         <v>1767</v>
       </c>
-      <c r="C212" t="s">
-        <v>1768</v>
-      </c>
       <c r="D212" s="33" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="E212" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="F212" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B213" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C213" t="s">
         <v>1769</v>
-      </c>
-      <c r="C213" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B214" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C214" t="s">
         <v>1771</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B215" s="1" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C215" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.4">
@@ -14742,115 +14746,115 @@
         <v>1076</v>
       </c>
       <c r="C216" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D216" s="33" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="E216" s="34" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="F216" s="32" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B217" s="1" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C217" t="s">
         <v>1774</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B218" s="1" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C218" t="s">
         <v>1776</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B219" s="1" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C219" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="D219" s="33" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="E219" s="34" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B220" s="1" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="C220" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B221" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C221" t="s">
         <v>1780</v>
-      </c>
-      <c r="C221" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B222" s="1" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="C222" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B223" s="1" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C223" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B224" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C224" t="s">
         <v>1784</v>
-      </c>
-      <c r="C224" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B225" s="1" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="C225" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B226" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C226" t="s">
         <v>1787</v>
-      </c>
-      <c r="C226" t="s">
-        <v>1788</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B227" s="1" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C227" t="s">
         <v>1789</v>
-      </c>
-      <c r="C227" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B228" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="C228" t="s">
         <v>430</v>
@@ -14858,255 +14862,255 @@
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B229" s="1" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C229" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B230" s="1" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C230" t="s">
         <v>1793</v>
-      </c>
-      <c r="C230" t="s">
-        <v>1794</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B231" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C231" t="s">
         <v>1795</v>
       </c>
-      <c r="C231" t="s">
-        <v>1796</v>
-      </c>
       <c r="D231" s="33" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="E231" s="34" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B232" s="1" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C232" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D232" s="33" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E232" s="34" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F232" s="32" t="s">
         <v>2578</v>
-      </c>
-      <c r="D232" s="33" t="s">
-        <v>2579</v>
-      </c>
-      <c r="E232" s="34" t="s">
-        <v>2101</v>
-      </c>
-      <c r="F232" s="32" t="s">
-        <v>2580</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B233" s="1" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C233" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B234" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C234" t="s">
         <v>1798</v>
-      </c>
-      <c r="C234" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B235" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C235" t="s">
         <v>1800</v>
-      </c>
-      <c r="C235" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B236" s="1" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="C236" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B237" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C237" t="s">
         <v>1803</v>
       </c>
-      <c r="C237" t="s">
-        <v>1804</v>
-      </c>
       <c r="D237" s="33" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="E237" s="34" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B238" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C238" t="s">
         <v>1805</v>
-      </c>
-      <c r="C238" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B239" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C239" t="s">
         <v>1807</v>
-      </c>
-      <c r="C239" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B240" s="1" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="C240" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="D240" s="33" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="E240" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B241" s="1" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C241" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B242" s="1" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C242" t="s">
         <v>1811</v>
       </c>
-      <c r="C242" t="s">
-        <v>1812</v>
-      </c>
       <c r="D242" s="33" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B243" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C243" t="s">
         <v>1813</v>
-      </c>
-      <c r="C243" t="s">
-        <v>1814</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B244" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C244" t="s">
         <v>1815</v>
       </c>
-      <c r="C244" t="s">
-        <v>1816</v>
-      </c>
       <c r="D244" s="33" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="E244" s="34" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B245" s="1" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C245" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B246" s="1" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="C246" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B247" s="1" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C247" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B248" s="1" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C248" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B249" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C249" t="s">
         <v>1820</v>
       </c>
-      <c r="C249" t="s">
-        <v>1821</v>
-      </c>
       <c r="D249" s="33" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="E249" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B250" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C250" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="E250" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B251" s="1" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="C251" t="s">
         <v>461</v>
@@ -15114,240 +15118,240 @@
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B252" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C252" t="s">
         <v>1823</v>
-      </c>
-      <c r="C252" t="s">
-        <v>1824</v>
       </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B253" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C253" t="s">
         <v>1825</v>
       </c>
-      <c r="C253" t="s">
-        <v>1826</v>
-      </c>
       <c r="D253" s="33" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="E253" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B254" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C254" t="s">
         <v>1827</v>
-      </c>
-      <c r="C254" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B255" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C255" t="s">
         <v>1829</v>
-      </c>
-      <c r="C255" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B256" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C256" t="s">
         <v>1831</v>
-      </c>
-      <c r="C256" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B257" s="1" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C257" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="D257" s="33" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="E257" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B258" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C258" t="s">
         <v>1833</v>
-      </c>
-      <c r="C258" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B259" s="1" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C259" t="s">
-        <v>2606</v>
+        <v>2600</v>
       </c>
       <c r="D259" s="33" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="E259" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="F259" s="32" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B260" s="1" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="C260" t="s">
         <v>416</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="E260" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B261" s="1" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C261" t="s">
-        <v>2605</v>
+        <v>2599</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2604</v>
+        <v>2598</v>
       </c>
       <c r="E261" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="F261" s="32" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B262" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C262" t="s">
         <v>1837</v>
       </c>
-      <c r="C262" t="s">
-        <v>1838</v>
-      </c>
       <c r="D262" s="33" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="E262" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B263" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C263" t="s">
         <v>1839</v>
-      </c>
-      <c r="C263" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C264" t="s">
         <v>1841</v>
-      </c>
-      <c r="C264" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C265" t="s">
         <v>1843</v>
-      </c>
-      <c r="C265" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B266" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C266" t="s">
         <v>1845</v>
-      </c>
-      <c r="C266" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B267" s="1" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C267" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="D267" s="33" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="E267" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B268" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="C268" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B269" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C269" t="s">
         <v>1849</v>
-      </c>
-      <c r="C269" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B270" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C270" t="s">
         <v>1851</v>
-      </c>
-      <c r="C270" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B271" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C271" t="s">
         <v>1853</v>
-      </c>
-      <c r="C271" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B272" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C272" t="s">
         <v>1855</v>
-      </c>
-      <c r="C272" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B273" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C273" t="s">
         <v>1857</v>
-      </c>
-      <c r="C273" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B274" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C274" t="s">
         <v>1859</v>
-      </c>
-      <c r="C274" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.4">
@@ -15355,62 +15359,62 @@
         <v>429</v>
       </c>
       <c r="C275" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B276" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C276" t="s">
         <v>1862</v>
-      </c>
-      <c r="C276" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B277" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C277" t="s">
         <v>1864</v>
       </c>
-      <c r="C277" t="s">
-        <v>1865</v>
-      </c>
       <c r="D277" s="33" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="E277" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B278" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C278" t="s">
         <v>1866</v>
       </c>
-      <c r="C278" t="s">
-        <v>1867</v>
-      </c>
       <c r="D278" s="33" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="E278" s="42" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B279" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C279" t="s">
         <v>1868</v>
       </c>
-      <c r="C279" t="s">
-        <v>1869</v>
-      </c>
       <c r="D279" s="41" t="s">
-        <v>2607</v>
+        <v>2601</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B280" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="C280" t="s">
         <v>1419</v>
@@ -15418,147 +15422,147 @@
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B281" s="1" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="C281" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B282" s="1" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C282" t="s">
         <v>1872</v>
-      </c>
-      <c r="C282" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B283" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C283" t="s">
         <v>1874</v>
-      </c>
-      <c r="C283" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B284" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C284" t="s">
         <v>1876</v>
-      </c>
-      <c r="C284" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B285" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C285" t="s">
         <v>1878</v>
-      </c>
-      <c r="C285" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B286" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C286" t="s">
         <v>1880</v>
-      </c>
-      <c r="C286" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B287" s="1" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C287" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="D287" s="33" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="E287" s="34" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B288" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C288" t="s">
         <v>1883</v>
-      </c>
-      <c r="C288" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B289" s="1" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C289" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B290" s="1" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C290" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B291" s="1" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C291" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="D291" s="33" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="E291" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B292" s="1" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C292" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="D292" s="33" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="E292" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="F292" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B293" s="1" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C293" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="E293" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B294" s="1" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C294" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
@@ -15566,10 +15570,10 @@
         <v>286</v>
       </c>
       <c r="C295" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="D295" s="33" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.4">
@@ -15577,124 +15581,124 @@
         <v>1424</v>
       </c>
       <c r="C296" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B297" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C297" t="s">
         <v>1967</v>
-      </c>
-      <c r="C297" t="s">
-        <v>1968</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B298" s="24" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C298" t="s">
         <v>1971</v>
       </c>
-      <c r="C298" t="s">
-        <v>1972</v>
-      </c>
       <c r="D298" s="33" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="F298" s="32" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B299" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C299" t="s">
         <v>1973</v>
       </c>
-      <c r="C299" t="s">
-        <v>1974</v>
-      </c>
       <c r="D299" s="33" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="E299" s="34" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B300" s="24" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C300" t="s">
         <v>1975</v>
-      </c>
-      <c r="C300" t="s">
-        <v>1976</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B301" s="18" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C301" t="s">
         <v>1993</v>
       </c>
-      <c r="C301" t="s">
-        <v>1994</v>
-      </c>
       <c r="D301" s="33" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B302" s="18" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C302" t="s">
         <v>1977</v>
       </c>
-      <c r="C302" t="s">
-        <v>1978</v>
-      </c>
       <c r="D302" s="33" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="E302" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B303" s="18" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="C303" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="D303" s="33" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="E303" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B304" s="26" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C304" t="s">
         <v>1981</v>
       </c>
-      <c r="C304" t="s">
-        <v>1982</v>
-      </c>
       <c r="D304" s="33" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="E304" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B305" s="1" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C305" t="s">
         <v>1987</v>
       </c>
-      <c r="C305" t="s">
-        <v>1988</v>
-      </c>
       <c r="D305" s="33" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="E305" s="34" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.4">
@@ -15702,131 +15706,131 @@
         <v>935</v>
       </c>
       <c r="C306" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="D306" s="33" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B307" s="1" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C307" t="s">
         <v>1995</v>
       </c>
-      <c r="C307" t="s">
-        <v>1996</v>
-      </c>
       <c r="D307" s="33" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="E307" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F307" s="32" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B308" s="27" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C308" t="s">
         <v>1999</v>
       </c>
-      <c r="C308" t="s">
-        <v>2000</v>
-      </c>
       <c r="D308" s="33" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="E308" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B309" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C309" t="s">
         <v>2001</v>
       </c>
-      <c r="C309" t="s">
-        <v>2002</v>
-      </c>
       <c r="D309" s="33" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="E309" s="34" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B310" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C310" t="s">
         <v>2003</v>
       </c>
-      <c r="C310" t="s">
-        <v>2004</v>
-      </c>
       <c r="D310" s="33" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="E310" s="34" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B311" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C311" t="s">
         <v>2011</v>
       </c>
-      <c r="C311" t="s">
-        <v>2012</v>
-      </c>
       <c r="D311" s="33" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="E311" s="34" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B312" s="1" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C312" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D312" s="33" t="s">
         <v>2140</v>
       </c>
-      <c r="D312" s="33" t="s">
-        <v>2142</v>
-      </c>
       <c r="E312" s="34" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B313" s="1" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C313" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="D313" s="33" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="E313" s="34" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B314" s="1" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C314" t="s">
-        <v>2015</v>
+        <v>2609</v>
       </c>
       <c r="D314" s="54" t="s">
-        <v>2585</v>
+        <v>2610</v>
       </c>
       <c r="E314" s="34" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="F314" s="32" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
@@ -15834,78 +15838,78 @@
         <v>153</v>
       </c>
       <c r="C315" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D315" s="33" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="E315" s="34" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="F315" s="32" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B316" s="1" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C316" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D316" s="33" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="E316" s="34" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B317" s="1" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C317" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D317" s="33" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="F317" s="32" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B318" s="1" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C318" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D318" s="33" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B319" s="1" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C319" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="D319" s="33" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="F319" s="32" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.4">
@@ -15913,294 +15917,294 @@
         <v>821</v>
       </c>
       <c r="C320" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="D320" s="33" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="E320" s="32" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="321" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B321" s="1" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="C321" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D321" s="33" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="E321" s="34" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="322" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B322" s="1" t="s">
         <v>1093</v>
       </c>
       <c r="C322" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="F322" s="32" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="323" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B323" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C323" t="s">
+        <v>2515</v>
+      </c>
+      <c r="D323" s="33" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E323" s="34" t="s">
+        <v>2493</v>
+      </c>
+      <c r="F323" s="32" t="s">
+        <v>2089</v>
+      </c>
+      <c r="G323" s="32" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="324" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B324" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C324" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D324" s="33" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E324" s="34" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F324" s="34" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="325" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B325" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C325" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D325" s="33" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E325" s="34" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F325" s="34" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="326" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B326" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C326" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D326" s="33" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E326" s="34" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="327" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B327" s="1" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C327" t="s">
         <v>2517</v>
       </c>
-      <c r="D323" s="33" t="s">
-        <v>2131</v>
-      </c>
-      <c r="E323" s="34" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F323" s="32" t="s">
-        <v>2091</v>
-      </c>
-      <c r="G323" s="32" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B324" s="1" t="s">
-        <v>1991</v>
-      </c>
-      <c r="C324" t="s">
-        <v>2135</v>
-      </c>
-      <c r="D324" s="33" t="s">
-        <v>2137</v>
-      </c>
-      <c r="E324" s="34" t="s">
-        <v>2085</v>
-      </c>
-      <c r="F324" s="34" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B325" s="1" t="s">
-        <v>1992</v>
-      </c>
-      <c r="C325" t="s">
-        <v>2136</v>
-      </c>
-      <c r="D325" s="33" t="s">
-        <v>2137</v>
-      </c>
-      <c r="E325" s="34" t="s">
-        <v>2085</v>
-      </c>
-      <c r="F325" s="34" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B326" s="1" t="s">
-        <v>2009</v>
-      </c>
-      <c r="C326" t="s">
-        <v>2518</v>
-      </c>
-      <c r="D326" s="33" t="s">
-        <v>2459</v>
-      </c>
-      <c r="E326" s="34" t="s">
-        <v>2090</v>
-      </c>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B327" s="1" t="s">
-        <v>1990</v>
-      </c>
-      <c r="C327" t="s">
-        <v>2519</v>
-      </c>
       <c r="D327" s="33" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="E327" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="328" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B328" s="1" t="s">
         <v>406</v>
       </c>
       <c r="C328" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="E328" s="34" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="329" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B329" s="1" t="s">
         <v>160</v>
       </c>
       <c r="C329" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="D329" s="41" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E329" s="42" t="s">
         <v>2461</v>
       </c>
-      <c r="E329" s="42" t="s">
-        <v>2463</v>
-      </c>
       <c r="F329" s="32" t="s">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="330" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B330" s="1" t="s">
         <v>1102</v>
       </c>
       <c r="C330" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="D330" s="33" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="E330" s="42" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="F330" s="32" t="s">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="331" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B331" s="1" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C331" t="s">
+        <v>2521</v>
+      </c>
+      <c r="D331" s="43" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E331" s="34" t="s">
         <v>2504</v>
       </c>
-      <c r="C331" t="s">
-        <v>2523</v>
-      </c>
-      <c r="D331" s="43" t="s">
-        <v>2505</v>
-      </c>
-      <c r="E331" s="34" t="s">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="332" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B332" s="1" t="s">
         <v>1146</v>
       </c>
       <c r="C332" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D332" s="33" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E332" s="34" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="333" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B333" s="1" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C333" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D333" s="33" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E333" s="34" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="334" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B334" s="1" t="s">
+        <v>2507</v>
+      </c>
+      <c r="C334" t="s">
         <v>2524</v>
       </c>
-      <c r="D332" s="33" t="s">
-        <v>2507</v>
-      </c>
-      <c r="E332" s="34" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B333" s="1" t="s">
+      <c r="D334" s="41" t="s">
+        <v>2509</v>
+      </c>
+      <c r="E334" s="34" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="335" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B335" s="1" t="s">
         <v>2508</v>
       </c>
-      <c r="C333" t="s">
-        <v>2525</v>
-      </c>
-      <c r="D333" s="33" t="s">
-        <v>2507</v>
-      </c>
-      <c r="E333" s="34" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B334" s="1" t="s">
+      <c r="C335" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D335" s="41" t="s">
         <v>2509</v>
       </c>
-      <c r="C334" t="s">
-        <v>2526</v>
-      </c>
-      <c r="D334" s="41" t="s">
-        <v>2511</v>
-      </c>
-      <c r="E334" s="34" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B335" s="1" t="s">
+      <c r="E335" s="34" t="s">
         <v>2510</v>
       </c>
-      <c r="C335" t="s">
-        <v>2515</v>
-      </c>
-      <c r="D335" s="41" t="s">
-        <v>2511</v>
-      </c>
-      <c r="E335" s="34" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A336" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="336" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B336" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C336" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D336" s="33" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E336" s="34" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B337" s="1" t="s">
-        <v>1761</v>
+        <v>2566</v>
       </c>
       <c r="C337" t="s">
         <v>2567</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="E337" s="34" t="s">
-        <v>2566</v>
-      </c>
-    </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.4">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B338" s="1" t="s">
-        <v>2568</v>
-      </c>
-      <c r="C338" t="s">
-        <v>2569</v>
-      </c>
-      <c r="D338" s="33" t="s">
-        <v>2570</v>
-      </c>
-      <c r="E338" s="34" t="s">
-        <v>2566</v>
-      </c>
-    </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B339" s="1" t="s">
-        <v>2582</v>
-      </c>
-      <c r="C339" s="55" t="s">
-        <v>2583</v>
-      </c>
-      <c r="D339" s="33" t="s">
-        <v>2584</v>
-      </c>
-      <c r="E339" s="32" t="s">
-        <v>2581</v>
+        <v>1021</v>
+      </c>
+      <c r="C338" s="55" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D338" s="54" t="s">
+        <v>2611</v>
+      </c>
+      <c r="E338" s="32" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A339" t="s">
+        <v>1889</v>
       </c>
     </row>
   </sheetData>
@@ -16330,15 +16334,15 @@
     <hyperlink ref="E335" r:id="rId109" xr:uid="{E85A37DE-DD8D-4FF4-AA31-96B38F5902E5}"/>
     <hyperlink ref="F315" r:id="rId110" display="無影言本祭" xr:uid="{9A0CC19B-9348-48FF-A0CC-CA3DEFCF51A5}"/>
     <hyperlink ref="F298" r:id="rId111" display="無影言本祭" xr:uid="{0BA89E84-457B-4E28-945D-1DCDB15B63B0}"/>
-    <hyperlink ref="E337" r:id="rId112" xr:uid="{C6217001-1ED9-4BE7-914A-0BDBF5BE318C}"/>
-    <hyperlink ref="E338" r:id="rId113" xr:uid="{BC9E6940-FF9A-4756-BB1B-0C4403762254}"/>
+    <hyperlink ref="E336" r:id="rId112" xr:uid="{C6217001-1ED9-4BE7-914A-0BDBF5BE318C}"/>
+    <hyperlink ref="E337" r:id="rId113" xr:uid="{BC9E6940-FF9A-4756-BB1B-0C4403762254}"/>
     <hyperlink ref="F216" r:id="rId114" xr:uid="{3C6377C7-1B66-4476-8E9C-A9D5A878A0AE}"/>
     <hyperlink ref="F259" r:id="rId115" xr:uid="{AA40B19D-9046-4C74-B04E-EDD95592AD0F}"/>
     <hyperlink ref="F163" r:id="rId116" xr:uid="{921360D1-C8F1-47DC-8965-EF1A27211120}"/>
     <hyperlink ref="F257" r:id="rId117" xr:uid="{D1CEAB88-533B-4592-96F7-9C2CA0598EF3}"/>
     <hyperlink ref="F232" r:id="rId118" xr:uid="{35EA88DE-206B-4EF8-9259-9E1E793C9E5B}"/>
     <hyperlink ref="F314" r:id="rId119" xr:uid="{00BD4916-443C-4D61-ADBA-08351BF0AA95}"/>
-    <hyperlink ref="E339" r:id="rId120" xr:uid="{35DD3EBE-71F4-4631-AFA7-387F800E7B2F}"/>
+    <hyperlink ref="E338" r:id="rId120" xr:uid="{35DD3EBE-71F4-4631-AFA7-387F800E7B2F}"/>
     <hyperlink ref="F330" r:id="rId121" xr:uid="{411BBBFD-4B20-4B8E-B6D7-4425E0FB9182}"/>
     <hyperlink ref="F329" r:id="rId122" xr:uid="{8FE7C2D8-229B-435B-8354-9A0EA83B7570}"/>
     <hyperlink ref="H193" r:id="rId123" xr:uid="{5A06E54E-D7FA-4163-B78F-09FB36783946}"/>
@@ -17268,7 +17272,7 @@
         <v>。</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
@@ -18135,7 +18139,7 @@
       </c>
       <c r="DE4" s="6" t="str">
         <f>_xlfn.XLOOKUP(DD4,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>捌?</v>
+        <v>避?</v>
       </c>
       <c r="DF4" s="7" t="s">
         <v>198</v>
@@ -20628,7 +20632,7 @@
       </c>
       <c r="CI9" s="6" t="str">
         <f>_xlfn.XLOOKUP(CH9,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>広?</v>
+        <v>広</v>
       </c>
       <c r="CJ9" s="7" t="s">
         <v>542</v>
@@ -24079,7 +24083,7 @@
       </c>
       <c r="AS16" s="6" t="str">
         <f>_xlfn.XLOOKUP(AR16,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>[侱]?</v>
+        <v>難?</v>
       </c>
       <c r="AT16" s="7" t="s">
         <v>1022</v>
@@ -27603,7 +27607,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -27688,489 +27692,492 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B1" s="45" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D1" s="46" t="s">
         <v>2125</v>
       </c>
-      <c r="C1" s="46" t="s">
-        <v>2126</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>2127</v>
-      </c>
       <c r="E1" s="46" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>2121</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>2122</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>2123</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>2124</v>
-      </c>
       <c r="E2" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D3" s="36" t="s">
         <v>2232</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>2233</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>2234</v>
-      </c>
       <c r="E3" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D4" s="36" t="s">
         <v>2235</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>2236</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>2237</v>
-      </c>
       <c r="E4" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
+        <v>2236</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>2238</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>2239</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>2240</v>
-      </c>
       <c r="E5" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>2241</v>
       </c>
-      <c r="C6" s="36" t="s">
-        <v>2242</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>2243</v>
-      </c>
       <c r="E6" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D7" s="36" t="s">
         <v>2244</v>
       </c>
-      <c r="C7" s="36" t="s">
-        <v>2245</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>2246</v>
-      </c>
       <c r="E7" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D9" s="36" t="s">
         <v>2249</v>
       </c>
-      <c r="C9" s="36" t="s">
-        <v>2250</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>2251</v>
-      </c>
       <c r="E9" s="36" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D11" s="36" t="s">
         <v>2254</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>2255</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>2256</v>
-      </c>
       <c r="E11" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="C14" s="36" t="s">
+        <v>2336</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E14" s="36" t="s">
         <v>2338</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>2256</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>2340</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="35" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D19" s="36" t="s">
         <v>2455</v>
       </c>
-      <c r="C19" s="36" t="s">
-        <v>2456</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>2457</v>
-      </c>
       <c r="E19" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="44" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="35" t="s">
+        <v>2528</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D21" s="36" t="s">
         <v>2530</v>
       </c>
-      <c r="C21" s="36" t="s">
-        <v>2531</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>2532</v>
-      </c>
       <c r="E21" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="35" t="s">
+        <v>2531</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D22" s="36" t="s">
         <v>2533</v>
       </c>
-      <c r="C22" s="36" t="s">
-        <v>2534</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>2535</v>
-      </c>
       <c r="E22" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="35" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="35" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="35" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B26" s="35" t="s">
+        <v>2540</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D26" s="36" t="s">
         <v>2542</v>
       </c>
-      <c r="C26" s="36" t="s">
-        <v>2543</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>2544</v>
-      </c>
       <c r="E26" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="35" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="35" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="35" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B30" s="35" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B31" s="35" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B32" s="35" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D32" s="36" t="s">
         <v>2560</v>
       </c>
-      <c r="C32" s="36" t="s">
-        <v>2561</v>
-      </c>
-      <c r="D32" s="36" t="s">
-        <v>2562</v>
-      </c>
       <c r="E32" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B33" s="35" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B34" s="39" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B35" s="35" t="s">
-        <v>2602</v>
+        <v>2596</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>2603</v>
+        <v>2597</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>2256</v>
+        <v>2254</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>2607</v>
       </c>
     </row>
   </sheetData>
@@ -28181,7 +28188,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED28C13D-14D9-4671-B3CF-1ADD2E368C21}">
-  <dimension ref="B1:D297"/>
+  <dimension ref="B1:D301"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="31"/>
@@ -28191,387 +28198,387 @@
   <sheetData>
     <row r="1" spans="2:4" s="49" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="47" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="C1" s="48" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="D1" s="48" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="31" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" s="31" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="31" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" s="31" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="31" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="31" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="31" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B10" s="31" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="31" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B12" s="31" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="31" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="31" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="31" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="31" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="31" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="31" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="31" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="31" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="31" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="31" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="31" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="31" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="31" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="31" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="31" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="31" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="31" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="31" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="31" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.4">
@@ -28579,443 +28586,443 @@
         <v>1160</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B55" s="31" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D62" s="32" t="s">
-        <v>2575</v>
+        <v>2105</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>2573</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B65" s="31" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B66" s="31" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B67" s="31" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B68" s="31" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B69" s="31" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B70" s="31" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B71" s="31" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="31" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B73" s="31" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B74" s="31" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="31" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="31" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B79" s="31" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B80" s="31" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B81" s="31" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B82" s="31" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="C82" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B83" s="31" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B84" s="31" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="C84" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B85" s="31" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="C85" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B86" s="31" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="C86" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B87" s="31" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B88" s="31" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B89" s="31" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B90" s="31" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B91" s="31" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B92" s="31" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B93" s="31" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="D93" s="34" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="D94" s="34" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B95" s="31" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C95" s="34" t="s">
         <v>2264</v>
-      </c>
-      <c r="C95" s="34" t="s">
-        <v>2266</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B96" s="31" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="31" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="31" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="31" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
@@ -29023,1576 +29030,1614 @@
         <v>949</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="31" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B105" s="31" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="31" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C106" s="34" t="s">
         <v>2274</v>
-      </c>
-      <c r="C106" s="34" t="s">
-        <v>2276</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="31" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="31" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="31" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="31" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="31" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="31" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="31" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="31" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="31" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="31" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="31" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="31" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="31" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="31" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="31" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="31" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="31" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="31" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B129" s="31" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B130" s="31" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B131" s="31" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C131" s="34" t="s">
         <v>2302</v>
       </c>
-      <c r="C131" s="34" t="s">
-        <v>2304</v>
-      </c>
       <c r="D131" s="34" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B132" s="31" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2304</v>
+        <v>2302</v>
+      </c>
+      <c r="D132" s="34" t="s">
+        <v>2315</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B134" s="31" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B135" s="31" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B136" s="31" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B137" s="31" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C137" s="34" t="s">
         <v>2309</v>
-      </c>
-      <c r="C137" s="34" t="s">
-        <v>2311</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B138" s="31" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B140" s="31" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B141" s="31" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B142" s="31" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C142" s="34" t="s">
         <v>2315</v>
-      </c>
-      <c r="C142" s="34" t="s">
-        <v>2317</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B143" s="31" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B145" s="31" t="s">
+        <v>2317</v>
+      </c>
+      <c r="C145" s="34" t="s">
         <v>2319</v>
-      </c>
-      <c r="C145" s="34" t="s">
-        <v>2321</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B146" s="31" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B148" s="31" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B149" s="31" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B150" s="31" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B151" s="31" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B152" s="31" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="C152" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B153" s="31" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="C153" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B154" s="31" t="s">
+        <v>2327</v>
+      </c>
+      <c r="C154" s="34" t="s">
         <v>2329</v>
-      </c>
-      <c r="C154" s="34" t="s">
-        <v>2331</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B155" s="31" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="C156" s="34" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B157" s="31" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B158" s="31" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C158" s="34" t="s">
         <v>2334</v>
-      </c>
-      <c r="C158" s="34" t="s">
-        <v>2336</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B159" s="31" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C166" s="34" t="s">
         <v>2348</v>
-      </c>
-      <c r="C166" s="34" t="s">
-        <v>2350</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B168" s="31" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C168" s="34" t="s">
         <v>2353</v>
-      </c>
-      <c r="C168" s="34" t="s">
-        <v>2355</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B172" s="31" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="D173" s="34" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C175" s="34" t="s">
         <v>2359</v>
-      </c>
-      <c r="C175" s="34" t="s">
-        <v>2361</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
+        <v>2486</v>
+      </c>
+      <c r="C178" s="34" t="s">
         <v>2488</v>
-      </c>
-      <c r="C178" s="34" t="s">
-        <v>2490</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B182" s="31" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B183" s="31" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B184" s="31" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B185" s="31" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C185" s="34" t="s">
         <v>2370</v>
-      </c>
-      <c r="C185" s="34" t="s">
-        <v>2372</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B186" s="31" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B188" s="31" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B189" s="31" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C189" s="34" t="s">
         <v>2375</v>
-      </c>
-      <c r="C189" s="34" t="s">
-        <v>2377</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B190" s="31" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B192" s="31" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C192" s="34" t="s">
         <v>2379</v>
-      </c>
-      <c r="C192" s="34" t="s">
-        <v>2381</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B193" s="31" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B196" s="31" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B197" s="31" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C197" s="34" t="s">
         <v>2384</v>
-      </c>
-      <c r="C197" s="34" t="s">
-        <v>2386</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B198" s="31" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B200" s="31" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B201" s="31" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B202" s="31" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C202" s="34" t="s">
         <v>2390</v>
-      </c>
-      <c r="C202" s="34" t="s">
-        <v>2392</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B203" s="31" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B207" s="31" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B208" s="31" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C208" s="34" t="s">
         <v>2397</v>
-      </c>
-      <c r="C208" s="34" t="s">
-        <v>2399</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B209" s="31" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B211" s="31" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B212" s="31" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C212" s="34" t="s">
         <v>2402</v>
-      </c>
-      <c r="C212" s="34" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B213" s="31" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="C214" s="34" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B215" s="31" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C215" s="34" t="s">
         <v>2406</v>
-      </c>
-      <c r="C215" s="34" t="s">
-        <v>2408</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B216" s="31" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B218" s="31" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
+        <v>2415</v>
+      </c>
+      <c r="C219" s="34" t="s">
         <v>2417</v>
-      </c>
-      <c r="C219" s="34" t="s">
-        <v>2419</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B220" s="31" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="C221" s="34" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="C223" s="42" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C224" s="34" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B225" s="31" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C225" s="34" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B226" s="31" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C226" s="34" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D226" s="34" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B227" s="31" t="s">
+        <v>2603</v>
+      </c>
+      <c r="C227" s="34" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B228" s="31" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C228" s="34" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B229" s="31" t="s">
+        <v>2424</v>
+      </c>
+      <c r="C229" s="34" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B230" s="31" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C230" s="34" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B231" s="31" t="s">
         <v>2426</v>
       </c>
-      <c r="C224" s="34" t="s">
+      <c r="C231" s="34" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B232" s="31" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C232" s="34" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B233" s="31" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C233" s="34" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B234" s="31" t="s">
         <v>2429</v>
       </c>
-    </row>
-    <row r="225" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B225" s="31" t="s">
-        <v>2427</v>
-      </c>
-      <c r="C225" s="34" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B226" s="31" t="s">
-        <v>2428</v>
-      </c>
-      <c r="C226" s="34" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B227" s="31" t="s">
-        <v>2348</v>
-      </c>
-      <c r="C227" s="34" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="228" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B228" s="31" t="s">
+      <c r="C234" s="34" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B235" s="31" t="s">
         <v>2430</v>
       </c>
-      <c r="C228" s="34" t="s">
+      <c r="C235" s="34" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B236" s="31" t="s">
+        <v>2432</v>
+      </c>
+      <c r="C236" s="34" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B237" s="31" t="s">
         <v>2433</v>
       </c>
-    </row>
-    <row r="229" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B229" s="31" t="s">
-        <v>2431</v>
-      </c>
-      <c r="C229" s="34" t="s">
-        <v>2433</v>
-      </c>
-    </row>
-    <row r="230" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B230" s="31" t="s">
-        <v>2432</v>
-      </c>
-      <c r="C230" s="34" t="s">
-        <v>2433</v>
-      </c>
-    </row>
-    <row r="231" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B231" s="31" t="s">
+      <c r="C237" s="34" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B238" s="31" t="s">
         <v>2434</v>
       </c>
-      <c r="C231" s="34" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="232" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B232" s="31" t="s">
+      <c r="C238" s="34" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B239" s="31" t="s">
         <v>2435</v>
       </c>
-      <c r="C232" s="34" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="233" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B233" s="31" t="s">
+      <c r="C239" s="34" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B240" s="31" t="s">
         <v>2436</v>
       </c>
-      <c r="C233" s="34" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="234" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B234" s="31" t="s">
+      <c r="C240" s="34" t="s">
         <v>2437</v>
-      </c>
-      <c r="C234" s="34" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="235" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B235" s="31" t="s">
-        <v>2438</v>
-      </c>
-      <c r="C235" s="34" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="236" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B236" s="31" t="s">
-        <v>2440</v>
-      </c>
-      <c r="C236" s="34" t="s">
-        <v>2441</v>
-      </c>
-    </row>
-    <row r="237" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B237" s="31" t="s">
-        <v>2442</v>
-      </c>
-      <c r="C237" s="34" t="s">
-        <v>2443</v>
-      </c>
-    </row>
-    <row r="238" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B238" s="31" t="s">
-        <v>2444</v>
-      </c>
-      <c r="C238" s="34" t="s">
-        <v>2445</v>
-      </c>
-    </row>
-    <row r="239" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B239" s="31" t="s">
-        <v>2446</v>
-      </c>
-      <c r="C239" s="34" t="s">
-        <v>2451</v>
-      </c>
-    </row>
-    <row r="240" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B240" s="31" t="s">
-        <v>2447</v>
-      </c>
-      <c r="C240" s="34" t="s">
-        <v>2451</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B241" s="31" t="s">
-        <v>2448</v>
+        <v>2438</v>
       </c>
       <c r="C241" s="34" t="s">
-        <v>2451</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B242" s="31" t="s">
-        <v>2449</v>
+        <v>2440</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2451</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B243" s="31" t="s">
-        <v>2450</v>
+        <v>2442</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2451</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2452</v>
-      </c>
-      <c r="C244" s="32" t="s">
-        <v>2548</v>
+        <v>2444</v>
+      </c>
+      <c r="C244" s="34" t="s">
+        <v>2449</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
-        <v>2546</v>
-      </c>
-      <c r="C245" s="32" t="s">
-        <v>2548</v>
+        <v>2445</v>
+      </c>
+      <c r="C245" s="34" t="s">
+        <v>2449</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B246" s="31" t="s">
-        <v>2547</v>
-      </c>
-      <c r="C246" s="32" t="s">
-        <v>2548</v>
+        <v>2446</v>
+      </c>
+      <c r="C246" s="34" t="s">
+        <v>2449</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
-        <v>2454</v>
-      </c>
-      <c r="C247" s="32" t="s">
-        <v>2548</v>
+        <v>2447</v>
+      </c>
+      <c r="C247" s="34" t="s">
+        <v>2449</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2464</v>
+        <v>2448</v>
       </c>
       <c r="C248" s="34" t="s">
-        <v>2098</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2465</v>
-      </c>
-      <c r="C249" s="34" t="s">
-        <v>2098</v>
+        <v>2450</v>
+      </c>
+      <c r="C249" s="32" t="s">
+        <v>2546</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2466</v>
-      </c>
-      <c r="C250" s="34" t="s">
-        <v>2098</v>
+        <v>2544</v>
+      </c>
+      <c r="C250" s="32" t="s">
+        <v>2546</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2467</v>
-      </c>
-      <c r="C251" s="34" t="s">
-        <v>2098</v>
+        <v>2545</v>
+      </c>
+      <c r="C251" s="32" t="s">
+        <v>2546</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2469</v>
-      </c>
-      <c r="C252" s="34" t="s">
-        <v>2097</v>
+        <v>2452</v>
+      </c>
+      <c r="C252" s="32" t="s">
+        <v>2546</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2470</v>
-      </c>
-      <c r="C253" s="32" t="s">
-        <v>2106</v>
+        <v>2462</v>
+      </c>
+      <c r="C253" s="34" t="s">
+        <v>2096</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2471</v>
-      </c>
-      <c r="C254" s="32" t="s">
-        <v>2106</v>
+        <v>2463</v>
+      </c>
+      <c r="C254" s="34" t="s">
+        <v>2096</v>
       </c>
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2472</v>
-      </c>
-      <c r="C255" s="32" t="s">
-        <v>2106</v>
+        <v>2464</v>
+      </c>
+      <c r="C255" s="34" t="s">
+        <v>2096</v>
       </c>
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2473</v>
+        <v>2465</v>
       </c>
       <c r="C256" s="34" t="s">
-        <v>2480</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2474</v>
+        <v>2467</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2480</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
-        <v>2475</v>
-      </c>
-      <c r="C258" s="34" t="s">
-        <v>2480</v>
+        <v>2468</v>
+      </c>
+      <c r="C258" s="32" t="s">
+        <v>2104</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
-        <v>2476</v>
-      </c>
-      <c r="C259" s="34" t="s">
-        <v>2480</v>
+        <v>2469</v>
+      </c>
+      <c r="C259" s="32" t="s">
+        <v>2104</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2477</v>
-      </c>
-      <c r="C260" s="34" t="s">
-        <v>2480</v>
+        <v>2470</v>
+      </c>
+      <c r="C260" s="32" t="s">
+        <v>2104</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
+        <v>2471</v>
+      </c>
+      <c r="C261" s="34" t="s">
         <v>2478</v>
-      </c>
-      <c r="C261" s="34" t="s">
-        <v>2480</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
-        <v>2479</v>
+        <v>2472</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
-        <v>2322</v>
+        <v>2473</v>
       </c>
       <c r="C263" s="34" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2481</v>
+        <v>2474</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2490</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
-        <v>2482</v>
+        <v>2475</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2490</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2483</v>
+        <v>2476</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2490</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2484</v>
+        <v>2477</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2490</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
-        <v>2485</v>
+        <v>2320</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2490</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2231</v>
+        <v>2479</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2486</v>
+        <v>2480</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
-        <v>2487</v>
+        <v>2481</v>
       </c>
       <c r="C271" s="34" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2491</v>
-      </c>
-      <c r="C272" s="32" t="s">
-        <v>2468</v>
+        <v>2482</v>
+      </c>
+      <c r="C272" s="34" t="s">
+        <v>2488</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
-        <v>2195</v>
-      </c>
-      <c r="C273" s="32" t="s">
-        <v>2468</v>
+        <v>2483</v>
+      </c>
+      <c r="C273" s="34" t="s">
+        <v>2488</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2492</v>
-      </c>
-      <c r="C274" s="32" t="s">
-        <v>2468</v>
+        <v>2229</v>
+      </c>
+      <c r="C274" s="34" t="s">
+        <v>2488</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2493</v>
+        <v>2484</v>
       </c>
       <c r="C275" s="34" t="s">
-        <v>2495</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
-        <v>2494</v>
+        <v>2485</v>
       </c>
       <c r="C276" s="34" t="s">
-        <v>2495</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2498</v>
+        <v>2489</v>
       </c>
       <c r="C277" s="32" t="s">
-        <v>2091</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2499</v>
+        <v>2193</v>
       </c>
       <c r="C278" s="32" t="s">
-        <v>2091</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2500</v>
+        <v>2490</v>
       </c>
       <c r="C279" s="32" t="s">
-        <v>2091</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="280" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B280" s="31" t="s">
-        <v>2501</v>
+        <v>2491</v>
       </c>
       <c r="C280" s="34" t="s">
-        <v>2258</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="281" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B281" s="31" t="s">
-        <v>2502</v>
+        <v>2492</v>
       </c>
       <c r="C281" s="34" t="s">
-        <v>2258</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="282" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B282" s="31" t="s">
-        <v>2586</v>
-      </c>
-      <c r="C282" s="34" t="s">
-        <v>2566</v>
+        <v>2496</v>
+      </c>
+      <c r="C282" s="32" t="s">
+        <v>2089</v>
       </c>
     </row>
     <row r="283" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B283" s="31" t="s">
-        <v>2587</v>
-      </c>
-      <c r="C283" s="34" t="s">
-        <v>2566</v>
+        <v>2497</v>
+      </c>
+      <c r="C283" s="32" t="s">
+        <v>2089</v>
       </c>
     </row>
     <row r="284" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B284" s="31" t="s">
-        <v>2588</v>
-      </c>
-      <c r="C284" s="34" t="s">
-        <v>2566</v>
+        <v>2498</v>
+      </c>
+      <c r="C284" s="32" t="s">
+        <v>2089</v>
       </c>
     </row>
     <row r="285" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B285" s="31" t="s">
-        <v>2589</v>
-      </c>
-      <c r="C285" s="32" t="s">
-        <v>2573</v>
+        <v>2499</v>
+      </c>
+      <c r="C285" s="34" t="s">
+        <v>2256</v>
       </c>
     </row>
     <row r="286" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B286" s="31" t="s">
-        <v>2590</v>
+        <v>2500</v>
       </c>
       <c r="C286" s="34" t="s">
-        <v>2591</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="287" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B287" s="31" t="s">
-        <v>2592</v>
+        <v>2580</v>
       </c>
       <c r="C287" s="34" t="s">
-        <v>2596</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="288" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B288" s="31" t="s">
-        <v>2593</v>
+        <v>2581</v>
       </c>
       <c r="C288" s="34" t="s">
-        <v>2596</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="289" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B289" s="31" t="s">
-        <v>2195</v>
+        <v>2582</v>
       </c>
       <c r="C289" s="34" t="s">
-        <v>2596</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="290" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B290" s="31" t="s">
-        <v>2196</v>
-      </c>
-      <c r="C290" s="34" t="s">
-        <v>2596</v>
+        <v>2583</v>
+      </c>
+      <c r="C290" s="32" t="s">
+        <v>2571</v>
       </c>
     </row>
     <row r="291" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B291" s="31" t="s">
-        <v>2594</v>
+        <v>2584</v>
       </c>
       <c r="C291" s="34" t="s">
-        <v>2596</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="292" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B292" s="31" t="s">
-        <v>2595</v>
+        <v>2586</v>
       </c>
       <c r="C292" s="34" t="s">
-        <v>2596</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="293" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B293" s="31" t="s">
-        <v>2332</v>
+        <v>2587</v>
       </c>
       <c r="C293" s="34" t="s">
-        <v>2580</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="294" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B294" s="31" t="s">
-        <v>2597</v>
+        <v>2193</v>
       </c>
       <c r="C294" s="34" t="s">
-        <v>2580</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="295" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B295" s="31" t="s">
-        <v>2598</v>
+        <v>2194</v>
       </c>
       <c r="C295" s="34" t="s">
-        <v>2580</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="296" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B296" s="31" t="s">
-        <v>2600</v>
-      </c>
-      <c r="C296" s="32" t="s">
-        <v>2575</v>
+        <v>2588</v>
+      </c>
+      <c r="C296" s="34" t="s">
+        <v>2590</v>
       </c>
     </row>
     <row r="297" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B297" s="31" t="s">
-        <v>2601</v>
-      </c>
-      <c r="C297" s="32" t="s">
-        <v>2575</v>
+        <v>2589</v>
+      </c>
+      <c r="C297" s="34" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B298" s="31" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C298" s="34" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B299" s="31" t="s">
+        <v>2591</v>
+      </c>
+      <c r="C299" s="34" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B300" s="31" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C300" s="34" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B301" s="31" t="s">
+        <v>2594</v>
+      </c>
+      <c r="C301" s="32" t="s">
+        <v>2573</v>
       </c>
     </row>
   </sheetData>
@@ -30698,59 +30743,62 @@
     <hyperlink ref="C218" r:id="rId98" xr:uid="{E32A61DB-E7C1-4C00-A9EA-3C2EE69560FA}"/>
     <hyperlink ref="C221" r:id="rId99" xr:uid="{F3012094-E137-4787-AE48-4A8F62EFE745}"/>
     <hyperlink ref="C222" r:id="rId100" xr:uid="{25CF5C66-B1C6-4B3A-84C7-C4ADF6D77959}"/>
-    <hyperlink ref="C224" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
-    <hyperlink ref="C225:C227" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
-    <hyperlink ref="C228" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
-    <hyperlink ref="C229:C230" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
-    <hyperlink ref="C231" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
-    <hyperlink ref="C232:C235" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
-    <hyperlink ref="C236" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
-    <hyperlink ref="C237" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
-    <hyperlink ref="C238" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
-    <hyperlink ref="C239" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
-    <hyperlink ref="C240:C243" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
+    <hyperlink ref="C229" r:id="rId101" xr:uid="{839EE523-C1EB-477A-937F-EE6EB1036699}"/>
+    <hyperlink ref="C230:C232" r:id="rId102" display="さかな屋" xr:uid="{07DEDAE6-0F0E-4F55-97E0-BD142C9B27AE}"/>
+    <hyperlink ref="C233" r:id="rId103" xr:uid="{502DBEC4-B7C5-4CFC-8584-ABDD4EA3F6ED}"/>
+    <hyperlink ref="C234:C235" r:id="rId104" display="にく屋" xr:uid="{DC6B22BE-216D-4D5A-8D80-2FAFCDB0AC3F}"/>
+    <hyperlink ref="C236" r:id="rId105" xr:uid="{EE401DC3-88F7-4249-8C9A-96605006DE2C}"/>
+    <hyperlink ref="C237:C240" r:id="rId106" display="やお屋" xr:uid="{12F780BD-5767-45CC-9334-FFF2BD577551}"/>
+    <hyperlink ref="C241" r:id="rId107" xr:uid="{AE17D87F-99BC-4B4D-A0DE-0E71DF97404B}"/>
+    <hyperlink ref="C242" r:id="rId108" xr:uid="{7CCF7295-4566-4BEF-8FF1-D5E5CCB7831A}"/>
+    <hyperlink ref="C243" r:id="rId109" xr:uid="{15AA386F-0DE6-4B5E-A7D5-A9425E0E9828}"/>
+    <hyperlink ref="C244" r:id="rId110" xr:uid="{D0B30C17-F063-4561-B237-C8C1CA22DFD0}"/>
+    <hyperlink ref="C245:C248" r:id="rId111" display="ろう" xr:uid="{3BD43DBD-55EF-41BE-A011-822B56E450C7}"/>
     <hyperlink ref="C223" r:id="rId112" display="●壁？" xr:uid="{49CFE894-D6FF-4DAD-A18A-E33C19DC9AC5}"/>
     <hyperlink ref="D74" r:id="rId113" xr:uid="{F3D3E429-A98C-4A89-8517-136EBFF9C669}"/>
-    <hyperlink ref="C252" r:id="rId114" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
-    <hyperlink ref="C253" r:id="rId115" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
-    <hyperlink ref="C254:C255" r:id="rId116" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
-    <hyperlink ref="C256" r:id="rId117" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
-    <hyperlink ref="C257:C263" r:id="rId118" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
-    <hyperlink ref="C264" r:id="rId119" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
-    <hyperlink ref="C265:C271" r:id="rId120" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
-    <hyperlink ref="C272" r:id="rId121" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
-    <hyperlink ref="C273" r:id="rId122" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
-    <hyperlink ref="C274" r:id="rId123" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
-    <hyperlink ref="C275" r:id="rId124" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
-    <hyperlink ref="C276" r:id="rId125" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
-    <hyperlink ref="C277" r:id="rId126" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
-    <hyperlink ref="C278" r:id="rId127" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
-    <hyperlink ref="C279" r:id="rId128" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
-    <hyperlink ref="C280" r:id="rId129" xr:uid="{638B7DD6-1594-44CE-9207-871F21E21DD3}"/>
-    <hyperlink ref="C281" r:id="rId130" xr:uid="{0A4BE00D-CD86-4A4E-ADBB-82650B816BF4}"/>
-    <hyperlink ref="C244" r:id="rId131" display="無影言本祭" xr:uid="{8D13B183-FF2F-461F-87EA-DF266C32877C}"/>
-    <hyperlink ref="C245" r:id="rId132" display="無影言本祭" xr:uid="{1204C86E-B414-49FA-9E5E-D39D616244E1}"/>
-    <hyperlink ref="C246:C247" r:id="rId133" display="無影言本祭" xr:uid="{E5562058-48A6-4B14-99CC-EFD928C85B1B}"/>
+    <hyperlink ref="C257" r:id="rId114" xr:uid="{65E40566-30C3-4405-8F7A-889FBFB7DFFA}"/>
+    <hyperlink ref="C258" r:id="rId115" xr:uid="{BE4AA912-B770-40E4-B906-EAE9C1551E1C}"/>
+    <hyperlink ref="C259:C260" r:id="rId116" display="防人？" xr:uid="{2B5523F8-A971-4220-8F3C-30D15C2EFAC1}"/>
+    <hyperlink ref="C261" r:id="rId117" xr:uid="{A2738428-E5CC-4B2A-93E5-98A379E30895}"/>
+    <hyperlink ref="C262:C268" r:id="rId118" display="けがれ" xr:uid="{0008DCD2-FF21-4623-AAC5-7D91862F0C2E}"/>
+    <hyperlink ref="C269" r:id="rId119" xr:uid="{BD07EEFC-0953-41F4-B152-A03CB1E62DC4}"/>
+    <hyperlink ref="C270:C276" r:id="rId120" display="うらみ" xr:uid="{AF7C3CCE-674F-45CE-8880-D3E6B96A72C7}"/>
+    <hyperlink ref="C277" r:id="rId121" display="○われ？" xr:uid="{93D39234-2F6B-48A9-AF1B-26A8DCC0436F}"/>
+    <hyperlink ref="C278" r:id="rId122" display="○われ？" xr:uid="{43B0567D-7FF1-4466-9A48-2925BB68E51E}"/>
+    <hyperlink ref="C279" r:id="rId123" display="○われ？" xr:uid="{730085F8-679A-4F43-A0AD-E4EC5F41661F}"/>
+    <hyperlink ref="C280" r:id="rId124" display="掟に関するお知らせ" xr:uid="{1A4DC9C6-4F62-44F4-BFAF-8D66E3D35D8B}"/>
+    <hyperlink ref="C281" r:id="rId125" display="掟に関するお知らせ" xr:uid="{EBD1E9CC-84B0-460B-A3E2-55F79D7D39D3}"/>
+    <hyperlink ref="C282" r:id="rId126" xr:uid="{E7E2781E-A84B-4ABF-BA0A-C0ACB4E628F5}"/>
+    <hyperlink ref="C283" r:id="rId127" xr:uid="{B4115520-C38F-4A66-BFE7-C7655D625C10}"/>
+    <hyperlink ref="C284" r:id="rId128" xr:uid="{7862982D-035B-43A4-B686-1000FA5D7C0D}"/>
+    <hyperlink ref="C285" r:id="rId129" xr:uid="{638B7DD6-1594-44CE-9207-871F21E21DD3}"/>
+    <hyperlink ref="C286" r:id="rId130" xr:uid="{0A4BE00D-CD86-4A4E-ADBB-82650B816BF4}"/>
+    <hyperlink ref="C249" r:id="rId131" display="無影言本祭" xr:uid="{8D13B183-FF2F-461F-87EA-DF266C32877C}"/>
+    <hyperlink ref="C250" r:id="rId132" display="無影言本祭" xr:uid="{1204C86E-B414-49FA-9E5E-D39D616244E1}"/>
+    <hyperlink ref="C251:C252" r:id="rId133" display="無影言本祭" xr:uid="{E5562058-48A6-4B14-99CC-EFD928C85B1B}"/>
     <hyperlink ref="C93" r:id="rId134" xr:uid="{157FEE6A-E3FD-4891-9A8C-DEA390CC9F8A}"/>
-    <hyperlink ref="C282" r:id="rId135" xr:uid="{0075B865-AC5C-4CD6-A96F-92FBBAAF2768}"/>
-    <hyperlink ref="C283" r:id="rId136" xr:uid="{C8BA9501-EE44-4CFB-8C71-4D8375052233}"/>
-    <hyperlink ref="C284" r:id="rId137" xr:uid="{C9150616-ED4F-4165-A477-B18E3B15B682}"/>
+    <hyperlink ref="C287" r:id="rId135" xr:uid="{0075B865-AC5C-4CD6-A96F-92FBBAAF2768}"/>
+    <hyperlink ref="C288" r:id="rId136" xr:uid="{C8BA9501-EE44-4CFB-8C71-4D8375052233}"/>
+    <hyperlink ref="C289" r:id="rId137" xr:uid="{C9150616-ED4F-4165-A477-B18E3B15B682}"/>
     <hyperlink ref="D39" r:id="rId138" xr:uid="{A814B798-1BD3-434C-B188-D49492030CCC}"/>
-    <hyperlink ref="C285" r:id="rId139" xr:uid="{C9E65C9C-C25F-45E6-B444-462D5DEBAEC0}"/>
-    <hyperlink ref="C286" r:id="rId140" xr:uid="{DBF7BAF5-49A3-4A8E-9DED-4B2887F3CE62}"/>
-    <hyperlink ref="C287" r:id="rId141" xr:uid="{856CA673-DC5F-4AEC-815F-9AD163802F68}"/>
-    <hyperlink ref="C288" r:id="rId142" xr:uid="{66C8586D-D06E-4AD0-9AC5-6D8C307A0945}"/>
-    <hyperlink ref="C289" r:id="rId143" xr:uid="{4D110E06-13FA-4A06-A46C-5E1613222922}"/>
-    <hyperlink ref="C290" r:id="rId144" xr:uid="{747DC27C-EFD4-4C85-8D9E-98E8076C2057}"/>
-    <hyperlink ref="C291" r:id="rId145" xr:uid="{0A0905C2-C20B-4D6D-8798-163F00EBF73E}"/>
-    <hyperlink ref="C292" r:id="rId146" xr:uid="{E708436D-D4B2-4575-AB05-3A5582112BA8}"/>
-    <hyperlink ref="C293" r:id="rId147" xr:uid="{BD02B744-CCFC-4E17-A6F9-B307C10818EA}"/>
-    <hyperlink ref="C294" r:id="rId148" xr:uid="{2E536251-83F9-4A2E-959C-69A043D41889}"/>
-    <hyperlink ref="C295" r:id="rId149" xr:uid="{93AC0A76-F50F-4760-8C14-2AC67D3644FA}"/>
+    <hyperlink ref="C290" r:id="rId139" xr:uid="{C9E65C9C-C25F-45E6-B444-462D5DEBAEC0}"/>
+    <hyperlink ref="C291" r:id="rId140" xr:uid="{DBF7BAF5-49A3-4A8E-9DED-4B2887F3CE62}"/>
+    <hyperlink ref="C292" r:id="rId141" xr:uid="{856CA673-DC5F-4AEC-815F-9AD163802F68}"/>
+    <hyperlink ref="C293" r:id="rId142" xr:uid="{66C8586D-D06E-4AD0-9AC5-6D8C307A0945}"/>
+    <hyperlink ref="C294" r:id="rId143" xr:uid="{4D110E06-13FA-4A06-A46C-5E1613222922}"/>
+    <hyperlink ref="C295" r:id="rId144" xr:uid="{747DC27C-EFD4-4C85-8D9E-98E8076C2057}"/>
+    <hyperlink ref="C296" r:id="rId145" xr:uid="{0A0905C2-C20B-4D6D-8798-163F00EBF73E}"/>
+    <hyperlink ref="C297" r:id="rId146" xr:uid="{E708436D-D4B2-4575-AB05-3A5582112BA8}"/>
+    <hyperlink ref="C298" r:id="rId147" xr:uid="{BD02B744-CCFC-4E17-A6F9-B307C10818EA}"/>
+    <hyperlink ref="C299" r:id="rId148" xr:uid="{2E536251-83F9-4A2E-959C-69A043D41889}"/>
+    <hyperlink ref="C300" r:id="rId149" xr:uid="{93AC0A76-F50F-4760-8C14-2AC67D3644FA}"/>
     <hyperlink ref="D173" r:id="rId150" xr:uid="{46A5ADB1-85DA-423D-B952-8BE749A562E8}"/>
-    <hyperlink ref="C296" r:id="rId151" xr:uid="{31232A6A-CA23-40C2-A40C-340903C41016}"/>
+    <hyperlink ref="C301" r:id="rId151" xr:uid="{31232A6A-CA23-40C2-A40C-340903C41016}"/>
     <hyperlink ref="D62" r:id="rId152" xr:uid="{6E0266CA-E8F5-47A8-A403-F33C1896B0E2}"/>
-    <hyperlink ref="C297" r:id="rId153" xr:uid="{7999C9A8-B4CB-4554-A69B-8553BF2B0081}"/>
+    <hyperlink ref="D226" r:id="rId153" xr:uid="{7999C9A8-B4CB-4554-A69B-8553BF2B0081}"/>
+    <hyperlink ref="C224" r:id="rId154" xr:uid="{526BD004-A80C-4961-870F-F33828CD8403}"/>
+    <hyperlink ref="C225:C228" r:id="rId155" display="祭だん" xr:uid="{82D9F577-9D3F-4642-8006-C0804437E317}"/>
+    <hyperlink ref="D132" r:id="rId156" xr:uid="{079AED01-7E13-48B1-AF30-0966E317E8BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2133" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76DE711C-29CE-4A27-B2C7-96DCFEBA07DF}"/>
+  <xr:revisionPtr revIDLastSave="2134" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0328935B-ED7B-45F5-922B-A13B4C360A93}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3353" uniqueCount="2737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="2735">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -12393,44 +12393,6 @@
   </si>
   <si>
     <t>丽</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>丽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]?</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>お丽ろ区さか屋</t>
   </si>
   <si>
     <t>匇</t>
@@ -13172,6 +13134,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -13489,7 +13455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:J344"/>
+  <dimension ref="A1:J343"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -14601,13 +14567,13 @@
         <v>2723</v>
       </c>
       <c r="C135" s="55" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D135" s="33" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E135" s="34" t="s">
         <v>2734</v>
-      </c>
-      <c r="D135" s="33" t="s">
-        <v>2735</v>
-      </c>
-      <c r="E135" s="34" t="s">
-        <v>2736</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.4">
@@ -15020,7 +14986,7 @@
         <v>757</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="E181" s="34" t="s">
         <v>2104</v>
@@ -15781,7 +15747,7 @@
         <v>2718</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="E251" s="34" t="s">
         <v>2094</v>
@@ -16903,13 +16869,13 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B341" s="1" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="C341" s="55" t="s">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="D341" s="33" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="E341" s="34" t="s">
         <v>2722</v>
@@ -16917,34 +16883,20 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B342" s="1" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="C342" s="55" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="E342" s="34" t="s">
         <v>2722</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B343" s="1" t="s">
-        <v>2729</v>
-      </c>
-      <c r="C343" s="55" t="s">
-        <v>2730</v>
-      </c>
-      <c r="D343" s="33" t="s">
-        <v>2731</v>
-      </c>
-      <c r="E343" s="34" t="s">
-        <v>2722</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A344" t="s">
+      <c r="A343" t="s">
         <v>1884</v>
       </c>
     </row>
@@ -17092,16 +17044,15 @@
     <hyperlink ref="F261" r:id="rId126" xr:uid="{F6A8D4BF-3BA3-4543-A279-4E8833A868D6}"/>
     <hyperlink ref="F277" r:id="rId127" xr:uid="{993902BA-7D34-48FB-8ACF-587A5B27410C}"/>
     <hyperlink ref="E340" r:id="rId128" xr:uid="{9AA5542F-D003-437E-8913-A9512DD01ADF}"/>
-    <hyperlink ref="E341" r:id="rId129" xr:uid="{8E545DFF-79B2-4813-A153-2F726141A418}"/>
-    <hyperlink ref="E342" r:id="rId130" xr:uid="{5A8B6FF2-64E9-40FB-A7C2-DF46C3FD4F52}"/>
-    <hyperlink ref="E343" r:id="rId131" xr:uid="{75E26C8C-85FC-485D-8511-5265A6C0CBAC}"/>
-    <hyperlink ref="E135" r:id="rId132" xr:uid="{73E16B9D-691D-42C8-A812-EF9F0DA5C4AA}"/>
-    <hyperlink ref="G180" r:id="rId133" xr:uid="{7343C3A1-5CF1-47F6-A5C4-7CF5A8BE76E7}"/>
-    <hyperlink ref="F250" r:id="rId134" xr:uid="{D139FC92-7C4A-469B-A143-9ADFF2564948}"/>
-    <hyperlink ref="F267" r:id="rId135" xr:uid="{E445BD3C-8B36-4199-8876-4A6BF79488C5}"/>
+    <hyperlink ref="E341" r:id="rId129" xr:uid="{5A8B6FF2-64E9-40FB-A7C2-DF46C3FD4F52}"/>
+    <hyperlink ref="E342" r:id="rId130" xr:uid="{75E26C8C-85FC-485D-8511-5265A6C0CBAC}"/>
+    <hyperlink ref="E135" r:id="rId131" xr:uid="{73E16B9D-691D-42C8-A812-EF9F0DA5C4AA}"/>
+    <hyperlink ref="G180" r:id="rId132" xr:uid="{7343C3A1-5CF1-47F6-A5C4-7CF5A8BE76E7}"/>
+    <hyperlink ref="F250" r:id="rId133" xr:uid="{D139FC92-7C4A-469B-A143-9ADFF2564948}"/>
+    <hyperlink ref="F267" r:id="rId134" xr:uid="{E445BD3C-8B36-4199-8876-4A6BF79488C5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId136"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId135"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2134" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0328935B-ED7B-45F5-922B-A13B4C360A93}"/>
+  <xr:revisionPtr revIDLastSave="2237" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ED5FC3A-AD67-411B-9F4F-E94D19437E9D}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView minimized="1" xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3349" uniqueCount="2735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="2760">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -6260,9 +6260,6 @@
     <t>か</t>
   </si>
   <si>
-    <t>丄</t>
-  </si>
-  <si>
     <t>き</t>
   </si>
   <si>
@@ -6455,9 +6452,6 @@
     <t>ぜ</t>
   </si>
   <si>
-    <t>仢</t>
-  </si>
-  <si>
     <t>ぞ</t>
   </si>
   <si>
@@ -6521,9 +6515,6 @@
     <t>ゃ</t>
   </si>
   <si>
-    <t>伖</t>
-  </si>
-  <si>
     <t>ゅ</t>
   </si>
   <si>
@@ -6857,9 +6848,6 @@
     <t>名</t>
   </si>
   <si>
-    <t>丏</t>
-  </si>
-  <si>
     <t>所</t>
   </si>
   <si>
@@ -7119,9 +7107,6 @@
   </si>
   <si>
     <t>匤</t>
-  </si>
-  <si>
-    <t>再?</t>
   </si>
   <si>
     <t>俳</t>
@@ -7307,9 +7292,6 @@
     <t>侕</t>
   </si>
   <si>
-    <t>亇</t>
-  </si>
-  <si>
     <t>义</t>
   </si>
   <si>
@@ -12176,16 +12158,6 @@
     <t>unicode表</t>
   </si>
   <si>
-    <t>○本壁とか</t>
-    <rPh sb="1" eb="2">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>桶地下考</t>
     <rPh sb="0" eb="4">
       <t>オケチカコウ</t>
@@ -12277,9 +12249,6 @@
     <t>焼肉屋</t>
   </si>
   <si>
-    <t>ラーメン屋</t>
-  </si>
-  <si>
     <t>ビストロ</t>
   </si>
   <si>
@@ -12319,10 +12288,6 @@
   </si>
   <si>
     <t>举丄丂乇儵</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>乏傯丗侕儵</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -12471,6 +12436,212 @@
   </si>
   <si>
     <t>おぼろ区</t>
+  </si>
+  <si>
+    <t>しゅくきぎ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桶地下考</t>
+    <rPh sb="0" eb="3">
+      <t>オケチカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丣伖乇丄亇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あった←？？！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○本壁とかかもしれない</t>
+    <rPh sb="1" eb="2">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>普</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>傚丄亇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>祝きぎ</t>
+    <rPh sb="0" eb="1">
+      <t>シュク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寄?</t>
+    <rPh sb="0" eb="1">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生</t>
+    <rPh sb="0" eb="1">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>僌丽买儼乡丌儵</t>
+  </si>
+  <si>
+    <t>おぼろ区さか屋</t>
+    <rPh sb="3" eb="4">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伛争</t>
+  </si>
+  <si>
+    <t>合ず</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単漢字</t>
+    <rPh sb="0" eb="3">
+      <t>タンカンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バッグに残されていたメモ　祝○儀？</t>
+    <rPh sb="4" eb="5">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>シュク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>々</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再へん ・再ど</t>
+    <rPh sb="0" eb="1">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>儷</t>
+  </si>
+  <si>
+    <t>除?</t>
+    <rPh sb="0" eb="1">
+      <t>ジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さく除されたか</t>
+    <rPh sb="2" eb="3">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーページ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丠</t>
+  </si>
+  <si>
+    <t>継?</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>业</t>
+  </si>
+  <si>
+    <t>葉?</t>
+    <rPh sb="0" eb="1">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>愛情？</t>
+    <rPh sb="0" eb="2">
+      <t>アイジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>来</t>
+    <rPh sb="0" eb="1">
+      <t>ライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>匇劈</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亡仢乇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満ぞく</t>
+    <rPh sb="0" eb="1">
+      <t>マン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -13134,10 +13305,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -13455,7 +13622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:J343"/>
+  <dimension ref="A1:J346"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -13468,7 +13635,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="49" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="49" t="s">
-        <v>1888</v>
+        <v>1883</v>
       </c>
       <c r="B1" s="50" t="s">
         <v>1560</v>
@@ -13477,25 +13644,25 @@
         <v>1561</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>2039</v>
+        <v>2033</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="52" t="s">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="52" t="s">
-        <v>2028</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="52" t="s">
-        <v>2029</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="52" t="s">
-        <v>2030</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -13732,7 +13899,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
-        <v>1881</v>
+        <v>1876</v>
       </c>
       <c r="C31">
         <v>29</v>
@@ -13844,7 +14011,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="1" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="C45">
         <v>43</v>
@@ -13988,7 +14155,7 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B63" s="1" t="s">
-        <v>1883</v>
+        <v>1878</v>
       </c>
       <c r="C63">
         <v>61</v>
@@ -14060,7 +14227,7 @@
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B72" s="1" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="C72" t="s">
         <v>1562</v>
@@ -14108,26 +14275,26 @@
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B78" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C78" t="s">
         <v>1572</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B79" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C79" t="s">
         <v>1574</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B80" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C80" t="s">
         <v>1576</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1577</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
@@ -14135,15 +14302,15 @@
         <v>72</v>
       </c>
       <c r="C81" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B82" s="1" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="C82" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.4">
@@ -14151,28 +14318,28 @@
         <v>1142</v>
       </c>
       <c r="C83" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B84" s="1" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
       <c r="C84" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B85" s="1" t="s">
-        <v>1887</v>
+        <v>1882</v>
       </c>
       <c r="C85" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B86" s="1" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
       <c r="C86" t="s">
         <v>863</v>
@@ -14183,15 +14350,15 @@
         <v>216</v>
       </c>
       <c r="C87" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B88" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C88" t="s">
         <v>1584</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.4">
@@ -14199,20 +14366,20 @@
         <v>373</v>
       </c>
       <c r="C89" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B90" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C90" t="s">
         <v>1587</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B91" s="1" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
       <c r="C91" t="s">
         <v>717</v>
@@ -14220,34 +14387,34 @@
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B92" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C92" t="s">
         <v>1589</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B93" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C93" t="s">
         <v>1591</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B94" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C94" t="s">
         <v>1593</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B95" s="1" t="s">
-        <v>1894</v>
+        <v>1889</v>
       </c>
       <c r="C95" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.4">
@@ -14255,28 +14422,28 @@
         <v>712</v>
       </c>
       <c r="C96" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C97" t="s">
         <v>1597</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C98" t="s">
         <v>1599</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="1" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="C99" t="s">
         <v>722</v>
@@ -14284,18 +14451,18 @@
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C100" t="s">
         <v>1601</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="1" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="C101" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
@@ -14303,23 +14470,23 @@
         <v>1214</v>
       </c>
       <c r="C102" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C103" t="s">
         <v>1605</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="1" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
       <c r="C104" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
@@ -14327,87 +14494,87 @@
         <v>287</v>
       </c>
       <c r="C105" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C106" t="s">
         <v>1609</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="1" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="C107" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="1" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="C108" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="1" t="s">
-        <v>1900</v>
+        <v>1895</v>
       </c>
       <c r="C109" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C110" t="s">
         <v>1614</v>
-      </c>
-      <c r="C110" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="1" t="s">
-        <v>1901</v>
+        <v>1896</v>
       </c>
       <c r="C111" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C112" t="s">
         <v>1617</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="1" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="C113" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="1" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="C114" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="1" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="C115" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
@@ -14415,116 +14582,116 @@
         <v>503</v>
       </c>
       <c r="C116" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="1" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="C117" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C118" t="s">
         <v>1624</v>
-      </c>
-      <c r="C118" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="1" t="s">
-        <v>1906</v>
+        <v>1147</v>
       </c>
       <c r="C119" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C120" t="s">
         <v>1627</v>
-      </c>
-      <c r="C120" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="1" t="s">
-        <v>1907</v>
+        <v>1901</v>
       </c>
       <c r="C121" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="1" t="s">
-        <v>1908</v>
+        <v>1902</v>
       </c>
       <c r="C122" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="1" t="s">
-        <v>1909</v>
+        <v>1903</v>
       </c>
       <c r="C123" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="1" t="s">
-        <v>1910</v>
+        <v>1904</v>
       </c>
       <c r="C124" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C125" t="s">
         <v>1633</v>
-      </c>
-      <c r="C125" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C126" t="s">
         <v>1635</v>
-      </c>
-      <c r="C126" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="1" t="s">
-        <v>1637</v>
+        <v>2756</v>
       </c>
       <c r="C127" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="1" t="s">
-        <v>1911</v>
+        <v>1905</v>
       </c>
       <c r="C128" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B129" s="1" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="C129" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B130" s="1" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="C130" t="s">
         <v>81</v>
@@ -14532,10 +14699,10 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B131" s="1" t="s">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="C131" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.4">
@@ -14543,194 +14710,194 @@
         <v>73</v>
       </c>
       <c r="C132" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B133" s="1" t="s">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="C133" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B134" s="1" t="s">
-        <v>1914</v>
+        <v>1908</v>
       </c>
       <c r="C134" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B135" s="1" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C135" s="55" t="s">
         <v>2723</v>
       </c>
-      <c r="C135" s="55" t="s">
-        <v>2732</v>
-      </c>
       <c r="D135" s="33" t="s">
-        <v>2733</v>
+        <v>2724</v>
       </c>
       <c r="E135" s="34" t="s">
-        <v>2734</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B136" s="1" t="s">
-        <v>1915</v>
+        <v>1909</v>
       </c>
       <c r="C136" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B137" s="1" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="C137" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B138" s="1" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="C138" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B139" s="1" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="C139" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B140" s="1" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="C140" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B141" s="1" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="C141" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B142" s="1" t="s">
-        <v>1916</v>
+        <v>1910</v>
       </c>
       <c r="C142" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B143" s="1" t="s">
-        <v>1659</v>
+        <v>1366</v>
       </c>
       <c r="C143" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B144" s="1" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="C144" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B145" s="1" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="C145" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B146" s="1" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="C146" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B147" s="1" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="C147" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B148" s="1" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="C148" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B149" s="1" t="s">
-        <v>1917</v>
+        <v>1911</v>
       </c>
       <c r="C149" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B150" s="1" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="C150" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B151" s="1" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="C151" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B152" s="1" t="s">
-        <v>1918</v>
+        <v>1912</v>
       </c>
       <c r="C152" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B153" s="1" t="s">
-        <v>1919</v>
+        <v>1913</v>
       </c>
       <c r="C153" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B154" s="1" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="C154" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B155" s="1" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="C155" t="s">
         <v>1433</v>
@@ -14738,162 +14905,162 @@
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B156" s="1" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="C156" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B157" s="1" t="s">
-        <v>1920</v>
+        <v>1914</v>
       </c>
       <c r="C157" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B158" s="1" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="C158" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="F158" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="G158" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B159" s="1" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="C159" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="D159" s="33" t="s">
-        <v>2033</v>
+        <v>2027</v>
       </c>
       <c r="E159" s="34" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B160" s="1" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
       <c r="C160" t="s">
-        <v>1997</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B161" s="1" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="C161" t="s">
-        <v>2019</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B162" s="1" t="s">
-        <v>1921</v>
+        <v>1915</v>
       </c>
       <c r="C162" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B163" s="1" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="C163" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>2073</v>
+        <v>2067</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>2499</v>
+        <v>2493</v>
       </c>
       <c r="F163" s="32" t="s">
-        <v>2559</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B164" s="1" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="C164" t="s">
-        <v>2596</v>
+        <v>2590</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>2560</v>
+        <v>2554</v>
       </c>
       <c r="E164" s="34" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B165" s="1" t="s">
-        <v>1922</v>
+        <v>1916</v>
       </c>
       <c r="C165" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B166" s="1" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="C166" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B167" s="1" t="s">
-        <v>1923</v>
+        <v>1917</v>
       </c>
       <c r="C167" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B168" s="1" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="C168" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B169" s="1" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
       <c r="C169" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B170" s="1" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="C170" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B171" s="1" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="C171" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B172" s="1" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="C172" t="s">
         <v>72</v>
@@ -14901,31 +15068,31 @@
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B173" s="1" t="s">
-        <v>1924</v>
+        <v>1918</v>
       </c>
       <c r="C173" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B174" s="1" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="C174" t="s">
-        <v>1980</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B175" s="1" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="C175" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B176" s="1" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
       <c r="C176" t="s">
         <v>856</v>
@@ -14933,375 +15100,375 @@
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B177" s="1" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
       <c r="C177" t="s">
-        <v>1998</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B178" s="1" t="s">
-        <v>1925</v>
+        <v>1919</v>
       </c>
       <c r="C178" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="179" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B179" s="1" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
       <c r="C179" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="F179" s="32" t="s">
-        <v>2102</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B180" s="1" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="C180" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="D180" s="33" t="s">
-        <v>2050</v>
+        <v>2044</v>
       </c>
       <c r="E180" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>2102</v>
+        <v>2096</v>
       </c>
       <c r="G180" s="34" t="s">
-        <v>2722</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B181" s="1" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="C181" t="s">
         <v>757</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>2730</v>
+        <v>2721</v>
       </c>
       <c r="E181" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B182" s="1" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
       <c r="C182" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B183" s="1" t="s">
-        <v>1926</v>
+        <v>1920</v>
       </c>
       <c r="C183" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B184" s="1" t="s">
-        <v>1927</v>
+        <v>1921</v>
       </c>
       <c r="C184" t="s">
-        <v>2123</v>
+        <v>2117</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2122</v>
+        <v>2116</v>
       </c>
       <c r="E184" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B185" s="1" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="C185" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>2121</v>
+        <v>2115</v>
       </c>
       <c r="E185" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B186" s="1" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="C186" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B187" s="1" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="C187" t="s">
-        <v>1977</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="188" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B188" s="1" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
       <c r="C188" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B189" s="1" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="C189" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
       <c r="D189" s="33" t="s">
-        <v>2044</v>
+        <v>2038</v>
       </c>
       <c r="E189" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B190" s="1" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
       <c r="C190" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B191" s="1" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="C191" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B192" s="1" t="s">
-        <v>1929</v>
+        <v>1923</v>
       </c>
       <c r="C192" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="193" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B193" s="1" t="s">
-        <v>1930</v>
+        <v>1924</v>
       </c>
       <c r="C193" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="E193" s="34" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="F193" s="32" t="s">
-        <v>2100</v>
+        <v>2094</v>
       </c>
       <c r="G193" s="32" t="s">
-        <v>2101</v>
+        <v>2095</v>
       </c>
       <c r="H193" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
       <c r="I193" s="34" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B194" s="1" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="C194" t="s">
-        <v>1976</v>
+        <v>1970</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>2581</v>
+        <v>2575</v>
       </c>
       <c r="E194" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>2100</v>
+        <v>2094</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>2101</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B195" s="1" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="C195" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="D195" s="33" t="s">
-        <v>2040</v>
+        <v>2034</v>
       </c>
       <c r="E195" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B196" s="1" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="C196" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="D196" s="33" t="s">
-        <v>2068</v>
+        <v>2062</v>
       </c>
       <c r="E196" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B197" s="1" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="C197" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="F197" s="34" t="s">
-        <v>2106</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B198" s="1" t="s">
-        <v>1931</v>
+        <v>1925</v>
       </c>
       <c r="C198" t="s">
-        <v>2127</v>
+        <v>2121</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>2117</v>
+        <v>2111</v>
       </c>
       <c r="E198" s="34" t="s">
-        <v>2098</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B199" s="1" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="C199" t="s">
-        <v>2128</v>
+        <v>2122</v>
       </c>
       <c r="F199" s="32" t="s">
-        <v>2099</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B200" s="1" t="s">
-        <v>1932</v>
+        <v>1926</v>
       </c>
       <c r="C200" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="D200" s="33" t="s">
-        <v>2069</v>
+        <v>2063</v>
       </c>
       <c r="E200" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B201" s="1" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="C201" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B202" s="1" t="s">
-        <v>1933</v>
+        <v>1927</v>
       </c>
       <c r="C202" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B203" s="1" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
       <c r="C203" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="204" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B204" s="1" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="C204" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B205" s="1" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="C205" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
       <c r="F205" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
       <c r="G205" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B206" s="1" t="s">
-        <v>1934</v>
+        <v>1928</v>
       </c>
       <c r="C206" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
       <c r="D206" s="33" t="s">
-        <v>2032</v>
+        <v>2026</v>
       </c>
       <c r="E206" s="34" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B207" s="1" t="s">
-        <v>1935</v>
+        <v>1929</v>
       </c>
       <c r="C207" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B208" s="1" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
       <c r="C208" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.4">
@@ -15309,21 +15476,21 @@
         <v>856</v>
       </c>
       <c r="C209" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
       <c r="D209" s="33" t="s">
-        <v>2046</v>
+        <v>2040</v>
       </c>
       <c r="E209" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B210" s="1" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
       <c r="C210" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.4">
@@ -15331,59 +15498,59 @@
         <v>1070</v>
       </c>
       <c r="C211" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B212" s="1" t="s">
-        <v>1936</v>
+        <v>1930</v>
       </c>
       <c r="C212" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
       <c r="F212" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B213" s="1" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
       <c r="C213" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
       <c r="D213" s="33" t="s">
-        <v>2118</v>
+        <v>2112</v>
       </c>
       <c r="E213" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B214" s="1" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
       <c r="C214" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B215" s="1" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
       <c r="C215" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B216" s="1" t="s">
-        <v>1937</v>
+        <v>1931</v>
       </c>
       <c r="C216" t="s">
-        <v>1988</v>
+        <v>1982</v>
       </c>
       <c r="F216" s="32" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
@@ -15391,112 +15558,112 @@
         <v>1076</v>
       </c>
       <c r="C217" t="s">
-        <v>2601</v>
+        <v>2595</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>2557</v>
+        <v>2551</v>
       </c>
       <c r="E217" s="34" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B218" s="1" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="C218" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B219" s="1" t="s">
-        <v>1771</v>
+        <v>1141</v>
       </c>
       <c r="C219" t="s">
-        <v>1772</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B220" s="1" t="s">
-        <v>1938</v>
+        <v>1932</v>
       </c>
       <c r="C220" t="s">
-        <v>1773</v>
+        <v>1769</v>
       </c>
       <c r="D220" s="33" t="s">
-        <v>2031</v>
+        <v>2025</v>
       </c>
       <c r="E220" s="34" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B221" s="1" t="s">
-        <v>1939</v>
+        <v>1933</v>
       </c>
       <c r="C221" t="s">
-        <v>1774</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B222" s="1" t="s">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="C222" t="s">
-        <v>1776</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B223" s="1" t="s">
-        <v>1940</v>
+        <v>1934</v>
       </c>
       <c r="C223" t="s">
-        <v>1777</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B224" s="1" t="s">
-        <v>1778</v>
+        <v>1774</v>
       </c>
       <c r="C224" t="s">
-        <v>1989</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B225" s="1" t="s">
-        <v>1779</v>
+        <v>1775</v>
       </c>
       <c r="C225" t="s">
-        <v>1780</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B226" s="1" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="C226" t="s">
-        <v>2001</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B227" s="1" t="s">
-        <v>1782</v>
+        <v>1778</v>
       </c>
       <c r="C227" t="s">
-        <v>1783</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B228" s="1" t="s">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="C228" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B229" s="1" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="C229" t="s">
         <v>430</v>
@@ -15504,258 +15671,258 @@
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B230" s="1" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="C230" t="s">
-        <v>1996</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B231" s="1" t="s">
-        <v>1788</v>
+        <v>1784</v>
       </c>
       <c r="C231" t="s">
-        <v>1789</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B232" s="1" t="s">
-        <v>1790</v>
+        <v>1786</v>
       </c>
       <c r="C232" t="s">
-        <v>1791</v>
+        <v>1787</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>2053</v>
+        <v>2047</v>
       </c>
       <c r="E232" s="34" t="s">
-        <v>2088</v>
+        <v>2082</v>
       </c>
       <c r="F232" s="32" t="s">
-        <v>2566</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B233" s="1" t="s">
-        <v>1941</v>
+        <v>1935</v>
       </c>
       <c r="C233" t="s">
-        <v>2564</v>
+        <v>2558</v>
       </c>
       <c r="D233" s="33" t="s">
-        <v>2565</v>
+        <v>2559</v>
       </c>
       <c r="E233" s="34" t="s">
-        <v>2090</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B234" s="1" t="s">
-        <v>1792</v>
+        <v>1788</v>
       </c>
       <c r="C234" t="s">
-        <v>2011</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B235" s="1" t="s">
-        <v>1793</v>
+        <v>1789</v>
       </c>
       <c r="C235" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B236" s="1" t="s">
-        <v>1795</v>
+        <v>1791</v>
       </c>
       <c r="C236" t="s">
-        <v>1796</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B237" s="1" t="s">
-        <v>1942</v>
+        <v>1936</v>
       </c>
       <c r="C237" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B238" s="1" t="s">
-        <v>1798</v>
+        <v>1794</v>
       </c>
       <c r="C238" t="s">
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="D238" s="33" t="s">
-        <v>2107</v>
+        <v>2101</v>
       </c>
       <c r="E238" s="34" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B239" s="1" t="s">
-        <v>1800</v>
+        <v>1796</v>
       </c>
       <c r="C239" t="s">
-        <v>1801</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B240" s="1" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="C240" t="s">
-        <v>1803</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B241" s="1" t="s">
-        <v>1943</v>
+        <v>1937</v>
       </c>
       <c r="C241" t="s">
-        <v>1804</v>
+        <v>1800</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>2034</v>
+        <v>2028</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B242" s="1" t="s">
-        <v>1944</v>
+        <v>1938</v>
       </c>
       <c r="C242" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>2035</v>
+        <v>2029</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>2091</v>
+        <v>2085</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>2098</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B243" s="1" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C243" t="s">
         <v>1302</v>
       </c>
       <c r="D243" s="33" t="s">
-        <v>2056</v>
+        <v>2050</v>
       </c>
       <c r="E243" s="34" t="s">
-        <v>2092</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B244" s="1" t="s">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="C244" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B245" s="1" t="s">
-        <v>1809</v>
+        <v>1805</v>
       </c>
       <c r="C245" t="s">
-        <v>1810</v>
+        <v>1806</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>2057</v>
+        <v>2051</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>2093</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B246" s="1" t="s">
-        <v>1945</v>
+        <v>1939</v>
       </c>
       <c r="C246" t="s">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>2055</v>
+        <v>2049</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>2092</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B247" s="1" t="s">
-        <v>1946</v>
+        <v>1940</v>
       </c>
       <c r="C247" t="s">
-        <v>1812</v>
+        <v>1808</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>2043</v>
+        <v>2037</v>
       </c>
       <c r="E247" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B248" s="1" t="s">
-        <v>1813</v>
+        <v>1809</v>
       </c>
       <c r="C248" t="s">
-        <v>2010</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B249" s="1" t="s">
-        <v>1947</v>
+        <v>1941</v>
       </c>
       <c r="C249" t="s">
-        <v>1999</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B250" s="1" t="s">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="C250" t="s">
-        <v>1815</v>
+        <v>1811</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2066</v>
+        <v>2060</v>
       </c>
       <c r="E250" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
       <c r="F250" s="34" t="s">
-        <v>2722</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B251" s="1" t="s">
-        <v>1948</v>
+        <v>1942</v>
       </c>
       <c r="C251" t="s">
-        <v>2718</v>
+        <v>2709</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>2731</v>
+        <v>2722</v>
       </c>
       <c r="E251" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B252" s="1" t="s">
-        <v>1816</v>
+        <v>1812</v>
       </c>
       <c r="C252" t="s">
         <v>461</v>
@@ -15763,243 +15930,243 @@
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B253" s="1" t="s">
-        <v>1817</v>
+        <v>1813</v>
       </c>
       <c r="C253" t="s">
-        <v>1818</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B254" s="1" t="s">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="C254" t="s">
-        <v>1820</v>
+        <v>1816</v>
       </c>
       <c r="D254" s="33" t="s">
-        <v>2048</v>
+        <v>2042</v>
       </c>
       <c r="E254" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B255" s="1" t="s">
-        <v>1821</v>
+        <v>1817</v>
       </c>
       <c r="C255" t="s">
-        <v>1822</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B256" s="1" t="s">
-        <v>1823</v>
+        <v>1819</v>
       </c>
       <c r="C256" t="s">
-        <v>1824</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B257" s="1" t="s">
-        <v>1825</v>
+        <v>1821</v>
       </c>
       <c r="C257" t="s">
-        <v>1826</v>
+        <v>1822</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B258" s="1" t="s">
-        <v>1949</v>
+        <v>1943</v>
       </c>
       <c r="C258" t="s">
-        <v>2563</v>
+        <v>2557</v>
       </c>
       <c r="D258" s="33" t="s">
-        <v>2562</v>
+        <v>2556</v>
       </c>
       <c r="E258" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B259" s="1" t="s">
-        <v>1827</v>
+        <v>1823</v>
       </c>
       <c r="C259" t="s">
-        <v>1828</v>
+        <v>1824</v>
       </c>
       <c r="F259" s="32" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B260" s="1" t="s">
-        <v>1950</v>
+        <v>1944</v>
       </c>
       <c r="C260" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2558</v>
+        <v>2552</v>
       </c>
       <c r="E260" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B261" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="C261" t="s">
         <v>416</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2119</v>
+        <v>2113</v>
       </c>
       <c r="E261" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
       <c r="F261" s="32" t="s">
-        <v>2567</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B262" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
       <c r="C262" t="s">
-        <v>2587</v>
+        <v>2581</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>2586</v>
+        <v>2580</v>
       </c>
       <c r="E262" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B263" s="1" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="C263" t="s">
-        <v>1832</v>
+        <v>1828</v>
       </c>
       <c r="D263" s="33" t="s">
-        <v>2067</v>
+        <v>2061</v>
       </c>
       <c r="E263" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="C264" t="s">
-        <v>1834</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="C265" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B266" s="1" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="C266" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B267" s="1" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="C267" t="s">
-        <v>1840</v>
+        <v>1836</v>
       </c>
       <c r="F267" s="34" t="s">
-        <v>2722</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B268" s="1" t="s">
-        <v>1951</v>
+        <v>1945</v>
       </c>
       <c r="C268" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
       <c r="D268" s="33" t="s">
-        <v>2065</v>
+        <v>2059</v>
       </c>
       <c r="E268" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B269" s="1" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
       <c r="C269" t="s">
-        <v>1975</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B270" s="1" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="C270" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B271" s="1" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="C271" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B272" s="1" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="C272" t="s">
-        <v>1848</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B273" s="1" t="s">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="C273" t="s">
-        <v>1850</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B274" s="1" t="s">
-        <v>1851</v>
+        <v>1847</v>
       </c>
       <c r="C274" t="s">
-        <v>1852</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B275" s="1" t="s">
-        <v>1853</v>
+        <v>1849</v>
       </c>
       <c r="C275" t="s">
-        <v>1854</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.4">
@@ -16007,65 +16174,65 @@
         <v>429</v>
       </c>
       <c r="C276" t="s">
-        <v>1855</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B277" s="1" t="s">
-        <v>1856</v>
+        <v>1852</v>
       </c>
       <c r="C277" t="s">
-        <v>1857</v>
+        <v>1853</v>
       </c>
       <c r="F277" s="34" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B278" s="1" t="s">
-        <v>1858</v>
+        <v>1854</v>
       </c>
       <c r="C278" t="s">
-        <v>1859</v>
+        <v>759</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2051</v>
+        <v>2744</v>
       </c>
       <c r="E278" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B279" s="1" t="s">
-        <v>1860</v>
+        <v>1855</v>
       </c>
       <c r="C279" t="s">
-        <v>1861</v>
+        <v>1856</v>
       </c>
       <c r="D279" s="33" t="s">
-        <v>2036</v>
+        <v>2030</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>2451</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B280" s="1" t="s">
-        <v>1862</v>
+        <v>1857</v>
       </c>
       <c r="C280" t="s">
-        <v>1863</v>
+        <v>1858</v>
       </c>
       <c r="D280" s="41" t="s">
-        <v>2589</v>
+        <v>2583</v>
       </c>
       <c r="E280" s="42" t="s">
-        <v>2451</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B281" s="1" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="C281" t="s">
         <v>1419</v>
@@ -16073,147 +16240,147 @@
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B282" s="1" t="s">
-        <v>1952</v>
+        <v>1946</v>
       </c>
       <c r="C282" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B283" s="1" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
       <c r="C283" t="s">
-        <v>1867</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B284" s="1" t="s">
-        <v>1868</v>
+        <v>1863</v>
       </c>
       <c r="C284" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B285" s="1" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="C285" t="s">
-        <v>1871</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B286" s="1" t="s">
-        <v>1872</v>
+        <v>1867</v>
       </c>
       <c r="C286" t="s">
-        <v>1873</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B287" s="1" t="s">
-        <v>1874</v>
+        <v>1869</v>
       </c>
       <c r="C287" t="s">
-        <v>1875</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B288" s="1" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
       <c r="C288" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="D288" s="33" t="s">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="E288" s="34" t="s">
-        <v>2088</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B289" s="1" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="C289" t="s">
-        <v>1878</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B290" s="1" t="s">
-        <v>1954</v>
+        <v>1948</v>
       </c>
       <c r="C290" t="s">
-        <v>1796</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B291" s="1" t="s">
-        <v>1955</v>
+        <v>1949</v>
       </c>
       <c r="C291" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B292" s="1" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="C292" t="s">
-        <v>1970</v>
+        <v>1964</v>
       </c>
       <c r="D292" s="33" t="s">
-        <v>2045</v>
+        <v>2039</v>
       </c>
       <c r="E292" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="F292" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B293" s="1" t="s">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="C293" t="s">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="E293" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B294" s="1" t="s">
-        <v>1957</v>
+        <v>1951</v>
       </c>
       <c r="C294" t="s">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="D294" s="33" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="E294" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B295" s="1" t="s">
-        <v>1958</v>
+        <v>1952</v>
       </c>
       <c r="C295" t="s">
-        <v>2021</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.4">
@@ -16221,10 +16388,10 @@
         <v>286</v>
       </c>
       <c r="C296" t="s">
-        <v>1961</v>
+        <v>1955</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2110</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
@@ -16232,124 +16399,124 @@
         <v>1424</v>
       </c>
       <c r="C297" t="s">
-        <v>1962</v>
+        <v>1956</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>2110</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B298" s="1" t="s">
-        <v>1959</v>
+        <v>1953</v>
       </c>
       <c r="C298" t="s">
-        <v>1960</v>
+        <v>1954</v>
       </c>
       <c r="F298" s="32" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B299" s="24" t="s">
-        <v>1963</v>
+        <v>1957</v>
       </c>
       <c r="C299" t="s">
-        <v>2688</v>
+        <v>2681</v>
       </c>
       <c r="D299" s="33" t="s">
-        <v>2060</v>
+        <v>2054</v>
       </c>
       <c r="E299" s="32" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B300" s="1" t="s">
-        <v>1964</v>
+        <v>1958</v>
       </c>
       <c r="C300" t="s">
-        <v>1965</v>
+        <v>1959</v>
       </c>
       <c r="D300" s="33" t="s">
-        <v>2052</v>
+        <v>2046</v>
       </c>
       <c r="E300" s="34" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B301" s="24" t="s">
-        <v>1966</v>
+        <v>1960</v>
       </c>
       <c r="C301" t="s">
-        <v>1967</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B302" s="18" t="s">
-        <v>1984</v>
+        <v>1978</v>
       </c>
       <c r="C302" t="s">
-        <v>1985</v>
+        <v>1979</v>
       </c>
       <c r="D302" s="33" t="s">
-        <v>2109</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B303" s="18" t="s">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="C303" t="s">
-        <v>1969</v>
+        <v>1963</v>
       </c>
       <c r="D303" s="33" t="s">
-        <v>2049</v>
+        <v>2043</v>
       </c>
       <c r="E303" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B304" s="18" t="s">
-        <v>1971</v>
+        <v>1965</v>
       </c>
       <c r="C304" t="s">
-        <v>1974</v>
+        <v>1968</v>
       </c>
       <c r="D304" s="33" t="s">
-        <v>2041</v>
+        <v>2035</v>
       </c>
       <c r="E304" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B305" s="26" t="s">
-        <v>1972</v>
+        <v>1966</v>
       </c>
       <c r="C305" t="s">
-        <v>1973</v>
+        <v>1967</v>
       </c>
       <c r="D305" s="33" t="s">
-        <v>2041</v>
+        <v>2035</v>
       </c>
       <c r="E305" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B306" s="1" t="s">
-        <v>1978</v>
+        <v>1972</v>
       </c>
       <c r="C306" t="s">
-        <v>1979</v>
+        <v>1973</v>
       </c>
       <c r="D306" s="33" t="s">
-        <v>2042</v>
+        <v>2036</v>
       </c>
       <c r="E306" s="34" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
@@ -16357,134 +16524,134 @@
         <v>935</v>
       </c>
       <c r="C307" t="s">
-        <v>2513</v>
+        <v>2507</v>
       </c>
       <c r="D307" s="33" t="s">
-        <v>2489</v>
+        <v>2483</v>
       </c>
       <c r="E307" s="32" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
       <c r="F307" s="32" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B308" s="1" t="s">
-        <v>1986</v>
+        <v>1980</v>
       </c>
       <c r="C308" t="s">
-        <v>1987</v>
+        <v>1981</v>
       </c>
       <c r="D308" s="33" t="s">
-        <v>2037</v>
+        <v>2031</v>
       </c>
       <c r="E308" s="34" t="s">
-        <v>2083</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B309" s="27" t="s">
-        <v>1990</v>
+        <v>1984</v>
       </c>
       <c r="C309" t="s">
-        <v>1991</v>
+        <v>1985</v>
       </c>
       <c r="D309" s="33" t="s">
-        <v>2038</v>
+        <v>2032</v>
       </c>
       <c r="E309" s="34" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B310" s="1" t="s">
-        <v>1992</v>
+        <v>1986</v>
       </c>
       <c r="C310" t="s">
-        <v>1993</v>
+        <v>1987</v>
       </c>
       <c r="D310" s="33" t="s">
-        <v>2070</v>
+        <v>2064</v>
       </c>
       <c r="E310" s="34" t="s">
-        <v>2085</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B311" s="1" t="s">
-        <v>1994</v>
+        <v>1988</v>
       </c>
       <c r="C311" t="s">
-        <v>1995</v>
+        <v>1989</v>
       </c>
       <c r="D311" s="33" t="s">
-        <v>2071</v>
+        <v>2065</v>
       </c>
       <c r="E311" s="34" t="s">
-        <v>2085</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B312" s="1" t="s">
-        <v>2002</v>
+        <v>1996</v>
       </c>
       <c r="C312" t="s">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="D312" s="33" t="s">
-        <v>2059</v>
+        <v>2053</v>
       </c>
       <c r="E312" s="34" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B313" s="1" t="s">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C313" t="s">
-        <v>2129</v>
+        <v>2123</v>
       </c>
       <c r="D313" s="33" t="s">
-        <v>2131</v>
+        <v>2125</v>
       </c>
       <c r="E313" s="34" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B314" s="1" t="s">
-        <v>2005</v>
+        <v>1999</v>
       </c>
       <c r="C314" t="s">
-        <v>2130</v>
+        <v>2124</v>
       </c>
       <c r="D314" s="33" t="s">
-        <v>2131</v>
+        <v>2125</v>
       </c>
       <c r="E314" s="34" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
       <c r="F314" s="32" t="s">
-        <v>2567</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B315" s="1" t="s">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C315" t="s">
-        <v>2597</v>
+        <v>2591</v>
       </c>
       <c r="D315" s="53" t="s">
-        <v>2598</v>
+        <v>2592</v>
       </c>
       <c r="E315" s="34" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
       <c r="F315" s="32" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
@@ -16492,75 +16659,75 @@
         <v>153</v>
       </c>
       <c r="C316" t="s">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="D316" s="33" t="s">
-        <v>2058</v>
+        <v>2052</v>
       </c>
       <c r="E316" s="34" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B317" s="1" t="s">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="C317" t="s">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="D317" s="33" t="s">
-        <v>2058</v>
+        <v>2052</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
       <c r="F317" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B318" s="1" t="s">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C318" t="s">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="D318" s="33" t="s">
-        <v>2061</v>
+        <v>2055</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B319" s="1" t="s">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C319" t="s">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="D319" s="33" t="s">
-        <v>2062</v>
+        <v>2056</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
       <c r="F319" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B320" s="1" t="s">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C320" t="s">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="D320" s="33" t="s">
-        <v>2064</v>
+        <v>2058</v>
       </c>
       <c r="E320" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.4">
@@ -16568,30 +16735,30 @@
         <v>821</v>
       </c>
       <c r="C321" t="s">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D321" s="33" t="s">
-        <v>2108</v>
+        <v>2102</v>
       </c>
       <c r="E321" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="322" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B322" s="1" t="s">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C322" t="s">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>2063</v>
+        <v>2057</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
       <c r="F322" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="323" spans="2:7" x14ac:dyDescent="0.4">
@@ -16599,19 +16766,19 @@
         <v>1093</v>
       </c>
       <c r="C323" t="s">
-        <v>2502</v>
+        <v>2496</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2105</v>
+        <v>2099</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
       <c r="F323" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>2500</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="324" spans="2:7" x14ac:dyDescent="0.4">
@@ -16619,78 +16786,78 @@
         <v>296</v>
       </c>
       <c r="C324" t="s">
-        <v>2503</v>
+        <v>2497</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2120</v>
+        <v>2114</v>
       </c>
       <c r="E324" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
       <c r="F324" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="325" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B325" s="1" t="s">
-        <v>1982</v>
+        <v>1976</v>
       </c>
       <c r="C325" t="s">
-        <v>2124</v>
+        <v>2118</v>
       </c>
       <c r="D325" s="33" t="s">
-        <v>2126</v>
+        <v>2120</v>
       </c>
       <c r="E325" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
       <c r="F325" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="326" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B326" s="1" t="s">
-        <v>1983</v>
+        <v>1977</v>
       </c>
       <c r="C326" t="s">
-        <v>2125</v>
+        <v>2119</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>2126</v>
+        <v>2120</v>
       </c>
       <c r="E326" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="327" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B327" s="1" t="s">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="C327" t="s">
-        <v>2504</v>
+        <v>2498</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2447</v>
+        <v>2441</v>
       </c>
       <c r="E327" s="34" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="328" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B328" s="1" t="s">
-        <v>1981</v>
+        <v>1975</v>
       </c>
       <c r="C328" t="s">
-        <v>2505</v>
+        <v>2499</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2446</v>
+        <v>2440</v>
       </c>
       <c r="E328" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="329" spans="2:7" x14ac:dyDescent="0.4">
@@ -16698,16 +16865,16 @@
         <v>406</v>
       </c>
       <c r="C329" t="s">
-        <v>2506</v>
+        <v>2500</v>
       </c>
       <c r="D329" s="33" t="s">
-        <v>2448</v>
+        <v>2442</v>
       </c>
       <c r="E329" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
       <c r="F329" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="330" spans="2:7" x14ac:dyDescent="0.4">
@@ -16715,16 +16882,16 @@
         <v>160</v>
       </c>
       <c r="C330" t="s">
-        <v>2507</v>
+        <v>2501</v>
       </c>
       <c r="D330" s="41" t="s">
-        <v>2449</v>
+        <v>2443</v>
       </c>
       <c r="E330" s="42" t="s">
-        <v>2451</v>
+        <v>2445</v>
       </c>
       <c r="F330" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="331" spans="2:7" x14ac:dyDescent="0.4">
@@ -16732,27 +16899,27 @@
         <v>1102</v>
       </c>
       <c r="C331" t="s">
-        <v>2508</v>
+        <v>2502</v>
       </c>
       <c r="D331" s="33" t="s">
-        <v>2450</v>
+        <v>2444</v>
       </c>
       <c r="E331" s="42" t="s">
-        <v>2451</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="332" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B332" s="1" t="s">
-        <v>2490</v>
+        <v>2484</v>
       </c>
       <c r="C332" t="s">
-        <v>2509</v>
+        <v>2503</v>
       </c>
       <c r="D332" s="43" t="s">
-        <v>2491</v>
+        <v>2485</v>
       </c>
       <c r="E332" s="34" t="s">
-        <v>2492</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="333" spans="2:7" x14ac:dyDescent="0.4">
@@ -16760,83 +16927,83 @@
         <v>1146</v>
       </c>
       <c r="C333" t="s">
-        <v>2510</v>
+        <v>2504</v>
       </c>
       <c r="D333" s="33" t="s">
-        <v>2493</v>
+        <v>2487</v>
       </c>
       <c r="E333" s="34" t="s">
-        <v>2493</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="334" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B334" s="1" t="s">
-        <v>2494</v>
+        <v>2488</v>
       </c>
       <c r="C334" t="s">
-        <v>2511</v>
+        <v>2505</v>
       </c>
       <c r="D334" s="33" t="s">
-        <v>2493</v>
+        <v>2487</v>
       </c>
       <c r="E334" s="34" t="s">
-        <v>2493</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="335" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
-        <v>2495</v>
+        <v>2489</v>
       </c>
       <c r="C335" t="s">
-        <v>2512</v>
+        <v>2506</v>
       </c>
       <c r="D335" s="41" t="s">
-        <v>2497</v>
+        <v>2491</v>
       </c>
       <c r="E335" s="34" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="336" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B336" s="1" t="s">
-        <v>2496</v>
+        <v>2490</v>
       </c>
       <c r="C336" t="s">
-        <v>2501</v>
+        <v>2495</v>
       </c>
       <c r="D336" s="41" t="s">
-        <v>2497</v>
+        <v>2491</v>
       </c>
       <c r="E336" s="34" t="s">
-        <v>2498</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B337" s="1" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="C337" t="s">
-        <v>2553</v>
+        <v>2547</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>2556</v>
+        <v>2550</v>
       </c>
       <c r="E337" s="34" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B338" s="1" t="s">
-        <v>2554</v>
+        <v>2548</v>
       </c>
       <c r="C338" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
       <c r="D338" s="33" t="s">
-        <v>2556</v>
+        <v>2550</v>
       </c>
       <c r="E338" s="34" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.4">
@@ -16844,60 +17011,96 @@
         <v>1021</v>
       </c>
       <c r="C339" t="s">
-        <v>2600</v>
+        <v>2594</v>
       </c>
       <c r="D339" s="53" t="s">
-        <v>2599</v>
+        <v>2593</v>
       </c>
       <c r="E339" s="32" t="s">
-        <v>2567</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B340" s="1" t="s">
-        <v>2719</v>
+        <v>2710</v>
       </c>
       <c r="C340" t="s">
-        <v>2720</v>
+        <v>2711</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>2721</v>
+        <v>2712</v>
       </c>
       <c r="E340" s="34" t="s">
-        <v>2722</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B341" s="1" t="s">
-        <v>2724</v>
+        <v>2715</v>
       </c>
       <c r="C341" s="55" t="s">
-        <v>2725</v>
+        <v>2716</v>
       </c>
       <c r="D341" s="33" t="s">
-        <v>2726</v>
+        <v>2717</v>
       </c>
       <c r="E341" s="34" t="s">
-        <v>2722</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B342" s="1" t="s">
-        <v>2727</v>
+        <v>2718</v>
       </c>
       <c r="C342" s="55" t="s">
-        <v>2728</v>
+        <v>2719</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>2729</v>
+        <v>2720</v>
       </c>
       <c r="E342" s="34" t="s">
-        <v>2722</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A343" t="s">
-        <v>1884</v>
+      <c r="B343" s="1" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C343" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D343" s="33" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E343" s="33" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B344" s="1" t="s">
+        <v>2749</v>
+      </c>
+      <c r="C344" t="s">
+        <v>2750</v>
+      </c>
+      <c r="D344" s="33" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B345" s="1" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C345" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D345" s="33" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A346" t="s">
+        <v>1879</v>
       </c>
     </row>
   </sheetData>
@@ -17973,11 +18176,11 @@
         <v>。</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="I3" s="6" t="str">
-        <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C,"が")</f>
+        <v>が</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>75</v>
@@ -19517,8 +19720,8 @@
         <v>289</v>
       </c>
       <c r="I6" s="6" t="str">
-        <f>_xlfn.XLOOKUP(H6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <f>_xlfn.XLOOKUP(H6,対応表!$B:$B,対応表!$C:$C,"け")</f>
+        <v>け</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>290</v>
@@ -19784,7 +19987,7 @@
       </c>
       <c r="CG6" s="6" t="str">
         <f>_xlfn.XLOOKUP(CF6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>除?</v>
       </c>
       <c r="CH6" s="7" t="s">
         <v>328</v>
@@ -21046,7 +21249,7 @@
       </c>
       <c r="E9" s="22" t="str" cm="1">
         <f t="array" ref="E9">_xlfn.XLOOKUP(D9,対応表!$B:B,対応表!$C:C,"葉")</f>
-        <v>葉</v>
+        <v>葉?</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>501</v>
@@ -24130,7 +24333,7 @@
       </c>
       <c r="E15" s="22" t="str" cm="1">
         <f t="array" ref="E15">_xlfn.XLOOKUP(D15,対応表!$B:B,対応表!$C:C,"継")</f>
-        <v>継</v>
+        <v>継?</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>930</v>
@@ -26634,7 +26837,7 @@
       </c>
       <c r="EC19" s="6" t="str">
         <f>_xlfn.XLOOKUP(EB19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>再?</v>
+        <v>再</v>
       </c>
       <c r="ED19" s="7" t="s">
         <v>1277</v>
@@ -28248,6 +28451,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -28308,7 +28512,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -28382,7 +28586,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C5E931-1AEC-434D-81A1-3EA98DBB914E}">
-  <dimension ref="B1:F93"/>
+  <dimension ref="B1:F98"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.25" style="35" bestFit="1" customWidth="1"/>
@@ -28394,1347 +28598,1512 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B1" s="54" t="s">
-        <v>2114</v>
+        <v>2108</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>2115</v>
+        <v>2109</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>2675</v>
+        <v>2669</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>2116</v>
+        <v>2110</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>2109</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
-        <v>2111</v>
+        <v>2105</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>2112</v>
+        <v>2106</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2113</v>
+        <v>2107</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
-        <v>2221</v>
+        <v>2215</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>2222</v>
+        <v>2216</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>2223</v>
+        <v>2217</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
-        <v>2224</v>
+        <v>2218</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>2225</v>
+        <v>2219</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>2226</v>
+        <v>2220</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
-        <v>2227</v>
+        <v>2221</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>2228</v>
+        <v>2222</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>2229</v>
+        <v>2223</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
-        <v>2230</v>
+        <v>2224</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>2231</v>
+        <v>2225</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>2232</v>
+        <v>2226</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
-        <v>2233</v>
+        <v>2227</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>2234</v>
+        <v>2228</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>2235</v>
+        <v>2229</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2236</v>
+        <v>2230</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>2049</v>
+        <v>2043</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2237</v>
+        <v>2231</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
-        <v>2238</v>
+        <v>2232</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>2239</v>
+        <v>2233</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>2240</v>
+        <v>2234</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>2515</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2241</v>
+        <v>2235</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>2047</v>
+        <v>2041</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2242</v>
+        <v>2236</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
-        <v>2243</v>
+        <v>2237</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>2244</v>
+        <v>2238</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
-        <v>2246</v>
+        <v>2240</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2247</v>
+        <v>2241</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>2329</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2248</v>
+        <v>2242</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>2051</v>
+        <v>2045</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
-        <v>2326</v>
+        <v>2320</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>2327</v>
+        <v>2321</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2398</v>
+        <v>2392</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2397</v>
+        <v>2391</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
-        <v>2399</v>
+        <v>2393</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>2400</v>
+        <v>2394</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2402</v>
+        <v>2396</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2401</v>
+        <v>2395</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="35" t="s">
-        <v>2072</v>
+        <v>2066</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2403</v>
+        <v>2397</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
-        <v>2443</v>
+        <v>2437</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>2444</v>
+        <v>2438</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>2445</v>
+        <v>2439</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="44" t="s">
-        <v>2531</v>
+        <v>2525</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>2514</v>
+        <v>2508</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="35" t="s">
-        <v>2516</v>
+        <v>2510</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>2517</v>
+        <v>2511</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>2518</v>
+        <v>2512</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="35" t="s">
-        <v>2519</v>
+        <v>2513</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>2520</v>
+        <v>2514</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>2521</v>
+        <v>2515</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="35" t="s">
-        <v>2522</v>
+        <v>2516</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>2523</v>
+        <v>2517</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>2237</v>
+        <v>2231</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="35" t="s">
-        <v>2524</v>
+        <v>2518</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>2525</v>
+        <v>2519</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="35" t="s">
-        <v>2526</v>
+        <v>2520</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>2527</v>
+        <v>2521</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="35" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>2529</v>
+        <v>2523</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>2530</v>
+        <v>2524</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="35" t="s">
-        <v>2535</v>
+        <v>2529</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>2536</v>
+        <v>2530</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>2548</v>
+        <v>2542</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="35" t="s">
-        <v>2537</v>
+        <v>2531</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>2538</v>
+        <v>2532</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>2541</v>
+        <v>2535</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B29" s="35" t="s">
-        <v>2539</v>
+        <v>2533</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>2540</v>
+        <v>2534</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="35" t="s">
-        <v>2542</v>
+        <v>2536</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>2543</v>
+        <v>2537</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>2232</v>
+        <v>2226</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B31" s="35" t="s">
-        <v>2544</v>
+        <v>2538</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>2545</v>
+        <v>2539</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>2232</v>
+        <v>2226</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B32" s="35" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>2547</v>
+        <v>2541</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>2548</v>
+        <v>2542</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="35" t="s">
-        <v>2549</v>
+        <v>2543</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>2550</v>
+        <v>2544</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>2548</v>
+        <v>2542</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="39" t="s">
-        <v>2551</v>
+        <v>2545</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>2329</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="35" t="s">
-        <v>2584</v>
+        <v>2578</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>2595</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B36" s="35" t="s">
-        <v>2662</v>
+        <v>2656</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>2602</v>
+        <v>2596</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B37" s="35" t="s">
-        <v>2603</v>
+        <v>2597</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>2604</v>
+        <v>2598</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>2679</v>
+        <v>2672</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B38" s="35" t="s">
-        <v>2605</v>
+        <v>2599</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>2606</v>
+        <v>2600</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B39" s="35" t="s">
-        <v>2663</v>
+        <v>2657</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>2607</v>
+        <v>2601</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B40" s="35" t="s">
-        <v>2664</v>
+        <v>2658</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>2608</v>
+        <v>2602</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>2245</v>
+        <v>2239</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B41" s="35" t="s">
-        <v>2611</v>
+        <v>2605</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>2433</v>
+        <v>2427</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B42" s="35" t="s">
-        <v>2612</v>
+        <v>2606</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>2613</v>
+        <v>2607</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B43" s="35" t="s">
-        <v>2549</v>
+        <v>2543</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>2614</v>
+        <v>2608</v>
       </c>
       <c r="D43" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B44" s="35" t="s">
-        <v>2615</v>
+        <v>2609</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>2616</v>
+        <v>2610</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B45" s="35" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>2617</v>
+        <v>2611</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="35" t="s">
-        <v>2618</v>
+        <v>2612</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>2619</v>
+        <v>2613</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B47" s="35" t="s">
-        <v>2620</v>
+        <v>2614</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>2621</v>
+        <v>2615</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="35" t="s">
-        <v>2622</v>
+        <v>2616</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>2623</v>
+        <v>2617</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" s="35" t="s">
-        <v>2624</v>
+        <v>2618</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>2625</v>
+        <v>2619</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="35" t="s">
-        <v>2626</v>
+        <v>2620</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>2627</v>
+        <v>2621</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" s="35" t="s">
-        <v>2628</v>
+        <v>2622</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>2629</v>
+        <v>2623</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" s="35" t="s">
-        <v>2630</v>
+        <v>2624</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>2631</v>
+        <v>2625</v>
       </c>
       <c r="D52" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B53" s="35" t="s">
-        <v>2632</v>
+        <v>2626</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>2633</v>
+        <v>2627</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B54" s="35" t="s">
-        <v>2634</v>
+        <v>2628</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>2635</v>
+        <v>2629</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" s="35" t="s">
-        <v>2636</v>
+        <v>2630</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>2637</v>
+        <v>2631</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="35" t="s">
-        <v>2638</v>
+        <v>2632</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>2639</v>
+        <v>2633</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B57" s="35" t="s">
-        <v>2640</v>
+        <v>2634</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>2641</v>
+        <v>2635</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B58" s="35" t="s">
-        <v>2642</v>
+        <v>2636</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>2643</v>
+        <v>2637</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B59" s="35" t="s">
-        <v>2644</v>
+        <v>2638</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>2645</v>
+        <v>2639</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B60" s="35" t="s">
-        <v>2646</v>
+        <v>2640</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>2647</v>
+        <v>2641</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B61" s="35" t="s">
-        <v>2648</v>
+        <v>2642</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>2649</v>
+        <v>2643</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B62" s="35" t="s">
-        <v>2650</v>
+        <v>2644</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>2651</v>
+        <v>2645</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B63" s="35" t="s">
-        <v>2652</v>
+        <v>2646</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>2653</v>
+        <v>2647</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F63" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B64" s="35" t="s">
-        <v>2654</v>
+        <v>2648</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>2655</v>
+        <v>2649</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B65" s="35" t="s">
-        <v>2656</v>
+        <v>2650</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>2657</v>
+        <v>2651</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F65" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B66" s="35" t="s">
-        <v>2658</v>
+        <v>2652</v>
       </c>
       <c r="C66" s="36" t="s">
-        <v>2659</v>
+        <v>2653</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F66" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B67" s="35" t="s">
-        <v>2660</v>
+        <v>2654</v>
       </c>
       <c r="C67" s="36" t="s">
-        <v>2661</v>
+        <v>2655</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>2717</v>
+        <v>2708</v>
       </c>
       <c r="F67" s="36" t="s">
-        <v>2328</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B68" s="35" t="s">
-        <v>2665</v>
+        <v>2659</v>
       </c>
       <c r="C68" s="36" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>2671</v>
+      </c>
+      <c r="E68" s="36" t="s">
         <v>2670</v>
-      </c>
-      <c r="D68" s="36" t="s">
-        <v>2677</v>
-      </c>
-      <c r="E68" s="36" t="s">
-        <v>2676</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B69" s="35" t="s">
-        <v>2666</v>
+        <v>2660</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>2667</v>
+        <v>2661</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>2677</v>
+        <v>2671</v>
+      </c>
+      <c r="F69" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B70" s="35" t="s">
-        <v>2668</v>
+        <v>2662</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>2669</v>
+        <v>2663</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>2677</v>
+        <v>2671</v>
       </c>
       <c r="E70" s="36" t="s">
-        <v>2676</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B71" s="35" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C71" s="36" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D71" s="36" t="s">
         <v>2671</v>
       </c>
-      <c r="C71" s="36" t="s">
-        <v>2672</v>
-      </c>
-      <c r="D71" s="36" t="s">
-        <v>2677</v>
+      <c r="F71" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B72" s="35" t="s">
-        <v>2673</v>
+        <v>2667</v>
       </c>
       <c r="C72" s="36" t="s">
-        <v>2674</v>
+        <v>2668</v>
       </c>
       <c r="D72" s="36" t="s">
-        <v>2677</v>
+        <v>2671</v>
       </c>
       <c r="E72" s="36" t="s">
-        <v>2678</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B73" s="35" t="s">
-        <v>2680</v>
+        <v>2673</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>2681</v>
+        <v>2674</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>2677</v>
+        <v>2671</v>
+      </c>
+      <c r="F73" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B74" s="35" t="s">
-        <v>2682</v>
+        <v>2675</v>
       </c>
       <c r="C74" s="36" t="s">
-        <v>2683</v>
+        <v>2676</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>2684</v>
+        <v>2677</v>
+      </c>
+      <c r="F74" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B75" s="35" t="s">
-        <v>2687</v>
+        <v>2680</v>
       </c>
       <c r="C75" s="36" t="s">
-        <v>2685</v>
+        <v>2678</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>2686</v>
+        <v>2679</v>
+      </c>
+      <c r="F75" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B76" s="35" t="s">
-        <v>2689</v>
+        <v>2682</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>2690</v>
+        <v>2683</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>2716</v>
+        <v>2707</v>
+      </c>
+      <c r="F76" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B77" s="35" t="s">
-        <v>2691</v>
+        <v>2684</v>
       </c>
       <c r="C77" s="36" t="s">
-        <v>2692</v>
+        <v>2685</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>2686</v>
+        <v>2679</v>
+      </c>
+      <c r="F77" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B78" s="35" t="s">
-        <v>2703</v>
+        <v>2695</v>
       </c>
       <c r="C78" t="s">
-        <v>2693</v>
+        <v>2686</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>2686</v>
+        <v>2679</v>
       </c>
       <c r="E78" s="36" t="s">
-        <v>2715</v>
+        <v>2706</v>
+      </c>
+      <c r="F78" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B79" s="35" t="s">
-        <v>2705</v>
+        <v>2697</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>2704</v>
+        <v>2696</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>2686</v>
+        <v>2679</v>
       </c>
       <c r="E79" s="36" t="s">
-        <v>2715</v>
+        <v>2706</v>
+      </c>
+      <c r="F79" s="36" t="s">
+        <v>2322</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B80" s="35" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C80" s="36" t="s">
+        <v>2687</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E80" s="36" t="s">
         <v>2706</v>
       </c>
-      <c r="C80" s="36" t="s">
+      <c r="F80" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B81" s="35" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>2688</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>2706</v>
+      </c>
+      <c r="F81" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B82" s="35" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>2706</v>
+      </c>
+      <c r="F82" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B83" s="35" t="s">
+        <v>2701</v>
+      </c>
+      <c r="C83" s="36" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E83" s="36" t="s">
+        <v>2706</v>
+      </c>
+      <c r="F83" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B84" s="39" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C84" s="40" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D84" s="40" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E84" s="40" t="s">
+        <v>2706</v>
+      </c>
+      <c r="F84" s="40" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B85" s="35" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E85" s="36" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B86" s="35" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B87" s="35" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C87" s="36" t="s">
         <v>2694</v>
       </c>
-      <c r="D80" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E80" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B81" s="35" t="s">
-        <v>2707</v>
-      </c>
-      <c r="C81" s="36" t="s">
-        <v>2695</v>
-      </c>
-      <c r="D81" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E81" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B82" s="35" t="s">
+      <c r="D87" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B88" s="35" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C88" s="36" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E88" s="36" t="s">
+        <v>2742</v>
+      </c>
+      <c r="F88" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B89" s="35" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C89" s="36" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>2727</v>
+      </c>
+      <c r="F89" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B90" s="35" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C90" s="36" t="s">
+        <v>2734</v>
+      </c>
+      <c r="D90" s="36" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B91" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" s="36" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B92" s="35" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C92" s="33" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D92" s="36" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B93" s="35" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C93" s="36" t="s">
+        <v>2754</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B94" s="35" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C94" s="36" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D94" s="36" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B95" s="35" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C95" s="36" t="s">
+        <v>2738</v>
+      </c>
+      <c r="D95" s="36" t="s">
         <v>2708</v>
       </c>
-      <c r="C82" s="36" t="s">
-        <v>2696</v>
-      </c>
-      <c r="D82" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E82" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B83" s="35" t="s">
-        <v>2709</v>
-      </c>
-      <c r="C83" s="36" t="s">
-        <v>2697</v>
-      </c>
-      <c r="D83" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E83" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B84" s="35" t="s">
-        <v>2710</v>
-      </c>
-      <c r="C84" s="36" t="s">
-        <v>2698</v>
-      </c>
-      <c r="D84" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E84" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B85" s="35" t="s">
-        <v>2711</v>
-      </c>
-      <c r="C85" s="36" t="s">
-        <v>2699</v>
-      </c>
-      <c r="D85" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E85" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B86" s="35" t="s">
-        <v>2712</v>
-      </c>
-      <c r="C86" s="36" t="s">
-        <v>2700</v>
-      </c>
-      <c r="D86" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E86" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B87" s="35" t="s">
-        <v>2713</v>
-      </c>
-      <c r="C87" s="36" t="s">
-        <v>2701</v>
-      </c>
-      <c r="D87" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E87" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B88" s="35" t="s">
-        <v>2714</v>
-      </c>
-      <c r="C88" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="D88" s="36" t="s">
-        <v>2686</v>
-      </c>
-      <c r="E88" s="36" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="C93"/>
+      <c r="F95" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B96" s="35" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C96" s="36" t="s">
+        <v>2740</v>
+      </c>
+      <c r="D96" s="36" t="s">
+        <v>2708</v>
+      </c>
+      <c r="F96" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B97" s="35" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C97" s="36" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="F97" s="36" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B98" s="35" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C98" s="36" t="s">
+        <v>2758</v>
+      </c>
+      <c r="D98" s="36" t="s">
+        <v>2759</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED28C13D-14D9-4671-B3CF-1ADD2E368C21}">
-  <dimension ref="B1:D301"/>
+  <dimension ref="B1:D302"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="31"/>
@@ -29744,387 +30113,387 @@
   <sheetData>
     <row r="1" spans="2:4" s="48" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="46" t="s">
-        <v>2181</v>
+        <v>2175</v>
       </c>
       <c r="C1" s="47" t="s">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="47" t="s">
-        <v>2026</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
-        <v>2132</v>
+        <v>2126</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="31" t="s">
-        <v>2133</v>
+        <v>2127</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" s="31" t="s">
-        <v>2134</v>
+        <v>2128</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="31" t="s">
-        <v>2135</v>
+        <v>2129</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" s="31" t="s">
-        <v>2136</v>
+        <v>2130</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="31" t="s">
-        <v>2137</v>
+        <v>2131</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="31" t="s">
-        <v>2140</v>
+        <v>2134</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="31" t="s">
-        <v>2141</v>
+        <v>2135</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B10" s="31" t="s">
-        <v>2138</v>
+        <v>2132</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="31" t="s">
-        <v>2139</v>
+        <v>2133</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B12" s="31" t="s">
-        <v>2142</v>
+        <v>2136</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
-        <v>2143</v>
+        <v>2137</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="31" t="s">
-        <v>2144</v>
+        <v>2138</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="31" t="s">
-        <v>2145</v>
+        <v>2139</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="31" t="s">
-        <v>2146</v>
+        <v>2140</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="31" t="s">
-        <v>2147</v>
+        <v>2141</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="31" t="s">
-        <v>2148</v>
+        <v>2142</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="31" t="s">
-        <v>2149</v>
+        <v>2143</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="31" t="s">
-        <v>2150</v>
+        <v>2144</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="31" t="s">
-        <v>2151</v>
+        <v>2145</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="31" t="s">
-        <v>2152</v>
+        <v>2146</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="31" t="s">
-        <v>2199</v>
+        <v>2193</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="31" t="s">
-        <v>2200</v>
+        <v>2194</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>2104</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="31" t="s">
-        <v>2153</v>
+        <v>2147</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="31" t="s">
-        <v>2154</v>
+        <v>2148</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="31" t="s">
-        <v>2155</v>
+        <v>2149</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="31" t="s">
-        <v>2156</v>
+        <v>2150</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>2082</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="31" t="s">
-        <v>2157</v>
+        <v>2151</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="31" t="s">
-        <v>2158</v>
+        <v>2152</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="31" t="s">
-        <v>2159</v>
+        <v>2153</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="31" t="s">
-        <v>2160</v>
+        <v>2154</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
-        <v>2161</v>
+        <v>2155</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
-        <v>2162</v>
+        <v>2156</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
-        <v>2163</v>
+        <v>2157</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
-        <v>2164</v>
+        <v>2158</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
-        <v>2165</v>
+        <v>2159</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
-        <v>2166</v>
+        <v>2160</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
-        <v>2167</v>
+        <v>2161</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>2559</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
-        <v>2168</v>
+        <v>2162</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
-        <v>2169</v>
+        <v>2163</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
-        <v>2170</v>
+        <v>2164</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
-        <v>2171</v>
+        <v>2165</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
-        <v>2182</v>
+        <v>2176</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
-        <v>2172</v>
+        <v>2166</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>2097</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
-        <v>2173</v>
+        <v>2167</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
-        <v>2174</v>
+        <v>2168</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.4">
@@ -30132,443 +30501,443 @@
         <v>1160</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
-        <v>2175</v>
+        <v>2169</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
-        <v>2176</v>
+        <v>2170</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
-        <v>2177</v>
+        <v>2171</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
-        <v>2178</v>
+        <v>2172</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
-        <v>2179</v>
+        <v>2173</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>2094</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
-        <v>2180</v>
+        <v>2174</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B55" s="31" t="s">
-        <v>2183</v>
+        <v>2177</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
-        <v>2184</v>
+        <v>2178</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
-        <v>2185</v>
+        <v>2179</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
-        <v>2186</v>
+        <v>2180</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
-        <v>2187</v>
+        <v>2181</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
-        <v>2188</v>
+        <v>2182</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
-        <v>2189</v>
+        <v>2183</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
-        <v>2190</v>
+        <v>2184</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
-        <v>2191</v>
+        <v>2185</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
-        <v>2192</v>
+        <v>2186</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B65" s="31" t="s">
-        <v>2193</v>
+        <v>2187</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B66" s="31" t="s">
-        <v>2194</v>
+        <v>2188</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B67" s="31" t="s">
-        <v>2195</v>
+        <v>2189</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B68" s="31" t="s">
-        <v>2196</v>
+        <v>2190</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B69" s="31" t="s">
-        <v>2197</v>
+        <v>2191</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B70" s="31" t="s">
-        <v>2198</v>
+        <v>2192</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B71" s="31" t="s">
-        <v>2201</v>
+        <v>2195</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="31" t="s">
-        <v>2202</v>
+        <v>2196</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B73" s="31" t="s">
-        <v>2203</v>
+        <v>2197</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B74" s="31" t="s">
-        <v>2204</v>
+        <v>2198</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
-        <v>2205</v>
+        <v>2199</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
-        <v>2206</v>
+        <v>2200</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="31" t="s">
-        <v>2207</v>
+        <v>2201</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="31" t="s">
-        <v>2208</v>
+        <v>2202</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B79" s="31" t="s">
-        <v>2209</v>
+        <v>2203</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B80" s="31" t="s">
-        <v>2210</v>
+        <v>2204</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B81" s="31" t="s">
-        <v>2211</v>
+        <v>2205</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B82" s="31" t="s">
-        <v>2212</v>
+        <v>2206</v>
       </c>
       <c r="C82" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B83" s="31" t="s">
-        <v>2213</v>
+        <v>2207</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B84" s="31" t="s">
-        <v>2214</v>
+        <v>2208</v>
       </c>
       <c r="C84" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B85" s="31" t="s">
-        <v>2215</v>
+        <v>2209</v>
       </c>
       <c r="C85" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B86" s="31" t="s">
-        <v>2216</v>
+        <v>2210</v>
       </c>
       <c r="C86" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B87" s="31" t="s">
-        <v>2217</v>
+        <v>2211</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B88" s="31" t="s">
-        <v>2218</v>
+        <v>2212</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B89" s="31" t="s">
-        <v>2219</v>
+        <v>2213</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B90" s="31" t="s">
-        <v>2220</v>
+        <v>2214</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B91" s="31" t="s">
-        <v>2249</v>
+        <v>2243</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>2250</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B92" s="31" t="s">
-        <v>2251</v>
+        <v>2245</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>2083</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B93" s="31" t="s">
-        <v>2441</v>
+        <v>2435</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
       <c r="D93" s="34" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2252</v>
+        <v>2246</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>2081</v>
+        <v>2075</v>
       </c>
       <c r="D94" s="34" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B95" s="31" t="s">
-        <v>2253</v>
+        <v>2247</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>2255</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B96" s="31" t="s">
-        <v>2254</v>
+        <v>2248</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2255</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
-        <v>2266</v>
+        <v>2260</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>2255</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2256</v>
+        <v>2250</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="31" t="s">
-        <v>2257</v>
+        <v>2251</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="31" t="s">
-        <v>2258</v>
+        <v>2252</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="31" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C101" s="34" t="s">
         <v>2259</v>
-      </c>
-      <c r="C101" s="34" t="s">
-        <v>2265</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
@@ -30576,1614 +30945,1622 @@
         <v>949</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>2260</v>
+        <v>2254</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="31" t="s">
-        <v>2261</v>
+        <v>2255</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B105" s="31" t="s">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="31" t="s">
-        <v>2263</v>
+        <v>2257</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="31" t="s">
-        <v>2264</v>
+        <v>2258</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
-        <v>2271</v>
+        <v>2265</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>2265</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2267</v>
+        <v>2261</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="31" t="s">
-        <v>2268</v>
+        <v>2262</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="31" t="s">
-        <v>2269</v>
+        <v>2263</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="31" t="s">
-        <v>2270</v>
+        <v>2264</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>2103</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2272</v>
+        <v>2266</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="31" t="s">
-        <v>2273</v>
+        <v>2267</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="31" t="s">
-        <v>2274</v>
+        <v>2268</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="31" t="s">
-        <v>2275</v>
+        <v>2269</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="31" t="s">
-        <v>2276</v>
+        <v>2270</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="31" t="s">
-        <v>2277</v>
+        <v>2271</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>2084</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="31" t="s">
-        <v>2278</v>
+        <v>2272</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="31" t="s">
-        <v>2279</v>
+        <v>2273</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="31" t="s">
-        <v>2280</v>
+        <v>2274</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>2089</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="31" t="s">
-        <v>2281</v>
+        <v>2275</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2282</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
-        <v>2283</v>
+        <v>2277</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>2282</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="31" t="s">
-        <v>2284</v>
+        <v>2278</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2282</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="31" t="s">
-        <v>2285</v>
+        <v>2279</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="31" t="s">
-        <v>2286</v>
+        <v>2280</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="31" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C127" s="34" t="s">
         <v>2287</v>
-      </c>
-      <c r="C127" s="34" t="s">
-        <v>2293</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="31" t="s">
-        <v>2288</v>
+        <v>2282</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B129" s="31" t="s">
-        <v>2289</v>
+        <v>2283</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B130" s="31" t="s">
-        <v>2290</v>
+        <v>2284</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B131" s="31" t="s">
-        <v>2291</v>
+        <v>2285</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
       <c r="D131" s="34" t="s">
-        <v>2353</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B132" s="31" t="s">
-        <v>2292</v>
+        <v>2286</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2293</v>
+        <v>2287</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>2306</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C133" s="34" t="s">
         <v>2294</v>
-      </c>
-      <c r="C133" s="34" t="s">
-        <v>2300</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B134" s="31" t="s">
-        <v>2295</v>
+        <v>2289</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2300</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B135" s="31" t="s">
-        <v>2296</v>
+        <v>2290</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>2300</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B136" s="31" t="s">
-        <v>2297</v>
+        <v>2291</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>2300</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B137" s="31" t="s">
-        <v>2298</v>
+        <v>2292</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>2300</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B138" s="31" t="s">
-        <v>2299</v>
+        <v>2293</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2300</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2301</v>
+        <v>2295</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2306</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B140" s="31" t="s">
-        <v>2302</v>
+        <v>2296</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>2306</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B141" s="31" t="s">
-        <v>2303</v>
+        <v>2297</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>2306</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B142" s="31" t="s">
-        <v>2304</v>
+        <v>2298</v>
       </c>
       <c r="C142" s="34" t="s">
-        <v>2306</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B143" s="31" t="s">
-        <v>2305</v>
+        <v>2299</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2306</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2307</v>
+        <v>2301</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>2310</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B145" s="31" t="s">
-        <v>2308</v>
+        <v>2302</v>
       </c>
       <c r="C145" s="34" t="s">
-        <v>2310</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B146" s="31" t="s">
-        <v>2309</v>
+        <v>2303</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2310</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2311</v>
+        <v>2305</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B148" s="31" t="s">
-        <v>2312</v>
+        <v>2306</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B149" s="31" t="s">
-        <v>2313</v>
+        <v>2307</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B150" s="31" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C150" s="34" t="s">
         <v>2314</v>
-      </c>
-      <c r="C150" s="34" t="s">
-        <v>2320</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B151" s="31" t="s">
-        <v>2315</v>
+        <v>2309</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B152" s="31" t="s">
-        <v>2316</v>
+        <v>2310</v>
       </c>
       <c r="C152" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B153" s="31" t="s">
-        <v>2317</v>
+        <v>2311</v>
       </c>
       <c r="C153" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B154" s="31" t="s">
-        <v>2318</v>
+        <v>2312</v>
       </c>
       <c r="C154" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B155" s="31" t="s">
-        <v>2319</v>
+        <v>2313</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2320</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
-        <v>2321</v>
+        <v>2315</v>
       </c>
       <c r="C156" s="34" t="s">
-        <v>2325</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B157" s="31" t="s">
-        <v>2322</v>
+        <v>2316</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>2325</v>
+        <v>2319</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B158" s="31" t="s">
-        <v>2323</v>
+        <v>2317</v>
       </c>
       <c r="C158" s="34" t="s">
-        <v>2325</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B159" s="31" t="s">
-        <v>2324</v>
+        <v>2318</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2325</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2330</v>
+        <v>2324</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
-        <v>2331</v>
+        <v>2325</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C162" s="34" t="s">
         <v>2332</v>
-      </c>
-      <c r="C162" s="34" t="s">
-        <v>2338</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
-        <v>2333</v>
+        <v>2327</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
-        <v>2334</v>
+        <v>2328</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
-        <v>2335</v>
+        <v>2329</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
-        <v>2336</v>
+        <v>2330</v>
       </c>
       <c r="C166" s="34" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
-        <v>2337</v>
+        <v>2331</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2338</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B168" s="31" t="s">
-        <v>2341</v>
+        <v>2335</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>2343</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
-        <v>2342</v>
+        <v>2336</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2343</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
-        <v>2339</v>
+        <v>2333</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>2343</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
-        <v>2340</v>
+        <v>2334</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>2343</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B172" s="31" t="s">
-        <v>2344</v>
+        <v>2338</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>2349</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
-        <v>2345</v>
+        <v>2339</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>2349</v>
+        <v>2343</v>
       </c>
       <c r="D173" s="34" t="s">
-        <v>2567</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
-        <v>2346</v>
+        <v>2340</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>2349</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
-        <v>2347</v>
+        <v>2341</v>
       </c>
       <c r="C175" s="34" t="s">
-        <v>2349</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
-        <v>2348</v>
+        <v>2342</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2349</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2350</v>
+        <v>2344</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2351</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
-        <v>2476</v>
+        <v>2470</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2477</v>
+        <v>2471</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2352</v>
+        <v>2346</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2353</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
-        <v>2354</v>
+        <v>2348</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>2353</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B182" s="31" t="s">
-        <v>2355</v>
+        <v>2349</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2353</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B183" s="31" t="s">
-        <v>2356</v>
+        <v>2350</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2353</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B184" s="31" t="s">
-        <v>2357</v>
+        <v>2351</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>2360</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B185" s="31" t="s">
-        <v>2358</v>
+        <v>2352</v>
       </c>
       <c r="C185" s="34" t="s">
-        <v>2360</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B186" s="31" t="s">
-        <v>2359</v>
+        <v>2353</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2360</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
-        <v>2361</v>
+        <v>2355</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>2365</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B188" s="31" t="s">
-        <v>2362</v>
+        <v>2356</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>2365</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B189" s="31" t="s">
-        <v>2363</v>
+        <v>2357</v>
       </c>
       <c r="C189" s="34" t="s">
-        <v>2365</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B190" s="31" t="s">
-        <v>2364</v>
+        <v>2358</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2365</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2366</v>
+        <v>2360</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B192" s="31" t="s">
-        <v>2367</v>
+        <v>2361</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B193" s="31" t="s">
-        <v>2368</v>
+        <v>2362</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
-        <v>2175</v>
+        <v>2169</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
-        <v>2370</v>
+        <v>2364</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>2374</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B196" s="31" t="s">
-        <v>2371</v>
+        <v>2365</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>2374</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B197" s="31" t="s">
-        <v>2372</v>
+        <v>2366</v>
       </c>
       <c r="C197" s="34" t="s">
-        <v>2374</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B198" s="31" t="s">
-        <v>2373</v>
+        <v>2367</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2374</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2375</v>
+        <v>2369</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B200" s="31" t="s">
-        <v>2376</v>
+        <v>2370</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B201" s="31" t="s">
-        <v>2377</v>
+        <v>2371</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B202" s="31" t="s">
-        <v>2378</v>
+        <v>2372</v>
       </c>
       <c r="C202" s="34" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B203" s="31" t="s">
-        <v>2379</v>
+        <v>2373</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2382</v>
+        <v>2376</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2387</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C205" s="34" t="s">
         <v>2381</v>
-      </c>
-      <c r="C205" s="34" t="s">
-        <v>2387</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
-        <v>2383</v>
+        <v>2377</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>2387</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B207" s="31" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>2387</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B208" s="31" t="s">
-        <v>2385</v>
+        <v>2379</v>
       </c>
       <c r="C208" s="34" t="s">
-        <v>2387</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B209" s="31" t="s">
-        <v>2386</v>
+        <v>2380</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2387</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
-        <v>2388</v>
+        <v>2382</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>2392</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B211" s="31" t="s">
-        <v>2389</v>
+        <v>2383</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>2392</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B212" s="31" t="s">
-        <v>2390</v>
+        <v>2384</v>
       </c>
       <c r="C212" s="34" t="s">
-        <v>2392</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B213" s="31" t="s">
-        <v>2391</v>
+        <v>2385</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2392</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2393</v>
+        <v>2387</v>
       </c>
       <c r="C214" s="34" t="s">
-        <v>2396</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B215" s="31" t="s">
-        <v>2394</v>
+        <v>2388</v>
       </c>
       <c r="C215" s="34" t="s">
-        <v>2396</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B216" s="31" t="s">
-        <v>2395</v>
+        <v>2389</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2396</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2404</v>
+        <v>2398</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2407</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B218" s="31" t="s">
-        <v>2408</v>
+        <v>2402</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2407</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
-        <v>2405</v>
+        <v>2399</v>
       </c>
       <c r="C219" s="34" t="s">
-        <v>2407</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B220" s="31" t="s">
-        <v>2406</v>
+        <v>2400</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2407</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
-        <v>2409</v>
+        <v>2403</v>
       </c>
       <c r="C221" s="34" t="s">
-        <v>2410</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2411</v>
+        <v>2405</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2412</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2413</v>
+        <v>2407</v>
       </c>
       <c r="C223" s="42" t="s">
-        <v>2451</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
-        <v>2593</v>
+        <v>2587</v>
       </c>
       <c r="C224" s="34" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="225" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B225" s="31" t="s">
-        <v>2590</v>
+        <v>2584</v>
       </c>
       <c r="C225" s="34" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="226" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B226" s="31" t="s">
-        <v>2583</v>
+        <v>2577</v>
       </c>
       <c r="C226" s="34" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
       <c r="D226" s="34" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="227" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B227" s="31" t="s">
-        <v>2591</v>
+        <v>2585</v>
       </c>
       <c r="C227" s="34" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="228" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B228" s="31" t="s">
-        <v>2592</v>
+        <v>2586</v>
       </c>
       <c r="C228" s="34" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="229" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B229" s="31" t="s">
-        <v>2414</v>
+        <v>2408</v>
       </c>
       <c r="C229" s="34" t="s">
-        <v>2417</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="230" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B230" s="31" t="s">
-        <v>2415</v>
+        <v>2409</v>
       </c>
       <c r="C230" s="34" t="s">
-        <v>2417</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="231" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B231" s="31" t="s">
-        <v>2416</v>
+        <v>2410</v>
       </c>
       <c r="C231" s="34" t="s">
-        <v>2417</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="232" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B232" s="31" t="s">
-        <v>2336</v>
+        <v>2330</v>
       </c>
       <c r="C232" s="34" t="s">
-        <v>2417</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="233" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B233" s="31" t="s">
-        <v>2418</v>
+        <v>2412</v>
       </c>
       <c r="C233" s="34" t="s">
-        <v>2421</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="234" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B234" s="31" t="s">
-        <v>2419</v>
+        <v>2413</v>
       </c>
       <c r="C234" s="34" t="s">
-        <v>2421</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="235" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B235" s="31" t="s">
-        <v>2420</v>
+        <v>2414</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>2421</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="236" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B236" s="31" t="s">
-        <v>2422</v>
+        <v>2416</v>
       </c>
       <c r="C236" s="34" t="s">
-        <v>2427</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="237" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B237" s="31" t="s">
-        <v>2423</v>
+        <v>2417</v>
       </c>
       <c r="C237" s="34" t="s">
-        <v>2427</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="238" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B238" s="31" t="s">
-        <v>2424</v>
+        <v>2418</v>
       </c>
       <c r="C238" s="34" t="s">
-        <v>2427</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="239" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B239" s="31" t="s">
-        <v>2425</v>
+        <v>2419</v>
       </c>
       <c r="C239" s="34" t="s">
-        <v>2427</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="240" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B240" s="31" t="s">
-        <v>2426</v>
+        <v>2420</v>
       </c>
       <c r="C240" s="34" t="s">
-        <v>2427</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B241" s="31" t="s">
-        <v>2428</v>
+        <v>2422</v>
       </c>
       <c r="C241" s="34" t="s">
-        <v>2429</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B242" s="31" t="s">
-        <v>2430</v>
+        <v>2424</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2431</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B243" s="31" t="s">
-        <v>2432</v>
+        <v>2426</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2433</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2434</v>
+        <v>2428</v>
       </c>
       <c r="C244" s="34" t="s">
-        <v>2439</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
-        <v>2435</v>
+        <v>2429</v>
       </c>
       <c r="C245" s="34" t="s">
-        <v>2439</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B246" s="31" t="s">
-        <v>2436</v>
+        <v>2430</v>
       </c>
       <c r="C246" s="34" t="s">
-        <v>2439</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
-        <v>2437</v>
+        <v>2431</v>
       </c>
       <c r="C247" s="34" t="s">
-        <v>2439</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2438</v>
+        <v>2432</v>
       </c>
       <c r="C248" s="34" t="s">
-        <v>2439</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2440</v>
+        <v>2434</v>
       </c>
       <c r="C249" s="32" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2532</v>
+        <v>2526</v>
       </c>
       <c r="C250" s="32" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2533</v>
+        <v>2527</v>
       </c>
       <c r="C251" s="32" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2442</v>
+        <v>2436</v>
       </c>
       <c r="C252" s="32" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2452</v>
+        <v>2446</v>
       </c>
       <c r="C253" s="34" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2453</v>
+        <v>2447</v>
       </c>
       <c r="C254" s="34" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2454</v>
+        <v>2448</v>
       </c>
       <c r="C255" s="34" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2455</v>
+        <v>2449</v>
       </c>
       <c r="C256" s="34" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2457</v>
+        <v>2451</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
-        <v>2458</v>
+        <v>2452</v>
       </c>
       <c r="C258" s="32" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
-        <v>2459</v>
+        <v>2453</v>
       </c>
       <c r="C259" s="32" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2460</v>
+        <v>2454</v>
       </c>
       <c r="C260" s="32" t="s">
-        <v>2095</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
-        <v>2461</v>
+        <v>2455</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C262" s="34" t="s">
         <v>2462</v>
-      </c>
-      <c r="C262" s="34" t="s">
-        <v>2468</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
-        <v>2463</v>
+        <v>2457</v>
       </c>
       <c r="C263" s="34" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2464</v>
+        <v>2458</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
-        <v>2465</v>
+        <v>2459</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2466</v>
+        <v>2460</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2467</v>
+        <v>2461</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
-        <v>2311</v>
+        <v>2305</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2468</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2469</v>
+        <v>2463</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2470</v>
+        <v>2464</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
-        <v>2471</v>
+        <v>2465</v>
       </c>
       <c r="C271" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
+        <v>2466</v>
+      </c>
+      <c r="C272" s="34" t="s">
         <v>2472</v>
-      </c>
-      <c r="C272" s="34" t="s">
-        <v>2478</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
-        <v>2473</v>
+        <v>2467</v>
       </c>
       <c r="C273" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2220</v>
+        <v>2214</v>
       </c>
       <c r="C274" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2474</v>
+        <v>2468</v>
       </c>
       <c r="C275" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
-        <v>2475</v>
+        <v>2469</v>
       </c>
       <c r="C276" s="34" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2479</v>
+        <v>2473</v>
       </c>
       <c r="C277" s="32" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2184</v>
+        <v>2178</v>
       </c>
       <c r="C278" s="32" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2480</v>
+        <v>2474</v>
       </c>
       <c r="C279" s="32" t="s">
-        <v>2456</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="280" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B280" s="31" t="s">
-        <v>2481</v>
+        <v>2475</v>
       </c>
       <c r="C280" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="281" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B281" s="31" t="s">
-        <v>2482</v>
+        <v>2476</v>
       </c>
       <c r="C281" s="34" t="s">
-        <v>2483</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="282" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B282" s="31" t="s">
-        <v>2484</v>
+        <v>2478</v>
       </c>
       <c r="C282" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="283" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B283" s="31" t="s">
-        <v>2485</v>
+        <v>2479</v>
       </c>
       <c r="C283" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="284" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B284" s="31" t="s">
-        <v>2486</v>
+        <v>2480</v>
       </c>
       <c r="C284" s="32" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="285" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B285" s="31" t="s">
-        <v>2487</v>
+        <v>2481</v>
       </c>
       <c r="C285" s="34" t="s">
-        <v>2247</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="286" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B286" s="31" t="s">
-        <v>2488</v>
+        <v>2482</v>
       </c>
       <c r="C286" s="34" t="s">
-        <v>2247</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="287" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B287" s="31" t="s">
-        <v>2568</v>
+        <v>2562</v>
       </c>
       <c r="C287" s="34" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="288" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B288" s="31" t="s">
-        <v>2569</v>
+        <v>2563</v>
       </c>
       <c r="C288" s="34" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="289" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B289" s="31" t="s">
-        <v>2570</v>
+        <v>2564</v>
       </c>
       <c r="C289" s="34" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="290" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B290" s="31" t="s">
-        <v>2571</v>
+        <v>2565</v>
       </c>
       <c r="C290" s="32" t="s">
-        <v>2559</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="291" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B291" s="31" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
       <c r="C291" s="34" t="s">
-        <v>2573</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="292" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B292" s="31" t="s">
-        <v>2574</v>
+        <v>2568</v>
       </c>
       <c r="C292" s="34" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="293" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B293" s="31" t="s">
-        <v>2575</v>
+        <v>2569</v>
       </c>
       <c r="C293" s="34" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="294" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B294" s="31" t="s">
-        <v>2184</v>
+        <v>2178</v>
       </c>
       <c r="C294" s="34" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="295" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B295" s="31" t="s">
-        <v>2185</v>
+        <v>2179</v>
       </c>
       <c r="C295" s="34" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="296" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B296" s="31" t="s">
-        <v>2576</v>
+        <v>2570</v>
       </c>
       <c r="C296" s="34" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="297" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B297" s="31" t="s">
-        <v>2577</v>
+        <v>2571</v>
       </c>
       <c r="C297" s="34" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="298" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B298" s="31" t="s">
-        <v>2321</v>
+        <v>2315</v>
       </c>
       <c r="C298" s="34" t="s">
-        <v>2566</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="299" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B299" s="31" t="s">
-        <v>2579</v>
+        <v>2573</v>
       </c>
       <c r="C299" s="34" t="s">
-        <v>2566</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="300" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B300" s="31" t="s">
-        <v>2580</v>
+        <v>2574</v>
       </c>
       <c r="C300" s="34" t="s">
-        <v>2566</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="301" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B301" s="31" t="s">
-        <v>2582</v>
+        <v>2576</v>
       </c>
       <c r="C301" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B302" s="31" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C302" s="34" t="s">
+        <v>2713</v>
       </c>
     </row>
   </sheetData>
@@ -32345,6 +32722,7 @@
     <hyperlink ref="C224" r:id="rId154" xr:uid="{526BD004-A80C-4961-870F-F33828CD8403}"/>
     <hyperlink ref="C225:C228" r:id="rId155" display="祭だん" xr:uid="{82D9F577-9D3F-4642-8006-C0804437E317}"/>
     <hyperlink ref="D132" r:id="rId156" xr:uid="{079AED01-7E13-48B1-AF30-0966E317E8BB}"/>
+    <hyperlink ref="C302" r:id="rId157" xr:uid="{B64E68D0-DD98-4949-B102-A6783BDF9DB3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -32361,10 +32739,10 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>2609</v>
+        <v>2603</v>
       </c>
       <c r="C2" t="s">
-        <v>2610</v>
+        <v>2604</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2237" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ED5FC3A-AD67-411B-9F4F-E94D19437E9D}"/>
+  <xr:revisionPtr revIDLastSave="2283" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD3017C9-44FC-4B59-B3ED-CB50A8A4E304}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11835" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="16770" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="2760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="2779">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -6575,9 +6575,6 @@
     <t>時</t>
   </si>
   <si>
-    <t>亳</t>
-  </si>
-  <si>
     <t>勁</t>
   </si>
   <si>
@@ -7031,13 +7028,7 @@
     <t>消?</t>
   </si>
   <si>
-    <t>佤</t>
-  </si>
-  <si>
     <t>無</t>
-  </si>
-  <si>
-    <t>主</t>
   </si>
   <si>
     <t>影</t>
@@ -7298,9 +7289,6 @@
     <t>兡</t>
   </si>
   <si>
-    <t>冯</t>
-  </si>
-  <si>
     <t>亏</t>
   </si>
   <si>
@@ -10520,13 +10508,6 @@
   </si>
   <si>
     <t>倂われ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>勀客</t>
-    <rPh sb="1" eb="2">
-      <t>キャク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -10969,10 +10950,6 @@
   </si>
   <si>
     <t>[介]?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[勀]?</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -12641,6 +12618,139 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>儌乥举剪</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>祭ばや子</t>
+    <rPh sb="0" eb="1">
+      <t>マツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桶地下孝</t>
+    <rPh sb="0" eb="3">
+      <t>オケチカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倾主</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人影</t>
+    <rPh sb="0" eb="2">
+      <t>ヒトカゲ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佤</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>冯</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>亳</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>万冯亳</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はざ間</t>
+    <rPh sb="2" eb="3">
+      <t>アイダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一乱仃侕</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こうえん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桶地下考</t>
+    <rPh sb="0" eb="3">
+      <t>オケチカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伕佄亇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひつぎ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桶地下考</t>
+    <rPh sb="0" eb="3">
+      <t>オケチカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丌侕僌丟</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かんおけ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>别伥乱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぶよう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遷?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遷客</t>
+    <rPh sb="1" eb="2">
+      <t>キャク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -13635,7 +13745,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="49" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="49" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
       <c r="B1" s="50" t="s">
         <v>1560</v>
@@ -13644,25 +13754,25 @@
         <v>1561</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="E1" s="51" t="s">
+        <v>2015</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G1" s="52" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H1" s="52" t="s">
+        <v>2018</v>
+      </c>
+      <c r="I1" s="52" t="s">
         <v>2019</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="J1" s="52" t="s">
         <v>2020</v>
-      </c>
-      <c r="G1" s="52" t="s">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="52" t="s">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="52" t="s">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="52" t="s">
-        <v>2024</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -13899,7 +14009,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="C31">
         <v>29</v>
@@ -14011,7 +14121,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="1" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
       <c r="C45">
         <v>43</v>
@@ -14155,7 +14265,7 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B63" s="1" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="C63">
         <v>61</v>
@@ -14227,7 +14337,7 @@
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B72" s="1" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="C72" t="s">
         <v>1562</v>
@@ -14299,7 +14409,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B81" s="1" t="s">
-        <v>72</v>
+        <v>2766</v>
       </c>
       <c r="C81" t="s">
         <v>1577</v>
@@ -14307,7 +14417,7 @@
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B82" s="1" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
       <c r="C82" t="s">
         <v>1578</v>
@@ -14323,7 +14433,7 @@
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B84" s="1" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="C84" t="s">
         <v>1580</v>
@@ -14331,7 +14441,7 @@
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B85" s="1" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="C85" t="s">
         <v>1581</v>
@@ -14339,7 +14449,7 @@
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B86" s="1" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="C86" t="s">
         <v>863</v>
@@ -14379,7 +14489,7 @@
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B91" s="1" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="C91" t="s">
         <v>717</v>
@@ -14411,7 +14521,7 @@
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B95" s="1" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="C95" t="s">
         <v>1594</v>
@@ -14443,7 +14553,7 @@
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="1" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
       <c r="C99" t="s">
         <v>722</v>
@@ -14459,7 +14569,7 @@
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="1" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
       <c r="C101" t="s">
         <v>1602</v>
@@ -14483,7 +14593,7 @@
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="1" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="C104" t="s">
         <v>1606</v>
@@ -14507,7 +14617,7 @@
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="1" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="C107" t="s">
         <v>1610</v>
@@ -14515,7 +14625,7 @@
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="1" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="C108" t="s">
         <v>1611</v>
@@ -14523,7 +14633,7 @@
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="1" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="C109" t="s">
         <v>1612</v>
@@ -14539,7 +14649,7 @@
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="1" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="C111" t="s">
         <v>1615</v>
@@ -14555,7 +14665,7 @@
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="1" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
       <c r="C113" t="s">
         <v>1618</v>
@@ -14563,7 +14673,7 @@
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="1" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="C114" t="s">
         <v>1619</v>
@@ -14571,7 +14681,7 @@
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="1" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="C115" t="s">
         <v>1620</v>
@@ -14587,7 +14697,7 @@
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="1" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="C117" t="s">
         <v>1622</v>
@@ -14619,7 +14729,7 @@
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="1" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="C121" t="s">
         <v>1628</v>
@@ -14627,7 +14737,7 @@
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="1" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
       <c r="C122" t="s">
         <v>1629</v>
@@ -14635,7 +14745,7 @@
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="1" t="s">
-        <v>1903</v>
+        <v>2762</v>
       </c>
       <c r="C123" t="s">
         <v>1630</v>
@@ -14643,7 +14753,7 @@
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="1" t="s">
-        <v>1904</v>
+        <v>1900</v>
       </c>
       <c r="C124" t="s">
         <v>1631</v>
@@ -14667,7 +14777,7 @@
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="1" t="s">
-        <v>2756</v>
+        <v>2750</v>
       </c>
       <c r="C127" t="s">
         <v>1636</v>
@@ -14675,7 +14785,7 @@
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="1" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="C128" t="s">
         <v>1637</v>
@@ -14699,7 +14809,7 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B131" s="1" t="s">
-        <v>1906</v>
+        <v>1902</v>
       </c>
       <c r="C131" t="s">
         <v>1641</v>
@@ -14715,7 +14825,7 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B133" s="1" t="s">
-        <v>1907</v>
+        <v>1903</v>
       </c>
       <c r="C133" t="s">
         <v>1643</v>
@@ -14723,7 +14833,7 @@
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B134" s="1" t="s">
-        <v>1908</v>
+        <v>1904</v>
       </c>
       <c r="C134" t="s">
         <v>1644</v>
@@ -14731,21 +14841,21 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B135" s="1" t="s">
-        <v>2714</v>
+        <v>2708</v>
       </c>
       <c r="C135" s="55" t="s">
-        <v>2723</v>
+        <v>2717</v>
       </c>
       <c r="D135" s="33" t="s">
-        <v>2724</v>
+        <v>2718</v>
       </c>
       <c r="E135" s="34" t="s">
-        <v>2725</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B136" s="1" t="s">
-        <v>1909</v>
+        <v>1905</v>
       </c>
       <c r="C136" t="s">
         <v>1645</v>
@@ -14793,7 +14903,7 @@
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B142" s="1" t="s">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="C142" t="s">
         <v>1656</v>
@@ -14849,7 +14959,7 @@
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B149" s="1" t="s">
-        <v>1911</v>
+        <v>1907</v>
       </c>
       <c r="C149" t="s">
         <v>1668</v>
@@ -14873,7 +14983,7 @@
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B152" s="1" t="s">
-        <v>1912</v>
+        <v>1908</v>
       </c>
       <c r="C152" t="s">
         <v>1673</v>
@@ -14881,7 +14991,7 @@
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B153" s="1" t="s">
-        <v>1913</v>
+        <v>1909</v>
       </c>
       <c r="C153" t="s">
         <v>1674</v>
@@ -14897,7 +15007,7 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B155" s="1" t="s">
-        <v>1677</v>
+        <v>2763</v>
       </c>
       <c r="C155" t="s">
         <v>1433</v>
@@ -14905,162 +15015,162 @@
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B156" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C156" t="s">
         <v>1678</v>
-      </c>
-      <c r="C156" t="s">
-        <v>1679</v>
       </c>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B157" s="1" t="s">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="C157" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B158" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C158" t="s">
         <v>1681</v>
       </c>
-      <c r="C158" t="s">
-        <v>1682</v>
-      </c>
       <c r="F158" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="G158" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B159" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C159" t="s">
         <v>1683</v>
       </c>
-      <c r="C159" t="s">
-        <v>1684</v>
-      </c>
       <c r="D159" s="33" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="E159" s="34" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B160" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="C160" t="s">
-        <v>1991</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B161" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C161" t="s">
-        <v>2013</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B162" s="1" t="s">
-        <v>1915</v>
+        <v>1911</v>
       </c>
       <c r="C162" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B163" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C163" t="s">
         <v>1688</v>
       </c>
-      <c r="C163" t="s">
-        <v>1689</v>
-      </c>
       <c r="D163" s="33" t="s">
-        <v>2067</v>
+        <v>2063</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>2493</v>
+        <v>2488</v>
       </c>
       <c r="F163" s="32" t="s">
-        <v>2553</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B164" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="C164" t="s">
-        <v>2590</v>
+        <v>2584</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>2554</v>
+        <v>2548</v>
       </c>
       <c r="E164" s="34" t="s">
-        <v>2071</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B165" s="1" t="s">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="C165" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B166" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C166" t="s">
         <v>1692</v>
-      </c>
-      <c r="C166" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B167" s="1" t="s">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="C167" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B168" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C168" t="s">
         <v>1695</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B169" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C169" t="s">
         <v>1697</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B170" s="1" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C170" t="s">
         <v>1699</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B171" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C171" t="s">
         <v>1701</v>
-      </c>
-      <c r="C171" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B172" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C172" t="s">
         <v>72</v>
@@ -15068,31 +15178,31 @@
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B173" s="1" t="s">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="C173" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B174" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="C174" t="s">
-        <v>1974</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B175" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C175" t="s">
         <v>1706</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B176" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C176" t="s">
         <v>856</v>
@@ -15100,375 +15210,375 @@
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B177" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="C177" t="s">
-        <v>1992</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B178" s="1" t="s">
-        <v>1919</v>
+        <v>1915</v>
       </c>
       <c r="C178" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="179" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B179" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C179" t="s">
         <v>1711</v>
       </c>
-      <c r="C179" t="s">
-        <v>1712</v>
-      </c>
       <c r="F179" s="32" t="s">
-        <v>2096</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B180" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C180" t="s">
         <v>1713</v>
       </c>
-      <c r="C180" t="s">
-        <v>1714</v>
-      </c>
       <c r="D180" s="33" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="E180" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>2096</v>
+        <v>2092</v>
       </c>
       <c r="G180" s="34" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B181" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C181" t="s">
         <v>757</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>2721</v>
+        <v>2715</v>
       </c>
       <c r="E181" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B182" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C182" t="s">
         <v>1716</v>
-      </c>
-      <c r="C182" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B183" s="1" t="s">
-        <v>1920</v>
+        <v>1916</v>
       </c>
       <c r="C183" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B184" s="1" t="s">
-        <v>1921</v>
+        <v>1917</v>
       </c>
       <c r="C184" t="s">
-        <v>2117</v>
+        <v>2113</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2116</v>
+        <v>2112</v>
       </c>
       <c r="E184" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
       <c r="G184" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B185" s="1" t="s">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="C185" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>2115</v>
+        <v>2111</v>
       </c>
       <c r="E185" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B186" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C186" t="s">
         <v>1720</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B187" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="C187" t="s">
-        <v>1971</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="188" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B188" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C188" t="s">
         <v>1723</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B189" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C189" t="s">
         <v>1725</v>
       </c>
-      <c r="C189" t="s">
-        <v>1726</v>
-      </c>
       <c r="D189" s="33" t="s">
-        <v>2038</v>
+        <v>2034</v>
       </c>
       <c r="E189" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B190" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C190" t="s">
         <v>1727</v>
-      </c>
-      <c r="C190" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B191" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C191" t="s">
         <v>1729</v>
-      </c>
-      <c r="C191" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B192" s="1" t="s">
-        <v>1923</v>
+        <v>1919</v>
       </c>
       <c r="C192" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="193" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B193" s="1" t="s">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="C193" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="E193" s="34" t="s">
-        <v>2073</v>
+        <v>2069</v>
       </c>
       <c r="F193" s="32" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
       <c r="G193" s="32" t="s">
-        <v>2095</v>
+        <v>2091</v>
       </c>
       <c r="H193" s="32" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
       <c r="I193" s="34" t="s">
-        <v>2073</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B194" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="C194" t="s">
-        <v>1970</v>
+        <v>1966</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>2575</v>
+        <v>2569</v>
       </c>
       <c r="E194" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>2095</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B195" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C195" t="s">
         <v>1734</v>
       </c>
-      <c r="C195" t="s">
-        <v>1735</v>
-      </c>
       <c r="D195" s="33" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="E195" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B196" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C196" t="s">
         <v>1736</v>
       </c>
-      <c r="C196" t="s">
-        <v>1737</v>
-      </c>
       <c r="D196" s="33" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="E196" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B197" s="1" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C197" t="s">
         <v>1738</v>
       </c>
-      <c r="C197" t="s">
-        <v>1739</v>
-      </c>
       <c r="F197" s="34" t="s">
-        <v>2100</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B198" s="1" t="s">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="C198" t="s">
-        <v>2121</v>
+        <v>2117</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>2111</v>
+        <v>2107</v>
       </c>
       <c r="E198" s="34" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B199" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="C199" t="s">
-        <v>2122</v>
+        <v>2118</v>
       </c>
       <c r="F199" s="32" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B200" s="1" t="s">
-        <v>1926</v>
+        <v>1922</v>
       </c>
       <c r="C200" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="D200" s="33" t="s">
-        <v>2063</v>
+        <v>2059</v>
       </c>
       <c r="E200" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B201" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C201" t="s">
         <v>1742</v>
-      </c>
-      <c r="C201" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="202" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B202" s="1" t="s">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="C202" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="203" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B203" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C203" t="s">
         <v>1745</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="204" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B204" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C204" t="s">
         <v>1747</v>
-      </c>
-      <c r="C204" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="205" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B205" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C205" t="s">
         <v>1749</v>
       </c>
-      <c r="C205" t="s">
-        <v>1750</v>
-      </c>
       <c r="F205" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
       <c r="G205" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B206" s="1" t="s">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="C206" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="D206" s="33" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="E206" s="34" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B207" s="1" t="s">
-        <v>1929</v>
+        <v>1925</v>
       </c>
       <c r="C207" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="208" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B208" s="1" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C208" t="s">
         <v>1753</v>
-      </c>
-      <c r="C208" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.4">
@@ -15476,21 +15586,21 @@
         <v>856</v>
       </c>
       <c r="C209" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D209" s="33" t="s">
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="E209" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B210" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C210" t="s">
         <v>1756</v>
-      </c>
-      <c r="C210" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.4">
@@ -15498,59 +15608,59 @@
         <v>1070</v>
       </c>
       <c r="C211" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B212" s="1" t="s">
-        <v>1930</v>
+        <v>1926</v>
       </c>
       <c r="C212" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="F212" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B213" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C213" t="s">
         <v>1760</v>
       </c>
-      <c r="C213" t="s">
-        <v>1761</v>
-      </c>
       <c r="D213" s="33" t="s">
-        <v>2112</v>
+        <v>2108</v>
       </c>
       <c r="E213" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B214" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C214" t="s">
         <v>1762</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B215" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C215" t="s">
         <v>1764</v>
-      </c>
-      <c r="C215" t="s">
-        <v>1765</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B216" s="1" t="s">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C216" t="s">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="F216" s="32" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
@@ -15558,21 +15668,21 @@
         <v>1076</v>
       </c>
       <c r="C217" t="s">
-        <v>2595</v>
+        <v>2589</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>2551</v>
+        <v>2545</v>
       </c>
       <c r="E217" s="34" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B218" s="1" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C218" t="s">
         <v>1766</v>
-      </c>
-      <c r="C218" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.4">
@@ -15580,90 +15690,90 @@
         <v>1141</v>
       </c>
       <c r="C219" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B220" s="1" t="s">
-        <v>1932</v>
+        <v>1928</v>
       </c>
       <c r="C220" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="D220" s="33" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="E220" s="34" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B221" s="1" t="s">
-        <v>1933</v>
+        <v>1929</v>
       </c>
       <c r="C221" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B222" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C222" t="s">
         <v>1771</v>
-      </c>
-      <c r="C222" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B223" s="1" t="s">
-        <v>1934</v>
+        <v>1930</v>
       </c>
       <c r="C223" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B224" s="1" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="C224" t="s">
-        <v>1983</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B225" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C225" t="s">
         <v>1775</v>
-      </c>
-      <c r="C225" t="s">
-        <v>1776</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B226" s="1" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="C226" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B227" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C227" t="s">
         <v>1778</v>
-      </c>
-      <c r="C227" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B228" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C228" t="s">
         <v>1780</v>
-      </c>
-      <c r="C228" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B229" s="1" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="C229" t="s">
         <v>430</v>
@@ -15671,258 +15781,258 @@
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B230" s="1" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C230" t="s">
-        <v>1990</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B231" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C231" t="s">
         <v>1784</v>
-      </c>
-      <c r="C231" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B232" s="1" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C232" t="s">
         <v>1786</v>
       </c>
-      <c r="C232" t="s">
-        <v>1787</v>
-      </c>
       <c r="D232" s="33" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="E232" s="34" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
       <c r="F232" s="32" t="s">
-        <v>2560</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B233" s="1" t="s">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="C233" t="s">
-        <v>2558</v>
+        <v>2552</v>
       </c>
       <c r="D233" s="33" t="s">
-        <v>2559</v>
+        <v>2553</v>
       </c>
       <c r="E233" s="34" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B234" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="C234" t="s">
-        <v>2005</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B235" s="1" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C235" t="s">
         <v>1789</v>
-      </c>
-      <c r="C235" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B236" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C236" t="s">
         <v>1791</v>
-      </c>
-      <c r="C236" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B237" s="1" t="s">
-        <v>1936</v>
+        <v>1932</v>
       </c>
       <c r="C237" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B238" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C238" t="s">
         <v>1794</v>
       </c>
-      <c r="C238" t="s">
-        <v>1795</v>
-      </c>
       <c r="D238" s="33" t="s">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="E238" s="34" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B239" s="1" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C239" t="s">
         <v>1796</v>
-      </c>
-      <c r="C239" t="s">
-        <v>1797</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B240" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C240" t="s">
         <v>1798</v>
-      </c>
-      <c r="C240" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B241" s="1" t="s">
-        <v>1937</v>
+        <v>1933</v>
       </c>
       <c r="C241" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B242" s="1" t="s">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="C242" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>2085</v>
+        <v>2081</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B243" s="1" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="C243" t="s">
         <v>1302</v>
       </c>
       <c r="D243" s="33" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="E243" s="34" t="s">
-        <v>2086</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B244" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C244" t="s">
         <v>1803</v>
-      </c>
-      <c r="C244" t="s">
-        <v>1804</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B245" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C245" t="s">
         <v>1805</v>
       </c>
-      <c r="C245" t="s">
-        <v>1806</v>
-      </c>
       <c r="D245" s="33" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B246" s="1" t="s">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="C246" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>2086</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B247" s="1" t="s">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="C247" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>2037</v>
+        <v>2033</v>
       </c>
       <c r="E247" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B248" s="1" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="C248" t="s">
-        <v>2004</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B249" s="1" t="s">
-        <v>1941</v>
+        <v>1937</v>
       </c>
       <c r="C249" t="s">
-        <v>1993</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B250" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C250" t="s">
         <v>1810</v>
       </c>
-      <c r="C250" t="s">
-        <v>1811</v>
-      </c>
       <c r="D250" s="33" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="E250" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
       <c r="F250" s="34" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B251" s="1" t="s">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="C251" t="s">
-        <v>2709</v>
+        <v>2703</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>2722</v>
+        <v>2716</v>
       </c>
       <c r="E251" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B252" s="1" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C252" t="s">
         <v>461</v>
@@ -15930,243 +16040,243 @@
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B253" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C253" t="s">
         <v>1813</v>
-      </c>
-      <c r="C253" t="s">
-        <v>1814</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B254" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C254" t="s">
         <v>1815</v>
       </c>
-      <c r="C254" t="s">
-        <v>1816</v>
-      </c>
       <c r="D254" s="33" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="E254" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B255" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C255" t="s">
         <v>1817</v>
-      </c>
-      <c r="C255" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B256" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C256" t="s">
         <v>1819</v>
-      </c>
-      <c r="C256" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B257" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C257" t="s">
         <v>1821</v>
       </c>
-      <c r="C257" t="s">
-        <v>1822</v>
-      </c>
       <c r="F257" s="32" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B258" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="C258" t="s">
-        <v>2557</v>
+        <v>2551</v>
       </c>
       <c r="D258" s="33" t="s">
-        <v>2556</v>
+        <v>2550</v>
       </c>
       <c r="E258" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B259" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C259" t="s">
         <v>1823</v>
       </c>
-      <c r="C259" t="s">
-        <v>1824</v>
-      </c>
       <c r="F259" s="32" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B260" s="1" t="s">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="C260" t="s">
-        <v>2582</v>
+        <v>2576</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="E260" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B261" s="1" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="C261" t="s">
         <v>416</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2113</v>
+        <v>2109</v>
       </c>
       <c r="E261" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="F261" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B262" s="1" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C262" t="s">
-        <v>2581</v>
+        <v>2575</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>2580</v>
+        <v>2574</v>
       </c>
       <c r="E262" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B263" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C263" t="s">
         <v>1827</v>
       </c>
-      <c r="C263" t="s">
-        <v>1828</v>
-      </c>
       <c r="D263" s="33" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="E263" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
-        <v>1829</v>
+        <v>2761</v>
       </c>
       <c r="C264" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
-        <v>1831</v>
+        <v>2757</v>
       </c>
       <c r="C265" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B266" s="1" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
       <c r="C266" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B267" s="1" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="C267" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="F267" s="34" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B268" s="1" t="s">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="C268" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="D268" s="33" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="E268" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B269" s="1" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="C269" t="s">
-        <v>1969</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B270" s="1" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="C270" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B271" s="1" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="C271" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B272" s="1" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="C272" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B273" s="1" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
       <c r="C273" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B274" s="1" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="C274" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B275" s="1" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="C275" t="s">
-        <v>1850</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.4">
@@ -16174,65 +16284,65 @@
         <v>429</v>
       </c>
       <c r="C276" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B277" s="1" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
       <c r="C277" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
       <c r="F277" s="34" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B278" s="1" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
       <c r="C278" t="s">
         <v>759</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2744</v>
+        <v>2738</v>
       </c>
       <c r="E278" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B279" s="1" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="C279" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
       <c r="D279" s="33" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>2445</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B280" s="1" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
       <c r="C280" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
       <c r="D280" s="41" t="s">
-        <v>2583</v>
+        <v>2577</v>
       </c>
       <c r="E280" s="42" t="s">
-        <v>2445</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B281" s="1" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
       <c r="C281" t="s">
         <v>1419</v>
@@ -16240,147 +16350,147 @@
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B282" s="1" t="s">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="C282" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B283" s="1" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="C283" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B284" s="1" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
       <c r="C284" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B285" s="1" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="C285" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B286" s="1" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
       <c r="C286" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B287" s="1" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="C287" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B288" s="1" t="s">
-        <v>1947</v>
+        <v>1943</v>
       </c>
       <c r="C288" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="D288" s="33" t="s">
-        <v>2048</v>
+        <v>2044</v>
       </c>
       <c r="E288" s="34" t="s">
-        <v>2082</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B289" s="1" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="C289" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B290" s="1" t="s">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="C290" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B291" s="1" t="s">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="C291" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
       <c r="F291" s="32" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B292" s="1" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="C292" t="s">
-        <v>1964</v>
+        <v>1960</v>
       </c>
       <c r="D292" s="33" t="s">
-        <v>2039</v>
+        <v>2035</v>
       </c>
       <c r="E292" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
       <c r="F292" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B293" s="1" t="s">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="C293" t="s">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="E293" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B294" s="1" t="s">
-        <v>1951</v>
+        <v>1947</v>
       </c>
       <c r="C294" t="s">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="D294" s="33" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="E294" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B295" s="1" t="s">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="C295" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.4">
@@ -16388,10 +16498,10 @@
         <v>286</v>
       </c>
       <c r="C296" t="s">
-        <v>1955</v>
+        <v>1951</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
@@ -16399,124 +16509,124 @@
         <v>1424</v>
       </c>
       <c r="C297" t="s">
-        <v>1956</v>
+        <v>1952</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B298" s="1" t="s">
-        <v>1953</v>
+        <v>1949</v>
       </c>
       <c r="C298" t="s">
-        <v>1954</v>
+        <v>1950</v>
       </c>
       <c r="F298" s="32" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B299" s="24" t="s">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="C299" t="s">
-        <v>2681</v>
+        <v>2675</v>
       </c>
       <c r="D299" s="33" t="s">
-        <v>2054</v>
+        <v>2050</v>
       </c>
       <c r="E299" s="32" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B300" s="1" t="s">
-        <v>1958</v>
+        <v>1954</v>
       </c>
       <c r="C300" t="s">
-        <v>1959</v>
+        <v>1955</v>
       </c>
       <c r="D300" s="33" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="E300" s="34" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B301" s="24" t="s">
-        <v>1960</v>
+        <v>1956</v>
       </c>
       <c r="C301" t="s">
-        <v>1961</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B302" s="18" t="s">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="C302" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="D302" s="33" t="s">
-        <v>2103</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B303" s="18" t="s">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="C303" t="s">
-        <v>1963</v>
+        <v>1959</v>
       </c>
       <c r="D303" s="33" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="E303" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B304" s="18" t="s">
-        <v>1965</v>
+        <v>1961</v>
       </c>
       <c r="C304" t="s">
-        <v>1968</v>
+        <v>1964</v>
       </c>
       <c r="D304" s="33" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="E304" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B305" s="26" t="s">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="C305" t="s">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="D305" s="33" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="E305" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B306" s="1" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="C306" t="s">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="D306" s="33" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="E306" s="34" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.4">
@@ -16524,134 +16634,134 @@
         <v>935</v>
       </c>
       <c r="C307" t="s">
-        <v>2507</v>
+        <v>2501</v>
       </c>
       <c r="D307" s="33" t="s">
-        <v>2483</v>
+        <v>2478</v>
       </c>
       <c r="E307" s="32" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
       <c r="F307" s="32" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B308" s="1" t="s">
-        <v>1980</v>
+        <v>1976</v>
       </c>
       <c r="C308" t="s">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="D308" s="33" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="E308" s="34" t="s">
-        <v>2077</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B309" s="27" t="s">
-        <v>1984</v>
+        <v>1980</v>
       </c>
       <c r="C309" t="s">
-        <v>1985</v>
+        <v>1981</v>
       </c>
       <c r="D309" s="33" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="E309" s="34" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B310" s="1" t="s">
-        <v>1986</v>
+        <v>1982</v>
       </c>
       <c r="C310" t="s">
-        <v>1987</v>
+        <v>1983</v>
       </c>
       <c r="D310" s="33" t="s">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="E310" s="34" t="s">
-        <v>2079</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B311" s="1" t="s">
-        <v>1988</v>
+        <v>1984</v>
       </c>
       <c r="C311" t="s">
-        <v>1989</v>
+        <v>1985</v>
       </c>
       <c r="D311" s="33" t="s">
-        <v>2065</v>
+        <v>2061</v>
       </c>
       <c r="E311" s="34" t="s">
-        <v>2079</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B312" s="1" t="s">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="C312" t="s">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="D312" s="33" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="E312" s="34" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B313" s="1" t="s">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="C313" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="D313" s="33" t="s">
-        <v>2125</v>
+        <v>2121</v>
       </c>
       <c r="E313" s="34" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B314" s="1" t="s">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="C314" t="s">
-        <v>2124</v>
+        <v>2120</v>
       </c>
       <c r="D314" s="33" t="s">
-        <v>2125</v>
+        <v>2121</v>
       </c>
       <c r="E314" s="34" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
       <c r="F314" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B315" s="1" t="s">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="C315" t="s">
-        <v>2591</v>
+        <v>2585</v>
       </c>
       <c r="D315" s="53" t="s">
-        <v>2592</v>
+        <v>2586</v>
       </c>
       <c r="E315" s="34" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
       <c r="F315" s="32" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
@@ -16659,75 +16769,75 @@
         <v>153</v>
       </c>
       <c r="C316" t="s">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="D316" s="33" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="E316" s="34" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B317" s="1" t="s">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="C317" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="D317" s="33" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="E317" s="34" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
       <c r="F317" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B318" s="1" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="C318" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="D318" s="33" t="s">
-        <v>2055</v>
+        <v>2051</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B319" s="1" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="C319" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="D319" s="33" t="s">
-        <v>2056</v>
+        <v>2052</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
       <c r="F319" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B320" s="1" t="s">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C320" t="s">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="D320" s="33" t="s">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="E320" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.4">
@@ -16735,30 +16845,30 @@
         <v>821</v>
       </c>
       <c r="C321" t="s">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="D321" s="33" t="s">
-        <v>2102</v>
+        <v>2098</v>
       </c>
       <c r="E321" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="322" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B322" s="1" t="s">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C322" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="D322" s="33" t="s">
-        <v>2057</v>
+        <v>2053</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
       <c r="F322" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="323" spans="2:7" x14ac:dyDescent="0.4">
@@ -16766,19 +16876,19 @@
         <v>1093</v>
       </c>
       <c r="C323" t="s">
-        <v>2496</v>
+        <v>2491</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2099</v>
+        <v>2095</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
       <c r="F323" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
       <c r="G323" s="32" t="s">
-        <v>2494</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="324" spans="2:7" x14ac:dyDescent="0.4">
@@ -16786,78 +16896,78 @@
         <v>296</v>
       </c>
       <c r="C324" t="s">
-        <v>2497</v>
+        <v>2492</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2114</v>
+        <v>2110</v>
       </c>
       <c r="E324" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
       <c r="F324" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="325" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B325" s="1" t="s">
-        <v>1976</v>
+        <v>1972</v>
       </c>
       <c r="C325" t="s">
-        <v>2118</v>
+        <v>2114</v>
       </c>
       <c r="D325" s="33" t="s">
-        <v>2120</v>
+        <v>2116</v>
       </c>
       <c r="E325" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="F325" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="326" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B326" s="1" t="s">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="C326" t="s">
-        <v>2119</v>
+        <v>2115</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>2120</v>
+        <v>2116</v>
       </c>
       <c r="E326" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="327" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B327" s="1" t="s">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="C327" t="s">
-        <v>2498</v>
+        <v>2777</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2441</v>
+        <v>2778</v>
       </c>
       <c r="E327" s="34" t="s">
-        <v>2073</v>
+        <v>2069</v>
       </c>
       <c r="F327" s="32" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="328" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B328" s="1" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="C328" t="s">
-        <v>2499</v>
+        <v>2493</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2440</v>
+        <v>2436</v>
       </c>
       <c r="E328" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="329" spans="2:7" x14ac:dyDescent="0.4">
@@ -16865,16 +16975,16 @@
         <v>406</v>
       </c>
       <c r="C329" t="s">
-        <v>2500</v>
+        <v>2494</v>
       </c>
       <c r="D329" s="33" t="s">
-        <v>2442</v>
+        <v>2437</v>
       </c>
       <c r="E329" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
       <c r="F329" s="32" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="330" spans="2:7" x14ac:dyDescent="0.4">
@@ -16882,16 +16992,16 @@
         <v>160</v>
       </c>
       <c r="C330" t="s">
-        <v>2501</v>
+        <v>2495</v>
       </c>
       <c r="D330" s="41" t="s">
-        <v>2443</v>
+        <v>2438</v>
       </c>
       <c r="E330" s="42" t="s">
-        <v>2445</v>
+        <v>2440</v>
       </c>
       <c r="F330" s="32" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="331" spans="2:7" x14ac:dyDescent="0.4">
@@ -16899,27 +17009,27 @@
         <v>1102</v>
       </c>
       <c r="C331" t="s">
-        <v>2502</v>
+        <v>2496</v>
       </c>
       <c r="D331" s="33" t="s">
-        <v>2444</v>
+        <v>2439</v>
       </c>
       <c r="E331" s="42" t="s">
-        <v>2445</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="332" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B332" s="1" t="s">
-        <v>2484</v>
+        <v>2479</v>
       </c>
       <c r="C332" t="s">
-        <v>2503</v>
+        <v>2497</v>
       </c>
       <c r="D332" s="43" t="s">
-        <v>2485</v>
+        <v>2480</v>
       </c>
       <c r="E332" s="34" t="s">
-        <v>2486</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="333" spans="2:7" x14ac:dyDescent="0.4">
@@ -16927,83 +17037,83 @@
         <v>1146</v>
       </c>
       <c r="C333" t="s">
-        <v>2504</v>
+        <v>2498</v>
       </c>
       <c r="D333" s="33" t="s">
-        <v>2487</v>
+        <v>2482</v>
       </c>
       <c r="E333" s="34" t="s">
-        <v>2487</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="334" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B334" s="1" t="s">
-        <v>2488</v>
+        <v>2483</v>
       </c>
       <c r="C334" t="s">
-        <v>2505</v>
+        <v>2499</v>
       </c>
       <c r="D334" s="33" t="s">
-        <v>2487</v>
+        <v>2482</v>
       </c>
       <c r="E334" s="34" t="s">
-        <v>2487</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="335" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
-        <v>2489</v>
+        <v>2484</v>
       </c>
       <c r="C335" t="s">
-        <v>2506</v>
+        <v>2500</v>
       </c>
       <c r="D335" s="41" t="s">
-        <v>2491</v>
+        <v>2486</v>
       </c>
       <c r="E335" s="34" t="s">
-        <v>2492</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="336" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B336" s="1" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C336" t="s">
         <v>2490</v>
       </c>
-      <c r="C336" t="s">
-        <v>2495</v>
-      </c>
       <c r="D336" s="41" t="s">
-        <v>2491</v>
+        <v>2486</v>
       </c>
       <c r="E336" s="34" t="s">
-        <v>2492</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B337" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="C337" t="s">
-        <v>2547</v>
+        <v>2541</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>2550</v>
+        <v>2544</v>
       </c>
       <c r="E337" s="34" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B338" s="1" t="s">
-        <v>2548</v>
+        <v>2542</v>
       </c>
       <c r="C338" t="s">
-        <v>2549</v>
+        <v>2543</v>
       </c>
       <c r="D338" s="33" t="s">
-        <v>2550</v>
+        <v>2544</v>
       </c>
       <c r="E338" s="34" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.4">
@@ -17011,96 +17121,96 @@
         <v>1021</v>
       </c>
       <c r="C339" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
       <c r="D339" s="53" t="s">
-        <v>2593</v>
+        <v>2587</v>
       </c>
       <c r="E339" s="32" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B340" s="1" t="s">
-        <v>2710</v>
+        <v>2704</v>
       </c>
       <c r="C340" t="s">
-        <v>2711</v>
+        <v>2705</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>2712</v>
+        <v>2706</v>
       </c>
       <c r="E340" s="34" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B341" s="1" t="s">
-        <v>2715</v>
+        <v>2709</v>
       </c>
       <c r="C341" s="55" t="s">
-        <v>2716</v>
+        <v>2710</v>
       </c>
       <c r="D341" s="33" t="s">
-        <v>2717</v>
+        <v>2711</v>
       </c>
       <c r="E341" s="34" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B342" s="1" t="s">
-        <v>2718</v>
+        <v>2712</v>
       </c>
       <c r="C342" s="55" t="s">
-        <v>2719</v>
+        <v>2713</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>2720</v>
+        <v>2714</v>
       </c>
       <c r="E342" s="34" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B343" s="1" t="s">
-        <v>2745</v>
+        <v>2739</v>
       </c>
       <c r="C343" t="s">
-        <v>2746</v>
+        <v>2740</v>
       </c>
       <c r="D343" s="33" t="s">
-        <v>2747</v>
+        <v>2741</v>
       </c>
       <c r="E343" s="33" t="s">
-        <v>2748</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B344" s="1" t="s">
-        <v>2749</v>
+        <v>2743</v>
       </c>
       <c r="C344" t="s">
-        <v>2750</v>
+        <v>2744</v>
       </c>
       <c r="D344" s="33" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B345" s="1" t="s">
-        <v>2751</v>
+        <v>2745</v>
       </c>
       <c r="C345" t="s">
-        <v>2752</v>
+        <v>2746</v>
       </c>
       <c r="D345" s="33" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
     </row>
   </sheetData>
@@ -18176,7 +18286,7 @@
         <v>。</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
       <c r="I3" s="6" t="str">
         <f>_xlfn.XLOOKUP(H3,対応表!$B:$B,対応表!$C:$C,"が")</f>
@@ -26801,8 +26911,8 @@
         <v>1271</v>
       </c>
       <c r="DS19" s="6" t="str">
-        <f>_xlfn.XLOOKUP(DR19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>[勀]?</v>
+        <f>_xlfn.XLOOKUP(DR19,対応表!$B:$B,対応表!$C:$C,"遷")</f>
+        <v>遷?</v>
       </c>
       <c r="DT19" s="7" t="s">
         <v>1272</v>
@@ -28512,7 +28622,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -28586,7 +28696,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C5E931-1AEC-434D-81A1-3EA98DBB914E}">
-  <dimension ref="B1:F98"/>
+  <dimension ref="B1:F105"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.25" style="35" bestFit="1" customWidth="1"/>
@@ -28598,1403 +28708,1403 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B1" s="54" t="s">
-        <v>2108</v>
+        <v>2104</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>2109</v>
+        <v>2105</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>2669</v>
+        <v>2663</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>2110</v>
+        <v>2106</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>2103</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
-        <v>2105</v>
+        <v>2101</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>2106</v>
+        <v>2102</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
-        <v>2215</v>
+        <v>2211</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>2216</v>
+        <v>2212</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>2217</v>
+        <v>2213</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
-        <v>2218</v>
+        <v>2214</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>2219</v>
+        <v>2215</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>2220</v>
+        <v>2216</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>2222</v>
+        <v>2218</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>2225</v>
+        <v>2221</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
-        <v>2227</v>
+        <v>2223</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>2228</v>
+        <v>2224</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>2229</v>
+        <v>2225</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2230</v>
+        <v>2226</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2231</v>
+        <v>2227</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
-        <v>2232</v>
+        <v>2228</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>2233</v>
+        <v>2229</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>2234</v>
+        <v>2230</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>2509</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2236</v>
+        <v>2232</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
-        <v>2237</v>
+        <v>2233</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
-        <v>2240</v>
+        <v>2236</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>2323</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2242</v>
+        <v>2238</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
-        <v>2320</v>
+        <v>2316</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>2321</v>
+        <v>2317</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2391</v>
+        <v>2387</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
-        <v>2393</v>
+        <v>2389</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>2394</v>
+        <v>2390</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2396</v>
+        <v>2392</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2395</v>
+        <v>2391</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="35" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2397</v>
+        <v>2393</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
-        <v>2437</v>
+        <v>2433</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>2438</v>
+        <v>2434</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="44" t="s">
-        <v>2525</v>
+        <v>2519</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>2508</v>
+        <v>2502</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="35" t="s">
-        <v>2510</v>
+        <v>2504</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>2511</v>
+        <v>2505</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>2512</v>
+        <v>2506</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="35" t="s">
-        <v>2513</v>
+        <v>2507</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>2514</v>
+        <v>2508</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>2515</v>
+        <v>2509</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="35" t="s">
-        <v>2516</v>
+        <v>2510</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>2517</v>
+        <v>2511</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>2231</v>
+        <v>2227</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="35" t="s">
-        <v>2518</v>
+        <v>2512</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>2519</v>
+        <v>2513</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="35" t="s">
-        <v>2520</v>
+        <v>2514</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>2521</v>
+        <v>2515</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="35" t="s">
-        <v>2522</v>
+        <v>2516</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>2523</v>
+        <v>2517</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>2524</v>
+        <v>2518</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="35" t="s">
-        <v>2529</v>
+        <v>2523</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>2530</v>
+        <v>2524</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>2542</v>
+        <v>2536</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="35" t="s">
-        <v>2531</v>
+        <v>2525</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>2532</v>
+        <v>2526</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>2535</v>
+        <v>2529</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B29" s="35" t="s">
-        <v>2533</v>
+        <v>2527</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>2534</v>
+        <v>2528</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="35" t="s">
-        <v>2536</v>
+        <v>2530</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>2537</v>
+        <v>2531</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B31" s="35" t="s">
-        <v>2538</v>
+        <v>2532</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>2539</v>
+        <v>2533</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B32" s="35" t="s">
-        <v>2540</v>
+        <v>2534</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>2541</v>
+        <v>2535</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>2542</v>
+        <v>2536</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="35" t="s">
-        <v>2543</v>
+        <v>2537</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>2544</v>
+        <v>2538</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>2542</v>
+        <v>2536</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="39" t="s">
-        <v>2545</v>
+        <v>2539</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>2323</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="35" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>2579</v>
+        <v>2573</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>2589</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B36" s="35" t="s">
-        <v>2656</v>
+        <v>2650</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>2596</v>
+        <v>2590</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B37" s="35" t="s">
-        <v>2597</v>
+        <v>2591</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>2598</v>
+        <v>2592</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>2672</v>
+        <v>2666</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B38" s="35" t="s">
-        <v>2599</v>
+        <v>2593</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>2600</v>
+        <v>2594</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B39" s="35" t="s">
-        <v>2657</v>
+        <v>2651</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>2601</v>
+        <v>2595</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B40" s="35" t="s">
-        <v>2658</v>
+        <v>2652</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>2602</v>
+        <v>2596</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B41" s="35" t="s">
-        <v>2605</v>
+        <v>2599</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>2427</v>
+        <v>2423</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B42" s="35" t="s">
-        <v>2606</v>
+        <v>2600</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>2607</v>
+        <v>2601</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B43" s="35" t="s">
-        <v>2543</v>
+        <v>2537</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>2608</v>
+        <v>2602</v>
       </c>
       <c r="D43" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B44" s="35" t="s">
-        <v>2609</v>
+        <v>2603</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>2610</v>
+        <v>2604</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B45" s="35" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>2611</v>
+        <v>2605</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="35" t="s">
-        <v>2612</v>
+        <v>2606</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>2613</v>
+        <v>2607</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B47" s="35" t="s">
-        <v>2614</v>
+        <v>2608</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>2615</v>
+        <v>2609</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="35" t="s">
-        <v>2616</v>
+        <v>2610</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>2617</v>
+        <v>2611</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" s="35" t="s">
-        <v>2618</v>
+        <v>2612</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>2619</v>
+        <v>2613</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="35" t="s">
-        <v>2620</v>
+        <v>2614</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>2621</v>
+        <v>2615</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" s="35" t="s">
-        <v>2622</v>
+        <v>2616</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>2623</v>
+        <v>2617</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" s="35" t="s">
-        <v>2624</v>
+        <v>2618</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>2625</v>
+        <v>2619</v>
       </c>
       <c r="D52" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B53" s="35" t="s">
-        <v>2626</v>
+        <v>2620</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>2627</v>
+        <v>2621</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B54" s="35" t="s">
-        <v>2628</v>
+        <v>2622</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>2629</v>
+        <v>2623</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" s="35" t="s">
-        <v>2630</v>
+        <v>2624</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>2631</v>
+        <v>2625</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="35" t="s">
-        <v>2632</v>
+        <v>2626</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>2633</v>
+        <v>2627</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B57" s="35" t="s">
-        <v>2634</v>
+        <v>2628</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>2635</v>
+        <v>2629</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B58" s="35" t="s">
-        <v>2636</v>
+        <v>2630</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>2637</v>
+        <v>2631</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B59" s="35" t="s">
-        <v>2638</v>
+        <v>2632</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>2639</v>
+        <v>2633</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B60" s="35" t="s">
-        <v>2640</v>
+        <v>2634</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>2641</v>
+        <v>2635</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B61" s="35" t="s">
-        <v>2642</v>
+        <v>2636</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>2643</v>
+        <v>2637</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B62" s="35" t="s">
-        <v>2644</v>
+        <v>2638</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>2645</v>
+        <v>2639</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B63" s="35" t="s">
-        <v>2646</v>
+        <v>2640</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>2647</v>
+        <v>2641</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F63" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B64" s="35" t="s">
-        <v>2648</v>
+        <v>2642</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>2649</v>
+        <v>2643</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B65" s="35" t="s">
-        <v>2650</v>
+        <v>2644</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>2651</v>
+        <v>2645</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F65" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B66" s="35" t="s">
-        <v>2652</v>
+        <v>2646</v>
       </c>
       <c r="C66" s="36" t="s">
-        <v>2653</v>
+        <v>2647</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F66" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B67" s="35" t="s">
-        <v>2654</v>
+        <v>2648</v>
       </c>
       <c r="C67" s="36" t="s">
-        <v>2655</v>
+        <v>2649</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F67" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B68" s="35" t="s">
-        <v>2659</v>
+        <v>2653</v>
       </c>
       <c r="C68" s="36" t="s">
+        <v>2658</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>2665</v>
+      </c>
+      <c r="E68" s="36" t="s">
         <v>2664</v>
-      </c>
-      <c r="D68" s="36" t="s">
-        <v>2671</v>
-      </c>
-      <c r="E68" s="36" t="s">
-        <v>2670</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B69" s="35" t="s">
-        <v>2660</v>
+        <v>2654</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>2661</v>
+        <v>2655</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>2671</v>
+        <v>2665</v>
       </c>
       <c r="F69" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B70" s="35" t="s">
-        <v>2662</v>
+        <v>2656</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>2663</v>
+        <v>2657</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>2671</v>
+        <v>2665</v>
       </c>
       <c r="E70" s="36" t="s">
-        <v>2670</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B71" s="35" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C71" s="36" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D71" s="36" t="s">
         <v>2665</v>
       </c>
-      <c r="C71" s="36" t="s">
-        <v>2666</v>
-      </c>
-      <c r="D71" s="36" t="s">
-        <v>2671</v>
-      </c>
       <c r="F71" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B72" s="35" t="s">
-        <v>2667</v>
+        <v>2661</v>
       </c>
       <c r="C72" s="36" t="s">
-        <v>2668</v>
+        <v>2662</v>
       </c>
       <c r="D72" s="36" t="s">
-        <v>2671</v>
+        <v>2665</v>
       </c>
       <c r="E72" s="36" t="s">
-        <v>2730</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B73" s="35" t="s">
-        <v>2673</v>
+        <v>2667</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>2674</v>
+        <v>2668</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>2671</v>
+        <v>2665</v>
       </c>
       <c r="F73" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B74" s="35" t="s">
-        <v>2675</v>
+        <v>2669</v>
       </c>
       <c r="C74" s="36" t="s">
-        <v>2676</v>
+        <v>2670</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>2677</v>
+        <v>2671</v>
       </c>
       <c r="F74" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B75" s="35" t="s">
-        <v>2680</v>
+        <v>2674</v>
       </c>
       <c r="C75" s="36" t="s">
-        <v>2678</v>
+        <v>2672</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="F75" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B76" s="35" t="s">
-        <v>2682</v>
+        <v>2676</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>2683</v>
+        <v>2677</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>2707</v>
+        <v>2701</v>
       </c>
       <c r="F76" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B77" s="35" t="s">
-        <v>2684</v>
+        <v>2678</v>
       </c>
       <c r="C77" s="36" t="s">
-        <v>2685</v>
+        <v>2679</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="F77" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B78" s="35" t="s">
-        <v>2695</v>
+        <v>2689</v>
       </c>
       <c r="C78" t="s">
-        <v>2686</v>
+        <v>2680</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E78" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
       <c r="F78" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B79" s="35" t="s">
-        <v>2697</v>
+        <v>2691</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>2696</v>
+        <v>2690</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E79" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
       <c r="F79" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B80" s="35" t="s">
-        <v>2698</v>
+        <v>2692</v>
       </c>
       <c r="C80" s="36" t="s">
-        <v>2687</v>
+        <v>2681</v>
       </c>
       <c r="D80" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E80" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
       <c r="F80" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B81" s="35" t="s">
-        <v>2699</v>
+        <v>2693</v>
       </c>
       <c r="C81" s="36" t="s">
-        <v>2688</v>
+        <v>2682</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E81" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B82" s="35" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>2673</v>
+      </c>
+      <c r="E82" s="36" t="s">
         <v>2700</v>
       </c>
-      <c r="C82" s="36" t="s">
-        <v>2689</v>
-      </c>
-      <c r="D82" s="36" t="s">
-        <v>2679</v>
-      </c>
-      <c r="E82" s="36" t="s">
-        <v>2706</v>
-      </c>
       <c r="F82" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B83" s="35" t="s">
-        <v>2701</v>
+        <v>2695</v>
       </c>
       <c r="C83" s="36" t="s">
-        <v>2690</v>
+        <v>2684</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E83" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
       <c r="F83" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B84" s="39" t="s">
-        <v>2702</v>
+        <v>2696</v>
       </c>
       <c r="C84" s="40" t="s">
-        <v>2691</v>
+        <v>2685</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
       <c r="F84" s="40" t="s">
-        <v>2729</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B85" s="35" t="s">
-        <v>2703</v>
+        <v>2697</v>
       </c>
       <c r="C85" s="36" t="s">
-        <v>2692</v>
+        <v>2686</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E85" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B86" s="35" t="s">
-        <v>2704</v>
+        <v>2698</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>2693</v>
+        <v>2687</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E86" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B87" s="35" t="s">
-        <v>2705</v>
+        <v>2699</v>
       </c>
       <c r="C87" s="36" t="s">
-        <v>2694</v>
+        <v>2688</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="E87" s="36" t="s">
-        <v>2706</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B88" s="35" t="s">
-        <v>2728</v>
+        <v>2722</v>
       </c>
       <c r="C88" s="36" t="s">
-        <v>2726</v>
+        <v>2720</v>
       </c>
       <c r="D88" s="36" t="s">
-        <v>2727</v>
+        <v>2721</v>
       </c>
       <c r="E88" s="36" t="s">
-        <v>2742</v>
+        <v>2736</v>
       </c>
       <c r="F88" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B89" s="35" t="s">
-        <v>2732</v>
+        <v>2726</v>
       </c>
       <c r="C89" s="36" t="s">
-        <v>2733</v>
+        <v>2727</v>
       </c>
       <c r="D89" s="36" t="s">
-        <v>2727</v>
+        <v>2721</v>
       </c>
       <c r="F89" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B90" s="35" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="C90" s="36" t="s">
-        <v>2734</v>
+        <v>2728</v>
       </c>
       <c r="D90" s="36" t="s">
-        <v>2741</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.4">
@@ -30002,32 +30112,32 @@
         <v>110</v>
       </c>
       <c r="C91" s="36" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D91" s="36" t="s">
         <v>2735</v>
-      </c>
-      <c r="D91" s="36" t="s">
-        <v>2741</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B92" s="35" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>2736</v>
+        <v>2730</v>
       </c>
       <c r="D92" s="36" t="s">
-        <v>2741</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B93" s="35" t="s">
-        <v>1941</v>
+        <v>1937</v>
       </c>
       <c r="C93" s="36" t="s">
-        <v>2754</v>
+        <v>2748</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>2741</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.4">
@@ -30035,63 +30145,140 @@
         <v>1144</v>
       </c>
       <c r="C94" s="36" t="s">
-        <v>2743</v>
+        <v>2737</v>
       </c>
       <c r="D94" s="36" t="s">
-        <v>2741</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B95" s="35" t="s">
-        <v>2737</v>
+        <v>2731</v>
       </c>
       <c r="C95" s="36" t="s">
-        <v>2738</v>
+        <v>2732</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F95" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B96" s="35" t="s">
-        <v>2739</v>
+        <v>2733</v>
       </c>
       <c r="C96" s="36" t="s">
-        <v>2740</v>
+        <v>2734</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>2708</v>
+        <v>2702</v>
       </c>
       <c r="F96" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B97" s="35" t="s">
-        <v>2755</v>
+        <v>2749</v>
       </c>
       <c r="C97" s="36" t="s">
-        <v>2753</v>
+        <v>2747</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>2679</v>
+        <v>2673</v>
       </c>
       <c r="F97" s="36" t="s">
-        <v>2322</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B98" s="35" t="s">
-        <v>2757</v>
+        <v>2751</v>
       </c>
       <c r="C98" s="36" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D98" s="36" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B99" s="35" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C99" s="36" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B100" s="35" t="s">
         <v>2758</v>
       </c>
-      <c r="D98" s="36" t="s">
+      <c r="C100" s="36" t="s">
         <v>2759</v>
+      </c>
+      <c r="D100" s="36" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B101" s="35" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C101" s="36" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D101" s="36" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B102" s="35" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C102" s="36" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D102" s="36" t="s">
+        <v>2769</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B103" s="35" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C103" s="36" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D103" s="36" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B104" s="35" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C104" s="36" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D104" s="36" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B105" s="35" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C105" s="36" t="s">
+        <v>2776</v>
+      </c>
+      <c r="D105" s="36" t="s">
+        <v>2760</v>
       </c>
     </row>
   </sheetData>
@@ -30113,387 +30300,387 @@
   <sheetData>
     <row r="1" spans="2:4" s="48" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="46" t="s">
-        <v>2175</v>
+        <v>2171</v>
       </c>
       <c r="C1" s="47" t="s">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D1" s="47" t="s">
-        <v>2020</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
-        <v>2126</v>
+        <v>2122</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="31" t="s">
-        <v>2127</v>
+        <v>2123</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" s="31" t="s">
-        <v>2128</v>
+        <v>2124</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="31" t="s">
-        <v>2129</v>
+        <v>2125</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" s="31" t="s">
-        <v>2130</v>
+        <v>2126</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="31" t="s">
-        <v>2131</v>
+        <v>2127</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="31" t="s">
-        <v>2134</v>
+        <v>2130</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="31" t="s">
-        <v>2135</v>
+        <v>2131</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B10" s="31" t="s">
-        <v>2132</v>
+        <v>2128</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="31" t="s">
-        <v>2133</v>
+        <v>2129</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B12" s="31" t="s">
-        <v>2136</v>
+        <v>2132</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
-        <v>2137</v>
+        <v>2133</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="31" t="s">
-        <v>2138</v>
+        <v>2134</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="31" t="s">
-        <v>2139</v>
+        <v>2135</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="31" t="s">
-        <v>2140</v>
+        <v>2136</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="31" t="s">
-        <v>2141</v>
+        <v>2137</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="31" t="s">
-        <v>2142</v>
+        <v>2138</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="31" t="s">
-        <v>2143</v>
+        <v>2139</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="31" t="s">
-        <v>2144</v>
+        <v>2140</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="31" t="s">
-        <v>2145</v>
+        <v>2141</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="31" t="s">
-        <v>2146</v>
+        <v>2142</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="31" t="s">
-        <v>2193</v>
+        <v>2189</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="31" t="s">
-        <v>2194</v>
+        <v>2190</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="31" t="s">
-        <v>2147</v>
+        <v>2143</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="31" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="31" t="s">
-        <v>2149</v>
+        <v>2145</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="31" t="s">
-        <v>2150</v>
+        <v>2146</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>2076</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="31" t="s">
-        <v>2151</v>
+        <v>2147</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="31" t="s">
-        <v>2152</v>
+        <v>2148</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="31" t="s">
-        <v>2153</v>
+        <v>2149</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="31" t="s">
-        <v>2154</v>
+        <v>2150</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
-        <v>2155</v>
+        <v>2151</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
-        <v>2156</v>
+        <v>2152</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
-        <v>2157</v>
+        <v>2153</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
-        <v>2158</v>
+        <v>2154</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
-        <v>2159</v>
+        <v>2155</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
-        <v>2160</v>
+        <v>2156</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>2553</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
-        <v>2176</v>
+        <v>2172</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
-        <v>2166</v>
+        <v>2162</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
-        <v>2167</v>
+        <v>2163</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
-        <v>2168</v>
+        <v>2164</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.4">
@@ -30501,443 +30688,443 @@
         <v>1160</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
-        <v>2170</v>
+        <v>2166</v>
       </c>
       <c r="C50" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
-        <v>2172</v>
+        <v>2168</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
-        <v>2173</v>
+        <v>2169</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
-        <v>2174</v>
+        <v>2170</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B55" s="31" t="s">
-        <v>2177</v>
+        <v>2173</v>
       </c>
       <c r="C55" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
-        <v>2178</v>
+        <v>2174</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="C57" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
-        <v>2180</v>
+        <v>2176</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
-        <v>2181</v>
+        <v>2177</v>
       </c>
       <c r="C59" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
-        <v>2182</v>
+        <v>2178</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
-        <v>2183</v>
+        <v>2179</v>
       </c>
       <c r="C61" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
-        <v>2184</v>
+        <v>2180</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
-        <v>2185</v>
+        <v>2181</v>
       </c>
       <c r="C63" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
-        <v>2186</v>
+        <v>2182</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B65" s="31" t="s">
-        <v>2187</v>
+        <v>2183</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B66" s="31" t="s">
-        <v>2188</v>
+        <v>2184</v>
       </c>
       <c r="C66" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B67" s="31" t="s">
-        <v>2189</v>
+        <v>2185</v>
       </c>
       <c r="C67" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B68" s="31" t="s">
-        <v>2190</v>
+        <v>2186</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B69" s="31" t="s">
-        <v>2191</v>
+        <v>2187</v>
       </c>
       <c r="C69" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B70" s="31" t="s">
-        <v>2192</v>
+        <v>2188</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B71" s="31" t="s">
-        <v>2195</v>
+        <v>2191</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="31" t="s">
-        <v>2196</v>
+        <v>2192</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B73" s="31" t="s">
-        <v>2197</v>
+        <v>2193</v>
       </c>
       <c r="C73" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B74" s="31" t="s">
-        <v>2198</v>
+        <v>2194</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
-        <v>2199</v>
+        <v>2195</v>
       </c>
       <c r="C75" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
-        <v>2200</v>
+        <v>2196</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="31" t="s">
-        <v>2201</v>
+        <v>2197</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="31" t="s">
-        <v>2202</v>
+        <v>2198</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B79" s="31" t="s">
-        <v>2203</v>
+        <v>2199</v>
       </c>
       <c r="C79" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B80" s="31" t="s">
-        <v>2204</v>
+        <v>2200</v>
       </c>
       <c r="C80" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B81" s="31" t="s">
-        <v>2205</v>
+        <v>2201</v>
       </c>
       <c r="C81" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B82" s="31" t="s">
-        <v>2206</v>
+        <v>2202</v>
       </c>
       <c r="C82" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B83" s="31" t="s">
-        <v>2207</v>
+        <v>2203</v>
       </c>
       <c r="C83" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B84" s="31" t="s">
-        <v>2208</v>
+        <v>2204</v>
       </c>
       <c r="C84" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B85" s="31" t="s">
-        <v>2209</v>
+        <v>2205</v>
       </c>
       <c r="C85" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B86" s="31" t="s">
-        <v>2210</v>
+        <v>2206</v>
       </c>
       <c r="C86" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B87" s="31" t="s">
-        <v>2211</v>
+        <v>2207</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B88" s="31" t="s">
-        <v>2212</v>
+        <v>2208</v>
       </c>
       <c r="C88" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B89" s="31" t="s">
-        <v>2213</v>
+        <v>2209</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B90" s="31" t="s">
-        <v>2214</v>
+        <v>2210</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B91" s="31" t="s">
-        <v>2243</v>
+        <v>2239</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>2244</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B92" s="31" t="s">
-        <v>2245</v>
+        <v>2241</v>
       </c>
       <c r="C92" s="34" t="s">
-        <v>2077</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B93" s="31" t="s">
-        <v>2435</v>
+        <v>2431</v>
       </c>
       <c r="C93" s="34" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="D93" s="34" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2246</v>
+        <v>2242</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="D94" s="34" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B95" s="31" t="s">
-        <v>2247</v>
+        <v>2243</v>
       </c>
       <c r="C95" s="34" t="s">
-        <v>2249</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B96" s="31" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2249</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>2249</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2250</v>
+        <v>2246</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="31" t="s">
-        <v>2251</v>
+        <v>2247</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="31" t="s">
-        <v>2252</v>
+        <v>2248</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="31" t="s">
-        <v>2253</v>
+        <v>2249</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
@@ -30945,1622 +31132,1622 @@
         <v>949</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>2254</v>
+        <v>2250</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="31" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C104" s="34" t="s">
         <v>2255</v>
-      </c>
-      <c r="C104" s="34" t="s">
-        <v>2259</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B105" s="31" t="s">
-        <v>2256</v>
+        <v>2252</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="31" t="s">
-        <v>2257</v>
+        <v>2253</v>
       </c>
       <c r="C106" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="31" t="s">
-        <v>2258</v>
+        <v>2254</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
-        <v>2265</v>
+        <v>2261</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2261</v>
+        <v>2257</v>
       </c>
       <c r="C109" s="34" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="31" t="s">
-        <v>2262</v>
+        <v>2258</v>
       </c>
       <c r="C110" s="34" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="31" t="s">
-        <v>2263</v>
+        <v>2259</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="31" t="s">
-        <v>2264</v>
+        <v>2260</v>
       </c>
       <c r="C112" s="34" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2266</v>
+        <v>2262</v>
       </c>
       <c r="C113" s="34" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="31" t="s">
-        <v>2267</v>
+        <v>2263</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="31" t="s">
-        <v>2268</v>
+        <v>2264</v>
       </c>
       <c r="C115" s="34" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="31" t="s">
-        <v>2269</v>
+        <v>2265</v>
       </c>
       <c r="C116" s="34" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="31" t="s">
-        <v>2270</v>
+        <v>2266</v>
       </c>
       <c r="C117" s="34" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="31" t="s">
-        <v>2271</v>
+        <v>2267</v>
       </c>
       <c r="C118" s="34" t="s">
-        <v>2078</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="31" t="s">
-        <v>2272</v>
+        <v>2268</v>
       </c>
       <c r="C119" s="34" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="31" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
       <c r="C120" s="34" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="31" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="31" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
-        <v>2277</v>
+        <v>2273</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="31" t="s">
-        <v>2278</v>
+        <v>2274</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2276</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="31" t="s">
-        <v>2279</v>
+        <v>2275</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="31" t="s">
-        <v>2280</v>
+        <v>2276</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="31" t="s">
-        <v>2281</v>
+        <v>2277</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="31" t="s">
-        <v>2282</v>
+        <v>2278</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B129" s="31" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C129" s="34" t="s">
         <v>2283</v>
-      </c>
-      <c r="C129" s="34" t="s">
-        <v>2287</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B130" s="31" t="s">
-        <v>2284</v>
+        <v>2280</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B131" s="31" t="s">
-        <v>2285</v>
+        <v>2281</v>
       </c>
       <c r="C131" s="34" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
       <c r="D131" s="34" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B132" s="31" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2287</v>
+        <v>2283</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
-        <v>2288</v>
+        <v>2284</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B134" s="31" t="s">
-        <v>2289</v>
+        <v>2285</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B135" s="31" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C135" s="34" t="s">
         <v>2290</v>
-      </c>
-      <c r="C135" s="34" t="s">
-        <v>2294</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B136" s="31" t="s">
-        <v>2291</v>
+        <v>2287</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B137" s="31" t="s">
-        <v>2292</v>
+        <v>2288</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B138" s="31" t="s">
-        <v>2293</v>
+        <v>2289</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2295</v>
+        <v>2291</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B140" s="31" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C140" s="34" t="s">
         <v>2296</v>
-      </c>
-      <c r="C140" s="34" t="s">
-        <v>2300</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B141" s="31" t="s">
-        <v>2297</v>
+        <v>2293</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B142" s="31" t="s">
-        <v>2298</v>
+        <v>2294</v>
       </c>
       <c r="C142" s="34" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B143" s="31" t="s">
-        <v>2299</v>
+        <v>2295</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2300</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2301</v>
+        <v>2297</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>2304</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B145" s="31" t="s">
-        <v>2302</v>
+        <v>2298</v>
       </c>
       <c r="C145" s="34" t="s">
-        <v>2304</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B146" s="31" t="s">
-        <v>2303</v>
+        <v>2299</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2304</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2305</v>
+        <v>2301</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B148" s="31" t="s">
-        <v>2306</v>
+        <v>2302</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B149" s="31" t="s">
-        <v>2307</v>
+        <v>2303</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B150" s="31" t="s">
-        <v>2308</v>
+        <v>2304</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B151" s="31" t="s">
-        <v>2309</v>
+        <v>2305</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B152" s="31" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C152" s="34" t="s">
         <v>2310</v>
-      </c>
-      <c r="C152" s="34" t="s">
-        <v>2314</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B153" s="31" t="s">
-        <v>2311</v>
+        <v>2307</v>
       </c>
       <c r="C153" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B154" s="31" t="s">
-        <v>2312</v>
+        <v>2308</v>
       </c>
       <c r="C154" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B155" s="31" t="s">
-        <v>2313</v>
+        <v>2309</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C156" s="34" t="s">
         <v>2315</v>
-      </c>
-      <c r="C156" s="34" t="s">
-        <v>2319</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B157" s="31" t="s">
-        <v>2316</v>
+        <v>2312</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>2319</v>
+        <v>2315</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B158" s="31" t="s">
-        <v>2317</v>
+        <v>2313</v>
       </c>
       <c r="C158" s="34" t="s">
-        <v>2319</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B159" s="31" t="s">
-        <v>2318</v>
+        <v>2314</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2319</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2324</v>
+        <v>2320</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
-        <v>2325</v>
+        <v>2321</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
-        <v>2327</v>
+        <v>2323</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C164" s="34" t="s">
         <v>2328</v>
-      </c>
-      <c r="C164" s="34" t="s">
-        <v>2332</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
-        <v>2329</v>
+        <v>2325</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
-        <v>2330</v>
+        <v>2326</v>
       </c>
       <c r="C166" s="34" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
-        <v>2331</v>
+        <v>2327</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2332</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B168" s="31" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
-        <v>2336</v>
+        <v>2332</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C170" s="34" t="s">
         <v>2333</v>
-      </c>
-      <c r="C170" s="34" t="s">
-        <v>2337</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
-        <v>2334</v>
+        <v>2330</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>2337</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B172" s="31" t="s">
-        <v>2338</v>
+        <v>2334</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C173" s="34" t="s">
         <v>2339</v>
       </c>
-      <c r="C173" s="34" t="s">
-        <v>2343</v>
-      </c>
       <c r="D173" s="34" t="s">
-        <v>2561</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
-        <v>2340</v>
+        <v>2336</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="C175" s="34" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2343</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2344</v>
+        <v>2340</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2345</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2471</v>
+        <v>2466</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
-        <v>2348</v>
+        <v>2344</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B182" s="31" t="s">
-        <v>2349</v>
+        <v>2345</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B183" s="31" t="s">
-        <v>2350</v>
+        <v>2346</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2347</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B184" s="31" t="s">
-        <v>2351</v>
+        <v>2347</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>2354</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B185" s="31" t="s">
-        <v>2352</v>
+        <v>2348</v>
       </c>
       <c r="C185" s="34" t="s">
-        <v>2354</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B186" s="31" t="s">
-        <v>2353</v>
+        <v>2349</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2354</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C187" s="34" t="s">
         <v>2355</v>
-      </c>
-      <c r="C187" s="34" t="s">
-        <v>2359</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B188" s="31" t="s">
-        <v>2356</v>
+        <v>2352</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B189" s="31" t="s">
-        <v>2357</v>
+        <v>2353</v>
       </c>
       <c r="C189" s="34" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B190" s="31" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2360</v>
+        <v>2356</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B192" s="31" t="s">
-        <v>2361</v>
+        <v>2357</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B193" s="31" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C195" s="34" t="s">
         <v>2364</v>
-      </c>
-      <c r="C195" s="34" t="s">
-        <v>2368</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B196" s="31" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B197" s="31" t="s">
-        <v>2366</v>
+        <v>2362</v>
       </c>
       <c r="C197" s="34" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B198" s="31" t="s">
-        <v>2367</v>
+        <v>2363</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2369</v>
+        <v>2365</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B200" s="31" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C200" s="34" t="s">
         <v>2370</v>
-      </c>
-      <c r="C200" s="34" t="s">
-        <v>2374</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B201" s="31" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B202" s="31" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
       <c r="C202" s="34" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B203" s="31" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2376</v>
+        <v>2372</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
-        <v>2375</v>
+        <v>2371</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C206" s="34" t="s">
         <v>2377</v>
-      </c>
-      <c r="C206" s="34" t="s">
-        <v>2381</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B207" s="31" t="s">
-        <v>2378</v>
+        <v>2374</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B208" s="31" t="s">
-        <v>2379</v>
+        <v>2375</v>
       </c>
       <c r="C208" s="34" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B209" s="31" t="s">
-        <v>2380</v>
+        <v>2376</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C210" s="34" t="s">
         <v>2382</v>
-      </c>
-      <c r="C210" s="34" t="s">
-        <v>2386</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B211" s="31" t="s">
-        <v>2383</v>
+        <v>2379</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B212" s="31" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="C212" s="34" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B213" s="31" t="s">
-        <v>2385</v>
+        <v>2381</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2387</v>
+        <v>2383</v>
       </c>
       <c r="C214" s="34" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B215" s="31" t="s">
-        <v>2388</v>
+        <v>2384</v>
       </c>
       <c r="C215" s="34" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B216" s="31" t="s">
-        <v>2389</v>
+        <v>2385</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2398</v>
+        <v>2394</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2401</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B218" s="31" t="s">
-        <v>2402</v>
+        <v>2398</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2401</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
-        <v>2399</v>
+        <v>2395</v>
       </c>
       <c r="C219" s="34" t="s">
-        <v>2401</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B220" s="31" t="s">
-        <v>2400</v>
+        <v>2396</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2401</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
-        <v>2403</v>
+        <v>2399</v>
       </c>
       <c r="C221" s="34" t="s">
-        <v>2404</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2405</v>
+        <v>2401</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2406</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2407</v>
+        <v>2403</v>
       </c>
       <c r="C223" s="42" t="s">
-        <v>2445</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
-        <v>2587</v>
+        <v>2581</v>
       </c>
       <c r="C224" s="34" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="225" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B225" s="31" t="s">
-        <v>2584</v>
+        <v>2578</v>
       </c>
       <c r="C225" s="34" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="226" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B226" s="31" t="s">
-        <v>2577</v>
+        <v>2571</v>
       </c>
       <c r="C226" s="34" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
       <c r="D226" s="34" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="227" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B227" s="31" t="s">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="C227" s="34" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="228" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B228" s="31" t="s">
-        <v>2586</v>
+        <v>2580</v>
       </c>
       <c r="C228" s="34" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="229" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B229" s="31" t="s">
-        <v>2408</v>
+        <v>2404</v>
       </c>
       <c r="C229" s="34" t="s">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="230" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B230" s="31" t="s">
-        <v>2409</v>
+        <v>2405</v>
       </c>
       <c r="C230" s="34" t="s">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="231" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B231" s="31" t="s">
-        <v>2410</v>
+        <v>2406</v>
       </c>
       <c r="C231" s="34" t="s">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="232" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B232" s="31" t="s">
-        <v>2330</v>
+        <v>2326</v>
       </c>
       <c r="C232" s="34" t="s">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="233" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B233" s="31" t="s">
-        <v>2412</v>
+        <v>2408</v>
       </c>
       <c r="C233" s="34" t="s">
-        <v>2415</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="234" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B234" s="31" t="s">
-        <v>2413</v>
+        <v>2409</v>
       </c>
       <c r="C234" s="34" t="s">
-        <v>2415</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="235" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B235" s="31" t="s">
-        <v>2414</v>
+        <v>2410</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>2415</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="236" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B236" s="31" t="s">
-        <v>2416</v>
+        <v>2412</v>
       </c>
       <c r="C236" s="34" t="s">
-        <v>2421</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="237" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B237" s="31" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C237" s="34" t="s">
         <v>2417</v>
-      </c>
-      <c r="C237" s="34" t="s">
-        <v>2421</v>
       </c>
     </row>
     <row r="238" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B238" s="31" t="s">
-        <v>2418</v>
+        <v>2414</v>
       </c>
       <c r="C238" s="34" t="s">
-        <v>2421</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="239" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B239" s="31" t="s">
-        <v>2419</v>
+        <v>2415</v>
       </c>
       <c r="C239" s="34" t="s">
-        <v>2421</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="240" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B240" s="31" t="s">
-        <v>2420</v>
+        <v>2416</v>
       </c>
       <c r="C240" s="34" t="s">
-        <v>2421</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B241" s="31" t="s">
-        <v>2422</v>
+        <v>2418</v>
       </c>
       <c r="C241" s="34" t="s">
-        <v>2423</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B242" s="31" t="s">
-        <v>2424</v>
+        <v>2420</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2425</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B243" s="31" t="s">
-        <v>2426</v>
+        <v>2422</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2427</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2428</v>
+        <v>2424</v>
       </c>
       <c r="C244" s="34" t="s">
-        <v>2433</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C245" s="34" t="s">
         <v>2429</v>
-      </c>
-      <c r="C245" s="34" t="s">
-        <v>2433</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B246" s="31" t="s">
-        <v>2430</v>
+        <v>2426</v>
       </c>
       <c r="C246" s="34" t="s">
-        <v>2433</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
-        <v>2431</v>
+        <v>2427</v>
       </c>
       <c r="C247" s="34" t="s">
-        <v>2433</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2432</v>
+        <v>2428</v>
       </c>
       <c r="C248" s="34" t="s">
-        <v>2433</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
       <c r="C249" s="32" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2526</v>
+        <v>2520</v>
       </c>
       <c r="C250" s="32" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2527</v>
+        <v>2521</v>
       </c>
       <c r="C251" s="32" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2436</v>
+        <v>2432</v>
       </c>
       <c r="C252" s="32" t="s">
-        <v>2528</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2446</v>
+        <v>2441</v>
       </c>
       <c r="C253" s="34" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2447</v>
+        <v>2442</v>
       </c>
       <c r="C254" s="34" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2448</v>
+        <v>2443</v>
       </c>
       <c r="C255" s="34" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2449</v>
+        <v>2444</v>
       </c>
       <c r="C256" s="34" t="s">
-        <v>2081</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2451</v>
+        <v>2446</v>
       </c>
       <c r="C257" s="34" t="s">
-        <v>2080</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
-        <v>2452</v>
+        <v>2447</v>
       </c>
       <c r="C258" s="32" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
-        <v>2453</v>
+        <v>2448</v>
       </c>
       <c r="C259" s="32" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2454</v>
+        <v>2449</v>
       </c>
       <c r="C260" s="32" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
-        <v>2455</v>
+        <v>2450</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
-        <v>2456</v>
+        <v>2451</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C263" s="34" t="s">
         <v>2457</v>
-      </c>
-      <c r="C263" s="34" t="s">
-        <v>2462</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2458</v>
+        <v>2453</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
-        <v>2459</v>
+        <v>2454</v>
       </c>
       <c r="C265" s="34" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2460</v>
+        <v>2455</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2461</v>
+        <v>2456</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
-        <v>2305</v>
+        <v>2301</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2463</v>
+        <v>2458</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2464</v>
+        <v>2459</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
-        <v>2465</v>
+        <v>2460</v>
       </c>
       <c r="C271" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2466</v>
+        <v>2461</v>
       </c>
       <c r="C272" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C273" s="34" t="s">
         <v>2467</v>
-      </c>
-      <c r="C273" s="34" t="s">
-        <v>2472</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2214</v>
+        <v>2210</v>
       </c>
       <c r="C274" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2468</v>
+        <v>2463</v>
       </c>
       <c r="C275" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
-        <v>2469</v>
+        <v>2464</v>
       </c>
       <c r="C276" s="34" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2473</v>
+        <v>2468</v>
       </c>
       <c r="C277" s="32" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2178</v>
+        <v>2174</v>
       </c>
       <c r="C278" s="32" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2474</v>
+        <v>2469</v>
       </c>
       <c r="C279" s="32" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="280" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B280" s="31" t="s">
-        <v>2475</v>
+        <v>2470</v>
       </c>
       <c r="C280" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="281" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B281" s="31" t="s">
-        <v>2476</v>
+        <v>2471</v>
       </c>
       <c r="C281" s="34" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="282" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B282" s="31" t="s">
-        <v>2478</v>
+        <v>2473</v>
       </c>
       <c r="C282" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="283" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B283" s="31" t="s">
-        <v>2479</v>
+        <v>2474</v>
       </c>
       <c r="C283" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="284" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B284" s="31" t="s">
-        <v>2480</v>
+        <v>2475</v>
       </c>
       <c r="C284" s="32" t="s">
-        <v>2074</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="285" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B285" s="31" t="s">
-        <v>2481</v>
+        <v>2476</v>
       </c>
       <c r="C285" s="34" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="286" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B286" s="31" t="s">
-        <v>2482</v>
+        <v>2477</v>
       </c>
       <c r="C286" s="34" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="287" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B287" s="31" t="s">
-        <v>2562</v>
+        <v>2556</v>
       </c>
       <c r="C287" s="34" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="288" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B288" s="31" t="s">
-        <v>2563</v>
+        <v>2557</v>
       </c>
       <c r="C288" s="34" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="289" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B289" s="31" t="s">
-        <v>2564</v>
+        <v>2558</v>
       </c>
       <c r="C289" s="34" t="s">
-        <v>2546</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="290" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B290" s="31" t="s">
-        <v>2565</v>
+        <v>2559</v>
       </c>
       <c r="C290" s="32" t="s">
-        <v>2553</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="291" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B291" s="31" t="s">
-        <v>2566</v>
+        <v>2560</v>
       </c>
       <c r="C291" s="34" t="s">
-        <v>2567</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="292" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B292" s="31" t="s">
-        <v>2568</v>
+        <v>2562</v>
       </c>
       <c r="C292" s="34" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="293" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B293" s="31" t="s">
-        <v>2569</v>
+        <v>2563</v>
       </c>
       <c r="C293" s="34" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="294" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B294" s="31" t="s">
-        <v>2178</v>
+        <v>2174</v>
       </c>
       <c r="C294" s="34" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="295" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B295" s="31" t="s">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="C295" s="34" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="296" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B296" s="31" t="s">
-        <v>2570</v>
+        <v>2564</v>
       </c>
       <c r="C296" s="34" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="297" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B297" s="31" t="s">
-        <v>2571</v>
+        <v>2565</v>
       </c>
       <c r="C297" s="34" t="s">
-        <v>2572</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="298" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B298" s="31" t="s">
-        <v>2315</v>
+        <v>2311</v>
       </c>
       <c r="C298" s="34" t="s">
-        <v>2560</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="299" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B299" s="31" t="s">
-        <v>2573</v>
+        <v>2567</v>
       </c>
       <c r="C299" s="34" t="s">
-        <v>2560</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="300" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B300" s="31" t="s">
-        <v>2574</v>
+        <v>2568</v>
       </c>
       <c r="C300" s="34" t="s">
-        <v>2560</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="301" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B301" s="31" t="s">
-        <v>2576</v>
+        <v>2570</v>
       </c>
       <c r="C301" s="32" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="302" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B302" s="31" t="s">
-        <v>2731</v>
+        <v>2725</v>
       </c>
       <c r="C302" s="34" t="s">
-        <v>2713</v>
+        <v>2707</v>
       </c>
     </row>
   </sheetData>
@@ -32739,10 +32926,10 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>2603</v>
+        <v>2597</v>
       </c>
       <c r="C2" t="s">
-        <v>2604</v>
+        <v>2598</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2283" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD3017C9-44FC-4B59-B3ED-CB50A8A4E304}"/>
+  <xr:revisionPtr revIDLastSave="2326" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CE8E6DA-40A8-4906-993D-3BAE3253EFFC}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="16770" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="2779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="2792">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -8179,13 +8179,6 @@
     <t>ほーむ</t>
   </si>
   <si>
-    <t>噴水</t>
-    <rPh sb="0" eb="2">
-      <t>フンスイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>いべんとのお知らせ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -8297,25 +8290,6 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>噴水 ・水覗象/王</t>
-    <rPh sb="0" eb="2">
-      <t>フンスイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ゾウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>オウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -10542,10 +10516,6 @@
     <rPh sb="1" eb="2">
       <t>カベ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>傎にあった</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -10946,10 +10916,6 @@
   </si>
   <si>
     <t>[俚]?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>[介]?</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -11005,10 +10971,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>[傎]?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -12747,9 +12709,116 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>罪を受けて遠い土地へ流された人や、左遷された人</t>
+  </si>
+  <si>
     <t>遷客</t>
+  </si>
+  <si>
+    <t>遷化</t>
+    <rPh sb="1" eb="2">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unicode</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高僧の死亡を、婉曲的に、かつ、敬っていう語</t>
+  </si>
+  <si>
+    <t>過○のお知らせ</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なさげ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遷客 ・遷化(unicode)</t>
     <rPh sb="1" eb="2">
       <t>キャク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センゲ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三丢侕</t>
+  </si>
+  <si>
+    <t>のれん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥?</t>
+    <rPh sb="0" eb="1">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奥にあった</t>
+    <rPh sb="0" eb="1">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おぼろ区</t>
+    <rPh sb="3" eb="4">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過状？（過失や過ちの記録）</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桶?</t>
+    <rPh sb="0" eb="1">
+      <t>オケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俚介</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俚介 ・介覗象/王</t>
+    <rPh sb="5" eb="6">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -13415,6 +13484,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -14409,7 +14482,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B81" s="1" t="s">
-        <v>2766</v>
+        <v>2761</v>
       </c>
       <c r="C81" t="s">
         <v>1577</v>
@@ -14745,7 +14818,7 @@
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="1" t="s">
-        <v>2762</v>
+        <v>2757</v>
       </c>
       <c r="C123" t="s">
         <v>1630</v>
@@ -14777,7 +14850,7 @@
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="1" t="s">
-        <v>2750</v>
+        <v>2745</v>
       </c>
       <c r="C127" t="s">
         <v>1636</v>
@@ -14841,16 +14914,16 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B135" s="1" t="s">
-        <v>2708</v>
+        <v>2703</v>
       </c>
       <c r="C135" s="55" t="s">
-        <v>2717</v>
+        <v>2712</v>
       </c>
       <c r="D135" s="33" t="s">
-        <v>2718</v>
+        <v>2713</v>
       </c>
       <c r="E135" s="34" t="s">
-        <v>2719</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.4">
@@ -15007,7 +15080,7 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B155" s="1" t="s">
-        <v>2763</v>
+        <v>2758</v>
       </c>
       <c r="C155" t="s">
         <v>1433</v>
@@ -15036,12 +15109,6 @@
       <c r="C158" t="s">
         <v>1681</v>
       </c>
-      <c r="F158" s="34" t="s">
-        <v>2094</v>
-      </c>
-      <c r="G158" s="34" t="s">
-        <v>2064</v>
-      </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B159" s="1" t="s">
@@ -15056,6 +15123,12 @@
       <c r="E159" s="34" t="s">
         <v>2065</v>
       </c>
+      <c r="F159" s="34" t="s">
+        <v>2094</v>
+      </c>
+      <c r="G159" s="34" t="s">
+        <v>2064</v>
+      </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B160" s="1" t="s">
@@ -15092,10 +15165,7 @@
         <v>2063</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>2488</v>
-      </c>
-      <c r="F163" s="32" t="s">
-        <v>2547</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.4">
@@ -15103,13 +15173,16 @@
         <v>1689</v>
       </c>
       <c r="C164" t="s">
-        <v>2584</v>
+        <v>2579</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="E164" s="34" t="s">
         <v>2067</v>
+      </c>
+      <c r="F164" s="32" t="s">
+        <v>2542</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.4">
@@ -15231,9 +15304,6 @@
       <c r="C179" t="s">
         <v>1711</v>
       </c>
-      <c r="F179" s="32" t="s">
-        <v>2092</v>
-      </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B180" s="1" t="s">
@@ -15251,9 +15321,6 @@
       <c r="F180" s="32" t="s">
         <v>2092</v>
       </c>
-      <c r="G180" s="34" t="s">
-        <v>2707</v>
-      </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B181" s="1" t="s">
@@ -15263,10 +15330,16 @@
         <v>757</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="E181" s="34" t="s">
         <v>2094</v>
+      </c>
+      <c r="F181" s="32" t="s">
+        <v>2092</v>
+      </c>
+      <c r="G181" s="34" t="s">
+        <v>2702</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.4">
@@ -15284,28 +15357,22 @@
       <c r="C183" t="s">
         <v>1717</v>
       </c>
-      <c r="F183" s="34" t="s">
-        <v>2086</v>
-      </c>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B184" s="1" t="s">
         <v>1917</v>
       </c>
       <c r="C184" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="E184" s="34" t="s">
         <v>2094</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2084</v>
-      </c>
-      <c r="G184" s="34" t="s">
-        <v>2472</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
@@ -15316,10 +15383,16 @@
         <v>1718</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="E185" s="34" t="s">
         <v>2094</v>
+      </c>
+      <c r="F185" s="34" t="s">
+        <v>2084</v>
+      </c>
+      <c r="G185" s="34" t="s">
+        <v>2469</v>
       </c>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.4">
@@ -15394,18 +15467,6 @@
       <c r="E193" s="34" t="s">
         <v>2069</v>
       </c>
-      <c r="F193" s="32" t="s">
-        <v>2090</v>
-      </c>
-      <c r="G193" s="32" t="s">
-        <v>2091</v>
-      </c>
-      <c r="H193" s="32" t="s">
-        <v>2549</v>
-      </c>
-      <c r="I193" s="34" t="s">
-        <v>2069</v>
-      </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B194" s="1" t="s">
@@ -15415,7 +15476,7 @@
         <v>1966</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>2569</v>
+        <v>2564</v>
       </c>
       <c r="E194" s="34" t="s">
         <v>2094</v>
@@ -15425,6 +15486,12 @@
       </c>
       <c r="G194" s="32" t="s">
         <v>2091</v>
+      </c>
+      <c r="H194" s="32" t="s">
+        <v>2544</v>
+      </c>
+      <c r="I194" s="34" t="s">
+        <v>2069</v>
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.4">
@@ -15440,6 +15507,12 @@
       <c r="E195" s="34" t="s">
         <v>2094</v>
       </c>
+      <c r="F195" s="32" t="s">
+        <v>2090</v>
+      </c>
+      <c r="G195" s="32" t="s">
+        <v>2091</v>
+      </c>
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B196" s="1" t="s">
@@ -15462,22 +15535,22 @@
       <c r="C197" t="s">
         <v>1738</v>
       </c>
-      <c r="F197" s="34" t="s">
-        <v>2096</v>
-      </c>
     </row>
     <row r="198" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B198" s="1" t="s">
         <v>1921</v>
       </c>
       <c r="C198" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="E198" s="34" t="s">
         <v>2088</v>
+      </c>
+      <c r="F198" s="34" t="s">
+        <v>2095</v>
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.4">
@@ -15485,10 +15558,7 @@
         <v>1739</v>
       </c>
       <c r="C199" t="s">
-        <v>2118</v>
-      </c>
-      <c r="F199" s="32" t="s">
-        <v>2089</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.4">
@@ -15504,6 +15574,9 @@
       <c r="E200" s="34" t="s">
         <v>2087</v>
       </c>
+      <c r="F200" s="32" t="s">
+        <v>2089</v>
+      </c>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B201" s="1" t="s">
@@ -15544,12 +15617,6 @@
       <c r="C205" t="s">
         <v>1749</v>
       </c>
-      <c r="F205" s="34" t="s">
-        <v>2094</v>
-      </c>
-      <c r="G205" s="34" t="s">
-        <v>2064</v>
-      </c>
     </row>
     <row r="206" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B206" s="1" t="s">
@@ -15564,6 +15631,12 @@
       <c r="E206" s="34" t="s">
         <v>2071</v>
       </c>
+      <c r="F206" s="34" t="s">
+        <v>2094</v>
+      </c>
+      <c r="G206" s="34" t="s">
+        <v>2064</v>
+      </c>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B207" s="1" t="s">
@@ -15618,9 +15691,6 @@
       <c r="C212" t="s">
         <v>1758</v>
       </c>
-      <c r="F212" s="34" t="s">
-        <v>2064</v>
-      </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B213" s="1" t="s">
@@ -15630,10 +15700,13 @@
         <v>1760</v>
       </c>
       <c r="D213" s="33" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="E213" s="34" t="s">
         <v>2068</v>
+      </c>
+      <c r="F213" s="34" t="s">
+        <v>2064</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.4">
@@ -15659,22 +15732,22 @@
       <c r="C216" t="s">
         <v>1978</v>
       </c>
-      <c r="F216" s="32" t="s">
-        <v>2540</v>
-      </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B217" s="1" t="s">
         <v>1076</v>
       </c>
       <c r="C217" t="s">
-        <v>2589</v>
+        <v>2584</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="E217" s="34" t="s">
         <v>2093</v>
+      </c>
+      <c r="F217" s="32" t="s">
+        <v>2535</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.4">
@@ -15808,22 +15881,22 @@
       <c r="E232" s="34" t="s">
         <v>2078</v>
       </c>
-      <c r="F232" s="32" t="s">
-        <v>2554</v>
-      </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B233" s="1" t="s">
         <v>1931</v>
       </c>
       <c r="C233" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="D233" s="33" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="E233" s="34" t="s">
         <v>2080</v>
+      </c>
+      <c r="F233" s="32" t="s">
+        <v>2549</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.4">
@@ -15866,7 +15939,7 @@
         <v>1794</v>
       </c>
       <c r="D238" s="33" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="E238" s="34" t="s">
         <v>2066</v>
@@ -15915,9 +15988,6 @@
       <c r="E242" s="34" t="s">
         <v>2081</v>
       </c>
-      <c r="F242" s="34" t="s">
-        <v>2088</v>
-      </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B243" s="1" t="s">
@@ -15932,6 +16002,9 @@
       <c r="E243" s="34" t="s">
         <v>2082</v>
       </c>
+      <c r="F243" s="34" t="s">
+        <v>2088</v>
+      </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B244" s="1" t="s">
@@ -16012,22 +16085,22 @@
       <c r="E250" s="34" t="s">
         <v>2084</v>
       </c>
-      <c r="F250" s="34" t="s">
-        <v>2707</v>
-      </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B251" s="1" t="s">
         <v>1938</v>
       </c>
       <c r="C251" t="s">
-        <v>2703</v>
+        <v>2698</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>2716</v>
+        <v>2711</v>
       </c>
       <c r="E251" s="34" t="s">
         <v>2084</v>
+      </c>
+      <c r="F251" s="34" t="s">
+        <v>2702</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.4">
@@ -16083,22 +16156,22 @@
       <c r="C257" t="s">
         <v>1821</v>
       </c>
-      <c r="F257" s="32" t="s">
-        <v>2549</v>
-      </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B258" s="1" t="s">
         <v>1939</v>
       </c>
       <c r="C258" t="s">
-        <v>2551</v>
+        <v>2546</v>
       </c>
       <c r="D258" s="33" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="E258" s="34" t="s">
         <v>2064</v>
+      </c>
+      <c r="F258" s="32" t="s">
+        <v>2544</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.4">
@@ -16108,25 +16181,22 @@
       <c r="C259" t="s">
         <v>1823</v>
       </c>
-      <c r="F259" s="32" t="s">
-        <v>2540</v>
-      </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B260" s="1" t="s">
         <v>1940</v>
       </c>
       <c r="C260" t="s">
-        <v>2576</v>
+        <v>2571</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="E260" s="34" t="s">
         <v>2064</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2522</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
@@ -16137,13 +16207,13 @@
         <v>416</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="E261" s="34" t="s">
         <v>2086</v>
       </c>
       <c r="F261" s="32" t="s">
-        <v>2555</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
@@ -16151,13 +16221,16 @@
         <v>1825</v>
       </c>
       <c r="C262" t="s">
-        <v>2575</v>
+        <v>2570</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>2574</v>
+        <v>2569</v>
       </c>
       <c r="E262" s="34" t="s">
         <v>2086</v>
+      </c>
+      <c r="F262" s="32" t="s">
+        <v>2550</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
@@ -16176,7 +16249,7 @@
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
-        <v>2761</v>
+        <v>2756</v>
       </c>
       <c r="C264" t="s">
         <v>1828</v>
@@ -16184,7 +16257,7 @@
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
-        <v>2757</v>
+        <v>2752</v>
       </c>
       <c r="C265" t="s">
         <v>1829</v>
@@ -16205,9 +16278,6 @@
       <c r="C267" t="s">
         <v>1833</v>
       </c>
-      <c r="F267" s="34" t="s">
-        <v>2707</v>
-      </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B268" s="1" t="s">
@@ -16222,6 +16292,9 @@
       <c r="E268" s="34" t="s">
         <v>2084</v>
       </c>
+      <c r="F268" s="34" t="s">
+        <v>2702</v>
+      </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B269" s="1" t="s">
@@ -16294,9 +16367,6 @@
       <c r="C277" t="s">
         <v>1850</v>
       </c>
-      <c r="F277" s="34" t="s">
-        <v>2566</v>
-      </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B278" s="1" t="s">
@@ -16306,10 +16376,13 @@
         <v>759</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="E278" s="34" t="s">
         <v>2064</v>
+      </c>
+      <c r="F278" s="34" t="s">
+        <v>2561</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.4">
@@ -16323,7 +16396,7 @@
         <v>2026</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>2440</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.4">
@@ -16334,10 +16407,10 @@
         <v>1855</v>
       </c>
       <c r="D280" s="41" t="s">
-        <v>2577</v>
+        <v>2572</v>
       </c>
       <c r="E280" s="42" t="s">
-        <v>2440</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.4">
@@ -16433,9 +16506,6 @@
       <c r="C291" t="s">
         <v>1871</v>
       </c>
-      <c r="F291" s="32" t="s">
-        <v>2445</v>
-      </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B292" s="1" t="s">
@@ -16450,8 +16520,8 @@
       <c r="E292" s="34" t="s">
         <v>2068</v>
       </c>
-      <c r="F292" s="34" t="s">
-        <v>2086</v>
+      <c r="F292" s="32" t="s">
+        <v>2442</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
@@ -16484,6 +16554,9 @@
       <c r="E294" s="34" t="s">
         <v>2064</v>
       </c>
+      <c r="F294" s="34" t="s">
+        <v>2086</v>
+      </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B295" s="1" t="s">
@@ -16501,7 +16574,7 @@
         <v>1951</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
@@ -16512,7 +16585,7 @@
         <v>1952</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.4">
@@ -16522,22 +16595,22 @@
       <c r="C298" t="s">
         <v>1950</v>
       </c>
-      <c r="F298" s="32" t="s">
-        <v>2522</v>
-      </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B299" s="24" t="s">
         <v>1953</v>
       </c>
       <c r="C299" t="s">
-        <v>2675</v>
+        <v>2670</v>
       </c>
       <c r="D299" s="33" t="s">
         <v>2050</v>
       </c>
       <c r="E299" s="32" t="s">
-        <v>2445</v>
+        <v>2442</v>
+      </c>
+      <c r="F299" s="32" t="s">
+        <v>2517</v>
       </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.4">
@@ -16570,7 +16643,7 @@
         <v>1975</v>
       </c>
       <c r="D302" s="33" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.4">
@@ -16634,16 +16707,13 @@
         <v>935</v>
       </c>
       <c r="C307" t="s">
-        <v>2501</v>
+        <v>2496</v>
       </c>
       <c r="D307" s="33" t="s">
-        <v>2478</v>
+        <v>2475</v>
       </c>
       <c r="E307" s="32" t="s">
-        <v>2445</v>
-      </c>
-      <c r="F307" s="32" t="s">
-        <v>2085</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.4">
@@ -16659,6 +16729,9 @@
       <c r="E308" s="34" t="s">
         <v>2073</v>
       </c>
+      <c r="F308" s="32" t="s">
+        <v>2085</v>
+      </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B309" s="27" t="s">
@@ -16721,10 +16794,10 @@
         <v>1994</v>
       </c>
       <c r="C313" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D313" s="33" t="s">
         <v>2119</v>
-      </c>
-      <c r="D313" s="33" t="s">
-        <v>2121</v>
       </c>
       <c r="E313" s="34" t="s">
         <v>2076</v>
@@ -16735,16 +16808,13 @@
         <v>1995</v>
       </c>
       <c r="C314" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="D314" s="33" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="E314" s="34" t="s">
         <v>2076</v>
-      </c>
-      <c r="F314" s="32" t="s">
-        <v>2555</v>
       </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.4">
@@ -16752,16 +16822,16 @@
         <v>1999</v>
       </c>
       <c r="C315" t="s">
-        <v>2585</v>
+        <v>2580</v>
       </c>
       <c r="D315" s="53" t="s">
-        <v>2586</v>
+        <v>2581</v>
       </c>
       <c r="E315" s="34" t="s">
         <v>2077</v>
       </c>
       <c r="F315" s="32" t="s">
-        <v>2522</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.4">
@@ -16777,6 +16847,9 @@
       <c r="E316" s="34" t="s">
         <v>2076</v>
       </c>
+      <c r="F316" s="32" t="s">
+        <v>2517</v>
+      </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B317" s="1" t="s">
@@ -16791,9 +16864,6 @@
       <c r="E317" s="34" t="s">
         <v>2076</v>
       </c>
-      <c r="F317" s="32" t="s">
-        <v>2070</v>
-      </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B318" s="1" t="s">
@@ -16806,7 +16876,10 @@
         <v>2051</v>
       </c>
       <c r="E318" s="34" t="s">
-        <v>2472</v>
+        <v>2469</v>
+      </c>
+      <c r="F318" s="32" t="s">
+        <v>2070</v>
       </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.4">
@@ -16820,10 +16893,7 @@
         <v>2052</v>
       </c>
       <c r="E319" s="34" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F319" s="32" t="s">
-        <v>2070</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.4">
@@ -16837,7 +16907,10 @@
         <v>2054</v>
       </c>
       <c r="E320" s="34" t="s">
-        <v>2472</v>
+        <v>2469</v>
+      </c>
+      <c r="F320" s="32" t="s">
+        <v>2070</v>
       </c>
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.4">
@@ -16848,7 +16921,7 @@
         <v>2010</v>
       </c>
       <c r="D321" s="33" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="E321" s="32" t="s">
         <v>2070</v>
@@ -16865,10 +16938,7 @@
         <v>2053</v>
       </c>
       <c r="E322" s="34" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F322" s="32" t="s">
-        <v>2070</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="323" spans="2:7" x14ac:dyDescent="0.4">
@@ -16876,19 +16946,16 @@
         <v>1093</v>
       </c>
       <c r="C323" t="s">
-        <v>2491</v>
+        <v>2488</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2095</v>
+        <v>2790</v>
       </c>
       <c r="E323" s="34" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
       <c r="F323" s="32" t="s">
         <v>2070</v>
-      </c>
-      <c r="G323" s="32" t="s">
-        <v>2489</v>
       </c>
     </row>
     <row r="324" spans="2:7" x14ac:dyDescent="0.4">
@@ -16896,16 +16963,19 @@
         <v>296</v>
       </c>
       <c r="C324" t="s">
-        <v>2492</v>
+        <v>2789</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2110</v>
+        <v>2791</v>
       </c>
       <c r="E324" s="34" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F324" s="34" t="s">
-        <v>2084</v>
+        <v>2469</v>
+      </c>
+      <c r="F324" s="32" t="s">
+        <v>2070</v>
+      </c>
+      <c r="G324" s="32" t="s">
+        <v>2486</v>
       </c>
     </row>
     <row r="325" spans="2:7" x14ac:dyDescent="0.4">
@@ -16913,10 +16983,10 @@
         <v>1972</v>
       </c>
       <c r="C325" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D325" s="33" t="s">
         <v>2114</v>
-      </c>
-      <c r="D325" s="33" t="s">
-        <v>2116</v>
       </c>
       <c r="E325" s="34" t="s">
         <v>2064</v>
@@ -16930,13 +17000,16 @@
         <v>1973</v>
       </c>
       <c r="C326" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="D326" s="33" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="E326" s="34" t="s">
         <v>2064</v>
+      </c>
+      <c r="F326" s="34" t="s">
+        <v>2084</v>
       </c>
     </row>
     <row r="327" spans="2:7" x14ac:dyDescent="0.4">
@@ -16944,16 +17017,13 @@
         <v>1990</v>
       </c>
       <c r="C327" t="s">
-        <v>2777</v>
+        <v>2772</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2778</v>
+        <v>2782</v>
       </c>
       <c r="E327" s="34" t="s">
         <v>2069</v>
-      </c>
-      <c r="F327" s="32" t="s">
-        <v>2445</v>
       </c>
     </row>
     <row r="328" spans="2:7" x14ac:dyDescent="0.4">
@@ -16961,30 +17031,28 @@
         <v>1971</v>
       </c>
       <c r="C328" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="D328" s="33" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="E328" s="34" t="s">
         <v>2068</v>
       </c>
+      <c r="F328" s="32"/>
     </row>
     <row r="329" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B329" s="1" t="s">
         <v>406</v>
       </c>
       <c r="C329" t="s">
-        <v>2494</v>
+        <v>2490</v>
       </c>
       <c r="D329" s="33" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="E329" s="34" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F329" s="32" t="s">
-        <v>2549</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="330" spans="2:7" x14ac:dyDescent="0.4">
@@ -16992,16 +17060,16 @@
         <v>160</v>
       </c>
       <c r="C330" t="s">
-        <v>2495</v>
+        <v>2491</v>
       </c>
       <c r="D330" s="41" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="E330" s="42" t="s">
-        <v>2440</v>
+        <v>2437</v>
       </c>
       <c r="F330" s="32" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="331" spans="2:7" x14ac:dyDescent="0.4">
@@ -17009,83 +17077,91 @@
         <v>1102</v>
       </c>
       <c r="C331" t="s">
-        <v>2496</v>
+        <v>2785</v>
       </c>
       <c r="D331" s="33" t="s">
-        <v>2439</v>
+        <v>2786</v>
       </c>
       <c r="E331" s="42" t="s">
-        <v>2440</v>
+        <v>2437</v>
+      </c>
+      <c r="F331" s="32" t="s">
+        <v>2544</v>
+      </c>
+      <c r="G331" s="32" t="s">
+        <v>2787</v>
       </c>
     </row>
     <row r="332" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B332" s="1" t="s">
-        <v>2479</v>
+        <v>2476</v>
       </c>
       <c r="C332" t="s">
-        <v>2497</v>
+        <v>2492</v>
       </c>
       <c r="D332" s="43" t="s">
-        <v>2480</v>
+        <v>2477</v>
       </c>
       <c r="E332" s="34" t="s">
-        <v>2481</v>
-      </c>
+        <v>2478</v>
+      </c>
+      <c r="F332" s="32"/>
+      <c r="G332" s="32"/>
     </row>
     <row r="333" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B333" s="1" t="s">
         <v>1146</v>
       </c>
       <c r="C333" t="s">
-        <v>2498</v>
+        <v>2493</v>
       </c>
       <c r="D333" s="33" t="s">
-        <v>2482</v>
+        <v>2479</v>
       </c>
       <c r="E333" s="34" t="s">
-        <v>2482</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="334" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B334" s="1" t="s">
-        <v>2483</v>
+        <v>2480</v>
       </c>
       <c r="C334" t="s">
-        <v>2499</v>
+        <v>2494</v>
       </c>
       <c r="D334" s="33" t="s">
-        <v>2482</v>
+        <v>2479</v>
       </c>
       <c r="E334" s="34" t="s">
-        <v>2482</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="335" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C335" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D335" s="41" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E335" s="34" t="s">
         <v>2484</v>
-      </c>
-      <c r="C335" t="s">
-        <v>2500</v>
-      </c>
-      <c r="D335" s="41" t="s">
-        <v>2486</v>
-      </c>
-      <c r="E335" s="34" t="s">
-        <v>2487</v>
       </c>
     </row>
     <row r="336" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B336" s="1" t="s">
-        <v>2485</v>
+        <v>2482</v>
       </c>
       <c r="C336" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="D336" s="41" t="s">
-        <v>2486</v>
+        <v>2483</v>
       </c>
       <c r="E336" s="34" t="s">
-        <v>2487</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.4">
@@ -17093,27 +17169,27 @@
         <v>1753</v>
       </c>
       <c r="C337" t="s">
-        <v>2541</v>
+        <v>2536</v>
       </c>
       <c r="D337" s="33" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
       <c r="E337" s="34" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B338" s="1" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="C338" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
       <c r="D338" s="33" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
       <c r="E338" s="34" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.4">
@@ -17121,91 +17197,91 @@
         <v>1021</v>
       </c>
       <c r="C339" t="s">
-        <v>2588</v>
+        <v>2583</v>
       </c>
       <c r="D339" s="53" t="s">
-        <v>2587</v>
+        <v>2582</v>
       </c>
       <c r="E339" s="32" t="s">
-        <v>2555</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B340" s="1" t="s">
-        <v>2704</v>
+        <v>2699</v>
       </c>
       <c r="C340" t="s">
-        <v>2705</v>
+        <v>2700</v>
       </c>
       <c r="D340" s="33" t="s">
-        <v>2706</v>
+        <v>2701</v>
       </c>
       <c r="E340" s="34" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B341" s="1" t="s">
-        <v>2709</v>
+        <v>2704</v>
       </c>
       <c r="C341" s="55" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="D341" s="33" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="E341" s="34" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B342" s="1" t="s">
-        <v>2712</v>
+        <v>2707</v>
       </c>
       <c r="C342" s="55" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="D342" s="33" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="E342" s="34" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B343" s="1" t="s">
-        <v>2739</v>
+        <v>2734</v>
       </c>
       <c r="C343" t="s">
-        <v>2740</v>
+        <v>2735</v>
       </c>
       <c r="D343" s="33" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="E343" s="33" t="s">
-        <v>2742</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B344" s="1" t="s">
-        <v>2743</v>
+        <v>2738</v>
       </c>
       <c r="C344" t="s">
-        <v>2744</v>
+        <v>2739</v>
       </c>
       <c r="D344" s="33" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B345" s="1" t="s">
-        <v>2745</v>
+        <v>2740</v>
       </c>
       <c r="C345" t="s">
-        <v>2746</v>
+        <v>2741</v>
       </c>
       <c r="D345" s="33" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.4">
@@ -17246,123 +17322,123 @@
     <hyperlink ref="E233" r:id="rId15" xr:uid="{C8B3A9F6-E20B-4806-986C-21837F397D46}"/>
     <hyperlink ref="E164" r:id="rId16" xr:uid="{4FE6B493-0A62-44D8-B265-E4BE0CF30A01}"/>
     <hyperlink ref="E159" r:id="rId17" xr:uid="{E7F50912-0B82-46DE-BFC1-44F9BF8D5AA1}"/>
-    <hyperlink ref="F179" r:id="rId18" xr:uid="{DB06038A-C39A-4D4D-842D-EFA08F8E8C30}"/>
+    <hyperlink ref="F180" r:id="rId18" xr:uid="{DB06038A-C39A-4D4D-842D-EFA08F8E8C30}"/>
     <hyperlink ref="E310" r:id="rId19" xr:uid="{80642AE9-EB09-43F8-8ED4-4296F935955A}"/>
     <hyperlink ref="E163" r:id="rId20" xr:uid="{AA4E558B-E442-4D3F-A743-A0D4BF133471}"/>
-    <hyperlink ref="F193" r:id="rId21" xr:uid="{D0003710-B87A-4132-8F8C-F03A94DB0D8E}"/>
-    <hyperlink ref="G194" r:id="rId22" xr:uid="{E145CBB8-9029-48BC-9EF6-24A9D6546912}"/>
+    <hyperlink ref="F194" r:id="rId21" xr:uid="{D0003710-B87A-4132-8F8C-F03A94DB0D8E}"/>
+    <hyperlink ref="G195" r:id="rId22" xr:uid="{E145CBB8-9029-48BC-9EF6-24A9D6546912}"/>
     <hyperlink ref="E200" r:id="rId23" xr:uid="{069318CA-733C-4637-8231-71BF8BDE174C}"/>
-    <hyperlink ref="F199" r:id="rId24" xr:uid="{606F5CDB-9747-4F64-AA15-7F28234FF649}"/>
+    <hyperlink ref="F200" r:id="rId24" xr:uid="{606F5CDB-9747-4F64-AA15-7F28234FF649}"/>
     <hyperlink ref="E243" r:id="rId25" xr:uid="{E4A3FF73-4921-408C-8FC8-576088C455C5}"/>
-    <hyperlink ref="F260" r:id="rId26" display="無影言本祭" xr:uid="{FD6022E8-CD2D-453D-B9BD-977A5A45A79A}"/>
-    <hyperlink ref="F307" r:id="rId27" xr:uid="{CB76E612-3F74-438D-AE6C-4556B87A3117}"/>
+    <hyperlink ref="F261" r:id="rId26" display="無影言本祭" xr:uid="{FD6022E8-CD2D-453D-B9BD-977A5A45A79A}"/>
+    <hyperlink ref="F308" r:id="rId27" xr:uid="{CB76E612-3F74-438D-AE6C-4556B87A3117}"/>
     <hyperlink ref="E312" r:id="rId28" xr:uid="{400C510C-E456-4A27-B24C-418D350D90BD}"/>
     <hyperlink ref="E315" r:id="rId29" xr:uid="{14C34214-6147-4305-92F1-69B213D1FA29}"/>
-    <hyperlink ref="F317" r:id="rId30" xr:uid="{DB7A9083-BA12-48B2-8FF0-15D58BECB5DE}"/>
-    <hyperlink ref="F327" r:id="rId31" display="○われ？" xr:uid="{B463ECED-0070-4C60-AB9F-1E345749E26F}"/>
-    <hyperlink ref="E254" r:id="rId32" xr:uid="{4F5E8AA4-E2BF-41E9-9FF9-67C354DB7071}"/>
-    <hyperlink ref="E258" r:id="rId33" xr:uid="{6212D2A7-A60E-4A8A-AC13-A29B95A7B7AD}"/>
-    <hyperlink ref="E260" r:id="rId34" xr:uid="{A312B211-7E36-48C6-86A6-43FFD50F9564}"/>
-    <hyperlink ref="E278" r:id="rId35" xr:uid="{57B1F815-44C0-490D-8DD0-A2C57F66B381}"/>
-    <hyperlink ref="E303" r:id="rId36" xr:uid="{10DAE240-14E7-4DE4-9086-1C76A7B2C1C2}"/>
-    <hyperlink ref="E325" r:id="rId37" xr:uid="{DD87348E-9210-439B-954F-C4B341F5F286}"/>
-    <hyperlink ref="E326" r:id="rId38" xr:uid="{B82F962C-17C5-48A6-9F5B-B7CD6194D005}"/>
-    <hyperlink ref="F212" r:id="rId39" xr:uid="{FBE5799F-EC50-4A5B-9DE1-C5C4BFCCC92C}"/>
-    <hyperlink ref="E293" r:id="rId40" xr:uid="{1EE495D5-212D-491A-9CC1-04E3004E4F7E}"/>
-    <hyperlink ref="E294" r:id="rId41" xr:uid="{466A8EC9-5237-4A15-8DB6-88D959EA8FF9}"/>
-    <hyperlink ref="E241" r:id="rId42" xr:uid="{43CF7CFC-B575-4CEF-990F-50420F12A526}"/>
-    <hyperlink ref="E213" r:id="rId43" xr:uid="{CD293A95-0BE7-4049-9C45-13227B9B3899}"/>
-    <hyperlink ref="E247" r:id="rId44" xr:uid="{9F3BBE7C-4C0F-46BC-A332-52D676A47F56}"/>
-    <hyperlink ref="E292" r:id="rId45" xr:uid="{C71E14FD-F4AF-4F58-8BDE-DD61974BA0D0}"/>
-    <hyperlink ref="E328" r:id="rId46" xr:uid="{202F65B8-C4AF-4ACA-B5DD-3359FDDB3851}"/>
-    <hyperlink ref="F319" r:id="rId47" xr:uid="{47BDEA1B-924E-4CE2-8E98-6DD194EE2BAD}"/>
-    <hyperlink ref="F322" r:id="rId48" xr:uid="{D6773DAB-BA6A-4BBB-A631-F34DE69BC44B}"/>
-    <hyperlink ref="F323" r:id="rId49" xr:uid="{56916333-2FE8-4766-9AD9-7CB741BE8F6E}"/>
-    <hyperlink ref="E311" r:id="rId50" xr:uid="{40287632-DAC3-4AF3-B01C-FF7ACA2A9408}"/>
-    <hyperlink ref="E313" r:id="rId51" xr:uid="{4016A78B-17C1-4E02-A76A-CAC2C130042E}"/>
-    <hyperlink ref="E314" r:id="rId52" xr:uid="{8814CF23-11DC-4AAF-98EB-6B1811273784}"/>
-    <hyperlink ref="E316" r:id="rId53" xr:uid="{43DA7E86-7356-439E-AEED-52273000DEC4}"/>
-    <hyperlink ref="E317" r:id="rId54" xr:uid="{D06B01CC-EC81-497A-A370-F094234CA4E4}"/>
-    <hyperlink ref="E232" r:id="rId55" xr:uid="{1E3206D5-6A5F-4BB3-B908-778C9EFD5B9B}"/>
-    <hyperlink ref="E246" r:id="rId56" xr:uid="{EC9D25F5-D3F5-4CFA-85E1-606706827C8F}"/>
-    <hyperlink ref="E245" r:id="rId57" xr:uid="{89A880A0-70F6-481F-8C12-0EE7303F03A2}"/>
-    <hyperlink ref="E250" r:id="rId58" xr:uid="{80A3A707-71DD-4447-82C9-04C263DDF404}"/>
-    <hyperlink ref="E251" r:id="rId59" xr:uid="{AB5C6BC9-BE79-41AB-8C59-570A0C795D4C}"/>
-    <hyperlink ref="E263" r:id="rId60" xr:uid="{C88C226C-07AE-4A36-8C1B-EE98C4EBF5DB}"/>
-    <hyperlink ref="E268" r:id="rId61" xr:uid="{F5172BF6-206F-4BB4-97A1-2BAE2C75241E}"/>
-    <hyperlink ref="E262" r:id="rId62" xr:uid="{83D6BB10-418D-422C-AA91-29FBCD86F8A1}"/>
-    <hyperlink ref="E209" r:id="rId63" xr:uid="{60BD73C8-48D6-44C7-B368-D1C7ECE0C9BC}"/>
-    <hyperlink ref="E206" r:id="rId64" xr:uid="{D3F60027-F747-4C8E-BFCB-BF56F7B70CF6}"/>
-    <hyperlink ref="E196" r:id="rId65" xr:uid="{BD5558B2-94A0-4F99-B693-982BFB0500B8}"/>
-    <hyperlink ref="E198" r:id="rId66" xr:uid="{375C6F58-F39A-4C58-88CA-0A2B8A19765B}"/>
-    <hyperlink ref="F242" r:id="rId67" xr:uid="{99AFF788-2968-42F3-B9A1-9905C969BC3D}"/>
-    <hyperlink ref="F194" r:id="rId68" xr:uid="{B43EF602-57AE-4CEB-93FF-6DC559FC4614}"/>
-    <hyperlink ref="G193" r:id="rId69" xr:uid="{1042BE84-60D9-4073-AE17-3A6941A318F6}"/>
-    <hyperlink ref="F180" r:id="rId70" xr:uid="{FC76A82A-A970-4297-80CC-32FC7060A565}"/>
-    <hyperlink ref="E184" r:id="rId71" xr:uid="{9A3CDCCF-A808-431C-80A7-55C881940664}"/>
-    <hyperlink ref="E185" r:id="rId72" xr:uid="{EF80A702-ACBB-45A9-86FB-8B71571E0E16}"/>
-    <hyperlink ref="E194" r:id="rId73" xr:uid="{94AF04F0-7E17-48D8-8076-7DD3D7AD03A8}"/>
-    <hyperlink ref="E195" r:id="rId74" xr:uid="{5C158E04-14E5-4376-BB48-6F0429F6732B}"/>
-    <hyperlink ref="E304" r:id="rId75" xr:uid="{D2590237-3BED-4C60-B750-4560557DBC76}"/>
-    <hyperlink ref="E305" r:id="rId76" xr:uid="{913DCE0F-4E27-441E-A370-EBDC71595DDE}"/>
-    <hyperlink ref="F205" r:id="rId77" xr:uid="{CF2F3FBE-5420-4936-8AF6-831F3F2157A3}"/>
-    <hyperlink ref="F158" r:id="rId78" xr:uid="{7F726D61-7F7F-4413-A22C-4011E2BCCB5F}"/>
-    <hyperlink ref="F197" r:id="rId79" xr:uid="{4865438C-E32A-496F-93EF-F7813CFF1DD3}"/>
-    <hyperlink ref="E238" r:id="rId80" xr:uid="{ADF7B2D9-F611-44B4-B8A5-05758C923B02}"/>
-    <hyperlink ref="E321" r:id="rId81" xr:uid="{51F6EE0C-4BDA-4D40-B448-F44D8CE199AF}"/>
-    <hyperlink ref="F324" r:id="rId82" xr:uid="{FA1433D3-A125-4D91-8655-CE3041406BBF}"/>
-    <hyperlink ref="F325" r:id="rId83" xr:uid="{E87B89B3-92DB-4654-B59A-DBB66B4F00DE}"/>
-    <hyperlink ref="F184" r:id="rId84" xr:uid="{0CEED77C-AE3C-4AC3-BA83-9660F17E5B98}"/>
-    <hyperlink ref="G323" r:id="rId85" display="水覗像/王？" xr:uid="{F00D9D1B-26F7-488C-B91C-F8141BE4536E}"/>
-    <hyperlink ref="F292" r:id="rId86" xr:uid="{2B802E9B-5D25-4BD1-AA45-D2032BA9C78D}"/>
-    <hyperlink ref="F293" r:id="rId87" xr:uid="{FE3EEB68-9021-4277-AAD9-27391243C61E}"/>
-    <hyperlink ref="F183" r:id="rId88" xr:uid="{97AC6B31-C5D9-4148-8AE1-3A52BFB6EC05}"/>
-    <hyperlink ref="G158" r:id="rId89" xr:uid="{B9C0917D-E21E-43D6-A01B-7E82133087C0}"/>
-    <hyperlink ref="G205" r:id="rId90" xr:uid="{AA239A2B-C23F-48FF-888A-322981A2C098}"/>
-    <hyperlink ref="E331" r:id="rId91" display="●壁？" xr:uid="{F990FDFE-4DF0-4673-9826-F0C1E126273C}"/>
-    <hyperlink ref="E279" r:id="rId92" display="●壁？" xr:uid="{5EA3C418-1B6D-445D-AE81-ACA7CC55CF94}"/>
-    <hyperlink ref="E280" r:id="rId93" display="●壁？" xr:uid="{CE7A30C3-A085-4A9F-87B9-7586D8CCA3E1}"/>
-    <hyperlink ref="F291" r:id="rId94" display="○われ？" xr:uid="{72D8E655-D6AE-40C9-ADBE-FF6E1136B3F9}"/>
-    <hyperlink ref="E299" r:id="rId95" display="○われ？" xr:uid="{BC289463-9110-4ED1-9FF2-E9A3D1EC3E3A}"/>
-    <hyperlink ref="E307" r:id="rId96" display="○われ？" xr:uid="{4B6267F3-44CD-4BC2-B76C-2E72EBB10DFB}"/>
-    <hyperlink ref="G184" r:id="rId97" display="掟に関するお知らせ" xr:uid="{A4DE5CC1-C14D-4DC0-B18B-F3F71753D776}"/>
-    <hyperlink ref="E318" r:id="rId98" display="掟に関するお知らせ" xr:uid="{62A2A5BA-0B54-402E-9C38-C4D9EB22DFCA}"/>
-    <hyperlink ref="E319" r:id="rId99" display="掟に関するお知らせ" xr:uid="{F3ACD306-3D5C-4845-9722-F5192163E0DB}"/>
-    <hyperlink ref="E320" r:id="rId100" display="掟に関するお知らせ" xr:uid="{4C069084-A3C6-4F17-9835-4852533E602C}"/>
-    <hyperlink ref="E322" r:id="rId101" display="掟に関するお知らせ" xr:uid="{43713843-F0BC-45EB-8141-CDDF434C1D96}"/>
-    <hyperlink ref="E323" r:id="rId102" display="掟に関するお知らせ" xr:uid="{48C7A341-761D-4FF9-B9EE-044C09F865E1}"/>
-    <hyperlink ref="E324" r:id="rId103" display="掟に関するお知らせ" xr:uid="{3F2B7D36-0F1F-424A-9F17-A1DE9DCD445A}"/>
-    <hyperlink ref="E329" r:id="rId104" display="掟に関するお知らせ" xr:uid="{0D72F1A9-4220-4BA0-8A4A-23A1D38533F1}"/>
-    <hyperlink ref="E332" r:id="rId105" xr:uid="{4E7486E6-9C9B-4F2B-B7BD-443D1F6304CC}"/>
-    <hyperlink ref="E333" r:id="rId106" xr:uid="{A0441298-7143-419D-A793-E976EACA92E3}"/>
-    <hyperlink ref="E334" r:id="rId107" xr:uid="{129E740A-4AA0-4F11-88A1-0B9A03860FF2}"/>
-    <hyperlink ref="E335" r:id="rId108" xr:uid="{C56117F9-1196-45F7-BA62-047C42ECB7D7}"/>
-    <hyperlink ref="E336" r:id="rId109" xr:uid="{E85A37DE-DD8D-4FF4-AA31-96B38F5902E5}"/>
-    <hyperlink ref="F315" r:id="rId110" display="無影言本祭" xr:uid="{9A0CC19B-9348-48FF-A0CC-CA3DEFCF51A5}"/>
-    <hyperlink ref="F298" r:id="rId111" display="無影言本祭" xr:uid="{0BA89E84-457B-4E28-945D-1DCDB15B63B0}"/>
-    <hyperlink ref="E337" r:id="rId112" xr:uid="{C6217001-1ED9-4BE7-914A-0BDBF5BE318C}"/>
-    <hyperlink ref="E338" r:id="rId113" xr:uid="{BC9E6940-FF9A-4756-BB1B-0C4403762254}"/>
-    <hyperlink ref="F216" r:id="rId114" xr:uid="{3C6377C7-1B66-4476-8E9C-A9D5A878A0AE}"/>
-    <hyperlink ref="F259" r:id="rId115" xr:uid="{AA40B19D-9046-4C74-B04E-EDD95592AD0F}"/>
-    <hyperlink ref="F163" r:id="rId116" xr:uid="{921360D1-C8F1-47DC-8965-EF1A27211120}"/>
-    <hyperlink ref="F257" r:id="rId117" xr:uid="{D1CEAB88-533B-4592-96F7-9C2CA0598EF3}"/>
-    <hyperlink ref="F232" r:id="rId118" xr:uid="{35EA88DE-206B-4EF8-9259-9E1E793C9E5B}"/>
-    <hyperlink ref="F314" r:id="rId119" xr:uid="{00BD4916-443C-4D61-ADBA-08351BF0AA95}"/>
-    <hyperlink ref="E339" r:id="rId120" xr:uid="{35DD3EBE-71F4-4631-AFA7-387F800E7B2F}"/>
-    <hyperlink ref="F330" r:id="rId121" xr:uid="{411BBBFD-4B20-4B8E-B6D7-4425E0FB9182}"/>
-    <hyperlink ref="F329" r:id="rId122" xr:uid="{8FE7C2D8-229B-435B-8354-9A0EA83B7570}"/>
-    <hyperlink ref="H193" r:id="rId123" xr:uid="{5A06E54E-D7FA-4163-B78F-09FB36783946}"/>
-    <hyperlink ref="E193" r:id="rId124" xr:uid="{F1E432DC-CBD9-4441-B594-95C84BFC9DE2}"/>
-    <hyperlink ref="I193" r:id="rId125" xr:uid="{26BA6F02-E1EA-4539-82D4-14963B73A27E}"/>
-    <hyperlink ref="F261" r:id="rId126" xr:uid="{F6A8D4BF-3BA3-4543-A279-4E8833A868D6}"/>
-    <hyperlink ref="F277" r:id="rId127" xr:uid="{993902BA-7D34-48FB-8ACF-587A5B27410C}"/>
-    <hyperlink ref="E340" r:id="rId128" xr:uid="{9AA5542F-D003-437E-8913-A9512DD01ADF}"/>
-    <hyperlink ref="E341" r:id="rId129" xr:uid="{5A8B6FF2-64E9-40FB-A7C2-DF46C3FD4F52}"/>
-    <hyperlink ref="E342" r:id="rId130" xr:uid="{75E26C8C-85FC-485D-8511-5265A6C0CBAC}"/>
-    <hyperlink ref="E135" r:id="rId131" xr:uid="{73E16B9D-691D-42C8-A812-EF9F0DA5C4AA}"/>
-    <hyperlink ref="G180" r:id="rId132" xr:uid="{7343C3A1-5CF1-47F6-A5C4-7CF5A8BE76E7}"/>
-    <hyperlink ref="F250" r:id="rId133" xr:uid="{D139FC92-7C4A-469B-A143-9ADFF2564948}"/>
-    <hyperlink ref="F267" r:id="rId134" xr:uid="{E445BD3C-8B36-4199-8876-4A6BF79488C5}"/>
+    <hyperlink ref="F318" r:id="rId30" xr:uid="{DB7A9083-BA12-48B2-8FF0-15D58BECB5DE}"/>
+    <hyperlink ref="E254" r:id="rId31" xr:uid="{4F5E8AA4-E2BF-41E9-9FF9-67C354DB7071}"/>
+    <hyperlink ref="E258" r:id="rId32" xr:uid="{6212D2A7-A60E-4A8A-AC13-A29B95A7B7AD}"/>
+    <hyperlink ref="E260" r:id="rId33" xr:uid="{A312B211-7E36-48C6-86A6-43FFD50F9564}"/>
+    <hyperlink ref="E278" r:id="rId34" xr:uid="{57B1F815-44C0-490D-8DD0-A2C57F66B381}"/>
+    <hyperlink ref="E303" r:id="rId35" xr:uid="{10DAE240-14E7-4DE4-9086-1C76A7B2C1C2}"/>
+    <hyperlink ref="E325" r:id="rId36" xr:uid="{DD87348E-9210-439B-954F-C4B341F5F286}"/>
+    <hyperlink ref="E326" r:id="rId37" xr:uid="{B82F962C-17C5-48A6-9F5B-B7CD6194D005}"/>
+    <hyperlink ref="F213" r:id="rId38" xr:uid="{FBE5799F-EC50-4A5B-9DE1-C5C4BFCCC92C}"/>
+    <hyperlink ref="E293" r:id="rId39" xr:uid="{1EE495D5-212D-491A-9CC1-04E3004E4F7E}"/>
+    <hyperlink ref="E294" r:id="rId40" xr:uid="{466A8EC9-5237-4A15-8DB6-88D959EA8FF9}"/>
+    <hyperlink ref="E241" r:id="rId41" xr:uid="{43CF7CFC-B575-4CEF-990F-50420F12A526}"/>
+    <hyperlink ref="E213" r:id="rId42" xr:uid="{CD293A95-0BE7-4049-9C45-13227B9B3899}"/>
+    <hyperlink ref="E247" r:id="rId43" xr:uid="{9F3BBE7C-4C0F-46BC-A332-52D676A47F56}"/>
+    <hyperlink ref="E292" r:id="rId44" xr:uid="{C71E14FD-F4AF-4F58-8BDE-DD61974BA0D0}"/>
+    <hyperlink ref="E328" r:id="rId45" xr:uid="{202F65B8-C4AF-4ACA-B5DD-3359FDDB3851}"/>
+    <hyperlink ref="F320" r:id="rId46" xr:uid="{47BDEA1B-924E-4CE2-8E98-6DD194EE2BAD}"/>
+    <hyperlink ref="F323" r:id="rId47" xr:uid="{D6773DAB-BA6A-4BBB-A631-F34DE69BC44B}"/>
+    <hyperlink ref="F324" r:id="rId48" xr:uid="{56916333-2FE8-4766-9AD9-7CB741BE8F6E}"/>
+    <hyperlink ref="E311" r:id="rId49" xr:uid="{40287632-DAC3-4AF3-B01C-FF7ACA2A9408}"/>
+    <hyperlink ref="E313" r:id="rId50" xr:uid="{4016A78B-17C1-4E02-A76A-CAC2C130042E}"/>
+    <hyperlink ref="E314" r:id="rId51" xr:uid="{8814CF23-11DC-4AAF-98EB-6B1811273784}"/>
+    <hyperlink ref="E316" r:id="rId52" xr:uid="{43DA7E86-7356-439E-AEED-52273000DEC4}"/>
+    <hyperlink ref="E317" r:id="rId53" xr:uid="{D06B01CC-EC81-497A-A370-F094234CA4E4}"/>
+    <hyperlink ref="E232" r:id="rId54" xr:uid="{1E3206D5-6A5F-4BB3-B908-778C9EFD5B9B}"/>
+    <hyperlink ref="E246" r:id="rId55" xr:uid="{EC9D25F5-D3F5-4CFA-85E1-606706827C8F}"/>
+    <hyperlink ref="E245" r:id="rId56" xr:uid="{89A880A0-70F6-481F-8C12-0EE7303F03A2}"/>
+    <hyperlink ref="E250" r:id="rId57" xr:uid="{80A3A707-71DD-4447-82C9-04C263DDF404}"/>
+    <hyperlink ref="E251" r:id="rId58" xr:uid="{AB5C6BC9-BE79-41AB-8C59-570A0C795D4C}"/>
+    <hyperlink ref="E263" r:id="rId59" xr:uid="{C88C226C-07AE-4A36-8C1B-EE98C4EBF5DB}"/>
+    <hyperlink ref="E268" r:id="rId60" xr:uid="{F5172BF6-206F-4BB4-97A1-2BAE2C75241E}"/>
+    <hyperlink ref="E262" r:id="rId61" xr:uid="{83D6BB10-418D-422C-AA91-29FBCD86F8A1}"/>
+    <hyperlink ref="E209" r:id="rId62" xr:uid="{60BD73C8-48D6-44C7-B368-D1C7ECE0C9BC}"/>
+    <hyperlink ref="E206" r:id="rId63" xr:uid="{D3F60027-F747-4C8E-BFCB-BF56F7B70CF6}"/>
+    <hyperlink ref="E196" r:id="rId64" xr:uid="{BD5558B2-94A0-4F99-B693-982BFB0500B8}"/>
+    <hyperlink ref="E198" r:id="rId65" xr:uid="{375C6F58-F39A-4C58-88CA-0A2B8A19765B}"/>
+    <hyperlink ref="F243" r:id="rId66" xr:uid="{99AFF788-2968-42F3-B9A1-9905C969BC3D}"/>
+    <hyperlink ref="F195" r:id="rId67" xr:uid="{B43EF602-57AE-4CEB-93FF-6DC559FC4614}"/>
+    <hyperlink ref="G194" r:id="rId68" xr:uid="{1042BE84-60D9-4073-AE17-3A6941A318F6}"/>
+    <hyperlink ref="F181" r:id="rId69" xr:uid="{FC76A82A-A970-4297-80CC-32FC7060A565}"/>
+    <hyperlink ref="E184" r:id="rId70" xr:uid="{9A3CDCCF-A808-431C-80A7-55C881940664}"/>
+    <hyperlink ref="E185" r:id="rId71" xr:uid="{EF80A702-ACBB-45A9-86FB-8B71571E0E16}"/>
+    <hyperlink ref="E194" r:id="rId72" xr:uid="{94AF04F0-7E17-48D8-8076-7DD3D7AD03A8}"/>
+    <hyperlink ref="E195" r:id="rId73" xr:uid="{5C158E04-14E5-4376-BB48-6F0429F6732B}"/>
+    <hyperlink ref="E304" r:id="rId74" xr:uid="{D2590237-3BED-4C60-B750-4560557DBC76}"/>
+    <hyperlink ref="E305" r:id="rId75" xr:uid="{913DCE0F-4E27-441E-A370-EBDC71595DDE}"/>
+    <hyperlink ref="F206" r:id="rId76" xr:uid="{CF2F3FBE-5420-4936-8AF6-831F3F2157A3}"/>
+    <hyperlink ref="F159" r:id="rId77" xr:uid="{7F726D61-7F7F-4413-A22C-4011E2BCCB5F}"/>
+    <hyperlink ref="F198" r:id="rId78" xr:uid="{4865438C-E32A-496F-93EF-F7813CFF1DD3}"/>
+    <hyperlink ref="E238" r:id="rId79" xr:uid="{ADF7B2D9-F611-44B4-B8A5-05758C923B02}"/>
+    <hyperlink ref="E321" r:id="rId80" xr:uid="{51F6EE0C-4BDA-4D40-B448-F44D8CE199AF}"/>
+    <hyperlink ref="F325" r:id="rId81" xr:uid="{FA1433D3-A125-4D91-8655-CE3041406BBF}"/>
+    <hyperlink ref="F326" r:id="rId82" xr:uid="{E87B89B3-92DB-4654-B59A-DBB66B4F00DE}"/>
+    <hyperlink ref="F185" r:id="rId83" xr:uid="{0CEED77C-AE3C-4AC3-BA83-9660F17E5B98}"/>
+    <hyperlink ref="G324" r:id="rId84" display="水覗像/王？" xr:uid="{F00D9D1B-26F7-488C-B91C-F8141BE4536E}"/>
+    <hyperlink ref="F293" r:id="rId85" xr:uid="{2B802E9B-5D25-4BD1-AA45-D2032BA9C78D}"/>
+    <hyperlink ref="F294" r:id="rId86" xr:uid="{FE3EEB68-9021-4277-AAD9-27391243C61E}"/>
+    <hyperlink ref="F184" r:id="rId87" xr:uid="{97AC6B31-C5D9-4148-8AE1-3A52BFB6EC05}"/>
+    <hyperlink ref="G159" r:id="rId88" xr:uid="{B9C0917D-E21E-43D6-A01B-7E82133087C0}"/>
+    <hyperlink ref="G206" r:id="rId89" xr:uid="{AA239A2B-C23F-48FF-888A-322981A2C098}"/>
+    <hyperlink ref="E331" r:id="rId90" display="●壁？" xr:uid="{F990FDFE-4DF0-4673-9826-F0C1E126273C}"/>
+    <hyperlink ref="E279" r:id="rId91" display="●壁？" xr:uid="{5EA3C418-1B6D-445D-AE81-ACA7CC55CF94}"/>
+    <hyperlink ref="E280" r:id="rId92" display="●壁？" xr:uid="{CE7A30C3-A085-4A9F-87B9-7586D8CCA3E1}"/>
+    <hyperlink ref="F292" r:id="rId93" display="○われ？" xr:uid="{72D8E655-D6AE-40C9-ADBE-FF6E1136B3F9}"/>
+    <hyperlink ref="E299" r:id="rId94" display="○われ？" xr:uid="{BC289463-9110-4ED1-9FF2-E9A3D1EC3E3A}"/>
+    <hyperlink ref="E307" r:id="rId95" display="○われ？" xr:uid="{4B6267F3-44CD-4BC2-B76C-2E72EBB10DFB}"/>
+    <hyperlink ref="G185" r:id="rId96" display="掟に関するお知らせ" xr:uid="{A4DE5CC1-C14D-4DC0-B18B-F3F71753D776}"/>
+    <hyperlink ref="E318" r:id="rId97" display="掟に関するお知らせ" xr:uid="{62A2A5BA-0B54-402E-9C38-C4D9EB22DFCA}"/>
+    <hyperlink ref="E319" r:id="rId98" display="掟に関するお知らせ" xr:uid="{F3ACD306-3D5C-4845-9722-F5192163E0DB}"/>
+    <hyperlink ref="E320" r:id="rId99" display="掟に関するお知らせ" xr:uid="{4C069084-A3C6-4F17-9835-4852533E602C}"/>
+    <hyperlink ref="E322" r:id="rId100" display="掟に関するお知らせ" xr:uid="{43713843-F0BC-45EB-8141-CDDF434C1D96}"/>
+    <hyperlink ref="E323" r:id="rId101" display="掟に関するお知らせ" xr:uid="{48C7A341-761D-4FF9-B9EE-044C09F865E1}"/>
+    <hyperlink ref="E324" r:id="rId102" display="掟に関するお知らせ" xr:uid="{3F2B7D36-0F1F-424A-9F17-A1DE9DCD445A}"/>
+    <hyperlink ref="E329" r:id="rId103" display="掟に関するお知らせ" xr:uid="{0D72F1A9-4220-4BA0-8A4A-23A1D38533F1}"/>
+    <hyperlink ref="E332" r:id="rId104" xr:uid="{4E7486E6-9C9B-4F2B-B7BD-443D1F6304CC}"/>
+    <hyperlink ref="E333" r:id="rId105" xr:uid="{A0441298-7143-419D-A793-E976EACA92E3}"/>
+    <hyperlink ref="E334" r:id="rId106" xr:uid="{129E740A-4AA0-4F11-88A1-0B9A03860FF2}"/>
+    <hyperlink ref="E335" r:id="rId107" xr:uid="{C56117F9-1196-45F7-BA62-047C42ECB7D7}"/>
+    <hyperlink ref="E336" r:id="rId108" xr:uid="{E85A37DE-DD8D-4FF4-AA31-96B38F5902E5}"/>
+    <hyperlink ref="F316" r:id="rId109" display="無影言本祭" xr:uid="{9A0CC19B-9348-48FF-A0CC-CA3DEFCF51A5}"/>
+    <hyperlink ref="F299" r:id="rId110" display="無影言本祭" xr:uid="{0BA89E84-457B-4E28-945D-1DCDB15B63B0}"/>
+    <hyperlink ref="E337" r:id="rId111" xr:uid="{C6217001-1ED9-4BE7-914A-0BDBF5BE318C}"/>
+    <hyperlink ref="E338" r:id="rId112" xr:uid="{BC9E6940-FF9A-4756-BB1B-0C4403762254}"/>
+    <hyperlink ref="F217" r:id="rId113" xr:uid="{3C6377C7-1B66-4476-8E9C-A9D5A878A0AE}"/>
+    <hyperlink ref="F260" r:id="rId114" xr:uid="{AA40B19D-9046-4C74-B04E-EDD95592AD0F}"/>
+    <hyperlink ref="F164" r:id="rId115" xr:uid="{921360D1-C8F1-47DC-8965-EF1A27211120}"/>
+    <hyperlink ref="F258" r:id="rId116" xr:uid="{D1CEAB88-533B-4592-96F7-9C2CA0598EF3}"/>
+    <hyperlink ref="F233" r:id="rId117" xr:uid="{35EA88DE-206B-4EF8-9259-9E1E793C9E5B}"/>
+    <hyperlink ref="F315" r:id="rId118" xr:uid="{00BD4916-443C-4D61-ADBA-08351BF0AA95}"/>
+    <hyperlink ref="E339" r:id="rId119" xr:uid="{35DD3EBE-71F4-4631-AFA7-387F800E7B2F}"/>
+    <hyperlink ref="F331" r:id="rId120" xr:uid="{411BBBFD-4B20-4B8E-B6D7-4425E0FB9182}"/>
+    <hyperlink ref="F330" r:id="rId121" xr:uid="{8FE7C2D8-229B-435B-8354-9A0EA83B7570}"/>
+    <hyperlink ref="H194" r:id="rId122" xr:uid="{5A06E54E-D7FA-4163-B78F-09FB36783946}"/>
+    <hyperlink ref="E193" r:id="rId123" xr:uid="{F1E432DC-CBD9-4441-B594-95C84BFC9DE2}"/>
+    <hyperlink ref="I194" r:id="rId124" xr:uid="{26BA6F02-E1EA-4539-82D4-14963B73A27E}"/>
+    <hyperlink ref="F262" r:id="rId125" xr:uid="{F6A8D4BF-3BA3-4543-A279-4E8833A868D6}"/>
+    <hyperlink ref="F278" r:id="rId126" xr:uid="{993902BA-7D34-48FB-8ACF-587A5B27410C}"/>
+    <hyperlink ref="E340" r:id="rId127" xr:uid="{9AA5542F-D003-437E-8913-A9512DD01ADF}"/>
+    <hyperlink ref="E341" r:id="rId128" xr:uid="{5A8B6FF2-64E9-40FB-A7C2-DF46C3FD4F52}"/>
+    <hyperlink ref="E342" r:id="rId129" xr:uid="{75E26C8C-85FC-485D-8511-5265A6C0CBAC}"/>
+    <hyperlink ref="E135" r:id="rId130" xr:uid="{73E16B9D-691D-42C8-A812-EF9F0DA5C4AA}"/>
+    <hyperlink ref="G181" r:id="rId131" xr:uid="{7343C3A1-5CF1-47F6-A5C4-7CF5A8BE76E7}"/>
+    <hyperlink ref="F251" r:id="rId132" xr:uid="{D139FC92-7C4A-469B-A143-9ADFF2564948}"/>
+    <hyperlink ref="F268" r:id="rId133" xr:uid="{E445BD3C-8B36-4199-8876-4A6BF79488C5}"/>
+    <hyperlink ref="G331" r:id="rId134" xr:uid="{8B0E2C80-F9A1-4AEB-83B8-0014F3EF88BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId135"/>
@@ -19880,7 +19956,7 @@
       </c>
       <c r="W6" s="6" t="str">
         <f>_xlfn.XLOOKUP(V6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>[介]?</v>
+        <v>桶?</v>
       </c>
       <c r="X6" s="17" t="s">
         <v>297</v>
@@ -25688,7 +25764,7 @@
       </c>
       <c r="BO17" s="6" t="str">
         <f>_xlfn.XLOOKUP(BN17,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>[傎]?</v>
+        <v>奥?</v>
       </c>
       <c r="BP17" s="7" t="s">
         <v>1103</v>
@@ -28696,7 +28772,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C5E931-1AEC-434D-81A1-3EA98DBB914E}">
-  <dimension ref="B1:F105"/>
+  <dimension ref="B1:F106"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.25" style="35" bestFit="1" customWidth="1"/>
@@ -28708,291 +28784,291 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B1" s="54" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C1" s="45" t="s">
         <v>2104</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="D1" s="45" t="s">
+        <v>2658</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>2105</v>
       </c>
-      <c r="D1" s="45" t="s">
-        <v>2663</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>2106</v>
-      </c>
       <c r="F1" s="45" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="38" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C2" s="36" t="s">
         <v>2101</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="D2" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E2" s="36" t="s">
         <v>2102</v>
       </c>
-      <c r="D2" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>2103</v>
-      </c>
       <c r="F2" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="35" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E3" s="36" t="s">
         <v>2211</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>2212</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>2213</v>
-      </c>
       <c r="F3" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B4" s="35" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E4" s="36" t="s">
         <v>2214</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>2215</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>2216</v>
-      </c>
       <c r="F4" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="35" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E5" s="36" t="s">
         <v>2217</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>2218</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>2219</v>
-      </c>
       <c r="F5" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="35" t="s">
+        <v>2218</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E6" s="36" t="s">
         <v>2220</v>
       </c>
-      <c r="C6" s="36" t="s">
-        <v>2221</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>2222</v>
-      </c>
       <c r="F6" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="35" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E7" s="36" t="s">
         <v>2223</v>
       </c>
-      <c r="C7" s="36" t="s">
-        <v>2224</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>2225</v>
-      </c>
       <c r="F7" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="35" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>2039</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="35" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E9" s="36" t="s">
         <v>2228</v>
       </c>
-      <c r="C9" s="36" t="s">
-        <v>2229</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>2230</v>
-      </c>
       <c r="F9" s="36" t="s">
-        <v>2503</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="35" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>2037</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="35" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E11" s="36" t="s">
         <v>2233</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>2235</v>
-      </c>
       <c r="F11" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="39" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="35" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>2041</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="35" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>2233</v>
+      </c>
+      <c r="F14" s="36" t="s">
         <v>2316</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>2317</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>2235</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>2318</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="35" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="35" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="35" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
@@ -29000,446 +29076,446 @@
         <v>2062</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="35" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>2433</v>
       </c>
-      <c r="C19" s="36" t="s">
-        <v>2434</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>2702</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>2435</v>
-      </c>
       <c r="F19" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="44" t="s">
-        <v>2519</v>
+        <v>2514</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>2502</v>
+        <v>2497</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="35" t="s">
-        <v>2504</v>
+        <v>2499</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>2505</v>
+        <v>2500</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>2506</v>
+        <v>2501</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="35" t="s">
-        <v>2507</v>
+        <v>2502</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>2508</v>
+        <v>2503</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>2509</v>
+        <v>2504</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="35" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="35" t="s">
-        <v>2512</v>
+        <v>2507</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="35" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="35" t="s">
-        <v>2516</v>
+        <v>2511</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>2517</v>
+        <v>2512</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="35" t="s">
-        <v>2523</v>
+        <v>2518</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>2524</v>
+        <v>2519</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="35" t="s">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>2529</v>
+        <v>2524</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B29" s="35" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>2528</v>
+        <v>2523</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="35" t="s">
-        <v>2530</v>
+        <v>2525</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>2531</v>
+        <v>2526</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B31" s="35" t="s">
-        <v>2532</v>
+        <v>2527</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>2533</v>
+        <v>2528</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B32" s="35" t="s">
-        <v>2534</v>
+        <v>2529</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="35" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>2538</v>
+        <v>2533</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="39" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="35" t="s">
-        <v>2572</v>
+        <v>2567</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>2573</v>
+        <v>2568</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>2583</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B36" s="35" t="s">
-        <v>2650</v>
+        <v>2645</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>2590</v>
+        <v>2585</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B37" s="35" t="s">
-        <v>2591</v>
+        <v>2586</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>2592</v>
+        <v>2587</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B38" s="35" t="s">
-        <v>2593</v>
+        <v>2588</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>2594</v>
+        <v>2589</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B39" s="35" t="s">
-        <v>2651</v>
+        <v>2646</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>2595</v>
+        <v>2590</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B40" s="35" t="s">
-        <v>2652</v>
+        <v>2647</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>2596</v>
+        <v>2591</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B41" s="35" t="s">
-        <v>2599</v>
+        <v>2594</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B42" s="35" t="s">
-        <v>2600</v>
+        <v>2595</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>2601</v>
+        <v>2596</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B43" s="35" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>2602</v>
+        <v>2597</v>
       </c>
       <c r="D43" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B44" s="35" t="s">
-        <v>2603</v>
+        <v>2598</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>2604</v>
+        <v>2599</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
@@ -29447,653 +29523,662 @@
         <v>1685</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>2605</v>
+        <v>2600</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="35" t="s">
-        <v>2606</v>
+        <v>2601</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>2607</v>
+        <v>2602</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B47" s="35" t="s">
-        <v>2608</v>
+        <v>2603</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>2609</v>
+        <v>2604</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="35" t="s">
-        <v>2610</v>
+        <v>2605</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>2611</v>
+        <v>2606</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" s="35" t="s">
-        <v>2612</v>
+        <v>2607</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>2613</v>
+        <v>2608</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="35" t="s">
-        <v>2614</v>
+        <v>2609</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>2615</v>
+        <v>2610</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B51" s="35" t="s">
-        <v>2616</v>
+        <v>2611</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>2617</v>
+        <v>2612</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B52" s="35" t="s">
-        <v>2618</v>
+        <v>2613</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>2619</v>
+        <v>2614</v>
       </c>
       <c r="D52" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B53" s="35" t="s">
-        <v>2620</v>
+        <v>2615</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>2621</v>
+        <v>2616</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B54" s="35" t="s">
-        <v>2622</v>
+        <v>2617</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>2623</v>
+        <v>2618</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" s="35" t="s">
-        <v>2624</v>
+        <v>2619</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>2625</v>
+        <v>2620</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="35" t="s">
-        <v>2626</v>
+        <v>2621</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>2627</v>
+        <v>2622</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B57" s="35" t="s">
-        <v>2628</v>
+        <v>2623</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>2629</v>
+        <v>2624</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B58" s="35" t="s">
-        <v>2630</v>
+        <v>2625</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>2631</v>
+        <v>2626</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B59" s="35" t="s">
-        <v>2632</v>
+        <v>2627</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>2633</v>
+        <v>2628</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B60" s="35" t="s">
-        <v>2634</v>
+        <v>2629</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>2635</v>
+        <v>2630</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B61" s="35" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>2637</v>
+        <v>2632</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B62" s="35" t="s">
-        <v>2638</v>
+        <v>2633</v>
       </c>
       <c r="C62" s="36" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B63" s="35" t="s">
-        <v>2640</v>
+        <v>2635</v>
       </c>
       <c r="C63" s="36" t="s">
-        <v>2641</v>
+        <v>2636</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F63" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B64" s="35" t="s">
-        <v>2642</v>
+        <v>2637</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>2643</v>
+        <v>2638</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B65" s="35" t="s">
-        <v>2644</v>
+        <v>2639</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>2645</v>
+        <v>2640</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F65" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B66" s="35" t="s">
-        <v>2646</v>
+        <v>2641</v>
       </c>
       <c r="C66" s="36" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F66" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B67" s="35" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="C67" s="36" t="s">
-        <v>2649</v>
+        <v>2644</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F67" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B68" s="35" t="s">
+        <v>2648</v>
+      </c>
+      <c r="C68" s="36" t="s">
         <v>2653</v>
       </c>
-      <c r="C68" s="36" t="s">
-        <v>2658</v>
-      </c>
       <c r="D68" s="36" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
       <c r="E68" s="36" t="s">
-        <v>2664</v>
+        <v>2659</v>
+      </c>
+      <c r="F68" s="36" t="s">
+        <v>2780</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B69" s="35" t="s">
-        <v>2654</v>
+        <v>2649</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>2655</v>
+        <v>2650</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
       <c r="F69" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B70" s="35" t="s">
-        <v>2656</v>
+        <v>2651</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>2657</v>
+        <v>2652</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
       <c r="E70" s="36" t="s">
-        <v>2664</v>
+        <v>2659</v>
+      </c>
+      <c r="F70" s="36" t="s">
+        <v>2780</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B71" s="35" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="C71" s="36" t="s">
+        <v>2655</v>
+      </c>
+      <c r="D71" s="36" t="s">
         <v>2660</v>
       </c>
-      <c r="D71" s="36" t="s">
-        <v>2665</v>
-      </c>
       <c r="F71" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B72" s="35" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="C72" s="36" t="s">
-        <v>2662</v>
+        <v>2657</v>
       </c>
       <c r="D72" s="36" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
       <c r="E72" s="36" t="s">
-        <v>2724</v>
+        <v>2719</v>
+      </c>
+      <c r="F72" s="36" t="s">
+        <v>2781</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B73" s="35" t="s">
-        <v>2667</v>
+        <v>2662</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
       <c r="F73" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B74" s="35" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
       <c r="C74" s="36" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="F74" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B75" s="35" t="s">
-        <v>2674</v>
+        <v>2669</v>
       </c>
       <c r="C75" s="36" t="s">
-        <v>2672</v>
+        <v>2667</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="F75" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B76" s="35" t="s">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>2677</v>
+        <v>2672</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>2701</v>
+        <v>2696</v>
       </c>
       <c r="F76" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B77" s="35" t="s">
-        <v>2678</v>
+        <v>2673</v>
       </c>
       <c r="C77" s="36" t="s">
-        <v>2679</v>
+        <v>2674</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="F77" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B78" s="35" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="C78" t="s">
-        <v>2680</v>
+        <v>2675</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E78" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="F78" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B79" s="35" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>2690</v>
+        <v>2685</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E79" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="F79" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B80" s="35" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="C80" s="36" t="s">
-        <v>2681</v>
+        <v>2676</v>
       </c>
       <c r="D80" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E80" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="F80" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B81" s="35" t="s">
-        <v>2693</v>
+        <v>2688</v>
       </c>
       <c r="C81" s="36" t="s">
-        <v>2682</v>
+        <v>2677</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E81" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B82" s="35" t="s">
-        <v>2694</v>
+        <v>2689</v>
       </c>
       <c r="C82" s="36" t="s">
-        <v>2683</v>
+        <v>2678</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E82" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="F82" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B83" s="35" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C83" s="36" t="s">
+        <v>2679</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>2668</v>
+      </c>
+      <c r="E83" s="36" t="s">
         <v>2695</v>
       </c>
-      <c r="C83" s="36" t="s">
-        <v>2684</v>
-      </c>
-      <c r="D83" s="36" t="s">
-        <v>2673</v>
-      </c>
-      <c r="E83" s="36" t="s">
-        <v>2700</v>
-      </c>
       <c r="F83" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B84" s="39" t="s">
-        <v>2696</v>
+        <v>2691</v>
       </c>
       <c r="C84" s="40" t="s">
-        <v>2685</v>
+        <v>2680</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="F84" s="40" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B85" s="35" t="s">
-        <v>2697</v>
+        <v>2692</v>
       </c>
       <c r="C85" s="36" t="s">
-        <v>2686</v>
+        <v>2681</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E85" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B86" s="35" t="s">
-        <v>2698</v>
+        <v>2693</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>2687</v>
+        <v>2682</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E86" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B87" s="35" t="s">
-        <v>2699</v>
+        <v>2694</v>
       </c>
       <c r="C87" s="36" t="s">
-        <v>2688</v>
+        <v>2683</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E87" s="36" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B88" s="35" t="s">
-        <v>2722</v>
+        <v>2717</v>
       </c>
       <c r="C88" s="36" t="s">
-        <v>2720</v>
+        <v>2715</v>
       </c>
       <c r="D88" s="36" t="s">
-        <v>2721</v>
+        <v>2716</v>
       </c>
       <c r="E88" s="36" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="F88" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B89" s="35" t="s">
-        <v>2726</v>
+        <v>2721</v>
       </c>
       <c r="C89" s="36" t="s">
-        <v>2727</v>
+        <v>2722</v>
       </c>
       <c r="D89" s="36" t="s">
-        <v>2721</v>
+        <v>2716</v>
       </c>
       <c r="F89" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.4">
@@ -30101,10 +30186,10 @@
         <v>1820</v>
       </c>
       <c r="C90" s="36" t="s">
-        <v>2728</v>
+        <v>2723</v>
       </c>
       <c r="D90" s="36" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.4">
@@ -30112,10 +30197,10 @@
         <v>110</v>
       </c>
       <c r="C91" s="36" t="s">
-        <v>2729</v>
+        <v>2724</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.4">
@@ -30123,10 +30208,10 @@
         <v>1722</v>
       </c>
       <c r="C92" s="33" t="s">
+        <v>2725</v>
+      </c>
+      <c r="D92" s="36" t="s">
         <v>2730</v>
-      </c>
-      <c r="D92" s="36" t="s">
-        <v>2735</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.4">
@@ -30134,10 +30219,10 @@
         <v>1937</v>
       </c>
       <c r="C93" s="36" t="s">
-        <v>2748</v>
+        <v>2743</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.4">
@@ -30145,140 +30230,178 @@
         <v>1144</v>
       </c>
       <c r="C94" s="36" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="D94" s="36" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B95" s="35" t="s">
-        <v>2731</v>
+        <v>2726</v>
       </c>
       <c r="C95" s="36" t="s">
-        <v>2732</v>
+        <v>2727</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F95" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B96" s="35" t="s">
-        <v>2733</v>
+        <v>2728</v>
       </c>
       <c r="C96" s="36" t="s">
-        <v>2734</v>
+        <v>2729</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="F96" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B97" s="35" t="s">
-        <v>2749</v>
+        <v>2744</v>
       </c>
       <c r="C97" s="36" t="s">
-        <v>2747</v>
+        <v>2742</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="F97" s="36" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B98" s="35" t="s">
-        <v>2751</v>
+        <v>2746</v>
       </c>
       <c r="C98" s="36" t="s">
-        <v>2752</v>
+        <v>2747</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>2753</v>
+        <v>2748</v>
+      </c>
+      <c r="F98" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B99" s="35" t="s">
-        <v>2754</v>
+        <v>2749</v>
       </c>
       <c r="C99" s="36" t="s">
-        <v>2755</v>
+        <v>2750</v>
       </c>
       <c r="D99" s="36" t="s">
-        <v>2756</v>
+        <v>2751</v>
+      </c>
+      <c r="F99" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B100" s="35" t="s">
-        <v>2758</v>
+        <v>2753</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>2759</v>
+        <v>2754</v>
       </c>
       <c r="D100" s="36" t="s">
-        <v>2760</v>
+        <v>2755</v>
+      </c>
+      <c r="F100" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B101" s="35" t="s">
-        <v>2764</v>
+        <v>2759</v>
       </c>
       <c r="C101" s="36" t="s">
-        <v>2765</v>
+        <v>2760</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>2760</v>
+        <v>2755</v>
+      </c>
+      <c r="F101" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B102" s="35" t="s">
-        <v>2767</v>
+        <v>2762</v>
       </c>
       <c r="C102" s="36" t="s">
-        <v>2768</v>
+        <v>2763</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>2769</v>
+        <v>2764</v>
+      </c>
+      <c r="F102" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B103" s="35" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="C103" s="36" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="D103" s="36" t="s">
-        <v>2772</v>
+        <v>2767</v>
+      </c>
+      <c r="F103" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B104" s="35" t="s">
-        <v>2773</v>
+        <v>2768</v>
       </c>
       <c r="C104" s="36" t="s">
-        <v>2774</v>
+        <v>2769</v>
       </c>
       <c r="D104" s="36" t="s">
-        <v>2772</v>
+        <v>2767</v>
+      </c>
+      <c r="F104" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B105" s="35" t="s">
-        <v>2775</v>
+        <v>2770</v>
       </c>
       <c r="C105" s="36" t="s">
-        <v>2776</v>
+        <v>2771</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>2760</v>
+        <v>2755</v>
+      </c>
+      <c r="F105" s="36" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B106" s="35" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C106" s="36" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D106" s="36" t="s">
+        <v>2697</v>
+      </c>
+      <c r="F106" s="36" t="s">
+        <v>2316</v>
       </c>
     </row>
   </sheetData>
@@ -30300,7 +30423,7 @@
   <sheetData>
     <row r="1" spans="2:4" s="48" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="B1" s="46" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="C1" s="47" t="s">
         <v>2015</v>
@@ -30311,7 +30434,7 @@
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="31" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="C2" s="34" t="s">
         <v>2094</v>
@@ -30319,7 +30442,7 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" s="31" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="C3" s="34" t="s">
         <v>2094</v>
@@ -30327,7 +30450,7 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" s="31" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="C4" s="34" t="s">
         <v>2094</v>
@@ -30335,7 +30458,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="31" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="C5" s="34" t="s">
         <v>2094</v>
@@ -30343,7 +30466,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B6" s="31" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="C6" s="34" t="s">
         <v>2094</v>
@@ -30351,7 +30474,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="31" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>2094</v>
@@ -30359,7 +30482,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="31" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>2094</v>
@@ -30367,7 +30490,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="31" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="C9" s="34" t="s">
         <v>2094</v>
@@ -30375,7 +30498,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B10" s="31" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>2094</v>
@@ -30383,7 +30506,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="31" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>2094</v>
@@ -30391,7 +30514,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B12" s="31" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>2094</v>
@@ -30399,7 +30522,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B13" s="31" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="C13" s="34" t="s">
         <v>2094</v>
@@ -30407,7 +30530,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="31" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="C14" s="34" t="s">
         <v>2094</v>
@@ -30415,7 +30538,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="31" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="C15" s="34" t="s">
         <v>2094</v>
@@ -30423,7 +30546,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="31" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="C16" s="34" t="s">
         <v>2094</v>
@@ -30431,7 +30554,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B17" s="31" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C17" s="34" t="s">
         <v>2094</v>
@@ -30439,7 +30562,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" s="31" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="C18" s="34" t="s">
         <v>2094</v>
@@ -30447,7 +30570,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="31" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="C19" s="34" t="s">
         <v>2094</v>
@@ -30455,7 +30578,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" s="31" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="C20" s="34" t="s">
         <v>2094</v>
@@ -30463,7 +30586,7 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B21" s="31" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="C21" s="34" t="s">
         <v>2094</v>
@@ -30471,7 +30594,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B22" s="31" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="C22" s="34" t="s">
         <v>2094</v>
@@ -30479,7 +30602,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="31" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="C23" s="34" t="s">
         <v>2094</v>
@@ -30487,7 +30610,7 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B24" s="31" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="C24" s="34" t="s">
         <v>2094</v>
@@ -30495,7 +30618,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="31" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>2072</v>
@@ -30503,7 +30626,7 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B26" s="31" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>2072</v>
@@ -30511,7 +30634,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B27" s="31" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>2072</v>
@@ -30519,7 +30642,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B28" s="31" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="C28" s="34" t="s">
         <v>2072</v>
@@ -30527,7 +30650,7 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B29" s="31" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="C29" s="34" t="s">
         <v>2068</v>
@@ -30535,7 +30658,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="31" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="C30" s="34" t="s">
         <v>2068</v>
@@ -30543,7 +30666,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B31" s="31" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="C31" s="34" t="s">
         <v>2068</v>
@@ -30551,7 +30674,7 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B32" s="31" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="C32" s="34" t="s">
         <v>2068</v>
@@ -30559,7 +30682,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="31" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="C33" s="34" t="s">
         <v>2068</v>
@@ -30570,7 +30693,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="31" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="C34" s="34" t="s">
         <v>2068</v>
@@ -30578,7 +30701,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" s="31" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="C35" s="34" t="s">
         <v>2068</v>
@@ -30586,7 +30709,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B36" s="31" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="C36" s="34" t="s">
         <v>2068</v>
@@ -30594,7 +30717,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B37" s="31" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C37" s="34" t="s">
         <v>2068</v>
@@ -30602,7 +30725,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="31" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="C38" s="34" t="s">
         <v>2068</v>
@@ -30610,18 +30733,18 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="31" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="C39" s="34" t="s">
         <v>2087</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="31" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="C40" s="34" t="s">
         <v>2087</v>
@@ -30629,7 +30752,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="31" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="C41" s="34" t="s">
         <v>2087</v>
@@ -30637,7 +30760,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" s="31" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="C42" s="34" t="s">
         <v>2087</v>
@@ -30645,7 +30768,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="31" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="C43" s="34" t="s">
         <v>2087</v>
@@ -30653,7 +30776,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B44" s="31" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="C44" s="34" t="s">
         <v>2087</v>
@@ -30661,7 +30784,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="31" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="C45" s="34" t="s">
         <v>2087</v>
@@ -30669,7 +30792,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B46" s="31" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="C46" s="34" t="s">
         <v>2084</v>
@@ -30677,7 +30800,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B47" s="31" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="C47" s="34" t="s">
         <v>2084</v>
@@ -30693,7 +30816,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B49" s="31" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="C49" s="34" t="s">
         <v>2084</v>
@@ -30701,7 +30824,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B50" s="31" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="C50" s="34" t="s">
         <v>2084</v>
@@ -30709,7 +30832,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B51" s="31" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="C51" s="34" t="s">
         <v>2084</v>
@@ -30717,7 +30840,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B52" s="31" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="C52" s="34" t="s">
         <v>2084</v>
@@ -30725,7 +30848,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B53" s="31" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="C53" s="34" t="s">
         <v>2084</v>
@@ -30733,7 +30856,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B54" s="31" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="C54" s="34" t="s">
         <v>2086</v>
@@ -30741,7 +30864,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B55" s="31" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="C55" s="34" t="s">
         <v>2086</v>
@@ -30749,7 +30872,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B56" s="31" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>2086</v>
@@ -30757,7 +30880,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B57" s="31" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="C57" s="34" t="s">
         <v>2086</v>
@@ -30765,7 +30888,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B58" s="31" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="C58" s="34" t="s">
         <v>2086</v>
@@ -30773,7 +30896,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B59" s="31" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="C59" s="34" t="s">
         <v>2086</v>
@@ -30781,7 +30904,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B60" s="31" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="C60" s="34" t="s">
         <v>2086</v>
@@ -30789,7 +30912,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B61" s="31" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="C61" s="34" t="s">
         <v>2086</v>
@@ -30797,18 +30920,18 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B62" s="31" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="C62" s="34" t="s">
         <v>2086</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B63" s="31" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="C63" s="34" t="s">
         <v>2086</v>
@@ -30816,7 +30939,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B64" s="31" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="C64" s="34" t="s">
         <v>2086</v>
@@ -30824,7 +30947,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B65" s="31" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="C65" s="34" t="s">
         <v>2086</v>
@@ -30832,7 +30955,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B66" s="31" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="C66" s="34" t="s">
         <v>2086</v>
@@ -30840,7 +30963,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B67" s="31" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="C67" s="34" t="s">
         <v>2086</v>
@@ -30848,7 +30971,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B68" s="31" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="C68" s="34" t="s">
         <v>2086</v>
@@ -30856,7 +30979,7 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B69" s="31" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="C69" s="34" t="s">
         <v>2086</v>
@@ -30864,7 +30987,7 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B70" s="31" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="C70" s="34" t="s">
         <v>2086</v>
@@ -30872,7 +30995,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B71" s="31" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="C71" s="34" t="s">
         <v>2064</v>
@@ -30880,7 +31003,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B72" s="31" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="C72" s="34" t="s">
         <v>2064</v>
@@ -30888,7 +31011,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B73" s="31" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="C73" s="34" t="s">
         <v>2064</v>
@@ -30896,7 +31019,7 @@
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B74" s="31" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="C74" s="34" t="s">
         <v>2064</v>
@@ -30907,7 +31030,7 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B75" s="31" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="C75" s="34" t="s">
         <v>2064</v>
@@ -30915,7 +31038,7 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B76" s="31" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="C76" s="34" t="s">
         <v>2064</v>
@@ -30923,7 +31046,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B77" s="31" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="C77" s="34" t="s">
         <v>2064</v>
@@ -30931,7 +31054,7 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B78" s="31" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="C78" s="34" t="s">
         <v>2064</v>
@@ -30939,7 +31062,7 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B79" s="31" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="C79" s="34" t="s">
         <v>2064</v>
@@ -30947,7 +31070,7 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B80" s="31" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="C80" s="34" t="s">
         <v>2064</v>
@@ -30955,7 +31078,7 @@
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B81" s="31" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="C81" s="34" t="s">
         <v>2064</v>
@@ -30963,7 +31086,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B82" s="31" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="C82" s="34" t="s">
         <v>2064</v>
@@ -30971,7 +31094,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B83" s="31" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="C83" s="34" t="s">
         <v>2064</v>
@@ -30979,7 +31102,7 @@
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B84" s="31" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="C84" s="34" t="s">
         <v>2064</v>
@@ -30987,7 +31110,7 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B85" s="31" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C85" s="34" t="s">
         <v>2064</v>
@@ -30995,7 +31118,7 @@
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B86" s="31" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="C86" s="34" t="s">
         <v>2064</v>
@@ -31003,7 +31126,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B87" s="31" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="C87" s="34" t="s">
         <v>2064</v>
@@ -31011,7 +31134,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B88" s="31" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="C88" s="34" t="s">
         <v>2064</v>
@@ -31019,7 +31142,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B89" s="31" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="C89" s="34" t="s">
         <v>2064</v>
@@ -31027,7 +31150,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B90" s="31" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="C90" s="34" t="s">
         <v>2064</v>
@@ -31035,15 +31158,15 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B91" s="31" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="C91" s="34" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B92" s="31" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="C92" s="34" t="s">
         <v>2073</v>
@@ -31051,80 +31174,80 @@
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B93" s="31" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="C93" s="34" t="s">
         <v>2071</v>
       </c>
       <c r="D93" s="34" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B94" s="31" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="C94" s="34" t="s">
         <v>2071</v>
       </c>
       <c r="D94" s="34" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B95" s="31" t="s">
+        <v>2241</v>
+      </c>
+      <c r="C95" s="34" t="s">
         <v>2243</v>
-      </c>
-      <c r="C95" s="34" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B96" s="31" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="C96" s="34" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B97" s="31" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B98" s="31" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B99" s="31" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="C99" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B100" s="31" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="C100" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B101" s="31" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.4">
@@ -31132,60 +31255,60 @@
         <v>949</v>
       </c>
       <c r="C102" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B103" s="31" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="C103" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B104" s="31" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="C104" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B105" s="31" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B106" s="31" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C106" s="34" t="s">
         <v>2253</v>
-      </c>
-      <c r="C106" s="34" t="s">
-        <v>2255</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B107" s="31" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B108" s="31" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="C108" s="34" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B109" s="31" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="C109" s="34" t="s">
         <v>2093</v>
@@ -31193,7 +31316,7 @@
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B110" s="31" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="C110" s="34" t="s">
         <v>2093</v>
@@ -31201,7 +31324,7 @@
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B111" s="31" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="C111" s="34" t="s">
         <v>2093</v>
@@ -31209,7 +31332,7 @@
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B112" s="31" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="C112" s="34" t="s">
         <v>2093</v>
@@ -31217,7 +31340,7 @@
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B113" s="31" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="C113" s="34" t="s">
         <v>2074</v>
@@ -31225,7 +31348,7 @@
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B114" s="31" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="C114" s="34" t="s">
         <v>2074</v>
@@ -31233,7 +31356,7 @@
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B115" s="31" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="C115" s="34" t="s">
         <v>2074</v>
@@ -31241,7 +31364,7 @@
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B116" s="31" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="C116" s="34" t="s">
         <v>2074</v>
@@ -31249,7 +31372,7 @@
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B117" s="31" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="C117" s="34" t="s">
         <v>2074</v>
@@ -31257,7 +31380,7 @@
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B118" s="31" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="C118" s="34" t="s">
         <v>2074</v>
@@ -31265,7 +31388,7 @@
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B119" s="31" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="C119" s="34" t="s">
         <v>2079</v>
@@ -31273,7 +31396,7 @@
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B120" s="31" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="C120" s="34" t="s">
         <v>2079</v>
@@ -31281,7 +31404,7 @@
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B121" s="31" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="C121" s="34" t="s">
         <v>2079</v>
@@ -31289,1070 +31412,1070 @@
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B122" s="31" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="C122" s="34" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="31" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="C123" s="34" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B124" s="31" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B125" s="31" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B126" s="31" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="31" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B128" s="31" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="C128" s="34" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B129" s="31" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B130" s="31" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="C130" s="34" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B131" s="31" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C131" s="34" t="s">
         <v>2281</v>
       </c>
-      <c r="C131" s="34" t="s">
-        <v>2283</v>
-      </c>
       <c r="D131" s="34" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B132" s="31" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="C132" s="34" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B133" s="31" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="C133" s="34" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B134" s="31" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B135" s="31" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B136" s="31" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B137" s="31" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C137" s="34" t="s">
         <v>2288</v>
-      </c>
-      <c r="C137" s="34" t="s">
-        <v>2290</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B138" s="31" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="C138" s="34" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B139" s="31" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B140" s="31" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B141" s="31" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="C141" s="34" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B142" s="31" t="s">
+        <v>2292</v>
+      </c>
+      <c r="C142" s="34" t="s">
         <v>2294</v>
-      </c>
-      <c r="C142" s="34" t="s">
-        <v>2296</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B143" s="31" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B144" s="31" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B145" s="31" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C145" s="34" t="s">
         <v>2298</v>
-      </c>
-      <c r="C145" s="34" t="s">
-        <v>2300</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B146" s="31" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="C146" s="34" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B147" s="31" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="C147" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B148" s="31" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="C148" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B149" s="31" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B150" s="31" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B151" s="31" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B152" s="31" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="C152" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B153" s="31" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="C153" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B154" s="31" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C154" s="34" t="s">
         <v>2308</v>
-      </c>
-      <c r="C154" s="34" t="s">
-        <v>2310</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B155" s="31" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B156" s="31" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="C156" s="34" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B157" s="31" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B158" s="31" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C158" s="34" t="s">
         <v>2313</v>
-      </c>
-      <c r="C158" s="34" t="s">
-        <v>2315</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B159" s="31" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B160" s="31" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="C160" s="34" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B161" s="31" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B162" s="31" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B163" s="31" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B164" s="31" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B165" s="31" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B166" s="31" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C166" s="34" t="s">
         <v>2326</v>
-      </c>
-      <c r="C166" s="34" t="s">
-        <v>2328</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B167" s="31" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B168" s="31" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C168" s="34" t="s">
         <v>2331</v>
-      </c>
-      <c r="C168" s="34" t="s">
-        <v>2333</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B169" s="31" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B170" s="31" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B171" s="31" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B172" s="31" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B173" s="31" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="D173" s="34" t="s">
-        <v>2555</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B174" s="31" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B175" s="31" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C175" s="34" t="s">
         <v>2337</v>
-      </c>
-      <c r="C175" s="34" t="s">
-        <v>2339</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B176" s="31" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B177" s="31" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B178" s="31" t="s">
-        <v>2465</v>
+        <v>2462</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B179" s="31" t="s">
-        <v>2466</v>
+        <v>2463</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B180" s="31" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B181" s="31" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B182" s="31" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B183" s="31" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B184" s="31" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B185" s="31" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C185" s="34" t="s">
         <v>2348</v>
-      </c>
-      <c r="C185" s="34" t="s">
-        <v>2350</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B186" s="31" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B187" s="31" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B188" s="31" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B189" s="31" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C189" s="34" t="s">
         <v>2353</v>
-      </c>
-      <c r="C189" s="34" t="s">
-        <v>2355</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B190" s="31" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B191" s="31" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B192" s="31" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C192" s="34" t="s">
         <v>2357</v>
-      </c>
-      <c r="C192" s="34" t="s">
-        <v>2359</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B193" s="31" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B194" s="31" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B195" s="31" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B196" s="31" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B197" s="31" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C197" s="34" t="s">
         <v>2362</v>
-      </c>
-      <c r="C197" s="34" t="s">
-        <v>2364</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B198" s="31" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B199" s="31" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B200" s="31" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B201" s="31" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B202" s="31" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C202" s="34" t="s">
         <v>2368</v>
-      </c>
-      <c r="C202" s="34" t="s">
-        <v>2370</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B203" s="31" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B204" s="31" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B205" s="31" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B206" s="31" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B207" s="31" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B208" s="31" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C208" s="34" t="s">
         <v>2375</v>
-      </c>
-      <c r="C208" s="34" t="s">
-        <v>2377</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B209" s="31" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B210" s="31" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B211" s="31" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B212" s="31" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C212" s="34" t="s">
         <v>2380</v>
-      </c>
-      <c r="C212" s="34" t="s">
-        <v>2382</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B213" s="31" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="C213" s="34" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B214" s="31" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="C214" s="34" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B215" s="31" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C215" s="34" t="s">
         <v>2384</v>
-      </c>
-      <c r="C215" s="34" t="s">
-        <v>2386</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B216" s="31" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="C216" s="34" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B217" s="31" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="C217" s="34" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B218" s="31" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="C218" s="34" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B219" s="31" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C219" s="34" t="s">
         <v>2395</v>
-      </c>
-      <c r="C219" s="34" t="s">
-        <v>2397</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B220" s="31" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="C220" s="34" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B221" s="31" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="C221" s="34" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B222" s="31" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="C222" s="34" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B223" s="31" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="C223" s="42" t="s">
-        <v>2440</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B224" s="31" t="s">
-        <v>2581</v>
+        <v>2576</v>
       </c>
       <c r="C224" s="34" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="225" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B225" s="31" t="s">
-        <v>2578</v>
+        <v>2573</v>
       </c>
       <c r="C225" s="34" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="226" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B226" s="31" t="s">
-        <v>2571</v>
+        <v>2566</v>
       </c>
       <c r="C226" s="34" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D226" s="34" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="227" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B227" s="31" t="s">
-        <v>2579</v>
+        <v>2574</v>
       </c>
       <c r="C227" s="34" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="228" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B228" s="31" t="s">
-        <v>2580</v>
+        <v>2575</v>
       </c>
       <c r="C228" s="34" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="229" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B229" s="31" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="C229" s="34" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="230" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B230" s="31" t="s">
+        <v>2403</v>
+      </c>
+      <c r="C230" s="34" t="s">
         <v>2405</v>
-      </c>
-      <c r="C230" s="34" t="s">
-        <v>2407</v>
       </c>
     </row>
     <row r="231" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B231" s="31" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="C231" s="34" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="232" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B232" s="31" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="C232" s="34" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="233" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B233" s="31" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="C233" s="34" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="234" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B234" s="31" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C234" s="34" t="s">
         <v>2409</v>
-      </c>
-      <c r="C234" s="34" t="s">
-        <v>2411</v>
       </c>
     </row>
     <row r="235" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B235" s="31" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="236" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B236" s="31" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="C236" s="34" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="237" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B237" s="31" t="s">
-        <v>2413</v>
+        <v>2411</v>
       </c>
       <c r="C237" s="34" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="238" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B238" s="31" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="C238" s="34" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="239" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B239" s="31" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C239" s="34" t="s">
         <v>2415</v>
-      </c>
-      <c r="C239" s="34" t="s">
-        <v>2417</v>
       </c>
     </row>
     <row r="240" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B240" s="31" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="C240" s="34" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B241" s="31" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="C241" s="34" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B242" s="31" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="C242" s="34" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B243" s="31" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="C243" s="34" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B244" s="31" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="C244" s="34" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B245" s="31" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="C245" s="34" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B246" s="31" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="C246" s="34" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B247" s="31" t="s">
+        <v>2425</v>
+      </c>
+      <c r="C247" s="34" t="s">
         <v>2427</v>
-      </c>
-      <c r="C247" s="34" t="s">
-        <v>2429</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B248" s="31" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="C248" s="34" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B249" s="31" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="C249" s="32" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B250" s="31" t="s">
-        <v>2520</v>
+        <v>2515</v>
       </c>
       <c r="C250" s="32" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B251" s="31" t="s">
-        <v>2521</v>
+        <v>2516</v>
       </c>
       <c r="C251" s="32" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B252" s="31" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="C252" s="32" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B253" s="31" t="s">
-        <v>2441</v>
+        <v>2438</v>
       </c>
       <c r="C253" s="34" t="s">
         <v>2077</v>
@@ -32360,7 +32483,7 @@
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B254" s="31" t="s">
-        <v>2442</v>
+        <v>2439</v>
       </c>
       <c r="C254" s="34" t="s">
         <v>2077</v>
@@ -32368,7 +32491,7 @@
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B255" s="31" t="s">
-        <v>2443</v>
+        <v>2440</v>
       </c>
       <c r="C255" s="34" t="s">
         <v>2077</v>
@@ -32376,7 +32499,7 @@
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B256" s="31" t="s">
-        <v>2444</v>
+        <v>2441</v>
       </c>
       <c r="C256" s="34" t="s">
         <v>2077</v>
@@ -32384,7 +32507,7 @@
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B257" s="31" t="s">
-        <v>2446</v>
+        <v>2443</v>
       </c>
       <c r="C257" s="34" t="s">
         <v>2076</v>
@@ -32392,7 +32515,7 @@
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B258" s="31" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="C258" s="32" t="s">
         <v>2085</v>
@@ -32400,7 +32523,7 @@
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B259" s="31" t="s">
-        <v>2448</v>
+        <v>2445</v>
       </c>
       <c r="C259" s="32" t="s">
         <v>2085</v>
@@ -32408,7 +32531,7 @@
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B260" s="31" t="s">
-        <v>2449</v>
+        <v>2446</v>
       </c>
       <c r="C260" s="32" t="s">
         <v>2085</v>
@@ -32416,175 +32539,175 @@
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B261" s="31" t="s">
-        <v>2450</v>
+        <v>2447</v>
       </c>
       <c r="C261" s="34" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B262" s="31" t="s">
-        <v>2451</v>
+        <v>2448</v>
       </c>
       <c r="C262" s="34" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B263" s="31" t="s">
-        <v>2452</v>
+        <v>2449</v>
       </c>
       <c r="C263" s="34" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B264" s="31" t="s">
-        <v>2453</v>
+        <v>2450</v>
       </c>
       <c r="C264" s="34" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B265" s="31" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C265" s="34" t="s">
         <v>2454</v>
-      </c>
-      <c r="C265" s="34" t="s">
-        <v>2457</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B266" s="31" t="s">
-        <v>2455</v>
+        <v>2452</v>
       </c>
       <c r="C266" s="34" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B267" s="31" t="s">
-        <v>2456</v>
+        <v>2453</v>
       </c>
       <c r="C267" s="34" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B268" s="31" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="C268" s="34" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B269" s="31" t="s">
-        <v>2458</v>
+        <v>2455</v>
       </c>
       <c r="C269" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B270" s="31" t="s">
-        <v>2459</v>
+        <v>2456</v>
       </c>
       <c r="C270" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B271" s="31" t="s">
-        <v>2460</v>
+        <v>2457</v>
       </c>
       <c r="C271" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B272" s="31" t="s">
-        <v>2461</v>
+        <v>2458</v>
       </c>
       <c r="C272" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B273" s="31" t="s">
-        <v>2462</v>
+        <v>2459</v>
       </c>
       <c r="C273" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B274" s="31" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="C274" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B275" s="31" t="s">
-        <v>2463</v>
+        <v>2460</v>
       </c>
       <c r="C275" s="34" t="s">
-        <v>2467</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B276" s="31" t="s">
+        <v>2461</v>
+      </c>
+      <c r="C276" s="34" t="s">
         <v>2464</v>
-      </c>
-      <c r="C276" s="34" t="s">
-        <v>2467</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B277" s="31" t="s">
-        <v>2468</v>
+        <v>2465</v>
       </c>
       <c r="C277" s="32" t="s">
-        <v>2445</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B278" s="31" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C278" s="32" t="s">
-        <v>2445</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B279" s="31" t="s">
-        <v>2469</v>
+        <v>2466</v>
       </c>
       <c r="C279" s="32" t="s">
-        <v>2445</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="280" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B280" s="31" t="s">
-        <v>2470</v>
+        <v>2467</v>
       </c>
       <c r="C280" s="34" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="281" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B281" s="31" t="s">
-        <v>2471</v>
+        <v>2468</v>
       </c>
       <c r="C281" s="34" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="282" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B282" s="31" t="s">
-        <v>2473</v>
+        <v>2470</v>
       </c>
       <c r="C282" s="32" t="s">
         <v>2070</v>
@@ -32592,7 +32715,7 @@
     </row>
     <row r="283" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B283" s="31" t="s">
-        <v>2474</v>
+        <v>2471</v>
       </c>
       <c r="C283" s="32" t="s">
         <v>2070</v>
@@ -32600,7 +32723,7 @@
     </row>
     <row r="284" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B284" s="31" t="s">
-        <v>2475</v>
+        <v>2472</v>
       </c>
       <c r="C284" s="32" t="s">
         <v>2070</v>
@@ -32608,146 +32731,146 @@
     </row>
     <row r="285" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B285" s="31" t="s">
-        <v>2476</v>
+        <v>2473</v>
       </c>
       <c r="C285" s="34" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="286" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B286" s="31" t="s">
-        <v>2477</v>
+        <v>2474</v>
       </c>
       <c r="C286" s="34" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="287" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B287" s="31" t="s">
-        <v>2556</v>
+        <v>2551</v>
       </c>
       <c r="C287" s="34" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="288" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B288" s="31" t="s">
-        <v>2557</v>
+        <v>2552</v>
       </c>
       <c r="C288" s="34" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="289" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B289" s="31" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="C289" s="34" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="290" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B290" s="31" t="s">
-        <v>2559</v>
+        <v>2554</v>
       </c>
       <c r="C290" s="32" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="291" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B291" s="31" t="s">
-        <v>2560</v>
+        <v>2555</v>
       </c>
       <c r="C291" s="34" t="s">
-        <v>2561</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="292" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B292" s="31" t="s">
-        <v>2562</v>
+        <v>2557</v>
       </c>
       <c r="C292" s="34" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="293" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B293" s="31" t="s">
-        <v>2563</v>
+        <v>2558</v>
       </c>
       <c r="C293" s="34" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="294" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B294" s="31" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="C294" s="34" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="295" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B295" s="31" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="C295" s="34" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="296" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B296" s="31" t="s">
-        <v>2564</v>
+        <v>2559</v>
       </c>
       <c r="C296" s="34" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="297" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B297" s="31" t="s">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="C297" s="34" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="298" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B298" s="31" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="C298" s="34" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="299" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B299" s="31" t="s">
-        <v>2567</v>
+        <v>2562</v>
       </c>
       <c r="C299" s="34" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="300" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B300" s="31" t="s">
-        <v>2568</v>
+        <v>2563</v>
       </c>
       <c r="C300" s="34" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="301" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B301" s="31" t="s">
-        <v>2570</v>
+        <v>2565</v>
       </c>
       <c r="C301" s="32" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="302" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B302" s="31" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="C302" s="34" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
     </row>
   </sheetData>
@@ -32917,19 +33040,49 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEDA90F-1F55-4F1D-8A87-9E5B8F59D731}">
-  <dimension ref="B2:C2"/>
+  <dimension ref="B2:D5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>2597</v>
+        <v>2592</v>
       </c>
       <c r="C2" t="s">
-        <v>2598</v>
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2778</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2788</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2326" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CE8E6DA-40A8-4906-993D-3BAE3253EFFC}"/>
+  <xr:revisionPtr revIDLastSave="2327" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C54C9753-355E-435F-BE27-1476202198B0}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="16770" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="13560" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -12799,13 +12799,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>桶?</t>
-    <rPh sb="0" eb="1">
-      <t>オケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>俚介</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -12820,6 +12813,10 @@
     <rPh sb="8" eb="9">
       <t>オウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[介]?</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -16949,7 +16946,7 @@
         <v>2488</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="E323" s="34" t="s">
         <v>2469</v>
@@ -16963,10 +16960,10 @@
         <v>296</v>
       </c>
       <c r="C324" t="s">
-        <v>2789</v>
+        <v>2791</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="E324" s="34" t="s">
         <v>2469</v>
@@ -19956,7 +19953,7 @@
       </c>
       <c r="W6" s="6" t="str">
         <f>_xlfn.XLOOKUP(V6,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v>桶?</v>
+        <v>[介]?</v>
       </c>
       <c r="X6" s="17" t="s">
         <v>297</v>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2327" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C54C9753-355E-435F-BE27-1476202198B0}"/>
+  <xr:revisionPtr revIDLastSave="2341" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F79736C8-AB42-4897-9221-53B918FBE929}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="13560" windowHeight="16305" tabRatio="668" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="13560" windowHeight="16305" tabRatio="668" activeTab="3" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="2792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="2796">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -12137,10 +12137,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>上亡</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -12579,10 +12575,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>儌乥举剪</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -12622,10 +12614,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>佤</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -12818,6 +12806,40 @@
   <si>
     <t>[介]?</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>卜</t>
+  </si>
+  <si>
+    <t>丸</t>
+  </si>
+  <si>
+    <t>気?</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>淑?</t>
+    <rPh sb="0" eb="1">
+      <t>シュク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>卜丸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>淑気</t>
+    <rPh sb="0" eb="2">
+      <t>シュクキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>_</t>
   </si>
 </sst>
 </file>
@@ -13481,10 +13503,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -13802,7 +13820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:J346"/>
+  <dimension ref="A1:J348"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -14479,7 +14497,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B81" s="1" t="s">
-        <v>2761</v>
+        <v>2758</v>
       </c>
       <c r="C81" t="s">
         <v>1577</v>
@@ -14815,7 +14833,7 @@
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="1" t="s">
-        <v>2757</v>
+        <v>2754</v>
       </c>
       <c r="C123" t="s">
         <v>1630</v>
@@ -14847,7 +14865,7 @@
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="1" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="C127" t="s">
         <v>1636</v>
@@ -14911,16 +14929,16 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B135" s="1" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="C135" s="55" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D135" s="33" t="s">
         <v>2712</v>
       </c>
-      <c r="D135" s="33" t="s">
+      <c r="E135" s="34" t="s">
         <v>2713</v>
-      </c>
-      <c r="E135" s="34" t="s">
-        <v>2714</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.4">
@@ -15077,7 +15095,7 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B155" s="1" t="s">
-        <v>2758</v>
+        <v>2755</v>
       </c>
       <c r="C155" t="s">
         <v>1433</v>
@@ -15327,7 +15345,7 @@
         <v>757</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="E181" s="34" t="s">
         <v>2094</v>
@@ -15336,7 +15354,7 @@
         <v>2092</v>
       </c>
       <c r="G181" s="34" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.4">
@@ -16088,16 +16106,16 @@
         <v>1938</v>
       </c>
       <c r="C251" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="E251" s="34" t="s">
         <v>2084</v>
       </c>
       <c r="F251" s="34" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.4">
@@ -16246,7 +16264,7 @@
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
-        <v>2756</v>
+        <v>2753</v>
       </c>
       <c r="C264" t="s">
         <v>1828</v>
@@ -16254,7 +16272,7 @@
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
       <c r="C265" t="s">
         <v>1829</v>
@@ -16290,7 +16308,7 @@
         <v>2084</v>
       </c>
       <c r="F268" s="34" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.4">
@@ -16373,7 +16391,7 @@
         <v>759</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="E278" s="34" t="s">
         <v>2064</v>
@@ -16598,7 +16616,7 @@
         <v>1953</v>
       </c>
       <c r="C299" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="D299" s="33" t="s">
         <v>2050</v>
@@ -16946,7 +16964,7 @@
         <v>2488</v>
       </c>
       <c r="D323" s="33" t="s">
-        <v>2789</v>
+        <v>2786</v>
       </c>
       <c r="E323" s="34" t="s">
         <v>2469</v>
@@ -16960,10 +16978,10 @@
         <v>296</v>
       </c>
       <c r="C324" t="s">
-        <v>2791</v>
+        <v>2788</v>
       </c>
       <c r="D324" s="33" t="s">
-        <v>2790</v>
+        <v>2787</v>
       </c>
       <c r="E324" s="34" t="s">
         <v>2469</v>
@@ -17014,10 +17032,10 @@
         <v>1990</v>
       </c>
       <c r="C327" t="s">
-        <v>2772</v>
+        <v>2769</v>
       </c>
       <c r="D327" s="33" t="s">
-        <v>2782</v>
+        <v>2779</v>
       </c>
       <c r="E327" s="34" t="s">
         <v>2069</v>
@@ -17074,10 +17092,10 @@
         <v>1102</v>
       </c>
       <c r="C331" t="s">
-        <v>2785</v>
+        <v>2782</v>
       </c>
       <c r="D331" s="33" t="s">
-        <v>2786</v>
+        <v>2783</v>
       </c>
       <c r="E331" s="42" t="s">
         <v>2437</v>
@@ -17086,7 +17104,7 @@
         <v>2544</v>
       </c>
       <c r="G331" s="32" t="s">
-        <v>2787</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="332" spans="2:7" x14ac:dyDescent="0.4">
@@ -17205,66 +17223,66 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B340" s="1" t="s">
+        <v>2698</v>
+      </c>
+      <c r="C340" t="s">
         <v>2699</v>
       </c>
-      <c r="C340" t="s">
+      <c r="D340" s="33" t="s">
         <v>2700</v>
       </c>
-      <c r="D340" s="33" t="s">
+      <c r="E340" s="34" t="s">
         <v>2701</v>
-      </c>
-      <c r="E340" s="34" t="s">
-        <v>2702</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B341" s="1" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C341" s="55" t="s">
         <v>2704</v>
       </c>
-      <c r="C341" s="55" t="s">
+      <c r="D341" s="33" t="s">
         <v>2705</v>
       </c>
-      <c r="D341" s="33" t="s">
-        <v>2706</v>
-      </c>
       <c r="E341" s="34" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B342" s="1" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C342" s="55" t="s">
         <v>2707</v>
       </c>
-      <c r="C342" s="55" t="s">
+      <c r="D342" s="33" t="s">
         <v>2708</v>
       </c>
-      <c r="D342" s="33" t="s">
-        <v>2709</v>
-      </c>
       <c r="E342" s="34" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B343" s="1" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C343" t="s">
         <v>2734</v>
       </c>
-      <c r="C343" t="s">
+      <c r="D343" s="33" t="s">
         <v>2735</v>
       </c>
-      <c r="D343" s="33" t="s">
+      <c r="E343" s="33" t="s">
         <v>2736</v>
-      </c>
-      <c r="E343" s="33" t="s">
-        <v>2737</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B344" s="1" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C344" t="s">
         <v>2738</v>
-      </c>
-      <c r="C344" t="s">
-        <v>2739</v>
       </c>
       <c r="D344" s="33" t="s">
         <v>2099</v>
@@ -17272,10 +17290,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B345" s="1" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C345" t="s">
         <v>2740</v>
-      </c>
-      <c r="C345" t="s">
-        <v>2741</v>
       </c>
       <c r="D345" s="33" t="s">
         <v>2099</v>
@@ -17284,6 +17302,22 @@
     <row r="346" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
         <v>1876</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B347" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C347" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B348" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C348" t="s">
+        <v>2791</v>
       </c>
     </row>
   </sheetData>
@@ -24985,7 +25019,7 @@
       </c>
       <c r="EI15" s="6" t="str">
         <f>_xlfn.XLOOKUP(EH15,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>淑?</v>
       </c>
       <c r="EJ15" s="7" t="s">
         <v>998</v>
@@ -26579,7 +26613,7 @@
       </c>
       <c r="G19" s="6" t="str">
         <f>_xlfn.XLOOKUP(F19,対応表!$B:$B,対応表!$C:$C," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>気?</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>1214</v>
@@ -28769,7 +28803,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36C5E931-1AEC-434D-81A1-3EA98DBB914E}">
-  <dimension ref="B1:F106"/>
+  <dimension ref="B1:F107"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.25" style="35" bestFit="1" customWidth="1"/>
@@ -28804,7 +28838,7 @@
         <v>2101</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>2102</v>
@@ -28821,7 +28855,7 @@
         <v>2210</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>2211</v>
@@ -28838,7 +28872,7 @@
         <v>2213</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E4" s="36" t="s">
         <v>2214</v>
@@ -28855,7 +28889,7 @@
         <v>2216</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>2217</v>
@@ -28872,7 +28906,7 @@
         <v>2219</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>2220</v>
@@ -28889,7 +28923,7 @@
         <v>2222</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E7" s="36" t="s">
         <v>2223</v>
@@ -28906,7 +28940,7 @@
         <v>2039</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>2225</v>
@@ -28923,7 +28957,7 @@
         <v>2227</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E9" s="36" t="s">
         <v>2228</v>
@@ -28940,7 +28974,7 @@
         <v>2037</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E10" s="36" t="s">
         <v>2230</v>
@@ -28957,7 +28991,7 @@
         <v>2232</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E11" s="36" t="s">
         <v>2233</v>
@@ -28974,7 +29008,7 @@
         <v>2235</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E12" s="40" t="s">
         <v>2233</v>
@@ -28991,7 +29025,7 @@
         <v>2041</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E13" s="36" t="s">
         <v>2233</v>
@@ -29008,7 +29042,7 @@
         <v>2315</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E14" s="36" t="s">
         <v>2233</v>
@@ -29025,7 +29059,7 @@
         <v>2385</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E15" s="36" t="s">
         <v>2233</v>
@@ -29042,7 +29076,7 @@
         <v>2388</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E16" s="36" t="s">
         <v>2233</v>
@@ -29059,7 +29093,7 @@
         <v>2389</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E17" s="36" t="s">
         <v>2233</v>
@@ -29076,7 +29110,7 @@
         <v>2391</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E18" s="36" t="s">
         <v>2233</v>
@@ -29093,7 +29127,7 @@
         <v>2432</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E19" s="36" t="s">
         <v>2433</v>
@@ -29110,7 +29144,7 @@
         <v>2497</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E20" s="36" t="s">
         <v>2233</v>
@@ -29127,7 +29161,7 @@
         <v>2500</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E21" s="36" t="s">
         <v>2501</v>
@@ -29144,7 +29178,7 @@
         <v>2503</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E22" s="36" t="s">
         <v>2504</v>
@@ -29161,7 +29195,7 @@
         <v>2506</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E23" s="36" t="s">
         <v>2225</v>
@@ -29178,7 +29212,7 @@
         <v>2508</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E24" s="36" t="s">
         <v>2233</v>
@@ -29195,7 +29229,7 @@
         <v>2510</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E25" s="36" t="s">
         <v>2233</v>
@@ -29212,7 +29246,7 @@
         <v>2512</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E26" s="36" t="s">
         <v>2513</v>
@@ -29229,7 +29263,7 @@
         <v>2519</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E27" s="36" t="s">
         <v>2531</v>
@@ -29246,7 +29280,7 @@
         <v>2521</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>2524</v>
@@ -29263,7 +29297,7 @@
         <v>2523</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E29" s="36" t="s">
         <v>2233</v>
@@ -29280,7 +29314,7 @@
         <v>2526</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E30" s="36" t="s">
         <v>2220</v>
@@ -29297,7 +29331,7 @@
         <v>2528</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E31" s="36" t="s">
         <v>2220</v>
@@ -29314,7 +29348,7 @@
         <v>2530</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E32" s="36" t="s">
         <v>2531</v>
@@ -29331,7 +29365,7 @@
         <v>2533</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E33" s="36" t="s">
         <v>2531</v>
@@ -29348,7 +29382,7 @@
         <v>2535</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>2233</v>
@@ -29365,7 +29399,7 @@
         <v>2568</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E35" s="36" t="s">
         <v>2233</v>
@@ -29382,7 +29416,7 @@
         <v>2585</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E36" s="36" t="s">
         <v>2233</v>
@@ -29416,7 +29450,7 @@
         <v>2589</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E38" s="36" t="s">
         <v>2233</v>
@@ -29433,7 +29467,7 @@
         <v>2590</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E39" s="36" t="s">
         <v>2233</v>
@@ -29450,7 +29484,7 @@
         <v>2591</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="E40" s="36" t="s">
         <v>2233</v>
@@ -29467,7 +29501,7 @@
         <v>2421</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F41" s="36" t="s">
         <v>2316</v>
@@ -29481,7 +29515,7 @@
         <v>2596</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F42" s="36" t="s">
         <v>2316</v>
@@ -29495,7 +29529,7 @@
         <v>2597</v>
       </c>
       <c r="D43" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F43" s="36" t="s">
         <v>2316</v>
@@ -29509,7 +29543,7 @@
         <v>2599</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F44" s="36" t="s">
         <v>2316</v>
@@ -29523,7 +29557,7 @@
         <v>2600</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F45" s="36" t="s">
         <v>2316</v>
@@ -29537,7 +29571,7 @@
         <v>2602</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F46" s="36" t="s">
         <v>2316</v>
@@ -29551,7 +29585,7 @@
         <v>2604</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F47" s="36" t="s">
         <v>2316</v>
@@ -29565,7 +29599,7 @@
         <v>2606</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F48" s="36" t="s">
         <v>2316</v>
@@ -29579,7 +29613,7 @@
         <v>2608</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F49" s="36" t="s">
         <v>2316</v>
@@ -29593,7 +29627,7 @@
         <v>2610</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F50" s="36" t="s">
         <v>2316</v>
@@ -29607,7 +29641,7 @@
         <v>2612</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F51" s="36" t="s">
         <v>2316</v>
@@ -29621,7 +29655,7 @@
         <v>2614</v>
       </c>
       <c r="D52" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F52" s="36" t="s">
         <v>2316</v>
@@ -29635,7 +29669,7 @@
         <v>2616</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F53" s="36" t="s">
         <v>2316</v>
@@ -29649,7 +29683,7 @@
         <v>2618</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F54" s="36" t="s">
         <v>2316</v>
@@ -29663,7 +29697,7 @@
         <v>2620</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F55" s="36" t="s">
         <v>2316</v>
@@ -29677,7 +29711,7 @@
         <v>2622</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F56" s="36" t="s">
         <v>2316</v>
@@ -29691,7 +29725,7 @@
         <v>2624</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F57" s="36" t="s">
         <v>2316</v>
@@ -29705,7 +29739,7 @@
         <v>2626</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F58" s="36" t="s">
         <v>2316</v>
@@ -29719,7 +29753,7 @@
         <v>2628</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F59" s="36" t="s">
         <v>2316</v>
@@ -29733,7 +29767,7 @@
         <v>2630</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F60" s="36" t="s">
         <v>2316</v>
@@ -29747,7 +29781,7 @@
         <v>2632</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F61" s="36" t="s">
         <v>2316</v>
@@ -29761,7 +29795,7 @@
         <v>2634</v>
       </c>
       <c r="D62" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F62" s="36" t="s">
         <v>2316</v>
@@ -29775,7 +29809,7 @@
         <v>2636</v>
       </c>
       <c r="D63" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F63" s="36" t="s">
         <v>2316</v>
@@ -29789,7 +29823,7 @@
         <v>2638</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F64" s="36" t="s">
         <v>2316</v>
@@ -29803,7 +29837,7 @@
         <v>2640</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F65" s="36" t="s">
         <v>2316</v>
@@ -29817,7 +29851,7 @@
         <v>2642</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F66" s="36" t="s">
         <v>2316</v>
@@ -29831,7 +29865,7 @@
         <v>2644</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F67" s="36" t="s">
         <v>2316</v>
@@ -29851,7 +29885,7 @@
         <v>2659</v>
       </c>
       <c r="F68" s="36" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.4">
@@ -29882,7 +29916,7 @@
         <v>2659</v>
       </c>
       <c r="F70" s="36" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.4">
@@ -29910,10 +29944,10 @@
         <v>2660</v>
       </c>
       <c r="E72" s="36" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="F72" s="36" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.4">
@@ -29946,13 +29980,13 @@
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B75" s="35" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="C75" s="36" t="s">
         <v>2667</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="F75" s="36" t="s">
         <v>2316</v>
@@ -29960,13 +29994,13 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B76" s="35" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C76" s="36" t="s">
         <v>2671</v>
       </c>
-      <c r="C76" s="36" t="s">
-        <v>2672</v>
-      </c>
       <c r="D76" s="36" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="F76" s="36" t="s">
         <v>2316</v>
@@ -29974,13 +30008,13 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B77" s="35" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C77" s="36" t="s">
         <v>2673</v>
       </c>
-      <c r="C77" s="36" t="s">
-        <v>2674</v>
-      </c>
       <c r="D77" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="F77" s="36" t="s">
         <v>2316</v>
@@ -29988,16 +30022,16 @@
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B78" s="35" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="C78" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E78" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="F78" s="36" t="s">
         <v>2316</v>
@@ -30005,16 +30039,16 @@
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B79" s="35" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E79" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="F79" s="36" t="s">
         <v>2316</v>
@@ -30022,16 +30056,16 @@
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B80" s="35" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="C80" s="36" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="D80" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E80" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="F80" s="36" t="s">
         <v>2316</v>
@@ -30039,16 +30073,16 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B81" s="35" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="C81" s="36" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E81" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="F81" s="36" t="s">
         <v>2316</v>
@@ -30056,16 +30090,16 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B82" s="35" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="C82" s="36" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E82" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="F82" s="36" t="s">
         <v>2316</v>
@@ -30073,16 +30107,16 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B83" s="35" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="C83" s="36" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E83" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="F83" s="36" t="s">
         <v>2316</v>
@@ -30090,75 +30124,75 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B84" s="39" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="C84" s="40" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="F84" s="40" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B85" s="35" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="C85" s="36" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E85" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B86" s="35" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="E86" s="36" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B87" s="35" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C87" s="36" t="s">
+        <v>2682</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>2795</v>
+      </c>
+      <c r="E87" s="36" t="s">
         <v>2694</v>
-      </c>
-      <c r="C87" s="36" t="s">
-        <v>2683</v>
-      </c>
-      <c r="D87" s="36" t="s">
-        <v>2668</v>
-      </c>
-      <c r="E87" s="36" t="s">
-        <v>2695</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B88" s="35" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="C88" s="36" t="s">
+        <v>2714</v>
+      </c>
+      <c r="D88" s="36" t="s">
         <v>2715</v>
       </c>
-      <c r="D88" s="36" t="s">
-        <v>2716</v>
-      </c>
       <c r="E88" s="36" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="F88" s="36" t="s">
         <v>2316</v>
@@ -30166,13 +30200,13 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B89" s="35" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C89" s="36" t="s">
         <v>2721</v>
       </c>
-      <c r="C89" s="36" t="s">
-        <v>2722</v>
-      </c>
       <c r="D89" s="36" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="F89" s="36" t="s">
         <v>2316</v>
@@ -30183,10 +30217,10 @@
         <v>1820</v>
       </c>
       <c r="C90" s="36" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="D90" s="36" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.4">
@@ -30194,10 +30228,10 @@
         <v>110</v>
       </c>
       <c r="C91" s="36" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.4">
@@ -30205,10 +30239,10 @@
         <v>1722</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="D92" s="36" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.4">
@@ -30216,10 +30250,10 @@
         <v>1937</v>
       </c>
       <c r="C93" s="36" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.4">
@@ -30227,21 +30261,21 @@
         <v>1144</v>
       </c>
       <c r="C94" s="36" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="D94" s="36" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B95" s="35" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C95" s="36" t="s">
         <v>2726</v>
       </c>
-      <c r="C95" s="36" t="s">
-        <v>2727</v>
-      </c>
       <c r="D95" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F95" s="36" t="s">
         <v>2316</v>
@@ -30249,13 +30283,13 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B96" s="35" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C96" s="36" t="s">
         <v>2728</v>
       </c>
-      <c r="C96" s="36" t="s">
-        <v>2729</v>
-      </c>
       <c r="D96" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F96" s="36" t="s">
         <v>2316</v>
@@ -30263,13 +30297,13 @@
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B97" s="35" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="C97" s="36" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>2668</v>
+        <v>2795</v>
       </c>
       <c r="F97" s="36" t="s">
         <v>2316</v>
@@ -30277,13 +30311,13 @@
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B98" s="35" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C98" s="36" t="s">
         <v>2746</v>
       </c>
-      <c r="C98" s="36" t="s">
-        <v>2747</v>
-      </c>
       <c r="D98" s="36" t="s">
-        <v>2748</v>
+        <v>2795</v>
       </c>
       <c r="F98" s="36" t="s">
         <v>2316</v>
@@ -30291,13 +30325,13 @@
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B99" s="35" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C99" s="36" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D99" s="36" t="s">
         <v>2749</v>
-      </c>
-      <c r="C99" s="36" t="s">
-        <v>2750</v>
-      </c>
-      <c r="D99" s="36" t="s">
-        <v>2751</v>
       </c>
       <c r="F99" s="36" t="s">
         <v>2316</v>
@@ -30305,13 +30339,13 @@
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B100" s="35" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="D100" s="36" t="s">
-        <v>2755</v>
+        <v>2795</v>
       </c>
       <c r="F100" s="36" t="s">
         <v>2316</v>
@@ -30319,13 +30353,13 @@
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B101" s="35" t="s">
-        <v>2759</v>
+        <v>2756</v>
       </c>
       <c r="C101" s="36" t="s">
-        <v>2760</v>
+        <v>2757</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>2755</v>
+        <v>2795</v>
       </c>
       <c r="F101" s="36" t="s">
         <v>2316</v>
@@ -30333,13 +30367,13 @@
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B102" s="35" t="s">
-        <v>2762</v>
+        <v>2759</v>
       </c>
       <c r="C102" s="36" t="s">
-        <v>2763</v>
+        <v>2760</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>2764</v>
+        <v>2761</v>
       </c>
       <c r="F102" s="36" t="s">
         <v>2316</v>
@@ -30347,13 +30381,13 @@
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B103" s="35" t="s">
-        <v>2765</v>
+        <v>2762</v>
       </c>
       <c r="C103" s="36" t="s">
-        <v>2766</v>
+        <v>2763</v>
       </c>
       <c r="D103" s="36" t="s">
-        <v>2767</v>
+        <v>2764</v>
       </c>
       <c r="F103" s="36" t="s">
         <v>2316</v>
@@ -30361,13 +30395,13 @@
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B104" s="35" t="s">
-        <v>2768</v>
+        <v>2765</v>
       </c>
       <c r="C104" s="36" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D104" s="36" t="s">
-        <v>2767</v>
+        <v>2764</v>
       </c>
       <c r="F104" s="36" t="s">
         <v>2316</v>
@@ -30375,13 +30409,13 @@
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B105" s="35" t="s">
-        <v>2770</v>
+        <v>2767</v>
       </c>
       <c r="C105" s="36" t="s">
-        <v>2771</v>
+        <v>2768</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>2755</v>
+        <v>2795</v>
       </c>
       <c r="F105" s="36" t="s">
         <v>2316</v>
@@ -30389,16 +30423,27 @@
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B106" s="35" t="s">
-        <v>2783</v>
+        <v>2780</v>
       </c>
       <c r="C106" s="36" t="s">
-        <v>2784</v>
+        <v>2781</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F106" s="36" t="s">
         <v>2316</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B107" s="35" t="s">
+        <v>2793</v>
+      </c>
+      <c r="C107" s="36" t="s">
+        <v>2794</v>
+      </c>
+      <c r="D107" s="36" t="s">
+        <v>2795</v>
       </c>
     </row>
   </sheetData>
@@ -32864,10 +32909,10 @@
     </row>
     <row r="302" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B302" s="31" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="C302" s="34" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
   </sheetData>
@@ -33054,32 +33099,32 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>2774</v>
+        <v>2771</v>
       </c>
       <c r="C3" t="s">
+        <v>2770</v>
+      </c>
+      <c r="D3" t="s">
         <v>2773</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2776</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C4" t="s">
         <v>2775</v>
       </c>
-      <c r="C4" t="s">
-        <v>2778</v>
-      </c>
       <c r="D4" t="s">
-        <v>2777</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>2779</v>
+        <v>2776</v>
       </c>
       <c r="C5" t="s">
-        <v>2788</v>
+        <v>2785</v>
       </c>
     </row>
   </sheetData>

--- a/桶文字対応表 from MAKU.xlsx
+++ b/桶文字対応表 from MAKU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C50243917C7CF35/okechika-henkan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2341" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F79736C8-AB42-4897-9221-53B918FBE929}"/>
+  <xr:revisionPtr revIDLastSave="2457" documentId="8_{D8CBA9BD-D283-4E9A-B411-3B84A074FC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86FBAF58-48E1-4CC9-AB95-ADB7ECA97BF5}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="13560" windowHeight="16305" tabRatio="668" activeTab="3" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="668" activeTab="4" xr2:uid="{9F16E5EF-0422-44C6-9445-EFA55A54836F}"/>
   </bookViews>
   <sheets>
     <sheet name="対応表" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="2796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="2835">
   <si>
     <t>ァ</t>
     <phoneticPr fontId="1"/>
@@ -7589,13 +7589,6 @@
     <t>乆</t>
   </si>
   <si>
-    <t>深?</t>
-    <rPh sb="0" eb="1">
-      <t>フカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>最</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -8065,13 +8058,6 @@
     <t>苦味</t>
     <rPh sb="0" eb="2">
       <t>ニガミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>深め</t>
-    <rPh sb="0" eb="1">
-      <t>フカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -12828,25 +12814,320 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>卜丸</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>淑気</t>
+    <t>_</t>
+  </si>
+  <si>
+    <t>丅</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>卜丸丅</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>淑気記</t>
     <rPh sb="0" eb="2">
       <t>シュクキ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>_</t>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シュクキギ　なのでは</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>淑気満つ？</t>
+    <rPh sb="0" eb="2">
+      <t>シュクキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>儳儴儵</t>
+  </si>
+  <si>
+    <t>恐○屋</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unicode表</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>齎す/齎戒</t>
+    <rPh sb="0" eb="1">
+      <t>モタラ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モタラ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>かけごえ+つぐない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灯す/灯？</t>
+    <rPh sb="0" eb="1">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>偬偭</t>
+  </si>
+  <si>
+    <t>価○</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乲乳</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>齎せ淑気満つ</t>
+  </si>
+  <si>
+    <t>勼</t>
+  </si>
+  <si>
+    <t>護?</t>
+    <rPh sb="0" eb="1">
+      <t>マモル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勽</t>
+  </si>
+  <si>
+    <t>神?</t>
+    <rPh sb="0" eb="1">
+      <t>カミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>儴</t>
+  </si>
+  <si>
+    <t>喝?</t>
+    <rPh sb="0" eb="1">
+      <t>カツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凲</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兀</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[凲]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[兀]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[伫]?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]?</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>守護神？</t>
+    <rPh sb="0" eb="3">
+      <t>シュゴシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>恐喝屋？</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我々の上に立つ凲兀</t>
+    <rPh sb="0" eb="2">
+      <t>ワレワレ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>侀</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伫</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兇</t>
+  </si>
+  <si>
+    <t>繋</t>
+    <rPh sb="0" eb="1">
+      <t>ツナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>よりふかい繋がり</t>
+    <rPh sb="5" eb="6">
+      <t>ツナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>守護神？が伫なら恐喝屋？は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>侀伫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>だ</t>
+    </r>
+    <rPh sb="0" eb="3">
+      <t>シュゴシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キョウカツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>介みず</t>
+    <rPh sb="0" eb="1">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強?</t>
+    <rPh sb="0" eb="1">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苦味？が強め</t>
+    <rPh sb="0" eb="2">
+      <t>ニガミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>怒</t>
+    <rPh sb="0" eb="1">
+      <t>オコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>摂</t>
+    <rPh sb="0" eb="1">
+      <t>セツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>販</t>
+    <rPh sb="0" eb="1">
+      <t>ハン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13123,6 +13404,20 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -13243,7 +13538,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -13412,12 +13707,54 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC1F0C8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -13820,11 +14157,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC662F-D86D-4637-B92E-2CD6E56E93FE}">
-  <dimension ref="A1:J348"/>
+  <dimension ref="A1:J356"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="4" max="4" width="28.125" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.875" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.375" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.375" style="31" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.125" style="31" bestFit="1" customWidth="1"/>
@@ -13842,25 +14179,25 @@
         <v>1561</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="E1" s="51" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F1" s="52" t="s">
         <v>2015</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="G1" s="52" t="s">
         <v>2016</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="H1" s="52" t="s">
         <v>2017</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="I1" s="52" t="s">
         <v>2018</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="J1" s="52" t="s">
         <v>2019</v>
-      </c>
-      <c r="J1" s="52" t="s">
-        <v>2020</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -14497,7 +14834,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B81" s="1" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
       <c r="C81" t="s">
         <v>1577</v>
@@ -14833,7 +15170,7 @@
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B123" s="1" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="C123" t="s">
         <v>1630</v>
@@ -14865,7 +15202,7 @@
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B127" s="1" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="C127" t="s">
         <v>1636</v>
@@ -14929,16 +15266,16 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B135" s="1" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
       <c r="C135" s="55" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D135" s="33" t="s">
+        <v>2710</v>
+      </c>
+      <c r="E135" s="34" t="s">
         <v>2711</v>
-      </c>
-      <c r="D135" s="33" t="s">
-        <v>2712</v>
-      </c>
-      <c r="E135" s="34" t="s">
-        <v>2713</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.4">
@@ -15095,7 +15432,7 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B155" s="1" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
       <c r="C155" t="s">
         <v>1433</v>
@@ -15133,16 +15470,16 @@
         <v>1683</v>
       </c>
       <c r="D159" s="33" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E159" s="34" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="F159" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="G159" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.4">
@@ -15150,7 +15487,7 @@
         <v>1684</v>
       </c>
       <c r="C160" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.4">
@@ -15158,7 +15495,7 @@
         <v>1685</v>
       </c>
       <c r="C161" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.4">
@@ -15177,10 +15514,10 @@
         <v>1688</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="E163" s="34" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.4">
@@ -15188,16 +15525,16 @@
         <v>1689</v>
       </c>
       <c r="C164" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="E164" s="34" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="F164" s="32" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.4">
@@ -15301,7 +15638,7 @@
         <v>1708</v>
       </c>
       <c r="C177" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.4">
@@ -15328,13 +15665,13 @@
         <v>1713</v>
       </c>
       <c r="D180" s="33" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="E180" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="F180" s="32" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.4">
@@ -15345,16 +15682,16 @@
         <v>757</v>
       </c>
       <c r="D181" s="33" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="E181" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F181" s="32" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="G181" s="34" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.4">
@@ -15378,16 +15715,16 @@
         <v>1917</v>
       </c>
       <c r="C184" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="E184" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.4">
@@ -15398,16 +15735,16 @@
         <v>1718</v>
       </c>
       <c r="D185" s="33" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="E185" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F185" s="34" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="G185" s="34" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.4">
@@ -15442,10 +15779,10 @@
         <v>1725</v>
       </c>
       <c r="D189" s="33" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="E189" s="34" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.4">
@@ -15480,7 +15817,7 @@
         <v>1731</v>
       </c>
       <c r="E193" s="34" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="194" spans="2:9" x14ac:dyDescent="0.4">
@@ -15491,22 +15828,22 @@
         <v>1966</v>
       </c>
       <c r="D194" s="33" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="E194" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="G194" s="32" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H194" s="32" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="I194" s="34" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="195" spans="2:9" x14ac:dyDescent="0.4">
@@ -15517,16 +15854,16 @@
         <v>1734</v>
       </c>
       <c r="D195" s="33" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="E195" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="F195" s="32" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="G195" s="32" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="196" spans="2:9" x14ac:dyDescent="0.4">
@@ -15537,10 +15874,10 @@
         <v>1736</v>
       </c>
       <c r="D196" s="33" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E196" s="34" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="197" spans="2:9" x14ac:dyDescent="0.4">
@@ -15556,16 +15893,16 @@
         <v>1921</v>
       </c>
       <c r="C198" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="D198" s="33" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="E198" s="34" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="F198" s="34" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="199" spans="2:9" x14ac:dyDescent="0.4">
@@ -15573,7 +15910,7 @@
         <v>1739</v>
       </c>
       <c r="C199" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="200" spans="2:9" x14ac:dyDescent="0.4">
@@ -15584,13 +15921,13 @@
         <v>1740</v>
       </c>
       <c r="D200" s="33" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E200" s="34" t="s">
+        <v>2085</v>
+      </c>
+      <c r="F200" s="32" t="s">
         <v>2087</v>
-      </c>
-      <c r="F200" s="32" t="s">
-        <v>2089</v>
       </c>
     </row>
     <row r="201" spans="2:9" x14ac:dyDescent="0.4">
@@ -15641,16 +15978,16 @@
         <v>1750</v>
       </c>
       <c r="D206" s="33" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E206" s="34" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="F206" s="34" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="G206" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="207" spans="2:9" x14ac:dyDescent="0.4">
@@ -15677,10 +16014,10 @@
         <v>1754</v>
       </c>
       <c r="D209" s="33" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E209" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.4">
@@ -15715,13 +16052,13 @@
         <v>1760</v>
       </c>
       <c r="D213" s="33" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="E213" s="34" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="F213" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.4">
@@ -15753,16 +16090,16 @@
         <v>1076</v>
       </c>
       <c r="C217" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="D217" s="33" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="E217" s="34" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="F217" s="32" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.4">
@@ -15789,10 +16126,10 @@
         <v>1768</v>
       </c>
       <c r="D220" s="33" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E220" s="34" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.4">
@@ -15840,7 +16177,7 @@
         <v>1776</v>
       </c>
       <c r="C226" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.4">
@@ -15872,7 +16209,7 @@
         <v>1782</v>
       </c>
       <c r="C230" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.4">
@@ -15891,10 +16228,10 @@
         <v>1786</v>
       </c>
       <c r="D232" s="33" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="E232" s="34" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.4">
@@ -15902,16 +16239,16 @@
         <v>1931</v>
       </c>
       <c r="C233" t="s">
+        <v>2545</v>
+      </c>
+      <c r="D233" s="33" t="s">
+        <v>2546</v>
+      </c>
+      <c r="E233" s="34" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F233" s="32" t="s">
         <v>2547</v>
-      </c>
-      <c r="D233" s="33" t="s">
-        <v>2548</v>
-      </c>
-      <c r="E233" s="34" t="s">
-        <v>2080</v>
-      </c>
-      <c r="F233" s="32" t="s">
-        <v>2549</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.4">
@@ -15919,7 +16256,7 @@
         <v>1787</v>
       </c>
       <c r="C234" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.4">
@@ -15954,10 +16291,10 @@
         <v>1794</v>
       </c>
       <c r="D238" s="33" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="E238" s="34" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.4">
@@ -15984,10 +16321,10 @@
         <v>1799</v>
       </c>
       <c r="D241" s="33" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.4">
@@ -15998,10 +16335,10 @@
         <v>1800</v>
       </c>
       <c r="D242" s="33" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.4">
@@ -16012,13 +16349,13 @@
         <v>1302</v>
       </c>
       <c r="D243" s="33" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="E243" s="34" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="F243" s="34" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.4">
@@ -16037,10 +16374,10 @@
         <v>1805</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.4">
@@ -16051,10 +16388,10 @@
         <v>1806</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.4">
@@ -16065,10 +16402,10 @@
         <v>1807</v>
       </c>
       <c r="D247" s="33" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E247" s="34" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.4">
@@ -16076,7 +16413,7 @@
         <v>1808</v>
       </c>
       <c r="C248" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.4">
@@ -16084,7 +16421,7 @@
         <v>1937</v>
       </c>
       <c r="C249" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.4">
@@ -16095,10 +16432,10 @@
         <v>1810</v>
       </c>
       <c r="D250" s="33" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="E250" s="34" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.4">
@@ -16106,16 +16443,16 @@
         <v>1938</v>
       </c>
       <c r="C251" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
       <c r="D251" s="33" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="E251" s="34" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="F251" s="34" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.4">
@@ -16142,10 +16479,10 @@
         <v>1815</v>
       </c>
       <c r="D254" s="33" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="E254" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.4">
@@ -16177,16 +16514,16 @@
         <v>1939</v>
       </c>
       <c r="C258" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="D258" s="33" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="E258" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="F258" s="32" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.4">
@@ -16202,16 +16539,16 @@
         <v>1940</v>
       </c>
       <c r="C260" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="D260" s="33" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="E260" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="F260" s="32" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.4">
@@ -16222,13 +16559,13 @@
         <v>416</v>
       </c>
       <c r="D261" s="33" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="E261" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="F261" s="32" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.4">
@@ -16236,16 +16573,16 @@
         <v>1825</v>
       </c>
       <c r="C262" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="D262" s="33" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="E262" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="F262" s="32" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.4">
@@ -16256,15 +16593,15 @@
         <v>1827</v>
       </c>
       <c r="D263" s="33" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E263" s="34" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="C264" t="s">
         <v>1828</v>
@@ -16272,7 +16609,7 @@
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
       <c r="C265" t="s">
         <v>1829</v>
@@ -16302,13 +16639,13 @@
         <v>1834</v>
       </c>
       <c r="D268" s="33" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="E268" s="34" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="F268" s="34" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.4">
@@ -16391,13 +16728,13 @@
         <v>759</v>
       </c>
       <c r="D278" s="33" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="E278" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="F278" s="34" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.4">
@@ -16408,10 +16745,10 @@
         <v>1853</v>
       </c>
       <c r="D279" s="33" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E279" s="42" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.4">
@@ -16422,10 +16759,10 @@
         <v>1855</v>
       </c>
       <c r="D280" s="41" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="E280" s="42" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.4">
@@ -16492,10 +16829,10 @@
         <v>1868</v>
       </c>
       <c r="D288" s="33" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="E288" s="34" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.4">
@@ -16530,13 +16867,13 @@
         <v>1960</v>
       </c>
       <c r="D292" s="33" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="E292" s="34" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="F292" s="32" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.4">
@@ -16544,16 +16881,16 @@
         <v>1946</v>
       </c>
       <c r="C293" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D293" s="33" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="E293" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="F293" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.4">
@@ -16561,16 +16898,16 @@
         <v>1947</v>
       </c>
       <c r="C294" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D294" s="33" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="E294" s="34" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="F294" s="34" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.4">
@@ -16578,7 +16915,7 @@
         <v>1948</v>
       </c>
       <c r="C295" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.4">
@@ -16589,7 +16926,7 @@
         <v>1951</v>
       </c>
       <c r="D296" s="33" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.4">
@@ -16600,7 +16937,7 @@
         <v>1952</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.4">
@@ -16616,16 +16953,16 @@
         <v>1953</v>
       </c>
       <c r="C299" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="D299" s="33" t="s">
-        <v>2050